--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10834" uniqueCount="4827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10835" uniqueCount="4827">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -50784,7 +50784,7 @@
         <v>4501</v>
       </c>
     </row>
-    <row r="2177" spans="1:6">
+    <row r="2177" spans="1:7">
       <c r="A2177" t="s">
         <v>2182</v>
       </c>
@@ -50798,7 +50798,7 @@
         <v>4637</v>
       </c>
     </row>
-    <row r="2178" spans="1:6">
+    <row r="2178" spans="1:7">
       <c r="A2178" t="s">
         <v>2183</v>
       </c>
@@ -50815,7 +50815,7 @@
         <v>4638</v>
       </c>
     </row>
-    <row r="2179" spans="1:6">
+    <row r="2179" spans="1:7">
       <c r="A2179" t="s">
         <v>2184</v>
       </c>
@@ -50832,7 +50832,7 @@
         <v>4639</v>
       </c>
     </row>
-    <row r="2180" spans="1:6">
+    <row r="2180" spans="1:7">
       <c r="A2180" t="s">
         <v>2185</v>
       </c>
@@ -50849,7 +50849,7 @@
         <v>4640</v>
       </c>
     </row>
-    <row r="2181" spans="1:6">
+    <row r="2181" spans="1:7">
       <c r="A2181" t="s">
         <v>2186</v>
       </c>
@@ -50863,7 +50863,7 @@
         <v>4641</v>
       </c>
     </row>
-    <row r="2182" spans="1:6">
+    <row r="2182" spans="1:7">
       <c r="A2182" t="s">
         <v>2187</v>
       </c>
@@ -50880,7 +50880,7 @@
         <v>4642</v>
       </c>
     </row>
-    <row r="2183" spans="1:6">
+    <row r="2183" spans="1:7">
       <c r="A2183" t="s">
         <v>2188</v>
       </c>
@@ -50897,7 +50897,7 @@
         <v>4643</v>
       </c>
     </row>
-    <row r="2184" spans="1:6">
+    <row r="2184" spans="1:7">
       <c r="A2184" t="s">
         <v>2189</v>
       </c>
@@ -50914,7 +50914,7 @@
         <v>4644</v>
       </c>
     </row>
-    <row r="2185" spans="1:6">
+    <row r="2185" spans="1:7">
       <c r="A2185" t="s">
         <v>2190</v>
       </c>
@@ -50930,8 +50930,11 @@
       <c r="E2185" t="s">
         <v>4645</v>
       </c>
-    </row>
-    <row r="2186" spans="1:6">
+      <c r="G2185" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:7">
       <c r="A2186" t="s">
         <v>2191</v>
       </c>
@@ -50948,7 +50951,7 @@
         <v>4646</v>
       </c>
     </row>
-    <row r="2187" spans="1:6">
+    <row r="2187" spans="1:7">
       <c r="A2187" t="s">
         <v>2192</v>
       </c>
@@ -50962,7 +50965,7 @@
         <v>4647</v>
       </c>
     </row>
-    <row r="2188" spans="1:6">
+    <row r="2188" spans="1:7">
       <c r="A2188" t="s">
         <v>2193</v>
       </c>
@@ -50976,7 +50979,7 @@
         <v>4648</v>
       </c>
     </row>
-    <row r="2189" spans="1:6">
+    <row r="2189" spans="1:7">
       <c r="A2189" t="s">
         <v>2194</v>
       </c>
@@ -50990,7 +50993,7 @@
         <v>4649</v>
       </c>
     </row>
-    <row r="2190" spans="1:6">
+    <row r="2190" spans="1:7">
       <c r="A2190" t="s">
         <v>2195</v>
       </c>
@@ -51004,7 +51007,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="2191" spans="1:6">
+    <row r="2191" spans="1:7">
       <c r="A2191" t="s">
         <v>2196</v>
       </c>
@@ -51021,7 +51024,7 @@
         <v>4816</v>
       </c>
     </row>
-    <row r="2192" spans="1:6">
+    <row r="2192" spans="1:7">
       <c r="A2192" t="s">
         <v>2197</v>
       </c>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10835" uniqueCount="4827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10857" uniqueCount="4827">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -48708,7 +48708,7 @@
         <v>4374</v>
       </c>
     </row>
-    <row r="2033" spans="1:4">
+    <row r="2033" spans="1:7">
       <c r="A2033" t="s">
         <v>2038</v>
       </c>
@@ -48722,7 +48722,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="2034" spans="1:4">
+    <row r="2034" spans="1:7">
       <c r="A2034" t="s">
         <v>2039</v>
       </c>
@@ -48736,7 +48736,7 @@
         <v>4376</v>
       </c>
     </row>
-    <row r="2035" spans="1:4">
+    <row r="2035" spans="1:7">
       <c r="A2035" t="s">
         <v>2040</v>
       </c>
@@ -48750,7 +48750,7 @@
         <v>4377</v>
       </c>
     </row>
-    <row r="2036" spans="1:4">
+    <row r="2036" spans="1:7">
       <c r="A2036" t="s">
         <v>2041</v>
       </c>
@@ -48764,7 +48764,7 @@
         <v>4378</v>
       </c>
     </row>
-    <row r="2037" spans="1:4">
+    <row r="2037" spans="1:7">
       <c r="A2037" t="s">
         <v>2042</v>
       </c>
@@ -48778,7 +48778,7 @@
         <v>4379</v>
       </c>
     </row>
-    <row r="2038" spans="1:4">
+    <row r="2038" spans="1:7">
       <c r="A2038" t="s">
         <v>2043</v>
       </c>
@@ -48792,7 +48792,7 @@
         <v>4380</v>
       </c>
     </row>
-    <row r="2039" spans="1:4">
+    <row r="2039" spans="1:7">
       <c r="A2039" t="s">
         <v>2044</v>
       </c>
@@ -48806,7 +48806,7 @@
         <v>4381</v>
       </c>
     </row>
-    <row r="2040" spans="1:4">
+    <row r="2040" spans="1:7">
       <c r="A2040" t="s">
         <v>2045</v>
       </c>
@@ -48820,7 +48820,7 @@
         <v>4382</v>
       </c>
     </row>
-    <row r="2041" spans="1:4">
+    <row r="2041" spans="1:7">
       <c r="A2041" t="s">
         <v>2046</v>
       </c>
@@ -48834,7 +48834,7 @@
         <v>4383</v>
       </c>
     </row>
-    <row r="2042" spans="1:4">
+    <row r="2042" spans="1:7">
       <c r="A2042" t="s">
         <v>2047</v>
       </c>
@@ -48848,7 +48848,7 @@
         <v>4384</v>
       </c>
     </row>
-    <row r="2043" spans="1:4">
+    <row r="2043" spans="1:7">
       <c r="A2043" t="s">
         <v>2048</v>
       </c>
@@ -48862,7 +48862,7 @@
         <v>4385</v>
       </c>
     </row>
-    <row r="2044" spans="1:4">
+    <row r="2044" spans="1:7">
       <c r="A2044" t="s">
         <v>2049</v>
       </c>
@@ -48876,7 +48876,7 @@
         <v>4386</v>
       </c>
     </row>
-    <row r="2045" spans="1:4">
+    <row r="2045" spans="1:7">
       <c r="A2045" t="s">
         <v>2050</v>
       </c>
@@ -48890,7 +48890,7 @@
         <v>4387</v>
       </c>
     </row>
-    <row r="2046" spans="1:4">
+    <row r="2046" spans="1:7">
       <c r="A2046" t="s">
         <v>2051</v>
       </c>
@@ -48904,7 +48904,7 @@
         <v>4388</v>
       </c>
     </row>
-    <row r="2047" spans="1:4">
+    <row r="2047" spans="1:7">
       <c r="A2047" t="s">
         <v>2052</v>
       </c>
@@ -48918,7 +48918,7 @@
         <v>4389</v>
       </c>
     </row>
-    <row r="2048" spans="1:4">
+    <row r="2048" spans="1:7">
       <c r="A2048" t="s">
         <v>2053</v>
       </c>
@@ -48931,8 +48931,11 @@
       <c r="D2048" t="s">
         <v>4390</v>
       </c>
-    </row>
-    <row r="2049" spans="1:4">
+      <c r="G2048" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2049" spans="1:7">
       <c r="A2049" t="s">
         <v>2054</v>
       </c>
@@ -48945,8 +48948,11 @@
       <c r="D2049" t="s">
         <v>4391</v>
       </c>
-    </row>
-    <row r="2050" spans="1:4">
+      <c r="G2049" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2050" spans="1:7">
       <c r="A2050" t="s">
         <v>2055</v>
       </c>
@@ -48959,8 +48965,11 @@
       <c r="D2050" t="s">
         <v>4392</v>
       </c>
-    </row>
-    <row r="2051" spans="1:4">
+      <c r="G2050" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2051" spans="1:7">
       <c r="A2051" t="s">
         <v>2056</v>
       </c>
@@ -48974,7 +48983,7 @@
         <v>4393</v>
       </c>
     </row>
-    <row r="2052" spans="1:4">
+    <row r="2052" spans="1:7">
       <c r="A2052" t="s">
         <v>2057</v>
       </c>
@@ -48988,7 +48997,7 @@
         <v>4394</v>
       </c>
     </row>
-    <row r="2053" spans="1:4">
+    <row r="2053" spans="1:7">
       <c r="A2053" t="s">
         <v>2058</v>
       </c>
@@ -49002,7 +49011,7 @@
         <v>4395</v>
       </c>
     </row>
-    <row r="2054" spans="1:4">
+    <row r="2054" spans="1:7">
       <c r="A2054" t="s">
         <v>2059</v>
       </c>
@@ -49016,7 +49025,7 @@
         <v>4319</v>
       </c>
     </row>
-    <row r="2055" spans="1:4">
+    <row r="2055" spans="1:7">
       <c r="A2055" t="s">
         <v>2060</v>
       </c>
@@ -49029,8 +49038,11 @@
       <c r="D2055" t="s">
         <v>4396</v>
       </c>
-    </row>
-    <row r="2056" spans="1:4">
+      <c r="G2055" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:7">
       <c r="A2056" t="s">
         <v>2061</v>
       </c>
@@ -49044,7 +49056,7 @@
         <v>4397</v>
       </c>
     </row>
-    <row r="2057" spans="1:4">
+    <row r="2057" spans="1:7">
       <c r="A2057" t="s">
         <v>2062</v>
       </c>
@@ -49058,7 +49070,7 @@
         <v>4343</v>
       </c>
     </row>
-    <row r="2058" spans="1:4">
+    <row r="2058" spans="1:7">
       <c r="A2058" t="s">
         <v>2063</v>
       </c>
@@ -49071,8 +49083,11 @@
       <c r="D2058" t="s">
         <v>4398</v>
       </c>
-    </row>
-    <row r="2059" spans="1:4">
+      <c r="G2058" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:7">
       <c r="A2059" t="s">
         <v>2064</v>
       </c>
@@ -49085,8 +49100,11 @@
       <c r="D2059" t="s">
         <v>4399</v>
       </c>
-    </row>
-    <row r="2060" spans="1:4">
+      <c r="G2059" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:7">
       <c r="A2060" t="s">
         <v>2065</v>
       </c>
@@ -49099,8 +49117,11 @@
       <c r="D2060" t="s">
         <v>4400</v>
       </c>
-    </row>
-    <row r="2061" spans="1:4">
+      <c r="G2060" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:7">
       <c r="A2061" t="s">
         <v>2066</v>
       </c>
@@ -49113,8 +49134,11 @@
       <c r="D2061" t="s">
         <v>4401</v>
       </c>
-    </row>
-    <row r="2062" spans="1:4">
+      <c r="G2061" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:7">
       <c r="A2062" t="s">
         <v>2067</v>
       </c>
@@ -49127,8 +49151,11 @@
       <c r="D2062" t="s">
         <v>4402</v>
       </c>
-    </row>
-    <row r="2063" spans="1:4">
+      <c r="G2062" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:7">
       <c r="A2063" t="s">
         <v>2068</v>
       </c>
@@ -49141,8 +49168,11 @@
       <c r="D2063" t="s">
         <v>4403</v>
       </c>
-    </row>
-    <row r="2064" spans="1:4">
+      <c r="G2063" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:7">
       <c r="A2064" t="s">
         <v>2069</v>
       </c>
@@ -49828,7 +49858,7 @@
         <v>4450</v>
       </c>
     </row>
-    <row r="2113" spans="1:4">
+    <row r="2113" spans="1:7">
       <c r="A2113" t="s">
         <v>2118</v>
       </c>
@@ -49842,7 +49872,7 @@
         <v>4451</v>
       </c>
     </row>
-    <row r="2114" spans="1:4">
+    <row r="2114" spans="1:7">
       <c r="A2114" t="s">
         <v>2119</v>
       </c>
@@ -49856,7 +49886,7 @@
         <v>4452</v>
       </c>
     </row>
-    <row r="2115" spans="1:4">
+    <row r="2115" spans="1:7">
       <c r="A2115" t="s">
         <v>2120</v>
       </c>
@@ -49870,7 +49900,7 @@
         <v>4453</v>
       </c>
     </row>
-    <row r="2116" spans="1:4">
+    <row r="2116" spans="1:7">
       <c r="A2116" t="s">
         <v>2121</v>
       </c>
@@ -49884,7 +49914,7 @@
         <v>4454</v>
       </c>
     </row>
-    <row r="2117" spans="1:4">
+    <row r="2117" spans="1:7">
       <c r="A2117" t="s">
         <v>2122</v>
       </c>
@@ -49898,7 +49928,7 @@
         <v>4455</v>
       </c>
     </row>
-    <row r="2118" spans="1:4">
+    <row r="2118" spans="1:7">
       <c r="A2118" t="s">
         <v>2123</v>
       </c>
@@ -49911,8 +49941,11 @@
       <c r="D2118" t="s">
         <v>4456</v>
       </c>
-    </row>
-    <row r="2119" spans="1:4">
+      <c r="G2118" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:7">
       <c r="A2119" t="s">
         <v>2124</v>
       </c>
@@ -49925,8 +49958,11 @@
       <c r="D2119" t="s">
         <v>4457</v>
       </c>
-    </row>
-    <row r="2120" spans="1:4">
+      <c r="G2119" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:7">
       <c r="A2120" t="s">
         <v>2125</v>
       </c>
@@ -49939,8 +49975,11 @@
       <c r="D2120" t="s">
         <v>4458</v>
       </c>
-    </row>
-    <row r="2121" spans="1:4">
+      <c r="G2120" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:7">
       <c r="A2121" t="s">
         <v>2126</v>
       </c>
@@ -49953,8 +49992,11 @@
       <c r="D2121" t="s">
         <v>4459</v>
       </c>
-    </row>
-    <row r="2122" spans="1:4">
+      <c r="G2121" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:7">
       <c r="A2122" t="s">
         <v>2127</v>
       </c>
@@ -49967,8 +50009,11 @@
       <c r="D2122" t="s">
         <v>4460</v>
       </c>
-    </row>
-    <row r="2123" spans="1:4">
+      <c r="G2122" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:7">
       <c r="A2123" t="s">
         <v>2128</v>
       </c>
@@ -49981,8 +50026,11 @@
       <c r="D2123" t="s">
         <v>4461</v>
       </c>
-    </row>
-    <row r="2124" spans="1:4">
+      <c r="G2123" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:7">
       <c r="A2124" t="s">
         <v>2129</v>
       </c>
@@ -49995,8 +50043,11 @@
       <c r="D2124" t="s">
         <v>4462</v>
       </c>
-    </row>
-    <row r="2125" spans="1:4">
+      <c r="G2124" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:7">
       <c r="A2125" t="s">
         <v>2130</v>
       </c>
@@ -50009,8 +50060,11 @@
       <c r="D2125" t="s">
         <v>4463</v>
       </c>
-    </row>
-    <row r="2126" spans="1:4">
+      <c r="G2125" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:7">
       <c r="A2126" t="s">
         <v>2131</v>
       </c>
@@ -50023,8 +50077,11 @@
       <c r="D2126" t="s">
         <v>4464</v>
       </c>
-    </row>
-    <row r="2127" spans="1:4">
+      <c r="G2126" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:7">
       <c r="A2127" t="s">
         <v>2132</v>
       </c>
@@ -50037,8 +50094,11 @@
       <c r="D2127" t="s">
         <v>4465</v>
       </c>
-    </row>
-    <row r="2128" spans="1:4">
+      <c r="G2127" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:7">
       <c r="A2128" t="s">
         <v>2133</v>
       </c>
@@ -50051,8 +50111,11 @@
       <c r="D2128" t="s">
         <v>4466</v>
       </c>
-    </row>
-    <row r="2129" spans="1:6">
+      <c r="G2128" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:7">
       <c r="A2129" t="s">
         <v>2134</v>
       </c>
@@ -50065,8 +50128,11 @@
       <c r="D2129" t="s">
         <v>4467</v>
       </c>
-    </row>
-    <row r="2130" spans="1:6">
+      <c r="G2129" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:7">
       <c r="A2130" t="s">
         <v>2135</v>
       </c>
@@ -50086,7 +50152,7 @@
         <v>4809</v>
       </c>
     </row>
-    <row r="2131" spans="1:6">
+    <row r="2131" spans="1:7">
       <c r="A2131" t="s">
         <v>2136</v>
       </c>
@@ -50103,7 +50169,7 @@
         <v>4615</v>
       </c>
     </row>
-    <row r="2132" spans="1:6">
+    <row r="2132" spans="1:7">
       <c r="A2132" t="s">
         <v>2137</v>
       </c>
@@ -50117,7 +50183,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2133" spans="1:6">
+    <row r="2133" spans="1:7">
       <c r="A2133" t="s">
         <v>2138</v>
       </c>
@@ -50131,7 +50197,7 @@
         <v>4470</v>
       </c>
     </row>
-    <row r="2134" spans="1:6">
+    <row r="2134" spans="1:7">
       <c r="A2134" t="s">
         <v>2139</v>
       </c>
@@ -50151,7 +50217,7 @@
         <v>4810</v>
       </c>
     </row>
-    <row r="2135" spans="1:6">
+    <row r="2135" spans="1:7">
       <c r="A2135" t="s">
         <v>2140</v>
       </c>
@@ -50165,7 +50231,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="2136" spans="1:6">
+    <row r="2136" spans="1:7">
       <c r="A2136" t="s">
         <v>2141</v>
       </c>
@@ -50179,7 +50245,7 @@
         <v>4473</v>
       </c>
     </row>
-    <row r="2137" spans="1:6">
+    <row r="2137" spans="1:7">
       <c r="A2137" t="s">
         <v>2142</v>
       </c>
@@ -50193,7 +50259,7 @@
         <v>4474</v>
       </c>
     </row>
-    <row r="2138" spans="1:6">
+    <row r="2138" spans="1:7">
       <c r="A2138" t="s">
         <v>2143</v>
       </c>
@@ -50207,7 +50273,7 @@
         <v>4475</v>
       </c>
     </row>
-    <row r="2139" spans="1:6">
+    <row r="2139" spans="1:7">
       <c r="A2139" t="s">
         <v>2144</v>
       </c>
@@ -50224,7 +50290,7 @@
         <v>4617</v>
       </c>
     </row>
-    <row r="2140" spans="1:6">
+    <row r="2140" spans="1:7">
       <c r="A2140" t="s">
         <v>2145</v>
       </c>
@@ -50244,7 +50310,7 @@
         <v>4811</v>
       </c>
     </row>
-    <row r="2141" spans="1:6">
+    <row r="2141" spans="1:7">
       <c r="A2141" t="s">
         <v>2146</v>
       </c>
@@ -50258,7 +50324,7 @@
         <v>4478</v>
       </c>
     </row>
-    <row r="2142" spans="1:6">
+    <row r="2142" spans="1:7">
       <c r="A2142" t="s">
         <v>2147</v>
       </c>
@@ -50272,7 +50338,7 @@
         <v>4619</v>
       </c>
     </row>
-    <row r="2143" spans="1:6">
+    <row r="2143" spans="1:7">
       <c r="A2143" t="s">
         <v>2148</v>
       </c>
@@ -50289,7 +50355,7 @@
         <v>4620</v>
       </c>
     </row>
-    <row r="2144" spans="1:6">
+    <row r="2144" spans="1:7">
       <c r="A2144" t="s">
         <v>2149</v>
       </c>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10857" uniqueCount="4826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10858" uniqueCount="4826">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -51013,6 +51013,9 @@
       <c r="E2186" t="s">
         <v>4645</v>
       </c>
+      <c r="G2186" t="s">
+        <v>4825</v>
+      </c>
     </row>
     <row r="2187" spans="1:7">
       <c r="A2187" t="s">

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10930" uniqueCount="4853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10942" uniqueCount="4853">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -14962,6 +14962,9 @@
       <c r="F2" t="s">
         <v>4697</v>
       </c>
+      <c r="G2" t="s">
+        <v>4852</v>
+      </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
@@ -14982,6 +14985,9 @@
       <c r="F3" t="s">
         <v>4697</v>
       </c>
+      <c r="G3" t="s">
+        <v>4852</v>
+      </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
@@ -15002,6 +15008,9 @@
       <c r="F4" t="s">
         <v>4697</v>
       </c>
+      <c r="G4" t="s">
+        <v>4852</v>
+      </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
@@ -15022,6 +15031,9 @@
       <c r="F5" t="s">
         <v>4697</v>
       </c>
+      <c r="G5" t="s">
+        <v>4852</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
@@ -15042,6 +15054,9 @@
       <c r="F6" t="s">
         <v>4697</v>
       </c>
+      <c r="G6" t="s">
+        <v>4852</v>
+      </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
@@ -15062,6 +15077,9 @@
       <c r="F7" t="s">
         <v>4697</v>
       </c>
+      <c r="G7" t="s">
+        <v>4852</v>
+      </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
@@ -15082,6 +15100,9 @@
       <c r="F8" t="s">
         <v>4697</v>
       </c>
+      <c r="G8" t="s">
+        <v>4852</v>
+      </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
@@ -15102,6 +15123,9 @@
       <c r="F9" t="s">
         <v>4697</v>
       </c>
+      <c r="G9" t="s">
+        <v>4852</v>
+      </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
@@ -15122,6 +15146,9 @@
       <c r="F10" t="s">
         <v>4697</v>
       </c>
+      <c r="G10" t="s">
+        <v>4852</v>
+      </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
@@ -15142,6 +15169,9 @@
       <c r="F11" t="s">
         <v>4697</v>
       </c>
+      <c r="G11" t="s">
+        <v>4852</v>
+      </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
@@ -15162,6 +15192,9 @@
       <c r="F12" t="s">
         <v>4697</v>
       </c>
+      <c r="G12" t="s">
+        <v>4852</v>
+      </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
@@ -15181,6 +15214,9 @@
       </c>
       <c r="F13" t="s">
         <v>4697</v>
+      </c>
+      <c r="G13" t="s">
+        <v>4852</v>
       </c>
     </row>
     <row r="14" spans="1:7">

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10942" uniqueCount="4853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10955" uniqueCount="4854">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -14573,6 +14573,9 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>SKIP</t>
   </si>
 </sst>
 </file>
@@ -49145,6 +49148,9 @@
       <c r="D2050" t="s">
         <v>4494</v>
       </c>
+      <c r="G2050" t="s">
+        <v>4853</v>
+      </c>
     </row>
     <row r="2051" spans="1:7">
       <c r="A2051" t="s">
@@ -49159,6 +49165,9 @@
       <c r="D2051" t="s">
         <v>4494</v>
       </c>
+      <c r="G2051" t="s">
+        <v>4853</v>
+      </c>
     </row>
     <row r="2052" spans="1:7">
       <c r="A2052" t="s">
@@ -49173,6 +49182,9 @@
       <c r="D2052" t="s">
         <v>4494</v>
       </c>
+      <c r="G2052" t="s">
+        <v>4853</v>
+      </c>
     </row>
     <row r="2053" spans="1:7">
       <c r="A2053" t="s">
@@ -49187,6 +49199,9 @@
       <c r="D2053" t="s">
         <v>4494</v>
       </c>
+      <c r="G2053" t="s">
+        <v>4853</v>
+      </c>
     </row>
     <row r="2054" spans="1:7">
       <c r="A2054" t="s">
@@ -49201,6 +49216,9 @@
       <c r="D2054" t="s">
         <v>4494</v>
       </c>
+      <c r="G2054" t="s">
+        <v>4853</v>
+      </c>
     </row>
     <row r="2055" spans="1:7">
       <c r="A2055" t="s">
@@ -49820,7 +49838,7 @@
         <v>4494</v>
       </c>
     </row>
-    <row r="2097" spans="1:4">
+    <row r="2097" spans="1:7">
       <c r="A2097" t="s">
         <v>2102</v>
       </c>
@@ -49834,7 +49852,7 @@
         <v>4494</v>
       </c>
     </row>
-    <row r="2098" spans="1:4">
+    <row r="2098" spans="1:7">
       <c r="A2098" t="s">
         <v>2103</v>
       </c>
@@ -49848,7 +49866,7 @@
         <v>4494</v>
       </c>
     </row>
-    <row r="2099" spans="1:4">
+    <row r="2099" spans="1:7">
       <c r="A2099" t="s">
         <v>2104</v>
       </c>
@@ -49862,7 +49880,7 @@
         <v>4494</v>
       </c>
     </row>
-    <row r="2100" spans="1:4">
+    <row r="2100" spans="1:7">
       <c r="A2100" t="s">
         <v>2105</v>
       </c>
@@ -49875,8 +49893,11 @@
       <c r="D2100" t="s">
         <v>4494</v>
       </c>
-    </row>
-    <row r="2101" spans="1:4">
+      <c r="G2100" t="s">
+        <v>4853</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:7">
       <c r="A2101" t="s">
         <v>2106</v>
       </c>
@@ -49889,8 +49910,11 @@
       <c r="D2101" t="s">
         <v>4494</v>
       </c>
-    </row>
-    <row r="2102" spans="1:4">
+      <c r="G2101" t="s">
+        <v>4853</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:7">
       <c r="A2102" t="s">
         <v>2107</v>
       </c>
@@ -49903,8 +49927,11 @@
       <c r="D2102" t="s">
         <v>4494</v>
       </c>
-    </row>
-    <row r="2103" spans="1:4">
+      <c r="G2102" t="s">
+        <v>4853</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:7">
       <c r="A2103" t="s">
         <v>2108</v>
       </c>
@@ -49917,8 +49944,11 @@
       <c r="D2103" t="s">
         <v>4494</v>
       </c>
-    </row>
-    <row r="2104" spans="1:4">
+      <c r="G2103" t="s">
+        <v>4853</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:7">
       <c r="A2104" t="s">
         <v>2109</v>
       </c>
@@ -49931,8 +49961,11 @@
       <c r="D2104" t="s">
         <v>4494</v>
       </c>
-    </row>
-    <row r="2105" spans="1:4">
+      <c r="G2104" t="s">
+        <v>4853</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:7">
       <c r="A2105" t="s">
         <v>2110</v>
       </c>
@@ -49945,8 +49978,11 @@
       <c r="D2105" t="s">
         <v>4494</v>
       </c>
-    </row>
-    <row r="2106" spans="1:4">
+      <c r="G2105" t="s">
+        <v>4853</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:7">
       <c r="A2106" t="s">
         <v>2111</v>
       </c>
@@ -49959,8 +49995,11 @@
       <c r="D2106" t="s">
         <v>4494</v>
       </c>
-    </row>
-    <row r="2107" spans="1:4">
+      <c r="G2106" t="s">
+        <v>4853</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:7">
       <c r="A2107" t="s">
         <v>2112</v>
       </c>
@@ -49973,8 +50012,11 @@
       <c r="D2107" t="s">
         <v>4494</v>
       </c>
-    </row>
-    <row r="2108" spans="1:4">
+      <c r="G2107" t="s">
+        <v>4853</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:7">
       <c r="A2108" t="s">
         <v>2113</v>
       </c>
@@ -49988,7 +50030,7 @@
         <v>4494</v>
       </c>
     </row>
-    <row r="2109" spans="1:4">
+    <row r="2109" spans="1:7">
       <c r="A2109" t="s">
         <v>2114</v>
       </c>
@@ -50002,7 +50044,7 @@
         <v>4494</v>
       </c>
     </row>
-    <row r="2110" spans="1:4">
+    <row r="2110" spans="1:7">
       <c r="A2110" t="s">
         <v>2115</v>
       </c>
@@ -50016,7 +50058,7 @@
         <v>4494</v>
       </c>
     </row>
-    <row r="2111" spans="1:4">
+    <row r="2111" spans="1:7">
       <c r="A2111" t="s">
         <v>2116</v>
       </c>
@@ -50030,7 +50072,7 @@
         <v>4494</v>
       </c>
     </row>
-    <row r="2112" spans="1:4">
+    <row r="2112" spans="1:7">
       <c r="A2112" t="s">
         <v>2117</v>
       </c>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10890" uniqueCount="4828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10955" uniqueCount="4828">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -48571,7 +48571,7 @@
         <v>4808</v>
       </c>
     </row>
-    <row r="2017" spans="1:6">
+    <row r="2017" spans="1:7">
       <c r="A2017" t="s">
         <v>2022</v>
       </c>
@@ -48591,7 +48591,7 @@
         <v>4809</v>
       </c>
     </row>
-    <row r="2018" spans="1:6">
+    <row r="2018" spans="1:7">
       <c r="A2018" t="s">
         <v>2023</v>
       </c>
@@ -48611,7 +48611,7 @@
         <v>4694</v>
       </c>
     </row>
-    <row r="2019" spans="1:6">
+    <row r="2019" spans="1:7">
       <c r="A2019" t="s">
         <v>2024</v>
       </c>
@@ -48631,7 +48631,7 @@
         <v>4700</v>
       </c>
     </row>
-    <row r="2020" spans="1:6">
+    <row r="2020" spans="1:7">
       <c r="A2020" t="s">
         <v>2025</v>
       </c>
@@ -48651,7 +48651,7 @@
         <v>4701</v>
       </c>
     </row>
-    <row r="2021" spans="1:6">
+    <row r="2021" spans="1:7">
       <c r="A2021" t="s">
         <v>2026</v>
       </c>
@@ -48665,7 +48665,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="2022" spans="1:6">
+    <row r="2022" spans="1:7">
       <c r="A2022" t="s">
         <v>2027</v>
       </c>
@@ -48679,7 +48679,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="2023" spans="1:6">
+    <row r="2023" spans="1:7">
       <c r="A2023" t="s">
         <v>2028</v>
       </c>
@@ -48693,7 +48693,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="2024" spans="1:6">
+    <row r="2024" spans="1:7">
       <c r="A2024" t="s">
         <v>2029</v>
       </c>
@@ -48707,7 +48707,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="2025" spans="1:6">
+    <row r="2025" spans="1:7">
       <c r="A2025" t="s">
         <v>2030</v>
       </c>
@@ -48721,7 +48721,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="2026" spans="1:6">
+    <row r="2026" spans="1:7">
       <c r="A2026" t="s">
         <v>2031</v>
       </c>
@@ -48734,8 +48734,11 @@
       <c r="D2026" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2027" spans="1:6">
+      <c r="G2026" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2027" spans="1:7">
       <c r="A2027" t="s">
         <v>2032</v>
       </c>
@@ -48748,8 +48751,11 @@
       <c r="D2027" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2028" spans="1:6">
+      <c r="G2027" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2028" spans="1:7">
       <c r="A2028" t="s">
         <v>2033</v>
       </c>
@@ -48762,8 +48768,11 @@
       <c r="D2028" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2029" spans="1:6">
+      <c r="G2028" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2029" spans="1:7">
       <c r="A2029" t="s">
         <v>2034</v>
       </c>
@@ -48776,8 +48785,11 @@
       <c r="D2029" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2030" spans="1:6">
+      <c r="G2029" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2030" spans="1:7">
       <c r="A2030" t="s">
         <v>2035</v>
       </c>
@@ -48790,8 +48802,11 @@
       <c r="D2030" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2031" spans="1:6">
+      <c r="G2030" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2031" spans="1:7">
       <c r="A2031" t="s">
         <v>2036</v>
       </c>
@@ -48804,8 +48819,11 @@
       <c r="D2031" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2032" spans="1:6">
+      <c r="G2031" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2032" spans="1:7">
       <c r="A2032" t="s">
         <v>2037</v>
       </c>
@@ -48818,8 +48836,11 @@
       <c r="D2032" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2033" spans="1:4">
+      <c r="G2032" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2033" spans="1:7">
       <c r="A2033" t="s">
         <v>2038</v>
       </c>
@@ -48832,8 +48853,11 @@
       <c r="D2033" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2034" spans="1:4">
+      <c r="G2033" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2034" spans="1:7">
       <c r="A2034" t="s">
         <v>2039</v>
       </c>
@@ -48846,8 +48870,11 @@
       <c r="D2034" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2035" spans="1:4">
+      <c r="G2034" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2035" spans="1:7">
       <c r="A2035" t="s">
         <v>2040</v>
       </c>
@@ -48860,8 +48887,11 @@
       <c r="D2035" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2036" spans="1:4">
+      <c r="G2035" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2036" spans="1:7">
       <c r="A2036" t="s">
         <v>2041</v>
       </c>
@@ -48874,8 +48904,11 @@
       <c r="D2036" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2037" spans="1:4">
+      <c r="G2036" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2037" spans="1:7">
       <c r="A2037" t="s">
         <v>2042</v>
       </c>
@@ -48888,8 +48921,11 @@
       <c r="D2037" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2038" spans="1:4">
+      <c r="G2037" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2038" spans="1:7">
       <c r="A2038" t="s">
         <v>2043</v>
       </c>
@@ -48902,8 +48938,11 @@
       <c r="D2038" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2039" spans="1:4">
+      <c r="G2038" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2039" spans="1:7">
       <c r="A2039" t="s">
         <v>2044</v>
       </c>
@@ -48916,8 +48955,11 @@
       <c r="D2039" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2040" spans="1:4">
+      <c r="G2039" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2040" spans="1:7">
       <c r="A2040" t="s">
         <v>2045</v>
       </c>
@@ -48930,8 +48972,11 @@
       <c r="D2040" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2041" spans="1:4">
+      <c r="G2040" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2041" spans="1:7">
       <c r="A2041" t="s">
         <v>2046</v>
       </c>
@@ -48944,8 +48989,11 @@
       <c r="D2041" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2042" spans="1:4">
+      <c r="G2041" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2042" spans="1:7">
       <c r="A2042" t="s">
         <v>2047</v>
       </c>
@@ -48958,8 +49006,11 @@
       <c r="D2042" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2043" spans="1:4">
+      <c r="G2042" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2043" spans="1:7">
       <c r="A2043" t="s">
         <v>2048</v>
       </c>
@@ -48973,7 +49024,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2044" spans="1:4">
+    <row r="2044" spans="1:7">
       <c r="A2044" t="s">
         <v>2049</v>
       </c>
@@ -48987,7 +49038,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2045" spans="1:4">
+    <row r="2045" spans="1:7">
       <c r="A2045" t="s">
         <v>2050</v>
       </c>
@@ -49001,7 +49052,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2046" spans="1:4">
+    <row r="2046" spans="1:7">
       <c r="A2046" t="s">
         <v>2051</v>
       </c>
@@ -49015,7 +49066,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2047" spans="1:4">
+    <row r="2047" spans="1:7">
       <c r="A2047" t="s">
         <v>2052</v>
       </c>
@@ -49029,7 +49080,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2048" spans="1:4">
+    <row r="2048" spans="1:7">
       <c r="A2048" t="s">
         <v>2053</v>
       </c>
@@ -49070,6 +49121,9 @@
       <c r="D2050" t="s">
         <v>4469</v>
       </c>
+      <c r="G2050" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2051" spans="1:7">
       <c r="A2051" t="s">
@@ -49084,6 +49138,9 @@
       <c r="D2051" t="s">
         <v>4469</v>
       </c>
+      <c r="G2051" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2052" spans="1:7">
       <c r="A2052" t="s">
@@ -49098,6 +49155,9 @@
       <c r="D2052" t="s">
         <v>4469</v>
       </c>
+      <c r="G2052" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2053" spans="1:7">
       <c r="A2053" t="s">
@@ -49112,6 +49172,9 @@
       <c r="D2053" t="s">
         <v>4469</v>
       </c>
+      <c r="G2053" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2054" spans="1:7">
       <c r="A2054" t="s">
@@ -49126,6 +49189,9 @@
       <c r="D2054" t="s">
         <v>4469</v>
       </c>
+      <c r="G2054" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2055" spans="1:7">
       <c r="A2055" t="s">
@@ -49205,6 +49271,9 @@
       <c r="D2059" t="s">
         <v>4469</v>
       </c>
+      <c r="G2059" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2060" spans="1:7">
       <c r="A2060" t="s">
@@ -49394,6 +49463,9 @@
       <c r="D2071" t="s">
         <v>4469</v>
       </c>
+      <c r="G2071" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2072" spans="1:7">
       <c r="A2072" t="s">
@@ -49408,6 +49480,9 @@
       <c r="D2072" t="s">
         <v>4469</v>
       </c>
+      <c r="G2072" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2073" spans="1:7">
       <c r="A2073" t="s">
@@ -49422,6 +49497,9 @@
       <c r="D2073" t="s">
         <v>4469</v>
       </c>
+      <c r="G2073" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2074" spans="1:7">
       <c r="A2074" t="s">
@@ -49436,6 +49514,9 @@
       <c r="D2074" t="s">
         <v>4469</v>
       </c>
+      <c r="G2074" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2075" spans="1:7">
       <c r="A2075" t="s">
@@ -49450,6 +49531,9 @@
       <c r="D2075" t="s">
         <v>4469</v>
       </c>
+      <c r="G2075" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2076" spans="1:7">
       <c r="A2076" t="s">
@@ -49464,6 +49548,9 @@
       <c r="D2076" t="s">
         <v>4469</v>
       </c>
+      <c r="G2076" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2077" spans="1:7">
       <c r="A2077" t="s">
@@ -49478,6 +49565,9 @@
       <c r="D2077" t="s">
         <v>4469</v>
       </c>
+      <c r="G2077" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2078" spans="1:7">
       <c r="A2078" t="s">
@@ -49492,6 +49582,9 @@
       <c r="D2078" t="s">
         <v>4469</v>
       </c>
+      <c r="G2078" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2079" spans="1:7">
       <c r="A2079" t="s">
@@ -49506,6 +49599,9 @@
       <c r="D2079" t="s">
         <v>4469</v>
       </c>
+      <c r="G2079" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2080" spans="1:7">
       <c r="A2080" t="s">
@@ -49520,8 +49616,11 @@
       <c r="D2080" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2081" spans="1:4">
+      <c r="G2080" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:7">
       <c r="A2081" t="s">
         <v>2086</v>
       </c>
@@ -49534,8 +49633,11 @@
       <c r="D2081" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2082" spans="1:4">
+      <c r="G2081" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:7">
       <c r="A2082" t="s">
         <v>2087</v>
       </c>
@@ -49548,8 +49650,11 @@
       <c r="D2082" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2083" spans="1:4">
+      <c r="G2082" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:7">
       <c r="A2083" t="s">
         <v>2088</v>
       </c>
@@ -49562,8 +49667,11 @@
       <c r="D2083" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2084" spans="1:4">
+      <c r="G2083" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:7">
       <c r="A2084" t="s">
         <v>2089</v>
       </c>
@@ -49576,8 +49684,11 @@
       <c r="D2084" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2085" spans="1:4">
+      <c r="G2084" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:7">
       <c r="A2085" t="s">
         <v>2090</v>
       </c>
@@ -49591,7 +49702,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2086" spans="1:4">
+    <row r="2086" spans="1:7">
       <c r="A2086" t="s">
         <v>2091</v>
       </c>
@@ -49605,7 +49716,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2087" spans="1:4">
+    <row r="2087" spans="1:7">
       <c r="A2087" t="s">
         <v>2092</v>
       </c>
@@ -49619,7 +49730,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2088" spans="1:4">
+    <row r="2088" spans="1:7">
       <c r="A2088" t="s">
         <v>2093</v>
       </c>
@@ -49633,7 +49744,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2089" spans="1:4">
+    <row r="2089" spans="1:7">
       <c r="A2089" t="s">
         <v>2094</v>
       </c>
@@ -49647,7 +49758,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2090" spans="1:4">
+    <row r="2090" spans="1:7">
       <c r="A2090" t="s">
         <v>2095</v>
       </c>
@@ -49661,7 +49772,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2091" spans="1:4">
+    <row r="2091" spans="1:7">
       <c r="A2091" t="s">
         <v>2096</v>
       </c>
@@ -49675,7 +49786,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2092" spans="1:4">
+    <row r="2092" spans="1:7">
       <c r="A2092" t="s">
         <v>2097</v>
       </c>
@@ -49689,7 +49800,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2093" spans="1:4">
+    <row r="2093" spans="1:7">
       <c r="A2093" t="s">
         <v>2098</v>
       </c>
@@ -49703,7 +49814,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2094" spans="1:4">
+    <row r="2094" spans="1:7">
       <c r="A2094" t="s">
         <v>2099</v>
       </c>
@@ -49717,7 +49828,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2095" spans="1:4">
+    <row r="2095" spans="1:7">
       <c r="A2095" t="s">
         <v>2100</v>
       </c>
@@ -49730,8 +49841,11 @@
       <c r="D2095" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2096" spans="1:4">
+      <c r="G2095" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:7">
       <c r="A2096" t="s">
         <v>2101</v>
       </c>
@@ -49744,8 +49858,11 @@
       <c r="D2096" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2097" spans="1:4">
+      <c r="G2096" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:7">
       <c r="A2097" t="s">
         <v>2102</v>
       </c>
@@ -49758,8 +49875,11 @@
       <c r="D2097" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2098" spans="1:4">
+      <c r="G2097" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:7">
       <c r="A2098" t="s">
         <v>2103</v>
       </c>
@@ -49772,8 +49892,11 @@
       <c r="D2098" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2099" spans="1:4">
+      <c r="G2098" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:7">
       <c r="A2099" t="s">
         <v>2104</v>
       </c>
@@ -49786,8 +49909,11 @@
       <c r="D2099" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2100" spans="1:4">
+      <c r="G2099" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:7">
       <c r="A2100" t="s">
         <v>2105</v>
       </c>
@@ -49801,7 +49927,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2101" spans="1:4">
+    <row r="2101" spans="1:7">
       <c r="A2101" t="s">
         <v>2106</v>
       </c>
@@ -49815,7 +49941,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2102" spans="1:4">
+    <row r="2102" spans="1:7">
       <c r="A2102" t="s">
         <v>2107</v>
       </c>
@@ -49829,7 +49955,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2103" spans="1:4">
+    <row r="2103" spans="1:7">
       <c r="A2103" t="s">
         <v>2108</v>
       </c>
@@ -49843,7 +49969,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2104" spans="1:4">
+    <row r="2104" spans="1:7">
       <c r="A2104" t="s">
         <v>2109</v>
       </c>
@@ -49857,7 +49983,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2105" spans="1:4">
+    <row r="2105" spans="1:7">
       <c r="A2105" t="s">
         <v>2110</v>
       </c>
@@ -49871,7 +49997,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2106" spans="1:4">
+    <row r="2106" spans="1:7">
       <c r="A2106" t="s">
         <v>2111</v>
       </c>
@@ -49885,7 +50011,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2107" spans="1:4">
+    <row r="2107" spans="1:7">
       <c r="A2107" t="s">
         <v>2112</v>
       </c>
@@ -49899,7 +50025,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2108" spans="1:4">
+    <row r="2108" spans="1:7">
       <c r="A2108" t="s">
         <v>2113</v>
       </c>
@@ -49913,7 +50039,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2109" spans="1:4">
+    <row r="2109" spans="1:7">
       <c r="A2109" t="s">
         <v>2114</v>
       </c>
@@ -49927,7 +50053,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2110" spans="1:4">
+    <row r="2110" spans="1:7">
       <c r="A2110" t="s">
         <v>2115</v>
       </c>
@@ -49941,7 +50067,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2111" spans="1:4">
+    <row r="2111" spans="1:7">
       <c r="A2111" t="s">
         <v>2116</v>
       </c>
@@ -49955,7 +50081,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2112" spans="1:4">
+    <row r="2112" spans="1:7">
       <c r="A2112" t="s">
         <v>2117</v>
       </c>
@@ -50229,7 +50355,7 @@
         <v>4827</v>
       </c>
     </row>
-    <row r="2129" spans="1:6">
+    <row r="2129" spans="1:7">
       <c r="A2129" t="s">
         <v>2134</v>
       </c>
@@ -50248,8 +50374,11 @@
       <c r="F2129" t="s">
         <v>4810</v>
       </c>
-    </row>
-    <row r="2130" spans="1:6">
+      <c r="G2129" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:7">
       <c r="A2130" t="s">
         <v>2135</v>
       </c>
@@ -50266,7 +50395,7 @@
         <v>4615</v>
       </c>
     </row>
-    <row r="2131" spans="1:6">
+    <row r="2131" spans="1:7">
       <c r="A2131" t="s">
         <v>2136</v>
       </c>
@@ -50280,7 +50409,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2132" spans="1:6">
+    <row r="2132" spans="1:7">
       <c r="A2132" t="s">
         <v>2137</v>
       </c>
@@ -50294,7 +50423,7 @@
         <v>4505</v>
       </c>
     </row>
-    <row r="2133" spans="1:6">
+    <row r="2133" spans="1:7">
       <c r="A2133" t="s">
         <v>2138</v>
       </c>
@@ -50314,7 +50443,7 @@
         <v>4811</v>
       </c>
     </row>
-    <row r="2134" spans="1:6">
+    <row r="2134" spans="1:7">
       <c r="A2134" t="s">
         <v>2139</v>
       </c>
@@ -50328,7 +50457,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2135" spans="1:6">
+    <row r="2135" spans="1:7">
       <c r="A2135" t="s">
         <v>2140</v>
       </c>
@@ -50342,7 +50471,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2136" spans="1:6">
+    <row r="2136" spans="1:7">
       <c r="A2136" t="s">
         <v>2141</v>
       </c>
@@ -50356,7 +50485,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2137" spans="1:6">
+    <row r="2137" spans="1:7">
       <c r="A2137" t="s">
         <v>2142</v>
       </c>
@@ -50370,7 +50499,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2138" spans="1:6">
+    <row r="2138" spans="1:7">
       <c r="A2138" t="s">
         <v>2143</v>
       </c>
@@ -50387,7 +50516,7 @@
         <v>4617</v>
       </c>
     </row>
-    <row r="2139" spans="1:6">
+    <row r="2139" spans="1:7">
       <c r="A2139" t="s">
         <v>2144</v>
       </c>
@@ -50407,7 +50536,7 @@
         <v>4812</v>
       </c>
     </row>
-    <row r="2140" spans="1:6">
+    <row r="2140" spans="1:7">
       <c r="A2140" t="s">
         <v>2145</v>
       </c>
@@ -50421,7 +50550,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2141" spans="1:6">
+    <row r="2141" spans="1:7">
       <c r="A2141" t="s">
         <v>2146</v>
       </c>
@@ -50435,7 +50564,7 @@
         <v>4619</v>
       </c>
     </row>
-    <row r="2142" spans="1:6">
+    <row r="2142" spans="1:7">
       <c r="A2142" t="s">
         <v>2147</v>
       </c>
@@ -50452,7 +50581,7 @@
         <v>4620</v>
       </c>
     </row>
-    <row r="2143" spans="1:6">
+    <row r="2143" spans="1:7">
       <c r="A2143" t="s">
         <v>2148</v>
       </c>
@@ -50469,7 +50598,7 @@
         <v>4621</v>
       </c>
     </row>
-    <row r="2144" spans="1:6">
+    <row r="2144" spans="1:7">
       <c r="A2144" t="s">
         <v>2149</v>
       </c>
@@ -50480,7 +50609,7 @@
         <v>4511</v>
       </c>
     </row>
-    <row r="2145" spans="1:6">
+    <row r="2145" spans="1:7">
       <c r="A2145" t="s">
         <v>2150</v>
       </c>
@@ -50491,7 +50620,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2146" spans="1:6">
+    <row r="2146" spans="1:7">
       <c r="A2146" t="s">
         <v>2151</v>
       </c>
@@ -50505,7 +50634,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2147" spans="1:6">
+    <row r="2147" spans="1:7">
       <c r="A2147" t="s">
         <v>2152</v>
       </c>
@@ -50519,7 +50648,7 @@
         <v>4508</v>
       </c>
     </row>
-    <row r="2148" spans="1:6">
+    <row r="2148" spans="1:7">
       <c r="A2148" t="s">
         <v>2153</v>
       </c>
@@ -50530,7 +50659,7 @@
         <v>4512</v>
       </c>
     </row>
-    <row r="2149" spans="1:6">
+    <row r="2149" spans="1:7">
       <c r="A2149" t="s">
         <v>2154</v>
       </c>
@@ -50541,7 +50670,7 @@
         <v>4513</v>
       </c>
     </row>
-    <row r="2150" spans="1:6">
+    <row r="2150" spans="1:7">
       <c r="A2150" t="s">
         <v>2155</v>
       </c>
@@ -50552,7 +50681,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2151" spans="1:6">
+    <row r="2151" spans="1:7">
       <c r="A2151" t="s">
         <v>2156</v>
       </c>
@@ -50565,8 +50694,11 @@
       <c r="D2151" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2152" spans="1:6">
+      <c r="G2151" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:7">
       <c r="A2152" t="s">
         <v>2157</v>
       </c>
@@ -50586,7 +50718,7 @@
         <v>4813</v>
       </c>
     </row>
-    <row r="2153" spans="1:6">
+    <row r="2153" spans="1:7">
       <c r="A2153" t="s">
         <v>2158</v>
       </c>
@@ -50600,7 +50732,7 @@
         <v>4514</v>
       </c>
     </row>
-    <row r="2154" spans="1:6">
+    <row r="2154" spans="1:7">
       <c r="A2154" t="s">
         <v>2159</v>
       </c>
@@ -50614,7 +50746,7 @@
         <v>4512</v>
       </c>
     </row>
-    <row r="2155" spans="1:6">
+    <row r="2155" spans="1:7">
       <c r="A2155" t="s">
         <v>2160</v>
       </c>
@@ -50628,7 +50760,7 @@
         <v>4623</v>
       </c>
     </row>
-    <row r="2156" spans="1:6">
+    <row r="2156" spans="1:7">
       <c r="A2156" t="s">
         <v>2161</v>
       </c>
@@ -50639,7 +50771,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2157" spans="1:6">
+    <row r="2157" spans="1:7">
       <c r="A2157" t="s">
         <v>2162</v>
       </c>
@@ -50650,7 +50782,7 @@
         <v>4516</v>
       </c>
     </row>
-    <row r="2158" spans="1:6">
+    <row r="2158" spans="1:7">
       <c r="A2158" t="s">
         <v>2163</v>
       </c>
@@ -50667,7 +50799,7 @@
         <v>4814</v>
       </c>
     </row>
-    <row r="2159" spans="1:6">
+    <row r="2159" spans="1:7">
       <c r="A2159" t="s">
         <v>2164</v>
       </c>
@@ -50687,7 +50819,7 @@
         <v>4815</v>
       </c>
     </row>
-    <row r="2160" spans="1:6">
+    <row r="2160" spans="1:7">
       <c r="A2160" t="s">
         <v>2165</v>
       </c>
@@ -51218,7 +51350,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2193" spans="1:6">
+    <row r="2193" spans="1:7">
       <c r="A2193" t="s">
         <v>2198</v>
       </c>
@@ -51229,7 +51361,7 @@
         <v>4528</v>
       </c>
     </row>
-    <row r="2194" spans="1:6">
+    <row r="2194" spans="1:7">
       <c r="A2194" t="s">
         <v>2199</v>
       </c>
@@ -51240,7 +51372,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2195" spans="1:6">
+    <row r="2195" spans="1:7">
       <c r="A2195" t="s">
         <v>2200</v>
       </c>
@@ -51260,7 +51392,7 @@
         <v>4819</v>
       </c>
     </row>
-    <row r="2196" spans="1:6">
+    <row r="2196" spans="1:7">
       <c r="A2196" t="s">
         <v>2201</v>
       </c>
@@ -51271,7 +51403,7 @@
         <v>4529</v>
       </c>
     </row>
-    <row r="2197" spans="1:6">
+    <row r="2197" spans="1:7">
       <c r="A2197" t="s">
         <v>2202</v>
       </c>
@@ -51282,7 +51414,7 @@
         <v>4530</v>
       </c>
     </row>
-    <row r="2198" spans="1:6">
+    <row r="2198" spans="1:7">
       <c r="A2198" t="s">
         <v>2203</v>
       </c>
@@ -51293,7 +51425,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2199" spans="1:6">
+    <row r="2199" spans="1:7">
       <c r="A2199" t="s">
         <v>2204</v>
       </c>
@@ -51309,8 +51441,11 @@
       <c r="E2199" t="s">
         <v>4651</v>
       </c>
-    </row>
-    <row r="2200" spans="1:6">
+      <c r="G2199" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:7">
       <c r="A2200" t="s">
         <v>2205</v>
       </c>
@@ -51326,8 +51461,11 @@
       <c r="F2200" t="s">
         <v>4820</v>
       </c>
-    </row>
-    <row r="2201" spans="1:6">
+      <c r="G2200" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:7">
       <c r="A2201" t="s">
         <v>2206</v>
       </c>
@@ -51338,7 +51476,7 @@
         <v>4530</v>
       </c>
     </row>
-    <row r="2202" spans="1:6">
+    <row r="2202" spans="1:7">
       <c r="A2202" t="s">
         <v>2207</v>
       </c>
@@ -51352,7 +51490,7 @@
         <v>4821</v>
       </c>
     </row>
-    <row r="2203" spans="1:6">
+    <row r="2203" spans="1:7">
       <c r="A2203" t="s">
         <v>2208</v>
       </c>
@@ -51366,7 +51504,7 @@
         <v>4652</v>
       </c>
     </row>
-    <row r="2204" spans="1:6">
+    <row r="2204" spans="1:7">
       <c r="A2204" t="s">
         <v>2209</v>
       </c>
@@ -51380,7 +51518,7 @@
         <v>4653</v>
       </c>
     </row>
-    <row r="2205" spans="1:6">
+    <row r="2205" spans="1:7">
       <c r="A2205" t="s">
         <v>2210</v>
       </c>
@@ -51394,7 +51532,7 @@
         <v>4654</v>
       </c>
     </row>
-    <row r="2206" spans="1:6">
+    <row r="2206" spans="1:7">
       <c r="A2206" t="s">
         <v>2211</v>
       </c>
@@ -51408,7 +51546,7 @@
         <v>4655</v>
       </c>
     </row>
-    <row r="2207" spans="1:6">
+    <row r="2207" spans="1:7">
       <c r="A2207" t="s">
         <v>2212</v>
       </c>
@@ -51422,7 +51560,7 @@
         <v>4656</v>
       </c>
     </row>
-    <row r="2208" spans="1:6">
+    <row r="2208" spans="1:7">
       <c r="A2208" t="s">
         <v>2213</v>
       </c>
@@ -51433,7 +51571,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2209" spans="1:6">
+    <row r="2209" spans="1:7">
       <c r="A2209" t="s">
         <v>2214</v>
       </c>
@@ -51444,7 +51582,7 @@
         <v>4533</v>
       </c>
     </row>
-    <row r="2210" spans="1:6">
+    <row r="2210" spans="1:7">
       <c r="A2210" t="s">
         <v>2215</v>
       </c>
@@ -51455,7 +51593,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2211" spans="1:6">
+    <row r="2211" spans="1:7">
       <c r="A2211" t="s">
         <v>2216</v>
       </c>
@@ -51469,7 +51607,7 @@
         <v>4505</v>
       </c>
     </row>
-    <row r="2212" spans="1:6">
+    <row r="2212" spans="1:7">
       <c r="A2212" t="s">
         <v>2217</v>
       </c>
@@ -51483,7 +51621,7 @@
         <v>4505</v>
       </c>
     </row>
-    <row r="2213" spans="1:6">
+    <row r="2213" spans="1:7">
       <c r="A2213" t="s">
         <v>2218</v>
       </c>
@@ -51499,8 +51637,11 @@
       <c r="F2213" t="s">
         <v>4822</v>
       </c>
-    </row>
-    <row r="2214" spans="1:6">
+      <c r="G2213" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:7">
       <c r="A2214" t="s">
         <v>2219</v>
       </c>
@@ -51517,7 +51658,7 @@
         <v>4657</v>
       </c>
     </row>
-    <row r="2215" spans="1:6">
+    <row r="2215" spans="1:7">
       <c r="A2215" t="s">
         <v>2220</v>
       </c>
@@ -51536,8 +51677,11 @@
       <c r="F2215" t="s">
         <v>4823</v>
       </c>
-    </row>
-    <row r="2216" spans="1:6">
+      <c r="G2215" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:7">
       <c r="A2216" t="s">
         <v>2221</v>
       </c>
@@ -51556,8 +51700,11 @@
       <c r="F2216" t="s">
         <v>4824</v>
       </c>
-    </row>
-    <row r="2217" spans="1:6">
+      <c r="G2216" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:7">
       <c r="A2217" t="s">
         <v>2222</v>
       </c>
@@ -51574,7 +51721,7 @@
         <v>4660</v>
       </c>
     </row>
-    <row r="2218" spans="1:6">
+    <row r="2218" spans="1:7">
       <c r="A2218" t="s">
         <v>2223</v>
       </c>
@@ -51593,8 +51740,11 @@
       <c r="F2218" t="s">
         <v>4825</v>
       </c>
-    </row>
-    <row r="2219" spans="1:6">
+      <c r="G2218" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:7">
       <c r="A2219" t="s">
         <v>2224</v>
       </c>
@@ -51607,8 +51757,11 @@
       <c r="D2219" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2220" spans="1:6">
+      <c r="G2219" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:7">
       <c r="A2220" t="s">
         <v>2225</v>
       </c>
@@ -51619,7 +51772,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2221" spans="1:6">
+    <row r="2221" spans="1:7">
       <c r="A2221" t="s">
         <v>2226</v>
       </c>
@@ -51630,7 +51783,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2222" spans="1:6">
+    <row r="2222" spans="1:7">
       <c r="A2222" t="s">
         <v>2227</v>
       </c>
@@ -51641,7 +51794,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2223" spans="1:6">
+    <row r="2223" spans="1:7">
       <c r="A2223" t="s">
         <v>2228</v>
       </c>
@@ -51654,8 +51807,11 @@
       <c r="D2223" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2224" spans="1:6">
+      <c r="G2223" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:7">
       <c r="A2224" t="s">
         <v>2229</v>
       </c>
@@ -51666,7 +51822,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2225" spans="1:5">
+    <row r="2225" spans="1:7">
       <c r="A2225" t="s">
         <v>2230</v>
       </c>
@@ -51677,7 +51833,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2226" spans="1:5">
+    <row r="2226" spans="1:7">
       <c r="A2226" t="s">
         <v>2231</v>
       </c>
@@ -51693,8 +51849,11 @@
       <c r="E2226" t="s">
         <v>4662</v>
       </c>
-    </row>
-    <row r="2227" spans="1:5">
+      <c r="G2226" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:7">
       <c r="A2227" t="s">
         <v>2232</v>
       </c>
@@ -51708,7 +51867,7 @@
         <v>4663</v>
       </c>
     </row>
-    <row r="2228" spans="1:5">
+    <row r="2228" spans="1:7">
       <c r="A2228" t="s">
         <v>2233</v>
       </c>
@@ -51719,7 +51878,7 @@
         <v>4511</v>
       </c>
     </row>
-    <row r="2229" spans="1:5">
+    <row r="2229" spans="1:7">
       <c r="A2229" t="s">
         <v>2234</v>
       </c>
@@ -51736,7 +51895,7 @@
         <v>4664</v>
       </c>
     </row>
-    <row r="2230" spans="1:5">
+    <row r="2230" spans="1:7">
       <c r="A2230" t="s">
         <v>2235</v>
       </c>
@@ -51752,8 +51911,11 @@
       <c r="E2230" t="s">
         <v>4665</v>
       </c>
-    </row>
-    <row r="2231" spans="1:5">
+      <c r="G2230" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:7">
       <c r="A2231" t="s">
         <v>2236</v>
       </c>
@@ -51766,8 +51928,11 @@
       <c r="D2231" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2232" spans="1:5">
+      <c r="G2231" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:7">
       <c r="A2232" t="s">
         <v>2237</v>
       </c>
@@ -51781,7 +51946,7 @@
         <v>4666</v>
       </c>
     </row>
-    <row r="2233" spans="1:5">
+    <row r="2233" spans="1:7">
       <c r="A2233" t="s">
         <v>2238</v>
       </c>
@@ -51795,7 +51960,7 @@
         <v>4667</v>
       </c>
     </row>
-    <row r="2234" spans="1:5">
+    <row r="2234" spans="1:7">
       <c r="A2234" t="s">
         <v>2239</v>
       </c>
@@ -51808,8 +51973,11 @@
       <c r="D2234" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2235" spans="1:5">
+      <c r="G2234" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:7">
       <c r="A2235" t="s">
         <v>2240</v>
       </c>
@@ -51822,8 +51990,11 @@
       <c r="D2235" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2236" spans="1:5">
+      <c r="G2235" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:7">
       <c r="A2236" t="s">
         <v>2241</v>
       </c>
@@ -51837,7 +52008,7 @@
         <v>4668</v>
       </c>
     </row>
-    <row r="2237" spans="1:5">
+    <row r="2237" spans="1:7">
       <c r="A2237" t="s">
         <v>2242</v>
       </c>
@@ -51853,8 +52024,11 @@
       <c r="E2237" t="s">
         <v>4669</v>
       </c>
-    </row>
-    <row r="2238" spans="1:5">
+      <c r="G2237" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:7">
       <c r="A2238" t="s">
         <v>2243</v>
       </c>
@@ -51870,8 +52044,11 @@
       <c r="E2238" t="s">
         <v>4669</v>
       </c>
-    </row>
-    <row r="2239" spans="1:5">
+      <c r="G2238" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:7">
       <c r="A2239" t="s">
         <v>2244</v>
       </c>
@@ -51882,7 +52059,7 @@
         <v>4537</v>
       </c>
     </row>
-    <row r="2240" spans="1:5">
+    <row r="2240" spans="1:7">
       <c r="A2240" t="s">
         <v>2245</v>
       </c>
@@ -51898,8 +52075,11 @@
       <c r="E2240" t="s">
         <v>4670</v>
       </c>
-    </row>
-    <row r="2241" spans="1:6">
+      <c r="G2240" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:7">
       <c r="A2241" t="s">
         <v>2246</v>
       </c>
@@ -51910,7 +52090,7 @@
         <v>4469</v>
       </c>
     </row>
-    <row r="2242" spans="1:6">
+    <row r="2242" spans="1:7">
       <c r="A2242" t="s">
         <v>2247</v>
       </c>
@@ -51923,8 +52103,11 @@
       <c r="D2242" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2243" spans="1:6">
+      <c r="G2242" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:7">
       <c r="A2243" t="s">
         <v>2248</v>
       </c>
@@ -51940,8 +52123,11 @@
       <c r="E2243" t="s">
         <v>4671</v>
       </c>
-    </row>
-    <row r="2244" spans="1:6">
+      <c r="G2243" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:7">
       <c r="A2244" t="s">
         <v>2249</v>
       </c>
@@ -51954,8 +52140,11 @@
       <c r="D2244" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2245" spans="1:6">
+      <c r="G2244" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:7">
       <c r="A2245" t="s">
         <v>2250</v>
       </c>
@@ -51969,7 +52158,7 @@
         <v>4531</v>
       </c>
     </row>
-    <row r="2246" spans="1:6">
+    <row r="2246" spans="1:7">
       <c r="A2246" t="s">
         <v>2251</v>
       </c>
@@ -51985,8 +52174,11 @@
       <c r="F2246" t="s">
         <v>4826</v>
       </c>
-    </row>
-    <row r="2247" spans="1:6">
+      <c r="G2246" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:7">
       <c r="A2247" t="s">
         <v>2252</v>
       </c>
@@ -51999,8 +52191,11 @@
       <c r="D2247" t="s">
         <v>4469</v>
       </c>
-    </row>
-    <row r="2248" spans="1:6">
+      <c r="G2247" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:7">
       <c r="A2248" t="s">
         <v>2253</v>
       </c>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10955" uniqueCount="4828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10965" uniqueCount="4828">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -49333,6 +49333,9 @@
       <c r="D2063" t="s">
         <v>4469</v>
       </c>
+      <c r="G2063" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2064" spans="1:7">
       <c r="A2064" t="s">
@@ -50052,6 +50055,9 @@
       <c r="D2109" t="s">
         <v>4469</v>
       </c>
+      <c r="G2109" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2110" spans="1:7">
       <c r="A2110" t="s">
@@ -50066,6 +50072,9 @@
       <c r="D2110" t="s">
         <v>4469</v>
       </c>
+      <c r="G2110" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2111" spans="1:7">
       <c r="A2111" t="s">
@@ -50080,6 +50089,9 @@
       <c r="D2111" t="s">
         <v>4469</v>
       </c>
+      <c r="G2111" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2112" spans="1:7">
       <c r="A2112" t="s">
@@ -50094,6 +50106,9 @@
       <c r="D2112" t="s">
         <v>4469</v>
       </c>
+      <c r="G2112" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2113" spans="1:7">
       <c r="A2113" t="s">
@@ -50108,6 +50123,9 @@
       <c r="D2113" t="s">
         <v>4469</v>
       </c>
+      <c r="G2113" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2114" spans="1:7">
       <c r="A2114" t="s">
@@ -50122,6 +50140,9 @@
       <c r="D2114" t="s">
         <v>4469</v>
       </c>
+      <c r="G2114" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2115" spans="1:7">
       <c r="A2115" t="s">
@@ -50136,6 +50157,9 @@
       <c r="D2115" t="s">
         <v>4469</v>
       </c>
+      <c r="G2115" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2116" spans="1:7">
       <c r="A2116" t="s">
@@ -50150,6 +50174,9 @@
       <c r="D2116" t="s">
         <v>4469</v>
       </c>
+      <c r="G2116" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2117" spans="1:7">
       <c r="A2117" t="s">
@@ -50797,6 +50824,9 @@
       </c>
       <c r="F2158" t="s">
         <v>4814</v>
+      </c>
+      <c r="G2158" t="s">
+        <v>4827</v>
       </c>
     </row>
     <row r="2159" spans="1:7">

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10965" uniqueCount="4828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10976" uniqueCount="4828">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -49257,6 +49257,9 @@
       <c r="D2058" t="s">
         <v>4469</v>
       </c>
+      <c r="G2058" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2059" spans="1:7">
       <c r="A2059" t="s">
@@ -49288,6 +49291,9 @@
       <c r="D2060" t="s">
         <v>4469</v>
       </c>
+      <c r="G2060" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2061" spans="1:7">
       <c r="A2061" t="s">
@@ -49929,6 +49935,9 @@
       <c r="D2100" t="s">
         <v>4469</v>
       </c>
+      <c r="G2100" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2101" spans="1:7">
       <c r="A2101" t="s">
@@ -49943,6 +49952,9 @@
       <c r="D2101" t="s">
         <v>4469</v>
       </c>
+      <c r="G2101" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2102" spans="1:7">
       <c r="A2102" t="s">
@@ -50435,6 +50447,9 @@
       <c r="D2131" t="s">
         <v>4469</v>
       </c>
+      <c r="G2131" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2132" spans="1:7">
       <c r="A2132" t="s">
@@ -50483,6 +50498,9 @@
       <c r="D2134" t="s">
         <v>4469</v>
       </c>
+      <c r="G2134" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2135" spans="1:7">
       <c r="A2135" t="s">
@@ -50497,6 +50515,9 @@
       <c r="D2135" t="s">
         <v>4469</v>
       </c>
+      <c r="G2135" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2136" spans="1:7">
       <c r="A2136" t="s">
@@ -50511,6 +50532,9 @@
       <c r="D2136" t="s">
         <v>4469</v>
       </c>
+      <c r="G2136" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2137" spans="1:7">
       <c r="A2137" t="s">
@@ -50525,6 +50549,9 @@
       <c r="D2137" t="s">
         <v>4469</v>
       </c>
+      <c r="G2137" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2138" spans="1:7">
       <c r="A2138" t="s">
@@ -50562,6 +50589,9 @@
       <c r="F2139" t="s">
         <v>4812</v>
       </c>
+      <c r="G2139" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2140" spans="1:7">
       <c r="A2140" t="s">
@@ -50575,6 +50605,9 @@
       </c>
       <c r="D2140" t="s">
         <v>4469</v>
+      </c>
+      <c r="G2140" t="s">
+        <v>4827</v>
       </c>
     </row>
     <row r="2141" spans="1:7">

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10976" uniqueCount="4828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10977" uniqueCount="4828">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -49969,6 +49969,9 @@
       <c r="D2102" t="s">
         <v>4469</v>
       </c>
+      <c r="G2102" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="2103" spans="1:7">
       <c r="A2103" t="s">

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -13426,208 +13426,208 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>Johannesburg</t>
-  </si>
-  <si>
-    <t>Randburg</t>
-  </si>
-  <si>
-    <t>Sandton</t>
-  </si>
-  <si>
-    <t>Yeoville</t>
-  </si>
-  <si>
-    <t>Alexandra</t>
-  </si>
-  <si>
-    <t>Roodepoort</t>
-  </si>
-  <si>
-    <t>Soweto</t>
-  </si>
-  <si>
-    <t>Brixton</t>
-  </si>
-  <si>
-    <t>Riverlea</t>
-  </si>
-  <si>
-    <t>Eldorado Park</t>
-  </si>
-  <si>
-    <t>Lenasia South</t>
-  </si>
-  <si>
-    <t>Orange Farm</t>
-  </si>
-  <si>
-    <t>Kliptown</t>
-  </si>
-  <si>
-    <t>Pretoria</t>
-  </si>
-  <si>
-    <t>Linksfield</t>
-  </si>
-  <si>
-    <t>Newtown</t>
-  </si>
-  <si>
-    <t>Braamfontein</t>
-  </si>
-  <si>
-    <t>Benoni</t>
-  </si>
-  <si>
-    <t>Johannesburg South</t>
-  </si>
-  <si>
-    <t>Johannesburg CBD</t>
-  </si>
-  <si>
-    <t>Rosebank</t>
-  </si>
-  <si>
-    <t>Krugersdorp</t>
-  </si>
-  <si>
-    <t>Lorentzville</t>
-  </si>
-  <si>
-    <t>Maboneng</t>
-  </si>
-  <si>
-    <t>Parkwood</t>
-  </si>
-  <si>
-    <t>Centurion</t>
-  </si>
-  <si>
-    <t>Midrand</t>
-  </si>
-  <si>
-    <t>Alberton</t>
-  </si>
-  <si>
-    <t>Edenvale</t>
-  </si>
-  <si>
-    <t>Boksburg</t>
-  </si>
-  <si>
-    <t>Kempton Park</t>
-  </si>
-  <si>
-    <t>Daveyton</t>
-  </si>
-  <si>
-    <t>Springs</t>
-  </si>
-  <si>
-    <t>Hillbrow</t>
-  </si>
-  <si>
-    <t>Constantia</t>
-  </si>
-  <si>
-    <t>Helderberg</t>
-  </si>
-  <si>
-    <t>Hout Bay</t>
-  </si>
-  <si>
-    <t>Fish Hoek</t>
-  </si>
-  <si>
-    <t>Muizenberg</t>
-  </si>
-  <si>
-    <t>Atlantis</t>
-  </si>
-  <si>
-    <t>Mitchells Plain</t>
-  </si>
-  <si>
-    <t>Gugulethu</t>
-  </si>
-  <si>
-    <t>Langa</t>
-  </si>
-  <si>
-    <t>Khayelitsha</t>
-  </si>
-  <si>
-    <t>Masiphumelele</t>
-  </si>
-  <si>
-    <t>Philippi East</t>
-  </si>
-  <si>
-    <t>Vrygrond</t>
-  </si>
-  <si>
-    <t>Westlake</t>
-  </si>
-  <si>
-    <t>Observatory</t>
-  </si>
-  <si>
-    <t>Rondebosch</t>
-  </si>
-  <si>
-    <t>Lavender Hill</t>
-  </si>
-  <si>
-    <t>Gardens</t>
-  </si>
-  <si>
-    <t>Woodstock</t>
-  </si>
-  <si>
-    <t>Elfindale</t>
-  </si>
-  <si>
-    <t>Tokai</t>
-  </si>
-  <si>
-    <t>Ottery</t>
-  </si>
-  <si>
-    <t>Lwandle</t>
-  </si>
-  <si>
-    <t>Green Point</t>
-  </si>
-  <si>
-    <t>Pinelands</t>
-  </si>
-  <si>
-    <t>Glencairn</t>
-  </si>
-  <si>
-    <t>Salt River</t>
-  </si>
-  <si>
-    <t>Wynberg</t>
-  </si>
-  <si>
-    <t>Athlone</t>
-  </si>
-  <si>
-    <t>Claremont</t>
-  </si>
-  <si>
-    <t>Ilitha Park</t>
-  </si>
-  <si>
-    <t>Rylands Estate</t>
-  </si>
-  <si>
-    <t>Brooklyn</t>
-  </si>
-  <si>
-    <t>V&amp;A Waterfront</t>
+    <t>Johannesburg, Cape Town</t>
+  </si>
+  <si>
+    <t>Randburg, Cape Town</t>
+  </si>
+  <si>
+    <t>Sandton, Cape Town</t>
+  </si>
+  <si>
+    <t>Yeoville, Cape Town</t>
+  </si>
+  <si>
+    <t>Alexandra, Cape Town</t>
+  </si>
+  <si>
+    <t>Roodepoort, Cape Town</t>
+  </si>
+  <si>
+    <t>Soweto, Cape Town</t>
+  </si>
+  <si>
+    <t>Brixton, Cape Town</t>
+  </si>
+  <si>
+    <t>Riverlea, Cape Town</t>
+  </si>
+  <si>
+    <t>Eldorado Park, Cape Town</t>
+  </si>
+  <si>
+    <t>Lenasia South, Cape Town</t>
+  </si>
+  <si>
+    <t>Orange Farm, Cape Town</t>
+  </si>
+  <si>
+    <t>Kliptown, Cape Town</t>
+  </si>
+  <si>
+    <t>Pretoria, Cape Town</t>
+  </si>
+  <si>
+    <t>Linksfield, Cape Town</t>
+  </si>
+  <si>
+    <t>Newtown, Cape Town</t>
+  </si>
+  <si>
+    <t>Braamfontein, Cape Town</t>
+  </si>
+  <si>
+    <t>Benoni, Cape Town</t>
+  </si>
+  <si>
+    <t>Johannesburg South, Cape Town</t>
+  </si>
+  <si>
+    <t>Johannesburg CBD, Cape Town</t>
+  </si>
+  <si>
+    <t>Rosebank, Cape Town</t>
+  </si>
+  <si>
+    <t>Krugersdorp, Cape Town</t>
+  </si>
+  <si>
+    <t>Lorentzville, Cape Town</t>
+  </si>
+  <si>
+    <t>Maboneng, Cape Town</t>
+  </si>
+  <si>
+    <t>Parkwood, Cape Town</t>
+  </si>
+  <si>
+    <t>Centurion, Cape Town</t>
+  </si>
+  <si>
+    <t>Midrand, Cape Town</t>
+  </si>
+  <si>
+    <t>Alberton, Cape Town</t>
+  </si>
+  <si>
+    <t>Edenvale, Cape Town</t>
+  </si>
+  <si>
+    <t>Boksburg, Cape Town</t>
+  </si>
+  <si>
+    <t>Kempton Park, Cape Town</t>
+  </si>
+  <si>
+    <t>Daveyton, Cape Town</t>
+  </si>
+  <si>
+    <t>Springs, Cape Town</t>
+  </si>
+  <si>
+    <t>Hillbrow, Cape Town</t>
+  </si>
+  <si>
+    <t>Constantia, Cape Town</t>
+  </si>
+  <si>
+    <t>Helderberg, Cape Town</t>
+  </si>
+  <si>
+    <t>Hout Bay, Cape Town</t>
+  </si>
+  <si>
+    <t>Fish Hoek, Cape Town</t>
+  </si>
+  <si>
+    <t>Muizenberg, Cape Town</t>
+  </si>
+  <si>
+    <t>Atlantis, Cape Town</t>
+  </si>
+  <si>
+    <t>Mitchells Plain, Cape Town</t>
+  </si>
+  <si>
+    <t>Gugulethu, Cape Town</t>
+  </si>
+  <si>
+    <t>Langa, Cape Town</t>
+  </si>
+  <si>
+    <t>Khayelitsha, Cape Town</t>
+  </si>
+  <si>
+    <t>Masiphumelele, Cape Town</t>
+  </si>
+  <si>
+    <t>Philippi East, Cape Town</t>
+  </si>
+  <si>
+    <t>Vrygrond, Cape Town</t>
+  </si>
+  <si>
+    <t>Westlake, Cape Town</t>
+  </si>
+  <si>
+    <t>Observatory, Cape Town</t>
+  </si>
+  <si>
+    <t>Rondebosch, Cape Town</t>
+  </si>
+  <si>
+    <t>Lavender Hill, Cape Town</t>
+  </si>
+  <si>
+    <t>Gardens, Cape Town</t>
+  </si>
+  <si>
+    <t>Woodstock, Cape Town</t>
+  </si>
+  <si>
+    <t>Elfindale, Cape Town</t>
+  </si>
+  <si>
+    <t>Tokai, Cape Town</t>
+  </si>
+  <si>
+    <t>Ottery, Cape Town</t>
+  </si>
+  <si>
+    <t>Lwandle, Cape Town</t>
+  </si>
+  <si>
+    <t>Green Point, Cape Town</t>
+  </si>
+  <si>
+    <t>Pinelands, Cape Town</t>
+  </si>
+  <si>
+    <t>Glencairn, Cape Town</t>
+  </si>
+  <si>
+    <t>Salt River, Cape Town</t>
+  </si>
+  <si>
+    <t>Wynberg, Cape Town</t>
+  </si>
+  <si>
+    <t>Athlone, Cape Town</t>
+  </si>
+  <si>
+    <t>Claremont, Cape Town</t>
+  </si>
+  <si>
+    <t>Ilitha Park, Cape Town</t>
+  </si>
+  <si>
+    <t>Rylands Estate, Cape Town</t>
+  </si>
+  <si>
+    <t>Brooklyn, Cape Town</t>
+  </si>
+  <si>
+    <t>V&amp;A Waterfront, Cape Town</t>
   </si>
   <si>
     <t>021 300 3200</t>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10977" uniqueCount="4828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11001" uniqueCount="4828">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -42668,6 +42668,9 @@
       <c r="D1606" t="s">
         <v>4471</v>
       </c>
+      <c r="G1606" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="1607" spans="1:7">
       <c r="A1607" t="s">
@@ -42696,6 +42699,9 @@
       <c r="D1608" t="s">
         <v>4471</v>
       </c>
+      <c r="G1608" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="1609" spans="1:7">
       <c r="A1609" t="s">
@@ -42710,6 +42716,9 @@
       <c r="D1609" t="s">
         <v>4471</v>
       </c>
+      <c r="G1609" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="1610" spans="1:7">
       <c r="A1610" t="s">
@@ -42724,6 +42733,9 @@
       <c r="D1610" t="s">
         <v>4471</v>
       </c>
+      <c r="G1610" t="s">
+        <v>4827</v>
+      </c>
     </row>
     <row r="1611" spans="1:7">
       <c r="A1611" t="s">
@@ -42809,7 +42821,7 @@
         <v>4471</v>
       </c>
     </row>
-    <row r="1617" spans="1:4">
+    <row r="1617" spans="1:7">
       <c r="A1617" t="s">
         <v>1622</v>
       </c>
@@ -42822,8 +42834,11 @@
       <c r="D1617" t="s">
         <v>4471</v>
       </c>
-    </row>
-    <row r="1618" spans="1:4">
+      <c r="G1617" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:7">
       <c r="A1618" t="s">
         <v>1623</v>
       </c>
@@ -42837,7 +42852,7 @@
         <v>4471</v>
       </c>
     </row>
-    <row r="1619" spans="1:4">
+    <row r="1619" spans="1:7">
       <c r="A1619" t="s">
         <v>1624</v>
       </c>
@@ -42850,8 +42865,11 @@
       <c r="D1619" t="s">
         <v>4471</v>
       </c>
-    </row>
-    <row r="1620" spans="1:4">
+      <c r="G1619" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:7">
       <c r="A1620" t="s">
         <v>1625</v>
       </c>
@@ -42864,8 +42882,11 @@
       <c r="D1620" t="s">
         <v>4471</v>
       </c>
-    </row>
-    <row r="1621" spans="1:4">
+      <c r="G1620" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:7">
       <c r="A1621" t="s">
         <v>1626</v>
       </c>
@@ -42878,8 +42899,11 @@
       <c r="D1621" t="s">
         <v>4471</v>
       </c>
-    </row>
-    <row r="1622" spans="1:4">
+      <c r="G1621" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:7">
       <c r="A1622" t="s">
         <v>1627</v>
       </c>
@@ -42892,8 +42916,11 @@
       <c r="D1622" t="s">
         <v>4471</v>
       </c>
-    </row>
-    <row r="1623" spans="1:4">
+      <c r="G1622" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:7">
       <c r="A1623" t="s">
         <v>1628</v>
       </c>
@@ -42906,8 +42933,11 @@
       <c r="D1623" t="s">
         <v>4471</v>
       </c>
-    </row>
-    <row r="1624" spans="1:4">
+      <c r="G1623" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:7">
       <c r="A1624" t="s">
         <v>1629</v>
       </c>
@@ -42920,8 +42950,11 @@
       <c r="D1624" t="s">
         <v>4471</v>
       </c>
-    </row>
-    <row r="1625" spans="1:4">
+      <c r="G1624" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:7">
       <c r="A1625" t="s">
         <v>1630</v>
       </c>
@@ -42935,7 +42968,7 @@
         <v>4471</v>
       </c>
     </row>
-    <row r="1626" spans="1:4">
+    <row r="1626" spans="1:7">
       <c r="A1626" t="s">
         <v>1631</v>
       </c>
@@ -42948,8 +42981,11 @@
       <c r="D1626" t="s">
         <v>4471</v>
       </c>
-    </row>
-    <row r="1627" spans="1:4">
+      <c r="G1626" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:7">
       <c r="A1627" t="s">
         <v>1632</v>
       </c>
@@ -42962,8 +42998,11 @@
       <c r="D1627" t="s">
         <v>4471</v>
       </c>
-    </row>
-    <row r="1628" spans="1:4">
+      <c r="G1627" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:7">
       <c r="A1628" t="s">
         <v>1633</v>
       </c>
@@ -42976,8 +43015,11 @@
       <c r="D1628" t="s">
         <v>4471</v>
       </c>
-    </row>
-    <row r="1629" spans="1:4">
+      <c r="G1628" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:7">
       <c r="A1629" t="s">
         <v>1634</v>
       </c>
@@ -42990,8 +43032,11 @@
       <c r="D1629" t="s">
         <v>4471</v>
       </c>
-    </row>
-    <row r="1630" spans="1:4">
+      <c r="G1629" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:7">
       <c r="A1630" t="s">
         <v>1635</v>
       </c>
@@ -43004,8 +43049,11 @@
       <c r="D1630" t="s">
         <v>4471</v>
       </c>
-    </row>
-    <row r="1631" spans="1:4">
+      <c r="G1630" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:7">
       <c r="A1631" t="s">
         <v>1636</v>
       </c>
@@ -43018,8 +43066,11 @@
       <c r="D1631" t="s">
         <v>4472</v>
       </c>
-    </row>
-    <row r="1632" spans="1:4">
+      <c r="G1631" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:7">
       <c r="A1632" t="s">
         <v>1637</v>
       </c>
@@ -43032,8 +43083,11 @@
       <c r="D1632" t="s">
         <v>4472</v>
       </c>
-    </row>
-    <row r="1633" spans="1:4">
+      <c r="G1632" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:7">
       <c r="A1633" t="s">
         <v>1638</v>
       </c>
@@ -43047,7 +43101,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="1634" spans="1:4">
+    <row r="1634" spans="1:7">
       <c r="A1634" t="s">
         <v>1639</v>
       </c>
@@ -43060,8 +43114,11 @@
       <c r="D1634" t="s">
         <v>4472</v>
       </c>
-    </row>
-    <row r="1635" spans="1:4">
+      <c r="G1634" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:7">
       <c r="A1635" t="s">
         <v>1640</v>
       </c>
@@ -43074,8 +43131,11 @@
       <c r="D1635" t="s">
         <v>4472</v>
       </c>
-    </row>
-    <row r="1636" spans="1:4">
+      <c r="G1635" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:7">
       <c r="A1636" t="s">
         <v>1641</v>
       </c>
@@ -43089,7 +43149,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="1637" spans="1:4">
+    <row r="1637" spans="1:7">
       <c r="A1637" t="s">
         <v>1642</v>
       </c>
@@ -43102,8 +43162,11 @@
       <c r="D1637" t="s">
         <v>4472</v>
       </c>
-    </row>
-    <row r="1638" spans="1:4">
+      <c r="G1637" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:7">
       <c r="A1638" t="s">
         <v>1643</v>
       </c>
@@ -43116,8 +43179,11 @@
       <c r="D1638" t="s">
         <v>4472</v>
       </c>
-    </row>
-    <row r="1639" spans="1:4">
+      <c r="G1638" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:7">
       <c r="A1639" t="s">
         <v>1644</v>
       </c>
@@ -43130,8 +43196,11 @@
       <c r="D1639" t="s">
         <v>4472</v>
       </c>
-    </row>
-    <row r="1640" spans="1:4">
+      <c r="G1639" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:7">
       <c r="A1640" t="s">
         <v>1645</v>
       </c>
@@ -43144,8 +43213,11 @@
       <c r="D1640" t="s">
         <v>4472</v>
       </c>
-    </row>
-    <row r="1641" spans="1:4">
+      <c r="G1640" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:7">
       <c r="A1641" t="s">
         <v>1646</v>
       </c>
@@ -43159,7 +43231,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="1642" spans="1:4">
+    <row r="1642" spans="1:7">
       <c r="A1642" t="s">
         <v>1647</v>
       </c>
@@ -43173,7 +43245,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="1643" spans="1:4">
+    <row r="1643" spans="1:7">
       <c r="A1643" t="s">
         <v>1648</v>
       </c>
@@ -43187,7 +43259,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="1644" spans="1:4">
+    <row r="1644" spans="1:7">
       <c r="A1644" t="s">
         <v>1649</v>
       </c>
@@ -43201,7 +43273,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="1645" spans="1:4">
+    <row r="1645" spans="1:7">
       <c r="A1645" t="s">
         <v>1650</v>
       </c>
@@ -43215,7 +43287,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="1646" spans="1:4">
+    <row r="1646" spans="1:7">
       <c r="A1646" t="s">
         <v>1651</v>
       </c>
@@ -43229,7 +43301,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="1647" spans="1:4">
+    <row r="1647" spans="1:7">
       <c r="A1647" t="s">
         <v>1652</v>
       </c>
@@ -43243,7 +43315,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="1648" spans="1:4">
+    <row r="1648" spans="1:7">
       <c r="A1648" t="s">
         <v>1653</v>
       </c>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="538">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -2622,6 +2622,9 @@
       <c r="D33" t="s">
         <v>438</v>
       </c>
+      <c r="G33" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
@@ -2636,6 +2639,9 @@
       <c r="D34" t="s">
         <v>438</v>
       </c>
+      <c r="G34" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
@@ -2650,6 +2656,9 @@
       <c r="D35" t="s">
         <v>438</v>
       </c>
+      <c r="G35" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
@@ -2664,6 +2673,9 @@
       <c r="D36" t="s">
         <v>438</v>
       </c>
+      <c r="G36" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
@@ -2678,6 +2690,9 @@
       <c r="D37" t="s">
         <v>438</v>
       </c>
+      <c r="G37" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
@@ -2692,6 +2707,9 @@
       <c r="D38" t="s">
         <v>438</v>
       </c>
+      <c r="G38" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
@@ -2706,6 +2724,9 @@
       <c r="D39" t="s">
         <v>438</v>
       </c>
+      <c r="G39" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
@@ -3309,6 +3330,9 @@
       <c r="D75" t="s">
         <v>438</v>
       </c>
+      <c r="G75" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
@@ -3323,6 +3347,9 @@
       <c r="D76" t="s">
         <v>438</v>
       </c>
+      <c r="G76" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
@@ -3337,6 +3364,9 @@
       <c r="D77" t="s">
         <v>438</v>
       </c>
+      <c r="G77" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
@@ -3351,6 +3381,9 @@
       <c r="D78" t="s">
         <v>438</v>
       </c>
+      <c r="G78" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
@@ -3365,6 +3398,9 @@
       <c r="D79" t="s">
         <v>438</v>
       </c>
+      <c r="G79" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
@@ -3379,6 +3415,9 @@
       <c r="D80" t="s">
         <v>438</v>
       </c>
+      <c r="G80" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
@@ -3393,6 +3432,9 @@
       <c r="D81" t="s">
         <v>438</v>
       </c>
+      <c r="G81" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
@@ -3407,6 +3449,9 @@
       <c r="D82" t="s">
         <v>438</v>
       </c>
+      <c r="G82" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
@@ -3421,6 +3466,9 @@
       <c r="D83" t="s">
         <v>438</v>
       </c>
+      <c r="G83" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
@@ -3435,6 +3483,9 @@
       <c r="D84" t="s">
         <v>438</v>
       </c>
+      <c r="G84" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
@@ -3585,6 +3636,9 @@
       <c r="D93" t="s">
         <v>438</v>
       </c>
+      <c r="G93" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
@@ -3599,6 +3653,9 @@
       <c r="D94" t="s">
         <v>438</v>
       </c>
+      <c r="G94" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
@@ -3613,6 +3670,9 @@
       <c r="D95" t="s">
         <v>438</v>
       </c>
+      <c r="G95" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
@@ -3627,6 +3687,9 @@
       <c r="D96" t="s">
         <v>438</v>
       </c>
+      <c r="G96" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
@@ -3641,6 +3704,9 @@
       <c r="D97" t="s">
         <v>438</v>
       </c>
+      <c r="G97" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" t="s">
@@ -3655,6 +3721,9 @@
       <c r="D98" t="s">
         <v>438</v>
       </c>
+      <c r="G98" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
@@ -4035,6 +4104,9 @@
       <c r="E120" t="s">
         <v>467</v>
       </c>
+      <c r="G120" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="121" spans="1:7">
       <c r="A121" t="s">
@@ -4066,6 +4138,9 @@
       <c r="D122" t="s">
         <v>441</v>
       </c>
+      <c r="G122" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" t="s">
@@ -4086,6 +4161,9 @@
       <c r="F123" t="s">
         <v>521</v>
       </c>
+      <c r="G123" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" t="s">
@@ -4171,6 +4249,9 @@
       <c r="E128" t="s">
         <v>469</v>
       </c>
+      <c r="G128" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" t="s">
@@ -4242,6 +4323,9 @@
       <c r="E132" t="s">
         <v>472</v>
       </c>
+      <c r="G132" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" t="s">
@@ -4259,6 +4343,9 @@
       <c r="E133" t="s">
         <v>473</v>
       </c>
+      <c r="G133" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134" t="s">
@@ -4295,6 +4382,9 @@
       <c r="D136" t="s">
         <v>438</v>
       </c>
+      <c r="G136" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" t="s">
@@ -4309,6 +4399,9 @@
       <c r="D137" t="s">
         <v>444</v>
       </c>
+      <c r="G137" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" t="s">
@@ -4379,6 +4472,9 @@
       <c r="F142" t="s">
         <v>523</v>
       </c>
+      <c r="G142" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="143" spans="1:7">
       <c r="A143" t="s">
@@ -4393,6 +4489,9 @@
       <c r="D143" t="s">
         <v>448</v>
       </c>
+      <c r="G143" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="144" spans="1:7">
       <c r="A144" t="s">
@@ -4475,6 +4574,9 @@
       <c r="E148" t="s">
         <v>477</v>
       </c>
+      <c r="G148" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="149" spans="1:7">
       <c r="A149" t="s">
@@ -4492,6 +4594,9 @@
       <c r="E149" t="s">
         <v>478</v>
       </c>
+      <c r="G149" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="150" spans="1:7">
       <c r="A150" t="s">
@@ -4509,6 +4614,9 @@
       <c r="E150" t="s">
         <v>479</v>
       </c>
+      <c r="G150" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" t="s">
@@ -4526,6 +4634,9 @@
       <c r="E151" t="s">
         <v>480</v>
       </c>
+      <c r="G151" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="152" spans="1:7">
       <c r="A152" t="s">
@@ -4543,6 +4654,9 @@
       <c r="E152" t="s">
         <v>481</v>
       </c>
+      <c r="G152" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="153" spans="1:7">
       <c r="A153" t="s">
@@ -4571,6 +4685,9 @@
       <c r="E154" t="s">
         <v>482</v>
       </c>
+      <c r="G154" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" t="s">
@@ -4585,6 +4702,9 @@
       <c r="D155" t="s">
         <v>438</v>
       </c>
+      <c r="G155" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156" t="s">
@@ -4599,6 +4719,9 @@
       <c r="D156" t="s">
         <v>438</v>
       </c>
+      <c r="G156" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157" t="s">
@@ -4879,6 +5002,9 @@
       <c r="D173" t="s">
         <v>438</v>
       </c>
+      <c r="G173" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="174" spans="1:7">
       <c r="A174" t="s">
@@ -4896,6 +5022,9 @@
       <c r="F174" t="s">
         <v>527</v>
       </c>
+      <c r="G174" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="175" spans="1:7">
       <c r="A175" t="s">
@@ -4913,6 +5042,9 @@
       <c r="F175" t="s">
         <v>528</v>
       </c>
+      <c r="G175" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="176" spans="1:7">
       <c r="A176" t="s">
@@ -4966,6 +5098,9 @@
       <c r="F179" t="s">
         <v>529</v>
       </c>
+      <c r="G179" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="180" spans="1:7">
       <c r="A180" t="s">
@@ -5170,6 +5305,9 @@
       <c r="D194" t="s">
         <v>441</v>
       </c>
+      <c r="G194" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="195" spans="1:7">
       <c r="A195" t="s">
@@ -5184,6 +5322,9 @@
       <c r="D195" t="s">
         <v>441</v>
       </c>
+      <c r="G195" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="196" spans="1:7">
       <c r="A196" t="s">
@@ -5658,6 +5799,9 @@
       </c>
       <c r="D224" t="s">
         <v>460</v>
+      </c>
+      <c r="G224" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="225" spans="1:7">

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="538">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -4742,6 +4742,9 @@
       <c r="F157" t="s">
         <v>526</v>
       </c>
+      <c r="G157" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="158" spans="1:7">
       <c r="A158" t="s">
@@ -4759,6 +4762,9 @@
       <c r="E158" t="s">
         <v>484</v>
       </c>
+      <c r="G158" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" t="s">
@@ -4776,6 +4782,9 @@
       <c r="E159" t="s">
         <v>485</v>
       </c>
+      <c r="G159" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="160" spans="1:7">
       <c r="A160" t="s">
@@ -4793,6 +4802,9 @@
       <c r="E160" t="s">
         <v>486</v>
       </c>
+      <c r="G160" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
@@ -4810,6 +4822,9 @@
       <c r="E161" t="s">
         <v>487</v>
       </c>
+      <c r="G161" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
@@ -4824,6 +4839,9 @@
       <c r="D162" t="s">
         <v>438</v>
       </c>
+      <c r="G162" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
@@ -4841,6 +4859,9 @@
       <c r="E163" t="s">
         <v>488</v>
       </c>
+      <c r="G163" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
@@ -4858,6 +4879,9 @@
       <c r="E164" t="s">
         <v>489</v>
       </c>
+      <c r="G164" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
@@ -4889,6 +4913,9 @@
       <c r="E166" t="s">
         <v>491</v>
       </c>
+      <c r="G166" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
@@ -4905,6 +4932,9 @@
       </c>
       <c r="E167" t="s">
         <v>492</v>
+      </c>
+      <c r="G167" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="168" spans="1:7">

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="538">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -2928,6 +2928,9 @@
       <c r="D51" t="s">
         <v>438</v>
       </c>
+      <c r="G51" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
@@ -2976,6 +2979,9 @@
       <c r="D54" t="s">
         <v>438</v>
       </c>
+      <c r="G54" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
@@ -4556,6 +4562,9 @@
       </c>
       <c r="F147" t="s">
         <v>525</v>
+      </c>
+      <c r="G147" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="148" spans="1:7">

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="541">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -715,6 +715,9 @@
     <t>Maties Underwater Club</t>
   </si>
   <si>
+    <t>Community Service Outreach Test</t>
+  </si>
+  <si>
     <t>info@ctsc.org.za</t>
   </si>
   <si>
@@ -1261,6 +1264,9 @@
     <t>info@capebirdclub.org.za</t>
   </si>
   <si>
+    <t>mrnnsu001@myuct.ac.za</t>
+  </si>
+  <si>
     <t>Museums &amp; Heritage</t>
   </si>
   <si>
@@ -1328,6 +1334,9 @@
   </si>
   <si>
     <t>Hobby &amp; Special Interest Clubs</t>
+  </si>
+  <si>
+    <t>Test</t>
   </si>
   <si>
     <t>Cape Town</t>
@@ -1972,7 +1981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G227"/>
+  <dimension ref="A1:G228"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2003,22 +2012,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2026,22 +2035,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D3" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E3" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F3" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G3" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2049,22 +2058,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D4" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E4" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F4" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G4" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2072,22 +2081,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D5" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E5" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F5" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G5" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2095,22 +2104,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C6" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D6" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E6" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F6" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G6" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2118,22 +2127,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C7" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D7" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E7" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F7" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G7" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2141,22 +2150,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C8" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D8" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E8" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F8" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G8" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2164,22 +2173,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C9" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D9" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E9" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F9" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G9" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2187,22 +2196,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C10" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D10" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E10" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F10" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G10" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2210,22 +2219,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C11" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D11" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E11" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F11" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G11" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2233,22 +2242,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C12" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D12" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E12" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F12" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G12" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2256,22 +2265,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C13" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D13" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E13" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F13" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G13" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2279,22 +2288,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C14" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D14" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E14" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="G14" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2302,22 +2311,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C15" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D15" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E15" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G15" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2325,16 +2334,16 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C16" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D16" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G16" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2342,16 +2351,16 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C17" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D17" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G17" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2359,16 +2368,16 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C18" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D18" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G18" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2376,16 +2385,16 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C19" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D19" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G19" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2393,16 +2402,16 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C20" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D20" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G20" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2410,16 +2419,16 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C21" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D21" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G21" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2427,16 +2436,16 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C22" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D22" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G22" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2444,16 +2453,16 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C23" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D23" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G23" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2461,16 +2470,16 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C24" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D24" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G24" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2478,16 +2487,16 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C25" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D25" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G25" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2495,16 +2504,16 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C26" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D26" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G26" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2512,16 +2521,16 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C27" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D27" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G27" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2529,16 +2538,16 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C28" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D28" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G28" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2546,16 +2555,16 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D29" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G29" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2563,16 +2572,16 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C30" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D30" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G30" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2580,16 +2589,16 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C31" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D31" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G31" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2597,16 +2606,16 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C32" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D32" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G32" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2614,16 +2623,16 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C33" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D33" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G33" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2631,16 +2640,16 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C34" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D34" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G34" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2648,16 +2657,16 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C35" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D35" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G35" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2665,16 +2674,16 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C36" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D36" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G36" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2682,16 +2691,16 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C37" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D37" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G37" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2699,16 +2708,16 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C38" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D38" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G38" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2716,16 +2725,16 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C39" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D39" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G39" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2733,16 +2742,16 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C40" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D40" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G40" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2750,16 +2759,16 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C41" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D41" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G41" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2767,16 +2776,16 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C42" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D42" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G42" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2784,16 +2793,16 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C43" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D43" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G43" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2801,16 +2810,16 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C44" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D44" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G44" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2818,16 +2827,16 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C45" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D45" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G45" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2835,16 +2844,16 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C46" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D46" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G46" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2852,16 +2861,16 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C47" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D47" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G47" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2869,16 +2878,16 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C48" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D48" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G48" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2886,16 +2895,16 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C49" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D49" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G49" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2903,16 +2912,16 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C50" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D50" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G50" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2920,16 +2929,16 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C51" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D51" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G51" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2937,16 +2946,16 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C52" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D52" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G52" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2954,16 +2963,16 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C53" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D53" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G53" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2971,16 +2980,16 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C54" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D54" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G54" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2988,16 +2997,16 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C55" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D55" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G55" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3005,16 +3014,16 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C56" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D56" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G56" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3022,16 +3031,16 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C57" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D57" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G57" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3039,16 +3048,16 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C58" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D58" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G58" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3056,16 +3065,16 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C59" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D59" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G59" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3073,16 +3082,16 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C60" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D60" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G60" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3090,16 +3099,16 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C61" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D61" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G61" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3107,16 +3116,16 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C62" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D62" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G62" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3124,16 +3133,16 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C63" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D63" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G63" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3141,16 +3150,16 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C64" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D64" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G64" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3158,16 +3167,16 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C65" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D65" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G65" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3175,16 +3184,16 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C66" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D66" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G66" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3192,16 +3201,16 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C67" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D67" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G67" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3209,16 +3218,16 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C68" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D68" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G68" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3226,16 +3235,16 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C69" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D69" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G69" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3243,16 +3252,16 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C70" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D70" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G70" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3260,16 +3269,16 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C71" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D71" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G71" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3277,16 +3286,16 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C72" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D72" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G72" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3294,16 +3303,16 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C73" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D73" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G73" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3311,16 +3320,16 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C74" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D74" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G74" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3328,16 +3337,16 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C75" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D75" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G75" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3345,16 +3354,16 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C76" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D76" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G76" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3362,16 +3371,16 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C77" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D77" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G77" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3379,16 +3388,16 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C78" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D78" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G78" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3396,16 +3405,16 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C79" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D79" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G79" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3413,16 +3422,16 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C80" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D80" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G80" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3430,16 +3439,16 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C81" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D81" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G81" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3447,16 +3456,16 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C82" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D82" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G82" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3464,16 +3473,16 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C83" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D83" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G83" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3481,16 +3490,16 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C84" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D84" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G84" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3498,16 +3507,16 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C85" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D85" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G85" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3515,16 +3524,16 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C86" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D86" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G86" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3532,16 +3541,16 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C87" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D87" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G87" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3549,16 +3558,16 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C88" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D88" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G88" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3566,16 +3575,16 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C89" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D89" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G89" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3583,16 +3592,16 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C90" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D90" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G90" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3600,16 +3609,16 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C91" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D91" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G91" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3617,16 +3626,16 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C92" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D92" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G92" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3634,16 +3643,16 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C93" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D93" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G93" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3651,16 +3660,16 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C94" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D94" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G94" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3668,16 +3677,16 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C95" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D95" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G95" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3685,16 +3694,16 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C96" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D96" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G96" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3702,16 +3711,16 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C97" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D97" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G97" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3719,16 +3728,16 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C98" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D98" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G98" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -3736,16 +3745,16 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C99" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D99" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G99" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -3753,16 +3762,16 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C100" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D100" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G100" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -3770,16 +3779,16 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C101" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D101" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G101" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -3787,16 +3796,16 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C102" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D102" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G102" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -3804,16 +3813,16 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C103" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D103" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G103" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -3821,16 +3830,16 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C104" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D104" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G104" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -3838,16 +3847,16 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C105" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D105" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G105" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -3855,16 +3864,16 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C106" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D106" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G106" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -3872,16 +3881,16 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C107" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D107" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G107" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -3889,16 +3898,16 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C108" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D108" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G108" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -3906,16 +3915,16 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C109" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D109" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G109" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -3923,16 +3932,16 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C110" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D110" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G110" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -3940,16 +3949,16 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C111" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D111" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G111" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -3957,16 +3966,16 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C112" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D112" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G112" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -3974,16 +3983,16 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C113" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D113" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G113" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -3991,16 +4000,16 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C114" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D114" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G114" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4008,16 +4017,16 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C115" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D115" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G115" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4025,16 +4034,16 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C116" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D116" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G116" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4042,16 +4051,16 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C117" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D117" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G117" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4059,16 +4068,16 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C118" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D118" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G118" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4076,22 +4085,22 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C119" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D119" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E119" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F119" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="G119" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4099,19 +4108,19 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C120" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D120" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E120" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="G120" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4119,16 +4128,16 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C121" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D121" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G121" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4136,16 +4145,16 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C122" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D122" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="G122" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4153,22 +4162,22 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C123" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D123" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E123" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F123" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="G123" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4176,16 +4185,16 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C124" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D124" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G124" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4193,16 +4202,16 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C125" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D125" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G125" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4210,16 +4219,16 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C126" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D126" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G126" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4227,16 +4236,16 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C127" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D127" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G127" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4244,19 +4253,19 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C128" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D128" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E128" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="G128" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4264,22 +4273,22 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C129" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D129" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E129" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F129" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="G129" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4287,16 +4296,16 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C130" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D130" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G130" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4304,13 +4313,13 @@
         <v>136</v>
       </c>
       <c r="C131" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D131" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E131" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4318,19 +4327,19 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C132" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D132" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E132" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="G132" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4338,19 +4347,19 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C133" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D133" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E133" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="G133" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4358,10 +4367,10 @@
         <v>139</v>
       </c>
       <c r="C134" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D134" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4369,10 +4378,10 @@
         <v>140</v>
       </c>
       <c r="C135" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D135" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4380,16 +4389,16 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C136" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D136" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G136" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4397,16 +4406,16 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C137" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D137" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="G137" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4414,10 +4423,10 @@
         <v>143</v>
       </c>
       <c r="C138" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D138" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4425,10 +4434,10 @@
         <v>144</v>
       </c>
       <c r="C139" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D139" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4436,10 +4445,10 @@
         <v>145</v>
       </c>
       <c r="C140" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D140" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4447,16 +4456,16 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C141" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D141" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G141" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4464,22 +4473,22 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C142" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D142" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E142" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F142" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="G142" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4487,16 +4496,16 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C143" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D143" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="G143" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4504,13 +4513,13 @@
         <v>149</v>
       </c>
       <c r="C144" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D144" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E144" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4518,10 +4527,10 @@
         <v>150</v>
       </c>
       <c r="C145" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D145" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4529,19 +4538,19 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C146" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D146" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F146" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="G146" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -4549,22 +4558,22 @@
         <v>152</v>
       </c>
       <c r="B147" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C147" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D147" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E147" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F147" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="G147" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -4572,19 +4581,19 @@
         <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C148" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D148" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E148" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="G148" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -4592,19 +4601,19 @@
         <v>154</v>
       </c>
       <c r="B149" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C149" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D149" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E149" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="G149" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -4612,19 +4621,19 @@
         <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C150" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D150" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E150" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="G150" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -4632,19 +4641,19 @@
         <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C151" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D151" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E151" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="G151" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -4652,19 +4661,19 @@
         <v>157</v>
       </c>
       <c r="B152" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C152" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D152" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E152" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="G152" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -4672,10 +4681,10 @@
         <v>158</v>
       </c>
       <c r="C153" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D153" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -4683,19 +4692,19 @@
         <v>159</v>
       </c>
       <c r="B154" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C154" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D154" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E154" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="G154" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -4703,16 +4712,16 @@
         <v>160</v>
       </c>
       <c r="B155" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C155" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D155" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G155" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -4720,16 +4729,16 @@
         <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C156" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D156" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G156" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -4737,22 +4746,22 @@
         <v>162</v>
       </c>
       <c r="B157" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C157" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D157" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E157" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F157" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="G157" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -4760,19 +4769,19 @@
         <v>163</v>
       </c>
       <c r="B158" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C158" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D158" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E158" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="G158" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -4780,19 +4789,19 @@
         <v>164</v>
       </c>
       <c r="B159" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D159" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E159" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="G159" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -4800,19 +4809,19 @@
         <v>165</v>
       </c>
       <c r="B160" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C160" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D160" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E160" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="G160" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -4820,19 +4829,19 @@
         <v>166</v>
       </c>
       <c r="B161" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C161" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D161" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E161" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G161" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -4840,16 +4849,16 @@
         <v>167</v>
       </c>
       <c r="B162" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C162" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D162" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G162" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -4857,19 +4866,19 @@
         <v>168</v>
       </c>
       <c r="B163" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C163" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D163" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E163" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="G163" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -4877,19 +4886,19 @@
         <v>169</v>
       </c>
       <c r="B164" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C164" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D164" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E164" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="G164" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -4897,13 +4906,13 @@
         <v>170</v>
       </c>
       <c r="C165" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D165" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E165" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -4911,19 +4920,19 @@
         <v>171</v>
       </c>
       <c r="B166" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C166" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D166" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E166" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="G166" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -4931,19 +4940,19 @@
         <v>172</v>
       </c>
       <c r="B167" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C167" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D167" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E167" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="G167" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -4951,19 +4960,19 @@
         <v>173</v>
       </c>
       <c r="B168" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C168" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D168" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E168" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="G168" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -4971,19 +4980,19 @@
         <v>174</v>
       </c>
       <c r="B169" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C169" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D169" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="E169" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="G169" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -4991,13 +5000,13 @@
         <v>175</v>
       </c>
       <c r="C170" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D170" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E170" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5005,13 +5014,13 @@
         <v>176</v>
       </c>
       <c r="C171" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D171" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E171" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5019,13 +5028,13 @@
         <v>177</v>
       </c>
       <c r="C172" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D172" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E172" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5033,16 +5042,16 @@
         <v>178</v>
       </c>
       <c r="B173" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C173" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D173" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G173" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5050,19 +5059,19 @@
         <v>179</v>
       </c>
       <c r="B174" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C174" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D174" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F174" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="G174" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5070,19 +5079,19 @@
         <v>180</v>
       </c>
       <c r="B175" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C175" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F175" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="G175" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5090,10 +5099,10 @@
         <v>181</v>
       </c>
       <c r="C176" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5101,10 +5110,10 @@
         <v>182</v>
       </c>
       <c r="C177" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D177" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5112,10 +5121,10 @@
         <v>183</v>
       </c>
       <c r="C178" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D178" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5123,22 +5132,22 @@
         <v>184</v>
       </c>
       <c r="B179" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C179" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D179" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E179" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F179" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="G179" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5146,10 +5155,10 @@
         <v>185</v>
       </c>
       <c r="C180" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D180" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5157,10 +5166,10 @@
         <v>186</v>
       </c>
       <c r="C181" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D181" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5168,19 +5177,19 @@
         <v>187</v>
       </c>
       <c r="B182" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C182" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D182" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E182" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="G182" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5188,19 +5197,19 @@
         <v>188</v>
       </c>
       <c r="B183" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C183" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D183" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F183" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="G183" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5208,10 +5217,10 @@
         <v>189</v>
       </c>
       <c r="C184" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D184" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5219,13 +5228,13 @@
         <v>190</v>
       </c>
       <c r="C185" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D185" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F185" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5233,13 +5242,13 @@
         <v>191</v>
       </c>
       <c r="C186" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D186" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E186" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5247,13 +5256,13 @@
         <v>192</v>
       </c>
       <c r="C187" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D187" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E187" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5261,13 +5270,13 @@
         <v>193</v>
       </c>
       <c r="C188" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D188" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E188" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5275,13 +5284,13 @@
         <v>194</v>
       </c>
       <c r="C189" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D189" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E189" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5289,13 +5298,13 @@
         <v>195</v>
       </c>
       <c r="C190" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D190" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E190" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5303,10 +5312,10 @@
         <v>196</v>
       </c>
       <c r="C191" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D191" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -5314,10 +5323,10 @@
         <v>197</v>
       </c>
       <c r="C192" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D192" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -5325,10 +5334,10 @@
         <v>198</v>
       </c>
       <c r="C193" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D193" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -5336,16 +5345,16 @@
         <v>199</v>
       </c>
       <c r="B194" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C194" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D194" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="G194" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -5353,16 +5362,16 @@
         <v>200</v>
       </c>
       <c r="B195" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C195" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D195" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="G195" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -5370,19 +5379,19 @@
         <v>201</v>
       </c>
       <c r="B196" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C196" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D196" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F196" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="G196" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -5390,22 +5399,22 @@
         <v>202</v>
       </c>
       <c r="B197" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C197" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D197" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E197" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F197" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="G197" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -5413,22 +5422,22 @@
         <v>203</v>
       </c>
       <c r="B198" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C198" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D198" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E198" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F198" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="G198" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -5436,22 +5445,22 @@
         <v>204</v>
       </c>
       <c r="B199" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C199" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D199" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E199" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="F199" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G199" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -5459,16 +5468,16 @@
         <v>205</v>
       </c>
       <c r="B200" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C200" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D200" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G200" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -5476,10 +5485,10 @@
         <v>206</v>
       </c>
       <c r="C201" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D201" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -5487,10 +5496,10 @@
         <v>207</v>
       </c>
       <c r="C202" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D202" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -5498,10 +5507,10 @@
         <v>208</v>
       </c>
       <c r="C203" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D203" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -5509,16 +5518,16 @@
         <v>209</v>
       </c>
       <c r="B204" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C204" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D204" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G204" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -5526,10 +5535,10 @@
         <v>210</v>
       </c>
       <c r="C205" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D205" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -5537,10 +5546,10 @@
         <v>211</v>
       </c>
       <c r="C206" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D206" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -5548,19 +5557,19 @@
         <v>212</v>
       </c>
       <c r="B207" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C207" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D207" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E207" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G207" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -5568,13 +5577,13 @@
         <v>213</v>
       </c>
       <c r="C208" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D208" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E208" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -5582,10 +5591,10 @@
         <v>214</v>
       </c>
       <c r="C209" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D209" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -5593,19 +5602,19 @@
         <v>215</v>
       </c>
       <c r="B210" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C210" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D210" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E210" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="G210" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -5613,16 +5622,16 @@
         <v>216</v>
       </c>
       <c r="B211" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C211" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D211" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G211" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -5630,13 +5639,13 @@
         <v>217</v>
       </c>
       <c r="C212" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D212" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E212" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -5644,13 +5653,13 @@
         <v>218</v>
       </c>
       <c r="C213" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D213" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E213" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -5658,16 +5667,16 @@
         <v>219</v>
       </c>
       <c r="B214" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C214" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D214" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G214" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -5675,16 +5684,16 @@
         <v>220</v>
       </c>
       <c r="B215" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C215" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D215" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G215" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -5692,13 +5701,13 @@
         <v>221</v>
       </c>
       <c r="C216" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D216" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E216" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -5706,19 +5715,19 @@
         <v>222</v>
       </c>
       <c r="B217" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C217" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D217" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E217" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="G217" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -5726,19 +5735,19 @@
         <v>223</v>
       </c>
       <c r="B218" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C218" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D218" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E218" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="G218" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -5746,19 +5755,19 @@
         <v>224</v>
       </c>
       <c r="B219" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C219" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D219" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E219" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="G219" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -5766,10 +5775,10 @@
         <v>225</v>
       </c>
       <c r="C220" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D220" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -5777,16 +5786,16 @@
         <v>226</v>
       </c>
       <c r="B221" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C221" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D221" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G221" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -5794,19 +5803,19 @@
         <v>227</v>
       </c>
       <c r="B222" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C222" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D222" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E222" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="G222" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -5814,16 +5823,16 @@
         <v>228</v>
       </c>
       <c r="B223" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C223" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D223" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G223" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -5831,16 +5840,16 @@
         <v>229</v>
       </c>
       <c r="B224" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C224" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D224" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="G224" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -5848,19 +5857,19 @@
         <v>230</v>
       </c>
       <c r="B225" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C225" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D225" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F225" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="G225" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -5868,16 +5877,16 @@
         <v>231</v>
       </c>
       <c r="B226" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C226" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D226" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G226" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -5885,10 +5894,27 @@
         <v>232</v>
       </c>
       <c r="C227" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D227" t="s">
-        <v>438</v>
+        <v>441</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228" t="s">
+        <v>233</v>
+      </c>
+      <c r="B228" t="s">
+        <v>416</v>
+      </c>
+      <c r="C228" t="s">
+        <v>440</v>
+      </c>
+      <c r="D228" t="s">
+        <v>441</v>
+      </c>
+      <c r="G228" t="s">
+        <v>540</v>
       </c>
     </row>
   </sheetData>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="538">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -715,9 +715,6 @@
     <t>Maties Underwater Club</t>
   </si>
   <si>
-    <t>Community Service Outreach Test</t>
-  </si>
-  <si>
     <t>info@ctsc.org.za</t>
   </si>
   <si>
@@ -1264,9 +1261,6 @@
     <t>info@capebirdclub.org.za</t>
   </si>
   <si>
-    <t>mrnnsu001@myuct.ac.za</t>
-  </si>
-  <si>
     <t>Museums &amp; Heritage</t>
   </si>
   <si>
@@ -1334,9 +1328,6 @@
   </si>
   <si>
     <t>Hobby &amp; Special Interest Clubs</t>
-  </si>
-  <si>
-    <t>Test</t>
   </si>
   <si>
     <t>Cape Town</t>
@@ -1981,7 +1972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G228"/>
+  <dimension ref="A1:G227"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2012,22 +2003,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="G2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2035,22 +2026,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D3" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E3" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F3" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="G3" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2058,22 +2049,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D4" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E4" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F4" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="G4" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2081,22 +2072,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C5" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D5" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E5" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F5" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="G5" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2104,22 +2095,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D6" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E6" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F6" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="G6" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2127,22 +2118,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C7" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D7" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E7" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F7" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="G7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2150,22 +2141,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C8" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D8" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E8" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F8" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="G8" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2173,22 +2164,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C9" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D9" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E9" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F9" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="G9" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2196,22 +2187,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C10" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D10" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E10" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F10" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="G10" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2219,22 +2210,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C11" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D11" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E11" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F11" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="G11" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2242,22 +2233,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C12" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D12" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E12" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F12" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="G12" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2265,22 +2256,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C13" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D13" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E13" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F13" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="G13" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2288,22 +2279,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C14" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D14" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E14" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="G14" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2311,22 +2302,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C15" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D15" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E15" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="G15" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2334,16 +2325,16 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C16" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D16" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G16" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2351,16 +2342,16 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C17" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D17" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G17" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2368,16 +2359,16 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C18" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D18" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G18" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2385,16 +2376,16 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C19" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D19" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G19" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2402,16 +2393,16 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C20" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D20" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G20" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2419,16 +2410,16 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C21" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D21" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G21" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2436,16 +2427,16 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C22" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D22" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G22" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2453,16 +2444,16 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C23" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D23" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G23" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2470,16 +2461,16 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C24" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D24" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G24" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2487,16 +2478,16 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C25" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D25" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G25" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2504,16 +2495,16 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C26" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D26" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G26" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2521,16 +2512,16 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C27" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D27" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G27" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2538,16 +2529,16 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C28" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D28" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G28" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2555,16 +2546,16 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C29" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D29" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G29" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2572,16 +2563,16 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D30" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G30" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2589,16 +2580,16 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C31" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D31" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G31" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2606,16 +2597,16 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C32" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D32" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G32" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2623,16 +2614,16 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C33" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D33" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G33" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2640,16 +2631,16 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C34" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D34" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G34" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2657,16 +2648,16 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C35" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D35" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G35" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2674,16 +2665,16 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C36" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D36" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G36" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2691,16 +2682,16 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C37" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D37" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G37" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2708,16 +2699,16 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C38" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D38" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G38" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2725,16 +2716,16 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C39" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D39" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G39" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2742,16 +2733,16 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C40" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D40" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G40" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2759,16 +2750,16 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C41" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D41" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G41" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2776,16 +2767,16 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C42" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D42" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G42" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2793,16 +2784,16 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C43" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D43" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G43" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2810,16 +2801,16 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C44" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D44" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G44" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2827,16 +2818,16 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C45" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D45" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G45" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2844,16 +2835,16 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C46" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D46" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G46" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2861,16 +2852,16 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C47" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D47" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G47" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2878,16 +2869,16 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C48" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D48" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G48" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2895,16 +2886,16 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C49" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D49" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G49" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2912,16 +2903,16 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C50" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D50" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G50" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2929,16 +2920,16 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C51" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D51" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G51" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2946,16 +2937,16 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C52" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D52" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G52" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2963,16 +2954,16 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C53" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D53" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G53" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2980,16 +2971,16 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C54" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D54" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G54" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2997,16 +2988,16 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C55" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D55" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G55" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3014,16 +3005,16 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C56" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D56" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G56" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3031,16 +3022,16 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C57" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D57" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G57" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3048,16 +3039,16 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C58" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D58" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G58" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3065,16 +3056,16 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C59" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D59" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G59" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3082,16 +3073,16 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C60" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D60" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G60" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3099,16 +3090,16 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C61" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D61" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G61" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3116,16 +3107,16 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C62" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D62" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G62" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3133,16 +3124,16 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C63" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D63" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G63" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3150,16 +3141,16 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C64" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D64" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G64" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3167,16 +3158,16 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C65" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D65" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G65" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3184,16 +3175,16 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C66" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D66" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G66" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3201,16 +3192,16 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C67" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D67" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G67" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3218,16 +3209,16 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C68" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D68" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G68" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3235,16 +3226,16 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C69" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D69" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G69" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3252,16 +3243,16 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C70" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D70" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G70" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3269,16 +3260,16 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C71" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D71" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G71" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3286,16 +3277,16 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C72" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D72" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G72" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3303,16 +3294,16 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C73" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D73" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G73" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3320,16 +3311,16 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C74" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D74" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G74" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3337,16 +3328,16 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C75" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D75" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G75" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3354,16 +3345,16 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C76" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D76" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G76" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3371,16 +3362,16 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C77" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D77" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G77" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3388,16 +3379,16 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C78" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D78" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G78" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3405,16 +3396,16 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C79" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D79" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G79" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3422,16 +3413,16 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C80" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D80" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G80" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3439,16 +3430,16 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C81" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D81" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G81" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3456,16 +3447,16 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C82" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D82" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G82" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3473,16 +3464,16 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C83" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D83" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G83" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3490,16 +3481,16 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C84" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D84" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G84" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3507,16 +3498,16 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C85" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D85" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G85" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3524,16 +3515,16 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C86" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D86" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G86" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3541,16 +3532,16 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C87" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D87" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G87" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3558,16 +3549,16 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C88" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D88" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G88" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3575,16 +3566,16 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C89" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D89" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G89" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3592,16 +3583,16 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C90" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D90" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G90" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3609,16 +3600,16 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C91" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D91" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G91" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3626,16 +3617,16 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C92" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D92" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G92" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3643,16 +3634,16 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C93" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D93" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G93" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3660,16 +3651,16 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C94" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D94" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G94" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3677,16 +3668,16 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C95" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D95" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G95" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3694,16 +3685,16 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C96" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D96" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G96" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3711,16 +3702,16 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C97" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D97" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G97" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3728,16 +3719,16 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C98" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D98" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G98" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -3745,16 +3736,16 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C99" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D99" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G99" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -3762,16 +3753,16 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C100" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D100" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G100" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -3779,16 +3770,16 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C101" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D101" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G101" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -3796,16 +3787,16 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C102" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D102" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G102" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -3813,16 +3804,16 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C103" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D103" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G103" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -3830,16 +3821,16 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C104" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D104" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G104" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -3847,16 +3838,16 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C105" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D105" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G105" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -3864,16 +3855,16 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C106" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D106" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G106" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -3881,16 +3872,16 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C107" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D107" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G107" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -3898,16 +3889,16 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C108" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D108" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G108" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -3915,16 +3906,16 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C109" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D109" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G109" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -3932,16 +3923,16 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C110" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D110" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G110" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -3949,16 +3940,16 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C111" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D111" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G111" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -3966,16 +3957,16 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C112" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D112" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G112" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -3983,16 +3974,16 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C113" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D113" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G113" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4000,16 +3991,16 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C114" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D114" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G114" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4017,16 +4008,16 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C115" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D115" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G115" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4034,16 +4025,16 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C116" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D116" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G116" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4051,16 +4042,16 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C117" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D117" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G117" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4068,16 +4059,16 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C118" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D118" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G118" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4085,22 +4076,22 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C119" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D119" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E119" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="F119" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="G119" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4108,19 +4099,19 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C120" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D120" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E120" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="G120" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4128,16 +4119,16 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C121" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D121" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G121" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4145,16 +4136,16 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C122" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D122" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="G122" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4162,22 +4153,22 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C123" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D123" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E123" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="F123" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G123" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4185,16 +4176,16 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C124" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D124" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G124" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4202,16 +4193,16 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C125" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D125" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G125" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4219,16 +4210,16 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C126" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D126" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G126" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4236,16 +4227,16 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C127" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D127" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G127" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4253,19 +4244,19 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C128" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D128" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E128" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="G128" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4273,22 +4264,22 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C129" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D129" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E129" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="F129" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="G129" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4296,16 +4287,16 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C130" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D130" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G130" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4313,13 +4304,13 @@
         <v>136</v>
       </c>
       <c r="C131" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D131" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E131" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4327,19 +4318,19 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C132" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D132" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E132" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="G132" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4347,19 +4338,19 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C133" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D133" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E133" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="G133" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4367,10 +4358,10 @@
         <v>139</v>
       </c>
       <c r="C134" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D134" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4378,10 +4369,10 @@
         <v>140</v>
       </c>
       <c r="C135" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D135" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4389,16 +4380,16 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C136" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D136" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G136" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4406,16 +4397,16 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C137" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D137" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="G137" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4423,10 +4414,10 @@
         <v>143</v>
       </c>
       <c r="C138" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D138" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4434,10 +4425,10 @@
         <v>144</v>
       </c>
       <c r="C139" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D139" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4445,10 +4436,10 @@
         <v>145</v>
       </c>
       <c r="C140" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D140" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4456,16 +4447,16 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C141" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D141" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G141" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4473,22 +4464,22 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C142" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D142" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E142" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F142" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="G142" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4496,16 +4487,16 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C143" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D143" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="G143" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4513,13 +4504,13 @@
         <v>149</v>
       </c>
       <c r="C144" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D144" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E144" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4527,10 +4518,10 @@
         <v>150</v>
       </c>
       <c r="C145" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D145" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4538,19 +4529,19 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C146" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D146" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F146" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="G146" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -4558,22 +4549,22 @@
         <v>152</v>
       </c>
       <c r="B147" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C147" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D147" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E147" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F147" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="G147" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -4581,19 +4572,19 @@
         <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C148" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D148" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E148" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="G148" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -4601,19 +4592,19 @@
         <v>154</v>
       </c>
       <c r="B149" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C149" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D149" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E149" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="G149" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -4621,19 +4612,19 @@
         <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C150" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D150" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E150" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="G150" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -4641,19 +4632,19 @@
         <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C151" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D151" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E151" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="G151" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -4661,19 +4652,19 @@
         <v>157</v>
       </c>
       <c r="B152" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C152" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D152" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E152" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="G152" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -4681,10 +4672,10 @@
         <v>158</v>
       </c>
       <c r="C153" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D153" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -4692,19 +4683,19 @@
         <v>159</v>
       </c>
       <c r="B154" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C154" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D154" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E154" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="G154" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -4712,16 +4703,16 @@
         <v>160</v>
       </c>
       <c r="B155" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C155" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D155" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G155" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -4729,16 +4720,16 @@
         <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C156" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D156" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G156" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -4746,22 +4737,22 @@
         <v>162</v>
       </c>
       <c r="B157" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C157" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D157" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E157" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F157" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="G157" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -4769,19 +4760,19 @@
         <v>163</v>
       </c>
       <c r="B158" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C158" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D158" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E158" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="G158" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -4789,19 +4780,19 @@
         <v>164</v>
       </c>
       <c r="B159" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C159" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D159" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E159" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="G159" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -4809,19 +4800,19 @@
         <v>165</v>
       </c>
       <c r="B160" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C160" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D160" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E160" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="G160" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -4829,19 +4820,19 @@
         <v>166</v>
       </c>
       <c r="B161" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C161" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D161" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E161" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="G161" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -4849,16 +4840,16 @@
         <v>167</v>
       </c>
       <c r="B162" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C162" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D162" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G162" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -4866,19 +4857,19 @@
         <v>168</v>
       </c>
       <c r="B163" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C163" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D163" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E163" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="G163" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -4886,19 +4877,19 @@
         <v>169</v>
       </c>
       <c r="B164" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C164" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D164" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E164" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="G164" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -4906,13 +4897,13 @@
         <v>170</v>
       </c>
       <c r="C165" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D165" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E165" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -4920,19 +4911,19 @@
         <v>171</v>
       </c>
       <c r="B166" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C166" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D166" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E166" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="G166" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -4940,19 +4931,19 @@
         <v>172</v>
       </c>
       <c r="B167" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C167" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D167" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E167" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="G167" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -4960,19 +4951,19 @@
         <v>173</v>
       </c>
       <c r="B168" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C168" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D168" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E168" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="G168" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -4980,19 +4971,19 @@
         <v>174</v>
       </c>
       <c r="B169" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C169" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D169" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E169" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="G169" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5000,13 +4991,13 @@
         <v>175</v>
       </c>
       <c r="C170" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D170" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E170" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5014,13 +5005,13 @@
         <v>176</v>
       </c>
       <c r="C171" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D171" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E171" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5028,13 +5019,13 @@
         <v>177</v>
       </c>
       <c r="C172" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D172" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E172" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5042,16 +5033,16 @@
         <v>178</v>
       </c>
       <c r="B173" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C173" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D173" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G173" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5059,19 +5050,19 @@
         <v>179</v>
       </c>
       <c r="B174" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C174" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D174" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F174" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="G174" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5079,19 +5070,19 @@
         <v>180</v>
       </c>
       <c r="B175" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C175" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D175" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F175" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="G175" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5099,10 +5090,10 @@
         <v>181</v>
       </c>
       <c r="C176" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D176" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5110,10 +5101,10 @@
         <v>182</v>
       </c>
       <c r="C177" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D177" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5121,10 +5112,10 @@
         <v>183</v>
       </c>
       <c r="C178" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5132,22 +5123,22 @@
         <v>184</v>
       </c>
       <c r="B179" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C179" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D179" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E179" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="F179" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="G179" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5155,10 +5146,10 @@
         <v>185</v>
       </c>
       <c r="C180" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D180" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5166,10 +5157,10 @@
         <v>186</v>
       </c>
       <c r="C181" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D181" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5177,19 +5168,19 @@
         <v>187</v>
       </c>
       <c r="B182" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C182" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D182" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E182" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="G182" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5197,19 +5188,19 @@
         <v>188</v>
       </c>
       <c r="B183" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C183" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D183" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F183" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="G183" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5217,10 +5208,10 @@
         <v>189</v>
       </c>
       <c r="C184" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D184" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5228,13 +5219,13 @@
         <v>190</v>
       </c>
       <c r="C185" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D185" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F185" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5242,13 +5233,13 @@
         <v>191</v>
       </c>
       <c r="C186" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D186" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E186" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5256,13 +5247,13 @@
         <v>192</v>
       </c>
       <c r="C187" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D187" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E187" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5270,13 +5261,13 @@
         <v>193</v>
       </c>
       <c r="C188" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D188" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E188" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5284,13 +5275,13 @@
         <v>194</v>
       </c>
       <c r="C189" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D189" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E189" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5298,13 +5289,13 @@
         <v>195</v>
       </c>
       <c r="C190" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D190" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E190" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5312,10 +5303,10 @@
         <v>196</v>
       </c>
       <c r="C191" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D191" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -5323,10 +5314,10 @@
         <v>197</v>
       </c>
       <c r="C192" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D192" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -5334,10 +5325,10 @@
         <v>198</v>
       </c>
       <c r="C193" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D193" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -5345,16 +5336,16 @@
         <v>199</v>
       </c>
       <c r="B194" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C194" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D194" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="G194" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -5362,16 +5353,16 @@
         <v>200</v>
       </c>
       <c r="B195" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C195" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D195" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="G195" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -5379,19 +5370,19 @@
         <v>201</v>
       </c>
       <c r="B196" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C196" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D196" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F196" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="G196" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -5399,22 +5390,22 @@
         <v>202</v>
       </c>
       <c r="B197" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C197" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D197" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E197" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="F197" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="G197" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -5422,22 +5413,22 @@
         <v>203</v>
       </c>
       <c r="B198" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C198" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D198" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E198" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="F198" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="G198" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -5445,22 +5436,22 @@
         <v>204</v>
       </c>
       <c r="B199" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C199" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D199" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E199" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="F199" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="G199" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -5468,16 +5459,16 @@
         <v>205</v>
       </c>
       <c r="B200" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C200" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D200" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G200" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -5485,10 +5476,10 @@
         <v>206</v>
       </c>
       <c r="C201" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D201" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -5496,10 +5487,10 @@
         <v>207</v>
       </c>
       <c r="C202" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D202" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -5507,10 +5498,10 @@
         <v>208</v>
       </c>
       <c r="C203" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D203" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -5518,16 +5509,16 @@
         <v>209</v>
       </c>
       <c r="B204" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C204" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D204" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G204" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -5535,10 +5526,10 @@
         <v>210</v>
       </c>
       <c r="C205" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D205" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -5546,10 +5537,10 @@
         <v>211</v>
       </c>
       <c r="C206" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D206" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -5557,19 +5548,19 @@
         <v>212</v>
       </c>
       <c r="B207" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C207" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D207" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E207" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="G207" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -5577,13 +5568,13 @@
         <v>213</v>
       </c>
       <c r="C208" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D208" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E208" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -5591,10 +5582,10 @@
         <v>214</v>
       </c>
       <c r="C209" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D209" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -5602,19 +5593,19 @@
         <v>215</v>
       </c>
       <c r="B210" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C210" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D210" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E210" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="G210" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -5622,16 +5613,16 @@
         <v>216</v>
       </c>
       <c r="B211" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C211" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D211" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G211" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -5639,13 +5630,13 @@
         <v>217</v>
       </c>
       <c r="C212" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D212" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E212" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -5653,13 +5644,13 @@
         <v>218</v>
       </c>
       <c r="C213" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D213" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E213" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -5667,16 +5658,16 @@
         <v>219</v>
       </c>
       <c r="B214" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C214" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D214" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G214" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -5684,16 +5675,16 @@
         <v>220</v>
       </c>
       <c r="B215" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C215" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D215" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G215" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -5701,13 +5692,13 @@
         <v>221</v>
       </c>
       <c r="C216" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D216" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E216" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -5715,19 +5706,19 @@
         <v>222</v>
       </c>
       <c r="B217" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C217" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D217" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E217" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="G217" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -5735,19 +5726,19 @@
         <v>223</v>
       </c>
       <c r="B218" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C218" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D218" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E218" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="G218" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -5755,19 +5746,19 @@
         <v>224</v>
       </c>
       <c r="B219" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C219" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D219" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E219" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="G219" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -5775,10 +5766,10 @@
         <v>225</v>
       </c>
       <c r="C220" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D220" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -5786,16 +5777,16 @@
         <v>226</v>
       </c>
       <c r="B221" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C221" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D221" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G221" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -5803,19 +5794,19 @@
         <v>227</v>
       </c>
       <c r="B222" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C222" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D222" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E222" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="G222" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -5823,16 +5814,16 @@
         <v>228</v>
       </c>
       <c r="B223" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C223" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D223" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G223" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -5840,16 +5831,16 @@
         <v>229</v>
       </c>
       <c r="B224" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C224" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D224" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="G224" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -5857,19 +5848,19 @@
         <v>230</v>
       </c>
       <c r="B225" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C225" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D225" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F225" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="G225" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -5877,16 +5868,16 @@
         <v>231</v>
       </c>
       <c r="B226" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C226" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D226" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="G226" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -5894,27 +5885,10 @@
         <v>232</v>
       </c>
       <c r="C227" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D227" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7">
-      <c r="A228" t="s">
-        <v>233</v>
-      </c>
-      <c r="B228" t="s">
-        <v>416</v>
-      </c>
-      <c r="C228" t="s">
-        <v>440</v>
-      </c>
-      <c r="D228" t="s">
-        <v>441</v>
-      </c>
-      <c r="G228" t="s">
-        <v>540</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="614">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -715,6 +715,120 @@
     <t>Maties Underwater Club</t>
   </si>
   <si>
+    <t>ACVV Somerset West</t>
+  </si>
+  <si>
+    <t>ACVV Cape Town</t>
+  </si>
+  <si>
+    <t>CINADE Frailcare Support</t>
+  </si>
+  <si>
+    <t>Gabriella Centre</t>
+  </si>
+  <si>
+    <t>Halli Trust</t>
+  </si>
+  <si>
+    <t>House of Boniwe</t>
+  </si>
+  <si>
+    <t>Souper Troopers</t>
+  </si>
+  <si>
+    <t>uManity Foundation</t>
+  </si>
+  <si>
+    <t>Common Good Foundation</t>
+  </si>
+  <si>
+    <t>Amava Oluntu</t>
+  </si>
+  <si>
+    <t>Union of Jewish Women</t>
+  </si>
+  <si>
+    <t>Catholic Welfare &amp; Development</t>
+  </si>
+  <si>
+    <t>Alulia Pty Ltd</t>
+  </si>
+  <si>
+    <t>Anene Booysen Skills Centre</t>
+  </si>
+  <si>
+    <t>Angels Resource Centres</t>
+  </si>
+  <si>
+    <t>Ayakhanya Foundation</t>
+  </si>
+  <si>
+    <t>SOS Africa</t>
+  </si>
+  <si>
+    <t>The Y Collab</t>
+  </si>
+  <si>
+    <t>African Legend</t>
+  </si>
+  <si>
+    <t>BeSmartKid</t>
+  </si>
+  <si>
+    <t>Teach Me 2</t>
+  </si>
+  <si>
+    <t>Paws-a-While</t>
+  </si>
+  <si>
+    <t>Tom Ro Haven</t>
+  </si>
+  <si>
+    <t>Foundation for Contemporary Research</t>
+  </si>
+  <si>
+    <t>Parkscape Association</t>
+  </si>
+  <si>
+    <t>Friends of the Liesbeek</t>
+  </si>
+  <si>
+    <t>Freshwater Research Centre</t>
+  </si>
+  <si>
+    <t>Friends of Blaauwberg</t>
+  </si>
+  <si>
+    <t>Orange Art Project</t>
+  </si>
+  <si>
+    <t>Jazzart Dance Theatre</t>
+  </si>
+  <si>
+    <t>Elim Night Shelter</t>
+  </si>
+  <si>
+    <t>Happy Valley</t>
+  </si>
+  <si>
+    <t>Loaves and Fishes</t>
+  </si>
+  <si>
+    <t>Moira Henderson House</t>
+  </si>
+  <si>
+    <t>Oasis Reach for Your Dream</t>
+  </si>
+  <si>
+    <t>Somerset West Night Shelter</t>
+  </si>
+  <si>
+    <t>The Haven Night Shelter - Bellville</t>
+  </si>
+  <si>
+    <t>The Haven Night Shelter - Claremont</t>
+  </si>
+  <si>
     <t>info@ctsc.org.za</t>
   </si>
   <si>
@@ -1259,6 +1373,120 @@
   </si>
   <si>
     <t>info@capebirdclub.org.za</t>
+  </si>
+  <si>
+    <t>ACVVSWE@TELKOMSA.NET</t>
+  </si>
+  <si>
+    <t>tamara@acvv.org.za</t>
+  </si>
+  <si>
+    <t>WILMAPAPIER2@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>INFO@GABRIELLACENTRE.ORG.ZA</t>
+  </si>
+  <si>
+    <t>HEIDI@HALLITRUST.CO.ZA</t>
+  </si>
+  <si>
+    <t>gwenj@houseofboniwe.co.za</t>
+  </si>
+  <si>
+    <t>kerry@soupertroopers.org</t>
+  </si>
+  <si>
+    <t>Darryn.Hector@uManity.co.za</t>
+  </si>
+  <si>
+    <t>info@commongood.org.za</t>
+  </si>
+  <si>
+    <t>info@amava.org</t>
+  </si>
+  <si>
+    <t>projects@ujwcape.co.za</t>
+  </si>
+  <si>
+    <t>zukile.tom@cwd.co.za</t>
+  </si>
+  <si>
+    <t>andile@alulia.co.za</t>
+  </si>
+  <si>
+    <t>solutionsbasenpo@outlook.com</t>
+  </si>
+  <si>
+    <t>angels@angelsinc.co.za</t>
+  </si>
+  <si>
+    <t>Ayakhanya@gmail.com</t>
+  </si>
+  <si>
+    <t>matt@sosafrica.com</t>
+  </si>
+  <si>
+    <t>meg@y-collab.com</t>
+  </si>
+  <si>
+    <t>katja@africanlegend.org.za</t>
+  </si>
+  <si>
+    <t>bsktutors@gmail.com</t>
+  </si>
+  <si>
+    <t>start@teachme2.com</t>
+  </si>
+  <si>
+    <t>info@pawsawhile.org</t>
+  </si>
+  <si>
+    <t>info@tomrohaven.org.za</t>
+  </si>
+  <si>
+    <t>info@fcr.org.za</t>
+  </si>
+  <si>
+    <t>info@parkscape.org.za</t>
+  </si>
+  <si>
+    <t>info@fol.org.za</t>
+  </si>
+  <si>
+    <t>admin@frcsa.org.za</t>
+  </si>
+  <si>
+    <t>Friendsofbca@mweb.co.za</t>
+  </si>
+  <si>
+    <t>info@orangeart.org.za</t>
+  </si>
+  <si>
+    <t>dance@jazzart.co.za</t>
+  </si>
+  <si>
+    <t>elimnightshelter@telkomsa.net</t>
+  </si>
+  <si>
+    <t>cynn@telkomsa.net</t>
+  </si>
+  <si>
+    <t>loavesfishes@telkomsa.net</t>
+  </si>
+  <si>
+    <t>moirahenderson@haven.org.za</t>
+  </si>
+  <si>
+    <t>oasisplace@mweb.co.za</t>
+  </si>
+  <si>
+    <t>manager@swnightshelter.org.za</t>
+  </si>
+  <si>
+    <t>sharon@haven.org.za</t>
+  </si>
+  <si>
+    <t>claremont@haven.org.za</t>
   </si>
   <si>
     <t>Museums &amp; Heritage</t>
@@ -1972,7 +2200,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G227"/>
+  <dimension ref="A1:G265"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2003,22 +2231,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>233</v>
+        <v>271</v>
       </c>
       <c r="C2" t="s">
-        <v>415</v>
+        <v>491</v>
       </c>
       <c r="D2" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E2" t="s">
-        <v>463</v>
+        <v>539</v>
       </c>
       <c r="F2" t="s">
-        <v>517</v>
+        <v>593</v>
       </c>
       <c r="G2" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2026,22 +2254,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="C3" t="s">
-        <v>415</v>
+        <v>491</v>
       </c>
       <c r="D3" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E3" t="s">
-        <v>463</v>
+        <v>539</v>
       </c>
       <c r="F3" t="s">
-        <v>517</v>
+        <v>593</v>
       </c>
       <c r="G3" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2049,22 +2277,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>235</v>
+        <v>273</v>
       </c>
       <c r="C4" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D4" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E4" t="s">
-        <v>463</v>
+        <v>539</v>
       </c>
       <c r="F4" t="s">
-        <v>517</v>
+        <v>593</v>
       </c>
       <c r="G4" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2072,22 +2300,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>236</v>
+        <v>274</v>
       </c>
       <c r="C5" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D5" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E5" t="s">
-        <v>463</v>
+        <v>539</v>
       </c>
       <c r="F5" t="s">
-        <v>517</v>
+        <v>593</v>
       </c>
       <c r="G5" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2095,22 +2323,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>237</v>
+        <v>275</v>
       </c>
       <c r="C6" t="s">
-        <v>415</v>
+        <v>491</v>
       </c>
       <c r="D6" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E6" t="s">
-        <v>463</v>
+        <v>539</v>
       </c>
       <c r="F6" t="s">
-        <v>517</v>
+        <v>593</v>
       </c>
       <c r="G6" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2118,22 +2346,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>238</v>
+        <v>276</v>
       </c>
       <c r="C7" t="s">
-        <v>415</v>
+        <v>491</v>
       </c>
       <c r="D7" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E7" t="s">
-        <v>463</v>
+        <v>539</v>
       </c>
       <c r="F7" t="s">
-        <v>517</v>
+        <v>593</v>
       </c>
       <c r="G7" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2141,22 +2369,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>239</v>
+        <v>277</v>
       </c>
       <c r="C8" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D8" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E8" t="s">
-        <v>463</v>
+        <v>539</v>
       </c>
       <c r="F8" t="s">
-        <v>517</v>
+        <v>593</v>
       </c>
       <c r="G8" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2164,22 +2392,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>240</v>
+        <v>278</v>
       </c>
       <c r="C9" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D9" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E9" t="s">
-        <v>463</v>
+        <v>539</v>
       </c>
       <c r="F9" t="s">
-        <v>517</v>
+        <v>593</v>
       </c>
       <c r="G9" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2187,22 +2415,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>241</v>
+        <v>279</v>
       </c>
       <c r="C10" t="s">
-        <v>417</v>
+        <v>493</v>
       </c>
       <c r="D10" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E10" t="s">
-        <v>463</v>
+        <v>539</v>
       </c>
       <c r="F10" t="s">
-        <v>517</v>
+        <v>593</v>
       </c>
       <c r="G10" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2210,22 +2438,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>242</v>
+        <v>280</v>
       </c>
       <c r="C11" t="s">
-        <v>417</v>
+        <v>493</v>
       </c>
       <c r="D11" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E11" t="s">
-        <v>463</v>
+        <v>539</v>
       </c>
       <c r="F11" t="s">
-        <v>517</v>
+        <v>593</v>
       </c>
       <c r="G11" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2233,22 +2461,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>243</v>
+        <v>281</v>
       </c>
       <c r="C12" t="s">
-        <v>418</v>
+        <v>494</v>
       </c>
       <c r="D12" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E12" t="s">
-        <v>463</v>
+        <v>539</v>
       </c>
       <c r="F12" t="s">
-        <v>517</v>
+        <v>593</v>
       </c>
       <c r="G12" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2256,22 +2484,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="C13" t="s">
-        <v>415</v>
+        <v>491</v>
       </c>
       <c r="D13" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E13" t="s">
-        <v>463</v>
+        <v>539</v>
       </c>
       <c r="F13" t="s">
-        <v>517</v>
+        <v>593</v>
       </c>
       <c r="G13" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2279,22 +2507,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="C14" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D14" t="s">
-        <v>439</v>
+        <v>515</v>
       </c>
       <c r="E14" t="s">
-        <v>464</v>
+        <v>540</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>518</v>
+        <v>594</v>
       </c>
       <c r="G14" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2302,22 +2530,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>246</v>
+        <v>284</v>
       </c>
       <c r="C15" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D15" t="s">
-        <v>439</v>
+        <v>515</v>
       </c>
       <c r="E15" t="s">
-        <v>465</v>
+        <v>541</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>519</v>
+        <v>595</v>
       </c>
       <c r="G15" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2325,16 +2553,16 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="C16" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="D16" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G16" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2342,16 +2570,16 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="C17" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="D17" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G17" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2359,16 +2587,16 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>249</v>
+        <v>287</v>
       </c>
       <c r="C18" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="D18" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G18" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2376,16 +2604,16 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>250</v>
+        <v>288</v>
       </c>
       <c r="C19" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="D19" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G19" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2393,16 +2621,16 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>251</v>
+        <v>289</v>
       </c>
       <c r="C20" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="D20" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G20" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2410,16 +2638,16 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>252</v>
+        <v>290</v>
       </c>
       <c r="C21" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="D21" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G21" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2427,16 +2655,16 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>253</v>
+        <v>291</v>
       </c>
       <c r="C22" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="D22" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G22" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2444,16 +2672,16 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>254</v>
+        <v>292</v>
       </c>
       <c r="C23" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="D23" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G23" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2461,16 +2689,16 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>255</v>
+        <v>293</v>
       </c>
       <c r="C24" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="D24" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G24" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2478,16 +2706,16 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>256</v>
+        <v>294</v>
       </c>
       <c r="C25" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="D25" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G25" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2495,16 +2723,16 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>257</v>
+        <v>295</v>
       </c>
       <c r="C26" t="s">
-        <v>421</v>
+        <v>497</v>
       </c>
       <c r="D26" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G26" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2512,16 +2740,16 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>258</v>
+        <v>296</v>
       </c>
       <c r="C27" t="s">
-        <v>421</v>
+        <v>497</v>
       </c>
       <c r="D27" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G27" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2529,16 +2757,16 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="C28" t="s">
-        <v>421</v>
+        <v>497</v>
       </c>
       <c r="D28" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G28" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2546,16 +2774,16 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>260</v>
+        <v>298</v>
       </c>
       <c r="C29" t="s">
-        <v>421</v>
+        <v>497</v>
       </c>
       <c r="D29" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G29" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2563,16 +2791,16 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>261</v>
+        <v>299</v>
       </c>
       <c r="C30" t="s">
-        <v>421</v>
+        <v>497</v>
       </c>
       <c r="D30" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G30" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2580,16 +2808,16 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>262</v>
+        <v>300</v>
       </c>
       <c r="C31" t="s">
-        <v>421</v>
+        <v>497</v>
       </c>
       <c r="D31" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G31" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2597,16 +2825,16 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>263</v>
+        <v>301</v>
       </c>
       <c r="C32" t="s">
-        <v>421</v>
+        <v>497</v>
       </c>
       <c r="D32" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G32" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2614,16 +2842,16 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>264</v>
+        <v>302</v>
       </c>
       <c r="C33" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D33" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G33" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2631,16 +2859,16 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>265</v>
+        <v>303</v>
       </c>
       <c r="C34" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D34" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G34" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2648,16 +2876,16 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>266</v>
+        <v>304</v>
       </c>
       <c r="C35" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D35" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G35" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2665,16 +2893,16 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>267</v>
+        <v>305</v>
       </c>
       <c r="C36" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D36" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G36" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2682,16 +2910,16 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="C37" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D37" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G37" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2699,16 +2927,16 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>269</v>
+        <v>307</v>
       </c>
       <c r="C38" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D38" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G38" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2716,16 +2944,16 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>270</v>
+        <v>308</v>
       </c>
       <c r="C39" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D39" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G39" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2733,16 +2961,16 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>271</v>
+        <v>309</v>
       </c>
       <c r="C40" t="s">
-        <v>423</v>
+        <v>499</v>
       </c>
       <c r="D40" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G40" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2750,16 +2978,16 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="C41" t="s">
-        <v>423</v>
+        <v>499</v>
       </c>
       <c r="D41" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G41" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2767,16 +2995,16 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>273</v>
+        <v>311</v>
       </c>
       <c r="C42" t="s">
-        <v>423</v>
+        <v>499</v>
       </c>
       <c r="D42" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G42" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2784,16 +3012,16 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>274</v>
+        <v>312</v>
       </c>
       <c r="C43" t="s">
-        <v>423</v>
+        <v>499</v>
       </c>
       <c r="D43" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G43" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2801,16 +3029,16 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>275</v>
+        <v>313</v>
       </c>
       <c r="C44" t="s">
-        <v>423</v>
+        <v>499</v>
       </c>
       <c r="D44" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G44" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2818,16 +3046,16 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>276</v>
+        <v>314</v>
       </c>
       <c r="C45" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D45" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G45" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2835,16 +3063,16 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>277</v>
+        <v>315</v>
       </c>
       <c r="C46" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D46" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G46" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2852,16 +3080,16 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>278</v>
+        <v>316</v>
       </c>
       <c r="C47" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D47" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G47" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2869,16 +3097,16 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>279</v>
+        <v>317</v>
       </c>
       <c r="C48" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D48" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G48" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2886,16 +3114,16 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>280</v>
+        <v>318</v>
       </c>
       <c r="C49" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D49" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G49" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2903,16 +3131,16 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>281</v>
+        <v>319</v>
       </c>
       <c r="C50" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D50" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G50" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2920,16 +3148,16 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>282</v>
+        <v>320</v>
       </c>
       <c r="C51" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D51" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G51" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2937,16 +3165,16 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="C52" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D52" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G52" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2954,16 +3182,16 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="C53" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D53" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G53" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2971,16 +3199,16 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>285</v>
+        <v>323</v>
       </c>
       <c r="C54" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D54" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G54" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2988,16 +3216,16 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>286</v>
+        <v>324</v>
       </c>
       <c r="C55" t="s">
-        <v>424</v>
+        <v>500</v>
       </c>
       <c r="D55" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G55" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3005,16 +3233,16 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>287</v>
+        <v>325</v>
       </c>
       <c r="C56" t="s">
-        <v>424</v>
+        <v>500</v>
       </c>
       <c r="D56" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G56" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3022,16 +3250,16 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="C57" t="s">
-        <v>424</v>
+        <v>500</v>
       </c>
       <c r="D57" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G57" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3039,16 +3267,16 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="C58" t="s">
-        <v>425</v>
+        <v>501</v>
       </c>
       <c r="D58" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G58" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3056,16 +3284,16 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="C59" t="s">
-        <v>425</v>
+        <v>501</v>
       </c>
       <c r="D59" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G59" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3073,16 +3301,16 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>291</v>
+        <v>329</v>
       </c>
       <c r="C60" t="s">
-        <v>425</v>
+        <v>501</v>
       </c>
       <c r="D60" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G60" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3090,16 +3318,16 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>292</v>
+        <v>330</v>
       </c>
       <c r="C61" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="D61" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G61" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3107,16 +3335,16 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>293</v>
+        <v>331</v>
       </c>
       <c r="C62" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="D62" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G62" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3124,16 +3352,16 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>294</v>
+        <v>332</v>
       </c>
       <c r="C63" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="D63" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G63" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3141,16 +3369,16 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>295</v>
+        <v>333</v>
       </c>
       <c r="C64" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="D64" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G64" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3158,16 +3386,16 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>296</v>
+        <v>334</v>
       </c>
       <c r="C65" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="D65" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G65" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3175,16 +3403,16 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>297</v>
+        <v>335</v>
       </c>
       <c r="C66" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="D66" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G66" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3192,16 +3420,16 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>298</v>
+        <v>336</v>
       </c>
       <c r="C67" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="D67" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G67" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3209,16 +3437,16 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>299</v>
+        <v>337</v>
       </c>
       <c r="C68" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="D68" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G68" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3226,16 +3454,16 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>300</v>
+        <v>338</v>
       </c>
       <c r="C69" t="s">
-        <v>421</v>
+        <v>497</v>
       </c>
       <c r="D69" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G69" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3243,16 +3471,16 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>301</v>
+        <v>339</v>
       </c>
       <c r="C70" t="s">
-        <v>421</v>
+        <v>497</v>
       </c>
       <c r="D70" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G70" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3260,16 +3488,16 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>302</v>
+        <v>340</v>
       </c>
       <c r="C71" t="s">
-        <v>421</v>
+        <v>497</v>
       </c>
       <c r="D71" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G71" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3277,16 +3505,16 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>303</v>
+        <v>341</v>
       </c>
       <c r="C72" t="s">
-        <v>421</v>
+        <v>497</v>
       </c>
       <c r="D72" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G72" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3294,16 +3522,16 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>304</v>
+        <v>342</v>
       </c>
       <c r="C73" t="s">
-        <v>421</v>
+        <v>497</v>
       </c>
       <c r="D73" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G73" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3311,16 +3539,16 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>305</v>
+        <v>343</v>
       </c>
       <c r="C74" t="s">
-        <v>421</v>
+        <v>497</v>
       </c>
       <c r="D74" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G74" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3328,16 +3556,16 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>306</v>
+        <v>344</v>
       </c>
       <c r="C75" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D75" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G75" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3345,16 +3573,16 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>307</v>
+        <v>345</v>
       </c>
       <c r="C76" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D76" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G76" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3362,16 +3590,16 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>308</v>
+        <v>346</v>
       </c>
       <c r="C77" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D77" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G77" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3379,16 +3607,16 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>309</v>
+        <v>347</v>
       </c>
       <c r="C78" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D78" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G78" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3396,16 +3624,16 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="C79" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D79" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G79" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3413,16 +3641,16 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>311</v>
+        <v>349</v>
       </c>
       <c r="C80" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D80" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G80" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3430,16 +3658,16 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>312</v>
+        <v>350</v>
       </c>
       <c r="C81" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D81" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G81" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3447,16 +3675,16 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>313</v>
+        <v>351</v>
       </c>
       <c r="C82" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D82" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G82" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3464,16 +3692,16 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>314</v>
+        <v>352</v>
       </c>
       <c r="C83" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D83" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G83" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3481,16 +3709,16 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>315</v>
+        <v>353</v>
       </c>
       <c r="C84" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D84" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G84" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3498,16 +3726,16 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>316</v>
+        <v>354</v>
       </c>
       <c r="C85" t="s">
-        <v>423</v>
+        <v>499</v>
       </c>
       <c r="D85" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G85" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3515,16 +3743,16 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>317</v>
+        <v>355</v>
       </c>
       <c r="C86" t="s">
-        <v>423</v>
+        <v>499</v>
       </c>
       <c r="D86" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G86" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3532,16 +3760,16 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>318</v>
+        <v>356</v>
       </c>
       <c r="C87" t="s">
-        <v>423</v>
+        <v>499</v>
       </c>
       <c r="D87" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G87" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3549,16 +3777,16 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="C88" t="s">
-        <v>423</v>
+        <v>499</v>
       </c>
       <c r="D88" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G88" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3566,16 +3794,16 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="C89" t="s">
-        <v>423</v>
+        <v>499</v>
       </c>
       <c r="D89" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G89" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3583,16 +3811,16 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
       <c r="C90" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D90" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G90" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3600,16 +3828,16 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>322</v>
+        <v>360</v>
       </c>
       <c r="C91" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D91" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G91" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3617,16 +3845,16 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>323</v>
+        <v>361</v>
       </c>
       <c r="C92" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D92" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G92" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3634,16 +3862,16 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>324</v>
+        <v>362</v>
       </c>
       <c r="C93" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D93" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G93" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3651,16 +3879,16 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>325</v>
+        <v>363</v>
       </c>
       <c r="C94" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D94" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G94" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3668,16 +3896,16 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>326</v>
+        <v>364</v>
       </c>
       <c r="C95" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D95" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G95" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3685,16 +3913,16 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>327</v>
+        <v>365</v>
       </c>
       <c r="C96" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D96" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G96" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3702,16 +3930,16 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="C97" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D97" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G97" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3719,16 +3947,16 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>329</v>
+        <v>367</v>
       </c>
       <c r="C98" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D98" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G98" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -3736,16 +3964,16 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>330</v>
+        <v>368</v>
       </c>
       <c r="C99" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D99" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G99" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -3753,16 +3981,16 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>331</v>
+        <v>369</v>
       </c>
       <c r="C100" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D100" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G100" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -3770,16 +3998,16 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>332</v>
+        <v>370</v>
       </c>
       <c r="C101" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D101" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G101" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -3787,16 +4015,16 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="C102" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D102" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G102" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -3804,16 +4032,16 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>334</v>
+        <v>372</v>
       </c>
       <c r="C103" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D103" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G103" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -3821,16 +4049,16 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="C104" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D104" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G104" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -3838,16 +4066,16 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>336</v>
+        <v>374</v>
       </c>
       <c r="C105" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D105" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G105" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -3855,16 +4083,16 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>337</v>
+        <v>375</v>
       </c>
       <c r="C106" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D106" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G106" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -3872,16 +4100,16 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>338</v>
+        <v>376</v>
       </c>
       <c r="C107" t="s">
-        <v>424</v>
+        <v>500</v>
       </c>
       <c r="D107" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G107" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -3889,16 +4117,16 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>339</v>
+        <v>377</v>
       </c>
       <c r="C108" t="s">
-        <v>424</v>
+        <v>500</v>
       </c>
       <c r="D108" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G108" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -3906,16 +4134,16 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>340</v>
+        <v>378</v>
       </c>
       <c r="C109" t="s">
-        <v>425</v>
+        <v>501</v>
       </c>
       <c r="D109" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G109" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -3923,16 +4151,16 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>341</v>
+        <v>379</v>
       </c>
       <c r="C110" t="s">
-        <v>425</v>
+        <v>501</v>
       </c>
       <c r="D110" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G110" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -3940,16 +4168,16 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>342</v>
+        <v>380</v>
       </c>
       <c r="C111" t="s">
-        <v>425</v>
+        <v>501</v>
       </c>
       <c r="D111" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G111" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -3957,16 +4185,16 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>343</v>
+        <v>381</v>
       </c>
       <c r="C112" t="s">
-        <v>425</v>
+        <v>501</v>
       </c>
       <c r="D112" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G112" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -3974,16 +4202,16 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>344</v>
+        <v>382</v>
       </c>
       <c r="C113" t="s">
-        <v>425</v>
+        <v>501</v>
       </c>
       <c r="D113" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G113" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -3991,16 +4219,16 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="C114" t="s">
-        <v>426</v>
+        <v>502</v>
       </c>
       <c r="D114" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G114" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4008,16 +4236,16 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>346</v>
+        <v>384</v>
       </c>
       <c r="C115" t="s">
-        <v>426</v>
+        <v>502</v>
       </c>
       <c r="D115" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G115" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4025,16 +4253,16 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>347</v>
+        <v>385</v>
       </c>
       <c r="C116" t="s">
-        <v>426</v>
+        <v>502</v>
       </c>
       <c r="D116" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G116" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4042,16 +4270,16 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>348</v>
+        <v>386</v>
       </c>
       <c r="C117" t="s">
-        <v>426</v>
+        <v>502</v>
       </c>
       <c r="D117" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G117" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4059,16 +4287,16 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>349</v>
+        <v>387</v>
       </c>
       <c r="C118" t="s">
-        <v>426</v>
+        <v>502</v>
       </c>
       <c r="D118" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G118" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4076,22 +4304,22 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>275</v>
+        <v>313</v>
       </c>
       <c r="C119" t="s">
-        <v>426</v>
+        <v>502</v>
       </c>
       <c r="D119" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E119" t="s">
-        <v>466</v>
+        <v>542</v>
       </c>
       <c r="F119" t="s">
-        <v>520</v>
+        <v>596</v>
       </c>
       <c r="G119" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4099,19 +4327,19 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>350</v>
+        <v>388</v>
       </c>
       <c r="C120" t="s">
-        <v>426</v>
+        <v>502</v>
       </c>
       <c r="D120" t="s">
-        <v>440</v>
+        <v>516</v>
       </c>
       <c r="E120" t="s">
-        <v>467</v>
+        <v>543</v>
       </c>
       <c r="G120" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4119,16 +4347,16 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>351</v>
+        <v>389</v>
       </c>
       <c r="C121" t="s">
-        <v>426</v>
+        <v>502</v>
       </c>
       <c r="D121" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G121" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4136,16 +4364,16 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
       <c r="C122" t="s">
-        <v>424</v>
+        <v>500</v>
       </c>
       <c r="D122" t="s">
-        <v>441</v>
+        <v>517</v>
       </c>
       <c r="G122" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4153,22 +4381,22 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>353</v>
+        <v>391</v>
       </c>
       <c r="C123" t="s">
-        <v>424</v>
+        <v>500</v>
       </c>
       <c r="D123" t="s">
-        <v>442</v>
+        <v>518</v>
       </c>
       <c r="E123" t="s">
-        <v>468</v>
+        <v>544</v>
       </c>
       <c r="F123" t="s">
-        <v>521</v>
+        <v>597</v>
       </c>
       <c r="G123" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4176,16 +4404,16 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>354</v>
+        <v>392</v>
       </c>
       <c r="C124" t="s">
-        <v>424</v>
+        <v>500</v>
       </c>
       <c r="D124" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G124" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4193,16 +4421,16 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="C125" t="s">
-        <v>424</v>
+        <v>500</v>
       </c>
       <c r="D125" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G125" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4210,16 +4438,16 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>356</v>
+        <v>394</v>
       </c>
       <c r="C126" t="s">
-        <v>424</v>
+        <v>500</v>
       </c>
       <c r="D126" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G126" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4227,16 +4455,16 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>357</v>
+        <v>395</v>
       </c>
       <c r="C127" t="s">
-        <v>424</v>
+        <v>500</v>
       </c>
       <c r="D127" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G127" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4244,19 +4472,19 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>358</v>
+        <v>396</v>
       </c>
       <c r="C128" t="s">
-        <v>424</v>
+        <v>500</v>
       </c>
       <c r="D128" t="s">
-        <v>443</v>
+        <v>519</v>
       </c>
       <c r="E128" t="s">
-        <v>469</v>
+        <v>545</v>
       </c>
       <c r="G128" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4264,22 +4492,22 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>359</v>
+        <v>397</v>
       </c>
       <c r="C129" t="s">
-        <v>425</v>
+        <v>501</v>
       </c>
       <c r="D129" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E129" t="s">
-        <v>470</v>
+        <v>546</v>
       </c>
       <c r="F129" t="s">
-        <v>522</v>
+        <v>598</v>
       </c>
       <c r="G129" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4287,16 +4515,16 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>360</v>
+        <v>398</v>
       </c>
       <c r="C130" t="s">
-        <v>425</v>
+        <v>501</v>
       </c>
       <c r="D130" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G130" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4304,13 +4532,13 @@
         <v>136</v>
       </c>
       <c r="C131" t="s">
-        <v>425</v>
+        <v>501</v>
       </c>
       <c r="D131" t="s">
-        <v>444</v>
+        <v>520</v>
       </c>
       <c r="E131" t="s">
-        <v>471</v>
+        <v>547</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4318,19 +4546,19 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>361</v>
+        <v>399</v>
       </c>
       <c r="C132" t="s">
-        <v>425</v>
+        <v>501</v>
       </c>
       <c r="D132" t="s">
-        <v>445</v>
+        <v>521</v>
       </c>
       <c r="E132" t="s">
-        <v>472</v>
+        <v>548</v>
       </c>
       <c r="G132" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4338,19 +4566,19 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>362</v>
+        <v>400</v>
       </c>
       <c r="C133" t="s">
-        <v>425</v>
+        <v>501</v>
       </c>
       <c r="D133" t="s">
-        <v>446</v>
+        <v>522</v>
       </c>
       <c r="E133" t="s">
-        <v>473</v>
+        <v>549</v>
       </c>
       <c r="G133" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4358,10 +4586,10 @@
         <v>139</v>
       </c>
       <c r="C134" t="s">
-        <v>425</v>
+        <v>501</v>
       </c>
       <c r="D134" t="s">
-        <v>447</v>
+        <v>523</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4369,10 +4597,10 @@
         <v>140</v>
       </c>
       <c r="C135" t="s">
-        <v>425</v>
+        <v>501</v>
       </c>
       <c r="D135" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4380,16 +4608,16 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>363</v>
+        <v>401</v>
       </c>
       <c r="C136" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D136" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G136" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4397,16 +4625,16 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>364</v>
+        <v>402</v>
       </c>
       <c r="C137" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D137" t="s">
-        <v>444</v>
+        <v>520</v>
       </c>
       <c r="G137" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4414,10 +4642,10 @@
         <v>143</v>
       </c>
       <c r="C138" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D138" t="s">
-        <v>448</v>
+        <v>524</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4425,10 +4653,10 @@
         <v>144</v>
       </c>
       <c r="C139" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D139" t="s">
-        <v>449</v>
+        <v>525</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4436,10 +4664,10 @@
         <v>145</v>
       </c>
       <c r="C140" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D140" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4447,16 +4675,16 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>280</v>
+        <v>318</v>
       </c>
       <c r="C141" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D141" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G141" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4464,22 +4692,22 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="C142" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D142" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E142" t="s">
-        <v>474</v>
+        <v>550</v>
       </c>
       <c r="F142" t="s">
-        <v>523</v>
+        <v>599</v>
       </c>
       <c r="G142" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4487,16 +4715,16 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>366</v>
+        <v>404</v>
       </c>
       <c r="C143" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D143" t="s">
-        <v>448</v>
+        <v>524</v>
       </c>
       <c r="G143" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4504,13 +4732,13 @@
         <v>149</v>
       </c>
       <c r="C144" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D144" t="s">
-        <v>450</v>
+        <v>526</v>
       </c>
       <c r="E144" t="s">
-        <v>475</v>
+        <v>551</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4518,10 +4746,10 @@
         <v>150</v>
       </c>
       <c r="C145" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D145" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4529,19 +4757,19 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>367</v>
+        <v>405</v>
       </c>
       <c r="C146" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="D146" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="F146" t="s">
-        <v>524</v>
+        <v>600</v>
       </c>
       <c r="G146" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -4549,22 +4777,22 @@
         <v>152</v>
       </c>
       <c r="B147" t="s">
-        <v>368</v>
+        <v>406</v>
       </c>
       <c r="C147" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D147" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E147" t="s">
-        <v>476</v>
+        <v>552</v>
       </c>
       <c r="F147" t="s">
-        <v>525</v>
+        <v>601</v>
       </c>
       <c r="G147" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -4572,19 +4800,19 @@
         <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>369</v>
+        <v>407</v>
       </c>
       <c r="C148" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D148" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E148" t="s">
-        <v>477</v>
+        <v>553</v>
       </c>
       <c r="G148" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -4592,19 +4820,19 @@
         <v>154</v>
       </c>
       <c r="B149" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="C149" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D149" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E149" t="s">
-        <v>478</v>
+        <v>554</v>
       </c>
       <c r="G149" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -4612,19 +4840,19 @@
         <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>371</v>
+        <v>409</v>
       </c>
       <c r="C150" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D150" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E150" t="s">
-        <v>479</v>
+        <v>555</v>
       </c>
       <c r="G150" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -4632,19 +4860,19 @@
         <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>372</v>
+        <v>410</v>
       </c>
       <c r="C151" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D151" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E151" t="s">
-        <v>480</v>
+        <v>556</v>
       </c>
       <c r="G151" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -4652,19 +4880,19 @@
         <v>157</v>
       </c>
       <c r="B152" t="s">
-        <v>373</v>
+        <v>411</v>
       </c>
       <c r="C152" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D152" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E152" t="s">
-        <v>481</v>
+        <v>557</v>
       </c>
       <c r="G152" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -4672,10 +4900,10 @@
         <v>158</v>
       </c>
       <c r="C153" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D153" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -4683,19 +4911,19 @@
         <v>159</v>
       </c>
       <c r="B154" t="s">
-        <v>374</v>
+        <v>412</v>
       </c>
       <c r="C154" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D154" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E154" t="s">
-        <v>482</v>
+        <v>558</v>
       </c>
       <c r="G154" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -4703,16 +4931,16 @@
         <v>160</v>
       </c>
       <c r="B155" t="s">
-        <v>375</v>
+        <v>413</v>
       </c>
       <c r="C155" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D155" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G155" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -4720,16 +4948,16 @@
         <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>376</v>
+        <v>414</v>
       </c>
       <c r="C156" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D156" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G156" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -4737,22 +4965,22 @@
         <v>162</v>
       </c>
       <c r="B157" t="s">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="C157" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D157" t="s">
-        <v>451</v>
+        <v>527</v>
       </c>
       <c r="E157" t="s">
-        <v>483</v>
+        <v>559</v>
       </c>
       <c r="F157" t="s">
-        <v>526</v>
+        <v>602</v>
       </c>
       <c r="G157" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -4760,19 +4988,19 @@
         <v>163</v>
       </c>
       <c r="B158" t="s">
-        <v>378</v>
+        <v>416</v>
       </c>
       <c r="C158" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D158" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E158" t="s">
-        <v>484</v>
+        <v>560</v>
       </c>
       <c r="G158" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -4780,19 +5008,19 @@
         <v>164</v>
       </c>
       <c r="B159" t="s">
-        <v>379</v>
+        <v>417</v>
       </c>
       <c r="C159" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D159" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E159" t="s">
-        <v>485</v>
+        <v>561</v>
       </c>
       <c r="G159" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -4800,19 +5028,19 @@
         <v>165</v>
       </c>
       <c r="B160" t="s">
-        <v>380</v>
+        <v>418</v>
       </c>
       <c r="C160" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D160" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E160" t="s">
-        <v>486</v>
+        <v>562</v>
       </c>
       <c r="G160" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -4820,19 +5048,19 @@
         <v>166</v>
       </c>
       <c r="B161" t="s">
-        <v>381</v>
+        <v>419</v>
       </c>
       <c r="C161" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D161" t="s">
-        <v>452</v>
+        <v>528</v>
       </c>
       <c r="E161" t="s">
-        <v>487</v>
+        <v>563</v>
       </c>
       <c r="G161" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -4840,16 +5068,16 @@
         <v>167</v>
       </c>
       <c r="B162" t="s">
-        <v>382</v>
+        <v>420</v>
       </c>
       <c r="C162" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D162" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G162" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -4857,19 +5085,19 @@
         <v>168</v>
       </c>
       <c r="B163" t="s">
-        <v>383</v>
+        <v>421</v>
       </c>
       <c r="C163" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D163" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E163" t="s">
-        <v>488</v>
+        <v>564</v>
       </c>
       <c r="G163" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -4877,19 +5105,19 @@
         <v>169</v>
       </c>
       <c r="B164" t="s">
-        <v>384</v>
+        <v>422</v>
       </c>
       <c r="C164" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D164" t="s">
-        <v>453</v>
+        <v>529</v>
       </c>
       <c r="E164" t="s">
-        <v>489</v>
+        <v>565</v>
       </c>
       <c r="G164" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -4897,13 +5125,13 @@
         <v>170</v>
       </c>
       <c r="C165" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D165" t="s">
-        <v>444</v>
+        <v>520</v>
       </c>
       <c r="E165" t="s">
-        <v>490</v>
+        <v>566</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -4911,19 +5139,19 @@
         <v>171</v>
       </c>
       <c r="B166" t="s">
-        <v>385</v>
+        <v>423</v>
       </c>
       <c r="C166" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D166" t="s">
-        <v>454</v>
+        <v>530</v>
       </c>
       <c r="E166" t="s">
-        <v>491</v>
+        <v>567</v>
       </c>
       <c r="G166" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -4931,19 +5159,19 @@
         <v>172</v>
       </c>
       <c r="B167" t="s">
-        <v>386</v>
+        <v>424</v>
       </c>
       <c r="C167" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="D167" t="s">
-        <v>455</v>
+        <v>531</v>
       </c>
       <c r="E167" t="s">
-        <v>492</v>
+        <v>568</v>
       </c>
       <c r="G167" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -4951,19 +5179,19 @@
         <v>173</v>
       </c>
       <c r="B168" t="s">
-        <v>387</v>
+        <v>425</v>
       </c>
       <c r="C168" t="s">
-        <v>415</v>
+        <v>491</v>
       </c>
       <c r="D168" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E168" t="s">
-        <v>493</v>
+        <v>569</v>
       </c>
       <c r="G168" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -4971,19 +5199,19 @@
         <v>174</v>
       </c>
       <c r="B169" t="s">
-        <v>388</v>
+        <v>426</v>
       </c>
       <c r="C169" t="s">
-        <v>415</v>
+        <v>491</v>
       </c>
       <c r="D169" t="s">
-        <v>456</v>
+        <v>532</v>
       </c>
       <c r="E169" t="s">
-        <v>494</v>
+        <v>570</v>
       </c>
       <c r="G169" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -4991,13 +5219,13 @@
         <v>175</v>
       </c>
       <c r="C170" t="s">
-        <v>415</v>
+        <v>491</v>
       </c>
       <c r="D170" t="s">
-        <v>457</v>
+        <v>533</v>
       </c>
       <c r="E170" t="s">
-        <v>495</v>
+        <v>571</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5005,13 +5233,13 @@
         <v>176</v>
       </c>
       <c r="C171" t="s">
-        <v>415</v>
+        <v>491</v>
       </c>
       <c r="D171" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E171" t="s">
-        <v>496</v>
+        <v>572</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5019,13 +5247,13 @@
         <v>177</v>
       </c>
       <c r="C172" t="s">
-        <v>415</v>
+        <v>491</v>
       </c>
       <c r="D172" t="s">
-        <v>444</v>
+        <v>520</v>
       </c>
       <c r="E172" t="s">
-        <v>497</v>
+        <v>573</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5033,16 +5261,16 @@
         <v>178</v>
       </c>
       <c r="B173" t="s">
-        <v>389</v>
+        <v>427</v>
       </c>
       <c r="C173" t="s">
-        <v>427</v>
+        <v>503</v>
       </c>
       <c r="D173" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G173" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5050,19 +5278,19 @@
         <v>179</v>
       </c>
       <c r="B174" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="C174" t="s">
-        <v>427</v>
+        <v>503</v>
       </c>
       <c r="D174" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="F174" t="s">
-        <v>527</v>
+        <v>603</v>
       </c>
       <c r="G174" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5070,19 +5298,19 @@
         <v>180</v>
       </c>
       <c r="B175" t="s">
-        <v>391</v>
+        <v>429</v>
       </c>
       <c r="C175" t="s">
-        <v>427</v>
+        <v>503</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="F175" t="s">
-        <v>528</v>
+        <v>604</v>
       </c>
       <c r="G175" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5090,10 +5318,10 @@
         <v>181</v>
       </c>
       <c r="C176" t="s">
-        <v>428</v>
+        <v>504</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5101,10 +5329,10 @@
         <v>182</v>
       </c>
       <c r="C177" t="s">
-        <v>428</v>
+        <v>504</v>
       </c>
       <c r="D177" t="s">
-        <v>458</v>
+        <v>534</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5112,10 +5340,10 @@
         <v>183</v>
       </c>
       <c r="C178" t="s">
-        <v>428</v>
+        <v>504</v>
       </c>
       <c r="D178" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5123,22 +5351,22 @@
         <v>184</v>
       </c>
       <c r="B179" t="s">
-        <v>392</v>
+        <v>430</v>
       </c>
       <c r="C179" t="s">
-        <v>429</v>
+        <v>505</v>
       </c>
       <c r="D179" t="s">
-        <v>458</v>
+        <v>534</v>
       </c>
       <c r="E179" t="s">
-        <v>498</v>
+        <v>574</v>
       </c>
       <c r="F179" t="s">
-        <v>529</v>
+        <v>605</v>
       </c>
       <c r="G179" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5146,10 +5374,10 @@
         <v>185</v>
       </c>
       <c r="C180" t="s">
-        <v>429</v>
+        <v>505</v>
       </c>
       <c r="D180" t="s">
-        <v>459</v>
+        <v>535</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5157,10 +5385,10 @@
         <v>186</v>
       </c>
       <c r="C181" t="s">
-        <v>429</v>
+        <v>505</v>
       </c>
       <c r="D181" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5168,19 +5396,19 @@
         <v>187</v>
       </c>
       <c r="B182" t="s">
-        <v>393</v>
+        <v>431</v>
       </c>
       <c r="C182" t="s">
-        <v>430</v>
+        <v>506</v>
       </c>
       <c r="D182" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E182" t="s">
-        <v>499</v>
+        <v>575</v>
       </c>
       <c r="G182" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5188,19 +5416,19 @@
         <v>188</v>
       </c>
       <c r="B183" t="s">
-        <v>394</v>
+        <v>432</v>
       </c>
       <c r="C183" t="s">
-        <v>430</v>
+        <v>506</v>
       </c>
       <c r="D183" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="F183" t="s">
-        <v>530</v>
+        <v>606</v>
       </c>
       <c r="G183" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5208,10 +5436,10 @@
         <v>189</v>
       </c>
       <c r="C184" t="s">
-        <v>430</v>
+        <v>506</v>
       </c>
       <c r="D184" t="s">
-        <v>459</v>
+        <v>535</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5219,13 +5447,13 @@
         <v>190</v>
       </c>
       <c r="C185" t="s">
-        <v>430</v>
+        <v>506</v>
       </c>
       <c r="D185" t="s">
-        <v>460</v>
+        <v>536</v>
       </c>
       <c r="F185" t="s">
-        <v>531</v>
+        <v>607</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5233,13 +5461,13 @@
         <v>191</v>
       </c>
       <c r="C186" t="s">
-        <v>431</v>
+        <v>507</v>
       </c>
       <c r="D186" t="s">
-        <v>461</v>
+        <v>537</v>
       </c>
       <c r="E186" t="s">
-        <v>500</v>
+        <v>576</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5247,13 +5475,13 @@
         <v>192</v>
       </c>
       <c r="C187" t="s">
-        <v>431</v>
+        <v>507</v>
       </c>
       <c r="D187" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E187" t="s">
-        <v>501</v>
+        <v>577</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5261,13 +5489,13 @@
         <v>193</v>
       </c>
       <c r="C188" t="s">
-        <v>431</v>
+        <v>507</v>
       </c>
       <c r="D188" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E188" t="s">
-        <v>502</v>
+        <v>578</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5275,13 +5503,13 @@
         <v>194</v>
       </c>
       <c r="C189" t="s">
-        <v>431</v>
+        <v>507</v>
       </c>
       <c r="D189" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E189" t="s">
-        <v>503</v>
+        <v>579</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5289,13 +5517,13 @@
         <v>195</v>
       </c>
       <c r="C190" t="s">
-        <v>431</v>
+        <v>507</v>
       </c>
       <c r="D190" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E190" t="s">
-        <v>504</v>
+        <v>580</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5303,10 +5531,10 @@
         <v>196</v>
       </c>
       <c r="C191" t="s">
-        <v>431</v>
+        <v>507</v>
       </c>
       <c r="D191" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -5314,10 +5542,10 @@
         <v>197</v>
       </c>
       <c r="C192" t="s">
-        <v>431</v>
+        <v>507</v>
       </c>
       <c r="D192" t="s">
-        <v>462</v>
+        <v>538</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -5325,10 +5553,10 @@
         <v>198</v>
       </c>
       <c r="C193" t="s">
-        <v>431</v>
+        <v>507</v>
       </c>
       <c r="D193" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -5336,16 +5564,16 @@
         <v>199</v>
       </c>
       <c r="B194" t="s">
-        <v>395</v>
+        <v>433</v>
       </c>
       <c r="C194" t="s">
-        <v>431</v>
+        <v>507</v>
       </c>
       <c r="D194" t="s">
-        <v>441</v>
+        <v>517</v>
       </c>
       <c r="G194" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -5353,16 +5581,16 @@
         <v>200</v>
       </c>
       <c r="B195" t="s">
-        <v>396</v>
+        <v>434</v>
       </c>
       <c r="C195" t="s">
-        <v>431</v>
+        <v>507</v>
       </c>
       <c r="D195" t="s">
-        <v>441</v>
+        <v>517</v>
       </c>
       <c r="G195" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -5370,19 +5598,19 @@
         <v>201</v>
       </c>
       <c r="B196" t="s">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="C196" t="s">
-        <v>418</v>
+        <v>494</v>
       </c>
       <c r="D196" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="F196" t="s">
-        <v>532</v>
+        <v>608</v>
       </c>
       <c r="G196" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -5390,22 +5618,22 @@
         <v>202</v>
       </c>
       <c r="B197" t="s">
-        <v>398</v>
+        <v>436</v>
       </c>
       <c r="C197" t="s">
-        <v>418</v>
+        <v>494</v>
       </c>
       <c r="D197" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E197" t="s">
-        <v>505</v>
+        <v>581</v>
       </c>
       <c r="F197" t="s">
-        <v>533</v>
+        <v>609</v>
       </c>
       <c r="G197" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -5413,22 +5641,22 @@
         <v>203</v>
       </c>
       <c r="B198" t="s">
-        <v>399</v>
+        <v>437</v>
       </c>
       <c r="C198" t="s">
-        <v>418</v>
+        <v>494</v>
       </c>
       <c r="D198" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E198" t="s">
-        <v>506</v>
+        <v>582</v>
       </c>
       <c r="F198" t="s">
-        <v>534</v>
+        <v>610</v>
       </c>
       <c r="G198" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -5436,22 +5664,22 @@
         <v>204</v>
       </c>
       <c r="B199" t="s">
-        <v>400</v>
+        <v>438</v>
       </c>
       <c r="C199" t="s">
-        <v>418</v>
+        <v>494</v>
       </c>
       <c r="D199" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E199" t="s">
-        <v>507</v>
+        <v>583</v>
       </c>
       <c r="F199" t="s">
-        <v>535</v>
+        <v>611</v>
       </c>
       <c r="G199" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -5459,16 +5687,16 @@
         <v>205</v>
       </c>
       <c r="B200" t="s">
-        <v>401</v>
+        <v>439</v>
       </c>
       <c r="C200" t="s">
-        <v>432</v>
+        <v>508</v>
       </c>
       <c r="D200" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G200" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -5476,10 +5704,10 @@
         <v>206</v>
       </c>
       <c r="C201" t="s">
-        <v>432</v>
+        <v>508</v>
       </c>
       <c r="D201" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -5487,10 +5715,10 @@
         <v>207</v>
       </c>
       <c r="C202" t="s">
-        <v>432</v>
+        <v>508</v>
       </c>
       <c r="D202" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -5498,10 +5726,10 @@
         <v>208</v>
       </c>
       <c r="C203" t="s">
-        <v>432</v>
+        <v>508</v>
       </c>
       <c r="D203" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -5509,16 +5737,16 @@
         <v>209</v>
       </c>
       <c r="B204" t="s">
-        <v>280</v>
+        <v>318</v>
       </c>
       <c r="C204" t="s">
-        <v>433</v>
+        <v>509</v>
       </c>
       <c r="D204" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G204" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -5526,10 +5754,10 @@
         <v>210</v>
       </c>
       <c r="C205" t="s">
-        <v>433</v>
+        <v>509</v>
       </c>
       <c r="D205" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -5537,10 +5765,10 @@
         <v>211</v>
       </c>
       <c r="C206" t="s">
-        <v>433</v>
+        <v>509</v>
       </c>
       <c r="D206" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -5548,19 +5776,19 @@
         <v>212</v>
       </c>
       <c r="B207" t="s">
-        <v>402</v>
+        <v>440</v>
       </c>
       <c r="C207" t="s">
-        <v>433</v>
+        <v>509</v>
       </c>
       <c r="D207" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E207" t="s">
-        <v>508</v>
+        <v>584</v>
       </c>
       <c r="G207" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -5568,13 +5796,13 @@
         <v>213</v>
       </c>
       <c r="C208" t="s">
-        <v>433</v>
+        <v>509</v>
       </c>
       <c r="D208" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E208" t="s">
-        <v>509</v>
+        <v>585</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -5582,10 +5810,10 @@
         <v>214</v>
       </c>
       <c r="C209" t="s">
-        <v>433</v>
+        <v>509</v>
       </c>
       <c r="D209" t="s">
-        <v>447</v>
+        <v>523</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -5593,19 +5821,19 @@
         <v>215</v>
       </c>
       <c r="B210" t="s">
-        <v>403</v>
+        <v>441</v>
       </c>
       <c r="C210" t="s">
-        <v>434</v>
+        <v>510</v>
       </c>
       <c r="D210" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E210" t="s">
-        <v>510</v>
+        <v>586</v>
       </c>
       <c r="G210" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -5613,16 +5841,16 @@
         <v>216</v>
       </c>
       <c r="B211" t="s">
-        <v>404</v>
+        <v>442</v>
       </c>
       <c r="C211" t="s">
-        <v>434</v>
+        <v>510</v>
       </c>
       <c r="D211" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G211" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -5630,13 +5858,13 @@
         <v>217</v>
       </c>
       <c r="C212" t="s">
-        <v>434</v>
+        <v>510</v>
       </c>
       <c r="D212" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E212" t="s">
-        <v>511</v>
+        <v>587</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -5644,13 +5872,13 @@
         <v>218</v>
       </c>
       <c r="C213" t="s">
-        <v>434</v>
+        <v>510</v>
       </c>
       <c r="D213" t="s">
-        <v>451</v>
+        <v>527</v>
       </c>
       <c r="E213" t="s">
-        <v>512</v>
+        <v>588</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -5658,16 +5886,16 @@
         <v>219</v>
       </c>
       <c r="B214" t="s">
-        <v>405</v>
+        <v>443</v>
       </c>
       <c r="C214" t="s">
-        <v>417</v>
+        <v>493</v>
       </c>
       <c r="D214" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G214" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -5675,16 +5903,16 @@
         <v>220</v>
       </c>
       <c r="B215" t="s">
-        <v>406</v>
+        <v>444</v>
       </c>
       <c r="C215" t="s">
-        <v>417</v>
+        <v>493</v>
       </c>
       <c r="D215" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G215" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -5692,13 +5920,13 @@
         <v>221</v>
       </c>
       <c r="C216" t="s">
-        <v>417</v>
+        <v>493</v>
       </c>
       <c r="D216" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E216" t="s">
-        <v>513</v>
+        <v>589</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -5706,19 +5934,19 @@
         <v>222</v>
       </c>
       <c r="B217" t="s">
-        <v>407</v>
+        <v>445</v>
       </c>
       <c r="C217" t="s">
-        <v>435</v>
+        <v>511</v>
       </c>
       <c r="D217" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E217" t="s">
-        <v>514</v>
+        <v>590</v>
       </c>
       <c r="G217" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -5726,19 +5954,19 @@
         <v>223</v>
       </c>
       <c r="B218" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="C218" t="s">
-        <v>435</v>
+        <v>511</v>
       </c>
       <c r="D218" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E218" t="s">
-        <v>514</v>
+        <v>590</v>
       </c>
       <c r="G218" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -5746,19 +5974,19 @@
         <v>224</v>
       </c>
       <c r="B219" t="s">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="C219" t="s">
-        <v>436</v>
+        <v>512</v>
       </c>
       <c r="D219" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E219" t="s">
-        <v>515</v>
+        <v>591</v>
       </c>
       <c r="G219" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -5766,10 +5994,10 @@
         <v>225</v>
       </c>
       <c r="C220" t="s">
-        <v>436</v>
+        <v>512</v>
       </c>
       <c r="D220" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -5777,16 +6005,16 @@
         <v>226</v>
       </c>
       <c r="B221" t="s">
-        <v>409</v>
+        <v>447</v>
       </c>
       <c r="C221" t="s">
-        <v>436</v>
+        <v>512</v>
       </c>
       <c r="D221" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G221" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -5794,19 +6022,19 @@
         <v>227</v>
       </c>
       <c r="B222" t="s">
-        <v>410</v>
+        <v>448</v>
       </c>
       <c r="C222" t="s">
-        <v>437</v>
+        <v>513</v>
       </c>
       <c r="D222" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="E222" t="s">
-        <v>516</v>
+        <v>592</v>
       </c>
       <c r="G222" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -5814,16 +6042,16 @@
         <v>228</v>
       </c>
       <c r="B223" t="s">
-        <v>411</v>
+        <v>449</v>
       </c>
       <c r="C223" t="s">
-        <v>437</v>
+        <v>513</v>
       </c>
       <c r="D223" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G223" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -5831,16 +6059,16 @@
         <v>229</v>
       </c>
       <c r="B224" t="s">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="C224" t="s">
-        <v>437</v>
+        <v>513</v>
       </c>
       <c r="D224" t="s">
-        <v>460</v>
+        <v>536</v>
       </c>
       <c r="G224" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -5848,19 +6076,19 @@
         <v>230</v>
       </c>
       <c r="B225" t="s">
-        <v>413</v>
+        <v>451</v>
       </c>
       <c r="C225" t="s">
-        <v>437</v>
+        <v>513</v>
       </c>
       <c r="D225" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="F225" t="s">
-        <v>536</v>
+        <v>612</v>
       </c>
       <c r="G225" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -5868,16 +6096,16 @@
         <v>231</v>
       </c>
       <c r="B226" t="s">
-        <v>414</v>
+        <v>452</v>
       </c>
       <c r="C226" t="s">
-        <v>437</v>
+        <v>513</v>
       </c>
       <c r="D226" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="G226" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -5885,10 +6113,542 @@
         <v>232</v>
       </c>
       <c r="C227" t="s">
-        <v>437</v>
+        <v>513</v>
       </c>
       <c r="D227" t="s">
-        <v>438</v>
+        <v>514</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228" t="s">
+        <v>233</v>
+      </c>
+      <c r="B228" t="s">
+        <v>453</v>
+      </c>
+      <c r="C228" t="s">
+        <v>498</v>
+      </c>
+      <c r="D228" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229" t="s">
+        <v>234</v>
+      </c>
+      <c r="B229" t="s">
+        <v>454</v>
+      </c>
+      <c r="C229" t="s">
+        <v>498</v>
+      </c>
+      <c r="D229" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7">
+      <c r="A230" t="s">
+        <v>235</v>
+      </c>
+      <c r="B230" t="s">
+        <v>455</v>
+      </c>
+      <c r="C230" t="s">
+        <v>498</v>
+      </c>
+      <c r="D230" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231" t="s">
+        <v>236</v>
+      </c>
+      <c r="B231" t="s">
+        <v>456</v>
+      </c>
+      <c r="C231" t="s">
+        <v>498</v>
+      </c>
+      <c r="D231" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7">
+      <c r="A232" t="s">
+        <v>237</v>
+      </c>
+      <c r="B232" t="s">
+        <v>457</v>
+      </c>
+      <c r="C232" t="s">
+        <v>498</v>
+      </c>
+      <c r="D232" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7">
+      <c r="A233" t="s">
+        <v>238</v>
+      </c>
+      <c r="B233" t="s">
+        <v>458</v>
+      </c>
+      <c r="C233" t="s">
+        <v>498</v>
+      </c>
+      <c r="D233" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7">
+      <c r="A234" t="s">
+        <v>239</v>
+      </c>
+      <c r="B234" t="s">
+        <v>459</v>
+      </c>
+      <c r="C234" t="s">
+        <v>498</v>
+      </c>
+      <c r="D234" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235" t="s">
+        <v>240</v>
+      </c>
+      <c r="B235" t="s">
+        <v>460</v>
+      </c>
+      <c r="C235" t="s">
+        <v>498</v>
+      </c>
+      <c r="D235" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7">
+      <c r="A236" t="s">
+        <v>241</v>
+      </c>
+      <c r="B236" t="s">
+        <v>461</v>
+      </c>
+      <c r="C236" t="s">
+        <v>498</v>
+      </c>
+      <c r="D236" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7">
+      <c r="A237" t="s">
+        <v>242</v>
+      </c>
+      <c r="B237" t="s">
+        <v>462</v>
+      </c>
+      <c r="C237" t="s">
+        <v>498</v>
+      </c>
+      <c r="D237" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7">
+      <c r="A238" t="s">
+        <v>243</v>
+      </c>
+      <c r="B238" t="s">
+        <v>463</v>
+      </c>
+      <c r="C238" t="s">
+        <v>498</v>
+      </c>
+      <c r="D238" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7">
+      <c r="A239" t="s">
+        <v>244</v>
+      </c>
+      <c r="B239" t="s">
+        <v>464</v>
+      </c>
+      <c r="C239" t="s">
+        <v>498</v>
+      </c>
+      <c r="D239" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240" t="s">
+        <v>245</v>
+      </c>
+      <c r="B240" t="s">
+        <v>465</v>
+      </c>
+      <c r="C240" t="s">
+        <v>492</v>
+      </c>
+      <c r="D240" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" t="s">
+        <v>246</v>
+      </c>
+      <c r="B241" t="s">
+        <v>466</v>
+      </c>
+      <c r="C241" t="s">
+        <v>492</v>
+      </c>
+      <c r="D241" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" t="s">
+        <v>247</v>
+      </c>
+      <c r="B242" t="s">
+        <v>467</v>
+      </c>
+      <c r="C242" t="s">
+        <v>492</v>
+      </c>
+      <c r="D242" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" t="s">
+        <v>248</v>
+      </c>
+      <c r="B243" t="s">
+        <v>468</v>
+      </c>
+      <c r="C243" t="s">
+        <v>492</v>
+      </c>
+      <c r="D243" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" t="s">
+        <v>249</v>
+      </c>
+      <c r="B244" t="s">
+        <v>469</v>
+      </c>
+      <c r="C244" t="s">
+        <v>492</v>
+      </c>
+      <c r="D244" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" t="s">
+        <v>250</v>
+      </c>
+      <c r="B245" t="s">
+        <v>470</v>
+      </c>
+      <c r="C245" t="s">
+        <v>492</v>
+      </c>
+      <c r="D245" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" t="s">
+        <v>251</v>
+      </c>
+      <c r="B246" t="s">
+        <v>471</v>
+      </c>
+      <c r="C246" t="s">
+        <v>492</v>
+      </c>
+      <c r="D246" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" t="s">
+        <v>252</v>
+      </c>
+      <c r="B247" t="s">
+        <v>472</v>
+      </c>
+      <c r="C247" t="s">
+        <v>492</v>
+      </c>
+      <c r="D247" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" t="s">
+        <v>253</v>
+      </c>
+      <c r="B248" t="s">
+        <v>473</v>
+      </c>
+      <c r="C248" t="s">
+        <v>492</v>
+      </c>
+      <c r="D248" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" t="s">
+        <v>254</v>
+      </c>
+      <c r="B249" t="s">
+        <v>474</v>
+      </c>
+      <c r="C249" t="s">
+        <v>500</v>
+      </c>
+      <c r="D249" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" t="s">
+        <v>255</v>
+      </c>
+      <c r="B250" t="s">
+        <v>475</v>
+      </c>
+      <c r="C250" t="s">
+        <v>500</v>
+      </c>
+      <c r="D250" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" t="s">
+        <v>256</v>
+      </c>
+      <c r="B251" t="s">
+        <v>476</v>
+      </c>
+      <c r="C251" t="s">
+        <v>501</v>
+      </c>
+      <c r="D251" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" t="s">
+        <v>257</v>
+      </c>
+      <c r="B252" t="s">
+        <v>477</v>
+      </c>
+      <c r="C252" t="s">
+        <v>501</v>
+      </c>
+      <c r="D252" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" t="s">
+        <v>258</v>
+      </c>
+      <c r="B253" t="s">
+        <v>478</v>
+      </c>
+      <c r="C253" t="s">
+        <v>501</v>
+      </c>
+      <c r="D253" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" t="s">
+        <v>259</v>
+      </c>
+      <c r="B254" t="s">
+        <v>479</v>
+      </c>
+      <c r="C254" t="s">
+        <v>501</v>
+      </c>
+      <c r="D254" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" t="s">
+        <v>260</v>
+      </c>
+      <c r="B255" t="s">
+        <v>480</v>
+      </c>
+      <c r="C255" t="s">
+        <v>501</v>
+      </c>
+      <c r="D255" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" t="s">
+        <v>261</v>
+      </c>
+      <c r="B256" t="s">
+        <v>481</v>
+      </c>
+      <c r="C256" t="s">
+        <v>495</v>
+      </c>
+      <c r="D256" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" t="s">
+        <v>262</v>
+      </c>
+      <c r="B257" t="s">
+        <v>482</v>
+      </c>
+      <c r="C257" t="s">
+        <v>495</v>
+      </c>
+      <c r="D257" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" t="s">
+        <v>263</v>
+      </c>
+      <c r="B258" t="s">
+        <v>483</v>
+      </c>
+      <c r="C258" t="s">
+        <v>498</v>
+      </c>
+      <c r="D258" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" t="s">
+        <v>264</v>
+      </c>
+      <c r="B259" t="s">
+        <v>484</v>
+      </c>
+      <c r="C259" t="s">
+        <v>498</v>
+      </c>
+      <c r="D259" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" t="s">
+        <v>265</v>
+      </c>
+      <c r="B260" t="s">
+        <v>485</v>
+      </c>
+      <c r="C260" t="s">
+        <v>498</v>
+      </c>
+      <c r="D260" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" t="s">
+        <v>266</v>
+      </c>
+      <c r="B261" t="s">
+        <v>486</v>
+      </c>
+      <c r="C261" t="s">
+        <v>498</v>
+      </c>
+      <c r="D261" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" t="s">
+        <v>267</v>
+      </c>
+      <c r="B262" t="s">
+        <v>487</v>
+      </c>
+      <c r="C262" t="s">
+        <v>498</v>
+      </c>
+      <c r="D262" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" t="s">
+        <v>268</v>
+      </c>
+      <c r="B263" t="s">
+        <v>488</v>
+      </c>
+      <c r="C263" t="s">
+        <v>498</v>
+      </c>
+      <c r="D263" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" t="s">
+        <v>269</v>
+      </c>
+      <c r="B264" t="s">
+        <v>489</v>
+      </c>
+      <c r="C264" t="s">
+        <v>498</v>
+      </c>
+      <c r="D264" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" t="s">
+        <v>270</v>
+      </c>
+      <c r="B265" t="s">
+        <v>490</v>
+      </c>
+      <c r="C265" t="s">
+        <v>498</v>
+      </c>
+      <c r="D265" t="s">
+        <v>514</v>
       </c>
     </row>
   </sheetData>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="654">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -829,6 +829,60 @@
     <t>The Haven Night Shelter - Claremont</t>
   </si>
   <si>
+    <t>Cancer Association SA</t>
+  </si>
+  <si>
+    <t>Centre for Justice and Crime Prevention</t>
+  </si>
+  <si>
+    <t>Ons Plek Projects Drop-in Centre</t>
+  </si>
+  <si>
+    <t>Congolese Civil Society of South Africa</t>
+  </si>
+  <si>
+    <t>Biowatch South Africa Trust</t>
+  </si>
+  <si>
+    <t>Masifundise Development Trust</t>
+  </si>
+  <si>
+    <t>The Peace Centre (Quaker Peace Centre)</t>
+  </si>
+  <si>
+    <t>Groote Schuur Community Improvement District</t>
+  </si>
+  <si>
+    <t>SAEP (South African Education and Environment Project)</t>
+  </si>
+  <si>
+    <t>The Message Trust</t>
+  </si>
+  <si>
+    <t>Kidzpositive Family Fund</t>
+  </si>
+  <si>
+    <t>Triangle Project</t>
+  </si>
+  <si>
+    <t>Milk Matters</t>
+  </si>
+  <si>
+    <t>Help The Rural Child</t>
+  </si>
+  <si>
+    <t>Scripture Union South Africa</t>
+  </si>
+  <si>
+    <t>St Giles Association for the Handicapped</t>
+  </si>
+  <si>
+    <t>Hello Poppy</t>
+  </si>
+  <si>
+    <t>Kolbe House</t>
+  </si>
+  <si>
     <t>info@ctsc.org.za</t>
   </si>
   <si>
@@ -1489,6 +1543,60 @@
     <t>claremont@haven.org.za</t>
   </si>
   <si>
+    <t>dduplooy@cansa.org.za</t>
+  </si>
+  <si>
+    <t>patrick@cjcp.org.za</t>
+  </si>
+  <si>
+    <t>pam.reflect@gmail.com</t>
+  </si>
+  <si>
+    <t>contact@congolesecivilsocietysa.org</t>
+  </si>
+  <si>
+    <t>biowatch@mweb.co.za</t>
+  </si>
+  <si>
+    <t>infocom@masifundise.org.za</t>
+  </si>
+  <si>
+    <t>peacecentre@peacecentre.org.za</t>
+  </si>
+  <si>
+    <t>info@gscid.co.za</t>
+  </si>
+  <si>
+    <t>tracey@saep.org</t>
+  </si>
+  <si>
+    <t>info@message.org.za</t>
+  </si>
+  <si>
+    <t>info@kidzpositive.org</t>
+  </si>
+  <si>
+    <t>reception@triangle.org.za</t>
+  </si>
+  <si>
+    <t>info@milkmatters.org</t>
+  </si>
+  <si>
+    <t>info@ruralchild.org.za</t>
+  </si>
+  <si>
+    <t>pearlm@su.org.za</t>
+  </si>
+  <si>
+    <t>stgiles@cybertrade.co.za</t>
+  </si>
+  <si>
+    <t>hello@hellopoppy.co.za</t>
+  </si>
+  <si>
+    <t>kolbe.house@telkomsa.net</t>
+  </si>
+  <si>
     <t>Museums &amp; Heritage</t>
   </si>
   <si>
@@ -1558,6 +1666,12 @@
     <t>Hobby &amp; Special Interest Clubs</t>
   </si>
   <si>
+    <t>Community Safety</t>
+  </si>
+  <si>
+    <t>Refugee &amp; Migrant Support</t>
+  </si>
+  <si>
     <t>Cape Town</t>
   </si>
   <si>
@@ -1631,6 +1745,12 @@
   </si>
   <si>
     <t>Claremont</t>
+  </si>
+  <si>
+    <t>Mowbray</t>
+  </si>
+  <si>
+    <t>Rondebosch East</t>
   </si>
   <si>
     <t>021 300 3200</t>
@@ -2200,7 +2320,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G265"/>
+  <dimension ref="A1:G283"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2231,22 +2351,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="C2" t="s">
-        <v>491</v>
+        <v>527</v>
       </c>
       <c r="D2" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E2" t="s">
-        <v>539</v>
+        <v>579</v>
       </c>
       <c r="F2" t="s">
-        <v>593</v>
+        <v>633</v>
       </c>
       <c r="G2" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2254,22 +2374,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="C3" t="s">
-        <v>491</v>
+        <v>527</v>
       </c>
       <c r="D3" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E3" t="s">
-        <v>539</v>
+        <v>579</v>
       </c>
       <c r="F3" t="s">
-        <v>593</v>
+        <v>633</v>
       </c>
       <c r="G3" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2277,22 +2397,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="C4" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D4" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E4" t="s">
-        <v>539</v>
+        <v>579</v>
       </c>
       <c r="F4" t="s">
-        <v>593</v>
+        <v>633</v>
       </c>
       <c r="G4" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2300,22 +2420,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="C5" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D5" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E5" t="s">
-        <v>539</v>
+        <v>579</v>
       </c>
       <c r="F5" t="s">
-        <v>593</v>
+        <v>633</v>
       </c>
       <c r="G5" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2323,22 +2443,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="C6" t="s">
-        <v>491</v>
+        <v>527</v>
       </c>
       <c r="D6" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E6" t="s">
-        <v>539</v>
+        <v>579</v>
       </c>
       <c r="F6" t="s">
-        <v>593</v>
+        <v>633</v>
       </c>
       <c r="G6" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2346,22 +2466,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="C7" t="s">
-        <v>491</v>
+        <v>527</v>
       </c>
       <c r="D7" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E7" t="s">
-        <v>539</v>
+        <v>579</v>
       </c>
       <c r="F7" t="s">
-        <v>593</v>
+        <v>633</v>
       </c>
       <c r="G7" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2369,22 +2489,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="C8" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D8" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E8" t="s">
-        <v>539</v>
+        <v>579</v>
       </c>
       <c r="F8" t="s">
-        <v>593</v>
+        <v>633</v>
       </c>
       <c r="G8" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2392,22 +2512,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="C9" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D9" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E9" t="s">
-        <v>539</v>
+        <v>579</v>
       </c>
       <c r="F9" t="s">
-        <v>593</v>
+        <v>633</v>
       </c>
       <c r="G9" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2415,22 +2535,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C10" t="s">
-        <v>493</v>
+        <v>529</v>
       </c>
       <c r="D10" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E10" t="s">
-        <v>539</v>
+        <v>579</v>
       </c>
       <c r="F10" t="s">
-        <v>593</v>
+        <v>633</v>
       </c>
       <c r="G10" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2438,22 +2558,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="C11" t="s">
-        <v>493</v>
+        <v>529</v>
       </c>
       <c r="D11" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E11" t="s">
-        <v>539</v>
+        <v>579</v>
       </c>
       <c r="F11" t="s">
-        <v>593</v>
+        <v>633</v>
       </c>
       <c r="G11" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2461,22 +2581,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="C12" t="s">
-        <v>494</v>
+        <v>530</v>
       </c>
       <c r="D12" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E12" t="s">
-        <v>539</v>
+        <v>579</v>
       </c>
       <c r="F12" t="s">
-        <v>593</v>
+        <v>633</v>
       </c>
       <c r="G12" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2484,22 +2604,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="C13" t="s">
-        <v>491</v>
+        <v>527</v>
       </c>
       <c r="D13" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E13" t="s">
-        <v>539</v>
+        <v>579</v>
       </c>
       <c r="F13" t="s">
-        <v>593</v>
+        <v>633</v>
       </c>
       <c r="G13" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2507,22 +2627,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="C14" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D14" t="s">
-        <v>515</v>
+        <v>553</v>
       </c>
       <c r="E14" t="s">
-        <v>540</v>
+        <v>580</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>594</v>
+        <v>634</v>
       </c>
       <c r="G14" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2530,22 +2650,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="C15" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D15" t="s">
-        <v>515</v>
+        <v>553</v>
       </c>
       <c r="E15" t="s">
-        <v>541</v>
+        <v>581</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>595</v>
+        <v>635</v>
       </c>
       <c r="G15" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2553,16 +2673,16 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="C16" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="D16" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G16" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2570,16 +2690,16 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="C17" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="D17" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G17" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2587,16 +2707,16 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="C18" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="D18" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G18" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2604,16 +2724,16 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="C19" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="D19" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G19" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2621,16 +2741,16 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="C20" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="D20" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G20" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2638,16 +2758,16 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="C21" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="D21" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G21" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2655,16 +2775,16 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="C22" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="D22" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G22" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2672,16 +2792,16 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="C23" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="D23" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G23" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2689,16 +2809,16 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="C24" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="D24" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G24" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2706,16 +2826,16 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="C25" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="D25" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G25" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2723,16 +2843,16 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="C26" t="s">
-        <v>497</v>
+        <v>533</v>
       </c>
       <c r="D26" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G26" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2740,16 +2860,16 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="C27" t="s">
-        <v>497</v>
+        <v>533</v>
       </c>
       <c r="D27" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G27" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2757,16 +2877,16 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="C28" t="s">
-        <v>497</v>
+        <v>533</v>
       </c>
       <c r="D28" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G28" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2774,16 +2894,16 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="C29" t="s">
-        <v>497</v>
+        <v>533</v>
       </c>
       <c r="D29" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G29" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2791,16 +2911,16 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="C30" t="s">
-        <v>497</v>
+        <v>533</v>
       </c>
       <c r="D30" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G30" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2808,16 +2928,16 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="C31" t="s">
-        <v>497</v>
+        <v>533</v>
       </c>
       <c r="D31" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G31" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2825,16 +2945,16 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="C32" t="s">
-        <v>497</v>
+        <v>533</v>
       </c>
       <c r="D32" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G32" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2842,16 +2962,16 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="C33" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D33" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G33" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2859,16 +2979,16 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="C34" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D34" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G34" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2876,16 +2996,16 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="C35" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D35" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G35" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2893,16 +3013,16 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="C36" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D36" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G36" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2910,16 +3030,16 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="C37" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D37" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G37" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2927,16 +3047,16 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="C38" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D38" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G38" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2944,16 +3064,16 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="C39" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D39" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G39" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2961,16 +3081,16 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="C40" t="s">
-        <v>499</v>
+        <v>535</v>
       </c>
       <c r="D40" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G40" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2978,16 +3098,16 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="C41" t="s">
-        <v>499</v>
+        <v>535</v>
       </c>
       <c r="D41" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G41" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2995,16 +3115,16 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="C42" t="s">
-        <v>499</v>
+        <v>535</v>
       </c>
       <c r="D42" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G42" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3012,16 +3132,16 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="C43" t="s">
-        <v>499</v>
+        <v>535</v>
       </c>
       <c r="D43" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G43" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3029,16 +3149,16 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="C44" t="s">
-        <v>499</v>
+        <v>535</v>
       </c>
       <c r="D44" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G44" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3046,16 +3166,16 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="C45" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D45" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G45" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3063,16 +3183,16 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="C46" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D46" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G46" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3080,16 +3200,16 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="C47" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D47" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G47" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3097,16 +3217,16 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="C48" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D48" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G48" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -3114,16 +3234,16 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="C49" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D49" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G49" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -3131,16 +3251,16 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="C50" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D50" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G50" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -3148,16 +3268,16 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="C51" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D51" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G51" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -3165,16 +3285,16 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="C52" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D52" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G52" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -3182,16 +3302,16 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="C53" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D53" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G53" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3199,16 +3319,16 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="C54" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D54" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G54" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -3216,16 +3336,16 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="C55" t="s">
-        <v>500</v>
+        <v>536</v>
       </c>
       <c r="D55" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G55" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3233,16 +3353,16 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="C56" t="s">
-        <v>500</v>
+        <v>536</v>
       </c>
       <c r="D56" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G56" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3250,16 +3370,16 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="C57" t="s">
-        <v>500</v>
+        <v>536</v>
       </c>
       <c r="D57" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G57" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3267,16 +3387,16 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="C58" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="D58" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G58" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3284,16 +3404,16 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="C59" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="D59" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G59" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3301,16 +3421,16 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="C60" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="D60" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G60" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3318,16 +3438,16 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="C61" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="D61" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G61" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3335,16 +3455,16 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="C62" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="D62" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G62" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3352,16 +3472,16 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="C63" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="D63" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G63" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3369,16 +3489,16 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="C64" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="D64" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G64" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3386,16 +3506,16 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="C65" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="D65" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G65" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3403,16 +3523,16 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="C66" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="D66" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G66" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3420,16 +3540,16 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="C67" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="D67" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G67" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3437,16 +3557,16 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="C68" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="D68" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G68" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3454,16 +3574,16 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C69" t="s">
-        <v>497</v>
+        <v>533</v>
       </c>
       <c r="D69" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G69" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3471,16 +3591,16 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="C70" t="s">
-        <v>497</v>
+        <v>533</v>
       </c>
       <c r="D70" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G70" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3488,16 +3608,16 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="C71" t="s">
-        <v>497</v>
+        <v>533</v>
       </c>
       <c r="D71" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G71" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3505,16 +3625,16 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="C72" t="s">
-        <v>497</v>
+        <v>533</v>
       </c>
       <c r="D72" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G72" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3522,16 +3642,16 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="C73" t="s">
-        <v>497</v>
+        <v>533</v>
       </c>
       <c r="D73" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G73" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3539,16 +3659,16 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="C74" t="s">
-        <v>497</v>
+        <v>533</v>
       </c>
       <c r="D74" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G74" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3556,16 +3676,16 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="C75" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D75" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G75" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3573,16 +3693,16 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="C76" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D76" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G76" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3590,16 +3710,16 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="C77" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D77" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G77" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3607,16 +3727,16 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="C78" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D78" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G78" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3624,16 +3744,16 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="C79" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D79" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G79" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3641,16 +3761,16 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="C80" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D80" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G80" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3658,16 +3778,16 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="C81" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D81" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G81" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3675,16 +3795,16 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="C82" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D82" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G82" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3692,16 +3812,16 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="C83" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D83" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G83" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3709,16 +3829,16 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="C84" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D84" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G84" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3726,16 +3846,16 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="C85" t="s">
-        <v>499</v>
+        <v>535</v>
       </c>
       <c r="D85" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G85" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3743,16 +3863,16 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="C86" t="s">
-        <v>499</v>
+        <v>535</v>
       </c>
       <c r="D86" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G86" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3760,16 +3880,16 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="C87" t="s">
-        <v>499</v>
+        <v>535</v>
       </c>
       <c r="D87" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G87" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3777,16 +3897,16 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="C88" t="s">
-        <v>499</v>
+        <v>535</v>
       </c>
       <c r="D88" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G88" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3794,16 +3914,16 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="C89" t="s">
-        <v>499</v>
+        <v>535</v>
       </c>
       <c r="D89" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G89" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3811,16 +3931,16 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="C90" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D90" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G90" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3828,16 +3948,16 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="C91" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D91" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G91" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3845,16 +3965,16 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="C92" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D92" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G92" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3862,16 +3982,16 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="C93" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D93" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G93" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3879,16 +3999,16 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="C94" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D94" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G94" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3896,16 +4016,16 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="C95" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D95" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G95" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3913,16 +4033,16 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="C96" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D96" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G96" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3930,16 +4050,16 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="C97" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D97" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G97" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3947,16 +4067,16 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="C98" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D98" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G98" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -3964,16 +4084,16 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="C99" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D99" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G99" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -3981,16 +4101,16 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="C100" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D100" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G100" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -3998,16 +4118,16 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="C101" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D101" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G101" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4015,16 +4135,16 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="C102" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D102" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G102" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4032,16 +4152,16 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="C103" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D103" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G103" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4049,16 +4169,16 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="C104" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D104" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G104" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4066,16 +4186,16 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="C105" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D105" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G105" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4083,16 +4203,16 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="C106" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D106" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G106" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4100,16 +4220,16 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="C107" t="s">
-        <v>500</v>
+        <v>536</v>
       </c>
       <c r="D107" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G107" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4117,16 +4237,16 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="C108" t="s">
-        <v>500</v>
+        <v>536</v>
       </c>
       <c r="D108" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G108" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4134,16 +4254,16 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="C109" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="D109" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G109" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4151,16 +4271,16 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="C110" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="D110" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G110" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4168,16 +4288,16 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="C111" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="D111" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G111" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4185,16 +4305,16 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="C112" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="D112" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G112" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4202,16 +4322,16 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="C113" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="D113" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G113" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4219,16 +4339,16 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="C114" t="s">
-        <v>502</v>
+        <v>538</v>
       </c>
       <c r="D114" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G114" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4236,16 +4356,16 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="C115" t="s">
-        <v>502</v>
+        <v>538</v>
       </c>
       <c r="D115" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G115" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4253,16 +4373,16 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="C116" t="s">
-        <v>502</v>
+        <v>538</v>
       </c>
       <c r="D116" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G116" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4270,16 +4390,16 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="C117" t="s">
-        <v>502</v>
+        <v>538</v>
       </c>
       <c r="D117" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G117" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4287,16 +4407,16 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="C118" t="s">
-        <v>502</v>
+        <v>538</v>
       </c>
       <c r="D118" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G118" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4304,22 +4424,22 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="C119" t="s">
-        <v>502</v>
+        <v>538</v>
       </c>
       <c r="D119" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E119" t="s">
-        <v>542</v>
+        <v>582</v>
       </c>
       <c r="F119" t="s">
-        <v>596</v>
+        <v>636</v>
       </c>
       <c r="G119" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4327,19 +4447,19 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="C120" t="s">
-        <v>502</v>
+        <v>538</v>
       </c>
       <c r="D120" t="s">
-        <v>516</v>
+        <v>554</v>
       </c>
       <c r="E120" t="s">
-        <v>543</v>
+        <v>583</v>
       </c>
       <c r="G120" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4347,16 +4467,16 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C121" t="s">
-        <v>502</v>
+        <v>538</v>
       </c>
       <c r="D121" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G121" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4364,16 +4484,16 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="C122" t="s">
-        <v>500</v>
+        <v>536</v>
       </c>
       <c r="D122" t="s">
-        <v>517</v>
+        <v>555</v>
       </c>
       <c r="G122" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4381,22 +4501,22 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="C123" t="s">
-        <v>500</v>
+        <v>536</v>
       </c>
       <c r="D123" t="s">
-        <v>518</v>
+        <v>556</v>
       </c>
       <c r="E123" t="s">
-        <v>544</v>
+        <v>584</v>
       </c>
       <c r="F123" t="s">
-        <v>597</v>
+        <v>637</v>
       </c>
       <c r="G123" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4404,16 +4524,16 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="C124" t="s">
-        <v>500</v>
+        <v>536</v>
       </c>
       <c r="D124" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G124" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4421,16 +4541,16 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C125" t="s">
-        <v>500</v>
+        <v>536</v>
       </c>
       <c r="D125" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G125" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4438,16 +4558,16 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="C126" t="s">
-        <v>500</v>
+        <v>536</v>
       </c>
       <c r="D126" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G126" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4455,16 +4575,16 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="C127" t="s">
-        <v>500</v>
+        <v>536</v>
       </c>
       <c r="D127" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G127" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4472,19 +4592,19 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="C128" t="s">
-        <v>500</v>
+        <v>536</v>
       </c>
       <c r="D128" t="s">
-        <v>519</v>
+        <v>557</v>
       </c>
       <c r="E128" t="s">
-        <v>545</v>
+        <v>585</v>
       </c>
       <c r="G128" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4492,22 +4612,22 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="C129" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="D129" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E129" t="s">
-        <v>546</v>
+        <v>586</v>
       </c>
       <c r="F129" t="s">
-        <v>598</v>
+        <v>638</v>
       </c>
       <c r="G129" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4515,16 +4635,16 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="C130" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="D130" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G130" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4532,13 +4652,13 @@
         <v>136</v>
       </c>
       <c r="C131" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="D131" t="s">
-        <v>520</v>
+        <v>558</v>
       </c>
       <c r="E131" t="s">
-        <v>547</v>
+        <v>587</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4546,19 +4666,19 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="C132" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="D132" t="s">
-        <v>521</v>
+        <v>559</v>
       </c>
       <c r="E132" t="s">
-        <v>548</v>
+        <v>588</v>
       </c>
       <c r="G132" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4566,19 +4686,19 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="C133" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="D133" t="s">
-        <v>522</v>
+        <v>560</v>
       </c>
       <c r="E133" t="s">
-        <v>549</v>
+        <v>589</v>
       </c>
       <c r="G133" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4586,10 +4706,10 @@
         <v>139</v>
       </c>
       <c r="C134" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="D134" t="s">
-        <v>523</v>
+        <v>561</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4597,10 +4717,10 @@
         <v>140</v>
       </c>
       <c r="C135" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="D135" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4608,16 +4728,16 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="C136" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D136" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G136" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4625,16 +4745,16 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="C137" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D137" t="s">
-        <v>520</v>
+        <v>558</v>
       </c>
       <c r="G137" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4642,10 +4762,10 @@
         <v>143</v>
       </c>
       <c r="C138" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D138" t="s">
-        <v>524</v>
+        <v>562</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4653,10 +4773,10 @@
         <v>144</v>
       </c>
       <c r="C139" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D139" t="s">
-        <v>525</v>
+        <v>563</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4664,10 +4784,10 @@
         <v>145</v>
       </c>
       <c r="C140" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D140" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4675,16 +4795,16 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="C141" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D141" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G141" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4692,22 +4812,22 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="C142" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D142" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E142" t="s">
-        <v>550</v>
+        <v>590</v>
       </c>
       <c r="F142" t="s">
-        <v>599</v>
+        <v>639</v>
       </c>
       <c r="G142" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4715,16 +4835,16 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="C143" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D143" t="s">
-        <v>524</v>
+        <v>562</v>
       </c>
       <c r="G143" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4732,13 +4852,13 @@
         <v>149</v>
       </c>
       <c r="C144" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D144" t="s">
-        <v>526</v>
+        <v>564</v>
       </c>
       <c r="E144" t="s">
-        <v>551</v>
+        <v>591</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4746,10 +4866,10 @@
         <v>150</v>
       </c>
       <c r="C145" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D145" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4757,19 +4877,19 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="C146" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D146" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="F146" t="s">
-        <v>600</v>
+        <v>640</v>
       </c>
       <c r="G146" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -4777,22 +4897,22 @@
         <v>152</v>
       </c>
       <c r="B147" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="C147" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D147" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E147" t="s">
-        <v>552</v>
+        <v>592</v>
       </c>
       <c r="F147" t="s">
-        <v>601</v>
+        <v>641</v>
       </c>
       <c r="G147" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -4800,19 +4920,19 @@
         <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="C148" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D148" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E148" t="s">
-        <v>553</v>
+        <v>593</v>
       </c>
       <c r="G148" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -4820,19 +4940,19 @@
         <v>154</v>
       </c>
       <c r="B149" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="C149" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D149" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E149" t="s">
-        <v>554</v>
+        <v>594</v>
       </c>
       <c r="G149" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -4840,19 +4960,19 @@
         <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="C150" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D150" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E150" t="s">
-        <v>555</v>
+        <v>595</v>
       </c>
       <c r="G150" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -4860,19 +4980,19 @@
         <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="C151" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D151" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E151" t="s">
-        <v>556</v>
+        <v>596</v>
       </c>
       <c r="G151" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -4880,19 +5000,19 @@
         <v>157</v>
       </c>
       <c r="B152" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="C152" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D152" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E152" t="s">
-        <v>557</v>
+        <v>597</v>
       </c>
       <c r="G152" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -4900,10 +5020,10 @@
         <v>158</v>
       </c>
       <c r="C153" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D153" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -4911,19 +5031,19 @@
         <v>159</v>
       </c>
       <c r="B154" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="C154" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D154" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E154" t="s">
-        <v>558</v>
+        <v>598</v>
       </c>
       <c r="G154" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -4931,16 +5051,16 @@
         <v>160</v>
       </c>
       <c r="B155" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C155" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D155" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G155" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -4948,16 +5068,16 @@
         <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="C156" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D156" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G156" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -4965,22 +5085,22 @@
         <v>162</v>
       </c>
       <c r="B157" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="C157" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D157" t="s">
-        <v>527</v>
+        <v>565</v>
       </c>
       <c r="E157" t="s">
-        <v>559</v>
+        <v>599</v>
       </c>
       <c r="F157" t="s">
-        <v>602</v>
+        <v>642</v>
       </c>
       <c r="G157" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -4988,19 +5108,19 @@
         <v>163</v>
       </c>
       <c r="B158" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="C158" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D158" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E158" t="s">
-        <v>560</v>
+        <v>600</v>
       </c>
       <c r="G158" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5008,19 +5128,19 @@
         <v>164</v>
       </c>
       <c r="B159" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="C159" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D159" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E159" t="s">
-        <v>561</v>
+        <v>601</v>
       </c>
       <c r="G159" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5028,19 +5148,19 @@
         <v>165</v>
       </c>
       <c r="B160" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="C160" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D160" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E160" t="s">
-        <v>562</v>
+        <v>602</v>
       </c>
       <c r="G160" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5048,19 +5168,19 @@
         <v>166</v>
       </c>
       <c r="B161" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="C161" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D161" t="s">
-        <v>528</v>
+        <v>566</v>
       </c>
       <c r="E161" t="s">
-        <v>563</v>
+        <v>603</v>
       </c>
       <c r="G161" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5068,16 +5188,16 @@
         <v>167</v>
       </c>
       <c r="B162" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="C162" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D162" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G162" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5085,19 +5205,19 @@
         <v>168</v>
       </c>
       <c r="B163" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="C163" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D163" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E163" t="s">
-        <v>564</v>
+        <v>604</v>
       </c>
       <c r="G163" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5105,19 +5225,19 @@
         <v>169</v>
       </c>
       <c r="B164" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="C164" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D164" t="s">
-        <v>529</v>
+        <v>567</v>
       </c>
       <c r="E164" t="s">
-        <v>565</v>
+        <v>605</v>
       </c>
       <c r="G164" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5125,13 +5245,13 @@
         <v>170</v>
       </c>
       <c r="C165" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D165" t="s">
-        <v>520</v>
+        <v>558</v>
       </c>
       <c r="E165" t="s">
-        <v>566</v>
+        <v>606</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5139,19 +5259,19 @@
         <v>171</v>
       </c>
       <c r="B166" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="C166" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D166" t="s">
-        <v>530</v>
+        <v>568</v>
       </c>
       <c r="E166" t="s">
-        <v>567</v>
+        <v>607</v>
       </c>
       <c r="G166" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5159,19 +5279,19 @@
         <v>172</v>
       </c>
       <c r="B167" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="C167" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D167" t="s">
-        <v>531</v>
+        <v>569</v>
       </c>
       <c r="E167" t="s">
-        <v>568</v>
+        <v>608</v>
       </c>
       <c r="G167" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5179,19 +5299,19 @@
         <v>173</v>
       </c>
       <c r="B168" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="C168" t="s">
-        <v>491</v>
+        <v>527</v>
       </c>
       <c r="D168" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E168" t="s">
-        <v>569</v>
+        <v>609</v>
       </c>
       <c r="G168" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5199,19 +5319,19 @@
         <v>174</v>
       </c>
       <c r="B169" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="C169" t="s">
-        <v>491</v>
+        <v>527</v>
       </c>
       <c r="D169" t="s">
-        <v>532</v>
+        <v>570</v>
       </c>
       <c r="E169" t="s">
-        <v>570</v>
+        <v>610</v>
       </c>
       <c r="G169" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5219,13 +5339,13 @@
         <v>175</v>
       </c>
       <c r="C170" t="s">
-        <v>491</v>
+        <v>527</v>
       </c>
       <c r="D170" t="s">
-        <v>533</v>
+        <v>571</v>
       </c>
       <c r="E170" t="s">
-        <v>571</v>
+        <v>611</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5233,13 +5353,13 @@
         <v>176</v>
       </c>
       <c r="C171" t="s">
-        <v>491</v>
+        <v>527</v>
       </c>
       <c r="D171" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E171" t="s">
-        <v>572</v>
+        <v>612</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5247,13 +5367,13 @@
         <v>177</v>
       </c>
       <c r="C172" t="s">
-        <v>491</v>
+        <v>527</v>
       </c>
       <c r="D172" t="s">
-        <v>520</v>
+        <v>558</v>
       </c>
       <c r="E172" t="s">
-        <v>573</v>
+        <v>613</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5261,16 +5381,16 @@
         <v>178</v>
       </c>
       <c r="B173" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="C173" t="s">
-        <v>503</v>
+        <v>539</v>
       </c>
       <c r="D173" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G173" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5278,19 +5398,19 @@
         <v>179</v>
       </c>
       <c r="B174" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="C174" t="s">
-        <v>503</v>
+        <v>539</v>
       </c>
       <c r="D174" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="F174" t="s">
-        <v>603</v>
+        <v>643</v>
       </c>
       <c r="G174" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5298,19 +5418,19 @@
         <v>180</v>
       </c>
       <c r="B175" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="C175" t="s">
-        <v>503</v>
+        <v>539</v>
       </c>
       <c r="D175" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="F175" t="s">
-        <v>604</v>
+        <v>644</v>
       </c>
       <c r="G175" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5318,10 +5438,10 @@
         <v>181</v>
       </c>
       <c r="C176" t="s">
-        <v>504</v>
+        <v>540</v>
       </c>
       <c r="D176" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5329,10 +5449,10 @@
         <v>182</v>
       </c>
       <c r="C177" t="s">
-        <v>504</v>
+        <v>540</v>
       </c>
       <c r="D177" t="s">
-        <v>534</v>
+        <v>572</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5340,10 +5460,10 @@
         <v>183</v>
       </c>
       <c r="C178" t="s">
-        <v>504</v>
+        <v>540</v>
       </c>
       <c r="D178" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5351,22 +5471,22 @@
         <v>184</v>
       </c>
       <c r="B179" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="C179" t="s">
-        <v>505</v>
+        <v>541</v>
       </c>
       <c r="D179" t="s">
-        <v>534</v>
+        <v>572</v>
       </c>
       <c r="E179" t="s">
-        <v>574</v>
+        <v>614</v>
       </c>
       <c r="F179" t="s">
-        <v>605</v>
+        <v>645</v>
       </c>
       <c r="G179" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5374,10 +5494,10 @@
         <v>185</v>
       </c>
       <c r="C180" t="s">
-        <v>505</v>
+        <v>541</v>
       </c>
       <c r="D180" t="s">
-        <v>535</v>
+        <v>573</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5385,10 +5505,10 @@
         <v>186</v>
       </c>
       <c r="C181" t="s">
-        <v>505</v>
+        <v>541</v>
       </c>
       <c r="D181" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5396,19 +5516,19 @@
         <v>187</v>
       </c>
       <c r="B182" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
       <c r="C182" t="s">
-        <v>506</v>
+        <v>542</v>
       </c>
       <c r="D182" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E182" t="s">
-        <v>575</v>
+        <v>615</v>
       </c>
       <c r="G182" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5416,19 +5536,19 @@
         <v>188</v>
       </c>
       <c r="B183" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="C183" t="s">
-        <v>506</v>
+        <v>542</v>
       </c>
       <c r="D183" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="F183" t="s">
-        <v>606</v>
+        <v>646</v>
       </c>
       <c r="G183" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5436,10 +5556,10 @@
         <v>189</v>
       </c>
       <c r="C184" t="s">
-        <v>506</v>
+        <v>542</v>
       </c>
       <c r="D184" t="s">
-        <v>535</v>
+        <v>573</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5447,13 +5567,13 @@
         <v>190</v>
       </c>
       <c r="C185" t="s">
-        <v>506</v>
+        <v>542</v>
       </c>
       <c r="D185" t="s">
-        <v>536</v>
+        <v>574</v>
       </c>
       <c r="F185" t="s">
-        <v>607</v>
+        <v>647</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5461,13 +5581,13 @@
         <v>191</v>
       </c>
       <c r="C186" t="s">
-        <v>507</v>
+        <v>543</v>
       </c>
       <c r="D186" t="s">
-        <v>537</v>
+        <v>575</v>
       </c>
       <c r="E186" t="s">
-        <v>576</v>
+        <v>616</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5475,13 +5595,13 @@
         <v>192</v>
       </c>
       <c r="C187" t="s">
-        <v>507</v>
+        <v>543</v>
       </c>
       <c r="D187" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E187" t="s">
-        <v>577</v>
+        <v>617</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5489,13 +5609,13 @@
         <v>193</v>
       </c>
       <c r="C188" t="s">
-        <v>507</v>
+        <v>543</v>
       </c>
       <c r="D188" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E188" t="s">
-        <v>578</v>
+        <v>618</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5503,13 +5623,13 @@
         <v>194</v>
       </c>
       <c r="C189" t="s">
-        <v>507</v>
+        <v>543</v>
       </c>
       <c r="D189" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E189" t="s">
-        <v>579</v>
+        <v>619</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5517,13 +5637,13 @@
         <v>195</v>
       </c>
       <c r="C190" t="s">
-        <v>507</v>
+        <v>543</v>
       </c>
       <c r="D190" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E190" t="s">
-        <v>580</v>
+        <v>620</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5531,10 +5651,10 @@
         <v>196</v>
       </c>
       <c r="C191" t="s">
-        <v>507</v>
+        <v>543</v>
       </c>
       <c r="D191" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -5542,10 +5662,10 @@
         <v>197</v>
       </c>
       <c r="C192" t="s">
-        <v>507</v>
+        <v>543</v>
       </c>
       <c r="D192" t="s">
-        <v>538</v>
+        <v>576</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -5553,10 +5673,10 @@
         <v>198</v>
       </c>
       <c r="C193" t="s">
-        <v>507</v>
+        <v>543</v>
       </c>
       <c r="D193" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -5564,16 +5684,16 @@
         <v>199</v>
       </c>
       <c r="B194" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="C194" t="s">
-        <v>507</v>
+        <v>543</v>
       </c>
       <c r="D194" t="s">
-        <v>517</v>
+        <v>555</v>
       </c>
       <c r="G194" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -5581,16 +5701,16 @@
         <v>200</v>
       </c>
       <c r="B195" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="C195" t="s">
-        <v>507</v>
+        <v>543</v>
       </c>
       <c r="D195" t="s">
-        <v>517</v>
+        <v>555</v>
       </c>
       <c r="G195" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -5598,19 +5718,19 @@
         <v>201</v>
       </c>
       <c r="B196" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="C196" t="s">
-        <v>494</v>
+        <v>530</v>
       </c>
       <c r="D196" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="F196" t="s">
-        <v>608</v>
+        <v>648</v>
       </c>
       <c r="G196" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -5618,22 +5738,22 @@
         <v>202</v>
       </c>
       <c r="B197" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="C197" t="s">
-        <v>494</v>
+        <v>530</v>
       </c>
       <c r="D197" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E197" t="s">
-        <v>581</v>
+        <v>621</v>
       </c>
       <c r="F197" t="s">
-        <v>609</v>
+        <v>649</v>
       </c>
       <c r="G197" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -5641,22 +5761,22 @@
         <v>203</v>
       </c>
       <c r="B198" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="C198" t="s">
-        <v>494</v>
+        <v>530</v>
       </c>
       <c r="D198" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E198" t="s">
-        <v>582</v>
+        <v>622</v>
       </c>
       <c r="F198" t="s">
-        <v>610</v>
+        <v>650</v>
       </c>
       <c r="G198" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -5664,22 +5784,22 @@
         <v>204</v>
       </c>
       <c r="B199" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="C199" t="s">
-        <v>494</v>
+        <v>530</v>
       </c>
       <c r="D199" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E199" t="s">
-        <v>583</v>
+        <v>623</v>
       </c>
       <c r="F199" t="s">
-        <v>611</v>
+        <v>651</v>
       </c>
       <c r="G199" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -5687,16 +5807,16 @@
         <v>205</v>
       </c>
       <c r="B200" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="C200" t="s">
-        <v>508</v>
+        <v>544</v>
       </c>
       <c r="D200" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G200" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -5704,10 +5824,10 @@
         <v>206</v>
       </c>
       <c r="C201" t="s">
-        <v>508</v>
+        <v>544</v>
       </c>
       <c r="D201" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -5715,10 +5835,10 @@
         <v>207</v>
       </c>
       <c r="C202" t="s">
-        <v>508</v>
+        <v>544</v>
       </c>
       <c r="D202" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -5726,10 +5846,10 @@
         <v>208</v>
       </c>
       <c r="C203" t="s">
-        <v>508</v>
+        <v>544</v>
       </c>
       <c r="D203" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -5737,16 +5857,16 @@
         <v>209</v>
       </c>
       <c r="B204" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="C204" t="s">
-        <v>509</v>
+        <v>545</v>
       </c>
       <c r="D204" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G204" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -5754,10 +5874,10 @@
         <v>210</v>
       </c>
       <c r="C205" t="s">
-        <v>509</v>
+        <v>545</v>
       </c>
       <c r="D205" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -5765,10 +5885,10 @@
         <v>211</v>
       </c>
       <c r="C206" t="s">
-        <v>509</v>
+        <v>545</v>
       </c>
       <c r="D206" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -5776,19 +5896,19 @@
         <v>212</v>
       </c>
       <c r="B207" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="C207" t="s">
-        <v>509</v>
+        <v>545</v>
       </c>
       <c r="D207" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E207" t="s">
-        <v>584</v>
+        <v>624</v>
       </c>
       <c r="G207" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -5796,13 +5916,13 @@
         <v>213</v>
       </c>
       <c r="C208" t="s">
-        <v>509</v>
+        <v>545</v>
       </c>
       <c r="D208" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E208" t="s">
-        <v>585</v>
+        <v>625</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -5810,10 +5930,10 @@
         <v>214</v>
       </c>
       <c r="C209" t="s">
-        <v>509</v>
+        <v>545</v>
       </c>
       <c r="D209" t="s">
-        <v>523</v>
+        <v>561</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -5821,19 +5941,19 @@
         <v>215</v>
       </c>
       <c r="B210" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="C210" t="s">
-        <v>510</v>
+        <v>546</v>
       </c>
       <c r="D210" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E210" t="s">
-        <v>586</v>
+        <v>626</v>
       </c>
       <c r="G210" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -5841,16 +5961,16 @@
         <v>216</v>
       </c>
       <c r="B211" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="C211" t="s">
-        <v>510</v>
+        <v>546</v>
       </c>
       <c r="D211" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G211" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -5858,13 +5978,13 @@
         <v>217</v>
       </c>
       <c r="C212" t="s">
-        <v>510</v>
+        <v>546</v>
       </c>
       <c r="D212" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E212" t="s">
-        <v>587</v>
+        <v>627</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -5872,13 +5992,13 @@
         <v>218</v>
       </c>
       <c r="C213" t="s">
-        <v>510</v>
+        <v>546</v>
       </c>
       <c r="D213" t="s">
-        <v>527</v>
+        <v>565</v>
       </c>
       <c r="E213" t="s">
-        <v>588</v>
+        <v>628</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -5886,16 +6006,16 @@
         <v>219</v>
       </c>
       <c r="B214" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="C214" t="s">
-        <v>493</v>
+        <v>529</v>
       </c>
       <c r="D214" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G214" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -5903,16 +6023,16 @@
         <v>220</v>
       </c>
       <c r="B215" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="C215" t="s">
-        <v>493</v>
+        <v>529</v>
       </c>
       <c r="D215" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G215" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -5920,13 +6040,13 @@
         <v>221</v>
       </c>
       <c r="C216" t="s">
-        <v>493</v>
+        <v>529</v>
       </c>
       <c r="D216" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E216" t="s">
-        <v>589</v>
+        <v>629</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -5934,19 +6054,19 @@
         <v>222</v>
       </c>
       <c r="B217" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="C217" t="s">
-        <v>511</v>
+        <v>547</v>
       </c>
       <c r="D217" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E217" t="s">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="G217" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -5954,19 +6074,19 @@
         <v>223</v>
       </c>
       <c r="B218" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="C218" t="s">
-        <v>511</v>
+        <v>547</v>
       </c>
       <c r="D218" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E218" t="s">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="G218" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -5974,19 +6094,19 @@
         <v>224</v>
       </c>
       <c r="B219" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="C219" t="s">
-        <v>512</v>
+        <v>548</v>
       </c>
       <c r="D219" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E219" t="s">
-        <v>591</v>
+        <v>631</v>
       </c>
       <c r="G219" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -5994,10 +6114,10 @@
         <v>225</v>
       </c>
       <c r="C220" t="s">
-        <v>512</v>
+        <v>548</v>
       </c>
       <c r="D220" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6005,16 +6125,16 @@
         <v>226</v>
       </c>
       <c r="B221" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="C221" t="s">
-        <v>512</v>
+        <v>548</v>
       </c>
       <c r="D221" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G221" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6022,19 +6142,19 @@
         <v>227</v>
       </c>
       <c r="B222" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="C222" t="s">
-        <v>513</v>
+        <v>549</v>
       </c>
       <c r="D222" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E222" t="s">
-        <v>592</v>
+        <v>632</v>
       </c>
       <c r="G222" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6042,16 +6162,16 @@
         <v>228</v>
       </c>
       <c r="B223" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="C223" t="s">
-        <v>513</v>
+        <v>549</v>
       </c>
       <c r="D223" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G223" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6059,16 +6179,16 @@
         <v>229</v>
       </c>
       <c r="B224" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="C224" t="s">
-        <v>513</v>
+        <v>549</v>
       </c>
       <c r="D224" t="s">
-        <v>536</v>
+        <v>574</v>
       </c>
       <c r="G224" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6076,19 +6196,19 @@
         <v>230</v>
       </c>
       <c r="B225" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="C225" t="s">
-        <v>513</v>
+        <v>549</v>
       </c>
       <c r="D225" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="F225" t="s">
-        <v>612</v>
+        <v>652</v>
       </c>
       <c r="G225" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6096,16 +6216,16 @@
         <v>231</v>
       </c>
       <c r="B226" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="C226" t="s">
-        <v>513</v>
+        <v>549</v>
       </c>
       <c r="D226" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G226" t="s">
-        <v>613</v>
+        <v>653</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6113,10 +6233,10 @@
         <v>232</v>
       </c>
       <c r="C227" t="s">
-        <v>513</v>
+        <v>549</v>
       </c>
       <c r="D227" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6124,13 +6244,16 @@
         <v>233</v>
       </c>
       <c r="B228" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="C228" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D228" t="s">
-        <v>514</v>
+        <v>552</v>
+      </c>
+      <c r="G228" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6138,13 +6261,16 @@
         <v>234</v>
       </c>
       <c r="B229" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="C229" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D229" t="s">
-        <v>514</v>
+        <v>552</v>
+      </c>
+      <c r="G229" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6152,13 +6278,16 @@
         <v>235</v>
       </c>
       <c r="B230" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="C230" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D230" t="s">
-        <v>514</v>
+        <v>552</v>
+      </c>
+      <c r="G230" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6166,13 +6295,16 @@
         <v>236</v>
       </c>
       <c r="B231" t="s">
-        <v>456</v>
+        <v>474</v>
       </c>
       <c r="C231" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D231" t="s">
-        <v>514</v>
+        <v>552</v>
+      </c>
+      <c r="G231" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6180,13 +6312,16 @@
         <v>237</v>
       </c>
       <c r="B232" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="C232" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D232" t="s">
-        <v>514</v>
+        <v>552</v>
+      </c>
+      <c r="G232" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6194,13 +6329,16 @@
         <v>238</v>
       </c>
       <c r="B233" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="C233" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D233" t="s">
-        <v>514</v>
+        <v>552</v>
+      </c>
+      <c r="G233" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6208,13 +6346,16 @@
         <v>239</v>
       </c>
       <c r="B234" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="C234" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D234" t="s">
-        <v>514</v>
+        <v>552</v>
+      </c>
+      <c r="G234" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -6222,13 +6363,16 @@
         <v>240</v>
       </c>
       <c r="B235" t="s">
-        <v>460</v>
+        <v>478</v>
       </c>
       <c r="C235" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D235" t="s">
-        <v>514</v>
+        <v>552</v>
+      </c>
+      <c r="G235" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -6236,13 +6380,16 @@
         <v>241</v>
       </c>
       <c r="B236" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="C236" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D236" t="s">
-        <v>514</v>
+        <v>552</v>
+      </c>
+      <c r="G236" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -6250,13 +6397,16 @@
         <v>242</v>
       </c>
       <c r="B237" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="C237" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D237" t="s">
-        <v>514</v>
+        <v>552</v>
+      </c>
+      <c r="G237" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -6264,13 +6414,16 @@
         <v>243</v>
       </c>
       <c r="B238" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="C238" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D238" t="s">
-        <v>514</v>
+        <v>552</v>
+      </c>
+      <c r="G238" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -6278,13 +6431,16 @@
         <v>244</v>
       </c>
       <c r="B239" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="C239" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D239" t="s">
-        <v>514</v>
+        <v>552</v>
+      </c>
+      <c r="G239" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -6292,363 +6448,717 @@
         <v>245</v>
       </c>
       <c r="B240" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="C240" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D240" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="241" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G240" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
       <c r="A241" t="s">
         <v>246</v>
       </c>
       <c r="B241" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="C241" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D241" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G241" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
       <c r="A242" t="s">
         <v>247</v>
       </c>
       <c r="B242" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="C242" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D242" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="243" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G242" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7">
       <c r="A243" t="s">
         <v>248</v>
       </c>
       <c r="B243" t="s">
-        <v>468</v>
+        <v>486</v>
       </c>
       <c r="C243" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D243" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="244" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G243" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
       <c r="A244" t="s">
         <v>249</v>
       </c>
       <c r="B244" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="C244" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D244" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="245" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G244" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
       <c r="A245" t="s">
         <v>250</v>
       </c>
       <c r="B245" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="C245" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D245" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G245" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7">
       <c r="A246" t="s">
         <v>251</v>
       </c>
       <c r="B246" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="C246" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D246" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="247" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G246" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7">
       <c r="A247" t="s">
         <v>252</v>
       </c>
       <c r="B247" t="s">
-        <v>472</v>
+        <v>490</v>
       </c>
       <c r="C247" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D247" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G247" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7">
       <c r="A248" t="s">
         <v>253</v>
       </c>
       <c r="B248" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="C248" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="D248" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G248" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7">
       <c r="A249" t="s">
         <v>254</v>
       </c>
       <c r="B249" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="C249" t="s">
-        <v>500</v>
+        <v>536</v>
       </c>
       <c r="D249" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G249" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
       <c r="A250" t="s">
         <v>255</v>
       </c>
       <c r="B250" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="C250" t="s">
-        <v>500</v>
+        <v>536</v>
       </c>
       <c r="D250" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="251" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G250" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
       <c r="A251" t="s">
         <v>256</v>
       </c>
       <c r="B251" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
       <c r="C251" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G251" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
       <c r="A252" t="s">
         <v>257</v>
       </c>
       <c r="B252" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="C252" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G252" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7">
       <c r="A253" t="s">
         <v>258</v>
       </c>
       <c r="B253" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="C253" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="D253" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="254" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G253" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7">
       <c r="A254" t="s">
         <v>259</v>
       </c>
       <c r="B254" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="C254" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="D254" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G254" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7">
       <c r="A255" t="s">
         <v>260</v>
       </c>
       <c r="B255" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="C255" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="D255" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G255" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7">
       <c r="A256" t="s">
         <v>261</v>
       </c>
       <c r="B256" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="C256" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D256" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G256" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
       <c r="A257" t="s">
         <v>262</v>
       </c>
       <c r="B257" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="C257" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D257" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G257" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
       <c r="A258" t="s">
         <v>263</v>
       </c>
       <c r="B258" t="s">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="C258" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D258" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="259" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G258" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
       <c r="A259" t="s">
         <v>264</v>
       </c>
       <c r="B259" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
       <c r="C259" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D259" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G259" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
       <c r="A260" t="s">
         <v>265</v>
       </c>
       <c r="B260" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="C260" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D260" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G260" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
       <c r="A261" t="s">
         <v>266</v>
       </c>
       <c r="B261" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="C261" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D261" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="262" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G261" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
       <c r="A262" t="s">
         <v>267</v>
       </c>
       <c r="B262" t="s">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="C262" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D262" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G262" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7">
       <c r="A263" t="s">
         <v>268</v>
       </c>
       <c r="B263" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="C263" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D263" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G263" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
       <c r="A264" t="s">
         <v>269</v>
       </c>
       <c r="B264" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="C264" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D264" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4">
+        <v>552</v>
+      </c>
+      <c r="G264" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
       <c r="A265" t="s">
         <v>270</v>
       </c>
       <c r="B265" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="C265" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="D265" t="s">
+        <v>552</v>
+      </c>
+      <c r="G265" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
+      <c r="A266" t="s">
+        <v>271</v>
+      </c>
+      <c r="B266" t="s">
+        <v>509</v>
+      </c>
+      <c r="C266" t="s">
+        <v>532</v>
+      </c>
+      <c r="D266" t="s">
+        <v>577</v>
+      </c>
+      <c r="G266" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
+      <c r="A267" t="s">
+        <v>272</v>
+      </c>
+      <c r="B267" t="s">
+        <v>510</v>
+      </c>
+      <c r="C267" t="s">
+        <v>550</v>
+      </c>
+      <c r="D267" t="s">
+        <v>577</v>
+      </c>
+      <c r="G267" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7">
+      <c r="A268" t="s">
+        <v>273</v>
+      </c>
+      <c r="B268" t="s">
+        <v>511</v>
+      </c>
+      <c r="C268" t="s">
+        <v>528</v>
+      </c>
+      <c r="D268" t="s">
+        <v>577</v>
+      </c>
+      <c r="G268" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
+      <c r="A269" t="s">
+        <v>274</v>
+      </c>
+      <c r="B269" t="s">
+        <v>512</v>
+      </c>
+      <c r="C269" t="s">
+        <v>551</v>
+      </c>
+      <c r="D269" t="s">
+        <v>577</v>
+      </c>
+      <c r="G269" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
+      <c r="A270" t="s">
+        <v>275</v>
+      </c>
+      <c r="B270" t="s">
+        <v>513</v>
+      </c>
+      <c r="C270" t="s">
+        <v>537</v>
+      </c>
+      <c r="D270" t="s">
+        <v>577</v>
+      </c>
+      <c r="G270" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7">
+      <c r="A271" t="s">
+        <v>276</v>
+      </c>
+      <c r="B271" t="s">
         <v>514</v>
+      </c>
+      <c r="C271" t="s">
+        <v>534</v>
+      </c>
+      <c r="D271" t="s">
+        <v>577</v>
+      </c>
+      <c r="G271" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
+      <c r="A272" t="s">
+        <v>277</v>
+      </c>
+      <c r="B272" t="s">
+        <v>515</v>
+      </c>
+      <c r="C272" t="s">
+        <v>534</v>
+      </c>
+      <c r="D272" t="s">
+        <v>577</v>
+      </c>
+      <c r="G272" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
+      <c r="A273" t="s">
+        <v>278</v>
+      </c>
+      <c r="B273" t="s">
+        <v>516</v>
+      </c>
+      <c r="C273" t="s">
+        <v>534</v>
+      </c>
+      <c r="D273" t="s">
+        <v>577</v>
+      </c>
+      <c r="G273" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
+      <c r="A274" t="s">
+        <v>279</v>
+      </c>
+      <c r="B274" t="s">
+        <v>517</v>
+      </c>
+      <c r="C274" t="s">
+        <v>528</v>
+      </c>
+      <c r="D274" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
+      <c r="A275" t="s">
+        <v>280</v>
+      </c>
+      <c r="B275" t="s">
+        <v>518</v>
+      </c>
+      <c r="C275" t="s">
+        <v>528</v>
+      </c>
+      <c r="D275" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
+      <c r="A276" t="s">
+        <v>281</v>
+      </c>
+      <c r="B276" t="s">
+        <v>519</v>
+      </c>
+      <c r="C276" t="s">
+        <v>532</v>
+      </c>
+      <c r="D276" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
+      <c r="A277" t="s">
+        <v>282</v>
+      </c>
+      <c r="B277" t="s">
+        <v>520</v>
+      </c>
+      <c r="C277" t="s">
+        <v>532</v>
+      </c>
+      <c r="D277" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
+      <c r="A278" t="s">
+        <v>283</v>
+      </c>
+      <c r="B278" t="s">
+        <v>521</v>
+      </c>
+      <c r="C278" t="s">
+        <v>532</v>
+      </c>
+      <c r="D278" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
+      <c r="A279" t="s">
+        <v>284</v>
+      </c>
+      <c r="B279" t="s">
+        <v>522</v>
+      </c>
+      <c r="C279" t="s">
+        <v>534</v>
+      </c>
+      <c r="D279" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
+      <c r="A280" t="s">
+        <v>285</v>
+      </c>
+      <c r="B280" t="s">
+        <v>523</v>
+      </c>
+      <c r="C280" t="s">
+        <v>528</v>
+      </c>
+      <c r="D280" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
+      <c r="A281" t="s">
+        <v>286</v>
+      </c>
+      <c r="B281" t="s">
+        <v>524</v>
+      </c>
+      <c r="C281" t="s">
+        <v>534</v>
+      </c>
+      <c r="D281" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282" t="s">
+        <v>287</v>
+      </c>
+      <c r="B282" t="s">
+        <v>525</v>
+      </c>
+      <c r="C282" t="s">
+        <v>533</v>
+      </c>
+      <c r="D282" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283" t="s">
+        <v>288</v>
+      </c>
+      <c r="B283" t="s">
+        <v>526</v>
+      </c>
+      <c r="C283" t="s">
+        <v>534</v>
+      </c>
+      <c r="D283" t="s">
+        <v>566</v>
       </c>
     </row>
   </sheetData>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="654">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -7034,6 +7034,9 @@
       <c r="D274" t="s">
         <v>577</v>
       </c>
+      <c r="G274" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="275" spans="1:7">
       <c r="A275" t="s">

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="654">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -7051,6 +7051,9 @@
       <c r="D275" t="s">
         <v>577</v>
       </c>
+      <c r="G275" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="276" spans="1:7">
       <c r="A276" t="s">
@@ -7065,6 +7068,9 @@
       <c r="D276" t="s">
         <v>577</v>
       </c>
+      <c r="G276" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="277" spans="1:7">
       <c r="A277" t="s">
@@ -7079,6 +7085,9 @@
       <c r="D277" t="s">
         <v>577</v>
       </c>
+      <c r="G277" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="278" spans="1:7">
       <c r="A278" t="s">
@@ -7093,6 +7102,9 @@
       <c r="D278" t="s">
         <v>577</v>
       </c>
+      <c r="G278" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="279" spans="1:7">
       <c r="A279" t="s">
@@ -7107,6 +7119,9 @@
       <c r="D279" t="s">
         <v>577</v>
       </c>
+      <c r="G279" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="280" spans="1:7">
       <c r="A280" t="s">
@@ -7121,6 +7136,9 @@
       <c r="D280" t="s">
         <v>566</v>
       </c>
+      <c r="G280" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="281" spans="1:7">
       <c r="A281" t="s">
@@ -7135,6 +7153,9 @@
       <c r="D281" t="s">
         <v>578</v>
       </c>
+      <c r="G281" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="282" spans="1:7">
       <c r="A282" t="s">
@@ -7149,6 +7170,9 @@
       <c r="D282" t="s">
         <v>566</v>
       </c>
+      <c r="G282" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="283" spans="1:7">
       <c r="A283" t="s">
@@ -7162,6 +7186,9 @@
       </c>
       <c r="D283" t="s">
         <v>566</v>
+      </c>
+      <c r="G283" t="s">
+        <v>653</v>
       </c>
     </row>
   </sheetData>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="653">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -1973,9 +1973,6 @@
   </si>
   <si>
     <t>www.cmacofct.com</t>
-  </si>
-  <si>
-    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -2365,9 +2362,6 @@
       <c r="F2" t="s">
         <v>633</v>
       </c>
-      <c r="G2" t="s">
-        <v>653</v>
-      </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
@@ -2388,9 +2382,6 @@
       <c r="F3" t="s">
         <v>633</v>
       </c>
-      <c r="G3" t="s">
-        <v>653</v>
-      </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
@@ -2411,9 +2402,6 @@
       <c r="F4" t="s">
         <v>633</v>
       </c>
-      <c r="G4" t="s">
-        <v>653</v>
-      </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
@@ -2434,9 +2422,6 @@
       <c r="F5" t="s">
         <v>633</v>
       </c>
-      <c r="G5" t="s">
-        <v>653</v>
-      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
@@ -2457,9 +2442,6 @@
       <c r="F6" t="s">
         <v>633</v>
       </c>
-      <c r="G6" t="s">
-        <v>653</v>
-      </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
@@ -2480,9 +2462,6 @@
       <c r="F7" t="s">
         <v>633</v>
       </c>
-      <c r="G7" t="s">
-        <v>653</v>
-      </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
@@ -2503,9 +2482,6 @@
       <c r="F8" t="s">
         <v>633</v>
       </c>
-      <c r="G8" t="s">
-        <v>653</v>
-      </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
@@ -2526,9 +2502,6 @@
       <c r="F9" t="s">
         <v>633</v>
       </c>
-      <c r="G9" t="s">
-        <v>653</v>
-      </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
@@ -2549,9 +2522,6 @@
       <c r="F10" t="s">
         <v>633</v>
       </c>
-      <c r="G10" t="s">
-        <v>653</v>
-      </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
@@ -2572,9 +2542,6 @@
       <c r="F11" t="s">
         <v>633</v>
       </c>
-      <c r="G11" t="s">
-        <v>653</v>
-      </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
@@ -2595,9 +2562,6 @@
       <c r="F12" t="s">
         <v>633</v>
       </c>
-      <c r="G12" t="s">
-        <v>653</v>
-      </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
@@ -2618,9 +2582,6 @@
       <c r="F13" t="s">
         <v>633</v>
       </c>
-      <c r="G13" t="s">
-        <v>653</v>
-      </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
@@ -2641,9 +2602,6 @@
       <c r="F14" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="G14" t="s">
-        <v>653</v>
-      </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
@@ -2664,9 +2622,6 @@
       <c r="F15" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="G15" t="s">
-        <v>653</v>
-      </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
@@ -2681,11 +2636,8 @@
       <c r="D16" t="s">
         <v>552</v>
       </c>
-      <c r="G16" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -2698,11 +2650,8 @@
       <c r="D17" t="s">
         <v>552</v>
       </c>
-      <c r="G17" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -2715,11 +2664,8 @@
       <c r="D18" t="s">
         <v>552</v>
       </c>
-      <c r="G18" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -2732,11 +2678,8 @@
       <c r="D19" t="s">
         <v>552</v>
       </c>
-      <c r="G19" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -2749,11 +2692,8 @@
       <c r="D20" t="s">
         <v>552</v>
       </c>
-      <c r="G20" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -2766,11 +2706,8 @@
       <c r="D21" t="s">
         <v>552</v>
       </c>
-      <c r="G21" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -2783,11 +2720,8 @@
       <c r="D22" t="s">
         <v>552</v>
       </c>
-      <c r="G22" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -2800,11 +2734,8 @@
       <c r="D23" t="s">
         <v>552</v>
       </c>
-      <c r="G23" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -2817,11 +2748,8 @@
       <c r="D24" t="s">
         <v>552</v>
       </c>
-      <c r="G24" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -2834,11 +2762,8 @@
       <c r="D25" t="s">
         <v>552</v>
       </c>
-      <c r="G25" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -2851,11 +2776,8 @@
       <c r="D26" t="s">
         <v>552</v>
       </c>
-      <c r="G26" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -2868,11 +2790,8 @@
       <c r="D27" t="s">
         <v>552</v>
       </c>
-      <c r="G27" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -2885,11 +2804,8 @@
       <c r="D28" t="s">
         <v>552</v>
       </c>
-      <c r="G28" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -2902,11 +2818,8 @@
       <c r="D29" t="s">
         <v>552</v>
       </c>
-      <c r="G29" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -2919,11 +2832,8 @@
       <c r="D30" t="s">
         <v>552</v>
       </c>
-      <c r="G30" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -2936,11 +2846,8 @@
       <c r="D31" t="s">
         <v>552</v>
       </c>
-      <c r="G31" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -2953,11 +2860,8 @@
       <c r="D32" t="s">
         <v>552</v>
       </c>
-      <c r="G32" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -2970,11 +2874,8 @@
       <c r="D33" t="s">
         <v>552</v>
       </c>
-      <c r="G33" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -2987,11 +2888,8 @@
       <c r="D34" t="s">
         <v>552</v>
       </c>
-      <c r="G34" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -3004,11 +2902,8 @@
       <c r="D35" t="s">
         <v>552</v>
       </c>
-      <c r="G35" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -3021,11 +2916,8 @@
       <c r="D36" t="s">
         <v>552</v>
       </c>
-      <c r="G36" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -3038,11 +2930,8 @@
       <c r="D37" t="s">
         <v>552</v>
       </c>
-      <c r="G37" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -3055,11 +2944,8 @@
       <c r="D38" t="s">
         <v>552</v>
       </c>
-      <c r="G38" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -3072,11 +2958,8 @@
       <c r="D39" t="s">
         <v>552</v>
       </c>
-      <c r="G39" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -3089,11 +2972,8 @@
       <c r="D40" t="s">
         <v>552</v>
       </c>
-      <c r="G40" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -3106,11 +2986,8 @@
       <c r="D41" t="s">
         <v>552</v>
       </c>
-      <c r="G41" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -3123,11 +3000,8 @@
       <c r="D42" t="s">
         <v>552</v>
       </c>
-      <c r="G42" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+    </row>
+    <row r="43" spans="1:4">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -3140,11 +3014,8 @@
       <c r="D43" t="s">
         <v>552</v>
       </c>
-      <c r="G43" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+    </row>
+    <row r="44" spans="1:4">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -3157,11 +3028,8 @@
       <c r="D44" t="s">
         <v>552</v>
       </c>
-      <c r="G44" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+    </row>
+    <row r="45" spans="1:4">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -3174,11 +3042,8 @@
       <c r="D45" t="s">
         <v>552</v>
       </c>
-      <c r="G45" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+    </row>
+    <row r="46" spans="1:4">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -3191,11 +3056,8 @@
       <c r="D46" t="s">
         <v>552</v>
       </c>
-      <c r="G46" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+    </row>
+    <row r="47" spans="1:4">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -3208,11 +3070,8 @@
       <c r="D47" t="s">
         <v>552</v>
       </c>
-      <c r="G47" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+    </row>
+    <row r="48" spans="1:4">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -3225,11 +3084,8 @@
       <c r="D48" t="s">
         <v>552</v>
       </c>
-      <c r="G48" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+    </row>
+    <row r="49" spans="1:4">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -3242,11 +3098,8 @@
       <c r="D49" t="s">
         <v>552</v>
       </c>
-      <c r="G49" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+    </row>
+    <row r="50" spans="1:4">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -3259,11 +3112,8 @@
       <c r="D50" t="s">
         <v>552</v>
       </c>
-      <c r="G50" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+    </row>
+    <row r="51" spans="1:4">
       <c r="A51" t="s">
         <v>56</v>
       </c>
@@ -3276,11 +3126,8 @@
       <c r="D51" t="s">
         <v>552</v>
       </c>
-      <c r="G51" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52" t="s">
         <v>57</v>
       </c>
@@ -3293,11 +3140,8 @@
       <c r="D52" t="s">
         <v>552</v>
       </c>
-      <c r="G52" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+    </row>
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
         <v>58</v>
       </c>
@@ -3310,11 +3154,8 @@
       <c r="D53" t="s">
         <v>552</v>
       </c>
-      <c r="G53" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
         <v>59</v>
       </c>
@@ -3327,11 +3168,8 @@
       <c r="D54" t="s">
         <v>552</v>
       </c>
-      <c r="G54" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+    </row>
+    <row r="55" spans="1:4">
       <c r="A55" t="s">
         <v>60</v>
       </c>
@@ -3344,11 +3182,8 @@
       <c r="D55" t="s">
         <v>552</v>
       </c>
-      <c r="G55" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+    </row>
+    <row r="56" spans="1:4">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -3361,11 +3196,8 @@
       <c r="D56" t="s">
         <v>552</v>
       </c>
-      <c r="G56" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+    </row>
+    <row r="57" spans="1:4">
       <c r="A57" t="s">
         <v>62</v>
       </c>
@@ -3378,11 +3210,8 @@
       <c r="D57" t="s">
         <v>552</v>
       </c>
-      <c r="G57" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+    </row>
+    <row r="58" spans="1:4">
       <c r="A58" t="s">
         <v>63</v>
       </c>
@@ -3395,11 +3224,8 @@
       <c r="D58" t="s">
         <v>552</v>
       </c>
-      <c r="G58" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+    </row>
+    <row r="59" spans="1:4">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -3412,11 +3238,8 @@
       <c r="D59" t="s">
         <v>552</v>
       </c>
-      <c r="G59" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+    </row>
+    <row r="60" spans="1:4">
       <c r="A60" t="s">
         <v>65</v>
       </c>
@@ -3429,11 +3252,8 @@
       <c r="D60" t="s">
         <v>552</v>
       </c>
-      <c r="G60" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+    </row>
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
         <v>66</v>
       </c>
@@ -3446,11 +3266,8 @@
       <c r="D61" t="s">
         <v>552</v>
       </c>
-      <c r="G61" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+    </row>
+    <row r="62" spans="1:4">
       <c r="A62" t="s">
         <v>67</v>
       </c>
@@ -3463,11 +3280,8 @@
       <c r="D62" t="s">
         <v>552</v>
       </c>
-      <c r="G62" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+    </row>
+    <row r="63" spans="1:4">
       <c r="A63" t="s">
         <v>68</v>
       </c>
@@ -3480,11 +3294,8 @@
       <c r="D63" t="s">
         <v>552</v>
       </c>
-      <c r="G63" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+    </row>
+    <row r="64" spans="1:4">
       <c r="A64" t="s">
         <v>69</v>
       </c>
@@ -3497,11 +3308,8 @@
       <c r="D64" t="s">
         <v>552</v>
       </c>
-      <c r="G64" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+    </row>
+    <row r="65" spans="1:4">
       <c r="A65" t="s">
         <v>70</v>
       </c>
@@ -3514,11 +3322,8 @@
       <c r="D65" t="s">
         <v>552</v>
       </c>
-      <c r="G65" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
+    </row>
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
         <v>71</v>
       </c>
@@ -3531,11 +3336,8 @@
       <c r="D66" t="s">
         <v>552</v>
       </c>
-      <c r="G66" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
+    </row>
+    <row r="67" spans="1:4">
       <c r="A67" t="s">
         <v>72</v>
       </c>
@@ -3548,11 +3350,8 @@
       <c r="D67" t="s">
         <v>552</v>
       </c>
-      <c r="G67" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
+    </row>
+    <row r="68" spans="1:4">
       <c r="A68" t="s">
         <v>73</v>
       </c>
@@ -3565,11 +3364,8 @@
       <c r="D68" t="s">
         <v>552</v>
       </c>
-      <c r="G68" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
+    </row>
+    <row r="69" spans="1:4">
       <c r="A69" t="s">
         <v>74</v>
       </c>
@@ -3582,11 +3378,8 @@
       <c r="D69" t="s">
         <v>552</v>
       </c>
-      <c r="G69" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
+    </row>
+    <row r="70" spans="1:4">
       <c r="A70" t="s">
         <v>75</v>
       </c>
@@ -3599,11 +3392,8 @@
       <c r="D70" t="s">
         <v>552</v>
       </c>
-      <c r="G70" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
+    </row>
+    <row r="71" spans="1:4">
       <c r="A71" t="s">
         <v>76</v>
       </c>
@@ -3616,11 +3406,8 @@
       <c r="D71" t="s">
         <v>552</v>
       </c>
-      <c r="G71" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
+    </row>
+    <row r="72" spans="1:4">
       <c r="A72" t="s">
         <v>77</v>
       </c>
@@ -3633,11 +3420,8 @@
       <c r="D72" t="s">
         <v>552</v>
       </c>
-      <c r="G72" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73" t="s">
         <v>78</v>
       </c>
@@ -3650,11 +3434,8 @@
       <c r="D73" t="s">
         <v>552</v>
       </c>
-      <c r="G73" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
+    </row>
+    <row r="74" spans="1:4">
       <c r="A74" t="s">
         <v>79</v>
       </c>
@@ -3667,11 +3448,8 @@
       <c r="D74" t="s">
         <v>552</v>
       </c>
-      <c r="G74" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
+    </row>
+    <row r="75" spans="1:4">
       <c r="A75" t="s">
         <v>80</v>
       </c>
@@ -3684,11 +3462,8 @@
       <c r="D75" t="s">
         <v>552</v>
       </c>
-      <c r="G75" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
+    </row>
+    <row r="76" spans="1:4">
       <c r="A76" t="s">
         <v>81</v>
       </c>
@@ -3701,11 +3476,8 @@
       <c r="D76" t="s">
         <v>552</v>
       </c>
-      <c r="G76" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
+    </row>
+    <row r="77" spans="1:4">
       <c r="A77" t="s">
         <v>82</v>
       </c>
@@ -3718,11 +3490,8 @@
       <c r="D77" t="s">
         <v>552</v>
       </c>
-      <c r="G77" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
+    </row>
+    <row r="78" spans="1:4">
       <c r="A78" t="s">
         <v>83</v>
       </c>
@@ -3735,11 +3504,8 @@
       <c r="D78" t="s">
         <v>552</v>
       </c>
-      <c r="G78" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
+    </row>
+    <row r="79" spans="1:4">
       <c r="A79" t="s">
         <v>84</v>
       </c>
@@ -3752,11 +3518,8 @@
       <c r="D79" t="s">
         <v>552</v>
       </c>
-      <c r="G79" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
+    </row>
+    <row r="80" spans="1:4">
       <c r="A80" t="s">
         <v>85</v>
       </c>
@@ -3769,11 +3532,8 @@
       <c r="D80" t="s">
         <v>552</v>
       </c>
-      <c r="G80" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
+    </row>
+    <row r="81" spans="1:4">
       <c r="A81" t="s">
         <v>86</v>
       </c>
@@ -3786,11 +3546,8 @@
       <c r="D81" t="s">
         <v>552</v>
       </c>
-      <c r="G81" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
+    </row>
+    <row r="82" spans="1:4">
       <c r="A82" t="s">
         <v>87</v>
       </c>
@@ -3803,11 +3560,8 @@
       <c r="D82" t="s">
         <v>552</v>
       </c>
-      <c r="G82" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
+    </row>
+    <row r="83" spans="1:4">
       <c r="A83" t="s">
         <v>88</v>
       </c>
@@ -3820,11 +3574,8 @@
       <c r="D83" t="s">
         <v>552</v>
       </c>
-      <c r="G83" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
+    </row>
+    <row r="84" spans="1:4">
       <c r="A84" t="s">
         <v>89</v>
       </c>
@@ -3837,11 +3588,8 @@
       <c r="D84" t="s">
         <v>552</v>
       </c>
-      <c r="G84" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
+    </row>
+    <row r="85" spans="1:4">
       <c r="A85" t="s">
         <v>90</v>
       </c>
@@ -3854,11 +3602,8 @@
       <c r="D85" t="s">
         <v>552</v>
       </c>
-      <c r="G85" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7">
+    </row>
+    <row r="86" spans="1:4">
       <c r="A86" t="s">
         <v>91</v>
       </c>
@@ -3871,11 +3616,8 @@
       <c r="D86" t="s">
         <v>552</v>
       </c>
-      <c r="G86" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7">
+    </row>
+    <row r="87" spans="1:4">
       <c r="A87" t="s">
         <v>92</v>
       </c>
@@ -3888,11 +3630,8 @@
       <c r="D87" t="s">
         <v>552</v>
       </c>
-      <c r="G87" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7">
+    </row>
+    <row r="88" spans="1:4">
       <c r="A88" t="s">
         <v>93</v>
       </c>
@@ -3905,11 +3644,8 @@
       <c r="D88" t="s">
         <v>552</v>
       </c>
-      <c r="G88" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7">
+    </row>
+    <row r="89" spans="1:4">
       <c r="A89" t="s">
         <v>94</v>
       </c>
@@ -3922,11 +3658,8 @@
       <c r="D89" t="s">
         <v>552</v>
       </c>
-      <c r="G89" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7">
+    </row>
+    <row r="90" spans="1:4">
       <c r="A90" t="s">
         <v>95</v>
       </c>
@@ -3939,11 +3672,8 @@
       <c r="D90" t="s">
         <v>552</v>
       </c>
-      <c r="G90" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7">
+    </row>
+    <row r="91" spans="1:4">
       <c r="A91" t="s">
         <v>96</v>
       </c>
@@ -3956,11 +3686,8 @@
       <c r="D91" t="s">
         <v>552</v>
       </c>
-      <c r="G91" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
+    </row>
+    <row r="92" spans="1:4">
       <c r="A92" t="s">
         <v>97</v>
       </c>
@@ -3973,11 +3700,8 @@
       <c r="D92" t="s">
         <v>552</v>
       </c>
-      <c r="G92" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
+    </row>
+    <row r="93" spans="1:4">
       <c r="A93" t="s">
         <v>98</v>
       </c>
@@ -3990,11 +3714,8 @@
       <c r="D93" t="s">
         <v>552</v>
       </c>
-      <c r="G93" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
+    </row>
+    <row r="94" spans="1:4">
       <c r="A94" t="s">
         <v>99</v>
       </c>
@@ -4007,11 +3728,8 @@
       <c r="D94" t="s">
         <v>552</v>
       </c>
-      <c r="G94" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
+    </row>
+    <row r="95" spans="1:4">
       <c r="A95" t="s">
         <v>100</v>
       </c>
@@ -4024,11 +3742,8 @@
       <c r="D95" t="s">
         <v>552</v>
       </c>
-      <c r="G95" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
+    </row>
+    <row r="96" spans="1:4">
       <c r="A96" t="s">
         <v>101</v>
       </c>
@@ -4041,11 +3756,8 @@
       <c r="D96" t="s">
         <v>552</v>
       </c>
-      <c r="G96" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
+    </row>
+    <row r="97" spans="1:4">
       <c r="A97" t="s">
         <v>102</v>
       </c>
@@ -4058,11 +3770,8 @@
       <c r="D97" t="s">
         <v>552</v>
       </c>
-      <c r="G97" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
+    </row>
+    <row r="98" spans="1:4">
       <c r="A98" t="s">
         <v>103</v>
       </c>
@@ -4075,11 +3784,8 @@
       <c r="D98" t="s">
         <v>552</v>
       </c>
-      <c r="G98" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
+    </row>
+    <row r="99" spans="1:4">
       <c r="A99" t="s">
         <v>104</v>
       </c>
@@ -4092,11 +3798,8 @@
       <c r="D99" t="s">
         <v>552</v>
       </c>
-      <c r="G99" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
+    </row>
+    <row r="100" spans="1:4">
       <c r="A100" t="s">
         <v>105</v>
       </c>
@@ -4109,11 +3812,8 @@
       <c r="D100" t="s">
         <v>552</v>
       </c>
-      <c r="G100" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7">
+    </row>
+    <row r="101" spans="1:4">
       <c r="A101" t="s">
         <v>106</v>
       </c>
@@ -4126,11 +3826,8 @@
       <c r="D101" t="s">
         <v>552</v>
       </c>
-      <c r="G101" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7">
+    </row>
+    <row r="102" spans="1:4">
       <c r="A102" t="s">
         <v>107</v>
       </c>
@@ -4143,11 +3840,8 @@
       <c r="D102" t="s">
         <v>552</v>
       </c>
-      <c r="G102" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
+    </row>
+    <row r="103" spans="1:4">
       <c r="A103" t="s">
         <v>108</v>
       </c>
@@ -4160,11 +3854,8 @@
       <c r="D103" t="s">
         <v>552</v>
       </c>
-      <c r="G103" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7">
+    </row>
+    <row r="104" spans="1:4">
       <c r="A104" t="s">
         <v>109</v>
       </c>
@@ -4177,11 +3868,8 @@
       <c r="D104" t="s">
         <v>552</v>
       </c>
-      <c r="G104" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7">
+    </row>
+    <row r="105" spans="1:4">
       <c r="A105" t="s">
         <v>110</v>
       </c>
@@ -4194,11 +3882,8 @@
       <c r="D105" t="s">
         <v>552</v>
       </c>
-      <c r="G105" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7">
+    </row>
+    <row r="106" spans="1:4">
       <c r="A106" t="s">
         <v>111</v>
       </c>
@@ -4211,11 +3896,8 @@
       <c r="D106" t="s">
         <v>552</v>
       </c>
-      <c r="G106" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7">
+    </row>
+    <row r="107" spans="1:4">
       <c r="A107" t="s">
         <v>112</v>
       </c>
@@ -4228,11 +3910,8 @@
       <c r="D107" t="s">
         <v>552</v>
       </c>
-      <c r="G107" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7">
+    </row>
+    <row r="108" spans="1:4">
       <c r="A108" t="s">
         <v>113</v>
       </c>
@@ -4245,11 +3924,8 @@
       <c r="D108" t="s">
         <v>552</v>
       </c>
-      <c r="G108" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7">
+    </row>
+    <row r="109" spans="1:4">
       <c r="A109" t="s">
         <v>114</v>
       </c>
@@ -4262,11 +3938,8 @@
       <c r="D109" t="s">
         <v>552</v>
       </c>
-      <c r="G109" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7">
+    </row>
+    <row r="110" spans="1:4">
       <c r="A110" t="s">
         <v>115</v>
       </c>
@@ -4279,11 +3952,8 @@
       <c r="D110" t="s">
         <v>552</v>
       </c>
-      <c r="G110" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7">
+    </row>
+    <row r="111" spans="1:4">
       <c r="A111" t="s">
         <v>116</v>
       </c>
@@ -4296,11 +3966,8 @@
       <c r="D111" t="s">
         <v>552</v>
       </c>
-      <c r="G111" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7">
+    </row>
+    <row r="112" spans="1:4">
       <c r="A112" t="s">
         <v>117</v>
       </c>
@@ -4313,11 +3980,8 @@
       <c r="D112" t="s">
         <v>552</v>
       </c>
-      <c r="G112" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>118</v>
       </c>
@@ -4330,11 +3994,8 @@
       <c r="D113" t="s">
         <v>552</v>
       </c>
-      <c r="G113" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>119</v>
       </c>
@@ -4347,11 +4008,8 @@
       <c r="D114" t="s">
         <v>552</v>
       </c>
-      <c r="G114" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>120</v>
       </c>
@@ -4364,11 +4022,8 @@
       <c r="D115" t="s">
         <v>552</v>
       </c>
-      <c r="G115" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
         <v>121</v>
       </c>
@@ -4381,11 +4036,8 @@
       <c r="D116" t="s">
         <v>552</v>
       </c>
-      <c r="G116" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>122</v>
       </c>
@@ -4398,11 +4050,8 @@
       <c r="D117" t="s">
         <v>552</v>
       </c>
-      <c r="G117" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>123</v>
       </c>
@@ -4415,11 +4064,8 @@
       <c r="D118" t="s">
         <v>552</v>
       </c>
-      <c r="G118" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>124</v>
       </c>
@@ -4438,11 +4084,8 @@
       <c r="F119" t="s">
         <v>636</v>
       </c>
-      <c r="G119" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7">
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>125</v>
       </c>
@@ -4458,11 +4101,8 @@
       <c r="E120" t="s">
         <v>583</v>
       </c>
-      <c r="G120" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7">
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
         <v>126</v>
       </c>
@@ -4475,11 +4115,8 @@
       <c r="D121" t="s">
         <v>552</v>
       </c>
-      <c r="G121" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7">
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
         <v>127</v>
       </c>
@@ -4492,11 +4129,8 @@
       <c r="D122" t="s">
         <v>555</v>
       </c>
-      <c r="G122" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7">
+    </row>
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
         <v>128</v>
       </c>
@@ -4515,11 +4149,8 @@
       <c r="F123" t="s">
         <v>637</v>
       </c>
-      <c r="G123" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7">
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>129</v>
       </c>
@@ -4532,11 +4163,8 @@
       <c r="D124" t="s">
         <v>552</v>
       </c>
-      <c r="G124" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7">
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>130</v>
       </c>
@@ -4549,11 +4177,8 @@
       <c r="D125" t="s">
         <v>552</v>
       </c>
-      <c r="G125" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>131</v>
       </c>
@@ -4566,11 +4191,8 @@
       <c r="D126" t="s">
         <v>552</v>
       </c>
-      <c r="G126" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>132</v>
       </c>
@@ -4583,11 +4205,8 @@
       <c r="D127" t="s">
         <v>552</v>
       </c>
-      <c r="G127" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7">
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>133</v>
       </c>
@@ -4603,11 +4222,8 @@
       <c r="E128" t="s">
         <v>585</v>
       </c>
-      <c r="G128" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7">
+    </row>
+    <row r="129" spans="1:6">
       <c r="A129" t="s">
         <v>134</v>
       </c>
@@ -4626,11 +4242,8 @@
       <c r="F129" t="s">
         <v>638</v>
       </c>
-      <c r="G129" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7">
+    </row>
+    <row r="130" spans="1:6">
       <c r="A130" t="s">
         <v>135</v>
       </c>
@@ -4643,11 +4256,8 @@
       <c r="D130" t="s">
         <v>552</v>
       </c>
-      <c r="G130" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7">
+    </row>
+    <row r="131" spans="1:6">
       <c r="A131" t="s">
         <v>136</v>
       </c>
@@ -4661,7 +4271,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:6">
       <c r="A132" t="s">
         <v>137</v>
       </c>
@@ -4677,11 +4287,8 @@
       <c r="E132" t="s">
         <v>588</v>
       </c>
-      <c r="G132" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7">
+    </row>
+    <row r="133" spans="1:6">
       <c r="A133" t="s">
         <v>138</v>
       </c>
@@ -4697,11 +4304,8 @@
       <c r="E133" t="s">
         <v>589</v>
       </c>
-      <c r="G133" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7">
+    </row>
+    <row r="134" spans="1:6">
       <c r="A134" t="s">
         <v>139</v>
       </c>
@@ -4712,7 +4316,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:6">
       <c r="A135" t="s">
         <v>140</v>
       </c>
@@ -4723,7 +4327,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:6">
       <c r="A136" t="s">
         <v>141</v>
       </c>
@@ -4736,11 +4340,8 @@
       <c r="D136" t="s">
         <v>552</v>
       </c>
-      <c r="G136" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7">
+    </row>
+    <row r="137" spans="1:6">
       <c r="A137" t="s">
         <v>142</v>
       </c>
@@ -4753,11 +4354,8 @@
       <c r="D137" t="s">
         <v>558</v>
       </c>
-      <c r="G137" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7">
+    </row>
+    <row r="138" spans="1:6">
       <c r="A138" t="s">
         <v>143</v>
       </c>
@@ -4768,7 +4366,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:6">
       <c r="A139" t="s">
         <v>144</v>
       </c>
@@ -4779,7 +4377,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:6">
       <c r="A140" t="s">
         <v>145</v>
       </c>
@@ -4790,7 +4388,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:6">
       <c r="A141" t="s">
         <v>146</v>
       </c>
@@ -4803,11 +4401,8 @@
       <c r="D141" t="s">
         <v>552</v>
       </c>
-      <c r="G141" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7">
+    </row>
+    <row r="142" spans="1:6">
       <c r="A142" t="s">
         <v>147</v>
       </c>
@@ -4826,11 +4421,8 @@
       <c r="F142" t="s">
         <v>639</v>
       </c>
-      <c r="G142" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7">
+    </row>
+    <row r="143" spans="1:6">
       <c r="A143" t="s">
         <v>148</v>
       </c>
@@ -4843,11 +4435,8 @@
       <c r="D143" t="s">
         <v>562</v>
       </c>
-      <c r="G143" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7">
+    </row>
+    <row r="144" spans="1:6">
       <c r="A144" t="s">
         <v>149</v>
       </c>
@@ -4861,7 +4450,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:6">
       <c r="A145" t="s">
         <v>150</v>
       </c>
@@ -4872,7 +4461,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:6">
       <c r="A146" t="s">
         <v>151</v>
       </c>
@@ -4888,11 +4477,8 @@
       <c r="F146" t="s">
         <v>640</v>
       </c>
-      <c r="G146" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7">
+    </row>
+    <row r="147" spans="1:6">
       <c r="A147" t="s">
         <v>152</v>
       </c>
@@ -4911,11 +4497,8 @@
       <c r="F147" t="s">
         <v>641</v>
       </c>
-      <c r="G147" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7">
+    </row>
+    <row r="148" spans="1:6">
       <c r="A148" t="s">
         <v>153</v>
       </c>
@@ -4931,11 +4514,8 @@
       <c r="E148" t="s">
         <v>593</v>
       </c>
-      <c r="G148" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7">
+    </row>
+    <row r="149" spans="1:6">
       <c r="A149" t="s">
         <v>154</v>
       </c>
@@ -4951,11 +4531,8 @@
       <c r="E149" t="s">
         <v>594</v>
       </c>
-      <c r="G149" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7">
+    </row>
+    <row r="150" spans="1:6">
       <c r="A150" t="s">
         <v>155</v>
       </c>
@@ -4971,11 +4548,8 @@
       <c r="E150" t="s">
         <v>595</v>
       </c>
-      <c r="G150" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7">
+    </row>
+    <row r="151" spans="1:6">
       <c r="A151" t="s">
         <v>156</v>
       </c>
@@ -4991,11 +4565,8 @@
       <c r="E151" t="s">
         <v>596</v>
       </c>
-      <c r="G151" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7">
+    </row>
+    <row r="152" spans="1:6">
       <c r="A152" t="s">
         <v>157</v>
       </c>
@@ -5011,11 +4582,8 @@
       <c r="E152" t="s">
         <v>597</v>
       </c>
-      <c r="G152" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7">
+    </row>
+    <row r="153" spans="1:6">
       <c r="A153" t="s">
         <v>158</v>
       </c>
@@ -5026,7 +4594,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" spans="1:6">
       <c r="A154" t="s">
         <v>159</v>
       </c>
@@ -5042,11 +4610,8 @@
       <c r="E154" t="s">
         <v>598</v>
       </c>
-      <c r="G154" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7">
+    </row>
+    <row r="155" spans="1:6">
       <c r="A155" t="s">
         <v>160</v>
       </c>
@@ -5059,11 +4624,8 @@
       <c r="D155" t="s">
         <v>552</v>
       </c>
-      <c r="G155" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7">
+    </row>
+    <row r="156" spans="1:6">
       <c r="A156" t="s">
         <v>161</v>
       </c>
@@ -5076,11 +4638,8 @@
       <c r="D156" t="s">
         <v>552</v>
       </c>
-      <c r="G156" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7">
+    </row>
+    <row r="157" spans="1:6">
       <c r="A157" t="s">
         <v>162</v>
       </c>
@@ -5099,11 +4658,8 @@
       <c r="F157" t="s">
         <v>642</v>
       </c>
-      <c r="G157" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7">
+    </row>
+    <row r="158" spans="1:6">
       <c r="A158" t="s">
         <v>163</v>
       </c>
@@ -5119,11 +4675,8 @@
       <c r="E158" t="s">
         <v>600</v>
       </c>
-      <c r="G158" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7">
+    </row>
+    <row r="159" spans="1:6">
       <c r="A159" t="s">
         <v>164</v>
       </c>
@@ -5139,11 +4692,8 @@
       <c r="E159" t="s">
         <v>601</v>
       </c>
-      <c r="G159" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7">
+    </row>
+    <row r="160" spans="1:6">
       <c r="A160" t="s">
         <v>165</v>
       </c>
@@ -5159,11 +4709,8 @@
       <c r="E160" t="s">
         <v>602</v>
       </c>
-      <c r="G160" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7">
+    </row>
+    <row r="161" spans="1:6">
       <c r="A161" t="s">
         <v>166</v>
       </c>
@@ -5179,11 +4726,8 @@
       <c r="E161" t="s">
         <v>603</v>
       </c>
-      <c r="G161" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7">
+    </row>
+    <row r="162" spans="1:6">
       <c r="A162" t="s">
         <v>167</v>
       </c>
@@ -5196,11 +4740,8 @@
       <c r="D162" t="s">
         <v>552</v>
       </c>
-      <c r="G162" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7">
+    </row>
+    <row r="163" spans="1:6">
       <c r="A163" t="s">
         <v>168</v>
       </c>
@@ -5216,11 +4757,8 @@
       <c r="E163" t="s">
         <v>604</v>
       </c>
-      <c r="G163" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7">
+    </row>
+    <row r="164" spans="1:6">
       <c r="A164" t="s">
         <v>169</v>
       </c>
@@ -5236,11 +4774,8 @@
       <c r="E164" t="s">
         <v>605</v>
       </c>
-      <c r="G164" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7">
+    </row>
+    <row r="165" spans="1:6">
       <c r="A165" t="s">
         <v>170</v>
       </c>
@@ -5254,7 +4789,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" spans="1:6">
       <c r="A166" t="s">
         <v>171</v>
       </c>
@@ -5270,11 +4805,8 @@
       <c r="E166" t="s">
         <v>607</v>
       </c>
-      <c r="G166" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7">
+    </row>
+    <row r="167" spans="1:6">
       <c r="A167" t="s">
         <v>172</v>
       </c>
@@ -5290,11 +4822,8 @@
       <c r="E167" t="s">
         <v>608</v>
       </c>
-      <c r="G167" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7">
+    </row>
+    <row r="168" spans="1:6">
       <c r="A168" t="s">
         <v>173</v>
       </c>
@@ -5310,11 +4839,8 @@
       <c r="E168" t="s">
         <v>609</v>
       </c>
-      <c r="G168" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7">
+    </row>
+    <row r="169" spans="1:6">
       <c r="A169" t="s">
         <v>174</v>
       </c>
@@ -5330,11 +4856,8 @@
       <c r="E169" t="s">
         <v>610</v>
       </c>
-      <c r="G169" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7">
+    </row>
+    <row r="170" spans="1:6">
       <c r="A170" t="s">
         <v>175</v>
       </c>
@@ -5348,7 +4871,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="171" spans="1:7">
+    <row r="171" spans="1:6">
       <c r="A171" t="s">
         <v>176</v>
       </c>
@@ -5362,7 +4885,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="172" spans="1:7">
+    <row r="172" spans="1:6">
       <c r="A172" t="s">
         <v>177</v>
       </c>
@@ -5376,7 +4899,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="173" spans="1:7">
+    <row r="173" spans="1:6">
       <c r="A173" t="s">
         <v>178</v>
       </c>
@@ -5389,11 +4912,8 @@
       <c r="D173" t="s">
         <v>552</v>
       </c>
-      <c r="G173" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7">
+    </row>
+    <row r="174" spans="1:6">
       <c r="A174" t="s">
         <v>179</v>
       </c>
@@ -5409,11 +4929,8 @@
       <c r="F174" t="s">
         <v>643</v>
       </c>
-      <c r="G174" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7">
+    </row>
+    <row r="175" spans="1:6">
       <c r="A175" t="s">
         <v>180</v>
       </c>
@@ -5429,11 +4946,8 @@
       <c r="F175" t="s">
         <v>644</v>
       </c>
-      <c r="G175" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7">
+    </row>
+    <row r="176" spans="1:6">
       <c r="A176" t="s">
         <v>181</v>
       </c>
@@ -5444,7 +4958,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" spans="1:6">
       <c r="A177" t="s">
         <v>182</v>
       </c>
@@ -5455,7 +4969,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" spans="1:6">
       <c r="A178" t="s">
         <v>183</v>
       </c>
@@ -5466,7 +4980,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" spans="1:6">
       <c r="A179" t="s">
         <v>184</v>
       </c>
@@ -5485,11 +4999,8 @@
       <c r="F179" t="s">
         <v>645</v>
       </c>
-      <c r="G179" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7">
+    </row>
+    <row r="180" spans="1:6">
       <c r="A180" t="s">
         <v>185</v>
       </c>
@@ -5500,7 +5011,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" spans="1:6">
       <c r="A181" t="s">
         <v>186</v>
       </c>
@@ -5511,7 +5022,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" spans="1:6">
       <c r="A182" t="s">
         <v>187</v>
       </c>
@@ -5527,11 +5038,8 @@
       <c r="E182" t="s">
         <v>615</v>
       </c>
-      <c r="G182" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7">
+    </row>
+    <row r="183" spans="1:6">
       <c r="A183" t="s">
         <v>188</v>
       </c>
@@ -5547,11 +5055,8 @@
       <c r="F183" t="s">
         <v>646</v>
       </c>
-      <c r="G183" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7">
+    </row>
+    <row r="184" spans="1:6">
       <c r="A184" t="s">
         <v>189</v>
       </c>
@@ -5562,7 +5067,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="185" spans="1:7">
+    <row r="185" spans="1:6">
       <c r="A185" t="s">
         <v>190</v>
       </c>
@@ -5576,7 +5081,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" spans="1:6">
       <c r="A186" t="s">
         <v>191</v>
       </c>
@@ -5590,7 +5095,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="187" spans="1:7">
+    <row r="187" spans="1:6">
       <c r="A187" t="s">
         <v>192</v>
       </c>
@@ -5604,7 +5109,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" spans="1:6">
       <c r="A188" t="s">
         <v>193</v>
       </c>
@@ -5618,7 +5123,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="189" spans="1:7">
+    <row r="189" spans="1:6">
       <c r="A189" t="s">
         <v>194</v>
       </c>
@@ -5632,7 +5137,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="190" spans="1:7">
+    <row r="190" spans="1:6">
       <c r="A190" t="s">
         <v>195</v>
       </c>
@@ -5646,7 +5151,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="191" spans="1:7">
+    <row r="191" spans="1:6">
       <c r="A191" t="s">
         <v>196</v>
       </c>
@@ -5657,7 +5162,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="192" spans="1:7">
+    <row r="192" spans="1:6">
       <c r="A192" t="s">
         <v>197</v>
       </c>
@@ -5668,7 +5173,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="193" spans="1:7">
+    <row r="193" spans="1:6">
       <c r="A193" t="s">
         <v>198</v>
       </c>
@@ -5679,7 +5184,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="194" spans="1:7">
+    <row r="194" spans="1:6">
       <c r="A194" t="s">
         <v>199</v>
       </c>
@@ -5692,11 +5197,8 @@
       <c r="D194" t="s">
         <v>555</v>
       </c>
-      <c r="G194" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7">
+    </row>
+    <row r="195" spans="1:6">
       <c r="A195" t="s">
         <v>200</v>
       </c>
@@ -5709,11 +5211,8 @@
       <c r="D195" t="s">
         <v>555</v>
       </c>
-      <c r="G195" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7">
+    </row>
+    <row r="196" spans="1:6">
       <c r="A196" t="s">
         <v>201</v>
       </c>
@@ -5729,11 +5228,8 @@
       <c r="F196" t="s">
         <v>648</v>
       </c>
-      <c r="G196" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7">
+    </row>
+    <row r="197" spans="1:6">
       <c r="A197" t="s">
         <v>202</v>
       </c>
@@ -5752,11 +5248,8 @@
       <c r="F197" t="s">
         <v>649</v>
       </c>
-      <c r="G197" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7">
+    </row>
+    <row r="198" spans="1:6">
       <c r="A198" t="s">
         <v>203</v>
       </c>
@@ -5775,11 +5268,8 @@
       <c r="F198" t="s">
         <v>650</v>
       </c>
-      <c r="G198" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7">
+    </row>
+    <row r="199" spans="1:6">
       <c r="A199" t="s">
         <v>204</v>
       </c>
@@ -5798,11 +5288,8 @@
       <c r="F199" t="s">
         <v>651</v>
       </c>
-      <c r="G199" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7">
+    </row>
+    <row r="200" spans="1:6">
       <c r="A200" t="s">
         <v>205</v>
       </c>
@@ -5815,11 +5302,8 @@
       <c r="D200" t="s">
         <v>552</v>
       </c>
-      <c r="G200" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7">
+    </row>
+    <row r="201" spans="1:6">
       <c r="A201" t="s">
         <v>206</v>
       </c>
@@ -5830,7 +5314,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="202" spans="1:7">
+    <row r="202" spans="1:6">
       <c r="A202" t="s">
         <v>207</v>
       </c>
@@ -5841,7 +5325,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="203" spans="1:7">
+    <row r="203" spans="1:6">
       <c r="A203" t="s">
         <v>208</v>
       </c>
@@ -5852,7 +5336,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="204" spans="1:7">
+    <row r="204" spans="1:6">
       <c r="A204" t="s">
         <v>209</v>
       </c>
@@ -5865,11 +5349,8 @@
       <c r="D204" t="s">
         <v>552</v>
       </c>
-      <c r="G204" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7">
+    </row>
+    <row r="205" spans="1:6">
       <c r="A205" t="s">
         <v>210</v>
       </c>
@@ -5880,7 +5361,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="206" spans="1:7">
+    <row r="206" spans="1:6">
       <c r="A206" t="s">
         <v>211</v>
       </c>
@@ -5891,7 +5372,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="207" spans="1:7">
+    <row r="207" spans="1:6">
       <c r="A207" t="s">
         <v>212</v>
       </c>
@@ -5907,11 +5388,8 @@
       <c r="E207" t="s">
         <v>624</v>
       </c>
-      <c r="G207" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7">
+    </row>
+    <row r="208" spans="1:6">
       <c r="A208" t="s">
         <v>213</v>
       </c>
@@ -5925,7 +5403,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="209" spans="1:7">
+    <row r="209" spans="1:5">
       <c r="A209" t="s">
         <v>214</v>
       </c>
@@ -5936,7 +5414,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="210" spans="1:7">
+    <row r="210" spans="1:5">
       <c r="A210" t="s">
         <v>215</v>
       </c>
@@ -5952,11 +5430,8 @@
       <c r="E210" t="s">
         <v>626</v>
       </c>
-      <c r="G210" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7">
+    </row>
+    <row r="211" spans="1:5">
       <c r="A211" t="s">
         <v>216</v>
       </c>
@@ -5969,11 +5444,8 @@
       <c r="D211" t="s">
         <v>552</v>
       </c>
-      <c r="G211" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7">
+    </row>
+    <row r="212" spans="1:5">
       <c r="A212" t="s">
         <v>217</v>
       </c>
@@ -5987,7 +5459,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="213" spans="1:7">
+    <row r="213" spans="1:5">
       <c r="A213" t="s">
         <v>218</v>
       </c>
@@ -6001,7 +5473,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="214" spans="1:7">
+    <row r="214" spans="1:5">
       <c r="A214" t="s">
         <v>219</v>
       </c>
@@ -6014,11 +5486,8 @@
       <c r="D214" t="s">
         <v>552</v>
       </c>
-      <c r="G214" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="215" spans="1:7">
+    </row>
+    <row r="215" spans="1:5">
       <c r="A215" t="s">
         <v>220</v>
       </c>
@@ -6031,11 +5500,8 @@
       <c r="D215" t="s">
         <v>552</v>
       </c>
-      <c r="G215" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7">
+    </row>
+    <row r="216" spans="1:5">
       <c r="A216" t="s">
         <v>221</v>
       </c>
@@ -6049,7 +5515,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="217" spans="1:7">
+    <row r="217" spans="1:5">
       <c r="A217" t="s">
         <v>222</v>
       </c>
@@ -6065,11 +5531,8 @@
       <c r="E217" t="s">
         <v>630</v>
       </c>
-      <c r="G217" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7">
+    </row>
+    <row r="218" spans="1:5">
       <c r="A218" t="s">
         <v>223</v>
       </c>
@@ -6085,11 +5548,8 @@
       <c r="E218" t="s">
         <v>630</v>
       </c>
-      <c r="G218" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7">
+    </row>
+    <row r="219" spans="1:5">
       <c r="A219" t="s">
         <v>224</v>
       </c>
@@ -6105,11 +5565,8 @@
       <c r="E219" t="s">
         <v>631</v>
       </c>
-      <c r="G219" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7">
+    </row>
+    <row r="220" spans="1:5">
       <c r="A220" t="s">
         <v>225</v>
       </c>
@@ -6120,7 +5577,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="221" spans="1:7">
+    <row r="221" spans="1:5">
       <c r="A221" t="s">
         <v>226</v>
       </c>
@@ -6133,11 +5590,8 @@
       <c r="D221" t="s">
         <v>552</v>
       </c>
-      <c r="G221" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7">
+    </row>
+    <row r="222" spans="1:5">
       <c r="A222" t="s">
         <v>227</v>
       </c>
@@ -6153,11 +5607,8 @@
       <c r="E222" t="s">
         <v>632</v>
       </c>
-      <c r="G222" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7">
+    </row>
+    <row r="223" spans="1:5">
       <c r="A223" t="s">
         <v>228</v>
       </c>
@@ -6170,11 +5621,8 @@
       <c r="D223" t="s">
         <v>552</v>
       </c>
-      <c r="G223" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7">
+    </row>
+    <row r="224" spans="1:5">
       <c r="A224" t="s">
         <v>229</v>
       </c>
@@ -6187,11 +5635,8 @@
       <c r="D224" t="s">
         <v>574</v>
       </c>
-      <c r="G224" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7">
+    </row>
+    <row r="225" spans="1:6">
       <c r="A225" t="s">
         <v>230</v>
       </c>
@@ -6207,11 +5652,8 @@
       <c r="F225" t="s">
         <v>652</v>
       </c>
-      <c r="G225" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7">
+    </row>
+    <row r="226" spans="1:6">
       <c r="A226" t="s">
         <v>231</v>
       </c>
@@ -6224,11 +5666,8 @@
       <c r="D226" t="s">
         <v>552</v>
       </c>
-      <c r="G226" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7">
+    </row>
+    <row r="227" spans="1:6">
       <c r="A227" t="s">
         <v>232</v>
       </c>
@@ -6239,7 +5678,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="228" spans="1:7">
+    <row r="228" spans="1:6">
       <c r="A228" t="s">
         <v>233</v>
       </c>
@@ -6252,11 +5691,8 @@
       <c r="D228" t="s">
         <v>552</v>
       </c>
-      <c r="G228" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7">
+    </row>
+    <row r="229" spans="1:6">
       <c r="A229" t="s">
         <v>234</v>
       </c>
@@ -6269,11 +5705,8 @@
       <c r="D229" t="s">
         <v>552</v>
       </c>
-      <c r="G229" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7">
+    </row>
+    <row r="230" spans="1:6">
       <c r="A230" t="s">
         <v>235</v>
       </c>
@@ -6286,11 +5719,8 @@
       <c r="D230" t="s">
         <v>552</v>
       </c>
-      <c r="G230" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7">
+    </row>
+    <row r="231" spans="1:6">
       <c r="A231" t="s">
         <v>236</v>
       </c>
@@ -6303,11 +5733,8 @@
       <c r="D231" t="s">
         <v>552</v>
       </c>
-      <c r="G231" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7">
+    </row>
+    <row r="232" spans="1:6">
       <c r="A232" t="s">
         <v>237</v>
       </c>
@@ -6320,11 +5747,8 @@
       <c r="D232" t="s">
         <v>552</v>
       </c>
-      <c r="G232" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7">
+    </row>
+    <row r="233" spans="1:6">
       <c r="A233" t="s">
         <v>238</v>
       </c>
@@ -6337,11 +5761,8 @@
       <c r="D233" t="s">
         <v>552</v>
       </c>
-      <c r="G233" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7">
+    </row>
+    <row r="234" spans="1:6">
       <c r="A234" t="s">
         <v>239</v>
       </c>
@@ -6354,11 +5775,8 @@
       <c r="D234" t="s">
         <v>552</v>
       </c>
-      <c r="G234" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7">
+    </row>
+    <row r="235" spans="1:6">
       <c r="A235" t="s">
         <v>240</v>
       </c>
@@ -6371,11 +5789,8 @@
       <c r="D235" t="s">
         <v>552</v>
       </c>
-      <c r="G235" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7">
+    </row>
+    <row r="236" spans="1:6">
       <c r="A236" t="s">
         <v>241</v>
       </c>
@@ -6388,11 +5803,8 @@
       <c r="D236" t="s">
         <v>552</v>
       </c>
-      <c r="G236" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7">
+    </row>
+    <row r="237" spans="1:6">
       <c r="A237" t="s">
         <v>242</v>
       </c>
@@ -6405,11 +5817,8 @@
       <c r="D237" t="s">
         <v>552</v>
       </c>
-      <c r="G237" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7">
+    </row>
+    <row r="238" spans="1:6">
       <c r="A238" t="s">
         <v>243</v>
       </c>
@@ -6422,11 +5831,8 @@
       <c r="D238" t="s">
         <v>552</v>
       </c>
-      <c r="G238" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7">
+    </row>
+    <row r="239" spans="1:6">
       <c r="A239" t="s">
         <v>244</v>
       </c>
@@ -6439,11 +5845,8 @@
       <c r="D239" t="s">
         <v>552</v>
       </c>
-      <c r="G239" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7">
+    </row>
+    <row r="240" spans="1:6">
       <c r="A240" t="s">
         <v>245</v>
       </c>
@@ -6456,11 +5859,8 @@
       <c r="D240" t="s">
         <v>552</v>
       </c>
-      <c r="G240" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7">
+    </row>
+    <row r="241" spans="1:4">
       <c r="A241" t="s">
         <v>246</v>
       </c>
@@ -6473,11 +5873,8 @@
       <c r="D241" t="s">
         <v>552</v>
       </c>
-      <c r="G241" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7">
+    </row>
+    <row r="242" spans="1:4">
       <c r="A242" t="s">
         <v>247</v>
       </c>
@@ -6490,11 +5887,8 @@
       <c r="D242" t="s">
         <v>552</v>
       </c>
-      <c r="G242" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7">
+    </row>
+    <row r="243" spans="1:4">
       <c r="A243" t="s">
         <v>248</v>
       </c>
@@ -6507,11 +5901,8 @@
       <c r="D243" t="s">
         <v>552</v>
       </c>
-      <c r="G243" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7">
+    </row>
+    <row r="244" spans="1:4">
       <c r="A244" t="s">
         <v>249</v>
       </c>
@@ -6524,11 +5915,8 @@
       <c r="D244" t="s">
         <v>552</v>
       </c>
-      <c r="G244" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7">
+    </row>
+    <row r="245" spans="1:4">
       <c r="A245" t="s">
         <v>250</v>
       </c>
@@ -6541,11 +5929,8 @@
       <c r="D245" t="s">
         <v>552</v>
       </c>
-      <c r="G245" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7">
+    </row>
+    <row r="246" spans="1:4">
       <c r="A246" t="s">
         <v>251</v>
       </c>
@@ -6558,11 +5943,8 @@
       <c r="D246" t="s">
         <v>552</v>
       </c>
-      <c r="G246" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7">
+    </row>
+    <row r="247" spans="1:4">
       <c r="A247" t="s">
         <v>252</v>
       </c>
@@ -6575,11 +5957,8 @@
       <c r="D247" t="s">
         <v>552</v>
       </c>
-      <c r="G247" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7">
+    </row>
+    <row r="248" spans="1:4">
       <c r="A248" t="s">
         <v>253</v>
       </c>
@@ -6592,11 +5971,8 @@
       <c r="D248" t="s">
         <v>552</v>
       </c>
-      <c r="G248" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7">
+    </row>
+    <row r="249" spans="1:4">
       <c r="A249" t="s">
         <v>254</v>
       </c>
@@ -6609,11 +5985,8 @@
       <c r="D249" t="s">
         <v>552</v>
       </c>
-      <c r="G249" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7">
+    </row>
+    <row r="250" spans="1:4">
       <c r="A250" t="s">
         <v>255</v>
       </c>
@@ -6626,11 +5999,8 @@
       <c r="D250" t="s">
         <v>552</v>
       </c>
-      <c r="G250" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7">
+    </row>
+    <row r="251" spans="1:4">
       <c r="A251" t="s">
         <v>256</v>
       </c>
@@ -6643,11 +6013,8 @@
       <c r="D251" t="s">
         <v>552</v>
       </c>
-      <c r="G251" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7">
+    </row>
+    <row r="252" spans="1:4">
       <c r="A252" t="s">
         <v>257</v>
       </c>
@@ -6660,11 +6027,8 @@
       <c r="D252" t="s">
         <v>552</v>
       </c>
-      <c r="G252" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7">
+    </row>
+    <row r="253" spans="1:4">
       <c r="A253" t="s">
         <v>258</v>
       </c>
@@ -6677,11 +6041,8 @@
       <c r="D253" t="s">
         <v>552</v>
       </c>
-      <c r="G253" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7">
+    </row>
+    <row r="254" spans="1:4">
       <c r="A254" t="s">
         <v>259</v>
       </c>
@@ -6694,11 +6055,8 @@
       <c r="D254" t="s">
         <v>552</v>
       </c>
-      <c r="G254" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7">
+    </row>
+    <row r="255" spans="1:4">
       <c r="A255" t="s">
         <v>260</v>
       </c>
@@ -6711,11 +6069,8 @@
       <c r="D255" t="s">
         <v>552</v>
       </c>
-      <c r="G255" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7">
+    </row>
+    <row r="256" spans="1:4">
       <c r="A256" t="s">
         <v>261</v>
       </c>
@@ -6728,11 +6083,8 @@
       <c r="D256" t="s">
         <v>552</v>
       </c>
-      <c r="G256" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7">
+    </row>
+    <row r="257" spans="1:4">
       <c r="A257" t="s">
         <v>262</v>
       </c>
@@ -6745,11 +6097,8 @@
       <c r="D257" t="s">
         <v>552</v>
       </c>
-      <c r="G257" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7">
+    </row>
+    <row r="258" spans="1:4">
       <c r="A258" t="s">
         <v>263</v>
       </c>
@@ -6762,11 +6111,8 @@
       <c r="D258" t="s">
         <v>552</v>
       </c>
-      <c r="G258" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7">
+    </row>
+    <row r="259" spans="1:4">
       <c r="A259" t="s">
         <v>264</v>
       </c>
@@ -6779,11 +6125,8 @@
       <c r="D259" t="s">
         <v>552</v>
       </c>
-      <c r="G259" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7">
+    </row>
+    <row r="260" spans="1:4">
       <c r="A260" t="s">
         <v>265</v>
       </c>
@@ -6796,11 +6139,8 @@
       <c r="D260" t="s">
         <v>552</v>
       </c>
-      <c r="G260" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7">
+    </row>
+    <row r="261" spans="1:4">
       <c r="A261" t="s">
         <v>266</v>
       </c>
@@ -6813,11 +6153,8 @@
       <c r="D261" t="s">
         <v>552</v>
       </c>
-      <c r="G261" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7">
+    </row>
+    <row r="262" spans="1:4">
       <c r="A262" t="s">
         <v>267</v>
       </c>
@@ -6830,11 +6167,8 @@
       <c r="D262" t="s">
         <v>552</v>
       </c>
-      <c r="G262" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7">
+    </row>
+    <row r="263" spans="1:4">
       <c r="A263" t="s">
         <v>268</v>
       </c>
@@ -6847,11 +6181,8 @@
       <c r="D263" t="s">
         <v>552</v>
       </c>
-      <c r="G263" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7">
+    </row>
+    <row r="264" spans="1:4">
       <c r="A264" t="s">
         <v>269</v>
       </c>
@@ -6864,11 +6195,8 @@
       <c r="D264" t="s">
         <v>552</v>
       </c>
-      <c r="G264" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7">
+    </row>
+    <row r="265" spans="1:4">
       <c r="A265" t="s">
         <v>270</v>
       </c>
@@ -6881,11 +6209,8 @@
       <c r="D265" t="s">
         <v>552</v>
       </c>
-      <c r="G265" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7">
+    </row>
+    <row r="266" spans="1:4">
       <c r="A266" t="s">
         <v>271</v>
       </c>
@@ -6898,11 +6223,8 @@
       <c r="D266" t="s">
         <v>577</v>
       </c>
-      <c r="G266" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7">
+    </row>
+    <row r="267" spans="1:4">
       <c r="A267" t="s">
         <v>272</v>
       </c>
@@ -6915,11 +6237,8 @@
       <c r="D267" t="s">
         <v>577</v>
       </c>
-      <c r="G267" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7">
+    </row>
+    <row r="268" spans="1:4">
       <c r="A268" t="s">
         <v>273</v>
       </c>
@@ -6932,11 +6251,8 @@
       <c r="D268" t="s">
         <v>577</v>
       </c>
-      <c r="G268" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7">
+    </row>
+    <row r="269" spans="1:4">
       <c r="A269" t="s">
         <v>274</v>
       </c>
@@ -6949,11 +6265,8 @@
       <c r="D269" t="s">
         <v>577</v>
       </c>
-      <c r="G269" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7">
+    </row>
+    <row r="270" spans="1:4">
       <c r="A270" t="s">
         <v>275</v>
       </c>
@@ -6966,11 +6279,8 @@
       <c r="D270" t="s">
         <v>577</v>
       </c>
-      <c r="G270" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7">
+    </row>
+    <row r="271" spans="1:4">
       <c r="A271" t="s">
         <v>276</v>
       </c>
@@ -6983,11 +6293,8 @@
       <c r="D271" t="s">
         <v>577</v>
       </c>
-      <c r="G271" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7">
+    </row>
+    <row r="272" spans="1:4">
       <c r="A272" t="s">
         <v>277</v>
       </c>
@@ -7000,11 +6307,8 @@
       <c r="D272" t="s">
         <v>577</v>
       </c>
-      <c r="G272" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7">
+    </row>
+    <row r="273" spans="1:4">
       <c r="A273" t="s">
         <v>278</v>
       </c>
@@ -7017,11 +6321,8 @@
       <c r="D273" t="s">
         <v>577</v>
       </c>
-      <c r="G273" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7">
+    </row>
+    <row r="274" spans="1:4">
       <c r="A274" t="s">
         <v>279</v>
       </c>
@@ -7034,11 +6335,8 @@
       <c r="D274" t="s">
         <v>577</v>
       </c>
-      <c r="G274" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7">
+    </row>
+    <row r="275" spans="1:4">
       <c r="A275" t="s">
         <v>280</v>
       </c>
@@ -7051,11 +6349,8 @@
       <c r="D275" t="s">
         <v>577</v>
       </c>
-      <c r="G275" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7">
+    </row>
+    <row r="276" spans="1:4">
       <c r="A276" t="s">
         <v>281</v>
       </c>
@@ -7068,11 +6363,8 @@
       <c r="D276" t="s">
         <v>577</v>
       </c>
-      <c r="G276" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7">
+    </row>
+    <row r="277" spans="1:4">
       <c r="A277" t="s">
         <v>282</v>
       </c>
@@ -7085,11 +6377,8 @@
       <c r="D277" t="s">
         <v>577</v>
       </c>
-      <c r="G277" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7">
+    </row>
+    <row r="278" spans="1:4">
       <c r="A278" t="s">
         <v>283</v>
       </c>
@@ -7102,11 +6391,8 @@
       <c r="D278" t="s">
         <v>577</v>
       </c>
-      <c r="G278" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7">
+    </row>
+    <row r="279" spans="1:4">
       <c r="A279" t="s">
         <v>284</v>
       </c>
@@ -7119,11 +6405,8 @@
       <c r="D279" t="s">
         <v>577</v>
       </c>
-      <c r="G279" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7">
+    </row>
+    <row r="280" spans="1:4">
       <c r="A280" t="s">
         <v>285</v>
       </c>
@@ -7136,11 +6419,8 @@
       <c r="D280" t="s">
         <v>566</v>
       </c>
-      <c r="G280" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7">
+    </row>
+    <row r="281" spans="1:4">
       <c r="A281" t="s">
         <v>286</v>
       </c>
@@ -7153,11 +6433,8 @@
       <c r="D281" t="s">
         <v>578</v>
       </c>
-      <c r="G281" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7">
+    </row>
+    <row r="282" spans="1:4">
       <c r="A282" t="s">
         <v>287</v>
       </c>
@@ -7170,11 +6447,8 @@
       <c r="D282" t="s">
         <v>566</v>
       </c>
-      <c r="G282" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7">
+    </row>
+    <row r="283" spans="1:4">
       <c r="A283" t="s">
         <v>288</v>
       </c>
@@ -7186,9 +6460,6 @@
       </c>
       <c r="D283" t="s">
         <v>566</v>
-      </c>
-      <c r="G283" t="s">
-        <v>653</v>
       </c>
     </row>
   </sheetData>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="654">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -1973,6 +1973,9 @@
   </si>
   <si>
     <t>www.cmacofct.com</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -2362,6 +2365,9 @@
       <c r="F2" t="s">
         <v>633</v>
       </c>
+      <c r="G2" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
@@ -2382,6 +2388,9 @@
       <c r="F3" t="s">
         <v>633</v>
       </c>
+      <c r="G3" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
@@ -2402,6 +2411,9 @@
       <c r="F4" t="s">
         <v>633</v>
       </c>
+      <c r="G4" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
@@ -2422,6 +2434,9 @@
       <c r="F5" t="s">
         <v>633</v>
       </c>
+      <c r="G5" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
@@ -2442,6 +2457,9 @@
       <c r="F6" t="s">
         <v>633</v>
       </c>
+      <c r="G6" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
@@ -2462,6 +2480,9 @@
       <c r="F7" t="s">
         <v>633</v>
       </c>
+      <c r="G7" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
@@ -2482,6 +2503,9 @@
       <c r="F8" t="s">
         <v>633</v>
       </c>
+      <c r="G8" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
@@ -2502,6 +2526,9 @@
       <c r="F9" t="s">
         <v>633</v>
       </c>
+      <c r="G9" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
@@ -2522,6 +2549,9 @@
       <c r="F10" t="s">
         <v>633</v>
       </c>
+      <c r="G10" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
@@ -2542,6 +2572,9 @@
       <c r="F11" t="s">
         <v>633</v>
       </c>
+      <c r="G11" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
@@ -2562,6 +2595,9 @@
       <c r="F12" t="s">
         <v>633</v>
       </c>
+      <c r="G12" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
@@ -2582,6 +2618,9 @@
       <c r="F13" t="s">
         <v>633</v>
       </c>
+      <c r="G13" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
@@ -2602,6 +2641,9 @@
       <c r="F14" s="1" t="s">
         <v>634</v>
       </c>
+      <c r="G14" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
@@ -2622,6 +2664,9 @@
       <c r="F15" s="1" t="s">
         <v>635</v>
       </c>
+      <c r="G15" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
@@ -2636,8 +2681,11 @@
       <c r="D16" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="G16" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -2650,8 +2698,11 @@
       <c r="D17" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="G17" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2715,11 @@
       <c r="D18" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="G18" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -2678,8 +2732,11 @@
       <c r="D19" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="G19" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -2692,8 +2749,11 @@
       <c r="D20" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="G20" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -2706,8 +2766,11 @@
       <c r="D21" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="G21" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -2720,8 +2783,11 @@
       <c r="D22" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="G22" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -2734,8 +2800,11 @@
       <c r="D23" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="G23" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -2748,8 +2817,11 @@
       <c r="D24" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="G24" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -2762,8 +2834,11 @@
       <c r="D25" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="G25" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -2776,8 +2851,11 @@
       <c r="D26" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="G26" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -2790,8 +2868,11 @@
       <c r="D27" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="G27" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -2804,8 +2885,11 @@
       <c r="D28" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="G28" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -2818,8 +2902,11 @@
       <c r="D29" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="G29" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -2832,8 +2919,11 @@
       <c r="D30" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="G30" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -2846,8 +2936,11 @@
       <c r="D31" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="G31" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -2860,8 +2953,11 @@
       <c r="D32" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="G32" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -2874,8 +2970,11 @@
       <c r="D33" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="G33" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -2888,8 +2987,11 @@
       <c r="D34" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="G34" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -2902,8 +3004,11 @@
       <c r="D35" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="G35" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -2916,8 +3021,11 @@
       <c r="D36" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="G36" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -2930,8 +3038,11 @@
       <c r="D37" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="38" spans="1:4">
+      <c r="G37" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -2944,8 +3055,11 @@
       <c r="D38" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="39" spans="1:4">
+      <c r="G38" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -2958,8 +3072,11 @@
       <c r="D39" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="40" spans="1:4">
+      <c r="G39" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -2972,8 +3089,11 @@
       <c r="D40" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="41" spans="1:4">
+      <c r="G40" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -2986,8 +3106,11 @@
       <c r="D41" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="42" spans="1:4">
+      <c r="G41" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -3000,8 +3123,11 @@
       <c r="D42" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="43" spans="1:4">
+      <c r="G42" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -3014,8 +3140,11 @@
       <c r="D43" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="44" spans="1:4">
+      <c r="G43" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -3028,8 +3157,11 @@
       <c r="D44" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="45" spans="1:4">
+      <c r="G44" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -3042,8 +3174,11 @@
       <c r="D45" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="46" spans="1:4">
+      <c r="G45" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -3056,8 +3191,11 @@
       <c r="D46" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="47" spans="1:4">
+      <c r="G46" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -3070,8 +3208,11 @@
       <c r="D47" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="48" spans="1:4">
+      <c r="G47" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -3084,8 +3225,11 @@
       <c r="D48" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="49" spans="1:4">
+      <c r="G48" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -3098,8 +3242,11 @@
       <c r="D49" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="50" spans="1:4">
+      <c r="G49" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -3112,8 +3259,11 @@
       <c r="D50" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="51" spans="1:4">
+      <c r="G50" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>56</v>
       </c>
@@ -3126,8 +3276,11 @@
       <c r="D51" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="52" spans="1:4">
+      <c r="G51" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>57</v>
       </c>
@@ -3140,8 +3293,11 @@
       <c r="D52" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="53" spans="1:4">
+      <c r="G52" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>58</v>
       </c>
@@ -3154,8 +3310,11 @@
       <c r="D53" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="54" spans="1:4">
+      <c r="G53" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>59</v>
       </c>
@@ -3168,8 +3327,11 @@
       <c r="D54" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="55" spans="1:4">
+      <c r="G54" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>60</v>
       </c>
@@ -3182,8 +3344,11 @@
       <c r="D55" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="56" spans="1:4">
+      <c r="G55" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -3196,8 +3361,11 @@
       <c r="D56" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="57" spans="1:4">
+      <c r="G56" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>62</v>
       </c>
@@ -3210,8 +3378,11 @@
       <c r="D57" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="58" spans="1:4">
+      <c r="G57" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>63</v>
       </c>
@@ -3224,8 +3395,11 @@
       <c r="D58" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="59" spans="1:4">
+      <c r="G58" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -3238,8 +3412,11 @@
       <c r="D59" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="60" spans="1:4">
+      <c r="G59" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>65</v>
       </c>
@@ -3252,8 +3429,11 @@
       <c r="D60" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="61" spans="1:4">
+      <c r="G60" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>66</v>
       </c>
@@ -3266,8 +3446,11 @@
       <c r="D61" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="62" spans="1:4">
+      <c r="G61" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>67</v>
       </c>
@@ -3280,8 +3463,11 @@
       <c r="D62" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="63" spans="1:4">
+      <c r="G62" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>68</v>
       </c>
@@ -3294,8 +3480,11 @@
       <c r="D63" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="64" spans="1:4">
+      <c r="G63" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
         <v>69</v>
       </c>
@@ -3308,8 +3497,11 @@
       <c r="D64" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="65" spans="1:4">
+      <c r="G64" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
         <v>70</v>
       </c>
@@ -3322,8 +3514,11 @@
       <c r="D65" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="66" spans="1:4">
+      <c r="G65" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
         <v>71</v>
       </c>
@@ -3336,8 +3531,11 @@
       <c r="D66" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="67" spans="1:4">
+      <c r="G66" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67" t="s">
         <v>72</v>
       </c>
@@ -3350,8 +3548,11 @@
       <c r="D67" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="68" spans="1:4">
+      <c r="G67" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
         <v>73</v>
       </c>
@@ -3364,8 +3565,11 @@
       <c r="D68" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="69" spans="1:4">
+      <c r="G68" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69" t="s">
         <v>74</v>
       </c>
@@ -3378,8 +3582,11 @@
       <c r="D69" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="70" spans="1:4">
+      <c r="G69" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
       <c r="A70" t="s">
         <v>75</v>
       </c>
@@ -3392,8 +3599,11 @@
       <c r="D70" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="71" spans="1:4">
+      <c r="G70" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
       <c r="A71" t="s">
         <v>76</v>
       </c>
@@ -3406,8 +3616,11 @@
       <c r="D71" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="72" spans="1:4">
+      <c r="G71" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
       <c r="A72" t="s">
         <v>77</v>
       </c>
@@ -3420,8 +3633,11 @@
       <c r="D72" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="73" spans="1:4">
+      <c r="G72" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
       <c r="A73" t="s">
         <v>78</v>
       </c>
@@ -3434,8 +3650,11 @@
       <c r="D73" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="74" spans="1:4">
+      <c r="G73" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
       <c r="A74" t="s">
         <v>79</v>
       </c>
@@ -3448,8 +3667,11 @@
       <c r="D74" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="75" spans="1:4">
+      <c r="G74" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
       <c r="A75" t="s">
         <v>80</v>
       </c>
@@ -3462,8 +3684,11 @@
       <c r="D75" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="76" spans="1:4">
+      <c r="G75" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
         <v>81</v>
       </c>
@@ -3476,8 +3701,11 @@
       <c r="D76" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="77" spans="1:4">
+      <c r="G76" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
         <v>82</v>
       </c>
@@ -3490,8 +3718,11 @@
       <c r="D77" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="78" spans="1:4">
+      <c r="G77" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
         <v>83</v>
       </c>
@@ -3504,8 +3735,11 @@
       <c r="D78" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="79" spans="1:4">
+      <c r="G78" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
       <c r="A79" t="s">
         <v>84</v>
       </c>
@@ -3518,8 +3752,11 @@
       <c r="D79" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="80" spans="1:4">
+      <c r="G79" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
       <c r="A80" t="s">
         <v>85</v>
       </c>
@@ -3532,8 +3769,11 @@
       <c r="D80" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="81" spans="1:4">
+      <c r="G80" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
       <c r="A81" t="s">
         <v>86</v>
       </c>
@@ -3546,8 +3786,11 @@
       <c r="D81" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="82" spans="1:4">
+      <c r="G81" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
       <c r="A82" t="s">
         <v>87</v>
       </c>
@@ -3560,8 +3803,11 @@
       <c r="D82" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="83" spans="1:4">
+      <c r="G82" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
       <c r="A83" t="s">
         <v>88</v>
       </c>
@@ -3574,8 +3820,11 @@
       <c r="D83" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="84" spans="1:4">
+      <c r="G83" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
       <c r="A84" t="s">
         <v>89</v>
       </c>
@@ -3588,8 +3837,11 @@
       <c r="D84" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="85" spans="1:4">
+      <c r="G84" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
       <c r="A85" t="s">
         <v>90</v>
       </c>
@@ -3602,8 +3854,11 @@
       <c r="D85" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="86" spans="1:4">
+      <c r="G85" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
       <c r="A86" t="s">
         <v>91</v>
       </c>
@@ -3616,8 +3871,11 @@
       <c r="D86" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="87" spans="1:4">
+      <c r="G86" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
       <c r="A87" t="s">
         <v>92</v>
       </c>
@@ -3630,8 +3888,11 @@
       <c r="D87" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="88" spans="1:4">
+      <c r="G87" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
       <c r="A88" t="s">
         <v>93</v>
       </c>
@@ -3644,8 +3905,11 @@
       <c r="D88" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="89" spans="1:4">
+      <c r="G88" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
       <c r="A89" t="s">
         <v>94</v>
       </c>
@@ -3658,8 +3922,11 @@
       <c r="D89" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="90" spans="1:4">
+      <c r="G89" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
       <c r="A90" t="s">
         <v>95</v>
       </c>
@@ -3672,8 +3939,11 @@
       <c r="D90" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="91" spans="1:4">
+      <c r="G90" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
       <c r="A91" t="s">
         <v>96</v>
       </c>
@@ -3686,8 +3956,11 @@
       <c r="D91" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="92" spans="1:4">
+      <c r="G91" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
       <c r="A92" t="s">
         <v>97</v>
       </c>
@@ -3700,8 +3973,11 @@
       <c r="D92" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="93" spans="1:4">
+      <c r="G92" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
       <c r="A93" t="s">
         <v>98</v>
       </c>
@@ -3714,8 +3990,11 @@
       <c r="D93" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="94" spans="1:4">
+      <c r="G93" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
       <c r="A94" t="s">
         <v>99</v>
       </c>
@@ -3728,8 +4007,11 @@
       <c r="D94" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="95" spans="1:4">
+      <c r="G94" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
       <c r="A95" t="s">
         <v>100</v>
       </c>
@@ -3742,8 +4024,11 @@
       <c r="D95" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="96" spans="1:4">
+      <c r="G95" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
       <c r="A96" t="s">
         <v>101</v>
       </c>
@@ -3756,8 +4041,11 @@
       <c r="D96" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="97" spans="1:4">
+      <c r="G96" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
       <c r="A97" t="s">
         <v>102</v>
       </c>
@@ -3770,8 +4058,11 @@
       <c r="D97" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="98" spans="1:4">
+      <c r="G97" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
       <c r="A98" t="s">
         <v>103</v>
       </c>
@@ -3784,8 +4075,11 @@
       <c r="D98" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="99" spans="1:4">
+      <c r="G98" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
       <c r="A99" t="s">
         <v>104</v>
       </c>
@@ -3798,8 +4092,11 @@
       <c r="D99" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="100" spans="1:4">
+      <c r="G99" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
       <c r="A100" t="s">
         <v>105</v>
       </c>
@@ -3812,8 +4109,11 @@
       <c r="D100" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="101" spans="1:4">
+      <c r="G100" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
       <c r="A101" t="s">
         <v>106</v>
       </c>
@@ -3826,8 +4126,11 @@
       <c r="D101" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="102" spans="1:4">
+      <c r="G101" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
       <c r="A102" t="s">
         <v>107</v>
       </c>
@@ -3840,8 +4143,11 @@
       <c r="D102" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="103" spans="1:4">
+      <c r="G102" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
       <c r="A103" t="s">
         <v>108</v>
       </c>
@@ -3854,8 +4160,11 @@
       <c r="D103" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="104" spans="1:4">
+      <c r="G103" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
       <c r="A104" t="s">
         <v>109</v>
       </c>
@@ -3868,8 +4177,11 @@
       <c r="D104" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
+      <c r="G104" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
       <c r="A105" t="s">
         <v>110</v>
       </c>
@@ -3882,8 +4194,11 @@
       <c r="D105" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="106" spans="1:4">
+      <c r="G105" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
       <c r="A106" t="s">
         <v>111</v>
       </c>
@@ -3896,8 +4211,11 @@
       <c r="D106" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="107" spans="1:4">
+      <c r="G106" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
       <c r="A107" t="s">
         <v>112</v>
       </c>
@@ -3910,8 +4228,11 @@
       <c r="D107" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="108" spans="1:4">
+      <c r="G107" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
       <c r="A108" t="s">
         <v>113</v>
       </c>
@@ -3924,8 +4245,11 @@
       <c r="D108" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="109" spans="1:4">
+      <c r="G108" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
       <c r="A109" t="s">
         <v>114</v>
       </c>
@@ -3938,8 +4262,11 @@
       <c r="D109" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
+      <c r="G109" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
       <c r="A110" t="s">
         <v>115</v>
       </c>
@@ -3952,8 +4279,11 @@
       <c r="D110" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="111" spans="1:4">
+      <c r="G110" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
       <c r="A111" t="s">
         <v>116</v>
       </c>
@@ -3966,8 +4296,11 @@
       <c r="D111" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
+      <c r="G111" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
       <c r="A112" t="s">
         <v>117</v>
       </c>
@@ -3980,8 +4313,11 @@
       <c r="D112" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="113" spans="1:6">
+      <c r="G112" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
       <c r="A113" t="s">
         <v>118</v>
       </c>
@@ -3994,8 +4330,11 @@
       <c r="D113" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="114" spans="1:6">
+      <c r="G113" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
       <c r="A114" t="s">
         <v>119</v>
       </c>
@@ -4008,8 +4347,11 @@
       <c r="D114" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="115" spans="1:6">
+      <c r="G114" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
       <c r="A115" t="s">
         <v>120</v>
       </c>
@@ -4022,8 +4364,11 @@
       <c r="D115" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="116" spans="1:6">
+      <c r="G115" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
       <c r="A116" t="s">
         <v>121</v>
       </c>
@@ -4036,8 +4381,11 @@
       <c r="D116" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="117" spans="1:6">
+      <c r="G116" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
       <c r="A117" t="s">
         <v>122</v>
       </c>
@@ -4050,8 +4398,11 @@
       <c r="D117" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="G117" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
       <c r="A118" t="s">
         <v>123</v>
       </c>
@@ -4064,8 +4415,11 @@
       <c r="D118" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="119" spans="1:6">
+      <c r="G118" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
       <c r="A119" t="s">
         <v>124</v>
       </c>
@@ -4084,8 +4438,11 @@
       <c r="F119" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="120" spans="1:6">
+      <c r="G119" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
       <c r="A120" t="s">
         <v>125</v>
       </c>
@@ -4101,8 +4458,11 @@
       <c r="E120" t="s">
         <v>583</v>
       </c>
-    </row>
-    <row r="121" spans="1:6">
+      <c r="G120" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
       <c r="A121" t="s">
         <v>126</v>
       </c>
@@ -4115,8 +4475,11 @@
       <c r="D121" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="122" spans="1:6">
+      <c r="G121" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
       <c r="A122" t="s">
         <v>127</v>
       </c>
@@ -4129,8 +4492,11 @@
       <c r="D122" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="123" spans="1:6">
+      <c r="G122" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
       <c r="A123" t="s">
         <v>128</v>
       </c>
@@ -4149,8 +4515,11 @@
       <c r="F123" t="s">
         <v>637</v>
       </c>
-    </row>
-    <row r="124" spans="1:6">
+      <c r="G123" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
       <c r="A124" t="s">
         <v>129</v>
       </c>
@@ -4163,8 +4532,11 @@
       <c r="D124" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="125" spans="1:6">
+      <c r="G124" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
       <c r="A125" t="s">
         <v>130</v>
       </c>
@@ -4177,8 +4549,11 @@
       <c r="D125" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="126" spans="1:6">
+      <c r="G125" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
       <c r="A126" t="s">
         <v>131</v>
       </c>
@@ -4191,8 +4566,11 @@
       <c r="D126" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="127" spans="1:6">
+      <c r="G126" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
       <c r="A127" t="s">
         <v>132</v>
       </c>
@@ -4205,8 +4583,11 @@
       <c r="D127" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="128" spans="1:6">
+      <c r="G127" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
       <c r="A128" t="s">
         <v>133</v>
       </c>
@@ -4222,8 +4603,11 @@
       <c r="E128" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="129" spans="1:6">
+      <c r="G128" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
       <c r="A129" t="s">
         <v>134</v>
       </c>
@@ -4242,8 +4626,11 @@
       <c r="F129" t="s">
         <v>638</v>
       </c>
-    </row>
-    <row r="130" spans="1:6">
+      <c r="G129" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
       <c r="A130" t="s">
         <v>135</v>
       </c>
@@ -4256,8 +4643,11 @@
       <c r="D130" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="131" spans="1:6">
+      <c r="G130" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
       <c r="A131" t="s">
         <v>136</v>
       </c>
@@ -4271,7 +4661,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:7">
       <c r="A132" t="s">
         <v>137</v>
       </c>
@@ -4287,8 +4677,11 @@
       <c r="E132" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="133" spans="1:6">
+      <c r="G132" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
       <c r="A133" t="s">
         <v>138</v>
       </c>
@@ -4304,8 +4697,11 @@
       <c r="E133" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="G133" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
       <c r="A134" t="s">
         <v>139</v>
       </c>
@@ -4316,7 +4712,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:7">
       <c r="A135" t="s">
         <v>140</v>
       </c>
@@ -4327,7 +4723,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:7">
       <c r="A136" t="s">
         <v>141</v>
       </c>
@@ -4340,8 +4736,11 @@
       <c r="D136" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="137" spans="1:6">
+      <c r="G136" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
       <c r="A137" t="s">
         <v>142</v>
       </c>
@@ -4354,8 +4753,11 @@
       <c r="D137" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="138" spans="1:6">
+      <c r="G137" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
       <c r="A138" t="s">
         <v>143</v>
       </c>
@@ -4366,7 +4768,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:7">
       <c r="A139" t="s">
         <v>144</v>
       </c>
@@ -4377,7 +4779,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:7">
       <c r="A140" t="s">
         <v>145</v>
       </c>
@@ -4388,7 +4790,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:7">
       <c r="A141" t="s">
         <v>146</v>
       </c>
@@ -4401,8 +4803,11 @@
       <c r="D141" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="142" spans="1:6">
+      <c r="G141" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
       <c r="A142" t="s">
         <v>147</v>
       </c>
@@ -4421,8 +4826,11 @@
       <c r="F142" t="s">
         <v>639</v>
       </c>
-    </row>
-    <row r="143" spans="1:6">
+      <c r="G142" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
       <c r="A143" t="s">
         <v>148</v>
       </c>
@@ -4435,8 +4843,11 @@
       <c r="D143" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="144" spans="1:6">
+      <c r="G143" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
       <c r="A144" t="s">
         <v>149</v>
       </c>
@@ -4450,7 +4861,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:7">
       <c r="A145" t="s">
         <v>150</v>
       </c>
@@ -4461,7 +4872,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="1:7">
       <c r="A146" t="s">
         <v>151</v>
       </c>
@@ -4477,8 +4888,11 @@
       <c r="F146" t="s">
         <v>640</v>
       </c>
-    </row>
-    <row r="147" spans="1:6">
+      <c r="G146" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
       <c r="A147" t="s">
         <v>152</v>
       </c>
@@ -4497,8 +4911,11 @@
       <c r="F147" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="148" spans="1:6">
+      <c r="G147" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
       <c r="A148" t="s">
         <v>153</v>
       </c>
@@ -4514,8 +4931,11 @@
       <c r="E148" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="149" spans="1:6">
+      <c r="G148" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
       <c r="A149" t="s">
         <v>154</v>
       </c>
@@ -4531,8 +4951,11 @@
       <c r="E149" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="150" spans="1:6">
+      <c r="G149" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
       <c r="A150" t="s">
         <v>155</v>
       </c>
@@ -4548,8 +4971,11 @@
       <c r="E150" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="G150" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
       <c r="A151" t="s">
         <v>156</v>
       </c>
@@ -4565,8 +4991,11 @@
       <c r="E151" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="152" spans="1:6">
+      <c r="G151" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
       <c r="A152" t="s">
         <v>157</v>
       </c>
@@ -4582,8 +5011,11 @@
       <c r="E152" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="153" spans="1:6">
+      <c r="G152" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
       <c r="A153" t="s">
         <v>158</v>
       </c>
@@ -4594,7 +5026,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:7">
       <c r="A154" t="s">
         <v>159</v>
       </c>
@@ -4610,8 +5042,11 @@
       <c r="E154" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="155" spans="1:6">
+      <c r="G154" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
       <c r="A155" t="s">
         <v>160</v>
       </c>
@@ -4624,8 +5059,11 @@
       <c r="D155" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="156" spans="1:6">
+      <c r="G155" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
       <c r="A156" t="s">
         <v>161</v>
       </c>
@@ -4638,8 +5076,11 @@
       <c r="D156" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="157" spans="1:6">
+      <c r="G156" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
       <c r="A157" t="s">
         <v>162</v>
       </c>
@@ -4658,8 +5099,11 @@
       <c r="F157" t="s">
         <v>642</v>
       </c>
-    </row>
-    <row r="158" spans="1:6">
+      <c r="G157" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
       <c r="A158" t="s">
         <v>163</v>
       </c>
@@ -4675,8 +5119,11 @@
       <c r="E158" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="159" spans="1:6">
+      <c r="G158" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
       <c r="A159" t="s">
         <v>164</v>
       </c>
@@ -4692,8 +5139,11 @@
       <c r="E159" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="160" spans="1:6">
+      <c r="G159" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7">
       <c r="A160" t="s">
         <v>165</v>
       </c>
@@ -4709,8 +5159,11 @@
       <c r="E160" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="161" spans="1:6">
+      <c r="G160" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
       <c r="A161" t="s">
         <v>166</v>
       </c>
@@ -4726,8 +5179,11 @@
       <c r="E161" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="162" spans="1:6">
+      <c r="G161" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7">
       <c r="A162" t="s">
         <v>167</v>
       </c>
@@ -4740,8 +5196,11 @@
       <c r="D162" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="163" spans="1:6">
+      <c r="G162" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
       <c r="A163" t="s">
         <v>168</v>
       </c>
@@ -4757,8 +5216,11 @@
       <c r="E163" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="164" spans="1:6">
+      <c r="G163" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
       <c r="A164" t="s">
         <v>169</v>
       </c>
@@ -4774,8 +5236,11 @@
       <c r="E164" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="165" spans="1:6">
+      <c r="G164" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
       <c r="A165" t="s">
         <v>170</v>
       </c>
@@ -4789,7 +5254,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166" spans="1:7">
       <c r="A166" t="s">
         <v>171</v>
       </c>
@@ -4805,8 +5270,11 @@
       <c r="E166" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="167" spans="1:6">
+      <c r="G166" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
       <c r="A167" t="s">
         <v>172</v>
       </c>
@@ -4822,8 +5290,11 @@
       <c r="E167" t="s">
         <v>608</v>
       </c>
-    </row>
-    <row r="168" spans="1:6">
+      <c r="G167" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7">
       <c r="A168" t="s">
         <v>173</v>
       </c>
@@ -4839,8 +5310,11 @@
       <c r="E168" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="169" spans="1:6">
+      <c r="G168" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
       <c r="A169" t="s">
         <v>174</v>
       </c>
@@ -4856,8 +5330,11 @@
       <c r="E169" t="s">
         <v>610</v>
       </c>
-    </row>
-    <row r="170" spans="1:6">
+      <c r="G169" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
       <c r="A170" t="s">
         <v>175</v>
       </c>
@@ -4871,7 +5348,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" spans="1:7">
       <c r="A171" t="s">
         <v>176</v>
       </c>
@@ -4885,7 +5362,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" spans="1:7">
       <c r="A172" t="s">
         <v>177</v>
       </c>
@@ -4899,7 +5376,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173" spans="1:7">
       <c r="A173" t="s">
         <v>178</v>
       </c>
@@ -4912,8 +5389,11 @@
       <c r="D173" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="174" spans="1:6">
+      <c r="G173" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7">
       <c r="A174" t="s">
         <v>179</v>
       </c>
@@ -4929,8 +5409,11 @@
       <c r="F174" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="175" spans="1:6">
+      <c r="G174" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
       <c r="A175" t="s">
         <v>180</v>
       </c>
@@ -4946,8 +5429,11 @@
       <c r="F175" t="s">
         <v>644</v>
       </c>
-    </row>
-    <row r="176" spans="1:6">
+      <c r="G175" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
       <c r="A176" t="s">
         <v>181</v>
       </c>
@@ -4958,7 +5444,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="177" spans="1:6">
+    <row r="177" spans="1:7">
       <c r="A177" t="s">
         <v>182</v>
       </c>
@@ -4969,7 +5455,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="178" spans="1:6">
+    <row r="178" spans="1:7">
       <c r="A178" t="s">
         <v>183</v>
       </c>
@@ -4980,7 +5466,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="179" spans="1:6">
+    <row r="179" spans="1:7">
       <c r="A179" t="s">
         <v>184</v>
       </c>
@@ -4999,8 +5485,11 @@
       <c r="F179" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="180" spans="1:6">
+      <c r="G179" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7">
       <c r="A180" t="s">
         <v>185</v>
       </c>
@@ -5011,7 +5500,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="181" spans="1:6">
+    <row r="181" spans="1:7">
       <c r="A181" t="s">
         <v>186</v>
       </c>
@@ -5022,7 +5511,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:7">
       <c r="A182" t="s">
         <v>187</v>
       </c>
@@ -5038,8 +5527,11 @@
       <c r="E182" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="183" spans="1:6">
+      <c r="G182" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7">
       <c r="A183" t="s">
         <v>188</v>
       </c>
@@ -5055,8 +5547,11 @@
       <c r="F183" t="s">
         <v>646</v>
       </c>
-    </row>
-    <row r="184" spans="1:6">
+      <c r="G183" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7">
       <c r="A184" t="s">
         <v>189</v>
       </c>
@@ -5067,7 +5562,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:7">
       <c r="A185" t="s">
         <v>190</v>
       </c>
@@ -5081,7 +5576,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="186" spans="1:6">
+    <row r="186" spans="1:7">
       <c r="A186" t="s">
         <v>191</v>
       </c>
@@ -5095,7 +5590,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:7">
       <c r="A187" t="s">
         <v>192</v>
       </c>
@@ -5109,7 +5604,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="188" spans="1:6">
+    <row r="188" spans="1:7">
       <c r="A188" t="s">
         <v>193</v>
       </c>
@@ -5123,7 +5618,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="189" spans="1:6">
+    <row r="189" spans="1:7">
       <c r="A189" t="s">
         <v>194</v>
       </c>
@@ -5137,7 +5632,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="190" spans="1:6">
+    <row r="190" spans="1:7">
       <c r="A190" t="s">
         <v>195</v>
       </c>
@@ -5151,7 +5646,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="191" spans="1:6">
+    <row r="191" spans="1:7">
       <c r="A191" t="s">
         <v>196</v>
       </c>
@@ -5162,7 +5657,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="192" spans="1:6">
+    <row r="192" spans="1:7">
       <c r="A192" t="s">
         <v>197</v>
       </c>
@@ -5173,7 +5668,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="193" spans="1:6">
+    <row r="193" spans="1:7">
       <c r="A193" t="s">
         <v>198</v>
       </c>
@@ -5184,7 +5679,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="194" spans="1:6">
+    <row r="194" spans="1:7">
       <c r="A194" t="s">
         <v>199</v>
       </c>
@@ -5197,8 +5692,11 @@
       <c r="D194" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="195" spans="1:6">
+      <c r="G194" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7">
       <c r="A195" t="s">
         <v>200</v>
       </c>
@@ -5211,8 +5709,11 @@
       <c r="D195" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="196" spans="1:6">
+      <c r="G195" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7">
       <c r="A196" t="s">
         <v>201</v>
       </c>
@@ -5228,8 +5729,11 @@
       <c r="F196" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="197" spans="1:6">
+      <c r="G196" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7">
       <c r="A197" t="s">
         <v>202</v>
       </c>
@@ -5248,8 +5752,11 @@
       <c r="F197" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="198" spans="1:6">
+      <c r="G197" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7">
       <c r="A198" t="s">
         <v>203</v>
       </c>
@@ -5268,8 +5775,11 @@
       <c r="F198" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="199" spans="1:6">
+      <c r="G198" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7">
       <c r="A199" t="s">
         <v>204</v>
       </c>
@@ -5288,8 +5798,11 @@
       <c r="F199" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="200" spans="1:6">
+      <c r="G199" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7">
       <c r="A200" t="s">
         <v>205</v>
       </c>
@@ -5302,8 +5815,11 @@
       <c r="D200" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="201" spans="1:6">
+      <c r="G200" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7">
       <c r="A201" t="s">
         <v>206</v>
       </c>
@@ -5314,7 +5830,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="202" spans="1:6">
+    <row r="202" spans="1:7">
       <c r="A202" t="s">
         <v>207</v>
       </c>
@@ -5325,7 +5841,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="203" spans="1:6">
+    <row r="203" spans="1:7">
       <c r="A203" t="s">
         <v>208</v>
       </c>
@@ -5336,7 +5852,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="204" spans="1:6">
+    <row r="204" spans="1:7">
       <c r="A204" t="s">
         <v>209</v>
       </c>
@@ -5349,8 +5865,11 @@
       <c r="D204" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="205" spans="1:6">
+      <c r="G204" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7">
       <c r="A205" t="s">
         <v>210</v>
       </c>
@@ -5361,7 +5880,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="206" spans="1:6">
+    <row r="206" spans="1:7">
       <c r="A206" t="s">
         <v>211</v>
       </c>
@@ -5372,7 +5891,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="207" spans="1:6">
+    <row r="207" spans="1:7">
       <c r="A207" t="s">
         <v>212</v>
       </c>
@@ -5388,8 +5907,11 @@
       <c r="E207" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="208" spans="1:6">
+      <c r="G207" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7">
       <c r="A208" t="s">
         <v>213</v>
       </c>
@@ -5403,7 +5925,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:7">
       <c r="A209" t="s">
         <v>214</v>
       </c>
@@ -5414,7 +5936,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:7">
       <c r="A210" t="s">
         <v>215</v>
       </c>
@@ -5430,8 +5952,11 @@
       <c r="E210" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="211" spans="1:5">
+      <c r="G210" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7">
       <c r="A211" t="s">
         <v>216</v>
       </c>
@@ -5444,8 +5969,11 @@
       <c r="D211" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="212" spans="1:5">
+      <c r="G211" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7">
       <c r="A212" t="s">
         <v>217</v>
       </c>
@@ -5459,7 +5987,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:7">
       <c r="A213" t="s">
         <v>218</v>
       </c>
@@ -5473,7 +6001,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:7">
       <c r="A214" t="s">
         <v>219</v>
       </c>
@@ -5486,8 +6014,11 @@
       <c r="D214" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="215" spans="1:5">
+      <c r="G214" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7">
       <c r="A215" t="s">
         <v>220</v>
       </c>
@@ -5500,8 +6031,11 @@
       <c r="D215" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="216" spans="1:5">
+      <c r="G215" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7">
       <c r="A216" t="s">
         <v>221</v>
       </c>
@@ -5515,7 +6049,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:7">
       <c r="A217" t="s">
         <v>222</v>
       </c>
@@ -5531,8 +6065,11 @@
       <c r="E217" t="s">
         <v>630</v>
       </c>
-    </row>
-    <row r="218" spans="1:5">
+      <c r="G217" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7">
       <c r="A218" t="s">
         <v>223</v>
       </c>
@@ -5548,8 +6085,11 @@
       <c r="E218" t="s">
         <v>630</v>
       </c>
-    </row>
-    <row r="219" spans="1:5">
+      <c r="G218" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7">
       <c r="A219" t="s">
         <v>224</v>
       </c>
@@ -5565,8 +6105,11 @@
       <c r="E219" t="s">
         <v>631</v>
       </c>
-    </row>
-    <row r="220" spans="1:5">
+      <c r="G219" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7">
       <c r="A220" t="s">
         <v>225</v>
       </c>
@@ -5577,7 +6120,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:7">
       <c r="A221" t="s">
         <v>226</v>
       </c>
@@ -5590,8 +6133,11 @@
       <c r="D221" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="222" spans="1:5">
+      <c r="G221" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7">
       <c r="A222" t="s">
         <v>227</v>
       </c>
@@ -5607,8 +6153,11 @@
       <c r="E222" t="s">
         <v>632</v>
       </c>
-    </row>
-    <row r="223" spans="1:5">
+      <c r="G222" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7">
       <c r="A223" t="s">
         <v>228</v>
       </c>
@@ -5621,8 +6170,11 @@
       <c r="D223" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="224" spans="1:5">
+      <c r="G223" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7">
       <c r="A224" t="s">
         <v>229</v>
       </c>
@@ -5635,8 +6187,11 @@
       <c r="D224" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="225" spans="1:6">
+      <c r="G224" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7">
       <c r="A225" t="s">
         <v>230</v>
       </c>
@@ -5652,8 +6207,11 @@
       <c r="F225" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="226" spans="1:6">
+      <c r="G225" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7">
       <c r="A226" t="s">
         <v>231</v>
       </c>
@@ -5666,8 +6224,11 @@
       <c r="D226" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="227" spans="1:6">
+      <c r="G226" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7">
       <c r="A227" t="s">
         <v>232</v>
       </c>
@@ -5678,7 +6239,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="228" spans="1:6">
+    <row r="228" spans="1:7">
       <c r="A228" t="s">
         <v>233</v>
       </c>
@@ -5691,8 +6252,11 @@
       <c r="D228" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="229" spans="1:6">
+      <c r="G228" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7">
       <c r="A229" t="s">
         <v>234</v>
       </c>
@@ -5705,8 +6269,11 @@
       <c r="D229" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="230" spans="1:6">
+      <c r="G229" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7">
       <c r="A230" t="s">
         <v>235</v>
       </c>
@@ -5719,8 +6286,11 @@
       <c r="D230" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="231" spans="1:6">
+      <c r="G230" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
       <c r="A231" t="s">
         <v>236</v>
       </c>
@@ -5733,8 +6303,11 @@
       <c r="D231" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="232" spans="1:6">
+      <c r="G231" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7">
       <c r="A232" t="s">
         <v>237</v>
       </c>
@@ -5747,8 +6320,11 @@
       <c r="D232" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="233" spans="1:6">
+      <c r="G232" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7">
       <c r="A233" t="s">
         <v>238</v>
       </c>
@@ -5761,8 +6337,11 @@
       <c r="D233" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="234" spans="1:6">
+      <c r="G233" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7">
       <c r="A234" t="s">
         <v>239</v>
       </c>
@@ -5775,8 +6354,11 @@
       <c r="D234" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="235" spans="1:6">
+      <c r="G234" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7">
       <c r="A235" t="s">
         <v>240</v>
       </c>
@@ -5789,8 +6371,11 @@
       <c r="D235" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="236" spans="1:6">
+      <c r="G235" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7">
       <c r="A236" t="s">
         <v>241</v>
       </c>
@@ -5803,8 +6388,11 @@
       <c r="D236" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="237" spans="1:6">
+      <c r="G236" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7">
       <c r="A237" t="s">
         <v>242</v>
       </c>
@@ -5817,8 +6405,11 @@
       <c r="D237" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="238" spans="1:6">
+      <c r="G237" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7">
       <c r="A238" t="s">
         <v>243</v>
       </c>
@@ -5831,8 +6422,11 @@
       <c r="D238" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="239" spans="1:6">
+      <c r="G238" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7">
       <c r="A239" t="s">
         <v>244</v>
       </c>
@@ -5845,8 +6439,11 @@
       <c r="D239" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="240" spans="1:6">
+      <c r="G239" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7">
       <c r="A240" t="s">
         <v>245</v>
       </c>
@@ -5859,8 +6456,11 @@
       <c r="D240" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="241" spans="1:4">
+      <c r="G240" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
       <c r="A241" t="s">
         <v>246</v>
       </c>
@@ -5873,8 +6473,11 @@
       <c r="D241" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="242" spans="1:4">
+      <c r="G241" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
       <c r="A242" t="s">
         <v>247</v>
       </c>
@@ -5887,8 +6490,11 @@
       <c r="D242" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="243" spans="1:4">
+      <c r="G242" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7">
       <c r="A243" t="s">
         <v>248</v>
       </c>
@@ -5901,8 +6507,11 @@
       <c r="D243" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="244" spans="1:4">
+      <c r="G243" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
       <c r="A244" t="s">
         <v>249</v>
       </c>
@@ -5915,8 +6524,11 @@
       <c r="D244" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="245" spans="1:4">
+      <c r="G244" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
       <c r="A245" t="s">
         <v>250</v>
       </c>
@@ -5929,8 +6541,11 @@
       <c r="D245" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="246" spans="1:4">
+      <c r="G245" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7">
       <c r="A246" t="s">
         <v>251</v>
       </c>
@@ -5943,8 +6558,11 @@
       <c r="D246" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="247" spans="1:4">
+      <c r="G246" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7">
       <c r="A247" t="s">
         <v>252</v>
       </c>
@@ -5957,8 +6575,11 @@
       <c r="D247" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="248" spans="1:4">
+      <c r="G247" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7">
       <c r="A248" t="s">
         <v>253</v>
       </c>
@@ -5971,8 +6592,11 @@
       <c r="D248" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="249" spans="1:4">
+      <c r="G248" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7">
       <c r="A249" t="s">
         <v>254</v>
       </c>
@@ -5985,8 +6609,11 @@
       <c r="D249" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="250" spans="1:4">
+      <c r="G249" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
       <c r="A250" t="s">
         <v>255</v>
       </c>
@@ -5999,8 +6626,11 @@
       <c r="D250" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="251" spans="1:4">
+      <c r="G250" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
       <c r="A251" t="s">
         <v>256</v>
       </c>
@@ -6013,8 +6643,11 @@
       <c r="D251" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="252" spans="1:4">
+      <c r="G251" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
       <c r="A252" t="s">
         <v>257</v>
       </c>
@@ -6027,8 +6660,11 @@
       <c r="D252" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="253" spans="1:4">
+      <c r="G252" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7">
       <c r="A253" t="s">
         <v>258</v>
       </c>
@@ -6041,8 +6677,11 @@
       <c r="D253" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="254" spans="1:4">
+      <c r="G253" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7">
       <c r="A254" t="s">
         <v>259</v>
       </c>
@@ -6055,8 +6694,11 @@
       <c r="D254" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="255" spans="1:4">
+      <c r="G254" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7">
       <c r="A255" t="s">
         <v>260</v>
       </c>
@@ -6069,8 +6711,11 @@
       <c r="D255" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="256" spans="1:4">
+      <c r="G255" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7">
       <c r="A256" t="s">
         <v>261</v>
       </c>
@@ -6083,8 +6728,11 @@
       <c r="D256" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="257" spans="1:4">
+      <c r="G256" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
       <c r="A257" t="s">
         <v>262</v>
       </c>
@@ -6097,8 +6745,11 @@
       <c r="D257" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="258" spans="1:4">
+      <c r="G257" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
       <c r="A258" t="s">
         <v>263</v>
       </c>
@@ -6111,8 +6762,11 @@
       <c r="D258" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="259" spans="1:4">
+      <c r="G258" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
       <c r="A259" t="s">
         <v>264</v>
       </c>
@@ -6125,8 +6779,11 @@
       <c r="D259" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="260" spans="1:4">
+      <c r="G259" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
       <c r="A260" t="s">
         <v>265</v>
       </c>
@@ -6139,8 +6796,11 @@
       <c r="D260" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="261" spans="1:4">
+      <c r="G260" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
       <c r="A261" t="s">
         <v>266</v>
       </c>
@@ -6153,8 +6813,11 @@
       <c r="D261" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="262" spans="1:4">
+      <c r="G261" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
       <c r="A262" t="s">
         <v>267</v>
       </c>
@@ -6167,8 +6830,11 @@
       <c r="D262" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="263" spans="1:4">
+      <c r="G262" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7">
       <c r="A263" t="s">
         <v>268</v>
       </c>
@@ -6181,8 +6847,11 @@
       <c r="D263" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="264" spans="1:4">
+      <c r="G263" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
       <c r="A264" t="s">
         <v>269</v>
       </c>
@@ -6195,8 +6864,11 @@
       <c r="D264" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="265" spans="1:4">
+      <c r="G264" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
       <c r="A265" t="s">
         <v>270</v>
       </c>
@@ -6209,8 +6881,11 @@
       <c r="D265" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="266" spans="1:4">
+      <c r="G265" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
       <c r="A266" t="s">
         <v>271</v>
       </c>
@@ -6223,8 +6898,11 @@
       <c r="D266" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="267" spans="1:4">
+      <c r="G266" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
       <c r="A267" t="s">
         <v>272</v>
       </c>
@@ -6237,8 +6915,11 @@
       <c r="D267" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="268" spans="1:4">
+      <c r="G267" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7">
       <c r="A268" t="s">
         <v>273</v>
       </c>
@@ -6251,8 +6932,11 @@
       <c r="D268" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="269" spans="1:4">
+      <c r="G268" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
       <c r="A269" t="s">
         <v>274</v>
       </c>
@@ -6265,8 +6949,11 @@
       <c r="D269" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="270" spans="1:4">
+      <c r="G269" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
       <c r="A270" t="s">
         <v>275</v>
       </c>
@@ -6279,8 +6966,11 @@
       <c r="D270" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="271" spans="1:4">
+      <c r="G270" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7">
       <c r="A271" t="s">
         <v>276</v>
       </c>
@@ -6293,8 +6983,11 @@
       <c r="D271" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="272" spans="1:4">
+      <c r="G271" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
       <c r="A272" t="s">
         <v>277</v>
       </c>
@@ -6307,8 +7000,11 @@
       <c r="D272" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="273" spans="1:4">
+      <c r="G272" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
       <c r="A273" t="s">
         <v>278</v>
       </c>
@@ -6321,8 +7017,11 @@
       <c r="D273" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="274" spans="1:4">
+      <c r="G273" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
       <c r="A274" t="s">
         <v>279</v>
       </c>
@@ -6335,8 +7034,11 @@
       <c r="D274" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="275" spans="1:4">
+      <c r="G274" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
       <c r="A275" t="s">
         <v>280</v>
       </c>
@@ -6349,8 +7051,11 @@
       <c r="D275" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="276" spans="1:4">
+      <c r="G275" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
       <c r="A276" t="s">
         <v>281</v>
       </c>
@@ -6363,8 +7068,11 @@
       <c r="D276" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="277" spans="1:4">
+      <c r="G276" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
       <c r="A277" t="s">
         <v>282</v>
       </c>
@@ -6377,8 +7085,11 @@
       <c r="D277" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="278" spans="1:4">
+      <c r="G277" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
       <c r="A278" t="s">
         <v>283</v>
       </c>
@@ -6391,8 +7102,11 @@
       <c r="D278" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="279" spans="1:4">
+      <c r="G278" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
       <c r="A279" t="s">
         <v>284</v>
       </c>
@@ -6405,8 +7119,11 @@
       <c r="D279" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="280" spans="1:4">
+      <c r="G279" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
       <c r="A280" t="s">
         <v>285</v>
       </c>
@@ -6419,8 +7136,11 @@
       <c r="D280" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="281" spans="1:4">
+      <c r="G280" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
       <c r="A281" t="s">
         <v>286</v>
       </c>
@@ -6433,8 +7153,11 @@
       <c r="D281" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="282" spans="1:4">
+      <c r="G281" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
       <c r="A282" t="s">
         <v>287</v>
       </c>
@@ -6447,8 +7170,11 @@
       <c r="D282" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="283" spans="1:4">
+      <c r="G282" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
       <c r="A283" t="s">
         <v>288</v>
       </c>
@@ -6460,6 +7186,9 @@
       </c>
       <c r="D283" t="s">
         <v>566</v>
+      </c>
+      <c r="G283" t="s">
+        <v>653</v>
       </c>
     </row>
   </sheetData>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="656">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -883,6 +883,9 @@
     <t>Kolbe House</t>
   </si>
   <si>
+    <t>Imrah Galant (Cape Town Science Centre)</t>
+  </si>
+  <si>
     <t>info@ctsc.org.za</t>
   </si>
   <si>
@@ -1595,6 +1598,9 @@
   </si>
   <si>
     <t>kolbe.house@telkomsa.net</t>
+  </si>
+  <si>
+    <t>Imrah@ctsc.org.za</t>
   </si>
   <si>
     <t>Museums &amp; Heritage</t>
@@ -2320,7 +2326,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G283"/>
+  <dimension ref="A1:G284"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2351,22 +2357,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="G2" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2374,22 +2380,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D3" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E3" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F3" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="G3" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2397,22 +2403,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C4" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D4" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E4" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F4" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="G4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2420,22 +2426,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C5" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D5" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E5" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F5" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="G5" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2443,22 +2449,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C6" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D6" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E6" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F6" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="G6" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2466,22 +2472,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C7" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D7" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E7" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F7" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="G7" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2489,22 +2495,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C8" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D8" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E8" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F8" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="G8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2512,22 +2518,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C9" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D9" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E9" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F9" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="G9" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2535,22 +2541,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C10" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D10" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E10" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F10" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="G10" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2558,22 +2564,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C11" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D11" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E11" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F11" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="G11" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2581,22 +2587,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C12" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D12" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E12" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F12" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="G12" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2604,22 +2610,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C13" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D13" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E13" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F13" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="G13" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2627,22 +2633,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C14" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D14" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E14" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="G14" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2650,22 +2656,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C15" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D15" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E15" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="G15" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2673,16 +2679,16 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C16" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D16" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G16" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2690,16 +2696,16 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C17" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D17" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G17" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2707,16 +2713,16 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C18" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D18" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G18" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2724,16 +2730,16 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C19" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D19" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G19" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2741,16 +2747,16 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C20" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D20" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G20" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2758,16 +2764,16 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C21" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D21" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G21" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2775,16 +2781,16 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C22" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D22" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G22" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2792,16 +2798,16 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C23" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D23" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G23" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2809,16 +2815,16 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C24" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D24" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G24" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2826,16 +2832,16 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C25" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D25" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G25" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2843,16 +2849,16 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C26" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D26" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G26" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2860,16 +2866,16 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C27" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D27" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G27" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2877,16 +2883,16 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C28" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D28" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G28" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2894,16 +2900,16 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C29" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D29" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G29" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2911,16 +2917,16 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C30" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D30" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G30" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2928,16 +2934,16 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C31" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D31" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G31" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2945,16 +2951,16 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C32" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D32" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G32" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2962,16 +2968,16 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C33" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D33" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G33" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2979,16 +2985,16 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C34" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D34" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G34" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2996,16 +3002,16 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C35" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D35" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G35" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3013,16 +3019,16 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C36" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D36" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G36" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -3030,16 +3036,16 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C37" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D37" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G37" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -3047,16 +3053,16 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C38" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D38" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G38" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -3064,16 +3070,16 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C39" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D39" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G39" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3081,16 +3087,16 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C40" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D40" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G40" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -3098,16 +3104,16 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C41" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D41" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G41" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3115,16 +3121,16 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C42" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D42" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G42" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3132,16 +3138,16 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C43" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D43" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G43" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3149,16 +3155,16 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C44" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D44" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G44" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3166,16 +3172,16 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C45" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D45" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G45" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3183,16 +3189,16 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C46" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D46" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G46" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3200,16 +3206,16 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C47" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D47" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G47" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3217,16 +3223,16 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C48" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D48" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G48" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -3234,16 +3240,16 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C49" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D49" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G49" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -3251,16 +3257,16 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C50" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D50" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G50" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -3268,16 +3274,16 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C51" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D51" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G51" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -3285,16 +3291,16 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C52" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D52" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G52" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -3302,16 +3308,16 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C53" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D53" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G53" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3319,16 +3325,16 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C54" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D54" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G54" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -3336,16 +3342,16 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C55" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D55" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G55" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3353,16 +3359,16 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C56" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D56" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G56" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3370,16 +3376,16 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C57" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D57" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G57" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3387,16 +3393,16 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C58" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D58" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G58" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3404,16 +3410,16 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C59" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D59" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G59" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3421,16 +3427,16 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C60" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D60" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G60" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3438,16 +3444,16 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C61" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D61" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G61" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3455,16 +3461,16 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C62" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D62" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G62" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3472,16 +3478,16 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C63" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D63" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G63" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3489,16 +3495,16 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C64" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D64" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G64" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3506,16 +3512,16 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C65" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D65" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G65" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3523,16 +3529,16 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C66" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D66" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G66" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3540,16 +3546,16 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C67" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D67" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G67" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3557,16 +3563,16 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C68" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D68" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G68" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3574,16 +3580,16 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C69" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D69" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G69" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3591,16 +3597,16 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C70" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D70" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G70" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3608,16 +3614,16 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C71" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D71" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G71" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3625,16 +3631,16 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C72" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D72" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G72" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3642,16 +3648,16 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C73" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D73" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G73" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3659,16 +3665,16 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C74" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D74" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G74" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3676,16 +3682,16 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C75" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D75" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G75" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3693,16 +3699,16 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C76" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D76" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G76" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3710,16 +3716,16 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C77" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D77" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G77" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3727,16 +3733,16 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C78" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D78" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G78" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3744,16 +3750,16 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C79" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D79" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G79" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3761,16 +3767,16 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C80" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D80" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G80" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3778,16 +3784,16 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C81" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D81" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G81" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3795,16 +3801,16 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C82" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D82" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G82" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3812,16 +3818,16 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C83" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D83" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G83" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3829,16 +3835,16 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C84" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D84" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G84" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3846,16 +3852,16 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C85" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D85" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G85" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3863,16 +3869,16 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C86" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D86" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G86" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3880,16 +3886,16 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C87" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D87" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G87" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3897,16 +3903,16 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C88" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D88" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G88" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3914,16 +3920,16 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C89" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D89" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G89" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3931,16 +3937,16 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C90" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D90" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G90" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3948,16 +3954,16 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C91" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D91" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G91" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3965,16 +3971,16 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C92" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D92" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G92" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3982,16 +3988,16 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C93" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D93" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G93" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3999,16 +4005,16 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C94" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D94" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G94" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -4016,16 +4022,16 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C95" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D95" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G95" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -4033,16 +4039,16 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C96" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D96" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G96" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4050,16 +4056,16 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C97" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D97" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G97" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4067,16 +4073,16 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C98" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D98" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G98" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4084,16 +4090,16 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C99" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D99" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G99" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4101,16 +4107,16 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C100" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D100" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G100" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4118,16 +4124,16 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C101" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D101" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G101" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4135,16 +4141,16 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C102" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D102" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G102" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4152,16 +4158,16 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C103" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D103" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G103" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4169,16 +4175,16 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C104" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D104" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G104" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4186,16 +4192,16 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C105" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D105" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G105" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4203,16 +4209,16 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C106" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D106" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G106" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4220,16 +4226,16 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C107" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D107" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G107" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4237,16 +4243,16 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C108" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D108" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G108" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4254,16 +4260,16 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C109" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D109" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G109" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4271,16 +4277,16 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C110" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D110" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G110" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4288,16 +4294,16 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C111" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D111" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G111" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4305,16 +4311,16 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C112" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D112" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G112" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4322,16 +4328,16 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C113" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D113" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G113" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4339,16 +4345,16 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C114" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D114" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G114" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4356,16 +4362,16 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C115" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D115" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G115" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4373,16 +4379,16 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C116" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D116" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G116" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4390,16 +4396,16 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C117" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D117" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G117" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4407,16 +4413,16 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C118" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D118" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G118" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4424,22 +4430,22 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C119" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D119" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E119" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="F119" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="G119" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4447,19 +4453,19 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C120" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D120" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E120" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="G120" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4467,16 +4473,16 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C121" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D121" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G121" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4484,16 +4490,16 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C122" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D122" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="G122" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4501,22 +4507,22 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C123" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D123" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E123" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="F123" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="G123" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4524,16 +4530,16 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C124" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D124" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G124" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4541,16 +4547,16 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C125" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D125" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G125" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4558,16 +4564,16 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C126" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D126" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G126" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4575,16 +4581,16 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C127" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D127" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G127" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4592,19 +4598,19 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C128" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D128" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E128" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="G128" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4612,22 +4618,22 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C129" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D129" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E129" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F129" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="G129" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4635,16 +4641,16 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C130" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D130" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G130" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4652,13 +4658,13 @@
         <v>136</v>
       </c>
       <c r="C131" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D131" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E131" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4666,19 +4672,19 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C132" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D132" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E132" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G132" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4686,19 +4692,19 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C133" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D133" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E133" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="G133" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4706,10 +4712,10 @@
         <v>139</v>
       </c>
       <c r="C134" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D134" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4717,10 +4723,10 @@
         <v>140</v>
       </c>
       <c r="C135" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D135" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4728,16 +4734,16 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C136" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D136" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G136" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4745,16 +4751,16 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C137" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D137" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="G137" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4762,10 +4768,10 @@
         <v>143</v>
       </c>
       <c r="C138" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D138" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4773,10 +4779,10 @@
         <v>144</v>
       </c>
       <c r="C139" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D139" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4784,10 +4790,10 @@
         <v>145</v>
       </c>
       <c r="C140" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D140" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4795,16 +4801,16 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C141" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D141" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G141" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4812,22 +4818,22 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C142" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D142" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E142" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="F142" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="G142" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4835,16 +4841,16 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C143" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D143" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="G143" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4852,13 +4858,13 @@
         <v>149</v>
       </c>
       <c r="C144" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D144" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E144" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4866,10 +4872,10 @@
         <v>150</v>
       </c>
       <c r="C145" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D145" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4877,19 +4883,19 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C146" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D146" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="F146" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="G146" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -4897,22 +4903,22 @@
         <v>152</v>
       </c>
       <c r="B147" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C147" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D147" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E147" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="F147" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="G147" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -4920,19 +4926,19 @@
         <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C148" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D148" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E148" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="G148" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -4940,19 +4946,19 @@
         <v>154</v>
       </c>
       <c r="B149" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C149" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D149" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E149" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G149" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -4960,19 +4966,19 @@
         <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C150" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D150" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E150" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="G150" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -4980,19 +4986,19 @@
         <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C151" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D151" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E151" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G151" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5000,19 +5006,19 @@
         <v>157</v>
       </c>
       <c r="B152" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C152" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D152" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E152" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="G152" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5020,10 +5026,10 @@
         <v>158</v>
       </c>
       <c r="C153" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D153" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5031,19 +5037,19 @@
         <v>159</v>
       </c>
       <c r="B154" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C154" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D154" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E154" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G154" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5051,16 +5057,16 @@
         <v>160</v>
       </c>
       <c r="B155" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C155" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D155" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G155" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5068,16 +5074,16 @@
         <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C156" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D156" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G156" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5085,22 +5091,22 @@
         <v>162</v>
       </c>
       <c r="B157" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C157" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D157" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E157" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="F157" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="G157" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5108,19 +5114,19 @@
         <v>163</v>
       </c>
       <c r="B158" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C158" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D158" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E158" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="G158" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5128,19 +5134,19 @@
         <v>164</v>
       </c>
       <c r="B159" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C159" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D159" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E159" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="G159" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5148,19 +5154,19 @@
         <v>165</v>
       </c>
       <c r="B160" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C160" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D160" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E160" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G160" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5168,19 +5174,19 @@
         <v>166</v>
       </c>
       <c r="B161" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C161" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D161" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E161" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="G161" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5188,16 +5194,16 @@
         <v>167</v>
       </c>
       <c r="B162" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C162" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D162" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G162" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5205,19 +5211,19 @@
         <v>168</v>
       </c>
       <c r="B163" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C163" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D163" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E163" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="G163" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5225,19 +5231,19 @@
         <v>169</v>
       </c>
       <c r="B164" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C164" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D164" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E164" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="G164" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5245,13 +5251,13 @@
         <v>170</v>
       </c>
       <c r="C165" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D165" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E165" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5259,19 +5265,19 @@
         <v>171</v>
       </c>
       <c r="B166" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C166" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D166" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E166" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="G166" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5279,19 +5285,19 @@
         <v>172</v>
       </c>
       <c r="B167" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C167" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D167" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E167" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="G167" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5299,19 +5305,19 @@
         <v>173</v>
       </c>
       <c r="B168" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C168" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D168" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E168" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="G168" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5319,19 +5325,19 @@
         <v>174</v>
       </c>
       <c r="B169" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C169" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D169" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E169" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="G169" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5339,13 +5345,13 @@
         <v>175</v>
       </c>
       <c r="C170" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D170" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E170" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5353,13 +5359,13 @@
         <v>176</v>
       </c>
       <c r="C171" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D171" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E171" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5367,13 +5373,13 @@
         <v>177</v>
       </c>
       <c r="C172" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D172" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E172" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5381,16 +5387,16 @@
         <v>178</v>
       </c>
       <c r="B173" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C173" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D173" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G173" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5398,19 +5404,19 @@
         <v>179</v>
       </c>
       <c r="B174" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C174" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D174" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="F174" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="G174" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5418,19 +5424,19 @@
         <v>180</v>
       </c>
       <c r="B175" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C175" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D175" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="F175" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="G175" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5438,10 +5444,10 @@
         <v>181</v>
       </c>
       <c r="C176" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D176" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5449,10 +5455,10 @@
         <v>182</v>
       </c>
       <c r="C177" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D177" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5460,10 +5466,10 @@
         <v>183</v>
       </c>
       <c r="C178" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D178" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5471,22 +5477,22 @@
         <v>184</v>
       </c>
       <c r="B179" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C179" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D179" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="E179" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="F179" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="G179" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5494,10 +5500,10 @@
         <v>185</v>
       </c>
       <c r="C180" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D180" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5505,10 +5511,10 @@
         <v>186</v>
       </c>
       <c r="C181" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D181" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5516,19 +5522,19 @@
         <v>187</v>
       </c>
       <c r="B182" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C182" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D182" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E182" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="G182" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5536,19 +5542,19 @@
         <v>188</v>
       </c>
       <c r="B183" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C183" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D183" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="F183" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="G183" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5556,10 +5562,10 @@
         <v>189</v>
       </c>
       <c r="C184" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D184" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5567,13 +5573,13 @@
         <v>190</v>
       </c>
       <c r="C185" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D185" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="F185" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5581,13 +5587,13 @@
         <v>191</v>
       </c>
       <c r="C186" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D186" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E186" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5595,13 +5601,13 @@
         <v>192</v>
       </c>
       <c r="C187" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D187" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E187" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5609,13 +5615,13 @@
         <v>193</v>
       </c>
       <c r="C188" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D188" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E188" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5623,13 +5629,13 @@
         <v>194</v>
       </c>
       <c r="C189" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D189" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E189" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5637,13 +5643,13 @@
         <v>195</v>
       </c>
       <c r="C190" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D190" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E190" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5651,10 +5657,10 @@
         <v>196</v>
       </c>
       <c r="C191" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D191" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -5662,10 +5668,10 @@
         <v>197</v>
       </c>
       <c r="C192" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D192" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -5673,10 +5679,10 @@
         <v>198</v>
       </c>
       <c r="C193" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D193" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -5684,16 +5690,16 @@
         <v>199</v>
       </c>
       <c r="B194" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C194" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D194" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="G194" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -5701,16 +5707,16 @@
         <v>200</v>
       </c>
       <c r="B195" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C195" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D195" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="G195" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -5718,19 +5724,19 @@
         <v>201</v>
       </c>
       <c r="B196" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C196" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D196" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="F196" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="G196" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -5738,22 +5744,22 @@
         <v>202</v>
       </c>
       <c r="B197" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C197" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D197" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E197" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F197" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="G197" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -5761,22 +5767,22 @@
         <v>203</v>
       </c>
       <c r="B198" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C198" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D198" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E198" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="F198" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="G198" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -5784,22 +5790,22 @@
         <v>204</v>
       </c>
       <c r="B199" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C199" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D199" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E199" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F199" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="G199" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -5807,16 +5813,16 @@
         <v>205</v>
       </c>
       <c r="B200" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C200" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D200" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G200" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -5824,10 +5830,10 @@
         <v>206</v>
       </c>
       <c r="C201" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D201" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -5835,10 +5841,10 @@
         <v>207</v>
       </c>
       <c r="C202" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D202" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -5846,10 +5852,10 @@
         <v>208</v>
       </c>
       <c r="C203" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D203" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -5857,16 +5863,16 @@
         <v>209</v>
       </c>
       <c r="B204" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C204" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D204" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G204" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -5874,10 +5880,10 @@
         <v>210</v>
       </c>
       <c r="C205" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D205" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -5885,10 +5891,10 @@
         <v>211</v>
       </c>
       <c r="C206" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D206" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -5896,19 +5902,19 @@
         <v>212</v>
       </c>
       <c r="B207" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C207" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D207" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E207" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="G207" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -5916,13 +5922,13 @@
         <v>213</v>
       </c>
       <c r="C208" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D208" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E208" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -5930,10 +5936,10 @@
         <v>214</v>
       </c>
       <c r="C209" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D209" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -5941,19 +5947,19 @@
         <v>215</v>
       </c>
       <c r="B210" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C210" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D210" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E210" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="G210" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -5961,16 +5967,16 @@
         <v>216</v>
       </c>
       <c r="B211" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C211" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D211" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G211" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -5978,13 +5984,13 @@
         <v>217</v>
       </c>
       <c r="C212" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D212" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E212" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -5992,13 +5998,13 @@
         <v>218</v>
       </c>
       <c r="C213" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D213" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E213" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6006,16 +6012,16 @@
         <v>219</v>
       </c>
       <c r="B214" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C214" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D214" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G214" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6023,16 +6029,16 @@
         <v>220</v>
       </c>
       <c r="B215" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C215" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D215" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G215" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6040,13 +6046,13 @@
         <v>221</v>
       </c>
       <c r="C216" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D216" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E216" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6054,19 +6060,19 @@
         <v>222</v>
       </c>
       <c r="B217" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C217" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D217" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E217" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="G217" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6074,19 +6080,19 @@
         <v>223</v>
       </c>
       <c r="B218" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C218" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D218" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E218" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="G218" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6094,19 +6100,19 @@
         <v>224</v>
       </c>
       <c r="B219" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C219" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D219" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E219" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="G219" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6114,10 +6120,10 @@
         <v>225</v>
       </c>
       <c r="C220" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D220" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6125,16 +6131,16 @@
         <v>226</v>
       </c>
       <c r="B221" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C221" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D221" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G221" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6142,19 +6148,19 @@
         <v>227</v>
       </c>
       <c r="B222" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C222" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D222" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E222" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="G222" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6162,16 +6168,16 @@
         <v>228</v>
       </c>
       <c r="B223" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C223" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D223" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G223" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6179,16 +6185,16 @@
         <v>229</v>
       </c>
       <c r="B224" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C224" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D224" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="G224" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6196,19 +6202,19 @@
         <v>230</v>
       </c>
       <c r="B225" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C225" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D225" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="F225" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="G225" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6216,16 +6222,16 @@
         <v>231</v>
       </c>
       <c r="B226" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C226" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D226" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G226" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6233,10 +6239,10 @@
         <v>232</v>
       </c>
       <c r="C227" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D227" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6244,16 +6250,16 @@
         <v>233</v>
       </c>
       <c r="B228" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C228" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D228" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G228" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6261,16 +6267,16 @@
         <v>234</v>
       </c>
       <c r="B229" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C229" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D229" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G229" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6278,16 +6284,16 @@
         <v>235</v>
       </c>
       <c r="B230" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C230" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D230" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G230" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6295,16 +6301,16 @@
         <v>236</v>
       </c>
       <c r="B231" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C231" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D231" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G231" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6312,16 +6318,16 @@
         <v>237</v>
       </c>
       <c r="B232" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C232" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D232" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G232" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6329,16 +6335,16 @@
         <v>238</v>
       </c>
       <c r="B233" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C233" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D233" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G233" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6346,16 +6352,16 @@
         <v>239</v>
       </c>
       <c r="B234" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C234" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D234" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G234" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -6363,16 +6369,16 @@
         <v>240</v>
       </c>
       <c r="B235" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C235" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D235" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G235" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -6380,16 +6386,16 @@
         <v>241</v>
       </c>
       <c r="B236" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C236" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D236" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G236" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -6397,16 +6403,16 @@
         <v>242</v>
       </c>
       <c r="B237" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C237" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D237" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G237" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -6414,16 +6420,16 @@
         <v>243</v>
       </c>
       <c r="B238" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C238" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D238" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G238" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -6431,16 +6437,16 @@
         <v>244</v>
       </c>
       <c r="B239" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C239" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D239" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G239" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -6448,16 +6454,16 @@
         <v>245</v>
       </c>
       <c r="B240" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C240" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D240" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G240" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -6465,16 +6471,16 @@
         <v>246</v>
       </c>
       <c r="B241" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C241" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D241" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G241" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -6482,16 +6488,16 @@
         <v>247</v>
       </c>
       <c r="B242" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C242" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D242" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G242" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -6499,16 +6505,16 @@
         <v>248</v>
       </c>
       <c r="B243" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C243" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D243" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G243" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -6516,16 +6522,16 @@
         <v>249</v>
       </c>
       <c r="B244" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C244" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D244" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G244" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -6533,16 +6539,16 @@
         <v>250</v>
       </c>
       <c r="B245" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C245" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D245" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G245" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -6550,16 +6556,16 @@
         <v>251</v>
       </c>
       <c r="B246" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C246" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D246" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G246" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -6567,16 +6573,16 @@
         <v>252</v>
       </c>
       <c r="B247" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C247" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D247" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G247" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -6584,16 +6590,16 @@
         <v>253</v>
       </c>
       <c r="B248" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C248" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D248" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G248" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -6601,16 +6607,16 @@
         <v>254</v>
       </c>
       <c r="B249" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C249" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D249" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G249" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -6618,16 +6624,16 @@
         <v>255</v>
       </c>
       <c r="B250" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C250" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D250" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G250" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -6635,16 +6641,16 @@
         <v>256</v>
       </c>
       <c r="B251" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C251" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D251" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G251" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -6652,16 +6658,16 @@
         <v>257</v>
       </c>
       <c r="B252" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C252" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D252" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G252" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -6669,16 +6675,16 @@
         <v>258</v>
       </c>
       <c r="B253" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C253" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D253" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G253" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -6686,16 +6692,16 @@
         <v>259</v>
       </c>
       <c r="B254" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C254" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D254" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G254" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -6703,16 +6709,16 @@
         <v>260</v>
       </c>
       <c r="B255" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C255" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D255" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G255" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -6720,16 +6726,16 @@
         <v>261</v>
       </c>
       <c r="B256" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C256" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D256" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G256" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -6737,16 +6743,16 @@
         <v>262</v>
       </c>
       <c r="B257" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C257" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D257" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G257" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -6754,16 +6760,16 @@
         <v>263</v>
       </c>
       <c r="B258" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C258" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D258" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G258" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -6771,16 +6777,16 @@
         <v>264</v>
       </c>
       <c r="B259" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C259" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D259" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G259" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -6788,16 +6794,16 @@
         <v>265</v>
       </c>
       <c r="B260" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C260" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D260" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G260" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -6805,16 +6811,16 @@
         <v>266</v>
       </c>
       <c r="B261" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C261" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D261" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G261" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -6822,16 +6828,16 @@
         <v>267</v>
       </c>
       <c r="B262" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C262" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D262" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G262" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -6839,16 +6845,16 @@
         <v>268</v>
       </c>
       <c r="B263" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C263" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D263" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G263" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -6856,16 +6862,16 @@
         <v>269</v>
       </c>
       <c r="B264" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C264" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D264" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G264" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -6873,16 +6879,16 @@
         <v>270</v>
       </c>
       <c r="B265" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C265" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D265" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G265" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -6890,16 +6896,16 @@
         <v>271</v>
       </c>
       <c r="B266" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C266" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D266" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G266" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -6907,16 +6913,16 @@
         <v>272</v>
       </c>
       <c r="B267" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C267" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D267" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G267" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -6924,16 +6930,16 @@
         <v>273</v>
       </c>
       <c r="B268" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C268" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D268" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G268" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -6941,16 +6947,16 @@
         <v>274</v>
       </c>
       <c r="B269" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C269" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D269" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G269" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -6958,16 +6964,16 @@
         <v>275</v>
       </c>
       <c r="B270" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C270" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D270" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G270" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -6975,16 +6981,16 @@
         <v>276</v>
       </c>
       <c r="B271" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C271" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D271" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G271" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -6992,16 +6998,16 @@
         <v>277</v>
       </c>
       <c r="B272" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C272" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D272" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G272" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7009,16 +7015,16 @@
         <v>278</v>
       </c>
       <c r="B273" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C273" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D273" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G273" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -7026,16 +7032,16 @@
         <v>279</v>
       </c>
       <c r="B274" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C274" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D274" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G274" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -7043,16 +7049,16 @@
         <v>280</v>
       </c>
       <c r="B275" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C275" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D275" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G275" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -7060,16 +7066,16 @@
         <v>281</v>
       </c>
       <c r="B276" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C276" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D276" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G276" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -7077,16 +7083,16 @@
         <v>282</v>
       </c>
       <c r="B277" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C277" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D277" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G277" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -7094,16 +7100,16 @@
         <v>283</v>
       </c>
       <c r="B278" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C278" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D278" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G278" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7111,16 +7117,16 @@
         <v>284</v>
       </c>
       <c r="B279" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C279" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D279" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G279" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7128,16 +7134,16 @@
         <v>285</v>
       </c>
       <c r="B280" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C280" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D280" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="G280" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -7145,16 +7151,16 @@
         <v>286</v>
       </c>
       <c r="B281" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C281" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D281" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="G281" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7162,16 +7168,16 @@
         <v>287</v>
       </c>
       <c r="B282" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C282" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D282" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="G282" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -7179,16 +7185,36 @@
         <v>288</v>
       </c>
       <c r="B283" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C283" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D283" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="G283" t="s">
-        <v>653</v>
+        <v>655</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284" t="s">
+        <v>289</v>
+      </c>
+      <c r="B284" t="s">
+        <v>528</v>
+      </c>
+      <c r="C284" t="s">
+        <v>529</v>
+      </c>
+      <c r="D284" t="s">
+        <v>554</v>
+      </c>
+      <c r="F284" t="s">
+        <v>635</v>
+      </c>
+      <c r="G284" t="s">
+        <v>655</v>
       </c>
     </row>
   </sheetData>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="703">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -886,6 +886,75 @@
     <t>Imrah Galant (Cape Town Science Centre)</t>
   </si>
   <si>
+    <t>Environmental Monitoring Group</t>
+  </si>
+  <si>
+    <t>Book Dash</t>
+  </si>
+  <si>
+    <t>arepp:Theatre for Life</t>
+  </si>
+  <si>
+    <t>Mowbray Rosebank CAN</t>
+  </si>
+  <si>
+    <t>Little Mowbray &amp; Rosebank Improvement District</t>
+  </si>
+  <si>
+    <t>Mowbray Maternity Hospital</t>
+  </si>
+  <si>
+    <t>Integration House Wellness Centre</t>
+  </si>
+  <si>
+    <t>Mowbray Presbyterian Church</t>
+  </si>
+  <si>
+    <t>Mowbray Library</t>
+  </si>
+  <si>
+    <t>Friends of Mostert's Mill</t>
+  </si>
+  <si>
+    <t>Rondebosch Vuleka Trust</t>
+  </si>
+  <si>
+    <t>Friends of Rondebosch Common</t>
+  </si>
+  <si>
+    <t>Rondebosch Community Improvement District</t>
+  </si>
+  <si>
+    <t>Foundation for Alcohol Related Research (FARR)</t>
+  </si>
+  <si>
+    <t>Outliers</t>
+  </si>
+  <si>
+    <t>St. Joseph's Adult Education Programme</t>
+  </si>
+  <si>
+    <t>Paedspal</t>
+  </si>
+  <si>
+    <t>Woodside</t>
+  </si>
+  <si>
+    <t>Beautiful Life Community Development</t>
+  </si>
+  <si>
+    <t>Goedgedacht Trust</t>
+  </si>
+  <si>
+    <t>Centre for Early Childhood Development</t>
+  </si>
+  <si>
+    <t>Westerford High School</t>
+  </si>
+  <si>
+    <t>Garlandale - Rondebosch East Residents' Association</t>
+  </si>
+  <si>
     <t>info@ctsc.org.za</t>
   </si>
   <si>
@@ -1601,6 +1670,78 @@
   </si>
   <si>
     <t>Imrah@ctsc.org.za</t>
+  </si>
+  <si>
+    <t>stephen@emg.org.za</t>
+  </si>
+  <si>
+    <t>team@bookdash.org</t>
+  </si>
+  <si>
+    <t>capeadmin@nullarepp.org.za</t>
+  </si>
+  <si>
+    <t>mowbrayrosebankcan@gmail.com</t>
+  </si>
+  <si>
+    <t>info@lmrid.capetown</t>
+  </si>
+  <si>
+    <t>Janine.Joemat@westerncape.gov.za</t>
+  </si>
+  <si>
+    <t>jacquikoep@gmail.com</t>
+  </si>
+  <si>
+    <t>mowbray.presby@telkomsa.net</t>
+  </si>
+  <si>
+    <t>mowbray.library@capetown.gov.za</t>
+  </si>
+  <si>
+    <t>pilotjhammer@gmail.com</t>
+  </si>
+  <si>
+    <t>frances@communitree.in</t>
+  </si>
+  <si>
+    <t>info@rondeboschvulekatrust.co.za</t>
+  </si>
+  <si>
+    <t>FriendsofRondeboschCommon@gmail.com</t>
+  </si>
+  <si>
+    <t>rcidoffices@gmail.com</t>
+  </si>
+  <si>
+    <t>lo@farrsa.org.za</t>
+  </si>
+  <si>
+    <t>info@outliers.org.za</t>
+  </si>
+  <si>
+    <t>kajl@global.co.za</t>
+  </si>
+  <si>
+    <t>info@paedspal.org.za</t>
+  </si>
+  <si>
+    <t>fundraiser@woodside.org.za</t>
+  </si>
+  <si>
+    <t>info@beautifullifecommunity.co.za</t>
+  </si>
+  <si>
+    <t>info@goedgedacht.org</t>
+  </si>
+  <si>
+    <t>cecd@iafrica.com</t>
+  </si>
+  <si>
+    <t>admin@westerford.co.za</t>
+  </si>
+  <si>
+    <t>roekeya@damonabadia.co.za</t>
   </si>
   <si>
     <t>Museums &amp; Heritage</t>
@@ -2326,7 +2467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G284"/>
+  <dimension ref="A1:G308"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2357,22 +2498,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="C2" t="s">
-        <v>529</v>
+        <v>576</v>
       </c>
       <c r="D2" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E2" t="s">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="F2" t="s">
-        <v>635</v>
+        <v>682</v>
       </c>
       <c r="G2" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2380,22 +2521,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="C3" t="s">
-        <v>529</v>
+        <v>576</v>
       </c>
       <c r="D3" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E3" t="s">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="F3" t="s">
-        <v>635</v>
+        <v>682</v>
       </c>
       <c r="G3" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2403,22 +2544,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="C4" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D4" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E4" t="s">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="F4" t="s">
-        <v>635</v>
+        <v>682</v>
       </c>
       <c r="G4" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2426,22 +2567,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="C5" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D5" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E5" t="s">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="F5" t="s">
-        <v>635</v>
+        <v>682</v>
       </c>
       <c r="G5" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2449,22 +2590,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="C6" t="s">
-        <v>529</v>
+        <v>576</v>
       </c>
       <c r="D6" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E6" t="s">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="F6" t="s">
-        <v>635</v>
+        <v>682</v>
       </c>
       <c r="G6" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2472,22 +2613,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="C7" t="s">
-        <v>529</v>
+        <v>576</v>
       </c>
       <c r="D7" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E7" t="s">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="F7" t="s">
-        <v>635</v>
+        <v>682</v>
       </c>
       <c r="G7" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2495,22 +2636,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="C8" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D8" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E8" t="s">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="F8" t="s">
-        <v>635</v>
+        <v>682</v>
       </c>
       <c r="G8" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2518,22 +2659,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="C9" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D9" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E9" t="s">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="F9" t="s">
-        <v>635</v>
+        <v>682</v>
       </c>
       <c r="G9" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2541,22 +2682,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="C10" t="s">
-        <v>531</v>
+        <v>578</v>
       </c>
       <c r="D10" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E10" t="s">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="F10" t="s">
-        <v>635</v>
+        <v>682</v>
       </c>
       <c r="G10" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2564,22 +2705,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="C11" t="s">
-        <v>531</v>
+        <v>578</v>
       </c>
       <c r="D11" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E11" t="s">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="F11" t="s">
-        <v>635</v>
+        <v>682</v>
       </c>
       <c r="G11" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2587,22 +2728,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="C12" t="s">
-        <v>532</v>
+        <v>579</v>
       </c>
       <c r="D12" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E12" t="s">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="F12" t="s">
-        <v>635</v>
+        <v>682</v>
       </c>
       <c r="G12" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2610,22 +2751,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="C13" t="s">
-        <v>529</v>
+        <v>576</v>
       </c>
       <c r="D13" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E13" t="s">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="F13" t="s">
-        <v>635</v>
+        <v>682</v>
       </c>
       <c r="G13" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2633,22 +2774,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="C14" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D14" t="s">
-        <v>555</v>
+        <v>602</v>
       </c>
       <c r="E14" t="s">
-        <v>582</v>
+        <v>629</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>636</v>
+        <v>683</v>
       </c>
       <c r="G14" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2656,22 +2797,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="C15" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D15" t="s">
-        <v>555</v>
+        <v>602</v>
       </c>
       <c r="E15" t="s">
-        <v>583</v>
+        <v>630</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>637</v>
+        <v>684</v>
       </c>
       <c r="G15" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2679,16 +2820,16 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="C16" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D16" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G16" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2696,16 +2837,16 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="C17" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D17" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G17" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2713,16 +2854,16 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="C18" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D18" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G18" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2730,16 +2871,16 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C19" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D19" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G19" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2747,16 +2888,16 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="C20" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D20" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G20" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2764,16 +2905,16 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="C21" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D21" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G21" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2781,16 +2922,16 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="C22" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D22" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G22" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2798,16 +2939,16 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="C23" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D23" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G23" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2815,16 +2956,16 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="C24" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D24" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G24" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2832,16 +2973,16 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="C25" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D25" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G25" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2849,16 +2990,16 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="C26" t="s">
-        <v>535</v>
+        <v>582</v>
       </c>
       <c r="D26" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G26" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2866,16 +3007,16 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C27" t="s">
-        <v>535</v>
+        <v>582</v>
       </c>
       <c r="D27" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G27" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2883,16 +3024,16 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="C28" t="s">
-        <v>535</v>
+        <v>582</v>
       </c>
       <c r="D28" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G28" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2900,16 +3041,16 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="C29" t="s">
-        <v>535</v>
+        <v>582</v>
       </c>
       <c r="D29" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G29" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2917,16 +3058,16 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="C30" t="s">
-        <v>535</v>
+        <v>582</v>
       </c>
       <c r="D30" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G30" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2934,16 +3075,16 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="C31" t="s">
-        <v>535</v>
+        <v>582</v>
       </c>
       <c r="D31" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G31" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2951,16 +3092,16 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="C32" t="s">
-        <v>535</v>
+        <v>582</v>
       </c>
       <c r="D32" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G32" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2968,16 +3109,16 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="C33" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D33" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G33" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2985,16 +3126,16 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="C34" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D34" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G34" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -3002,16 +3143,16 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="C35" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D35" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G35" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3019,16 +3160,16 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="C36" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D36" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G36" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -3036,16 +3177,16 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="C37" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D37" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G37" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -3053,16 +3194,16 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="C38" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D38" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G38" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -3070,16 +3211,16 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
       <c r="C39" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D39" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G39" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3087,16 +3228,16 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="C40" t="s">
-        <v>537</v>
+        <v>584</v>
       </c>
       <c r="D40" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G40" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -3104,16 +3245,16 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="C41" t="s">
-        <v>537</v>
+        <v>584</v>
       </c>
       <c r="D41" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G41" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3121,16 +3262,16 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>330</v>
+        <v>353</v>
       </c>
       <c r="C42" t="s">
-        <v>537</v>
+        <v>584</v>
       </c>
       <c r="D42" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G42" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3138,16 +3279,16 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>331</v>
+        <v>354</v>
       </c>
       <c r="C43" t="s">
-        <v>537</v>
+        <v>584</v>
       </c>
       <c r="D43" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G43" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3155,16 +3296,16 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="C44" t="s">
-        <v>537</v>
+        <v>584</v>
       </c>
       <c r="D44" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G44" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3172,16 +3313,16 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>333</v>
+        <v>356</v>
       </c>
       <c r="C45" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D45" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G45" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3189,16 +3330,16 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="C46" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D46" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G46" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3206,16 +3347,16 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>335</v>
+        <v>358</v>
       </c>
       <c r="C47" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D47" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G47" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3223,16 +3364,16 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="C48" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D48" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G48" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -3240,16 +3381,16 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="C49" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D49" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G49" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -3257,16 +3398,16 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="C50" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D50" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G50" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -3274,16 +3415,16 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="C51" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D51" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G51" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -3291,16 +3432,16 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="C52" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D52" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G52" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -3308,16 +3449,16 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="C53" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D53" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G53" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3325,16 +3466,16 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="C54" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D54" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G54" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -3342,16 +3483,16 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="C55" t="s">
-        <v>538</v>
+        <v>585</v>
       </c>
       <c r="D55" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G55" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3359,16 +3500,16 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="C56" t="s">
-        <v>538</v>
+        <v>585</v>
       </c>
       <c r="D56" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G56" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3376,16 +3517,16 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="C57" t="s">
-        <v>538</v>
+        <v>585</v>
       </c>
       <c r="D57" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G57" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3393,16 +3534,16 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="C58" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="D58" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G58" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3410,16 +3551,16 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="C59" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="D59" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G59" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3427,16 +3568,16 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="C60" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="D60" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G60" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3444,16 +3585,16 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="C61" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D61" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G61" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3461,16 +3602,16 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="C62" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D62" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G62" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3478,16 +3619,16 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="C63" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D63" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G63" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3495,16 +3636,16 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="C64" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D64" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G64" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3512,16 +3653,16 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="C65" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D65" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G65" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3529,16 +3670,16 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="C66" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D66" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G66" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3546,16 +3687,16 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="C67" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D67" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G67" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3563,16 +3704,16 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="C68" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D68" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G68" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3580,16 +3721,16 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>357</v>
+        <v>380</v>
       </c>
       <c r="C69" t="s">
-        <v>535</v>
+        <v>582</v>
       </c>
       <c r="D69" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G69" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3597,16 +3738,16 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="C70" t="s">
-        <v>535</v>
+        <v>582</v>
       </c>
       <c r="D70" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G70" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3614,16 +3755,16 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="C71" t="s">
-        <v>535</v>
+        <v>582</v>
       </c>
       <c r="D71" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G71" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3631,16 +3772,16 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="C72" t="s">
-        <v>535</v>
+        <v>582</v>
       </c>
       <c r="D72" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G72" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3648,16 +3789,16 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="C73" t="s">
-        <v>535</v>
+        <v>582</v>
       </c>
       <c r="D73" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G73" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3665,16 +3806,16 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="C74" t="s">
-        <v>535</v>
+        <v>582</v>
       </c>
       <c r="D74" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G74" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3682,16 +3823,16 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="C75" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D75" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G75" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3699,16 +3840,16 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="C76" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D76" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G76" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3716,16 +3857,16 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="C77" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D77" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G77" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3733,16 +3874,16 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
       <c r="C78" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D78" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G78" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3750,16 +3891,16 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="C79" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D79" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G79" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3767,16 +3908,16 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="C80" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D80" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G80" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3784,16 +3925,16 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="C81" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D81" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G81" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3801,16 +3942,16 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>370</v>
+        <v>393</v>
       </c>
       <c r="C82" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D82" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G82" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3818,16 +3959,16 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>371</v>
+        <v>394</v>
       </c>
       <c r="C83" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D83" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G83" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3835,16 +3976,16 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>372</v>
+        <v>395</v>
       </c>
       <c r="C84" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D84" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G84" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3852,16 +3993,16 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="C85" t="s">
-        <v>537</v>
+        <v>584</v>
       </c>
       <c r="D85" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G85" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3869,16 +4010,16 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="C86" t="s">
-        <v>537</v>
+        <v>584</v>
       </c>
       <c r="D86" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G86" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3886,16 +4027,16 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="C87" t="s">
-        <v>537</v>
+        <v>584</v>
       </c>
       <c r="D87" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G87" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3903,16 +4044,16 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>376</v>
+        <v>399</v>
       </c>
       <c r="C88" t="s">
-        <v>537</v>
+        <v>584</v>
       </c>
       <c r="D88" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G88" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3920,16 +4061,16 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>377</v>
+        <v>400</v>
       </c>
       <c r="C89" t="s">
-        <v>537</v>
+        <v>584</v>
       </c>
       <c r="D89" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G89" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3937,16 +4078,16 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>378</v>
+        <v>401</v>
       </c>
       <c r="C90" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D90" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G90" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3954,16 +4095,16 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="C91" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D91" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G91" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3971,16 +4112,16 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>380</v>
+        <v>403</v>
       </c>
       <c r="C92" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D92" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G92" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3988,16 +4129,16 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="C93" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D93" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G93" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -4005,16 +4146,16 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="C94" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D94" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G94" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -4022,16 +4163,16 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>383</v>
+        <v>406</v>
       </c>
       <c r="C95" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D95" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G95" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -4039,16 +4180,16 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="C96" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D96" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G96" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4056,16 +4197,16 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="C97" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D97" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G97" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4073,16 +4214,16 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="C98" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D98" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G98" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4090,16 +4231,16 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="C99" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D99" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G99" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4107,16 +4248,16 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="C100" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D100" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G100" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4124,16 +4265,16 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>389</v>
+        <v>412</v>
       </c>
       <c r="C101" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D101" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G101" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4141,16 +4282,16 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>390</v>
+        <v>413</v>
       </c>
       <c r="C102" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D102" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G102" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4158,16 +4299,16 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>391</v>
+        <v>414</v>
       </c>
       <c r="C103" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D103" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G103" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4175,16 +4316,16 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>392</v>
+        <v>415</v>
       </c>
       <c r="C104" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D104" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G104" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4192,16 +4333,16 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="C105" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D105" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G105" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4209,16 +4350,16 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
       <c r="C106" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D106" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G106" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4226,16 +4367,16 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>395</v>
+        <v>418</v>
       </c>
       <c r="C107" t="s">
-        <v>538</v>
+        <v>585</v>
       </c>
       <c r="D107" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G107" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4243,16 +4384,16 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>396</v>
+        <v>419</v>
       </c>
       <c r="C108" t="s">
-        <v>538</v>
+        <v>585</v>
       </c>
       <c r="D108" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G108" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4260,16 +4401,16 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>397</v>
+        <v>420</v>
       </c>
       <c r="C109" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="D109" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G109" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4277,16 +4418,16 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="C110" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="D110" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G110" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4294,16 +4435,16 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="C111" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="D111" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G111" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4311,16 +4452,16 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>400</v>
+        <v>423</v>
       </c>
       <c r="C112" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="D112" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G112" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4328,16 +4469,16 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>401</v>
+        <v>424</v>
       </c>
       <c r="C113" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="D113" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G113" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4345,16 +4486,16 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>402</v>
+        <v>425</v>
       </c>
       <c r="C114" t="s">
-        <v>540</v>
+        <v>587</v>
       </c>
       <c r="D114" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G114" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4362,16 +4503,16 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="C115" t="s">
-        <v>540</v>
+        <v>587</v>
       </c>
       <c r="D115" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G115" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4379,16 +4520,16 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>404</v>
+        <v>427</v>
       </c>
       <c r="C116" t="s">
-        <v>540</v>
+        <v>587</v>
       </c>
       <c r="D116" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G116" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4396,16 +4537,16 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>405</v>
+        <v>428</v>
       </c>
       <c r="C117" t="s">
-        <v>540</v>
+        <v>587</v>
       </c>
       <c r="D117" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G117" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4413,16 +4554,16 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>406</v>
+        <v>429</v>
       </c>
       <c r="C118" t="s">
-        <v>540</v>
+        <v>587</v>
       </c>
       <c r="D118" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G118" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4430,22 +4571,22 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="C119" t="s">
-        <v>540</v>
+        <v>587</v>
       </c>
       <c r="D119" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E119" t="s">
-        <v>584</v>
+        <v>631</v>
       </c>
       <c r="F119" t="s">
-        <v>638</v>
+        <v>685</v>
       </c>
       <c r="G119" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4453,19 +4594,19 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>407</v>
+        <v>430</v>
       </c>
       <c r="C120" t="s">
-        <v>540</v>
+        <v>587</v>
       </c>
       <c r="D120" t="s">
-        <v>556</v>
+        <v>603</v>
       </c>
       <c r="E120" t="s">
-        <v>585</v>
+        <v>632</v>
       </c>
       <c r="G120" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4473,16 +4614,16 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="C121" t="s">
-        <v>540</v>
+        <v>587</v>
       </c>
       <c r="D121" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G121" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4490,16 +4631,16 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="C122" t="s">
-        <v>538</v>
+        <v>585</v>
       </c>
       <c r="D122" t="s">
-        <v>557</v>
+        <v>604</v>
       </c>
       <c r="G122" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4507,22 +4648,22 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>410</v>
+        <v>433</v>
       </c>
       <c r="C123" t="s">
-        <v>538</v>
+        <v>585</v>
       </c>
       <c r="D123" t="s">
-        <v>558</v>
+        <v>605</v>
       </c>
       <c r="E123" t="s">
-        <v>586</v>
+        <v>633</v>
       </c>
       <c r="F123" t="s">
-        <v>639</v>
+        <v>686</v>
       </c>
       <c r="G123" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4530,16 +4671,16 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="C124" t="s">
-        <v>538</v>
+        <v>585</v>
       </c>
       <c r="D124" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G124" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4547,16 +4688,16 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="C125" t="s">
-        <v>538</v>
+        <v>585</v>
       </c>
       <c r="D125" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G125" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4564,16 +4705,16 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>413</v>
+        <v>436</v>
       </c>
       <c r="C126" t="s">
-        <v>538</v>
+        <v>585</v>
       </c>
       <c r="D126" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G126" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4581,16 +4722,16 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="C127" t="s">
-        <v>538</v>
+        <v>585</v>
       </c>
       <c r="D127" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G127" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4598,19 +4739,19 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>415</v>
+        <v>438</v>
       </c>
       <c r="C128" t="s">
-        <v>538</v>
+        <v>585</v>
       </c>
       <c r="D128" t="s">
-        <v>559</v>
+        <v>606</v>
       </c>
       <c r="E128" t="s">
-        <v>587</v>
+        <v>634</v>
       </c>
       <c r="G128" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4618,22 +4759,22 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>416</v>
+        <v>439</v>
       </c>
       <c r="C129" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="D129" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E129" t="s">
-        <v>588</v>
+        <v>635</v>
       </c>
       <c r="F129" t="s">
-        <v>640</v>
+        <v>687</v>
       </c>
       <c r="G129" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4641,16 +4782,16 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>417</v>
+        <v>440</v>
       </c>
       <c r="C130" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="D130" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G130" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4658,13 +4799,13 @@
         <v>136</v>
       </c>
       <c r="C131" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="D131" t="s">
-        <v>560</v>
+        <v>607</v>
       </c>
       <c r="E131" t="s">
-        <v>589</v>
+        <v>636</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4672,19 +4813,19 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="C132" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="D132" t="s">
-        <v>561</v>
+        <v>608</v>
       </c>
       <c r="E132" t="s">
-        <v>590</v>
+        <v>637</v>
       </c>
       <c r="G132" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4692,19 +4833,19 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>419</v>
+        <v>442</v>
       </c>
       <c r="C133" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="D133" t="s">
-        <v>562</v>
+        <v>609</v>
       </c>
       <c r="E133" t="s">
-        <v>591</v>
+        <v>638</v>
       </c>
       <c r="G133" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4712,10 +4853,10 @@
         <v>139</v>
       </c>
       <c r="C134" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="D134" t="s">
-        <v>563</v>
+        <v>610</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4723,10 +4864,10 @@
         <v>140</v>
       </c>
       <c r="C135" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="D135" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4734,16 +4875,16 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="C136" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D136" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G136" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4751,16 +4892,16 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>421</v>
+        <v>444</v>
       </c>
       <c r="C137" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D137" t="s">
-        <v>560</v>
+        <v>607</v>
       </c>
       <c r="G137" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4768,10 +4909,10 @@
         <v>143</v>
       </c>
       <c r="C138" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D138" t="s">
-        <v>564</v>
+        <v>611</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4779,10 +4920,10 @@
         <v>144</v>
       </c>
       <c r="C139" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D139" t="s">
-        <v>565</v>
+        <v>612</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4790,10 +4931,10 @@
         <v>145</v>
       </c>
       <c r="C140" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D140" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4801,16 +4942,16 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="C141" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D141" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G141" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4818,22 +4959,22 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="C142" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D142" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E142" t="s">
-        <v>592</v>
+        <v>639</v>
       </c>
       <c r="F142" t="s">
-        <v>641</v>
+        <v>688</v>
       </c>
       <c r="G142" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4841,16 +4982,16 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>423</v>
+        <v>446</v>
       </c>
       <c r="C143" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D143" t="s">
-        <v>564</v>
+        <v>611</v>
       </c>
       <c r="G143" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4858,13 +4999,13 @@
         <v>149</v>
       </c>
       <c r="C144" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D144" t="s">
-        <v>566</v>
+        <v>613</v>
       </c>
       <c r="E144" t="s">
-        <v>593</v>
+        <v>640</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4872,10 +5013,10 @@
         <v>150</v>
       </c>
       <c r="C145" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D145" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4883,19 +5024,19 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>424</v>
+        <v>447</v>
       </c>
       <c r="C146" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D146" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="F146" t="s">
-        <v>642</v>
+        <v>689</v>
       </c>
       <c r="G146" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -4903,22 +5044,22 @@
         <v>152</v>
       </c>
       <c r="B147" t="s">
-        <v>425</v>
+        <v>448</v>
       </c>
       <c r="C147" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D147" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E147" t="s">
-        <v>594</v>
+        <v>641</v>
       </c>
       <c r="F147" t="s">
-        <v>643</v>
+        <v>690</v>
       </c>
       <c r="G147" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -4926,19 +5067,19 @@
         <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>426</v>
+        <v>449</v>
       </c>
       <c r="C148" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D148" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E148" t="s">
-        <v>595</v>
+        <v>642</v>
       </c>
       <c r="G148" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -4946,19 +5087,19 @@
         <v>154</v>
       </c>
       <c r="B149" t="s">
-        <v>427</v>
+        <v>450</v>
       </c>
       <c r="C149" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D149" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E149" t="s">
-        <v>596</v>
+        <v>643</v>
       </c>
       <c r="G149" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -4966,19 +5107,19 @@
         <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>428</v>
+        <v>451</v>
       </c>
       <c r="C150" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D150" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E150" t="s">
-        <v>597</v>
+        <v>644</v>
       </c>
       <c r="G150" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -4986,19 +5127,19 @@
         <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="C151" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D151" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E151" t="s">
-        <v>598</v>
+        <v>645</v>
       </c>
       <c r="G151" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5006,19 +5147,19 @@
         <v>157</v>
       </c>
       <c r="B152" t="s">
-        <v>430</v>
+        <v>453</v>
       </c>
       <c r="C152" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D152" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E152" t="s">
-        <v>599</v>
+        <v>646</v>
       </c>
       <c r="G152" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5026,10 +5167,10 @@
         <v>158</v>
       </c>
       <c r="C153" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D153" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5037,19 +5178,19 @@
         <v>159</v>
       </c>
       <c r="B154" t="s">
-        <v>431</v>
+        <v>454</v>
       </c>
       <c r="C154" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D154" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E154" t="s">
-        <v>600</v>
+        <v>647</v>
       </c>
       <c r="G154" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5057,16 +5198,16 @@
         <v>160</v>
       </c>
       <c r="B155" t="s">
-        <v>432</v>
+        <v>455</v>
       </c>
       <c r="C155" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D155" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G155" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5074,16 +5215,16 @@
         <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>433</v>
+        <v>456</v>
       </c>
       <c r="C156" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D156" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G156" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5091,22 +5232,22 @@
         <v>162</v>
       </c>
       <c r="B157" t="s">
-        <v>434</v>
+        <v>457</v>
       </c>
       <c r="C157" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D157" t="s">
-        <v>567</v>
+        <v>614</v>
       </c>
       <c r="E157" t="s">
-        <v>601</v>
+        <v>648</v>
       </c>
       <c r="F157" t="s">
-        <v>644</v>
+        <v>691</v>
       </c>
       <c r="G157" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5114,19 +5255,19 @@
         <v>163</v>
       </c>
       <c r="B158" t="s">
-        <v>435</v>
+        <v>458</v>
       </c>
       <c r="C158" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D158" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E158" t="s">
-        <v>602</v>
+        <v>649</v>
       </c>
       <c r="G158" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5134,19 +5275,19 @@
         <v>164</v>
       </c>
       <c r="B159" t="s">
-        <v>436</v>
+        <v>459</v>
       </c>
       <c r="C159" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D159" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E159" t="s">
-        <v>603</v>
+        <v>650</v>
       </c>
       <c r="G159" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5154,19 +5295,19 @@
         <v>165</v>
       </c>
       <c r="B160" t="s">
-        <v>437</v>
+        <v>460</v>
       </c>
       <c r="C160" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D160" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E160" t="s">
-        <v>604</v>
+        <v>651</v>
       </c>
       <c r="G160" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5174,19 +5315,19 @@
         <v>166</v>
       </c>
       <c r="B161" t="s">
-        <v>438</v>
+        <v>461</v>
       </c>
       <c r="C161" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D161" t="s">
-        <v>568</v>
+        <v>615</v>
       </c>
       <c r="E161" t="s">
-        <v>605</v>
+        <v>652</v>
       </c>
       <c r="G161" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5194,16 +5335,16 @@
         <v>167</v>
       </c>
       <c r="B162" t="s">
-        <v>439</v>
+        <v>462</v>
       </c>
       <c r="C162" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D162" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G162" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5211,19 +5352,19 @@
         <v>168</v>
       </c>
       <c r="B163" t="s">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="C163" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D163" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E163" t="s">
-        <v>606</v>
+        <v>653</v>
       </c>
       <c r="G163" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5231,19 +5372,19 @@
         <v>169</v>
       </c>
       <c r="B164" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="C164" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D164" t="s">
-        <v>569</v>
+        <v>616</v>
       </c>
       <c r="E164" t="s">
-        <v>607</v>
+        <v>654</v>
       </c>
       <c r="G164" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5251,13 +5392,13 @@
         <v>170</v>
       </c>
       <c r="C165" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D165" t="s">
-        <v>560</v>
+        <v>607</v>
       </c>
       <c r="E165" t="s">
-        <v>608</v>
+        <v>655</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5265,19 +5406,19 @@
         <v>171</v>
       </c>
       <c r="B166" t="s">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="C166" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D166" t="s">
-        <v>570</v>
+        <v>617</v>
       </c>
       <c r="E166" t="s">
-        <v>609</v>
+        <v>656</v>
       </c>
       <c r="G166" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5285,19 +5426,19 @@
         <v>172</v>
       </c>
       <c r="B167" t="s">
-        <v>443</v>
+        <v>466</v>
       </c>
       <c r="C167" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D167" t="s">
-        <v>571</v>
+        <v>618</v>
       </c>
       <c r="E167" t="s">
-        <v>610</v>
+        <v>657</v>
       </c>
       <c r="G167" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5305,19 +5446,19 @@
         <v>173</v>
       </c>
       <c r="B168" t="s">
-        <v>444</v>
+        <v>467</v>
       </c>
       <c r="C168" t="s">
-        <v>529</v>
+        <v>576</v>
       </c>
       <c r="D168" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E168" t="s">
-        <v>611</v>
+        <v>658</v>
       </c>
       <c r="G168" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5325,19 +5466,19 @@
         <v>174</v>
       </c>
       <c r="B169" t="s">
-        <v>445</v>
+        <v>468</v>
       </c>
       <c r="C169" t="s">
-        <v>529</v>
+        <v>576</v>
       </c>
       <c r="D169" t="s">
-        <v>572</v>
+        <v>619</v>
       </c>
       <c r="E169" t="s">
-        <v>612</v>
+        <v>659</v>
       </c>
       <c r="G169" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5345,13 +5486,13 @@
         <v>175</v>
       </c>
       <c r="C170" t="s">
-        <v>529</v>
+        <v>576</v>
       </c>
       <c r="D170" t="s">
-        <v>573</v>
+        <v>620</v>
       </c>
       <c r="E170" t="s">
-        <v>613</v>
+        <v>660</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5359,13 +5500,13 @@
         <v>176</v>
       </c>
       <c r="C171" t="s">
-        <v>529</v>
+        <v>576</v>
       </c>
       <c r="D171" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E171" t="s">
-        <v>614</v>
+        <v>661</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5373,13 +5514,13 @@
         <v>177</v>
       </c>
       <c r="C172" t="s">
-        <v>529</v>
+        <v>576</v>
       </c>
       <c r="D172" t="s">
-        <v>560</v>
+        <v>607</v>
       </c>
       <c r="E172" t="s">
-        <v>615</v>
+        <v>662</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5387,16 +5528,16 @@
         <v>178</v>
       </c>
       <c r="B173" t="s">
-        <v>446</v>
+        <v>469</v>
       </c>
       <c r="C173" t="s">
-        <v>541</v>
+        <v>588</v>
       </c>
       <c r="D173" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G173" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5404,19 +5545,19 @@
         <v>179</v>
       </c>
       <c r="B174" t="s">
-        <v>447</v>
+        <v>470</v>
       </c>
       <c r="C174" t="s">
-        <v>541</v>
+        <v>588</v>
       </c>
       <c r="D174" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="F174" t="s">
-        <v>645</v>
+        <v>692</v>
       </c>
       <c r="G174" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5424,19 +5565,19 @@
         <v>180</v>
       </c>
       <c r="B175" t="s">
-        <v>448</v>
+        <v>471</v>
       </c>
       <c r="C175" t="s">
-        <v>541</v>
+        <v>588</v>
       </c>
       <c r="D175" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="F175" t="s">
-        <v>646</v>
+        <v>693</v>
       </c>
       <c r="G175" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5444,10 +5585,10 @@
         <v>181</v>
       </c>
       <c r="C176" t="s">
-        <v>542</v>
+        <v>589</v>
       </c>
       <c r="D176" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5455,10 +5596,10 @@
         <v>182</v>
       </c>
       <c r="C177" t="s">
-        <v>542</v>
+        <v>589</v>
       </c>
       <c r="D177" t="s">
-        <v>574</v>
+        <v>621</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5466,10 +5607,10 @@
         <v>183</v>
       </c>
       <c r="C178" t="s">
-        <v>542</v>
+        <v>589</v>
       </c>
       <c r="D178" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5477,22 +5618,22 @@
         <v>184</v>
       </c>
       <c r="B179" t="s">
-        <v>449</v>
+        <v>472</v>
       </c>
       <c r="C179" t="s">
-        <v>543</v>
+        <v>590</v>
       </c>
       <c r="D179" t="s">
-        <v>574</v>
+        <v>621</v>
       </c>
       <c r="E179" t="s">
-        <v>616</v>
+        <v>663</v>
       </c>
       <c r="F179" t="s">
-        <v>647</v>
+        <v>694</v>
       </c>
       <c r="G179" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5500,10 +5641,10 @@
         <v>185</v>
       </c>
       <c r="C180" t="s">
-        <v>543</v>
+        <v>590</v>
       </c>
       <c r="D180" t="s">
-        <v>575</v>
+        <v>622</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5511,10 +5652,10 @@
         <v>186</v>
       </c>
       <c r="C181" t="s">
-        <v>543</v>
+        <v>590</v>
       </c>
       <c r="D181" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5522,19 +5663,19 @@
         <v>187</v>
       </c>
       <c r="B182" t="s">
-        <v>450</v>
+        <v>473</v>
       </c>
       <c r="C182" t="s">
-        <v>544</v>
+        <v>591</v>
       </c>
       <c r="D182" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E182" t="s">
-        <v>617</v>
+        <v>664</v>
       </c>
       <c r="G182" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5542,19 +5683,19 @@
         <v>188</v>
       </c>
       <c r="B183" t="s">
-        <v>451</v>
+        <v>474</v>
       </c>
       <c r="C183" t="s">
-        <v>544</v>
+        <v>591</v>
       </c>
       <c r="D183" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="F183" t="s">
-        <v>648</v>
+        <v>695</v>
       </c>
       <c r="G183" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5562,10 +5703,10 @@
         <v>189</v>
       </c>
       <c r="C184" t="s">
-        <v>544</v>
+        <v>591</v>
       </c>
       <c r="D184" t="s">
-        <v>575</v>
+        <v>622</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5573,13 +5714,13 @@
         <v>190</v>
       </c>
       <c r="C185" t="s">
-        <v>544</v>
+        <v>591</v>
       </c>
       <c r="D185" t="s">
-        <v>576</v>
+        <v>623</v>
       </c>
       <c r="F185" t="s">
-        <v>649</v>
+        <v>696</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5587,13 +5728,13 @@
         <v>191</v>
       </c>
       <c r="C186" t="s">
-        <v>545</v>
+        <v>592</v>
       </c>
       <c r="D186" t="s">
-        <v>577</v>
+        <v>624</v>
       </c>
       <c r="E186" t="s">
-        <v>618</v>
+        <v>665</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5601,13 +5742,13 @@
         <v>192</v>
       </c>
       <c r="C187" t="s">
-        <v>545</v>
+        <v>592</v>
       </c>
       <c r="D187" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E187" t="s">
-        <v>619</v>
+        <v>666</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5615,13 +5756,13 @@
         <v>193</v>
       </c>
       <c r="C188" t="s">
-        <v>545</v>
+        <v>592</v>
       </c>
       <c r="D188" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E188" t="s">
-        <v>620</v>
+        <v>667</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5629,13 +5770,13 @@
         <v>194</v>
       </c>
       <c r="C189" t="s">
-        <v>545</v>
+        <v>592</v>
       </c>
       <c r="D189" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E189" t="s">
-        <v>621</v>
+        <v>668</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5643,13 +5784,13 @@
         <v>195</v>
       </c>
       <c r="C190" t="s">
-        <v>545</v>
+        <v>592</v>
       </c>
       <c r="D190" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E190" t="s">
-        <v>622</v>
+        <v>669</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5657,10 +5798,10 @@
         <v>196</v>
       </c>
       <c r="C191" t="s">
-        <v>545</v>
+        <v>592</v>
       </c>
       <c r="D191" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -5668,10 +5809,10 @@
         <v>197</v>
       </c>
       <c r="C192" t="s">
-        <v>545</v>
+        <v>592</v>
       </c>
       <c r="D192" t="s">
-        <v>578</v>
+        <v>625</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -5679,10 +5820,10 @@
         <v>198</v>
       </c>
       <c r="C193" t="s">
-        <v>545</v>
+        <v>592</v>
       </c>
       <c r="D193" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -5690,16 +5831,16 @@
         <v>199</v>
       </c>
       <c r="B194" t="s">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="C194" t="s">
-        <v>545</v>
+        <v>592</v>
       </c>
       <c r="D194" t="s">
-        <v>557</v>
+        <v>604</v>
       </c>
       <c r="G194" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -5707,16 +5848,16 @@
         <v>200</v>
       </c>
       <c r="B195" t="s">
-        <v>453</v>
+        <v>476</v>
       </c>
       <c r="C195" t="s">
-        <v>545</v>
+        <v>592</v>
       </c>
       <c r="D195" t="s">
-        <v>557</v>
+        <v>604</v>
       </c>
       <c r="G195" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -5724,19 +5865,19 @@
         <v>201</v>
       </c>
       <c r="B196" t="s">
-        <v>454</v>
+        <v>477</v>
       </c>
       <c r="C196" t="s">
-        <v>532</v>
+        <v>579</v>
       </c>
       <c r="D196" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="F196" t="s">
-        <v>650</v>
+        <v>697</v>
       </c>
       <c r="G196" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -5744,22 +5885,22 @@
         <v>202</v>
       </c>
       <c r="B197" t="s">
-        <v>455</v>
+        <v>478</v>
       </c>
       <c r="C197" t="s">
-        <v>532</v>
+        <v>579</v>
       </c>
       <c r="D197" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E197" t="s">
-        <v>623</v>
+        <v>670</v>
       </c>
       <c r="F197" t="s">
-        <v>651</v>
+        <v>698</v>
       </c>
       <c r="G197" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -5767,22 +5908,22 @@
         <v>203</v>
       </c>
       <c r="B198" t="s">
-        <v>456</v>
+        <v>479</v>
       </c>
       <c r="C198" t="s">
-        <v>532</v>
+        <v>579</v>
       </c>
       <c r="D198" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E198" t="s">
-        <v>624</v>
+        <v>671</v>
       </c>
       <c r="F198" t="s">
-        <v>652</v>
+        <v>699</v>
       </c>
       <c r="G198" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -5790,22 +5931,22 @@
         <v>204</v>
       </c>
       <c r="B199" t="s">
-        <v>457</v>
+        <v>480</v>
       </c>
       <c r="C199" t="s">
-        <v>532</v>
+        <v>579</v>
       </c>
       <c r="D199" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E199" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="F199" t="s">
-        <v>653</v>
+        <v>700</v>
       </c>
       <c r="G199" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -5813,16 +5954,16 @@
         <v>205</v>
       </c>
       <c r="B200" t="s">
-        <v>458</v>
+        <v>481</v>
       </c>
       <c r="C200" t="s">
-        <v>546</v>
+        <v>593</v>
       </c>
       <c r="D200" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G200" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -5830,10 +5971,10 @@
         <v>206</v>
       </c>
       <c r="C201" t="s">
-        <v>546</v>
+        <v>593</v>
       </c>
       <c r="D201" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -5841,10 +5982,10 @@
         <v>207</v>
       </c>
       <c r="C202" t="s">
-        <v>546</v>
+        <v>593</v>
       </c>
       <c r="D202" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -5852,10 +5993,10 @@
         <v>208</v>
       </c>
       <c r="C203" t="s">
-        <v>546</v>
+        <v>593</v>
       </c>
       <c r="D203" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -5863,16 +6004,16 @@
         <v>209</v>
       </c>
       <c r="B204" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="C204" t="s">
-        <v>547</v>
+        <v>594</v>
       </c>
       <c r="D204" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G204" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -5880,10 +6021,10 @@
         <v>210</v>
       </c>
       <c r="C205" t="s">
-        <v>547</v>
+        <v>594</v>
       </c>
       <c r="D205" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -5891,10 +6032,10 @@
         <v>211</v>
       </c>
       <c r="C206" t="s">
-        <v>547</v>
+        <v>594</v>
       </c>
       <c r="D206" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -5902,19 +6043,19 @@
         <v>212</v>
       </c>
       <c r="B207" t="s">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="C207" t="s">
-        <v>547</v>
+        <v>594</v>
       </c>
       <c r="D207" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E207" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="G207" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -5922,13 +6063,13 @@
         <v>213</v>
       </c>
       <c r="C208" t="s">
-        <v>547</v>
+        <v>594</v>
       </c>
       <c r="D208" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E208" t="s">
-        <v>627</v>
+        <v>674</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -5936,10 +6077,10 @@
         <v>214</v>
       </c>
       <c r="C209" t="s">
-        <v>547</v>
+        <v>594</v>
       </c>
       <c r="D209" t="s">
-        <v>563</v>
+        <v>610</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -5947,19 +6088,19 @@
         <v>215</v>
       </c>
       <c r="B210" t="s">
-        <v>460</v>
+        <v>483</v>
       </c>
       <c r="C210" t="s">
-        <v>548</v>
+        <v>595</v>
       </c>
       <c r="D210" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E210" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="G210" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -5967,16 +6108,16 @@
         <v>216</v>
       </c>
       <c r="B211" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="C211" t="s">
-        <v>548</v>
+        <v>595</v>
       </c>
       <c r="D211" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G211" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -5984,13 +6125,13 @@
         <v>217</v>
       </c>
       <c r="C212" t="s">
-        <v>548</v>
+        <v>595</v>
       </c>
       <c r="D212" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E212" t="s">
-        <v>629</v>
+        <v>676</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -5998,13 +6139,13 @@
         <v>218</v>
       </c>
       <c r="C213" t="s">
-        <v>548</v>
+        <v>595</v>
       </c>
       <c r="D213" t="s">
-        <v>567</v>
+        <v>614</v>
       </c>
       <c r="E213" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6012,16 +6153,16 @@
         <v>219</v>
       </c>
       <c r="B214" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="C214" t="s">
-        <v>531</v>
+        <v>578</v>
       </c>
       <c r="D214" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G214" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6029,16 +6170,16 @@
         <v>220</v>
       </c>
       <c r="B215" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
       <c r="C215" t="s">
-        <v>531</v>
+        <v>578</v>
       </c>
       <c r="D215" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G215" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6046,13 +6187,13 @@
         <v>221</v>
       </c>
       <c r="C216" t="s">
-        <v>531</v>
+        <v>578</v>
       </c>
       <c r="D216" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E216" t="s">
-        <v>631</v>
+        <v>678</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6060,19 +6201,19 @@
         <v>222</v>
       </c>
       <c r="B217" t="s">
-        <v>464</v>
+        <v>487</v>
       </c>
       <c r="C217" t="s">
-        <v>549</v>
+        <v>596</v>
       </c>
       <c r="D217" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E217" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="G217" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6080,19 +6221,19 @@
         <v>223</v>
       </c>
       <c r="B218" t="s">
-        <v>465</v>
+        <v>488</v>
       </c>
       <c r="C218" t="s">
-        <v>549</v>
+        <v>596</v>
       </c>
       <c r="D218" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E218" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="G218" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6100,19 +6241,19 @@
         <v>224</v>
       </c>
       <c r="B219" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="C219" t="s">
-        <v>550</v>
+        <v>597</v>
       </c>
       <c r="D219" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E219" t="s">
-        <v>633</v>
+        <v>680</v>
       </c>
       <c r="G219" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6120,10 +6261,10 @@
         <v>225</v>
       </c>
       <c r="C220" t="s">
-        <v>550</v>
+        <v>597</v>
       </c>
       <c r="D220" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6131,16 +6272,16 @@
         <v>226</v>
       </c>
       <c r="B221" t="s">
-        <v>466</v>
+        <v>489</v>
       </c>
       <c r="C221" t="s">
-        <v>550</v>
+        <v>597</v>
       </c>
       <c r="D221" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G221" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6148,19 +6289,19 @@
         <v>227</v>
       </c>
       <c r="B222" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="C222" t="s">
-        <v>551</v>
+        <v>598</v>
       </c>
       <c r="D222" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="E222" t="s">
-        <v>634</v>
+        <v>681</v>
       </c>
       <c r="G222" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6168,16 +6309,16 @@
         <v>228</v>
       </c>
       <c r="B223" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="C223" t="s">
-        <v>551</v>
+        <v>598</v>
       </c>
       <c r="D223" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G223" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6185,16 +6326,16 @@
         <v>229</v>
       </c>
       <c r="B224" t="s">
-        <v>469</v>
+        <v>492</v>
       </c>
       <c r="C224" t="s">
-        <v>551</v>
+        <v>598</v>
       </c>
       <c r="D224" t="s">
-        <v>576</v>
+        <v>623</v>
       </c>
       <c r="G224" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6202,19 +6343,19 @@
         <v>230</v>
       </c>
       <c r="B225" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="C225" t="s">
-        <v>551</v>
+        <v>598</v>
       </c>
       <c r="D225" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="F225" t="s">
-        <v>654</v>
+        <v>701</v>
       </c>
       <c r="G225" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6222,16 +6363,16 @@
         <v>231</v>
       </c>
       <c r="B226" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="C226" t="s">
-        <v>551</v>
+        <v>598</v>
       </c>
       <c r="D226" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G226" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6239,10 +6380,10 @@
         <v>232</v>
       </c>
       <c r="C227" t="s">
-        <v>551</v>
+        <v>598</v>
       </c>
       <c r="D227" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6250,16 +6391,16 @@
         <v>233</v>
       </c>
       <c r="B228" t="s">
-        <v>472</v>
+        <v>495</v>
       </c>
       <c r="C228" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D228" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G228" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6267,16 +6408,16 @@
         <v>234</v>
       </c>
       <c r="B229" t="s">
-        <v>473</v>
+        <v>496</v>
       </c>
       <c r="C229" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D229" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G229" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6284,16 +6425,16 @@
         <v>235</v>
       </c>
       <c r="B230" t="s">
-        <v>474</v>
+        <v>497</v>
       </c>
       <c r="C230" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D230" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G230" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6301,16 +6442,16 @@
         <v>236</v>
       </c>
       <c r="B231" t="s">
-        <v>475</v>
+        <v>498</v>
       </c>
       <c r="C231" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D231" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G231" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6318,16 +6459,16 @@
         <v>237</v>
       </c>
       <c r="B232" t="s">
-        <v>476</v>
+        <v>499</v>
       </c>
       <c r="C232" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D232" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G232" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6335,16 +6476,16 @@
         <v>238</v>
       </c>
       <c r="B233" t="s">
-        <v>477</v>
+        <v>500</v>
       </c>
       <c r="C233" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D233" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G233" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6352,16 +6493,16 @@
         <v>239</v>
       </c>
       <c r="B234" t="s">
-        <v>478</v>
+        <v>501</v>
       </c>
       <c r="C234" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D234" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G234" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -6369,16 +6510,16 @@
         <v>240</v>
       </c>
       <c r="B235" t="s">
-        <v>479</v>
+        <v>502</v>
       </c>
       <c r="C235" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D235" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G235" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -6386,16 +6527,16 @@
         <v>241</v>
       </c>
       <c r="B236" t="s">
-        <v>480</v>
+        <v>503</v>
       </c>
       <c r="C236" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D236" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G236" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -6403,16 +6544,16 @@
         <v>242</v>
       </c>
       <c r="B237" t="s">
-        <v>481</v>
+        <v>504</v>
       </c>
       <c r="C237" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D237" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G237" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -6420,16 +6561,16 @@
         <v>243</v>
       </c>
       <c r="B238" t="s">
-        <v>482</v>
+        <v>505</v>
       </c>
       <c r="C238" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D238" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G238" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -6437,16 +6578,16 @@
         <v>244</v>
       </c>
       <c r="B239" t="s">
-        <v>483</v>
+        <v>506</v>
       </c>
       <c r="C239" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D239" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G239" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -6454,16 +6595,16 @@
         <v>245</v>
       </c>
       <c r="B240" t="s">
-        <v>484</v>
+        <v>507</v>
       </c>
       <c r="C240" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D240" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G240" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -6471,16 +6612,16 @@
         <v>246</v>
       </c>
       <c r="B241" t="s">
-        <v>485</v>
+        <v>508</v>
       </c>
       <c r="C241" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D241" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G241" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -6488,16 +6629,16 @@
         <v>247</v>
       </c>
       <c r="B242" t="s">
-        <v>486</v>
+        <v>509</v>
       </c>
       <c r="C242" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D242" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G242" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -6505,16 +6646,16 @@
         <v>248</v>
       </c>
       <c r="B243" t="s">
-        <v>487</v>
+        <v>510</v>
       </c>
       <c r="C243" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D243" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G243" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -6522,16 +6663,16 @@
         <v>249</v>
       </c>
       <c r="B244" t="s">
-        <v>488</v>
+        <v>511</v>
       </c>
       <c r="C244" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D244" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G244" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -6539,16 +6680,16 @@
         <v>250</v>
       </c>
       <c r="B245" t="s">
-        <v>489</v>
+        <v>512</v>
       </c>
       <c r="C245" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D245" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G245" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -6556,16 +6697,16 @@
         <v>251</v>
       </c>
       <c r="B246" t="s">
-        <v>490</v>
+        <v>513</v>
       </c>
       <c r="C246" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D246" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G246" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -6573,16 +6714,16 @@
         <v>252</v>
       </c>
       <c r="B247" t="s">
-        <v>491</v>
+        <v>514</v>
       </c>
       <c r="C247" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D247" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G247" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -6590,16 +6731,16 @@
         <v>253</v>
       </c>
       <c r="B248" t="s">
-        <v>492</v>
+        <v>515</v>
       </c>
       <c r="C248" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D248" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G248" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -6607,16 +6748,16 @@
         <v>254</v>
       </c>
       <c r="B249" t="s">
-        <v>493</v>
+        <v>516</v>
       </c>
       <c r="C249" t="s">
-        <v>538</v>
+        <v>585</v>
       </c>
       <c r="D249" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G249" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -6624,16 +6765,16 @@
         <v>255</v>
       </c>
       <c r="B250" t="s">
-        <v>494</v>
+        <v>517</v>
       </c>
       <c r="C250" t="s">
-        <v>538</v>
+        <v>585</v>
       </c>
       <c r="D250" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G250" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -6641,16 +6782,16 @@
         <v>256</v>
       </c>
       <c r="B251" t="s">
-        <v>495</v>
+        <v>518</v>
       </c>
       <c r="C251" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="D251" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G251" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -6658,16 +6799,16 @@
         <v>257</v>
       </c>
       <c r="B252" t="s">
-        <v>496</v>
+        <v>519</v>
       </c>
       <c r="C252" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="D252" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G252" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -6675,16 +6816,16 @@
         <v>258</v>
       </c>
       <c r="B253" t="s">
-        <v>497</v>
+        <v>520</v>
       </c>
       <c r="C253" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="D253" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G253" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -6692,16 +6833,16 @@
         <v>259</v>
       </c>
       <c r="B254" t="s">
-        <v>498</v>
+        <v>521</v>
       </c>
       <c r="C254" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="D254" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G254" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -6709,16 +6850,16 @@
         <v>260</v>
       </c>
       <c r="B255" t="s">
-        <v>499</v>
+        <v>522</v>
       </c>
       <c r="C255" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="D255" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G255" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -6726,16 +6867,16 @@
         <v>261</v>
       </c>
       <c r="B256" t="s">
-        <v>500</v>
+        <v>523</v>
       </c>
       <c r="C256" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D256" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G256" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -6743,16 +6884,16 @@
         <v>262</v>
       </c>
       <c r="B257" t="s">
-        <v>501</v>
+        <v>524</v>
       </c>
       <c r="C257" t="s">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="D257" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G257" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -6760,16 +6901,16 @@
         <v>263</v>
       </c>
       <c r="B258" t="s">
-        <v>502</v>
+        <v>525</v>
       </c>
       <c r="C258" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D258" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G258" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -6777,16 +6918,16 @@
         <v>264</v>
       </c>
       <c r="B259" t="s">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="C259" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D259" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G259" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -6794,16 +6935,16 @@
         <v>265</v>
       </c>
       <c r="B260" t="s">
-        <v>504</v>
+        <v>527</v>
       </c>
       <c r="C260" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D260" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G260" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -6811,16 +6952,16 @@
         <v>266</v>
       </c>
       <c r="B261" t="s">
-        <v>505</v>
+        <v>528</v>
       </c>
       <c r="C261" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D261" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G261" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -6828,16 +6969,16 @@
         <v>267</v>
       </c>
       <c r="B262" t="s">
-        <v>506</v>
+        <v>529</v>
       </c>
       <c r="C262" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D262" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G262" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -6845,16 +6986,16 @@
         <v>268</v>
       </c>
       <c r="B263" t="s">
-        <v>507</v>
+        <v>530</v>
       </c>
       <c r="C263" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D263" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G263" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -6862,16 +7003,16 @@
         <v>269</v>
       </c>
       <c r="B264" t="s">
-        <v>508</v>
+        <v>531</v>
       </c>
       <c r="C264" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D264" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G264" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -6879,16 +7020,16 @@
         <v>270</v>
       </c>
       <c r="B265" t="s">
-        <v>509</v>
+        <v>532</v>
       </c>
       <c r="C265" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D265" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="G265" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -6896,16 +7037,16 @@
         <v>271</v>
       </c>
       <c r="B266" t="s">
-        <v>510</v>
+        <v>533</v>
       </c>
       <c r="C266" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D266" t="s">
-        <v>579</v>
+        <v>626</v>
       </c>
       <c r="G266" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -6913,16 +7054,16 @@
         <v>272</v>
       </c>
       <c r="B267" t="s">
-        <v>511</v>
+        <v>534</v>
       </c>
       <c r="C267" t="s">
-        <v>552</v>
+        <v>599</v>
       </c>
       <c r="D267" t="s">
-        <v>579</v>
+        <v>626</v>
       </c>
       <c r="G267" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -6930,16 +7071,16 @@
         <v>273</v>
       </c>
       <c r="B268" t="s">
-        <v>512</v>
+        <v>535</v>
       </c>
       <c r="C268" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D268" t="s">
-        <v>579</v>
+        <v>626</v>
       </c>
       <c r="G268" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -6947,16 +7088,16 @@
         <v>274</v>
       </c>
       <c r="B269" t="s">
-        <v>513</v>
+        <v>536</v>
       </c>
       <c r="C269" t="s">
-        <v>553</v>
+        <v>600</v>
       </c>
       <c r="D269" t="s">
-        <v>579</v>
+        <v>626</v>
       </c>
       <c r="G269" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -6964,16 +7105,16 @@
         <v>275</v>
       </c>
       <c r="B270" t="s">
-        <v>514</v>
+        <v>537</v>
       </c>
       <c r="C270" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="D270" t="s">
-        <v>579</v>
+        <v>626</v>
       </c>
       <c r="G270" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -6981,16 +7122,16 @@
         <v>276</v>
       </c>
       <c r="B271" t="s">
-        <v>515</v>
+        <v>538</v>
       </c>
       <c r="C271" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D271" t="s">
-        <v>579</v>
+        <v>626</v>
       </c>
       <c r="G271" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -6998,16 +7139,16 @@
         <v>277</v>
       </c>
       <c r="B272" t="s">
-        <v>516</v>
+        <v>539</v>
       </c>
       <c r="C272" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D272" t="s">
-        <v>579</v>
+        <v>626</v>
       </c>
       <c r="G272" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7015,16 +7156,16 @@
         <v>278</v>
       </c>
       <c r="B273" t="s">
-        <v>517</v>
+        <v>540</v>
       </c>
       <c r="C273" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D273" t="s">
-        <v>579</v>
+        <v>626</v>
       </c>
       <c r="G273" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -7032,16 +7173,16 @@
         <v>279</v>
       </c>
       <c r="B274" t="s">
-        <v>518</v>
+        <v>541</v>
       </c>
       <c r="C274" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D274" t="s">
-        <v>579</v>
+        <v>626</v>
       </c>
       <c r="G274" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -7049,16 +7190,16 @@
         <v>280</v>
       </c>
       <c r="B275" t="s">
-        <v>519</v>
+        <v>542</v>
       </c>
       <c r="C275" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D275" t="s">
-        <v>579</v>
+        <v>626</v>
       </c>
       <c r="G275" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -7066,16 +7207,16 @@
         <v>281</v>
       </c>
       <c r="B276" t="s">
-        <v>520</v>
+        <v>543</v>
       </c>
       <c r="C276" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D276" t="s">
-        <v>579</v>
+        <v>626</v>
       </c>
       <c r="G276" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -7083,16 +7224,16 @@
         <v>282</v>
       </c>
       <c r="B277" t="s">
-        <v>521</v>
+        <v>544</v>
       </c>
       <c r="C277" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D277" t="s">
-        <v>579</v>
+        <v>626</v>
       </c>
       <c r="G277" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -7100,16 +7241,16 @@
         <v>283</v>
       </c>
       <c r="B278" t="s">
-        <v>522</v>
+        <v>545</v>
       </c>
       <c r="C278" t="s">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D278" t="s">
-        <v>579</v>
+        <v>626</v>
       </c>
       <c r="G278" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7117,16 +7258,16 @@
         <v>284</v>
       </c>
       <c r="B279" t="s">
-        <v>523</v>
+        <v>546</v>
       </c>
       <c r="C279" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D279" t="s">
-        <v>579</v>
+        <v>626</v>
       </c>
       <c r="G279" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7134,16 +7275,16 @@
         <v>285</v>
       </c>
       <c r="B280" t="s">
-        <v>524</v>
+        <v>547</v>
       </c>
       <c r="C280" t="s">
-        <v>530</v>
+        <v>577</v>
       </c>
       <c r="D280" t="s">
-        <v>568</v>
+        <v>615</v>
       </c>
       <c r="G280" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -7151,16 +7292,16 @@
         <v>286</v>
       </c>
       <c r="B281" t="s">
-        <v>525</v>
+        <v>548</v>
       </c>
       <c r="C281" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D281" t="s">
-        <v>580</v>
+        <v>627</v>
       </c>
       <c r="G281" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7168,16 +7309,16 @@
         <v>287</v>
       </c>
       <c r="B282" t="s">
-        <v>526</v>
+        <v>549</v>
       </c>
       <c r="C282" t="s">
-        <v>535</v>
+        <v>582</v>
       </c>
       <c r="D282" t="s">
-        <v>568</v>
+        <v>615</v>
       </c>
       <c r="G282" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -7185,16 +7326,16 @@
         <v>288</v>
       </c>
       <c r="B283" t="s">
-        <v>527</v>
+        <v>550</v>
       </c>
       <c r="C283" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="D283" t="s">
-        <v>568</v>
+        <v>615</v>
       </c>
       <c r="G283" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -7202,19 +7343,361 @@
         <v>289</v>
       </c>
       <c r="B284" t="s">
-        <v>528</v>
+        <v>551</v>
       </c>
       <c r="C284" t="s">
-        <v>529</v>
+        <v>576</v>
       </c>
       <c r="D284" t="s">
+        <v>601</v>
+      </c>
+      <c r="F284" t="s">
+        <v>682</v>
+      </c>
+      <c r="G284" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285" t="s">
+        <v>290</v>
+      </c>
+      <c r="B285" t="s">
+        <v>552</v>
+      </c>
+      <c r="C285" t="s">
+        <v>586</v>
+      </c>
+      <c r="D285" t="s">
+        <v>626</v>
+      </c>
+      <c r="G285" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286" t="s">
+        <v>291</v>
+      </c>
+      <c r="B286" t="s">
+        <v>553</v>
+      </c>
+      <c r="C286" t="s">
+        <v>577</v>
+      </c>
+      <c r="D286" t="s">
+        <v>626</v>
+      </c>
+      <c r="G286" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287" t="s">
+        <v>292</v>
+      </c>
+      <c r="B287" t="s">
         <v>554</v>
       </c>
-      <c r="F284" t="s">
-        <v>635</v>
-      </c>
-      <c r="G284" t="s">
-        <v>655</v>
+      <c r="C287" t="s">
+        <v>580</v>
+      </c>
+      <c r="D287" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
+      <c r="A288" t="s">
+        <v>293</v>
+      </c>
+      <c r="B288" t="s">
+        <v>555</v>
+      </c>
+      <c r="C288" t="s">
+        <v>583</v>
+      </c>
+      <c r="D288" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" t="s">
+        <v>294</v>
+      </c>
+      <c r="B289" t="s">
+        <v>556</v>
+      </c>
+      <c r="C289" t="s">
+        <v>583</v>
+      </c>
+      <c r="D289" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" t="s">
+        <v>295</v>
+      </c>
+      <c r="B290" t="s">
+        <v>557</v>
+      </c>
+      <c r="C290" t="s">
+        <v>581</v>
+      </c>
+      <c r="D290" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" t="s">
+        <v>296</v>
+      </c>
+      <c r="B291" t="s">
+        <v>558</v>
+      </c>
+      <c r="C291" t="s">
+        <v>581</v>
+      </c>
+      <c r="D291" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" t="s">
+        <v>297</v>
+      </c>
+      <c r="B292" t="s">
+        <v>559</v>
+      </c>
+      <c r="C292" t="s">
+        <v>583</v>
+      </c>
+      <c r="D292" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" t="s">
+        <v>298</v>
+      </c>
+      <c r="B293" t="s">
+        <v>560</v>
+      </c>
+      <c r="C293" t="s">
+        <v>588</v>
+      </c>
+      <c r="D293" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" t="s">
+        <v>299</v>
+      </c>
+      <c r="B294" t="s">
+        <v>561</v>
+      </c>
+      <c r="C294" t="s">
+        <v>580</v>
+      </c>
+      <c r="D294" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" t="s">
+        <v>135</v>
+      </c>
+      <c r="B295" t="s">
+        <v>562</v>
+      </c>
+      <c r="C295" t="s">
+        <v>586</v>
+      </c>
+      <c r="D295" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" t="s">
+        <v>300</v>
+      </c>
+      <c r="B296" t="s">
+        <v>563</v>
+      </c>
+      <c r="C296" t="s">
+        <v>577</v>
+      </c>
+      <c r="D296" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" t="s">
+        <v>301</v>
+      </c>
+      <c r="B297" t="s">
+        <v>564</v>
+      </c>
+      <c r="C297" t="s">
+        <v>586</v>
+      </c>
+      <c r="D297" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" t="s">
+        <v>302</v>
+      </c>
+      <c r="B298" t="s">
+        <v>565</v>
+      </c>
+      <c r="C298" t="s">
+        <v>583</v>
+      </c>
+      <c r="D298" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" t="s">
+        <v>303</v>
+      </c>
+      <c r="B299" t="s">
+        <v>566</v>
+      </c>
+      <c r="C299" t="s">
+        <v>581</v>
+      </c>
+      <c r="D299" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" t="s">
+        <v>304</v>
+      </c>
+      <c r="B300" t="s">
+        <v>567</v>
+      </c>
+      <c r="C300" t="s">
+        <v>577</v>
+      </c>
+      <c r="D300" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" t="s">
+        <v>305</v>
+      </c>
+      <c r="B301" t="s">
+        <v>568</v>
+      </c>
+      <c r="C301" t="s">
+        <v>577</v>
+      </c>
+      <c r="D301" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" t="s">
+        <v>306</v>
+      </c>
+      <c r="B302" t="s">
+        <v>569</v>
+      </c>
+      <c r="C302" t="s">
+        <v>581</v>
+      </c>
+      <c r="D302" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" t="s">
+        <v>307</v>
+      </c>
+      <c r="B303" t="s">
+        <v>570</v>
+      </c>
+      <c r="C303" t="s">
+        <v>582</v>
+      </c>
+      <c r="D303" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" t="s">
+        <v>308</v>
+      </c>
+      <c r="B304" t="s">
+        <v>571</v>
+      </c>
+      <c r="C304" t="s">
+        <v>583</v>
+      </c>
+      <c r="D304" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
+      <c r="A305" t="s">
+        <v>309</v>
+      </c>
+      <c r="B305" t="s">
+        <v>572</v>
+      </c>
+      <c r="C305" t="s">
+        <v>583</v>
+      </c>
+      <c r="D305" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
+      <c r="A306" t="s">
+        <v>310</v>
+      </c>
+      <c r="B306" t="s">
+        <v>573</v>
+      </c>
+      <c r="C306" t="s">
+        <v>577</v>
+      </c>
+      <c r="D306" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
+      <c r="A307" t="s">
+        <v>311</v>
+      </c>
+      <c r="B307" t="s">
+        <v>574</v>
+      </c>
+      <c r="C307" t="s">
+        <v>577</v>
+      </c>
+      <c r="D307" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
+      <c r="A308" t="s">
+        <v>312</v>
+      </c>
+      <c r="B308" t="s">
+        <v>575</v>
+      </c>
+      <c r="C308" t="s">
+        <v>583</v>
+      </c>
+      <c r="D308" t="s">
+        <v>627</v>
       </c>
     </row>
   </sheetData>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="703">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -7405,6 +7405,9 @@
       <c r="D287" t="s">
         <v>626</v>
       </c>
+      <c r="G287" t="s">
+        <v>702</v>
+      </c>
     </row>
     <row r="288" spans="1:7">
       <c r="A288" t="s">
@@ -7419,8 +7422,11 @@
       <c r="D288" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="289" spans="1:4">
+      <c r="G288" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7">
       <c r="A289" t="s">
         <v>294</v>
       </c>
@@ -7433,8 +7439,11 @@
       <c r="D289" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="290" spans="1:4">
+      <c r="G289" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7">
       <c r="A290" t="s">
         <v>295</v>
       </c>
@@ -7447,8 +7456,11 @@
       <c r="D290" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="291" spans="1:4">
+      <c r="G290" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7">
       <c r="A291" t="s">
         <v>296</v>
       </c>
@@ -7461,8 +7473,11 @@
       <c r="D291" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="292" spans="1:4">
+      <c r="G291" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7">
       <c r="A292" t="s">
         <v>297</v>
       </c>
@@ -7475,8 +7490,11 @@
       <c r="D292" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="293" spans="1:4">
+      <c r="G292" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7">
       <c r="A293" t="s">
         <v>298</v>
       </c>
@@ -7489,8 +7507,11 @@
       <c r="D293" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="294" spans="1:4">
+      <c r="G293" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7">
       <c r="A294" t="s">
         <v>299</v>
       </c>
@@ -7503,8 +7524,11 @@
       <c r="D294" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="295" spans="1:4">
+      <c r="G294" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7">
       <c r="A295" t="s">
         <v>135</v>
       </c>
@@ -7517,8 +7541,11 @@
       <c r="D295" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="296" spans="1:4">
+      <c r="G295" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7">
       <c r="A296" t="s">
         <v>300</v>
       </c>
@@ -7531,8 +7558,11 @@
       <c r="D296" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="297" spans="1:4">
+      <c r="G296" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7">
       <c r="A297" t="s">
         <v>301</v>
       </c>
@@ -7545,8 +7575,11 @@
       <c r="D297" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="298" spans="1:4">
+      <c r="G297" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7">
       <c r="A298" t="s">
         <v>302</v>
       </c>
@@ -7559,8 +7592,11 @@
       <c r="D298" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="299" spans="1:4">
+      <c r="G298" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7">
       <c r="A299" t="s">
         <v>303</v>
       </c>
@@ -7573,8 +7609,11 @@
       <c r="D299" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="300" spans="1:4">
+      <c r="G299" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
       <c r="A300" t="s">
         <v>304</v>
       </c>
@@ -7587,8 +7626,11 @@
       <c r="D300" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="301" spans="1:4">
+      <c r="G300" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7">
       <c r="A301" t="s">
         <v>305</v>
       </c>
@@ -7601,8 +7643,11 @@
       <c r="D301" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="302" spans="1:4">
+      <c r="G301" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7">
       <c r="A302" t="s">
         <v>306</v>
       </c>
@@ -7615,8 +7660,11 @@
       <c r="D302" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="303" spans="1:4">
+      <c r="G302" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7">
       <c r="A303" t="s">
         <v>307</v>
       </c>
@@ -7629,8 +7677,11 @@
       <c r="D303" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="304" spans="1:4">
+      <c r="G303" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7">
       <c r="A304" t="s">
         <v>308</v>
       </c>
@@ -7643,8 +7694,11 @@
       <c r="D304" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="305" spans="1:4">
+      <c r="G304" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7">
       <c r="A305" t="s">
         <v>309</v>
       </c>
@@ -7657,8 +7711,11 @@
       <c r="D305" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="306" spans="1:4">
+      <c r="G305" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7">
       <c r="A306" t="s">
         <v>310</v>
       </c>
@@ -7671,8 +7728,11 @@
       <c r="D306" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="307" spans="1:4">
+      <c r="G306" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7">
       <c r="A307" t="s">
         <v>311</v>
       </c>
@@ -7685,8 +7745,11 @@
       <c r="D307" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="308" spans="1:4">
+      <c r="G307" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7">
       <c r="A308" t="s">
         <v>312</v>
       </c>
@@ -7698,6 +7761,9 @@
       </c>
       <c r="D308" t="s">
         <v>627</v>
+      </c>
+      <c r="G308" t="s">
+        <v>702</v>
       </c>
     </row>
   </sheetData>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="731">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -955,6 +955,42 @@
     <t>Garlandale - Rondebosch East Residents' Association</t>
   </si>
   <si>
+    <t>Observatory Improvement District</t>
+  </si>
+  <si>
+    <t>Rosebank Residents Association</t>
+  </si>
+  <si>
+    <t>Woodstock Peace Alliance</t>
+  </si>
+  <si>
+    <t>Salt River Circle</t>
+  </si>
+  <si>
+    <t>Claremont Methodist Church</t>
+  </si>
+  <si>
+    <t>Newlands Residents Association</t>
+  </si>
+  <si>
+    <t>Wynberg Boys High School</t>
+  </si>
+  <si>
+    <t>Wynberg Girls High School</t>
+  </si>
+  <si>
+    <t>Lansdowne Civic Association</t>
+  </si>
+  <si>
+    <t>Kenilworth Racecourse Conservation Area</t>
+  </si>
+  <si>
+    <t>Little Theatre (UCT)</t>
+  </si>
+  <si>
+    <t>Mosterts Mill Restoration Trust</t>
+  </si>
+  <si>
     <t>info@ctsc.org.za</t>
   </si>
   <si>
@@ -1744,6 +1780,42 @@
     <t>roekeya@damonabadia.co.za</t>
   </si>
   <si>
+    <t>info@obsid.co.za</t>
+  </si>
+  <si>
+    <t>info@rosebankra.co.za</t>
+  </si>
+  <si>
+    <t>info@woodstockpeace.org.za</t>
+  </si>
+  <si>
+    <t>info@saltrivercircle.co.za</t>
+  </si>
+  <si>
+    <t>office@claremontmethodist.org.za</t>
+  </si>
+  <si>
+    <t>info@newlandsra.co.za</t>
+  </si>
+  <si>
+    <t>info@wbhs.org.za</t>
+  </si>
+  <si>
+    <t>info@wghs.co.za</t>
+  </si>
+  <si>
+    <t>info@lansdownecivic.co.za</t>
+  </si>
+  <si>
+    <t>info@kenilworthracecourse.co.za</t>
+  </si>
+  <si>
+    <t>littletheatre@uct.ac.za</t>
+  </si>
+  <si>
+    <t>info@mostertsmill.org.za</t>
+  </si>
+  <si>
     <t>Museums &amp; Heritage</t>
   </si>
   <si>
@@ -1898,6 +1970,18 @@
   </si>
   <si>
     <t>Rondebosch East</t>
+  </si>
+  <si>
+    <t>Rosebank</t>
+  </si>
+  <si>
+    <t>Newlands</t>
+  </si>
+  <si>
+    <t>Lansdowne</t>
+  </si>
+  <si>
+    <t>Kenilworth</t>
   </si>
   <si>
     <t>021 300 3200</t>
@@ -2467,7 +2551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G308"/>
+  <dimension ref="A1:G320"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2498,22 +2582,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="C2" t="s">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="D2" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E2" t="s">
-        <v>628</v>
+        <v>656</v>
       </c>
       <c r="F2" t="s">
-        <v>682</v>
+        <v>710</v>
       </c>
       <c r="G2" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2521,22 +2605,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="C3" t="s">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="D3" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E3" t="s">
-        <v>628</v>
+        <v>656</v>
       </c>
       <c r="F3" t="s">
-        <v>682</v>
+        <v>710</v>
       </c>
       <c r="G3" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2544,22 +2628,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="C4" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D4" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E4" t="s">
-        <v>628</v>
+        <v>656</v>
       </c>
       <c r="F4" t="s">
-        <v>682</v>
+        <v>710</v>
       </c>
       <c r="G4" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2567,22 +2651,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="C5" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D5" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E5" t="s">
-        <v>628</v>
+        <v>656</v>
       </c>
       <c r="F5" t="s">
-        <v>682</v>
+        <v>710</v>
       </c>
       <c r="G5" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2590,22 +2674,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="C6" t="s">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="D6" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E6" t="s">
-        <v>628</v>
+        <v>656</v>
       </c>
       <c r="F6" t="s">
-        <v>682</v>
+        <v>710</v>
       </c>
       <c r="G6" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2613,22 +2697,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="C7" t="s">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="D7" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E7" t="s">
-        <v>628</v>
+        <v>656</v>
       </c>
       <c r="F7" t="s">
-        <v>682</v>
+        <v>710</v>
       </c>
       <c r="G7" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2636,22 +2720,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="C8" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D8" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E8" t="s">
-        <v>628</v>
+        <v>656</v>
       </c>
       <c r="F8" t="s">
-        <v>682</v>
+        <v>710</v>
       </c>
       <c r="G8" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2659,22 +2743,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="C9" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D9" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E9" t="s">
-        <v>628</v>
+        <v>656</v>
       </c>
       <c r="F9" t="s">
-        <v>682</v>
+        <v>710</v>
       </c>
       <c r="G9" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2682,22 +2766,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="C10" t="s">
-        <v>578</v>
+        <v>602</v>
       </c>
       <c r="D10" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E10" t="s">
-        <v>628</v>
+        <v>656</v>
       </c>
       <c r="F10" t="s">
-        <v>682</v>
+        <v>710</v>
       </c>
       <c r="G10" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2705,22 +2789,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="C11" t="s">
-        <v>578</v>
+        <v>602</v>
       </c>
       <c r="D11" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E11" t="s">
-        <v>628</v>
+        <v>656</v>
       </c>
       <c r="F11" t="s">
-        <v>682</v>
+        <v>710</v>
       </c>
       <c r="G11" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2728,22 +2812,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="C12" t="s">
-        <v>579</v>
+        <v>603</v>
       </c>
       <c r="D12" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E12" t="s">
-        <v>628</v>
+        <v>656</v>
       </c>
       <c r="F12" t="s">
-        <v>682</v>
+        <v>710</v>
       </c>
       <c r="G12" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2751,22 +2835,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="C13" t="s">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="D13" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E13" t="s">
-        <v>628</v>
+        <v>656</v>
       </c>
       <c r="F13" t="s">
-        <v>682</v>
+        <v>710</v>
       </c>
       <c r="G13" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2774,22 +2858,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="C14" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D14" t="s">
-        <v>602</v>
+        <v>626</v>
       </c>
       <c r="E14" t="s">
-        <v>629</v>
+        <v>657</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>683</v>
+        <v>711</v>
       </c>
       <c r="G14" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2797,22 +2881,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="C15" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D15" t="s">
-        <v>602</v>
+        <v>626</v>
       </c>
       <c r="E15" t="s">
-        <v>630</v>
+        <v>658</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>684</v>
+        <v>712</v>
       </c>
       <c r="G15" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2820,16 +2904,16 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="C16" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D16" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G16" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2837,16 +2921,16 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="C17" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D17" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G17" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2854,16 +2938,16 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="C18" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D18" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G18" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2871,16 +2955,16 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="C19" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D19" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G19" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2888,16 +2972,16 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="C20" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D20" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G20" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2905,16 +2989,16 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="C21" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D21" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G21" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2922,16 +3006,16 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="C22" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D22" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G22" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2939,16 +3023,16 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="C23" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D23" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G23" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2956,16 +3040,16 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="C24" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D24" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G24" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2973,16 +3057,16 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="C25" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D25" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G25" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2990,16 +3074,16 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="C26" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="D26" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G26" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3007,16 +3091,16 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="C27" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="D27" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G27" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -3024,16 +3108,16 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="C28" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="D28" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G28" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3041,16 +3125,16 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="C29" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="D29" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G29" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -3058,16 +3142,16 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="C30" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="D30" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G30" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3075,16 +3159,16 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="C31" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="D31" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G31" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3092,16 +3176,16 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="C32" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="D32" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G32" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3109,16 +3193,16 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="C33" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D33" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G33" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -3126,16 +3210,16 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="C34" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D34" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G34" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -3143,16 +3227,16 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="C35" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D35" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G35" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3160,16 +3244,16 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="C36" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D36" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G36" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -3177,16 +3261,16 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C37" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D37" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G37" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -3194,16 +3278,16 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C38" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D38" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G38" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -3211,16 +3295,16 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="C39" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D39" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G39" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3228,16 +3312,16 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C40" t="s">
-        <v>584</v>
+        <v>608</v>
       </c>
       <c r="D40" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G40" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -3245,16 +3329,16 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="C41" t="s">
-        <v>584</v>
+        <v>608</v>
       </c>
       <c r="D41" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G41" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3262,16 +3346,16 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="C42" t="s">
-        <v>584</v>
+        <v>608</v>
       </c>
       <c r="D42" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G42" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3279,16 +3363,16 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="C43" t="s">
-        <v>584</v>
+        <v>608</v>
       </c>
       <c r="D43" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G43" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3296,16 +3380,16 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="C44" t="s">
-        <v>584</v>
+        <v>608</v>
       </c>
       <c r="D44" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G44" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3313,16 +3397,16 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="C45" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D45" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G45" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3330,16 +3414,16 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="C46" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D46" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G46" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3347,16 +3431,16 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="C47" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D47" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G47" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3364,16 +3448,16 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="C48" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D48" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G48" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -3381,16 +3465,16 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="C49" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D49" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G49" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -3398,16 +3482,16 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="C50" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D50" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G50" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -3415,16 +3499,16 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="C51" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D51" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G51" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -3432,16 +3516,16 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="C52" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D52" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G52" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -3449,16 +3533,16 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="C53" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D53" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G53" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3466,16 +3550,16 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="C54" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D54" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G54" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -3483,16 +3567,16 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="C55" t="s">
-        <v>585</v>
+        <v>609</v>
       </c>
       <c r="D55" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G55" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3500,16 +3584,16 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="C56" t="s">
-        <v>585</v>
+        <v>609</v>
       </c>
       <c r="D56" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G56" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3517,16 +3601,16 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="C57" t="s">
-        <v>585</v>
+        <v>609</v>
       </c>
       <c r="D57" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G57" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3534,16 +3618,16 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="C58" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D58" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G58" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3551,16 +3635,16 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="C59" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D59" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G59" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3568,16 +3652,16 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C60" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D60" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G60" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3585,16 +3669,16 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="C61" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D61" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G61" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3602,16 +3686,16 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C62" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D62" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G62" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3619,16 +3703,16 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="C63" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D63" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G63" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3636,16 +3720,16 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="C64" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D64" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G64" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3653,16 +3737,16 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="C65" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D65" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G65" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3670,16 +3754,16 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="C66" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D66" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G66" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3687,16 +3771,16 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="C67" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D67" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G67" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3704,16 +3788,16 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C68" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D68" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G68" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3721,16 +3805,16 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="C69" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="D69" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G69" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3738,16 +3822,16 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="C70" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="D70" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G70" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3755,16 +3839,16 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="C71" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="D71" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G71" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3772,16 +3856,16 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="C72" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="D72" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G72" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3789,16 +3873,16 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="C73" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="D73" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G73" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3806,16 +3890,16 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="C74" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="D74" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G74" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3823,16 +3907,16 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="C75" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D75" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G75" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3840,16 +3924,16 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="C76" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D76" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G76" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3857,16 +3941,16 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="C77" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D77" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G77" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3874,16 +3958,16 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="C78" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D78" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G78" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3891,16 +3975,16 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="C79" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D79" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G79" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3908,16 +3992,16 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="C80" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D80" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G80" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3925,16 +4009,16 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="C81" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D81" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G81" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3942,16 +4026,16 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="C82" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D82" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G82" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3959,16 +4043,16 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="C83" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D83" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G83" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3976,16 +4060,16 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="C84" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D84" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G84" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3993,16 +4077,16 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="C85" t="s">
-        <v>584</v>
+        <v>608</v>
       </c>
       <c r="D85" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G85" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4010,16 +4094,16 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="C86" t="s">
-        <v>584</v>
+        <v>608</v>
       </c>
       <c r="D86" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G86" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4027,16 +4111,16 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="C87" t="s">
-        <v>584</v>
+        <v>608</v>
       </c>
       <c r="D87" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G87" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4044,16 +4128,16 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="C88" t="s">
-        <v>584</v>
+        <v>608</v>
       </c>
       <c r="D88" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G88" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4061,16 +4145,16 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="C89" t="s">
-        <v>584</v>
+        <v>608</v>
       </c>
       <c r="D89" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G89" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4078,16 +4162,16 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="C90" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D90" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G90" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4095,16 +4179,16 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="C91" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D91" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G91" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4112,16 +4196,16 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="C92" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D92" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G92" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -4129,16 +4213,16 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="C93" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D93" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G93" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -4146,16 +4230,16 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="C94" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D94" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G94" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -4163,16 +4247,16 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="C95" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D95" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G95" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -4180,16 +4264,16 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="C96" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D96" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G96" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4197,16 +4281,16 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="C97" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D97" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G97" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4214,16 +4298,16 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="C98" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D98" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G98" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4231,16 +4315,16 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="C99" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D99" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G99" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4248,16 +4332,16 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="C100" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D100" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G100" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4265,16 +4349,16 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="C101" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D101" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G101" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4282,16 +4366,16 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="C102" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D102" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G102" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4299,16 +4383,16 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="C103" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D103" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G103" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4316,16 +4400,16 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="C104" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D104" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G104" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4333,16 +4417,16 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="C105" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D105" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G105" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4350,16 +4434,16 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="C106" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D106" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G106" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4367,16 +4451,16 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="C107" t="s">
-        <v>585</v>
+        <v>609</v>
       </c>
       <c r="D107" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G107" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4384,16 +4468,16 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="C108" t="s">
-        <v>585</v>
+        <v>609</v>
       </c>
       <c r="D108" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G108" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4401,16 +4485,16 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C109" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D109" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G109" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4418,16 +4502,16 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="C110" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D110" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G110" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4435,16 +4519,16 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="C111" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D111" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G111" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4452,16 +4536,16 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="C112" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D112" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G112" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4469,16 +4553,16 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="C113" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D113" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G113" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4486,16 +4570,16 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="C114" t="s">
-        <v>587</v>
+        <v>611</v>
       </c>
       <c r="D114" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G114" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4503,16 +4587,16 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="C115" t="s">
-        <v>587</v>
+        <v>611</v>
       </c>
       <c r="D115" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G115" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4520,16 +4604,16 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="C116" t="s">
-        <v>587</v>
+        <v>611</v>
       </c>
       <c r="D116" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G116" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4537,16 +4621,16 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="C117" t="s">
-        <v>587</v>
+        <v>611</v>
       </c>
       <c r="D117" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G117" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4554,16 +4638,16 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="C118" t="s">
-        <v>587</v>
+        <v>611</v>
       </c>
       <c r="D118" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G118" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4571,22 +4655,22 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="C119" t="s">
-        <v>587</v>
+        <v>611</v>
       </c>
       <c r="D119" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E119" t="s">
-        <v>631</v>
+        <v>659</v>
       </c>
       <c r="F119" t="s">
-        <v>685</v>
+        <v>713</v>
       </c>
       <c r="G119" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4594,19 +4678,19 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="C120" t="s">
-        <v>587</v>
+        <v>611</v>
       </c>
       <c r="D120" t="s">
-        <v>603</v>
+        <v>627</v>
       </c>
       <c r="E120" t="s">
-        <v>632</v>
+        <v>660</v>
       </c>
       <c r="G120" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4614,16 +4698,16 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="C121" t="s">
-        <v>587</v>
+        <v>611</v>
       </c>
       <c r="D121" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G121" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4631,16 +4715,16 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="C122" t="s">
-        <v>585</v>
+        <v>609</v>
       </c>
       <c r="D122" t="s">
-        <v>604</v>
+        <v>628</v>
       </c>
       <c r="G122" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4648,22 +4732,22 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="C123" t="s">
-        <v>585</v>
+        <v>609</v>
       </c>
       <c r="D123" t="s">
-        <v>605</v>
+        <v>629</v>
       </c>
       <c r="E123" t="s">
-        <v>633</v>
+        <v>661</v>
       </c>
       <c r="F123" t="s">
-        <v>686</v>
+        <v>714</v>
       </c>
       <c r="G123" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4671,16 +4755,16 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="C124" t="s">
-        <v>585</v>
+        <v>609</v>
       </c>
       <c r="D124" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G124" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4688,16 +4772,16 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="C125" t="s">
-        <v>585</v>
+        <v>609</v>
       </c>
       <c r="D125" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G125" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4705,16 +4789,16 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C126" t="s">
-        <v>585</v>
+        <v>609</v>
       </c>
       <c r="D126" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G126" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4722,16 +4806,16 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="C127" t="s">
-        <v>585</v>
+        <v>609</v>
       </c>
       <c r="D127" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G127" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4739,19 +4823,19 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="C128" t="s">
-        <v>585</v>
+        <v>609</v>
       </c>
       <c r="D128" t="s">
-        <v>606</v>
+        <v>630</v>
       </c>
       <c r="E128" t="s">
-        <v>634</v>
+        <v>662</v>
       </c>
       <c r="G128" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4759,22 +4843,22 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="C129" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D129" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E129" t="s">
-        <v>635</v>
+        <v>663</v>
       </c>
       <c r="F129" t="s">
-        <v>687</v>
+        <v>715</v>
       </c>
       <c r="G129" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4782,16 +4866,16 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="C130" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D130" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G130" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4799,13 +4883,13 @@
         <v>136</v>
       </c>
       <c r="C131" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D131" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="E131" t="s">
-        <v>636</v>
+        <v>664</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4813,19 +4897,19 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="C132" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D132" t="s">
-        <v>608</v>
+        <v>632</v>
       </c>
       <c r="E132" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
       <c r="G132" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4833,19 +4917,19 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="C133" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D133" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="E133" t="s">
-        <v>638</v>
+        <v>666</v>
       </c>
       <c r="G133" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4853,10 +4937,10 @@
         <v>139</v>
       </c>
       <c r="C134" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D134" t="s">
-        <v>610</v>
+        <v>634</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4864,10 +4948,10 @@
         <v>140</v>
       </c>
       <c r="C135" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D135" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4875,16 +4959,16 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="C136" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D136" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G136" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4892,16 +4976,16 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="C137" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D137" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="G137" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4909,10 +4993,10 @@
         <v>143</v>
       </c>
       <c r="C138" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D138" t="s">
-        <v>611</v>
+        <v>635</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4920,10 +5004,10 @@
         <v>144</v>
       </c>
       <c r="C139" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D139" t="s">
-        <v>612</v>
+        <v>636</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4931,10 +5015,10 @@
         <v>145</v>
       </c>
       <c r="C140" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D140" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4942,16 +5026,16 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="C141" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D141" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G141" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4959,22 +5043,22 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="C142" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D142" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E142" t="s">
-        <v>639</v>
+        <v>667</v>
       </c>
       <c r="F142" t="s">
-        <v>688</v>
+        <v>716</v>
       </c>
       <c r="G142" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4982,16 +5066,16 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="C143" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D143" t="s">
-        <v>611</v>
+        <v>635</v>
       </c>
       <c r="G143" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4999,13 +5083,13 @@
         <v>149</v>
       </c>
       <c r="C144" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D144" t="s">
-        <v>613</v>
+        <v>637</v>
       </c>
       <c r="E144" t="s">
-        <v>640</v>
+        <v>668</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -5013,10 +5097,10 @@
         <v>150</v>
       </c>
       <c r="C145" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D145" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -5024,19 +5108,19 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="C146" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D146" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="F146" t="s">
-        <v>689</v>
+        <v>717</v>
       </c>
       <c r="G146" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -5044,22 +5128,22 @@
         <v>152</v>
       </c>
       <c r="B147" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="C147" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D147" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E147" t="s">
-        <v>641</v>
+        <v>669</v>
       </c>
       <c r="F147" t="s">
-        <v>690</v>
+        <v>718</v>
       </c>
       <c r="G147" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5067,19 +5151,19 @@
         <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="C148" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D148" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E148" t="s">
-        <v>642</v>
+        <v>670</v>
       </c>
       <c r="G148" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5087,19 +5171,19 @@
         <v>154</v>
       </c>
       <c r="B149" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="C149" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D149" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E149" t="s">
-        <v>643</v>
+        <v>671</v>
       </c>
       <c r="G149" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5107,19 +5191,19 @@
         <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="C150" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D150" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E150" t="s">
-        <v>644</v>
+        <v>672</v>
       </c>
       <c r="G150" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5127,19 +5211,19 @@
         <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="C151" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D151" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E151" t="s">
-        <v>645</v>
+        <v>673</v>
       </c>
       <c r="G151" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5147,19 +5231,19 @@
         <v>157</v>
       </c>
       <c r="B152" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="C152" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D152" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E152" t="s">
-        <v>646</v>
+        <v>674</v>
       </c>
       <c r="G152" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5167,10 +5251,10 @@
         <v>158</v>
       </c>
       <c r="C153" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D153" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5178,19 +5262,19 @@
         <v>159</v>
       </c>
       <c r="B154" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="C154" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D154" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E154" t="s">
-        <v>647</v>
+        <v>675</v>
       </c>
       <c r="G154" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5198,16 +5282,16 @@
         <v>160</v>
       </c>
       <c r="B155" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="C155" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D155" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G155" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5215,16 +5299,16 @@
         <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="C156" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D156" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G156" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5232,22 +5316,22 @@
         <v>162</v>
       </c>
       <c r="B157" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="C157" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D157" t="s">
-        <v>614</v>
+        <v>638</v>
       </c>
       <c r="E157" t="s">
-        <v>648</v>
+        <v>676</v>
       </c>
       <c r="F157" t="s">
-        <v>691</v>
+        <v>719</v>
       </c>
       <c r="G157" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5255,19 +5339,19 @@
         <v>163</v>
       </c>
       <c r="B158" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="C158" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D158" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E158" t="s">
-        <v>649</v>
+        <v>677</v>
       </c>
       <c r="G158" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5275,19 +5359,19 @@
         <v>164</v>
       </c>
       <c r="B159" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="C159" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D159" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E159" t="s">
-        <v>650</v>
+        <v>678</v>
       </c>
       <c r="G159" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5295,19 +5379,19 @@
         <v>165</v>
       </c>
       <c r="B160" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="C160" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D160" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E160" t="s">
-        <v>651</v>
+        <v>679</v>
       </c>
       <c r="G160" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5315,19 +5399,19 @@
         <v>166</v>
       </c>
       <c r="B161" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="C161" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D161" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="E161" t="s">
-        <v>652</v>
+        <v>680</v>
       </c>
       <c r="G161" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5335,16 +5419,16 @@
         <v>167</v>
       </c>
       <c r="B162" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="C162" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D162" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G162" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5352,19 +5436,19 @@
         <v>168</v>
       </c>
       <c r="B163" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="C163" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D163" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E163" t="s">
-        <v>653</v>
+        <v>681</v>
       </c>
       <c r="G163" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5372,19 +5456,19 @@
         <v>169</v>
       </c>
       <c r="B164" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="C164" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D164" t="s">
-        <v>616</v>
+        <v>640</v>
       </c>
       <c r="E164" t="s">
-        <v>654</v>
+        <v>682</v>
       </c>
       <c r="G164" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5392,13 +5476,13 @@
         <v>170</v>
       </c>
       <c r="C165" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D165" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="E165" t="s">
-        <v>655</v>
+        <v>683</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5406,19 +5490,19 @@
         <v>171</v>
       </c>
       <c r="B166" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="C166" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D166" t="s">
-        <v>617</v>
+        <v>641</v>
       </c>
       <c r="E166" t="s">
-        <v>656</v>
+        <v>684</v>
       </c>
       <c r="G166" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5426,19 +5510,19 @@
         <v>172</v>
       </c>
       <c r="B167" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="C167" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D167" t="s">
-        <v>618</v>
+        <v>642</v>
       </c>
       <c r="E167" t="s">
-        <v>657</v>
+        <v>685</v>
       </c>
       <c r="G167" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5446,19 +5530,19 @@
         <v>173</v>
       </c>
       <c r="B168" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="C168" t="s">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="D168" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E168" t="s">
-        <v>658</v>
+        <v>686</v>
       </c>
       <c r="G168" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5466,19 +5550,19 @@
         <v>174</v>
       </c>
       <c r="B169" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="C169" t="s">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="D169" t="s">
-        <v>619</v>
+        <v>643</v>
       </c>
       <c r="E169" t="s">
-        <v>659</v>
+        <v>687</v>
       </c>
       <c r="G169" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5486,13 +5570,13 @@
         <v>175</v>
       </c>
       <c r="C170" t="s">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="D170" t="s">
-        <v>620</v>
+        <v>644</v>
       </c>
       <c r="E170" t="s">
-        <v>660</v>
+        <v>688</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5500,13 +5584,13 @@
         <v>176</v>
       </c>
       <c r="C171" t="s">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="D171" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E171" t="s">
-        <v>661</v>
+        <v>689</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5514,13 +5598,13 @@
         <v>177</v>
       </c>
       <c r="C172" t="s">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="D172" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="E172" t="s">
-        <v>662</v>
+        <v>690</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5528,16 +5612,16 @@
         <v>178</v>
       </c>
       <c r="B173" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="C173" t="s">
-        <v>588</v>
+        <v>612</v>
       </c>
       <c r="D173" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G173" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5545,19 +5629,19 @@
         <v>179</v>
       </c>
       <c r="B174" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="C174" t="s">
-        <v>588</v>
+        <v>612</v>
       </c>
       <c r="D174" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="F174" t="s">
-        <v>692</v>
+        <v>720</v>
       </c>
       <c r="G174" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5565,19 +5649,19 @@
         <v>180</v>
       </c>
       <c r="B175" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="C175" t="s">
-        <v>588</v>
+        <v>612</v>
       </c>
       <c r="D175" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="F175" t="s">
-        <v>693</v>
+        <v>721</v>
       </c>
       <c r="G175" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5585,10 +5669,10 @@
         <v>181</v>
       </c>
       <c r="C176" t="s">
-        <v>589</v>
+        <v>613</v>
       </c>
       <c r="D176" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5596,10 +5680,10 @@
         <v>182</v>
       </c>
       <c r="C177" t="s">
-        <v>589</v>
+        <v>613</v>
       </c>
       <c r="D177" t="s">
-        <v>621</v>
+        <v>645</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5607,10 +5691,10 @@
         <v>183</v>
       </c>
       <c r="C178" t="s">
-        <v>589</v>
+        <v>613</v>
       </c>
       <c r="D178" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5618,22 +5702,22 @@
         <v>184</v>
       </c>
       <c r="B179" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="C179" t="s">
-        <v>590</v>
+        <v>614</v>
       </c>
       <c r="D179" t="s">
-        <v>621</v>
+        <v>645</v>
       </c>
       <c r="E179" t="s">
-        <v>663</v>
+        <v>691</v>
       </c>
       <c r="F179" t="s">
-        <v>694</v>
+        <v>722</v>
       </c>
       <c r="G179" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5641,10 +5725,10 @@
         <v>185</v>
       </c>
       <c r="C180" t="s">
-        <v>590</v>
+        <v>614</v>
       </c>
       <c r="D180" t="s">
-        <v>622</v>
+        <v>646</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5652,10 +5736,10 @@
         <v>186</v>
       </c>
       <c r="C181" t="s">
-        <v>590</v>
+        <v>614</v>
       </c>
       <c r="D181" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5663,19 +5747,19 @@
         <v>187</v>
       </c>
       <c r="B182" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="C182" t="s">
-        <v>591</v>
+        <v>615</v>
       </c>
       <c r="D182" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E182" t="s">
-        <v>664</v>
+        <v>692</v>
       </c>
       <c r="G182" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5683,19 +5767,19 @@
         <v>188</v>
       </c>
       <c r="B183" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="C183" t="s">
-        <v>591</v>
+        <v>615</v>
       </c>
       <c r="D183" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="F183" t="s">
-        <v>695</v>
+        <v>723</v>
       </c>
       <c r="G183" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5703,10 +5787,10 @@
         <v>189</v>
       </c>
       <c r="C184" t="s">
-        <v>591</v>
+        <v>615</v>
       </c>
       <c r="D184" t="s">
-        <v>622</v>
+        <v>646</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5714,13 +5798,13 @@
         <v>190</v>
       </c>
       <c r="C185" t="s">
-        <v>591</v>
+        <v>615</v>
       </c>
       <c r="D185" t="s">
-        <v>623</v>
+        <v>647</v>
       </c>
       <c r="F185" t="s">
-        <v>696</v>
+        <v>724</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5728,13 +5812,13 @@
         <v>191</v>
       </c>
       <c r="C186" t="s">
-        <v>592</v>
+        <v>616</v>
       </c>
       <c r="D186" t="s">
-        <v>624</v>
+        <v>648</v>
       </c>
       <c r="E186" t="s">
-        <v>665</v>
+        <v>693</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5742,13 +5826,13 @@
         <v>192</v>
       </c>
       <c r="C187" t="s">
-        <v>592</v>
+        <v>616</v>
       </c>
       <c r="D187" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E187" t="s">
-        <v>666</v>
+        <v>694</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5756,13 +5840,13 @@
         <v>193</v>
       </c>
       <c r="C188" t="s">
-        <v>592</v>
+        <v>616</v>
       </c>
       <c r="D188" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E188" t="s">
-        <v>667</v>
+        <v>695</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5770,13 +5854,13 @@
         <v>194</v>
       </c>
       <c r="C189" t="s">
-        <v>592</v>
+        <v>616</v>
       </c>
       <c r="D189" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E189" t="s">
-        <v>668</v>
+        <v>696</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5784,13 +5868,13 @@
         <v>195</v>
       </c>
       <c r="C190" t="s">
-        <v>592</v>
+        <v>616</v>
       </c>
       <c r="D190" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E190" t="s">
-        <v>669</v>
+        <v>697</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5798,10 +5882,10 @@
         <v>196</v>
       </c>
       <c r="C191" t="s">
-        <v>592</v>
+        <v>616</v>
       </c>
       <c r="D191" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -5809,10 +5893,10 @@
         <v>197</v>
       </c>
       <c r="C192" t="s">
-        <v>592</v>
+        <v>616</v>
       </c>
       <c r="D192" t="s">
-        <v>625</v>
+        <v>649</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -5820,10 +5904,10 @@
         <v>198</v>
       </c>
       <c r="C193" t="s">
-        <v>592</v>
+        <v>616</v>
       </c>
       <c r="D193" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -5831,16 +5915,16 @@
         <v>199</v>
       </c>
       <c r="B194" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="C194" t="s">
-        <v>592</v>
+        <v>616</v>
       </c>
       <c r="D194" t="s">
-        <v>604</v>
+        <v>628</v>
       </c>
       <c r="G194" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -5848,16 +5932,16 @@
         <v>200</v>
       </c>
       <c r="B195" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="C195" t="s">
-        <v>592</v>
+        <v>616</v>
       </c>
       <c r="D195" t="s">
-        <v>604</v>
+        <v>628</v>
       </c>
       <c r="G195" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -5865,19 +5949,19 @@
         <v>201</v>
       </c>
       <c r="B196" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C196" t="s">
-        <v>579</v>
+        <v>603</v>
       </c>
       <c r="D196" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="F196" t="s">
-        <v>697</v>
+        <v>725</v>
       </c>
       <c r="G196" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -5885,22 +5969,22 @@
         <v>202</v>
       </c>
       <c r="B197" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="C197" t="s">
-        <v>579</v>
+        <v>603</v>
       </c>
       <c r="D197" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E197" t="s">
-        <v>670</v>
+        <v>698</v>
       </c>
       <c r="F197" t="s">
-        <v>698</v>
+        <v>726</v>
       </c>
       <c r="G197" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -5908,22 +5992,22 @@
         <v>203</v>
       </c>
       <c r="B198" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="C198" t="s">
-        <v>579</v>
+        <v>603</v>
       </c>
       <c r="D198" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E198" t="s">
-        <v>671</v>
+        <v>699</v>
       </c>
       <c r="F198" t="s">
-        <v>699</v>
+        <v>727</v>
       </c>
       <c r="G198" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -5931,22 +6015,22 @@
         <v>204</v>
       </c>
       <c r="B199" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="C199" t="s">
-        <v>579</v>
+        <v>603</v>
       </c>
       <c r="D199" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E199" t="s">
-        <v>672</v>
+        <v>700</v>
       </c>
       <c r="F199" t="s">
-        <v>700</v>
+        <v>728</v>
       </c>
       <c r="G199" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -5954,16 +6038,16 @@
         <v>205</v>
       </c>
       <c r="B200" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="C200" t="s">
-        <v>593</v>
+        <v>617</v>
       </c>
       <c r="D200" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G200" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -5971,10 +6055,10 @@
         <v>206</v>
       </c>
       <c r="C201" t="s">
-        <v>593</v>
+        <v>617</v>
       </c>
       <c r="D201" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -5982,10 +6066,10 @@
         <v>207</v>
       </c>
       <c r="C202" t="s">
-        <v>593</v>
+        <v>617</v>
       </c>
       <c r="D202" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -5993,10 +6077,10 @@
         <v>208</v>
       </c>
       <c r="C203" t="s">
-        <v>593</v>
+        <v>617</v>
       </c>
       <c r="D203" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6004,16 +6088,16 @@
         <v>209</v>
       </c>
       <c r="B204" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="C204" t="s">
-        <v>594</v>
+        <v>618</v>
       </c>
       <c r="D204" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G204" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6021,10 +6105,10 @@
         <v>210</v>
       </c>
       <c r="C205" t="s">
-        <v>594</v>
+        <v>618</v>
       </c>
       <c r="D205" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6032,10 +6116,10 @@
         <v>211</v>
       </c>
       <c r="C206" t="s">
-        <v>594</v>
+        <v>618</v>
       </c>
       <c r="D206" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6043,19 +6127,19 @@
         <v>212</v>
       </c>
       <c r="B207" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="C207" t="s">
-        <v>594</v>
+        <v>618</v>
       </c>
       <c r="D207" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E207" t="s">
-        <v>673</v>
+        <v>701</v>
       </c>
       <c r="G207" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6063,13 +6147,13 @@
         <v>213</v>
       </c>
       <c r="C208" t="s">
-        <v>594</v>
+        <v>618</v>
       </c>
       <c r="D208" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E208" t="s">
-        <v>674</v>
+        <v>702</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6077,10 +6161,10 @@
         <v>214</v>
       </c>
       <c r="C209" t="s">
-        <v>594</v>
+        <v>618</v>
       </c>
       <c r="D209" t="s">
-        <v>610</v>
+        <v>634</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6088,19 +6172,19 @@
         <v>215</v>
       </c>
       <c r="B210" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="C210" t="s">
-        <v>595</v>
+        <v>619</v>
       </c>
       <c r="D210" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E210" t="s">
-        <v>675</v>
+        <v>703</v>
       </c>
       <c r="G210" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6108,16 +6192,16 @@
         <v>216</v>
       </c>
       <c r="B211" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="C211" t="s">
-        <v>595</v>
+        <v>619</v>
       </c>
       <c r="D211" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G211" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6125,13 +6209,13 @@
         <v>217</v>
       </c>
       <c r="C212" t="s">
-        <v>595</v>
+        <v>619</v>
       </c>
       <c r="D212" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E212" t="s">
-        <v>676</v>
+        <v>704</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6139,13 +6223,13 @@
         <v>218</v>
       </c>
       <c r="C213" t="s">
-        <v>595</v>
+        <v>619</v>
       </c>
       <c r="D213" t="s">
-        <v>614</v>
+        <v>638</v>
       </c>
       <c r="E213" t="s">
-        <v>677</v>
+        <v>705</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6153,16 +6237,16 @@
         <v>219</v>
       </c>
       <c r="B214" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="C214" t="s">
-        <v>578</v>
+        <v>602</v>
       </c>
       <c r="D214" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G214" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6170,16 +6254,16 @@
         <v>220</v>
       </c>
       <c r="B215" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="C215" t="s">
-        <v>578</v>
+        <v>602</v>
       </c>
       <c r="D215" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G215" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6187,13 +6271,13 @@
         <v>221</v>
       </c>
       <c r="C216" t="s">
-        <v>578</v>
+        <v>602</v>
       </c>
       <c r="D216" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E216" t="s">
-        <v>678</v>
+        <v>706</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6201,19 +6285,19 @@
         <v>222</v>
       </c>
       <c r="B217" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C217" t="s">
-        <v>596</v>
+        <v>620</v>
       </c>
       <c r="D217" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E217" t="s">
-        <v>679</v>
+        <v>707</v>
       </c>
       <c r="G217" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6221,19 +6305,19 @@
         <v>223</v>
       </c>
       <c r="B218" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="C218" t="s">
-        <v>596</v>
+        <v>620</v>
       </c>
       <c r="D218" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E218" t="s">
-        <v>679</v>
+        <v>707</v>
       </c>
       <c r="G218" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6241,19 +6325,19 @@
         <v>224</v>
       </c>
       <c r="B219" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="C219" t="s">
-        <v>597</v>
+        <v>621</v>
       </c>
       <c r="D219" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E219" t="s">
-        <v>680</v>
+        <v>708</v>
       </c>
       <c r="G219" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6261,10 +6345,10 @@
         <v>225</v>
       </c>
       <c r="C220" t="s">
-        <v>597</v>
+        <v>621</v>
       </c>
       <c r="D220" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6272,16 +6356,16 @@
         <v>226</v>
       </c>
       <c r="B221" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="C221" t="s">
-        <v>597</v>
+        <v>621</v>
       </c>
       <c r="D221" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G221" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6289,19 +6373,19 @@
         <v>227</v>
       </c>
       <c r="B222" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="C222" t="s">
-        <v>598</v>
+        <v>622</v>
       </c>
       <c r="D222" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="E222" t="s">
-        <v>681</v>
+        <v>709</v>
       </c>
       <c r="G222" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6309,16 +6393,16 @@
         <v>228</v>
       </c>
       <c r="B223" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="C223" t="s">
-        <v>598</v>
+        <v>622</v>
       </c>
       <c r="D223" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G223" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6326,16 +6410,16 @@
         <v>229</v>
       </c>
       <c r="B224" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="C224" t="s">
-        <v>598</v>
+        <v>622</v>
       </c>
       <c r="D224" t="s">
-        <v>623</v>
+        <v>647</v>
       </c>
       <c r="G224" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6343,19 +6427,19 @@
         <v>230</v>
       </c>
       <c r="B225" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="C225" t="s">
-        <v>598</v>
+        <v>622</v>
       </c>
       <c r="D225" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="F225" t="s">
-        <v>701</v>
+        <v>729</v>
       </c>
       <c r="G225" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6363,16 +6447,16 @@
         <v>231</v>
       </c>
       <c r="B226" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="C226" t="s">
-        <v>598</v>
+        <v>622</v>
       </c>
       <c r="D226" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G226" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6380,10 +6464,10 @@
         <v>232</v>
       </c>
       <c r="C227" t="s">
-        <v>598</v>
+        <v>622</v>
       </c>
       <c r="D227" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6391,16 +6475,16 @@
         <v>233</v>
       </c>
       <c r="B228" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="C228" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D228" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G228" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6408,16 +6492,16 @@
         <v>234</v>
       </c>
       <c r="B229" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="C229" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D229" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G229" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6425,16 +6509,16 @@
         <v>235</v>
       </c>
       <c r="B230" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="C230" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D230" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G230" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6442,16 +6526,16 @@
         <v>236</v>
       </c>
       <c r="B231" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="C231" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D231" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G231" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6459,16 +6543,16 @@
         <v>237</v>
       </c>
       <c r="B232" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="C232" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D232" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G232" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6476,16 +6560,16 @@
         <v>238</v>
       </c>
       <c r="B233" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="C233" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D233" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G233" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6493,16 +6577,16 @@
         <v>239</v>
       </c>
       <c r="B234" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="C234" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D234" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G234" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -6510,16 +6594,16 @@
         <v>240</v>
       </c>
       <c r="B235" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="C235" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D235" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G235" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -6527,16 +6611,16 @@
         <v>241</v>
       </c>
       <c r="B236" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="C236" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D236" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G236" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -6544,16 +6628,16 @@
         <v>242</v>
       </c>
       <c r="B237" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="C237" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D237" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G237" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -6561,16 +6645,16 @@
         <v>243</v>
       </c>
       <c r="B238" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="C238" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D238" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G238" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -6578,16 +6662,16 @@
         <v>244</v>
       </c>
       <c r="B239" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="C239" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D239" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G239" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -6595,16 +6679,16 @@
         <v>245</v>
       </c>
       <c r="B240" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="C240" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D240" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G240" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -6612,16 +6696,16 @@
         <v>246</v>
       </c>
       <c r="B241" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="C241" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D241" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G241" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -6629,16 +6713,16 @@
         <v>247</v>
       </c>
       <c r="B242" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="C242" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D242" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G242" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -6646,16 +6730,16 @@
         <v>248</v>
       </c>
       <c r="B243" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="C243" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D243" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G243" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -6663,16 +6747,16 @@
         <v>249</v>
       </c>
       <c r="B244" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="C244" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D244" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G244" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -6680,16 +6764,16 @@
         <v>250</v>
       </c>
       <c r="B245" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="C245" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D245" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G245" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -6697,16 +6781,16 @@
         <v>251</v>
       </c>
       <c r="B246" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="C246" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D246" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G246" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -6714,16 +6798,16 @@
         <v>252</v>
       </c>
       <c r="B247" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="C247" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D247" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G247" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -6731,16 +6815,16 @@
         <v>253</v>
       </c>
       <c r="B248" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="C248" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D248" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G248" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -6748,16 +6832,16 @@
         <v>254</v>
       </c>
       <c r="B249" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="C249" t="s">
-        <v>585</v>
+        <v>609</v>
       </c>
       <c r="D249" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G249" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -6765,16 +6849,16 @@
         <v>255</v>
       </c>
       <c r="B250" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="C250" t="s">
-        <v>585</v>
+        <v>609</v>
       </c>
       <c r="D250" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G250" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -6782,16 +6866,16 @@
         <v>256</v>
       </c>
       <c r="B251" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="C251" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D251" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G251" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -6799,16 +6883,16 @@
         <v>257</v>
       </c>
       <c r="B252" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="C252" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D252" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G252" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -6816,16 +6900,16 @@
         <v>258</v>
       </c>
       <c r="B253" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="C253" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D253" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G253" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -6833,16 +6917,16 @@
         <v>259</v>
       </c>
       <c r="B254" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="C254" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D254" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G254" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -6850,16 +6934,16 @@
         <v>260</v>
       </c>
       <c r="B255" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="C255" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D255" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G255" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -6867,16 +6951,16 @@
         <v>261</v>
       </c>
       <c r="B256" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="C256" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D256" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G256" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -6884,16 +6968,16 @@
         <v>262</v>
       </c>
       <c r="B257" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="C257" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D257" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G257" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -6901,16 +6985,16 @@
         <v>263</v>
       </c>
       <c r="B258" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="C258" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D258" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G258" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -6918,16 +7002,16 @@
         <v>264</v>
       </c>
       <c r="B259" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="C259" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D259" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G259" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -6935,16 +7019,16 @@
         <v>265</v>
       </c>
       <c r="B260" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="C260" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D260" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G260" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -6952,16 +7036,16 @@
         <v>266</v>
       </c>
       <c r="B261" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="C261" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D261" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G261" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -6969,16 +7053,16 @@
         <v>267</v>
       </c>
       <c r="B262" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="C262" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D262" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G262" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -6986,16 +7070,16 @@
         <v>268</v>
       </c>
       <c r="B263" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="C263" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D263" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G263" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7003,16 +7087,16 @@
         <v>269</v>
       </c>
       <c r="B264" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="C264" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D264" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G264" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -7020,16 +7104,16 @@
         <v>270</v>
       </c>
       <c r="B265" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="C265" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D265" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="G265" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -7037,16 +7121,16 @@
         <v>271</v>
       </c>
       <c r="B266" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="C266" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D266" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G266" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7054,16 +7138,16 @@
         <v>272</v>
       </c>
       <c r="B267" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="C267" t="s">
-        <v>599</v>
+        <v>623</v>
       </c>
       <c r="D267" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G267" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7071,16 +7155,16 @@
         <v>273</v>
       </c>
       <c r="B268" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="C268" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D268" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G268" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7088,16 +7172,16 @@
         <v>274</v>
       </c>
       <c r="B269" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="C269" t="s">
-        <v>600</v>
+        <v>624</v>
       </c>
       <c r="D269" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G269" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7105,16 +7189,16 @@
         <v>275</v>
       </c>
       <c r="B270" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="C270" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D270" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G270" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7122,16 +7206,16 @@
         <v>276</v>
       </c>
       <c r="B271" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="C271" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D271" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G271" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -7139,16 +7223,16 @@
         <v>277</v>
       </c>
       <c r="B272" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="C272" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D272" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G272" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7156,16 +7240,16 @@
         <v>278</v>
       </c>
       <c r="B273" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="C273" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D273" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G273" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -7173,16 +7257,16 @@
         <v>279</v>
       </c>
       <c r="B274" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="C274" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D274" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G274" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -7190,16 +7274,16 @@
         <v>280</v>
       </c>
       <c r="B275" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="C275" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D275" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G275" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -7207,16 +7291,16 @@
         <v>281</v>
       </c>
       <c r="B276" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="C276" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D276" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G276" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -7224,16 +7308,16 @@
         <v>282</v>
       </c>
       <c r="B277" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="C277" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D277" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G277" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -7241,16 +7325,16 @@
         <v>283</v>
       </c>
       <c r="B278" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="C278" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D278" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G278" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7258,16 +7342,16 @@
         <v>284</v>
       </c>
       <c r="B279" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="C279" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D279" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G279" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7275,16 +7359,16 @@
         <v>285</v>
       </c>
       <c r="B280" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="C280" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D280" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="G280" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -7292,16 +7376,16 @@
         <v>286</v>
       </c>
       <c r="B281" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="C281" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D281" t="s">
-        <v>627</v>
+        <v>651</v>
       </c>
       <c r="G281" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7309,16 +7393,16 @@
         <v>287</v>
       </c>
       <c r="B282" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="C282" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="D282" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="G282" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -7326,16 +7410,16 @@
         <v>288</v>
       </c>
       <c r="B283" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="C283" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D283" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="G283" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -7343,19 +7427,19 @@
         <v>289</v>
       </c>
       <c r="B284" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="C284" t="s">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="D284" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="F284" t="s">
-        <v>682</v>
+        <v>710</v>
       </c>
       <c r="G284" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -7363,16 +7447,16 @@
         <v>290</v>
       </c>
       <c r="B285" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="C285" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D285" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G285" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -7380,16 +7464,16 @@
         <v>291</v>
       </c>
       <c r="B286" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="C286" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D286" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G286" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -7397,16 +7481,16 @@
         <v>292</v>
       </c>
       <c r="B287" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="C287" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D287" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G287" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -7414,16 +7498,16 @@
         <v>293</v>
       </c>
       <c r="B288" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="C288" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D288" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G288" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -7431,16 +7515,16 @@
         <v>294</v>
       </c>
       <c r="B289" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="C289" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D289" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G289" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -7448,16 +7532,16 @@
         <v>295</v>
       </c>
       <c r="B290" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="C290" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D290" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G290" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -7465,16 +7549,16 @@
         <v>296</v>
       </c>
       <c r="B291" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="C291" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D291" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G291" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -7482,16 +7566,16 @@
         <v>297</v>
       </c>
       <c r="B292" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="C292" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D292" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G292" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -7499,16 +7583,16 @@
         <v>298</v>
       </c>
       <c r="B293" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="C293" t="s">
-        <v>588</v>
+        <v>612</v>
       </c>
       <c r="D293" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G293" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -7516,16 +7600,16 @@
         <v>299</v>
       </c>
       <c r="B294" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="C294" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D294" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G294" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -7533,16 +7617,16 @@
         <v>135</v>
       </c>
       <c r="B295" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="C295" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D295" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="G295" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -7550,16 +7634,16 @@
         <v>300</v>
       </c>
       <c r="B296" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="C296" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D296" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="G296" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="297" spans="1:7">
@@ -7567,16 +7651,16 @@
         <v>301</v>
       </c>
       <c r="B297" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="C297" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="D297" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="G297" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="298" spans="1:7">
@@ -7584,16 +7668,16 @@
         <v>302</v>
       </c>
       <c r="B298" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="C298" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D298" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="G298" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="299" spans="1:7">
@@ -7601,16 +7685,16 @@
         <v>303</v>
       </c>
       <c r="B299" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="C299" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D299" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="G299" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="300" spans="1:7">
@@ -7618,16 +7702,16 @@
         <v>304</v>
       </c>
       <c r="B300" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="C300" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D300" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="G300" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="301" spans="1:7">
@@ -7635,16 +7719,16 @@
         <v>305</v>
       </c>
       <c r="B301" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="C301" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D301" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="G301" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="302" spans="1:7">
@@ -7652,16 +7736,16 @@
         <v>306</v>
       </c>
       <c r="B302" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="C302" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D302" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="G302" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -7669,16 +7753,16 @@
         <v>307</v>
       </c>
       <c r="B303" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="C303" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="D303" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="G303" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="304" spans="1:7">
@@ -7686,16 +7770,16 @@
         <v>308</v>
       </c>
       <c r="B304" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="C304" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D304" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="G304" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="305" spans="1:7">
@@ -7703,16 +7787,16 @@
         <v>309</v>
       </c>
       <c r="B305" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="C305" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D305" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="G305" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="306" spans="1:7">
@@ -7720,16 +7804,16 @@
         <v>310</v>
       </c>
       <c r="B306" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="C306" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D306" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="G306" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="307" spans="1:7">
@@ -7737,16 +7821,16 @@
         <v>311</v>
       </c>
       <c r="B307" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="C307" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D307" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="G307" t="s">
-        <v>702</v>
+        <v>730</v>
       </c>
     </row>
     <row r="308" spans="1:7">
@@ -7754,16 +7838,220 @@
         <v>312</v>
       </c>
       <c r="B308" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="C308" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="D308" t="s">
-        <v>627</v>
+        <v>651</v>
       </c>
       <c r="G308" t="s">
-        <v>702</v>
+        <v>730</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7">
+      <c r="A309" t="s">
+        <v>313</v>
+      </c>
+      <c r="B309" t="s">
+        <v>588</v>
+      </c>
+      <c r="C309" t="s">
+        <v>607</v>
+      </c>
+      <c r="D309" t="s">
+        <v>638</v>
+      </c>
+      <c r="G309" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7">
+      <c r="A310" t="s">
+        <v>314</v>
+      </c>
+      <c r="B310" t="s">
+        <v>589</v>
+      </c>
+      <c r="C310" t="s">
+        <v>607</v>
+      </c>
+      <c r="D310" t="s">
+        <v>652</v>
+      </c>
+      <c r="G310" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7">
+      <c r="A311" t="s">
+        <v>315</v>
+      </c>
+      <c r="B311" t="s">
+        <v>590</v>
+      </c>
+      <c r="C311" t="s">
+        <v>607</v>
+      </c>
+      <c r="D311" t="s">
+        <v>640</v>
+      </c>
+      <c r="G311" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7">
+      <c r="A312" t="s">
+        <v>316</v>
+      </c>
+      <c r="B312" t="s">
+        <v>591</v>
+      </c>
+      <c r="C312" t="s">
+        <v>607</v>
+      </c>
+      <c r="D312" t="s">
+        <v>646</v>
+      </c>
+      <c r="G312" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7">
+      <c r="A313" t="s">
+        <v>317</v>
+      </c>
+      <c r="B313" t="s">
+        <v>592</v>
+      </c>
+      <c r="C313" t="s">
+        <v>607</v>
+      </c>
+      <c r="D313" t="s">
+        <v>649</v>
+      </c>
+      <c r="G313" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7">
+      <c r="A314" t="s">
+        <v>318</v>
+      </c>
+      <c r="B314" t="s">
+        <v>593</v>
+      </c>
+      <c r="C314" t="s">
+        <v>607</v>
+      </c>
+      <c r="D314" t="s">
+        <v>653</v>
+      </c>
+      <c r="G314" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7">
+      <c r="A315" t="s">
+        <v>319</v>
+      </c>
+      <c r="B315" t="s">
+        <v>594</v>
+      </c>
+      <c r="C315" t="s">
+        <v>601</v>
+      </c>
+      <c r="D315" t="s">
+        <v>647</v>
+      </c>
+      <c r="G315" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7">
+      <c r="A316" t="s">
+        <v>320</v>
+      </c>
+      <c r="B316" t="s">
+        <v>595</v>
+      </c>
+      <c r="C316" t="s">
+        <v>601</v>
+      </c>
+      <c r="D316" t="s">
+        <v>647</v>
+      </c>
+      <c r="G316" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7">
+      <c r="A317" t="s">
+        <v>321</v>
+      </c>
+      <c r="B317" t="s">
+        <v>596</v>
+      </c>
+      <c r="C317" t="s">
+        <v>607</v>
+      </c>
+      <c r="D317" t="s">
+        <v>654</v>
+      </c>
+      <c r="G317" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7">
+      <c r="A318" t="s">
+        <v>322</v>
+      </c>
+      <c r="B318" t="s">
+        <v>597</v>
+      </c>
+      <c r="C318" t="s">
+        <v>610</v>
+      </c>
+      <c r="D318" t="s">
+        <v>655</v>
+      </c>
+      <c r="G318" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7">
+      <c r="A319" t="s">
+        <v>323</v>
+      </c>
+      <c r="B319" t="s">
+        <v>598</v>
+      </c>
+      <c r="C319" t="s">
+        <v>604</v>
+      </c>
+      <c r="D319" t="s">
+        <v>639</v>
+      </c>
+      <c r="G319" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7">
+      <c r="A320" t="s">
+        <v>324</v>
+      </c>
+      <c r="B320" t="s">
+        <v>599</v>
+      </c>
+      <c r="C320" t="s">
+        <v>604</v>
+      </c>
+      <c r="D320" t="s">
+        <v>650</v>
+      </c>
+      <c r="G320" t="s">
+        <v>730</v>
       </c>
     </row>
   </sheetData>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="736">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -35,6 +35,21 @@
   </si>
   <si>
     <t>Sent</t>
+  </si>
+  <si>
+    <t>FollowUpSent</t>
+  </si>
+  <si>
+    <t>FollowUpDate</t>
+  </si>
+  <si>
+    <t>Replied</t>
+  </si>
+  <si>
+    <t>ReplyDate</t>
+  </si>
+  <si>
+    <t>ReplySubject</t>
   </si>
   <si>
     <t>Cape Town Science Centre</t>
@@ -2551,10 +2566,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G320"/>
+  <dimension ref="A1:L320"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2576,5482 +2591,5497 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C2" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="D2" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E2" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="F2" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="G2" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C3" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="D3" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E3" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="F3" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="G3" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C4" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D4" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E4" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="F4" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="G4" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C5" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D5" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E5" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="F5" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="G5" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C6" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="D6" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E6" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="F6" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="G6" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C7" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="D7" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E7" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="F7" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="G7" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C8" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D8" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E8" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="F8" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="G8" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C9" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D9" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E9" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="F9" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="G9" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C10" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="D10" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E10" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="F10" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="G10" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C11" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="D11" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E11" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="F11" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="G11" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C12" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="D12" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E12" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="F12" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="G12" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C13" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="D13" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E13" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="F13" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="G13" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C14" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D14" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="E14" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="G14" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C15" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D15" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="E15" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="G15" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C16" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D16" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G16" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C17" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D17" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G17" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C18" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D18" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G18" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C19" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D19" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G19" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="C20" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D20" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G20" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C21" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D21" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G21" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C22" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D22" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G22" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C23" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D23" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G23" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C24" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D24" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G24" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C25" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D25" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G25" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C26" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D26" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G26" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C27" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D27" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G27" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C28" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D28" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G28" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C29" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D29" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G29" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C30" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D30" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G30" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B31" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C31" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D31" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G31" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C32" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D32" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G32" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C33" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D33" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G33" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C34" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D34" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G34" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C35" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D35" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G35" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C36" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D36" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G36" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C37" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D37" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G37" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B38" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C38" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D38" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G38" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C39" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D39" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G39" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B40" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C40" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="D40" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G40" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C41" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="D41" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G41" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C42" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="D42" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G42" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B43" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C43" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="D43" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G43" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B44" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C44" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="D44" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G44" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B45" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C45" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D45" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G45" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B46" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C46" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D46" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G46" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B47" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C47" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D47" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G47" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B48" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C48" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D48" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G48" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B49" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C49" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D49" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G49" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C50" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D50" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G50" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B51" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C51" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D51" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G51" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B52" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C52" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D52" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G52" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B53" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C53" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D53" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G53" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B54" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C54" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D54" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G54" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B55" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C55" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D55" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G55" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B56" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="C56" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D56" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G56" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B57" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C57" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D57" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G57" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B58" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C58" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D58" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G58" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B59" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C59" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D59" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G59" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B60" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C60" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D60" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G60" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B61" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C61" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D61" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G61" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B62" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C62" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D62" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G62" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B63" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C63" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D63" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G63" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B64" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C64" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D64" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G64" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B65" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C65" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D65" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G65" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B66" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C66" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D66" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G66" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B67" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C67" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D67" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G67" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B68" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C68" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D68" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G68" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B69" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C69" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D69" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G69" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B70" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C70" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D70" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G70" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B71" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C71" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D71" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G71" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B72" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C72" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D72" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G72" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B73" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C73" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D73" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G73" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B74" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C74" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D74" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G74" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B75" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C75" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D75" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G75" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B76" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C76" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D76" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G76" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B77" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C77" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D77" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G77" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B78" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C78" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D78" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G78" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B79" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C79" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D79" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G79" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B80" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C80" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D80" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G80" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B81" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C81" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D81" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G81" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B82" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C82" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D82" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G82" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B83" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C83" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D83" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G83" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B84" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C84" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D84" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G84" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B85" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C85" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="D85" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G85" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B86" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C86" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="D86" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G86" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B87" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C87" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="D87" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G87" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B88" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C88" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="D88" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G88" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B89" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C89" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="D89" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G89" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B90" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C90" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D90" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G90" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B91" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C91" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D91" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G91" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B92" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C92" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D92" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G92" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B93" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C93" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D93" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G93" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B94" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C94" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D94" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G94" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B95" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C95" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D95" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G95" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B96" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C96" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D96" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G96" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B97" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C97" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D97" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G97" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B98" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C98" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D98" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G98" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B99" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C99" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D99" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G99" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B100" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C100" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D100" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G100" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B101" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C101" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D101" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G101" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B102" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C102" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D102" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G102" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B103" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C103" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D103" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G103" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B104" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C104" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D104" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G104" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B105" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="C105" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D105" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G105" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B106" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C106" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D106" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G106" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B107" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C107" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D107" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G107" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B108" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C108" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D108" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G108" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B109" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C109" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D109" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G109" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B110" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C110" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D110" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G110" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B111" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C111" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D111" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G111" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B112" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C112" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D112" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G112" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B113" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C113" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D113" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G113" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B114" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C114" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="D114" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G114" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B115" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C115" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="D115" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G115" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B116" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C116" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="D116" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G116" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B117" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C117" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="D117" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G117" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B118" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C118" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="D118" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G118" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B119" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C119" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="D119" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E119" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="F119" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="G119" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B120" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C120" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="D120" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="E120" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="G120" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="121" spans="1:7">
       <c r="A121" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B121" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C121" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="D121" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G121" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B122" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C122" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D122" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="G122" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B123" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C123" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D123" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="E123" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="F123" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="G123" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B124" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="C124" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D124" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G124" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B125" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C125" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D125" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G125" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B126" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="C126" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D126" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G126" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B127" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C127" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D127" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G127" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B128" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="C128" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D128" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="E128" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="G128" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B129" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C129" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D129" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E129" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="F129" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="G129" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B130" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="C130" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D130" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G130" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C131" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D131" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="E131" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B132" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C132" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D132" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="E132" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="G132" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B133" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C133" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D133" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="E133" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="G133" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C134" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D134" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C135" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D135" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B136" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C136" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D136" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G136" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B137" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C137" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D137" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="G137" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C138" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D138" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
     </row>
     <row r="139" spans="1:7">
       <c r="A139" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C139" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D139" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
     </row>
     <row r="140" spans="1:7">
       <c r="A140" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C140" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D140" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="A141" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B141" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C141" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D141" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G141" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="142" spans="1:7">
       <c r="A142" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B142" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C142" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D142" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E142" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="F142" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="G142" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="143" spans="1:7">
       <c r="A143" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B143" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C143" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D143" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="G143" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="144" spans="1:7">
       <c r="A144" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C144" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D144" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="E144" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C145" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D145" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="146" spans="1:7">
       <c r="A146" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B146" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C146" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D146" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="F146" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="G146" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="147" spans="1:7">
       <c r="A147" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B147" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C147" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D147" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E147" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="F147" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="G147" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="148" spans="1:7">
       <c r="A148" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B148" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C148" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D148" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E148" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="G148" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="149" spans="1:7">
       <c r="A149" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B149" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C149" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D149" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E149" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="G149" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="150" spans="1:7">
       <c r="A150" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B150" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="C150" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D150" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E150" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="G150" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B151" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C151" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D151" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E151" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="G151" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="152" spans="1:7">
       <c r="A152" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B152" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C152" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D152" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E152" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="G152" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="153" spans="1:7">
       <c r="A153" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C153" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D153" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B154" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C154" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D154" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E154" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="G154" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B155" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C155" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D155" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G155" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B156" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C156" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D156" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G156" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B157" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C157" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D157" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="E157" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="F157" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="G157" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="158" spans="1:7">
       <c r="A158" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B158" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C158" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D158" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E158" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="G158" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B159" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C159" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D159" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E159" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="G159" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="160" spans="1:7">
       <c r="A160" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B160" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C160" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D160" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E160" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="G160" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B161" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C161" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D161" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="E161" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="G161" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B162" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C162" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D162" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G162" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B163" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="C163" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D163" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E163" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="G163" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B164" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C164" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D164" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="E164" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="G164" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C165" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D165" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="E165" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
     </row>
     <row r="166" spans="1:7">
       <c r="A166" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B166" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="C166" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D166" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="E166" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="G166" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B167" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C167" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D167" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="E167" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="G167" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="168" spans="1:7">
       <c r="A168" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B168" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="C168" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="D168" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E168" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="G168" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="169" spans="1:7">
       <c r="A169" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B169" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C169" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="D169" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="E169" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="G169" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="170" spans="1:7">
       <c r="A170" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C170" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="D170" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="E170" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
     </row>
     <row r="171" spans="1:7">
       <c r="A171" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C171" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="D171" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E171" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
     </row>
     <row r="172" spans="1:7">
       <c r="A172" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C172" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="D172" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="E172" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
     </row>
     <row r="173" spans="1:7">
       <c r="A173" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B173" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C173" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="D173" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G173" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="174" spans="1:7">
       <c r="A174" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B174" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C174" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="D174" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="F174" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="G174" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="175" spans="1:7">
       <c r="A175" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B175" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="C175" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="D175" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="F175" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="G175" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="176" spans="1:7">
       <c r="A176" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C176" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="D176" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="177" spans="1:7">
       <c r="A177" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C177" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="D177" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
     </row>
     <row r="178" spans="1:7">
       <c r="A178" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C178" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="D178" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="179" spans="1:7">
       <c r="A179" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B179" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="C179" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="D179" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="E179" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="F179" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="G179" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="180" spans="1:7">
       <c r="A180" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C180" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="D180" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
     </row>
     <row r="181" spans="1:7">
       <c r="A181" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C181" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="D181" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="182" spans="1:7">
       <c r="A182" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B182" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C182" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="D182" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E182" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="G182" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="183" spans="1:7">
       <c r="A183" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B183" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C183" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="D183" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="F183" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="G183" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="184" spans="1:7">
       <c r="A184" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C184" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="D184" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
     </row>
     <row r="185" spans="1:7">
       <c r="A185" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C185" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="D185" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="F185" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
     </row>
     <row r="186" spans="1:7">
       <c r="A186" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C186" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="D186" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="E186" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
     </row>
     <row r="187" spans="1:7">
       <c r="A187" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C187" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="D187" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E187" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
     </row>
     <row r="188" spans="1:7">
       <c r="A188" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C188" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="D188" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E188" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
     </row>
     <row r="189" spans="1:7">
       <c r="A189" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C189" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="D189" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E189" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
     </row>
     <row r="190" spans="1:7">
       <c r="A190" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C190" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="D190" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E190" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
     </row>
     <row r="191" spans="1:7">
       <c r="A191" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C191" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="D191" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="192" spans="1:7">
       <c r="A192" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C192" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="D192" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
     </row>
     <row r="193" spans="1:7">
       <c r="A193" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C193" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="D193" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="194" spans="1:7">
       <c r="A194" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B194" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C194" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="D194" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="G194" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="195" spans="1:7">
       <c r="A195" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B195" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C195" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="D195" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="G195" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="196" spans="1:7">
       <c r="A196" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B196" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C196" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="D196" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="F196" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="G196" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="197" spans="1:7">
       <c r="A197" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B197" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C197" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="D197" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E197" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="F197" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="G197" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="198" spans="1:7">
       <c r="A198" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B198" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="C198" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="D198" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E198" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="F198" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="G198" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="199" spans="1:7">
       <c r="A199" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B199" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C199" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="D199" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E199" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="F199" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="G199" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="200" spans="1:7">
       <c r="A200" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B200" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="C200" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="D200" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G200" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="201" spans="1:7">
       <c r="A201" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C201" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="D201" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="202" spans="1:7">
       <c r="A202" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C202" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="D202" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="203" spans="1:7">
       <c r="A203" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C203" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="D203" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="204" spans="1:7">
       <c r="A204" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B204" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C204" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="D204" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G204" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="205" spans="1:7">
       <c r="A205" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C205" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="D205" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="206" spans="1:7">
       <c r="A206" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C206" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="D206" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="207" spans="1:7">
       <c r="A207" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B207" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C207" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="D207" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E207" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="G207" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="208" spans="1:7">
       <c r="A208" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C208" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="D208" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E208" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
     </row>
     <row r="209" spans="1:7">
       <c r="A209" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C209" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="D209" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
     </row>
     <row r="210" spans="1:7">
       <c r="A210" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B210" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="C210" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="D210" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E210" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="G210" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="211" spans="1:7">
       <c r="A211" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B211" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="C211" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="D211" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G211" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="212" spans="1:7">
       <c r="A212" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C212" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="D212" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E212" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
     </row>
     <row r="213" spans="1:7">
       <c r="A213" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C213" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="D213" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="E213" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
     </row>
     <row r="214" spans="1:7">
       <c r="A214" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B214" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="C214" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="D214" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G214" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="215" spans="1:7">
       <c r="A215" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B215" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C215" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="D215" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G215" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="216" spans="1:7">
       <c r="A216" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C216" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="D216" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E216" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
     </row>
     <row r="217" spans="1:7">
       <c r="A217" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B217" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="C217" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="D217" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E217" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="G217" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="218" spans="1:7">
       <c r="A218" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B218" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="C218" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="D218" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E218" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="G218" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="219" spans="1:7">
       <c r="A219" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B219" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C219" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="D219" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E219" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="G219" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="220" spans="1:7">
       <c r="A220" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C220" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="D220" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="221" spans="1:7">
       <c r="A221" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B221" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="C221" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="D221" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G221" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="222" spans="1:7">
       <c r="A222" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B222" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="C222" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="D222" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E222" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="G222" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="223" spans="1:7">
       <c r="A223" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B223" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="C223" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="D223" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G223" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="224" spans="1:7">
       <c r="A224" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B224" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="C224" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="D224" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="G224" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="225" spans="1:7">
       <c r="A225" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B225" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="C225" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="D225" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="F225" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="G225" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="226" spans="1:7">
       <c r="A226" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B226" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C226" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="D226" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G226" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="227" spans="1:7">
       <c r="A227" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C227" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="D227" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="228" spans="1:7">
       <c r="A228" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B228" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="C228" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D228" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G228" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="229" spans="1:7">
       <c r="A229" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B229" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C229" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D229" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G229" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="230" spans="1:7">
       <c r="A230" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B230" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C230" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D230" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G230" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="231" spans="1:7">
       <c r="A231" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B231" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="C231" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D231" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G231" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="232" spans="1:7">
       <c r="A232" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B232" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="C232" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D232" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G232" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="233" spans="1:7">
       <c r="A233" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B233" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C233" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D233" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G233" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="234" spans="1:7">
       <c r="A234" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B234" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="C234" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D234" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G234" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="235" spans="1:7">
       <c r="A235" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B235" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="C235" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D235" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G235" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="236" spans="1:7">
       <c r="A236" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B236" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C236" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D236" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G236" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="237" spans="1:7">
       <c r="A237" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B237" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="C237" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D237" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G237" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="238" spans="1:7">
       <c r="A238" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B238" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="C238" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D238" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G238" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="239" spans="1:7">
       <c r="A239" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B239" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="C239" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D239" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G239" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="240" spans="1:7">
       <c r="A240" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B240" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="C240" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D240" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G240" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="241" spans="1:7">
       <c r="A241" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B241" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="C241" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D241" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G241" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="242" spans="1:7">
       <c r="A242" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B242" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="C242" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D242" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G242" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="243" spans="1:7">
       <c r="A243" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B243" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="C243" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D243" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G243" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="244" spans="1:7">
       <c r="A244" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B244" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="C244" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D244" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G244" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="245" spans="1:7">
       <c r="A245" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B245" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C245" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D245" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G245" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="246" spans="1:7">
       <c r="A246" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B246" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C246" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D246" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G246" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="247" spans="1:7">
       <c r="A247" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B247" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="C247" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D247" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G247" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="248" spans="1:7">
       <c r="A248" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B248" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="C248" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D248" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G248" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="249" spans="1:7">
       <c r="A249" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B249" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="C249" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D249" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G249" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="250" spans="1:7">
       <c r="A250" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B250" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C250" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D250" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G250" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="251" spans="1:7">
       <c r="A251" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B251" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C251" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D251" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G251" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="252" spans="1:7">
       <c r="A252" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B252" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="C252" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D252" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G252" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="253" spans="1:7">
       <c r="A253" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B253" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="C253" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D253" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G253" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="254" spans="1:7">
       <c r="A254" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B254" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="C254" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D254" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G254" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="255" spans="1:7">
       <c r="A255" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B255" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="C255" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D255" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G255" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="256" spans="1:7">
       <c r="A256" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B256" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C256" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D256" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G256" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="257" spans="1:7">
       <c r="A257" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B257" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="C257" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D257" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G257" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="258" spans="1:7">
       <c r="A258" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B258" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="C258" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D258" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G258" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="259" spans="1:7">
       <c r="A259" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B259" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="C259" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D259" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G259" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="260" spans="1:7">
       <c r="A260" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B260" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="C260" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D260" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G260" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="261" spans="1:7">
       <c r="A261" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B261" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="C261" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D261" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G261" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="262" spans="1:7">
       <c r="A262" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B262" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="C262" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D262" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G262" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="263" spans="1:7">
       <c r="A263" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B263" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="C263" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D263" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G263" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="264" spans="1:7">
       <c r="A264" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B264" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="C264" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D264" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G264" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="265" spans="1:7">
       <c r="A265" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B265" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="C265" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D265" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G265" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="266" spans="1:7">
       <c r="A266" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B266" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="C266" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D266" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G266" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="267" spans="1:7">
       <c r="A267" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B267" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C267" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="D267" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G267" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="268" spans="1:7">
       <c r="A268" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B268" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C268" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D268" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G268" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="269" spans="1:7">
       <c r="A269" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B269" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C269" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="D269" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G269" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="270" spans="1:7">
       <c r="A270" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B270" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="C270" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D270" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G270" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="271" spans="1:7">
       <c r="A271" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B271" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="C271" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D271" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G271" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="272" spans="1:7">
       <c r="A272" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B272" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="C272" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D272" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G272" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="273" spans="1:7">
       <c r="A273" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B273" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="C273" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D273" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G273" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="274" spans="1:7">
       <c r="A274" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B274" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="C274" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D274" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G274" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="275" spans="1:7">
       <c r="A275" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B275" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="C275" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D275" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G275" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="276" spans="1:7">
       <c r="A276" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B276" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="C276" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D276" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G276" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="277" spans="1:7">
       <c r="A277" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B277" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="C277" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D277" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G277" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="278" spans="1:7">
       <c r="A278" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B278" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C278" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D278" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G278" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="279" spans="1:7">
       <c r="A279" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B279" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="C279" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D279" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G279" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="280" spans="1:7">
       <c r="A280" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B280" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="C280" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D280" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="G280" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="281" spans="1:7">
       <c r="A281" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B281" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="C281" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D281" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="G281" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="282" spans="1:7">
       <c r="A282" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B282" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C282" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D282" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="G282" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="283" spans="1:7">
       <c r="A283" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B283" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="C283" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D283" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="G283" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="284" spans="1:7">
       <c r="A284" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B284" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="C284" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="D284" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="F284" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="G284" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="285" spans="1:7">
       <c r="A285" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B285" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="C285" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D285" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G285" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="286" spans="1:7">
       <c r="A286" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B286" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="C286" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D286" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G286" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="287" spans="1:7">
       <c r="A287" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B287" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="C287" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D287" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G287" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="288" spans="1:7">
       <c r="A288" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B288" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="C288" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D288" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G288" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="289" spans="1:7">
       <c r="A289" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B289" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C289" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D289" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G289" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="290" spans="1:7">
       <c r="A290" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B290" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="C290" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D290" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G290" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="291" spans="1:7">
       <c r="A291" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B291" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="C291" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D291" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G291" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="292" spans="1:7">
       <c r="A292" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B292" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C292" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D292" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G292" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="293" spans="1:7">
       <c r="A293" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B293" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="C293" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="D293" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G293" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="294" spans="1:7">
       <c r="A294" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B294" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C294" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D294" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G294" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="295" spans="1:7">
       <c r="A295" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B295" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C295" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D295" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G295" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="296" spans="1:7">
       <c r="A296" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B296" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="C296" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D296" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="G296" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="297" spans="1:7">
       <c r="A297" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B297" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C297" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D297" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="G297" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="298" spans="1:7">
       <c r="A298" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B298" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="C298" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D298" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="G298" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="299" spans="1:7">
       <c r="A299" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B299" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="C299" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D299" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="G299" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="300" spans="1:7">
       <c r="A300" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B300" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C300" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D300" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="G300" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="301" spans="1:7">
       <c r="A301" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B301" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="C301" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D301" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="G301" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="302" spans="1:7">
       <c r="A302" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B302" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C302" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D302" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="G302" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="303" spans="1:7">
       <c r="A303" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B303" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C303" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D303" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="G303" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="304" spans="1:7">
       <c r="A304" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B304" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C304" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D304" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="G304" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="305" spans="1:7">
       <c r="A305" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B305" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="C305" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D305" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="G305" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="306" spans="1:7">
       <c r="A306" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B306" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C306" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D306" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="G306" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="307" spans="1:7">
       <c r="A307" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B307" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C307" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D307" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="G307" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="308" spans="1:7">
       <c r="A308" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B308" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="C308" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D308" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="G308" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="309" spans="1:7">
       <c r="A309" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B309" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C309" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D309" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="G309" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="310" spans="1:7">
       <c r="A310" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B310" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="C310" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D310" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="G310" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="311" spans="1:7">
       <c r="A311" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B311" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="C311" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D311" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="G311" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="312" spans="1:7">
       <c r="A312" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B312" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="C312" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D312" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="G312" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="313" spans="1:7">
       <c r="A313" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B313" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C313" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D313" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="G313" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="314" spans="1:7">
       <c r="A314" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B314" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="C314" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D314" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="G314" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="315" spans="1:7">
       <c r="A315" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B315" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="C315" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D315" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="G315" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="316" spans="1:7">
       <c r="A316" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B316" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="C316" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D316" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="G316" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="317" spans="1:7">
       <c r="A317" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B317" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C317" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="D317" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="G317" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="318" spans="1:7">
       <c r="A318" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B318" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C318" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="D318" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="G318" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="319" spans="1:7">
       <c r="A319" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B319" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="C319" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D319" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="G319" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="320" spans="1:7">
       <c r="A320" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B320" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="C320" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D320" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G320" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
   </sheetData>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,54 +14,2211 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="736">
   <si>
     <t>Organisation Name</t>
   </si>
   <si>
+    <t>Email</t>
+  </si>
+  <si>
     <t>Category</t>
   </si>
   <si>
     <t>Location</t>
   </si>
   <si>
-    <t>Email</t>
-  </si>
-  <si>
     <t>Phone</t>
   </si>
   <si>
     <t>Website</t>
   </si>
   <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
     <t>Sent</t>
   </si>
   <si>
-    <t>Amazon clôture mon compte - 60 Millions de Consommateurs</t>
+    <t>FollowUpSent</t>
+  </si>
+  <si>
+    <t>FollowUpDate</t>
+  </si>
+  <si>
+    <t>Replied</t>
+  </si>
+  <si>
+    <t>ReplyDate</t>
+  </si>
+  <si>
+    <t>ReplySubject</t>
+  </si>
+  <si>
+    <t>Cape Town Science Centre</t>
+  </si>
+  <si>
+    <t>Cape Town Science Centre - Bookings</t>
+  </si>
+  <si>
+    <t>Cape Town Science Centre - STEM Clubs</t>
+  </si>
+  <si>
+    <t>Cape Town Science Centre - REACH</t>
+  </si>
+  <si>
+    <t>Cape Town Science Centre - Admin</t>
+  </si>
+  <si>
+    <t>Cape Town Science Centre - Portia</t>
+  </si>
+  <si>
+    <t>Cape Town Science Centre - Phillip Engelbrecht</t>
+  </si>
+  <si>
+    <t>Cape Town Science Centre - Umr Chippendale</t>
+  </si>
+  <si>
+    <t>Cape Town Science Centre - Muneerah</t>
+  </si>
+  <si>
+    <t>Cape Town Science Centre - Grant</t>
+  </si>
+  <si>
+    <t>Cape Town Science Centre - Gabi Gelderblom</t>
+  </si>
+  <si>
+    <t>Cape Town Science Centre - Busi</t>
+  </si>
+  <si>
+    <t>Johannesburg Art Gallery</t>
+  </si>
+  <si>
+    <t>Standard Bank Gallery</t>
+  </si>
+  <si>
+    <t>Cape Mental Health</t>
+  </si>
+  <si>
+    <t>Cape Town Drug Counselling Centre</t>
+  </si>
+  <si>
+    <t>SANCA Western Cape</t>
+  </si>
+  <si>
+    <t>St Luke's Combined Hospices</t>
+  </si>
+  <si>
+    <t>Nazareth House Cape Town</t>
+  </si>
+  <si>
+    <t>Rape Crisis Cape Town Trust</t>
+  </si>
+  <si>
+    <t>Groote Schuur Hospital Trust</t>
+  </si>
+  <si>
+    <t>TB HIV Care</t>
+  </si>
+  <si>
+    <t>Mothers2Mothers South Africa</t>
+  </si>
+  <si>
+    <t>Desmond Tutu HIV Foundation</t>
+  </si>
+  <si>
+    <t>Highlands House</t>
+  </si>
+  <si>
+    <t>Camphill Village West Coast</t>
+  </si>
+  <si>
+    <t>Sandown House Retirement Village</t>
+  </si>
+  <si>
+    <t>Vineyard Old Age Home</t>
+  </si>
+  <si>
+    <t>Rosedale Old Age Home</t>
+  </si>
+  <si>
+    <t>Hubertus Old Age Home</t>
+  </si>
+  <si>
+    <t>Age in Action</t>
+  </si>
+  <si>
+    <t>Ikamva Labantu</t>
+  </si>
+  <si>
+    <t>Community Chest of the Western Cape</t>
+  </si>
+  <si>
+    <t>The Big Issue</t>
+  </si>
+  <si>
+    <t>Mould Empower Serve (MES)</t>
+  </si>
+  <si>
+    <t>Habitat for Humanity South Africa</t>
+  </si>
+  <si>
+    <t>Salesian Institute Youth Projects</t>
+  </si>
+  <si>
+    <t>Ubuntu Pathways</t>
+  </si>
+  <si>
+    <t>NSRI National Sea Rescue Institute</t>
+  </si>
+  <si>
+    <t>Volunteer Wildfire Services</t>
+  </si>
+  <si>
+    <t>Wilderness Search and Rescue WSAR</t>
+  </si>
+  <si>
+    <t>St John Ambulance Western Cape</t>
+  </si>
+  <si>
+    <t>Mountain Club of South Africa Cape Town</t>
+  </si>
+  <si>
+    <t>Artscape Theatre Centre</t>
+  </si>
+  <si>
+    <t>Baxter Theatre Centre</t>
+  </si>
+  <si>
+    <t>Iziko Museums of South Africa</t>
+  </si>
+  <si>
+    <t>Zeitz Museum of Contemporary Art Africa</t>
+  </si>
+  <si>
+    <t>Cape Town Philharmonic Orchestra</t>
+  </si>
+  <si>
+    <t>Cape Town Opera</t>
+  </si>
+  <si>
+    <t>IkamvaYouth</t>
+  </si>
+  <si>
+    <t>The Shine Centre</t>
+  </si>
+  <si>
+    <t>Christel House South Africa</t>
+  </si>
+  <si>
+    <t>The Learning Trust</t>
+  </si>
+  <si>
+    <t>Cape of Good Hope SPCA</t>
+  </si>
+  <si>
+    <t>TEARS Animal Rescue</t>
+  </si>
+  <si>
+    <t>Animal Rescue Organisation ARO</t>
+  </si>
+  <si>
+    <t>SANCCOB</t>
+  </si>
+  <si>
+    <t>Greenpop</t>
+  </si>
+  <si>
+    <t>Cape Leopard Trust</t>
+  </si>
+  <si>
+    <t>Anova Health Institute</t>
+  </si>
+  <si>
+    <t>BroadReach Healthcare</t>
+  </si>
+  <si>
+    <t>Western Cape Network on Health and Welfare</t>
+  </si>
+  <si>
+    <t>Cancer Association of South Africa (CANSA) WC</t>
+  </si>
+  <si>
+    <t>Hospice Palliative Care Association WC</t>
+  </si>
+  <si>
+    <t>Marie Stopes South Africa</t>
+  </si>
+  <si>
+    <t>Sonke Gender Justice</t>
+  </si>
+  <si>
+    <t>Treatment Action Campaign</t>
+  </si>
+  <si>
+    <t>Neighbourhood Old Age Homes (NOAH)</t>
+  </si>
+  <si>
+    <t>Cape Peninsula Organisation for the Aged</t>
+  </si>
+  <si>
+    <t>Pinelands Village Retirement</t>
+  </si>
+  <si>
+    <t>Huise vir Bejaardes</t>
+  </si>
+  <si>
+    <t>St Joseph's Home for the Aged</t>
+  </si>
+  <si>
+    <t>Maitland Cottage Home</t>
+  </si>
+  <si>
+    <t>Violence Prevention through Urban Upgrading (VPUU)</t>
+  </si>
+  <si>
+    <t>Community Organisation Resource Centre (CORC)</t>
+  </si>
+  <si>
+    <t>Development Action Group</t>
+  </si>
+  <si>
+    <t>Isandla Institute</t>
+  </si>
+  <si>
+    <t>SERI (Socio-Economic Rights Institute)</t>
+  </si>
+  <si>
+    <t>Ndifuna Ukwazi</t>
+  </si>
+  <si>
+    <t>The Warehouse</t>
+  </si>
+  <si>
+    <t>Living Hope</t>
+  </si>
+  <si>
+    <t>Nazarene Development Trust</t>
+  </si>
+  <si>
+    <t>Ubuntu Football</t>
+  </si>
+  <si>
+    <t>Cape Town Emergency Volunteer Corps</t>
+  </si>
+  <si>
+    <t>Metro Rescue</t>
+  </si>
+  <si>
+    <t>Disaster Management Volunteers</t>
+  </si>
+  <si>
+    <t>Lifesaving Western Cape</t>
+  </si>
+  <si>
+    <t>Cape Town Fire Volunteer Services</t>
+  </si>
+  <si>
+    <t>The Fugard Theatre</t>
+  </si>
+  <si>
+    <t>Alexander Bar Theatre</t>
+  </si>
+  <si>
+    <t>Theatre Arts Admin Collective</t>
+  </si>
+  <si>
+    <t>Cape Town Comedy Club</t>
+  </si>
+  <si>
+    <t>Kalk Bay Theatre</t>
+  </si>
+  <si>
+    <t>Young Blood Gallery</t>
+  </si>
+  <si>
+    <t>AVA Gallery</t>
+  </si>
+  <si>
+    <t>Cape Town Art Fair</t>
+  </si>
+  <si>
+    <t>Design Indaba</t>
+  </si>
+  <si>
+    <t>Bottomup</t>
+  </si>
+  <si>
+    <t>Salesian Life Choices</t>
+  </si>
+  <si>
+    <t>Ikamva Labantu Youth</t>
+  </si>
+  <si>
+    <t>Action Volunteers Africa</t>
+  </si>
+  <si>
+    <t>The President's Award for Youth Empowerment WC</t>
+  </si>
+  <si>
+    <t>Rlabs</t>
+  </si>
+  <si>
+    <t>Ampath Foundation</t>
+  </si>
+  <si>
+    <t>Shine Literacy</t>
+  </si>
+  <si>
+    <t>Cheetah Outreach</t>
+  </si>
+  <si>
+    <t>Panthera Africa</t>
+  </si>
+  <si>
+    <t>WESSA Western Cape</t>
+  </si>
+  <si>
+    <t>Friends of Table Mountain</t>
+  </si>
+  <si>
+    <t>Cape Town Environmental Education Trust (CTEET)</t>
+  </si>
+  <si>
+    <t>Kirstenbosch Volunteers</t>
+  </si>
+  <si>
+    <t>Sustainable Seas Trust</t>
+  </si>
+  <si>
+    <t>Western Province Rugby Union</t>
+  </si>
+  <si>
+    <t>Western Province Cricket Association</t>
+  </si>
+  <si>
+    <t>Cape Town Cycle Tour Trust</t>
+  </si>
+  <si>
+    <t>Two Oceans Marathon</t>
+  </si>
+  <si>
+    <t>Cape Town Spurs FC</t>
+  </si>
+  <si>
+    <t>Mountain Club of South Africa (MCSA)</t>
+  </si>
+  <si>
+    <t>SA Riding for the Disabled</t>
+  </si>
+  <si>
+    <t>H.H. Beach Sailing Club</t>
+  </si>
+  <si>
+    <t>Animal Welfare Society Helderberg</t>
+  </si>
+  <si>
+    <t>DARG (Domestic Animal Rescue Group)</t>
+  </si>
+  <si>
+    <t>African Tails</t>
+  </si>
+  <si>
+    <t>Animal Anti-Cruelty League</t>
+  </si>
+  <si>
+    <t>Animal Lifeline</t>
+  </si>
+  <si>
+    <t>Animal Rescue Organisation</t>
+  </si>
+  <si>
+    <t>Dolphin Action and Protection Group</t>
+  </si>
+  <si>
+    <t>Abalimi Bezekhaya</t>
+  </si>
+  <si>
+    <t>Communitree</t>
+  </si>
+  <si>
+    <t>Muizenberg Cleansweep</t>
+  </si>
+  <si>
+    <t>Witzands Conservation Area</t>
+  </si>
+  <si>
+    <t>Wolfgat Nature Reserve</t>
+  </si>
+  <si>
+    <t>Gugulethu Urban Food Forest Initiative</t>
+  </si>
+  <si>
+    <t>Neighbourhood Gardens</t>
+  </si>
+  <si>
+    <t>Cape Cultural Collective</t>
+  </si>
+  <si>
+    <t>Masque Theatre</t>
+  </si>
+  <si>
+    <t>Guga S'thebe Cultural Centre</t>
+  </si>
+  <si>
+    <t>Isivivana Centre</t>
+  </si>
+  <si>
+    <t>The Mothertongue Project</t>
+  </si>
+  <si>
+    <t>Cape Philharmonic Orchestra</t>
+  </si>
+  <si>
+    <t>District Six Museum Foundation</t>
+  </si>
+  <si>
+    <t>Just Grace</t>
+  </si>
+  <si>
+    <t>Ingcambu Neqhayiya Community Development</t>
+  </si>
+  <si>
+    <t>Sikhululekile Reading Development</t>
+  </si>
+  <si>
+    <t>Wordworks</t>
+  </si>
+  <si>
+    <t>Khulisa Social Solutions</t>
+  </si>
+  <si>
+    <t>U-Turn Homeless Ministries</t>
+  </si>
+  <si>
+    <t>The Hope Exchange</t>
+  </si>
+  <si>
+    <t>Straatwerk</t>
+  </si>
+  <si>
+    <t>Ons Plek</t>
+  </si>
+  <si>
+    <t>The Homestead</t>
+  </si>
+  <si>
+    <t>Ubuntu Circle of Courage</t>
+  </si>
+  <si>
+    <t>Oasis Association</t>
+  </si>
+  <si>
+    <t>Olive Leaf Foundation</t>
+  </si>
+  <si>
+    <t>The Deaf Community of Cape Town</t>
+  </si>
+  <si>
+    <t>Wola Nani</t>
+  </si>
+  <si>
+    <t>Mfesane</t>
+  </si>
+  <si>
+    <t>Black Sash</t>
+  </si>
+  <si>
+    <t>Cape Town Child Welfare Society</t>
+  </si>
+  <si>
+    <t>Marsh Memorial Homes</t>
+  </si>
+  <si>
+    <t>Uzwelo Youth Development</t>
+  </si>
+  <si>
+    <t>The Chaeli Campaign</t>
+  </si>
+  <si>
+    <t>SAYes Mentoring</t>
+  </si>
+  <si>
+    <t>Local Surf Lounge Academy</t>
+  </si>
+  <si>
+    <t>Chrysalis Academy</t>
+  </si>
+  <si>
+    <t>Ottery Youth Care Centre</t>
+  </si>
+  <si>
+    <t>Robben Island Museum</t>
+  </si>
+  <si>
+    <t>Lwandle Migrant Labour Museum</t>
+  </si>
+  <si>
+    <t>Cape Medical Museum</t>
+  </si>
+  <si>
+    <t>Koopmans-De Wet House</t>
+  </si>
+  <si>
+    <t>Muizenberg Historical Conservation Society</t>
+  </si>
+  <si>
+    <t>Human Library Cape Town</t>
+  </si>
+  <si>
+    <t>Na'l'ibali</t>
+  </si>
+  <si>
+    <t>Lalela Project</t>
+  </si>
+  <si>
+    <t>Friends of Jack Muller Park</t>
+  </si>
+  <si>
+    <t>Oude Molen Eco Village Food Garden</t>
+  </si>
+  <si>
+    <t>Community Women Action</t>
+  </si>
+  <si>
+    <t>Yes We Can Sport AND Jazz Foundation</t>
+  </si>
+  <si>
+    <t>Salt River Community House</t>
+  </si>
+  <si>
+    <t>Institute for Music and Indigenous Arts Development (IMAD)</t>
+  </si>
+  <si>
+    <t>Molteno Reservoir Heritage Association</t>
+  </si>
+  <si>
+    <t>Cape Town Heritage Foundation</t>
+  </si>
+  <si>
+    <t>Salt River Heritage Society</t>
+  </si>
+  <si>
+    <t>Old Wynberg Village Society</t>
+  </si>
+  <si>
+    <t>Vygieskraal Civic Association</t>
+  </si>
+  <si>
+    <t>Lincoln Estate Ratepayers Association</t>
+  </si>
+  <si>
+    <t>Mountview Residence Association</t>
+  </si>
+  <si>
+    <t>Penlyn Estate Civic Association</t>
+  </si>
+  <si>
+    <t>Pinati Estate Civic Association</t>
+  </si>
+  <si>
+    <t>Belvedere East Civic Association</t>
+  </si>
+  <si>
+    <t>Claremont Village Civic Association</t>
+  </si>
+  <si>
+    <t>Greater Lynfrae Civic Association</t>
+  </si>
+  <si>
+    <t>Beverly Hills Helderberg Residents Association</t>
+  </si>
+  <si>
+    <t>Helderberg Community Civic Organisation</t>
+  </si>
+  <si>
+    <t>The Voice of the Cape</t>
+  </si>
+  <si>
+    <t>Fine Music Radio</t>
+  </si>
+  <si>
+    <t>Helderberg FM</t>
+  </si>
+  <si>
+    <t>Radio Disa</t>
+  </si>
+  <si>
+    <t>Trust for Community Outreach and Education (TCOE)</t>
+  </si>
+  <si>
+    <t>Rural Women's Assembly</t>
+  </si>
+  <si>
+    <t>Inyanda National Land Rights Movement</t>
+  </si>
+  <si>
+    <t>Mawubuye Land Rights Forum</t>
+  </si>
+  <si>
+    <t>Cape Town Philharmonic Youth Orchestra</t>
+  </si>
+  <si>
+    <t>Symphony Choir of Cape Town</t>
+  </si>
+  <si>
+    <t>Rosa Choir</t>
+  </si>
+  <si>
+    <t>Jungle Theatre Company</t>
+  </si>
+  <si>
+    <t>New African Theatre Association</t>
+  </si>
+  <si>
+    <t>Likwhezi Arts</t>
+  </si>
+  <si>
+    <t>Hands of Honour</t>
+  </si>
+  <si>
+    <t>Work For Love</t>
+  </si>
+  <si>
+    <t>Nadezhda Job Centre</t>
+  </si>
+  <si>
+    <t>South African Institute for Entrepreneurship</t>
+  </si>
+  <si>
+    <t>Cape Town Volunteer Centre</t>
+  </si>
+  <si>
+    <t>SevaUnite</t>
+  </si>
+  <si>
+    <t>New Day Organisational Development Services</t>
+  </si>
+  <si>
+    <t>Cape Town Tourism Visitor Information Centre</t>
+  </si>
+  <si>
+    <t>City Hall Visitor Experience Office</t>
+  </si>
+  <si>
+    <t>Cape Mental Health (Kite Festival)</t>
+  </si>
+  <si>
+    <t>Young Urbanists</t>
+  </si>
+  <si>
+    <t>Roxy Davis Foundation</t>
+  </si>
+  <si>
+    <t>Wild Buggers Beach Buggy Club</t>
+  </si>
+  <si>
+    <t>Cape Town Craft Club</t>
+  </si>
+  <si>
+    <t>Creative Camera Club</t>
+  </si>
+  <si>
+    <t>Classical Music Appreciation of Cape Town</t>
+  </si>
+  <si>
+    <t>Cape Bird Club</t>
+  </si>
+  <si>
+    <t>Maties Underwater Club</t>
+  </si>
+  <si>
+    <t>ACVV Somerset West</t>
+  </si>
+  <si>
+    <t>ACVV Cape Town</t>
+  </si>
+  <si>
+    <t>CINADE Frailcare Support</t>
+  </si>
+  <si>
+    <t>Gabriella Centre</t>
+  </si>
+  <si>
+    <t>Halli Trust</t>
+  </si>
+  <si>
+    <t>House of Boniwe</t>
+  </si>
+  <si>
+    <t>Souper Troopers</t>
+  </si>
+  <si>
+    <t>uManity Foundation</t>
+  </si>
+  <si>
+    <t>Common Good Foundation</t>
+  </si>
+  <si>
+    <t>Amava Oluntu</t>
+  </si>
+  <si>
+    <t>Union of Jewish Women</t>
+  </si>
+  <si>
+    <t>Catholic Welfare &amp; Development</t>
+  </si>
+  <si>
+    <t>Alulia Pty Ltd</t>
+  </si>
+  <si>
+    <t>Anene Booysen Skills Centre</t>
+  </si>
+  <si>
+    <t>Angels Resource Centres</t>
+  </si>
+  <si>
+    <t>Ayakhanya Foundation</t>
+  </si>
+  <si>
+    <t>SOS Africa</t>
+  </si>
+  <si>
+    <t>The Y Collab</t>
+  </si>
+  <si>
+    <t>African Legend</t>
+  </si>
+  <si>
+    <t>BeSmartKid</t>
+  </si>
+  <si>
+    <t>Teach Me 2</t>
+  </si>
+  <si>
+    <t>Paws-a-While</t>
+  </si>
+  <si>
+    <t>Tom Ro Haven</t>
+  </si>
+  <si>
+    <t>Foundation for Contemporary Research</t>
+  </si>
+  <si>
+    <t>Parkscape Association</t>
+  </si>
+  <si>
+    <t>Friends of the Liesbeek</t>
+  </si>
+  <si>
+    <t>Freshwater Research Centre</t>
+  </si>
+  <si>
+    <t>Friends of Blaauwberg</t>
+  </si>
+  <si>
+    <t>Orange Art Project</t>
+  </si>
+  <si>
+    <t>Jazzart Dance Theatre</t>
+  </si>
+  <si>
+    <t>Elim Night Shelter</t>
+  </si>
+  <si>
+    <t>Happy Valley</t>
+  </si>
+  <si>
+    <t>Loaves and Fishes</t>
+  </si>
+  <si>
+    <t>Moira Henderson House</t>
+  </si>
+  <si>
+    <t>Oasis Reach for Your Dream</t>
+  </si>
+  <si>
+    <t>Somerset West Night Shelter</t>
+  </si>
+  <si>
+    <t>The Haven Night Shelter - Bellville</t>
+  </si>
+  <si>
+    <t>The Haven Night Shelter - Claremont</t>
+  </si>
+  <si>
+    <t>Cancer Association SA</t>
+  </si>
+  <si>
+    <t>Centre for Justice and Crime Prevention</t>
+  </si>
+  <si>
+    <t>Ons Plek Projects Drop-in Centre</t>
+  </si>
+  <si>
+    <t>Congolese Civil Society of South Africa</t>
+  </si>
+  <si>
+    <t>Biowatch South Africa Trust</t>
+  </si>
+  <si>
+    <t>Masifundise Development Trust</t>
+  </si>
+  <si>
+    <t>The Peace Centre (Quaker Peace Centre)</t>
+  </si>
+  <si>
+    <t>Groote Schuur Community Improvement District</t>
+  </si>
+  <si>
+    <t>SAEP (South African Education and Environment Project)</t>
+  </si>
+  <si>
+    <t>The Message Trust</t>
+  </si>
+  <si>
+    <t>Kidzpositive Family Fund</t>
+  </si>
+  <si>
+    <t>Triangle Project</t>
+  </si>
+  <si>
+    <t>Milk Matters</t>
+  </si>
+  <si>
+    <t>Help The Rural Child</t>
+  </si>
+  <si>
+    <t>Scripture Union South Africa</t>
+  </si>
+  <si>
+    <t>St Giles Association for the Handicapped</t>
+  </si>
+  <si>
+    <t>Hello Poppy</t>
+  </si>
+  <si>
+    <t>Kolbe House</t>
+  </si>
+  <si>
+    <t>Imrah Galant (Cape Town Science Centre)</t>
+  </si>
+  <si>
+    <t>Environmental Monitoring Group</t>
+  </si>
+  <si>
+    <t>Book Dash</t>
+  </si>
+  <si>
+    <t>arepp:Theatre for Life</t>
+  </si>
+  <si>
+    <t>Mowbray Rosebank CAN</t>
+  </si>
+  <si>
+    <t>Little Mowbray &amp; Rosebank Improvement District</t>
+  </si>
+  <si>
+    <t>Mowbray Maternity Hospital</t>
+  </si>
+  <si>
+    <t>Integration House Wellness Centre</t>
+  </si>
+  <si>
+    <t>Mowbray Presbyterian Church</t>
+  </si>
+  <si>
+    <t>Mowbray Library</t>
+  </si>
+  <si>
+    <t>Friends of Mostert's Mill</t>
+  </si>
+  <si>
+    <t>Rondebosch Vuleka Trust</t>
+  </si>
+  <si>
+    <t>Friends of Rondebosch Common</t>
+  </si>
+  <si>
+    <t>Rondebosch Community Improvement District</t>
+  </si>
+  <si>
+    <t>Foundation for Alcohol Related Research (FARR)</t>
+  </si>
+  <si>
+    <t>Outliers</t>
+  </si>
+  <si>
+    <t>St. Joseph's Adult Education Programme</t>
+  </si>
+  <si>
+    <t>Paedspal</t>
+  </si>
+  <si>
+    <t>Woodside</t>
+  </si>
+  <si>
+    <t>Beautiful Life Community Development</t>
+  </si>
+  <si>
+    <t>Goedgedacht Trust</t>
+  </si>
+  <si>
+    <t>Centre for Early Childhood Development</t>
+  </si>
+  <si>
+    <t>Westerford High School</t>
+  </si>
+  <si>
+    <t>Garlandale - Rondebosch East Residents' Association</t>
+  </si>
+  <si>
+    <t>Observatory Improvement District</t>
+  </si>
+  <si>
+    <t>Rosebank Residents Association</t>
+  </si>
+  <si>
+    <t>Woodstock Peace Alliance</t>
+  </si>
+  <si>
+    <t>Salt River Circle</t>
+  </si>
+  <si>
+    <t>Claremont Methodist Church</t>
+  </si>
+  <si>
+    <t>Newlands Residents Association</t>
+  </si>
+  <si>
+    <t>Wynberg Boys High School</t>
+  </si>
+  <si>
+    <t>Wynberg Girls High School</t>
+  </si>
+  <si>
+    <t>Lansdowne Civic Association</t>
+  </si>
+  <si>
+    <t>Kenilworth Racecourse Conservation Area</t>
+  </si>
+  <si>
+    <t>Little Theatre (UCT)</t>
+  </si>
+  <si>
+    <t>Mosterts Mill Restoration Trust</t>
+  </si>
+  <si>
+    <t>info@ctsc.org.za</t>
+  </si>
+  <si>
+    <t>bookings@ctsc.org.za</t>
+  </si>
+  <si>
+    <t>stemclubs@ctsc.org.za</t>
+  </si>
+  <si>
+    <t>reach@ctsc.org.za</t>
+  </si>
+  <si>
+    <t>admin@ctsc.org.za</t>
+  </si>
+  <si>
+    <t>portia@ctsc.org.za</t>
+  </si>
+  <si>
+    <t>phillip@ctsc.org.za</t>
+  </si>
+  <si>
+    <t>umr@ctsc.org.za</t>
+  </si>
+  <si>
+    <t>muneerah@ctsc.org.za</t>
+  </si>
+  <si>
+    <t>grant@ctsc.org.za</t>
+  </si>
+  <si>
+    <t>gabi@ctsc.org.za</t>
+  </si>
+  <si>
+    <t>busi@ctsc.org.za</t>
+  </si>
+  <si>
+    <t>info@joburgartgallery.org.za</t>
+  </si>
+  <si>
+    <t>info@standardbankgallery.co.za</t>
+  </si>
+  <si>
+    <t>info@capementalhealth.co.za</t>
+  </si>
+  <si>
+    <t>info@drugcentre.org.za</t>
+  </si>
+  <si>
+    <t>sancawc@mweb.co.za</t>
+  </si>
+  <si>
+    <t>info@stlukeshospice.co.za</t>
+  </si>
+  <si>
+    <t>admin@nazarethhouse.org.za</t>
+  </si>
+  <si>
+    <t>info@rapecrisis.org.za</t>
+  </si>
+  <si>
+    <t>info@gshospitaltrust.org.za</t>
+  </si>
+  <si>
+    <t>info@tbhivcare.org</t>
+  </si>
+  <si>
+    <t>info@m2m.org</t>
+  </si>
+  <si>
+    <t>info@dthf.org.za</t>
+  </si>
+  <si>
+    <t>info@highlandshouse.co.za</t>
+  </si>
+  <si>
+    <t>info@camphill.org.za</t>
+  </si>
+  <si>
+    <t>info@sandownhouse.co.za</t>
+  </si>
+  <si>
+    <t>admin@vineyardoldage.co.za</t>
+  </si>
+  <si>
+    <t>info@rosedale.org.za</t>
+  </si>
+  <si>
+    <t>info@hubertus.co.za</t>
+  </si>
+  <si>
+    <t>info@ageinaction.co.za</t>
+  </si>
+  <si>
+    <t>info@ikamva.co.za</t>
+  </si>
+  <si>
+    <t>info@comchest.org.za</t>
+  </si>
+  <si>
+    <t>info@bigissue.org.za</t>
+  </si>
+  <si>
+    <t>info@mes.org.za</t>
+  </si>
+  <si>
+    <t>info@habitat.org.za</t>
+  </si>
+  <si>
+    <t>info@salesianyouth.org.za</t>
+  </si>
+  <si>
+    <t>info@ubuntupathways.org</t>
+  </si>
+  <si>
+    <t>info@searescue.org.za</t>
+  </si>
+  <si>
+    <t>info@vws.org.za</t>
+  </si>
+  <si>
+    <t>info@wsar.org.za</t>
+  </si>
+  <si>
+    <t>info@stjohnwc.org.za</t>
+  </si>
+  <si>
+    <t>mcsacapetown@iafrica.com</t>
+  </si>
+  <si>
+    <t>info@artscape.co.za</t>
+  </si>
+  <si>
+    <t>info@baxter.co.za</t>
+  </si>
+  <si>
+    <t>info@iziko.org.za</t>
+  </si>
+  <si>
+    <t>info@zeitzmocaa.museum</t>
+  </si>
+  <si>
+    <t>info@cpo.org.za</t>
+  </si>
+  <si>
+    <t>info@capetownopera.co.za</t>
+  </si>
+  <si>
+    <t>info@ikamvayouth.org</t>
+  </si>
+  <si>
+    <t>info@shinecentre.org.za</t>
+  </si>
+  <si>
+    <t>info@christelhouse.org.za</t>
+  </si>
+  <si>
+    <t>info@thelearningtrust.org</t>
+  </si>
+  <si>
+    <t>info@capespca.co.za</t>
+  </si>
+  <si>
+    <t>adoptions@tears.org.za</t>
+  </si>
+  <si>
+    <t>aro@animalrescue.org.za</t>
+  </si>
+  <si>
+    <t>info@sanccob.co.za</t>
+  </si>
+  <si>
+    <t>info@greenpop.org</t>
+  </si>
+  <si>
+    <t>clt@capeleopard.org.za</t>
+  </si>
+  <si>
+    <t>info@anovahealth.co.za</t>
+  </si>
+  <si>
+    <t>info@broadreach.co.za</t>
+  </si>
+  <si>
+    <t>info@wcnhw.org.za</t>
+  </si>
+  <si>
+    <t>info@cansa.org.za</t>
+  </si>
+  <si>
+    <t>info@hpca.co.za</t>
+  </si>
+  <si>
+    <t>info@mariestopes.org.za</t>
+  </si>
+  <si>
+    <t>info@genderjustice.org.za</t>
+  </si>
+  <si>
+    <t>info@tac.org.za</t>
+  </si>
+  <si>
+    <t>info@noah.org.za</t>
+  </si>
+  <si>
+    <t>info@cpoa.co.za</t>
+  </si>
+  <si>
+    <t>info@pinelandsvillage.co.za</t>
+  </si>
+  <si>
+    <t>info@huisevirbejaardes.co.za</t>
+  </si>
+  <si>
+    <t>info@stjosephshome.co.za</t>
+  </si>
+  <si>
+    <t>info@maitlandcottage.co.za</t>
+  </si>
+  <si>
+    <t>info@vpuu.org.za</t>
+  </si>
+  <si>
+    <t>info@corc.co.za</t>
+  </si>
+  <si>
+    <t>info@dag.org.za</t>
+  </si>
+  <si>
+    <t>info@isandla.org.za</t>
+  </si>
+  <si>
+    <t>info@seri-sa.org</t>
+  </si>
+  <si>
+    <t>info@nu.org.za</t>
+  </si>
+  <si>
+    <t>info@thewarehouse.org.za</t>
+  </si>
+  <si>
+    <t>info@livinghope.co.za</t>
+  </si>
+  <si>
+    <t>info@nazarene.org.za</t>
+  </si>
+  <si>
+    <t>info@ubuntufootball.org.za</t>
+  </si>
+  <si>
+    <t>info@ctevc.org.za</t>
+  </si>
+  <si>
+    <t>info@metrorescue.co.za</t>
+  </si>
+  <si>
+    <t>info@capetown.gov.za</t>
+  </si>
+  <si>
+    <t>info@lifesavingwc.co.za</t>
+  </si>
+  <si>
+    <t>info@firevolunteers.co.za</t>
+  </si>
+  <si>
+    <t>info@thefugard.com</t>
+  </si>
+  <si>
+    <t>info@alexanderbar.co.za</t>
+  </si>
+  <si>
+    <t>info@theatrearts.co.za</t>
+  </si>
+  <si>
+    <t>info@capetowncomedyclub.co.za</t>
+  </si>
+  <si>
+    <t>info@kalkbaytheatre.co.za</t>
+  </si>
+  <si>
+    <t>info@youngblood.co.za</t>
+  </si>
+  <si>
+    <t>info@ava.co.za</t>
+  </si>
+  <si>
+    <t>info@capetownartfair.co.za</t>
+  </si>
+  <si>
+    <t>info@designindaba.com</t>
+  </si>
+  <si>
+    <t>info@bottomup.co.za</t>
+  </si>
+  <si>
+    <t>info@lifechoices.org.za</t>
+  </si>
+  <si>
+    <t>youth@ikamva.co.za</t>
+  </si>
+  <si>
+    <t>info@avafrica.org.za</t>
+  </si>
+  <si>
+    <t>wc@presidentsaward.org.za</t>
+  </si>
+  <si>
+    <t>info@rlabs.org.za</t>
+  </si>
+  <si>
+    <t>info@ampathfoundation.com</t>
+  </si>
+  <si>
+    <t>info@shineliteracy.org.za</t>
+  </si>
+  <si>
+    <t>info@cheetah.co.za</t>
+  </si>
+  <si>
+    <t>info@pantheraafrica.org</t>
+  </si>
+  <si>
+    <t>wc@wessa.co.za</t>
+  </si>
+  <si>
+    <t>info@fotm.org.za</t>
+  </si>
+  <si>
+    <t>info@cteet.co.za</t>
+  </si>
+  <si>
+    <t>volunteers@sanbi.org.za</t>
+  </si>
+  <si>
+    <t>info@sst.org.za</t>
+  </si>
+  <si>
+    <t>info@wprugby.co.za</t>
+  </si>
+  <si>
+    <t>info@wpca.co.za</t>
+  </si>
+  <si>
+    <t>info@capetowncycletour.com</t>
+  </si>
+  <si>
+    <t>info@twooceansmarathon.org.za</t>
+  </si>
+  <si>
+    <t>info@capetownspurs.co.za</t>
+  </si>
+  <si>
+    <t>info@sarda.org.za</t>
+  </si>
+  <si>
+    <t>doretted@mweb.co.za</t>
+  </si>
+  <si>
+    <t>moira.awshelderberg@gmail.com</t>
+  </si>
+  <si>
+    <t>info@darg.org.za</t>
+  </si>
+  <si>
+    <t>adoptions@africantails.co.za</t>
+  </si>
+  <si>
+    <t>controlinspector@aacl-ct.co.za</t>
+  </si>
+  <si>
+    <t>hello@animallifeline.org.za</t>
+  </si>
+  <si>
+    <t>vet@animalrescue.org.za</t>
+  </si>
+  <si>
+    <t>mwdapg@mweb.co.za</t>
+  </si>
+  <si>
+    <t>info@abalimi.org.za</t>
+  </si>
+  <si>
+    <t>info@communitree.org</t>
+  </si>
+  <si>
+    <t>witsands.reserve@capetown.gov.za</t>
+  </si>
+  <si>
+    <t>wolfgat.naturereserve@capetown.gov.za</t>
+  </si>
+  <si>
+    <t>info@capeculturalcollective.org</t>
+  </si>
+  <si>
+    <t>info@masquetheatre.co.za</t>
+  </si>
+  <si>
+    <t>info@districtsix.co.za</t>
+  </si>
+  <si>
+    <t>info@justgrace.org.za</t>
+  </si>
+  <si>
+    <t>info@wordworks.org.za</t>
+  </si>
+  <si>
+    <t>info@khulisa.org.za</t>
+  </si>
+  <si>
+    <t>info@homeless.org.za</t>
+  </si>
+  <si>
+    <t>info@thehopeexchange.org</t>
+  </si>
+  <si>
+    <t>lisa@straatwerk.org.za</t>
+  </si>
+  <si>
+    <t>onsplek@onsplek.org.za</t>
+  </si>
+  <si>
+    <t>info@homestead.org.za</t>
+  </si>
+  <si>
+    <t>services@oasis.org.za</t>
+  </si>
+  <si>
+    <t>wessel.vandenberg@olf.org.za</t>
+  </si>
+  <si>
+    <t>dct@worldonline.co.za</t>
+  </si>
+  <si>
+    <t>wolanani@wolanani.co.za</t>
+  </si>
+  <si>
+    <t>admin@mfesane.org.za</t>
+  </si>
+  <si>
+    <t>info@blacksash.org.za</t>
+  </si>
+  <si>
+    <t>info@helpkids.org.za</t>
+  </si>
+  <si>
+    <t>info@marshmemorial.org.za</t>
+  </si>
+  <si>
+    <t>admin@uzwelo.org</t>
+  </si>
+  <si>
+    <t>comms@chaelicampaign.org</t>
+  </si>
+  <si>
+    <t>info@sayes.org.za</t>
+  </si>
+  <si>
+    <t>info@chrysalisacademy.org.za</t>
+  </si>
+  <si>
+    <t>OtteryYouth@telkomsa.net</t>
+  </si>
+  <si>
+    <t>info@robbenisland.org.za</t>
+  </si>
+  <si>
+    <t>info@lwandle.com</t>
+  </si>
+  <si>
+    <t>info@humanlibrarycapetown.org</t>
+  </si>
+  <si>
+    <t>info@nalibali.org</t>
+  </si>
+  <si>
+    <t>info@lalelaproject.org</t>
+  </si>
+  <si>
+    <t>r.solomons@yeswecansportandjazz.com</t>
+  </si>
+  <si>
+    <t>vhjarch@kingsley.co.za</t>
+  </si>
+  <si>
+    <t>info@cthf.co.za</t>
+  </si>
+  <si>
+    <t>beverlyhillshra@gmail.com</t>
+  </si>
+  <si>
+    <t>juriesn@yahoo.com</t>
+  </si>
+  <si>
+    <t>info@vocfm.co.za</t>
+  </si>
+  <si>
+    <t>fmr@fmr.co.za</t>
+  </si>
+  <si>
+    <t>feedback@helderbergfm.co.za</t>
+  </si>
+  <si>
+    <t>info@disafm.com</t>
+  </si>
+  <si>
+    <t>info@tcoe.org.za</t>
+  </si>
+  <si>
+    <t>info@jungletheatre.co.za</t>
+  </si>
+  <si>
+    <t>info@handsofhonour.org.za</t>
+  </si>
+  <si>
+    <t>info@workforlove.org.za</t>
+  </si>
+  <si>
+    <t>southafrica@icvolunteers.org</t>
+  </si>
+  <si>
+    <t>info@sevaunite.org</t>
+  </si>
+  <si>
+    <t>info@capetown.travel</t>
+  </si>
+  <si>
+    <t>cityhall@capetown.travel</t>
+  </si>
+  <si>
+    <t>info@roxydavisfoundation.org</t>
+  </si>
+  <si>
+    <t>anton@wildbuggers.co.za</t>
+  </si>
+  <si>
+    <t>hello@capetowncraftclub.com</t>
+  </si>
+  <si>
+    <t>info@creativecameraclub.co.za</t>
+  </si>
+  <si>
+    <t>info@cmacofct.com</t>
+  </si>
+  <si>
+    <t>info@capebirdclub.org.za</t>
+  </si>
+  <si>
+    <t>ACVVSWE@TELKOMSA.NET</t>
+  </si>
+  <si>
+    <t>tamara@acvv.org.za</t>
+  </si>
+  <si>
+    <t>WILMAPAPIER2@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>INFO@GABRIELLACENTRE.ORG.ZA</t>
+  </si>
+  <si>
+    <t>HEIDI@HALLITRUST.CO.ZA</t>
+  </si>
+  <si>
+    <t>gwenj@houseofboniwe.co.za</t>
+  </si>
+  <si>
+    <t>kerry@soupertroopers.org</t>
+  </si>
+  <si>
+    <t>Darryn.Hector@uManity.co.za</t>
+  </si>
+  <si>
+    <t>info@commongood.org.za</t>
+  </si>
+  <si>
+    <t>info@amava.org</t>
+  </si>
+  <si>
+    <t>projects@ujwcape.co.za</t>
+  </si>
+  <si>
+    <t>zukile.tom@cwd.co.za</t>
+  </si>
+  <si>
+    <t>andile@alulia.co.za</t>
+  </si>
+  <si>
+    <t>solutionsbasenpo@outlook.com</t>
+  </si>
+  <si>
+    <t>angels@angelsinc.co.za</t>
+  </si>
+  <si>
+    <t>Ayakhanya@gmail.com</t>
+  </si>
+  <si>
+    <t>matt@sosafrica.com</t>
+  </si>
+  <si>
+    <t>meg@y-collab.com</t>
+  </si>
+  <si>
+    <t>katja@africanlegend.org.za</t>
+  </si>
+  <si>
+    <t>bsktutors@gmail.com</t>
+  </si>
+  <si>
+    <t>start@teachme2.com</t>
+  </si>
+  <si>
+    <t>info@pawsawhile.org</t>
+  </si>
+  <si>
+    <t>info@tomrohaven.org.za</t>
+  </si>
+  <si>
+    <t>info@fcr.org.za</t>
+  </si>
+  <si>
+    <t>info@parkscape.org.za</t>
+  </si>
+  <si>
+    <t>info@fol.org.za</t>
+  </si>
+  <si>
+    <t>admin@frcsa.org.za</t>
+  </si>
+  <si>
+    <t>Friendsofbca@mweb.co.za</t>
+  </si>
+  <si>
+    <t>info@orangeart.org.za</t>
+  </si>
+  <si>
+    <t>dance@jazzart.co.za</t>
+  </si>
+  <si>
+    <t>elimnightshelter@telkomsa.net</t>
+  </si>
+  <si>
+    <t>cynn@telkomsa.net</t>
+  </si>
+  <si>
+    <t>loavesfishes@telkomsa.net</t>
+  </si>
+  <si>
+    <t>moirahenderson@haven.org.za</t>
+  </si>
+  <si>
+    <t>oasisplace@mweb.co.za</t>
+  </si>
+  <si>
+    <t>manager@swnightshelter.org.za</t>
+  </si>
+  <si>
+    <t>sharon@haven.org.za</t>
+  </si>
+  <si>
+    <t>claremont@haven.org.za</t>
+  </si>
+  <si>
+    <t>dduplooy@cansa.org.za</t>
+  </si>
+  <si>
+    <t>patrick@cjcp.org.za</t>
+  </si>
+  <si>
+    <t>pam.reflect@gmail.com</t>
+  </si>
+  <si>
+    <t>contact@congolesecivilsocietysa.org</t>
+  </si>
+  <si>
+    <t>biowatch@mweb.co.za</t>
+  </si>
+  <si>
+    <t>infocom@masifundise.org.za</t>
+  </si>
+  <si>
+    <t>peacecentre@peacecentre.org.za</t>
+  </si>
+  <si>
+    <t>info@gscid.co.za</t>
+  </si>
+  <si>
+    <t>tracey@saep.org</t>
+  </si>
+  <si>
+    <t>info@message.org.za</t>
+  </si>
+  <si>
+    <t>info@kidzpositive.org</t>
+  </si>
+  <si>
+    <t>reception@triangle.org.za</t>
+  </si>
+  <si>
+    <t>info@milkmatters.org</t>
+  </si>
+  <si>
+    <t>info@ruralchild.org.za</t>
+  </si>
+  <si>
+    <t>pearlm@su.org.za</t>
+  </si>
+  <si>
+    <t>stgiles@cybertrade.co.za</t>
+  </si>
+  <si>
+    <t>hello@hellopoppy.co.za</t>
+  </si>
+  <si>
+    <t>kolbe.house@telkomsa.net</t>
+  </si>
+  <si>
+    <t>Imrah@ctsc.org.za</t>
+  </si>
+  <si>
+    <t>stephen@emg.org.za</t>
+  </si>
+  <si>
+    <t>team@bookdash.org</t>
+  </si>
+  <si>
+    <t>capeadmin@nullarepp.org.za</t>
+  </si>
+  <si>
+    <t>mowbrayrosebankcan@gmail.com</t>
+  </si>
+  <si>
+    <t>info@lmrid.capetown</t>
+  </si>
+  <si>
+    <t>Janine.Joemat@westerncape.gov.za</t>
+  </si>
+  <si>
+    <t>jacquikoep@gmail.com</t>
+  </si>
+  <si>
+    <t>mowbray.presby@telkomsa.net</t>
+  </si>
+  <si>
+    <t>mowbray.library@capetown.gov.za</t>
+  </si>
+  <si>
+    <t>pilotjhammer@gmail.com</t>
+  </si>
+  <si>
+    <t>frances@communitree.in</t>
+  </si>
+  <si>
+    <t>info@rondeboschvulekatrust.co.za</t>
+  </si>
+  <si>
+    <t>FriendsofRondeboschCommon@gmail.com</t>
+  </si>
+  <si>
+    <t>rcidoffices@gmail.com</t>
+  </si>
+  <si>
+    <t>lo@farrsa.org.za</t>
+  </si>
+  <si>
+    <t>info@outliers.org.za</t>
+  </si>
+  <si>
+    <t>kajl@global.co.za</t>
+  </si>
+  <si>
+    <t>info@paedspal.org.za</t>
+  </si>
+  <si>
+    <t>fundraiser@woodside.org.za</t>
+  </si>
+  <si>
+    <t>info@beautifullifecommunity.co.za</t>
+  </si>
+  <si>
+    <t>info@goedgedacht.org</t>
+  </si>
+  <si>
+    <t>cecd@iafrica.com</t>
+  </si>
+  <si>
+    <t>admin@westerford.co.za</t>
+  </si>
+  <si>
+    <t>roekeya@damonabadia.co.za</t>
+  </si>
+  <si>
+    <t>info@obsid.co.za</t>
+  </si>
+  <si>
+    <t>info@rosebankra.co.za</t>
+  </si>
+  <si>
+    <t>info@woodstockpeace.org.za</t>
+  </si>
+  <si>
+    <t>info@saltrivercircle.co.za</t>
+  </si>
+  <si>
+    <t>office@claremontmethodist.org.za</t>
+  </si>
+  <si>
+    <t>info@newlandsra.co.za</t>
+  </si>
+  <si>
+    <t>info@wbhs.org.za</t>
+  </si>
+  <si>
+    <t>info@wghs.co.za</t>
+  </si>
+  <si>
+    <t>info@lansdownecivic.co.za</t>
+  </si>
+  <si>
+    <t>info@kenilworthracecourse.co.za</t>
+  </si>
+  <si>
+    <t>littletheatre@uct.ac.za</t>
+  </si>
+  <si>
+    <t>info@mostertsmill.org.za</t>
+  </si>
+  <si>
+    <t>Museums &amp; Heritage</t>
   </si>
   <si>
     <t>Youth &amp; Tutoring</t>
   </si>
   <si>
+    <t>Volunteer Centres &amp; NGO Support</t>
+  </si>
+  <si>
+    <t>Community Media &amp; Radio</t>
+  </si>
+  <si>
+    <t>Arts &amp; Culture</t>
+  </si>
+  <si>
+    <t>Health &amp; Wellness</t>
+  </si>
+  <si>
+    <t>Senior Care</t>
+  </si>
+  <si>
+    <t>Community Development</t>
+  </si>
+  <si>
+    <t>Emergency &amp; Rescue</t>
+  </si>
+  <si>
+    <t>Animal Welfare</t>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>Sports &amp; Recreation</t>
+  </si>
+  <si>
+    <t>Libraries &amp; Reading Programmes</t>
+  </si>
+  <si>
+    <t>Public Parks &amp; Gardens</t>
+  </si>
+  <si>
+    <t>Cultural Centres &amp; Community Halls</t>
+  </si>
+  <si>
+    <t>Historic Sites &amp; Preservation</t>
+  </si>
+  <si>
+    <t>Neighbourhood Associations</t>
+  </si>
+  <si>
+    <t>Community Markets &amp; Farmers Markets</t>
+  </si>
+  <si>
+    <t>Performing Arts &amp; Music Groups</t>
+  </si>
+  <si>
+    <t>Adult Education &amp; Skills Training</t>
+  </si>
+  <si>
+    <t>Tourism &amp; Visitor Information</t>
+  </si>
+  <si>
+    <t>Community Events &amp; Festivals</t>
+  </si>
+  <si>
+    <t>Hobby &amp; Special Interest Clubs</t>
+  </si>
+  <si>
+    <t>Community Safety</t>
+  </si>
+  <si>
+    <t>Refugee &amp; Migrant Support</t>
+  </si>
+  <si>
     <t>Cape Town</t>
   </si>
   <si>
-    <t>ofm@amazon.fr</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5683f4650fb6a310c347c6ed5446d5ee75c1e03cbc870409969a7c809bfa2393JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e5dc6c5-e08f-6720-28d0-d129e1136640&amp;u=a1aHR0cHM6Ly93d3cuNjBtaWxsaW9ucy1tYWcuY29tL2ZvcnVtL2QvMjA4NzM3LWFtYXpvbi1jbG90dXJlLW1vbi1jb21wdGU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>Cape Town CBD</t>
-  </si>
-  <si>
-    <t>Bing</t>
+    <t>Johannesburg CBD</t>
+  </si>
+  <si>
+    <t>Constantia</t>
+  </si>
+  <si>
+    <t>Helderberg</t>
+  </si>
+  <si>
+    <t>Hout Bay</t>
+  </si>
+  <si>
+    <t>Fish Hoek</t>
+  </si>
+  <si>
+    <t>Muizenberg</t>
+  </si>
+  <si>
+    <t>Atlantis</t>
+  </si>
+  <si>
+    <t>Mitchells Plain</t>
+  </si>
+  <si>
+    <t>Gugulethu</t>
+  </si>
+  <si>
+    <t>Langa</t>
+  </si>
+  <si>
+    <t>Khayelitsha</t>
+  </si>
+  <si>
+    <t>Philippi East</t>
+  </si>
+  <si>
+    <t>Observatory</t>
+  </si>
+  <si>
+    <t>Rondebosch</t>
+  </si>
+  <si>
+    <t>Woodstock</t>
+  </si>
+  <si>
+    <t>Tokai</t>
+  </si>
+  <si>
+    <t>Ottery</t>
+  </si>
+  <si>
+    <t>Lwandle</t>
+  </si>
+  <si>
+    <t>Green Point</t>
+  </si>
+  <si>
+    <t>Pinelands</t>
+  </si>
+  <si>
+    <t>Salt River</t>
+  </si>
+  <si>
+    <t>Wynberg</t>
+  </si>
+  <si>
+    <t>Athlone</t>
+  </si>
+  <si>
+    <t>Claremont</t>
+  </si>
+  <si>
+    <t>Mowbray</t>
+  </si>
+  <si>
+    <t>Rondebosch East</t>
+  </si>
+  <si>
+    <t>Rosebank</t>
+  </si>
+  <si>
+    <t>Newlands</t>
+  </si>
+  <si>
+    <t>Lansdowne</t>
+  </si>
+  <si>
+    <t>Kenilworth</t>
+  </si>
+  <si>
+    <t>021 300 3200</t>
+  </si>
+  <si>
+    <t>+27 11 725 3130</t>
+  </si>
+  <si>
+    <t>+27 11 631 1889</t>
+  </si>
+  <si>
+    <t>021 465 3412</t>
+  </si>
+  <si>
+    <t>021 794 4393</t>
+  </si>
+  <si>
+    <t>021 790 0383</t>
+  </si>
+  <si>
+    <t>021 782 5845</t>
+  </si>
+  <si>
+    <t>021 371 1653</t>
+  </si>
+  <si>
+    <t>021 788 5702</t>
+  </si>
+  <si>
+    <t>021 577 5000</t>
+  </si>
+  <si>
+    <t>021 371 5141</t>
+  </si>
+  <si>
+    <t>021 466 7200</t>
+  </si>
+  <si>
+    <t>072 343 3552</t>
+  </si>
+  <si>
+    <t>021 788 4135</t>
+  </si>
+  <si>
+    <t>021 674 6119</t>
+  </si>
+  <si>
+    <t>021 461 5508</t>
+  </si>
+  <si>
+    <t>021 425 0140</t>
+  </si>
+  <si>
+    <t>021 685 4052</t>
+  </si>
+  <si>
+    <t>021 419 9763</t>
+  </si>
+  <si>
+    <t>021 671 2698</t>
+  </si>
+  <si>
+    <t>021 447 2091</t>
+  </si>
+  <si>
+    <t>021 945 3992</t>
+  </si>
+  <si>
+    <t>021 461 7804</t>
+  </si>
+  <si>
+    <t>021 638 3127</t>
+  </si>
+  <si>
+    <t>021 689 9301</t>
+  </si>
+  <si>
+    <t>021 762 3835</t>
+  </si>
+  <si>
+    <t>021 830 0795</t>
+  </si>
+  <si>
+    <t>066 005 4449</t>
+  </si>
+  <si>
+    <t>021 712 1023</t>
+  </si>
+  <si>
+    <t>021 703 3030</t>
+  </si>
+  <si>
+    <t>021 413 4200</t>
+  </si>
+  <si>
+    <t>021 845 6119</t>
+  </si>
+  <si>
+    <t>021 418 5663</t>
+  </si>
+  <si>
+    <t>021 481 3935</t>
+  </si>
+  <si>
+    <t>021 788 9295</t>
+  </si>
+  <si>
+    <t>067 206 5837</t>
+  </si>
+  <si>
+    <t>083 646 6616</t>
+  </si>
+  <si>
+    <t>021 697 5682</t>
+  </si>
+  <si>
+    <t>084 083 0002</t>
+  </si>
+  <si>
+    <t>021 692 2646</t>
+  </si>
+  <si>
+    <t>083 589 7589</t>
+  </si>
+  <si>
+    <t>021 692 2045</t>
+  </si>
+  <si>
+    <t>021 401 1013</t>
+  </si>
+  <si>
+    <t>021 100 6936</t>
+  </si>
+  <si>
+    <t>021 859 1105</t>
+  </si>
+  <si>
+    <t>021 788 5641</t>
+  </si>
+  <si>
+    <t>021 696 2392</t>
+  </si>
+  <si>
+    <t>072 138 9150</t>
+  </si>
+  <si>
+    <t>021 982 0079</t>
+  </si>
+  <si>
+    <t>021 447 2023</t>
+  </si>
+  <si>
+    <t>021 761 7807</t>
+  </si>
+  <si>
+    <t>086 132 2223</t>
+  </si>
+  <si>
+    <t>021 447 9040</t>
+  </si>
+  <si>
+    <t>082 497 7721</t>
+  </si>
+  <si>
+    <t>www.ctsc.org.za</t>
+  </si>
+  <si>
+    <t>https://www.joburg.org.za</t>
+  </si>
+  <si>
+    <t>https://www.standardbank.com</t>
+  </si>
+  <si>
+    <t>www.mcsa.org.za</t>
+  </si>
+  <si>
+    <t>www.darg.org.za</t>
+  </si>
+  <si>
+    <t>www.abalimi.org.za</t>
+  </si>
+  <si>
+    <t>www.districtsix.co.za</t>
+  </si>
+  <si>
+    <t>www.wordworks.org.za</t>
+  </si>
+  <si>
+    <t>www.khulisa.org.za</t>
+  </si>
+  <si>
+    <t>www.wolanani.co.za</t>
+  </si>
+  <si>
+    <t>www.nalibali.org</t>
+  </si>
+  <si>
+    <t>www.lalelaproject.org</t>
+  </si>
+  <si>
+    <t>www.yeswecansportandjazz.com</t>
+  </si>
+  <si>
+    <t>www.cthf.co.za</t>
+  </si>
+  <si>
+    <t>oldwynbergvillagesociety.org</t>
+  </si>
+  <si>
+    <t>www.vocfm.co.za</t>
+  </si>
+  <si>
+    <t>www.fmr.co.za</t>
+  </si>
+  <si>
+    <t>helderbergfm.co.za</t>
+  </si>
+  <si>
+    <t>www.disafm.co.za</t>
+  </si>
+  <si>
+    <t>www.cmacofct.com</t>
   </si>
   <si>
     <t>Yes</t>
@@ -409,10 +2566,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:L320"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -440,36 +2597,5497 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>330</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>605</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="E2" t="s">
+        <v>661</v>
+      </c>
+      <c r="F2" t="s">
+        <v>715</v>
+      </c>
+      <c r="G2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="B3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C3" t="s">
+        <v>605</v>
+      </c>
+      <c r="D3" t="s">
+        <v>630</v>
+      </c>
+      <c r="E3" t="s">
+        <v>661</v>
+      </c>
+      <c r="F3" t="s">
+        <v>715</v>
+      </c>
+      <c r="G3" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+      <c r="B4" t="s">
+        <v>332</v>
+      </c>
+      <c r="C4" t="s">
+        <v>606</v>
+      </c>
+      <c r="D4" t="s">
+        <v>630</v>
+      </c>
+      <c r="E4" t="s">
+        <v>661</v>
+      </c>
+      <c r="F4" t="s">
+        <v>715</v>
+      </c>
+      <c r="G4" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
+      <c r="B5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C5" t="s">
+        <v>606</v>
+      </c>
+      <c r="D5" t="s">
+        <v>630</v>
+      </c>
+      <c r="E5" t="s">
+        <v>661</v>
+      </c>
+      <c r="F5" t="s">
+        <v>715</v>
+      </c>
+      <c r="G5" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
         <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>334</v>
+      </c>
+      <c r="C6" t="s">
+        <v>605</v>
+      </c>
+      <c r="D6" t="s">
+        <v>630</v>
+      </c>
+      <c r="E6" t="s">
+        <v>661</v>
+      </c>
+      <c r="F6" t="s">
+        <v>715</v>
+      </c>
+      <c r="G6" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>335</v>
+      </c>
+      <c r="C7" t="s">
+        <v>605</v>
+      </c>
+      <c r="D7" t="s">
+        <v>630</v>
+      </c>
+      <c r="E7" t="s">
+        <v>661</v>
+      </c>
+      <c r="F7" t="s">
+        <v>715</v>
+      </c>
+      <c r="G7" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>336</v>
+      </c>
+      <c r="C8" t="s">
+        <v>606</v>
+      </c>
+      <c r="D8" t="s">
+        <v>630</v>
+      </c>
+      <c r="E8" t="s">
+        <v>661</v>
+      </c>
+      <c r="F8" t="s">
+        <v>715</v>
+      </c>
+      <c r="G8" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>337</v>
+      </c>
+      <c r="C9" t="s">
+        <v>606</v>
+      </c>
+      <c r="D9" t="s">
+        <v>630</v>
+      </c>
+      <c r="E9" t="s">
+        <v>661</v>
+      </c>
+      <c r="F9" t="s">
+        <v>715</v>
+      </c>
+      <c r="G9" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10" t="s">
+        <v>607</v>
+      </c>
+      <c r="D10" t="s">
+        <v>630</v>
+      </c>
+      <c r="E10" t="s">
+        <v>661</v>
+      </c>
+      <c r="F10" t="s">
+        <v>715</v>
+      </c>
+      <c r="G10" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>339</v>
+      </c>
+      <c r="C11" t="s">
+        <v>607</v>
+      </c>
+      <c r="D11" t="s">
+        <v>630</v>
+      </c>
+      <c r="E11" t="s">
+        <v>661</v>
+      </c>
+      <c r="F11" t="s">
+        <v>715</v>
+      </c>
+      <c r="G11" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>340</v>
+      </c>
+      <c r="C12" t="s">
+        <v>608</v>
+      </c>
+      <c r="D12" t="s">
+        <v>630</v>
+      </c>
+      <c r="E12" t="s">
+        <v>661</v>
+      </c>
+      <c r="F12" t="s">
+        <v>715</v>
+      </c>
+      <c r="G12" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>341</v>
+      </c>
+      <c r="C13" t="s">
+        <v>605</v>
+      </c>
+      <c r="D13" t="s">
+        <v>630</v>
+      </c>
+      <c r="E13" t="s">
+        <v>661</v>
+      </c>
+      <c r="F13" t="s">
+        <v>715</v>
+      </c>
+      <c r="G13" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>342</v>
+      </c>
+      <c r="C14" t="s">
+        <v>609</v>
+      </c>
+      <c r="D14" t="s">
+        <v>631</v>
+      </c>
+      <c r="E14" t="s">
+        <v>662</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="G14" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>343</v>
+      </c>
+      <c r="C15" t="s">
+        <v>609</v>
+      </c>
+      <c r="D15" t="s">
+        <v>631</v>
+      </c>
+      <c r="E15" t="s">
+        <v>663</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="G15" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>344</v>
+      </c>
+      <c r="C16" t="s">
+        <v>610</v>
+      </c>
+      <c r="D16" t="s">
+        <v>630</v>
+      </c>
+      <c r="G16" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>345</v>
+      </c>
+      <c r="C17" t="s">
+        <v>610</v>
+      </c>
+      <c r="D17" t="s">
+        <v>630</v>
+      </c>
+      <c r="G17" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s">
+        <v>346</v>
+      </c>
+      <c r="C18" t="s">
+        <v>610</v>
+      </c>
+      <c r="D18" t="s">
+        <v>630</v>
+      </c>
+      <c r="G18" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" t="s">
+        <v>347</v>
+      </c>
+      <c r="C19" t="s">
+        <v>610</v>
+      </c>
+      <c r="D19" t="s">
+        <v>630</v>
+      </c>
+      <c r="G19" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s">
+        <v>348</v>
+      </c>
+      <c r="C20" t="s">
+        <v>610</v>
+      </c>
+      <c r="D20" t="s">
+        <v>630</v>
+      </c>
+      <c r="G20" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" t="s">
+        <v>349</v>
+      </c>
+      <c r="C21" t="s">
+        <v>610</v>
+      </c>
+      <c r="D21" t="s">
+        <v>630</v>
+      </c>
+      <c r="G21" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" t="s">
+        <v>350</v>
+      </c>
+      <c r="C22" t="s">
+        <v>610</v>
+      </c>
+      <c r="D22" t="s">
+        <v>630</v>
+      </c>
+      <c r="G22" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" t="s">
+        <v>351</v>
+      </c>
+      <c r="C23" t="s">
+        <v>610</v>
+      </c>
+      <c r="D23" t="s">
+        <v>630</v>
+      </c>
+      <c r="G23" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" t="s">
+        <v>352</v>
+      </c>
+      <c r="C24" t="s">
+        <v>610</v>
+      </c>
+      <c r="D24" t="s">
+        <v>630</v>
+      </c>
+      <c r="G24" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" t="s">
+        <v>353</v>
+      </c>
+      <c r="C25" t="s">
+        <v>610</v>
+      </c>
+      <c r="D25" t="s">
+        <v>630</v>
+      </c>
+      <c r="G25" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" t="s">
+        <v>354</v>
+      </c>
+      <c r="C26" t="s">
+        <v>611</v>
+      </c>
+      <c r="D26" t="s">
+        <v>630</v>
+      </c>
+      <c r="G26" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" t="s">
+        <v>355</v>
+      </c>
+      <c r="C27" t="s">
+        <v>611</v>
+      </c>
+      <c r="D27" t="s">
+        <v>630</v>
+      </c>
+      <c r="G27" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" t="s">
+        <v>356</v>
+      </c>
+      <c r="C28" t="s">
+        <v>611</v>
+      </c>
+      <c r="D28" t="s">
+        <v>630</v>
+      </c>
+      <c r="G28" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" t="s">
+        <v>357</v>
+      </c>
+      <c r="C29" t="s">
+        <v>611</v>
+      </c>
+      <c r="D29" t="s">
+        <v>630</v>
+      </c>
+      <c r="G29" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" t="s">
+        <v>358</v>
+      </c>
+      <c r="C30" t="s">
+        <v>611</v>
+      </c>
+      <c r="D30" t="s">
+        <v>630</v>
+      </c>
+      <c r="G30" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" t="s">
+        <v>359</v>
+      </c>
+      <c r="C31" t="s">
+        <v>611</v>
+      </c>
+      <c r="D31" t="s">
+        <v>630</v>
+      </c>
+      <c r="G31" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" t="s">
+        <v>360</v>
+      </c>
+      <c r="C32" t="s">
+        <v>611</v>
+      </c>
+      <c r="D32" t="s">
+        <v>630</v>
+      </c>
+      <c r="G32" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" t="s">
+        <v>361</v>
+      </c>
+      <c r="C33" t="s">
+        <v>612</v>
+      </c>
+      <c r="D33" t="s">
+        <v>630</v>
+      </c>
+      <c r="G33" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" t="s">
+        <v>362</v>
+      </c>
+      <c r="C34" t="s">
+        <v>612</v>
+      </c>
+      <c r="D34" t="s">
+        <v>630</v>
+      </c>
+      <c r="G34" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" t="s">
+        <v>363</v>
+      </c>
+      <c r="C35" t="s">
+        <v>612</v>
+      </c>
+      <c r="D35" t="s">
+        <v>630</v>
+      </c>
+      <c r="G35" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" t="s">
+        <v>364</v>
+      </c>
+      <c r="C36" t="s">
+        <v>612</v>
+      </c>
+      <c r="D36" t="s">
+        <v>630</v>
+      </c>
+      <c r="G36" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" t="s">
+        <v>365</v>
+      </c>
+      <c r="C37" t="s">
+        <v>612</v>
+      </c>
+      <c r="D37" t="s">
+        <v>630</v>
+      </c>
+      <c r="G37" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" t="s">
+        <v>366</v>
+      </c>
+      <c r="C38" t="s">
+        <v>612</v>
+      </c>
+      <c r="D38" t="s">
+        <v>630</v>
+      </c>
+      <c r="G38" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" t="s">
+        <v>367</v>
+      </c>
+      <c r="C39" t="s">
+        <v>612</v>
+      </c>
+      <c r="D39" t="s">
+        <v>630</v>
+      </c>
+      <c r="G39" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" t="s">
+        <v>368</v>
+      </c>
+      <c r="C40" t="s">
+        <v>613</v>
+      </c>
+      <c r="D40" t="s">
+        <v>630</v>
+      </c>
+      <c r="G40" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" t="s">
+        <v>369</v>
+      </c>
+      <c r="C41" t="s">
+        <v>613</v>
+      </c>
+      <c r="D41" t="s">
+        <v>630</v>
+      </c>
+      <c r="G41" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" t="s">
+        <v>370</v>
+      </c>
+      <c r="C42" t="s">
+        <v>613</v>
+      </c>
+      <c r="D42" t="s">
+        <v>630</v>
+      </c>
+      <c r="G42" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" t="s">
+        <v>371</v>
+      </c>
+      <c r="C43" t="s">
+        <v>613</v>
+      </c>
+      <c r="D43" t="s">
+        <v>630</v>
+      </c>
+      <c r="G43" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" t="s">
+        <v>372</v>
+      </c>
+      <c r="C44" t="s">
+        <v>613</v>
+      </c>
+      <c r="D44" t="s">
+        <v>630</v>
+      </c>
+      <c r="G44" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45" t="s">
+        <v>373</v>
+      </c>
+      <c r="C45" t="s">
+        <v>609</v>
+      </c>
+      <c r="D45" t="s">
+        <v>630</v>
+      </c>
+      <c r="G45" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" t="s">
+        <v>374</v>
+      </c>
+      <c r="C46" t="s">
+        <v>609</v>
+      </c>
+      <c r="D46" t="s">
+        <v>630</v>
+      </c>
+      <c r="G46" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>57</v>
+      </c>
+      <c r="B47" t="s">
+        <v>375</v>
+      </c>
+      <c r="C47" t="s">
+        <v>609</v>
+      </c>
+      <c r="D47" t="s">
+        <v>630</v>
+      </c>
+      <c r="G47" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" t="s">
+        <v>376</v>
+      </c>
+      <c r="C48" t="s">
+        <v>609</v>
+      </c>
+      <c r="D48" t="s">
+        <v>630</v>
+      </c>
+      <c r="G48" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49" t="s">
+        <v>377</v>
+      </c>
+      <c r="C49" t="s">
+        <v>609</v>
+      </c>
+      <c r="D49" t="s">
+        <v>630</v>
+      </c>
+      <c r="G49" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>60</v>
+      </c>
+      <c r="B50" t="s">
+        <v>378</v>
+      </c>
+      <c r="C50" t="s">
+        <v>609</v>
+      </c>
+      <c r="D50" t="s">
+        <v>630</v>
+      </c>
+      <c r="G50" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" t="s">
+        <v>379</v>
+      </c>
+      <c r="C51" t="s">
+        <v>606</v>
+      </c>
+      <c r="D51" t="s">
+        <v>630</v>
+      </c>
+      <c r="G51" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>62</v>
+      </c>
+      <c r="B52" t="s">
+        <v>380</v>
+      </c>
+      <c r="C52" t="s">
+        <v>606</v>
+      </c>
+      <c r="D52" t="s">
+        <v>630</v>
+      </c>
+      <c r="G52" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>63</v>
+      </c>
+      <c r="B53" t="s">
+        <v>381</v>
+      </c>
+      <c r="C53" t="s">
+        <v>606</v>
+      </c>
+      <c r="D53" t="s">
+        <v>630</v>
+      </c>
+      <c r="G53" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>64</v>
+      </c>
+      <c r="B54" t="s">
+        <v>382</v>
+      </c>
+      <c r="C54" t="s">
+        <v>606</v>
+      </c>
+      <c r="D54" t="s">
+        <v>630</v>
+      </c>
+      <c r="G54" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" t="s">
+        <v>383</v>
+      </c>
+      <c r="C55" t="s">
+        <v>614</v>
+      </c>
+      <c r="D55" t="s">
+        <v>630</v>
+      </c>
+      <c r="G55" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56" t="s">
+        <v>384</v>
+      </c>
+      <c r="C56" t="s">
+        <v>614</v>
+      </c>
+      <c r="D56" t="s">
+        <v>630</v>
+      </c>
+      <c r="G56" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>67</v>
+      </c>
+      <c r="B57" t="s">
+        <v>385</v>
+      </c>
+      <c r="C57" t="s">
+        <v>614</v>
+      </c>
+      <c r="D57" t="s">
+        <v>630</v>
+      </c>
+      <c r="G57" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" t="s">
+        <v>386</v>
+      </c>
+      <c r="C58" t="s">
+        <v>615</v>
+      </c>
+      <c r="D58" t="s">
+        <v>630</v>
+      </c>
+      <c r="G58" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59" t="s">
+        <v>387</v>
+      </c>
+      <c r="C59" t="s">
+        <v>615</v>
+      </c>
+      <c r="D59" t="s">
+        <v>630</v>
+      </c>
+      <c r="G59" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>70</v>
+      </c>
+      <c r="B60" t="s">
+        <v>388</v>
+      </c>
+      <c r="C60" t="s">
+        <v>615</v>
+      </c>
+      <c r="D60" t="s">
+        <v>630</v>
+      </c>
+      <c r="G60" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>71</v>
+      </c>
+      <c r="B61" t="s">
+        <v>389</v>
+      </c>
+      <c r="C61" t="s">
+        <v>610</v>
+      </c>
+      <c r="D61" t="s">
+        <v>630</v>
+      </c>
+      <c r="G61" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>72</v>
+      </c>
+      <c r="B62" t="s">
+        <v>390</v>
+      </c>
+      <c r="C62" t="s">
+        <v>610</v>
+      </c>
+      <c r="D62" t="s">
+        <v>630</v>
+      </c>
+      <c r="G62" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>73</v>
+      </c>
+      <c r="B63" t="s">
+        <v>391</v>
+      </c>
+      <c r="C63" t="s">
+        <v>610</v>
+      </c>
+      <c r="D63" t="s">
+        <v>630</v>
+      </c>
+      <c r="G63" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>74</v>
+      </c>
+      <c r="B64" t="s">
+        <v>392</v>
+      </c>
+      <c r="C64" t="s">
+        <v>610</v>
+      </c>
+      <c r="D64" t="s">
+        <v>630</v>
+      </c>
+      <c r="G64" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>75</v>
+      </c>
+      <c r="B65" t="s">
+        <v>393</v>
+      </c>
+      <c r="C65" t="s">
+        <v>610</v>
+      </c>
+      <c r="D65" t="s">
+        <v>630</v>
+      </c>
+      <c r="G65" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" t="s">
+        <v>76</v>
+      </c>
+      <c r="B66" t="s">
+        <v>394</v>
+      </c>
+      <c r="C66" t="s">
+        <v>610</v>
+      </c>
+      <c r="D66" t="s">
+        <v>630</v>
+      </c>
+      <c r="G66" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" t="s">
+        <v>77</v>
+      </c>
+      <c r="B67" t="s">
+        <v>395</v>
+      </c>
+      <c r="C67" t="s">
+        <v>610</v>
+      </c>
+      <c r="D67" t="s">
+        <v>630</v>
+      </c>
+      <c r="G67" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" t="s">
+        <v>78</v>
+      </c>
+      <c r="B68" t="s">
+        <v>396</v>
+      </c>
+      <c r="C68" t="s">
+        <v>610</v>
+      </c>
+      <c r="D68" t="s">
+        <v>630</v>
+      </c>
+      <c r="G68" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" t="s">
+        <v>79</v>
+      </c>
+      <c r="B69" t="s">
+        <v>397</v>
+      </c>
+      <c r="C69" t="s">
+        <v>611</v>
+      </c>
+      <c r="D69" t="s">
+        <v>630</v>
+      </c>
+      <c r="G69" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" t="s">
+        <v>80</v>
+      </c>
+      <c r="B70" t="s">
+        <v>398</v>
+      </c>
+      <c r="C70" t="s">
+        <v>611</v>
+      </c>
+      <c r="D70" t="s">
+        <v>630</v>
+      </c>
+      <c r="G70" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" t="s">
+        <v>81</v>
+      </c>
+      <c r="B71" t="s">
+        <v>399</v>
+      </c>
+      <c r="C71" t="s">
+        <v>611</v>
+      </c>
+      <c r="D71" t="s">
+        <v>630</v>
+      </c>
+      <c r="G71" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
+        <v>82</v>
+      </c>
+      <c r="B72" t="s">
+        <v>400</v>
+      </c>
+      <c r="C72" t="s">
+        <v>611</v>
+      </c>
+      <c r="D72" t="s">
+        <v>630</v>
+      </c>
+      <c r="G72" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
+        <v>83</v>
+      </c>
+      <c r="B73" t="s">
+        <v>401</v>
+      </c>
+      <c r="C73" t="s">
+        <v>611</v>
+      </c>
+      <c r="D73" t="s">
+        <v>630</v>
+      </c>
+      <c r="G73" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" t="s">
+        <v>84</v>
+      </c>
+      <c r="B74" t="s">
+        <v>402</v>
+      </c>
+      <c r="C74" t="s">
+        <v>611</v>
+      </c>
+      <c r="D74" t="s">
+        <v>630</v>
+      </c>
+      <c r="G74" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
+        <v>85</v>
+      </c>
+      <c r="B75" t="s">
+        <v>403</v>
+      </c>
+      <c r="C75" t="s">
+        <v>612</v>
+      </c>
+      <c r="D75" t="s">
+        <v>630</v>
+      </c>
+      <c r="G75" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" t="s">
+        <v>86</v>
+      </c>
+      <c r="B76" t="s">
+        <v>404</v>
+      </c>
+      <c r="C76" t="s">
+        <v>612</v>
+      </c>
+      <c r="D76" t="s">
+        <v>630</v>
+      </c>
+      <c r="G76" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" t="s">
+        <v>87</v>
+      </c>
+      <c r="B77" t="s">
+        <v>405</v>
+      </c>
+      <c r="C77" t="s">
+        <v>612</v>
+      </c>
+      <c r="D77" t="s">
+        <v>630</v>
+      </c>
+      <c r="G77" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" t="s">
+        <v>88</v>
+      </c>
+      <c r="B78" t="s">
+        <v>406</v>
+      </c>
+      <c r="C78" t="s">
+        <v>612</v>
+      </c>
+      <c r="D78" t="s">
+        <v>630</v>
+      </c>
+      <c r="G78" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" t="s">
+        <v>89</v>
+      </c>
+      <c r="B79" t="s">
+        <v>407</v>
+      </c>
+      <c r="C79" t="s">
+        <v>612</v>
+      </c>
+      <c r="D79" t="s">
+        <v>630</v>
+      </c>
+      <c r="G79" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" t="s">
+        <v>90</v>
+      </c>
+      <c r="B80" t="s">
+        <v>408</v>
+      </c>
+      <c r="C80" t="s">
+        <v>612</v>
+      </c>
+      <c r="D80" t="s">
+        <v>630</v>
+      </c>
+      <c r="G80" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" t="s">
+        <v>91</v>
+      </c>
+      <c r="B81" t="s">
+        <v>409</v>
+      </c>
+      <c r="C81" t="s">
+        <v>612</v>
+      </c>
+      <c r="D81" t="s">
+        <v>630</v>
+      </c>
+      <c r="G81" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" t="s">
+        <v>92</v>
+      </c>
+      <c r="B82" t="s">
+        <v>410</v>
+      </c>
+      <c r="C82" t="s">
+        <v>612</v>
+      </c>
+      <c r="D82" t="s">
+        <v>630</v>
+      </c>
+      <c r="G82" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" t="s">
+        <v>93</v>
+      </c>
+      <c r="B83" t="s">
+        <v>411</v>
+      </c>
+      <c r="C83" t="s">
+        <v>612</v>
+      </c>
+      <c r="D83" t="s">
+        <v>630</v>
+      </c>
+      <c r="G83" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" t="s">
+        <v>94</v>
+      </c>
+      <c r="B84" t="s">
+        <v>412</v>
+      </c>
+      <c r="C84" t="s">
+        <v>612</v>
+      </c>
+      <c r="D84" t="s">
+        <v>630</v>
+      </c>
+      <c r="G84" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" t="s">
+        <v>95</v>
+      </c>
+      <c r="B85" t="s">
+        <v>413</v>
+      </c>
+      <c r="C85" t="s">
+        <v>613</v>
+      </c>
+      <c r="D85" t="s">
+        <v>630</v>
+      </c>
+      <c r="G85" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" t="s">
+        <v>96</v>
+      </c>
+      <c r="B86" t="s">
+        <v>414</v>
+      </c>
+      <c r="C86" t="s">
+        <v>613</v>
+      </c>
+      <c r="D86" t="s">
+        <v>630</v>
+      </c>
+      <c r="G86" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" t="s">
+        <v>97</v>
+      </c>
+      <c r="B87" t="s">
+        <v>415</v>
+      </c>
+      <c r="C87" t="s">
+        <v>613</v>
+      </c>
+      <c r="D87" t="s">
+        <v>630</v>
+      </c>
+      <c r="G87" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" t="s">
+        <v>98</v>
+      </c>
+      <c r="B88" t="s">
+        <v>416</v>
+      </c>
+      <c r="C88" t="s">
+        <v>613</v>
+      </c>
+      <c r="D88" t="s">
+        <v>630</v>
+      </c>
+      <c r="G88" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" t="s">
+        <v>99</v>
+      </c>
+      <c r="B89" t="s">
+        <v>417</v>
+      </c>
+      <c r="C89" t="s">
+        <v>613</v>
+      </c>
+      <c r="D89" t="s">
+        <v>630</v>
+      </c>
+      <c r="G89" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" t="s">
+        <v>100</v>
+      </c>
+      <c r="B90" t="s">
+        <v>418</v>
+      </c>
+      <c r="C90" t="s">
+        <v>609</v>
+      </c>
+      <c r="D90" t="s">
+        <v>630</v>
+      </c>
+      <c r="G90" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" t="s">
+        <v>101</v>
+      </c>
+      <c r="B91" t="s">
+        <v>419</v>
+      </c>
+      <c r="C91" t="s">
+        <v>609</v>
+      </c>
+      <c r="D91" t="s">
+        <v>630</v>
+      </c>
+      <c r="G91" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" t="s">
+        <v>102</v>
+      </c>
+      <c r="B92" t="s">
+        <v>420</v>
+      </c>
+      <c r="C92" t="s">
+        <v>609</v>
+      </c>
+      <c r="D92" t="s">
+        <v>630</v>
+      </c>
+      <c r="G92" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" t="s">
+        <v>103</v>
+      </c>
+      <c r="B93" t="s">
+        <v>421</v>
+      </c>
+      <c r="C93" t="s">
+        <v>609</v>
+      </c>
+      <c r="D93" t="s">
+        <v>630</v>
+      </c>
+      <c r="G93" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" t="s">
+        <v>104</v>
+      </c>
+      <c r="B94" t="s">
+        <v>422</v>
+      </c>
+      <c r="C94" t="s">
+        <v>609</v>
+      </c>
+      <c r="D94" t="s">
+        <v>630</v>
+      </c>
+      <c r="G94" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" t="s">
+        <v>105</v>
+      </c>
+      <c r="B95" t="s">
+        <v>423</v>
+      </c>
+      <c r="C95" t="s">
+        <v>609</v>
+      </c>
+      <c r="D95" t="s">
+        <v>630</v>
+      </c>
+      <c r="G95" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" t="s">
+        <v>106</v>
+      </c>
+      <c r="B96" t="s">
+        <v>424</v>
+      </c>
+      <c r="C96" t="s">
+        <v>609</v>
+      </c>
+      <c r="D96" t="s">
+        <v>630</v>
+      </c>
+      <c r="G96" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" t="s">
+        <v>107</v>
+      </c>
+      <c r="B97" t="s">
+        <v>425</v>
+      </c>
+      <c r="C97" t="s">
+        <v>609</v>
+      </c>
+      <c r="D97" t="s">
+        <v>630</v>
+      </c>
+      <c r="G97" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" t="s">
+        <v>108</v>
+      </c>
+      <c r="B98" t="s">
+        <v>426</v>
+      </c>
+      <c r="C98" t="s">
+        <v>609</v>
+      </c>
+      <c r="D98" t="s">
+        <v>630</v>
+      </c>
+      <c r="G98" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" t="s">
+        <v>109</v>
+      </c>
+      <c r="B99" t="s">
+        <v>427</v>
+      </c>
+      <c r="C99" t="s">
+        <v>606</v>
+      </c>
+      <c r="D99" t="s">
+        <v>630</v>
+      </c>
+      <c r="G99" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" t="s">
+        <v>110</v>
+      </c>
+      <c r="B100" t="s">
+        <v>428</v>
+      </c>
+      <c r="C100" t="s">
+        <v>606</v>
+      </c>
+      <c r="D100" t="s">
+        <v>630</v>
+      </c>
+      <c r="G100" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" t="s">
+        <v>111</v>
+      </c>
+      <c r="B101" t="s">
+        <v>429</v>
+      </c>
+      <c r="C101" t="s">
+        <v>606</v>
+      </c>
+      <c r="D101" t="s">
+        <v>630</v>
+      </c>
+      <c r="G101" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" t="s">
+        <v>112</v>
+      </c>
+      <c r="B102" t="s">
+        <v>430</v>
+      </c>
+      <c r="C102" t="s">
+        <v>606</v>
+      </c>
+      <c r="D102" t="s">
+        <v>630</v>
+      </c>
+      <c r="G102" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" t="s">
+        <v>113</v>
+      </c>
+      <c r="B103" t="s">
+        <v>431</v>
+      </c>
+      <c r="C103" t="s">
+        <v>606</v>
+      </c>
+      <c r="D103" t="s">
+        <v>630</v>
+      </c>
+      <c r="G103" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" t="s">
+        <v>114</v>
+      </c>
+      <c r="B104" t="s">
+        <v>432</v>
+      </c>
+      <c r="C104" t="s">
+        <v>606</v>
+      </c>
+      <c r="D104" t="s">
+        <v>630</v>
+      </c>
+      <c r="G104" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" t="s">
+        <v>115</v>
+      </c>
+      <c r="B105" t="s">
+        <v>433</v>
+      </c>
+      <c r="C105" t="s">
+        <v>606</v>
+      </c>
+      <c r="D105" t="s">
+        <v>630</v>
+      </c>
+      <c r="G105" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" t="s">
+        <v>116</v>
+      </c>
+      <c r="B106" t="s">
+        <v>434</v>
+      </c>
+      <c r="C106" t="s">
+        <v>606</v>
+      </c>
+      <c r="D106" t="s">
+        <v>630</v>
+      </c>
+      <c r="G106" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" t="s">
+        <v>117</v>
+      </c>
+      <c r="B107" t="s">
+        <v>435</v>
+      </c>
+      <c r="C107" t="s">
+        <v>614</v>
+      </c>
+      <c r="D107" t="s">
+        <v>630</v>
+      </c>
+      <c r="G107" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" t="s">
+        <v>118</v>
+      </c>
+      <c r="B108" t="s">
+        <v>436</v>
+      </c>
+      <c r="C108" t="s">
+        <v>614</v>
+      </c>
+      <c r="D108" t="s">
+        <v>630</v>
+      </c>
+      <c r="G108" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" t="s">
+        <v>119</v>
+      </c>
+      <c r="B109" t="s">
+        <v>437</v>
+      </c>
+      <c r="C109" t="s">
+        <v>615</v>
+      </c>
+      <c r="D109" t="s">
+        <v>630</v>
+      </c>
+      <c r="G109" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" t="s">
+        <v>120</v>
+      </c>
+      <c r="B110" t="s">
+        <v>438</v>
+      </c>
+      <c r="C110" t="s">
+        <v>615</v>
+      </c>
+      <c r="D110" t="s">
+        <v>630</v>
+      </c>
+      <c r="G110" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" t="s">
+        <v>121</v>
+      </c>
+      <c r="B111" t="s">
+        <v>439</v>
+      </c>
+      <c r="C111" t="s">
+        <v>615</v>
+      </c>
+      <c r="D111" t="s">
+        <v>630</v>
+      </c>
+      <c r="G111" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" t="s">
+        <v>122</v>
+      </c>
+      <c r="B112" t="s">
+        <v>440</v>
+      </c>
+      <c r="C112" t="s">
+        <v>615</v>
+      </c>
+      <c r="D112" t="s">
+        <v>630</v>
+      </c>
+      <c r="G112" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" t="s">
+        <v>123</v>
+      </c>
+      <c r="B113" t="s">
+        <v>441</v>
+      </c>
+      <c r="C113" t="s">
+        <v>615</v>
+      </c>
+      <c r="D113" t="s">
+        <v>630</v>
+      </c>
+      <c r="G113" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" t="s">
+        <v>124</v>
+      </c>
+      <c r="B114" t="s">
+        <v>442</v>
+      </c>
+      <c r="C114" t="s">
+        <v>616</v>
+      </c>
+      <c r="D114" t="s">
+        <v>630</v>
+      </c>
+      <c r="G114" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" t="s">
+        <v>125</v>
+      </c>
+      <c r="B115" t="s">
+        <v>443</v>
+      </c>
+      <c r="C115" t="s">
+        <v>616</v>
+      </c>
+      <c r="D115" t="s">
+        <v>630</v>
+      </c>
+      <c r="G115" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" t="s">
+        <v>126</v>
+      </c>
+      <c r="B116" t="s">
+        <v>444</v>
+      </c>
+      <c r="C116" t="s">
+        <v>616</v>
+      </c>
+      <c r="D116" t="s">
+        <v>630</v>
+      </c>
+      <c r="G116" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" t="s">
+        <v>127</v>
+      </c>
+      <c r="B117" t="s">
+        <v>445</v>
+      </c>
+      <c r="C117" t="s">
+        <v>616</v>
+      </c>
+      <c r="D117" t="s">
+        <v>630</v>
+      </c>
+      <c r="G117" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" t="s">
+        <v>128</v>
+      </c>
+      <c r="B118" t="s">
+        <v>446</v>
+      </c>
+      <c r="C118" t="s">
+        <v>616</v>
+      </c>
+      <c r="D118" t="s">
+        <v>630</v>
+      </c>
+      <c r="G118" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" t="s">
+        <v>129</v>
+      </c>
+      <c r="B119" t="s">
+        <v>372</v>
+      </c>
+      <c r="C119" t="s">
+        <v>616</v>
+      </c>
+      <c r="D119" t="s">
+        <v>630</v>
+      </c>
+      <c r="E119" t="s">
+        <v>664</v>
+      </c>
+      <c r="F119" t="s">
+        <v>718</v>
+      </c>
+      <c r="G119" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" t="s">
+        <v>130</v>
+      </c>
+      <c r="B120" t="s">
+        <v>447</v>
+      </c>
+      <c r="C120" t="s">
+        <v>616</v>
+      </c>
+      <c r="D120" t="s">
+        <v>632</v>
+      </c>
+      <c r="E120" t="s">
+        <v>665</v>
+      </c>
+      <c r="G120" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" t="s">
+        <v>131</v>
+      </c>
+      <c r="B121" t="s">
+        <v>448</v>
+      </c>
+      <c r="C121" t="s">
+        <v>616</v>
+      </c>
+      <c r="D121" t="s">
+        <v>630</v>
+      </c>
+      <c r="G121" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" t="s">
+        <v>132</v>
+      </c>
+      <c r="B122" t="s">
+        <v>449</v>
+      </c>
+      <c r="C122" t="s">
+        <v>614</v>
+      </c>
+      <c r="D122" t="s">
+        <v>633</v>
+      </c>
+      <c r="G122" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" t="s">
+        <v>133</v>
+      </c>
+      <c r="B123" t="s">
+        <v>450</v>
+      </c>
+      <c r="C123" t="s">
+        <v>614</v>
+      </c>
+      <c r="D123" t="s">
+        <v>634</v>
+      </c>
+      <c r="E123" t="s">
+        <v>666</v>
+      </c>
+      <c r="F123" t="s">
+        <v>719</v>
+      </c>
+      <c r="G123" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" t="s">
+        <v>134</v>
+      </c>
+      <c r="B124" t="s">
+        <v>451</v>
+      </c>
+      <c r="C124" t="s">
+        <v>614</v>
+      </c>
+      <c r="D124" t="s">
+        <v>630</v>
+      </c>
+      <c r="G124" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" t="s">
+        <v>135</v>
+      </c>
+      <c r="B125" t="s">
+        <v>452</v>
+      </c>
+      <c r="C125" t="s">
+        <v>614</v>
+      </c>
+      <c r="D125" t="s">
+        <v>630</v>
+      </c>
+      <c r="G125" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" t="s">
+        <v>136</v>
+      </c>
+      <c r="B126" t="s">
+        <v>453</v>
+      </c>
+      <c r="C126" t="s">
+        <v>614</v>
+      </c>
+      <c r="D126" t="s">
+        <v>630</v>
+      </c>
+      <c r="G126" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" t="s">
+        <v>137</v>
+      </c>
+      <c r="B127" t="s">
+        <v>454</v>
+      </c>
+      <c r="C127" t="s">
+        <v>614</v>
+      </c>
+      <c r="D127" t="s">
+        <v>630</v>
+      </c>
+      <c r="G127" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" t="s">
+        <v>138</v>
+      </c>
+      <c r="B128" t="s">
+        <v>455</v>
+      </c>
+      <c r="C128" t="s">
+        <v>614</v>
+      </c>
+      <c r="D128" t="s">
+        <v>635</v>
+      </c>
+      <c r="E128" t="s">
+        <v>667</v>
+      </c>
+      <c r="G128" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" t="s">
+        <v>139</v>
+      </c>
+      <c r="B129" t="s">
+        <v>456</v>
+      </c>
+      <c r="C129" t="s">
+        <v>615</v>
+      </c>
+      <c r="D129" t="s">
+        <v>630</v>
+      </c>
+      <c r="E129" t="s">
+        <v>668</v>
+      </c>
+      <c r="F129" t="s">
+        <v>720</v>
+      </c>
+      <c r="G129" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" t="s">
+        <v>140</v>
+      </c>
+      <c r="B130" t="s">
+        <v>457</v>
+      </c>
+      <c r="C130" t="s">
+        <v>615</v>
+      </c>
+      <c r="D130" t="s">
+        <v>630</v>
+      </c>
+      <c r="G130" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" t="s">
+        <v>141</v>
+      </c>
+      <c r="C131" t="s">
+        <v>615</v>
+      </c>
+      <c r="D131" t="s">
+        <v>636</v>
+      </c>
+      <c r="E131" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" t="s">
+        <v>142</v>
+      </c>
+      <c r="B132" t="s">
+        <v>458</v>
+      </c>
+      <c r="C132" t="s">
+        <v>615</v>
+      </c>
+      <c r="D132" t="s">
+        <v>637</v>
+      </c>
+      <c r="E132" t="s">
+        <v>670</v>
+      </c>
+      <c r="G132" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" t="s">
+        <v>143</v>
+      </c>
+      <c r="B133" t="s">
+        <v>459</v>
+      </c>
+      <c r="C133" t="s">
+        <v>615</v>
+      </c>
+      <c r="D133" t="s">
+        <v>638</v>
+      </c>
+      <c r="E133" t="s">
+        <v>671</v>
+      </c>
+      <c r="G133" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" t="s">
+        <v>144</v>
+      </c>
+      <c r="C134" t="s">
+        <v>615</v>
+      </c>
+      <c r="D134" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" t="s">
+        <v>145</v>
+      </c>
+      <c r="C135" t="s">
+        <v>615</v>
+      </c>
+      <c r="D135" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" t="s">
+        <v>146</v>
+      </c>
+      <c r="B136" t="s">
+        <v>460</v>
+      </c>
+      <c r="C136" t="s">
+        <v>609</v>
+      </c>
+      <c r="D136" t="s">
+        <v>630</v>
+      </c>
+      <c r="G136" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" t="s">
+        <v>147</v>
+      </c>
+      <c r="B137" t="s">
+        <v>461</v>
+      </c>
+      <c r="C137" t="s">
+        <v>609</v>
+      </c>
+      <c r="D137" t="s">
+        <v>636</v>
+      </c>
+      <c r="G137" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138" t="s">
+        <v>148</v>
+      </c>
+      <c r="C138" t="s">
+        <v>609</v>
+      </c>
+      <c r="D138" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" t="s">
+        <v>149</v>
+      </c>
+      <c r="C139" t="s">
+        <v>609</v>
+      </c>
+      <c r="D139" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" t="s">
+        <v>150</v>
+      </c>
+      <c r="C140" t="s">
+        <v>609</v>
+      </c>
+      <c r="D140" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141" t="s">
+        <v>151</v>
+      </c>
+      <c r="B141" t="s">
+        <v>377</v>
+      </c>
+      <c r="C141" t="s">
+        <v>609</v>
+      </c>
+      <c r="D141" t="s">
+        <v>630</v>
+      </c>
+      <c r="G141" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" t="s">
+        <v>152</v>
+      </c>
+      <c r="B142" t="s">
+        <v>462</v>
+      </c>
+      <c r="C142" t="s">
+        <v>609</v>
+      </c>
+      <c r="D142" t="s">
+        <v>630</v>
+      </c>
+      <c r="E142" t="s">
+        <v>672</v>
+      </c>
+      <c r="F142" t="s">
+        <v>721</v>
+      </c>
+      <c r="G142" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143" t="s">
+        <v>153</v>
+      </c>
+      <c r="B143" t="s">
+        <v>463</v>
+      </c>
+      <c r="C143" t="s">
+        <v>606</v>
+      </c>
+      <c r="D143" t="s">
+        <v>640</v>
+      </c>
+      <c r="G143" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" t="s">
+        <v>154</v>
+      </c>
+      <c r="C144" t="s">
+        <v>606</v>
+      </c>
+      <c r="D144" t="s">
+        <v>642</v>
+      </c>
+      <c r="E144" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145" t="s">
+        <v>155</v>
+      </c>
+      <c r="C145" t="s">
+        <v>606</v>
+      </c>
+      <c r="D145" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" t="s">
+        <v>156</v>
+      </c>
+      <c r="B146" t="s">
+        <v>464</v>
+      </c>
+      <c r="C146" t="s">
+        <v>606</v>
+      </c>
+      <c r="D146" t="s">
+        <v>630</v>
+      </c>
+      <c r="F146" t="s">
+        <v>722</v>
+      </c>
+      <c r="G146" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" t="s">
+        <v>157</v>
+      </c>
+      <c r="B147" t="s">
+        <v>465</v>
+      </c>
+      <c r="C147" t="s">
+        <v>612</v>
+      </c>
+      <c r="D147" t="s">
+        <v>630</v>
+      </c>
+      <c r="E147" t="s">
+        <v>674</v>
+      </c>
+      <c r="F147" t="s">
+        <v>723</v>
+      </c>
+      <c r="G147" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148" t="s">
+        <v>158</v>
+      </c>
+      <c r="B148" t="s">
+        <v>466</v>
+      </c>
+      <c r="C148" t="s">
+        <v>612</v>
+      </c>
+      <c r="D148" t="s">
+        <v>630</v>
+      </c>
+      <c r="E148" t="s">
+        <v>675</v>
+      </c>
+      <c r="G148" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" t="s">
+        <v>159</v>
+      </c>
+      <c r="B149" t="s">
+        <v>467</v>
+      </c>
+      <c r="C149" t="s">
+        <v>612</v>
+      </c>
+      <c r="D149" t="s">
+        <v>630</v>
+      </c>
+      <c r="E149" t="s">
+        <v>676</v>
+      </c>
+      <c r="G149" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150" t="s">
+        <v>160</v>
+      </c>
+      <c r="B150" t="s">
+        <v>468</v>
+      </c>
+      <c r="C150" t="s">
+        <v>612</v>
+      </c>
+      <c r="D150" t="s">
+        <v>630</v>
+      </c>
+      <c r="E150" t="s">
+        <v>677</v>
+      </c>
+      <c r="G150" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" t="s">
+        <v>161</v>
+      </c>
+      <c r="B151" t="s">
+        <v>469</v>
+      </c>
+      <c r="C151" t="s">
+        <v>612</v>
+      </c>
+      <c r="D151" t="s">
+        <v>630</v>
+      </c>
+      <c r="E151" t="s">
+        <v>678</v>
+      </c>
+      <c r="G151" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" t="s">
+        <v>162</v>
+      </c>
+      <c r="B152" t="s">
+        <v>470</v>
+      </c>
+      <c r="C152" t="s">
+        <v>612</v>
+      </c>
+      <c r="D152" t="s">
+        <v>630</v>
+      </c>
+      <c r="E152" t="s">
+        <v>679</v>
+      </c>
+      <c r="G152" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" t="s">
+        <v>163</v>
+      </c>
+      <c r="C153" t="s">
+        <v>612</v>
+      </c>
+      <c r="D153" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" t="s">
+        <v>164</v>
+      </c>
+      <c r="B154" t="s">
+        <v>471</v>
+      </c>
+      <c r="C154" t="s">
+        <v>612</v>
+      </c>
+      <c r="D154" t="s">
+        <v>630</v>
+      </c>
+      <c r="E154" t="s">
+        <v>680</v>
+      </c>
+      <c r="G154" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155" t="s">
+        <v>165</v>
+      </c>
+      <c r="B155" t="s">
+        <v>472</v>
+      </c>
+      <c r="C155" t="s">
+        <v>612</v>
+      </c>
+      <c r="D155" t="s">
+        <v>630</v>
+      </c>
+      <c r="G155" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156" t="s">
+        <v>166</v>
+      </c>
+      <c r="B156" t="s">
+        <v>473</v>
+      </c>
+      <c r="C156" t="s">
+        <v>612</v>
+      </c>
+      <c r="D156" t="s">
+        <v>630</v>
+      </c>
+      <c r="G156" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" t="s">
+        <v>167</v>
+      </c>
+      <c r="B157" t="s">
+        <v>474</v>
+      </c>
+      <c r="C157" t="s">
+        <v>612</v>
+      </c>
+      <c r="D157" t="s">
+        <v>643</v>
+      </c>
+      <c r="E157" t="s">
+        <v>681</v>
+      </c>
+      <c r="F157" t="s">
+        <v>724</v>
+      </c>
+      <c r="G157" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158" t="s">
+        <v>168</v>
+      </c>
+      <c r="B158" t="s">
+        <v>475</v>
+      </c>
+      <c r="C158" t="s">
+        <v>612</v>
+      </c>
+      <c r="D158" t="s">
+        <v>630</v>
+      </c>
+      <c r="E158" t="s">
+        <v>682</v>
+      </c>
+      <c r="G158" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159" t="s">
+        <v>169</v>
+      </c>
+      <c r="B159" t="s">
+        <v>476</v>
+      </c>
+      <c r="C159" t="s">
+        <v>612</v>
+      </c>
+      <c r="D159" t="s">
+        <v>630</v>
+      </c>
+      <c r="E159" t="s">
+        <v>683</v>
+      </c>
+      <c r="G159" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7">
+      <c r="A160" t="s">
+        <v>170</v>
+      </c>
+      <c r="B160" t="s">
+        <v>477</v>
+      </c>
+      <c r="C160" t="s">
+        <v>612</v>
+      </c>
+      <c r="D160" t="s">
+        <v>630</v>
+      </c>
+      <c r="E160" t="s">
+        <v>684</v>
+      </c>
+      <c r="G160" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" t="s">
+        <v>171</v>
+      </c>
+      <c r="B161" t="s">
+        <v>478</v>
+      </c>
+      <c r="C161" t="s">
+        <v>612</v>
+      </c>
+      <c r="D161" t="s">
+        <v>644</v>
+      </c>
+      <c r="E161" t="s">
+        <v>685</v>
+      </c>
+      <c r="G161" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="A162" t="s">
+        <v>172</v>
+      </c>
+      <c r="B162" t="s">
+        <v>479</v>
+      </c>
+      <c r="C162" t="s">
+        <v>612</v>
+      </c>
+      <c r="D162" t="s">
+        <v>630</v>
+      </c>
+      <c r="G162" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" t="s">
+        <v>173</v>
+      </c>
+      <c r="B163" t="s">
+        <v>480</v>
+      </c>
+      <c r="C163" t="s">
+        <v>612</v>
+      </c>
+      <c r="D163" t="s">
+        <v>630</v>
+      </c>
+      <c r="E163" t="s">
+        <v>686</v>
+      </c>
+      <c r="G163" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164" t="s">
+        <v>174</v>
+      </c>
+      <c r="B164" t="s">
+        <v>481</v>
+      </c>
+      <c r="C164" t="s">
+        <v>612</v>
+      </c>
+      <c r="D164" t="s">
+        <v>645</v>
+      </c>
+      <c r="E164" t="s">
+        <v>687</v>
+      </c>
+      <c r="G164" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" t="s">
+        <v>175</v>
+      </c>
+      <c r="C165" t="s">
+        <v>612</v>
+      </c>
+      <c r="D165" t="s">
+        <v>636</v>
+      </c>
+      <c r="E165" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166" t="s">
+        <v>176</v>
+      </c>
+      <c r="B166" t="s">
+        <v>482</v>
+      </c>
+      <c r="C166" t="s">
+        <v>612</v>
+      </c>
+      <c r="D166" t="s">
+        <v>646</v>
+      </c>
+      <c r="E166" t="s">
+        <v>689</v>
+      </c>
+      <c r="G166" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" t="s">
+        <v>177</v>
+      </c>
+      <c r="B167" t="s">
+        <v>483</v>
+      </c>
+      <c r="C167" t="s">
+        <v>612</v>
+      </c>
+      <c r="D167" t="s">
+        <v>647</v>
+      </c>
+      <c r="E167" t="s">
+        <v>690</v>
+      </c>
+      <c r="G167" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" t="s">
+        <v>178</v>
+      </c>
+      <c r="B168" t="s">
+        <v>484</v>
+      </c>
+      <c r="C168" t="s">
+        <v>605</v>
+      </c>
+      <c r="D168" t="s">
+        <v>630</v>
+      </c>
+      <c r="E168" t="s">
+        <v>691</v>
+      </c>
+      <c r="G168" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169" t="s">
+        <v>179</v>
+      </c>
+      <c r="B169" t="s">
+        <v>485</v>
+      </c>
+      <c r="C169" t="s">
+        <v>605</v>
+      </c>
+      <c r="D169" t="s">
+        <v>648</v>
+      </c>
+      <c r="E169" t="s">
+        <v>692</v>
+      </c>
+      <c r="G169" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" t="s">
+        <v>180</v>
+      </c>
+      <c r="C170" t="s">
+        <v>605</v>
+      </c>
+      <c r="D170" t="s">
+        <v>649</v>
+      </c>
+      <c r="E170" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" t="s">
+        <v>181</v>
+      </c>
+      <c r="C171" t="s">
+        <v>605</v>
+      </c>
+      <c r="D171" t="s">
+        <v>630</v>
+      </c>
+      <c r="E171" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" t="s">
+        <v>182</v>
+      </c>
+      <c r="C172" t="s">
+        <v>605</v>
+      </c>
+      <c r="D172" t="s">
+        <v>636</v>
+      </c>
+      <c r="E172" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173" t="s">
+        <v>183</v>
+      </c>
+      <c r="B173" t="s">
+        <v>486</v>
+      </c>
+      <c r="C173" t="s">
+        <v>617</v>
+      </c>
+      <c r="D173" t="s">
+        <v>630</v>
+      </c>
+      <c r="G173" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7">
+      <c r="A174" t="s">
+        <v>184</v>
+      </c>
+      <c r="B174" t="s">
+        <v>487</v>
+      </c>
+      <c r="C174" t="s">
+        <v>617</v>
+      </c>
+      <c r="D174" t="s">
+        <v>630</v>
+      </c>
+      <c r="F174" t="s">
+        <v>725</v>
+      </c>
+      <c r="G174" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175" t="s">
+        <v>185</v>
+      </c>
+      <c r="B175" t="s">
+        <v>488</v>
+      </c>
+      <c r="C175" t="s">
+        <v>617</v>
+      </c>
+      <c r="D175" t="s">
+        <v>630</v>
+      </c>
+      <c r="F175" t="s">
+        <v>726</v>
+      </c>
+      <c r="G175" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176" t="s">
+        <v>186</v>
+      </c>
+      <c r="C176" t="s">
+        <v>618</v>
+      </c>
+      <c r="D176" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7">
+      <c r="A177" t="s">
+        <v>187</v>
+      </c>
+      <c r="C177" t="s">
+        <v>618</v>
+      </c>
+      <c r="D177" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7">
+      <c r="A178" t="s">
+        <v>188</v>
+      </c>
+      <c r="C178" t="s">
+        <v>618</v>
+      </c>
+      <c r="D178" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7">
+      <c r="A179" t="s">
+        <v>189</v>
+      </c>
+      <c r="B179" t="s">
+        <v>489</v>
+      </c>
+      <c r="C179" t="s">
+        <v>619</v>
+      </c>
+      <c r="D179" t="s">
+        <v>650</v>
+      </c>
+      <c r="E179" t="s">
+        <v>696</v>
+      </c>
+      <c r="F179" t="s">
+        <v>727</v>
+      </c>
+      <c r="G179" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7">
+      <c r="A180" t="s">
+        <v>190</v>
+      </c>
+      <c r="C180" t="s">
+        <v>619</v>
+      </c>
+      <c r="D180" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7">
+      <c r="A181" t="s">
+        <v>191</v>
+      </c>
+      <c r="C181" t="s">
+        <v>619</v>
+      </c>
+      <c r="D181" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7">
+      <c r="A182" t="s">
+        <v>192</v>
+      </c>
+      <c r="B182" t="s">
+        <v>490</v>
+      </c>
+      <c r="C182" t="s">
+        <v>620</v>
+      </c>
+      <c r="D182" t="s">
+        <v>630</v>
+      </c>
+      <c r="E182" t="s">
+        <v>697</v>
+      </c>
+      <c r="G182" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183" t="s">
+        <v>193</v>
+      </c>
+      <c r="B183" t="s">
+        <v>491</v>
+      </c>
+      <c r="C183" t="s">
+        <v>620</v>
+      </c>
+      <c r="D183" t="s">
+        <v>630</v>
+      </c>
+      <c r="F183" t="s">
+        <v>728</v>
+      </c>
+      <c r="G183" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184" t="s">
+        <v>194</v>
+      </c>
+      <c r="C184" t="s">
+        <v>620</v>
+      </c>
+      <c r="D184" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" t="s">
+        <v>195</v>
+      </c>
+      <c r="C185" t="s">
+        <v>620</v>
+      </c>
+      <c r="D185" t="s">
+        <v>652</v>
+      </c>
+      <c r="F185" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="A186" t="s">
+        <v>196</v>
+      </c>
+      <c r="C186" t="s">
+        <v>621</v>
+      </c>
+      <c r="D186" t="s">
+        <v>653</v>
+      </c>
+      <c r="E186" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187" t="s">
+        <v>197</v>
+      </c>
+      <c r="C187" t="s">
+        <v>621</v>
+      </c>
+      <c r="D187" t="s">
+        <v>630</v>
+      </c>
+      <c r="E187" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188" t="s">
+        <v>198</v>
+      </c>
+      <c r="C188" t="s">
+        <v>621</v>
+      </c>
+      <c r="D188" t="s">
+        <v>630</v>
+      </c>
+      <c r="E188" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7">
+      <c r="A189" t="s">
+        <v>199</v>
+      </c>
+      <c r="C189" t="s">
+        <v>621</v>
+      </c>
+      <c r="D189" t="s">
+        <v>630</v>
+      </c>
+      <c r="E189" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7">
+      <c r="A190" t="s">
+        <v>200</v>
+      </c>
+      <c r="C190" t="s">
+        <v>621</v>
+      </c>
+      <c r="D190" t="s">
+        <v>630</v>
+      </c>
+      <c r="E190" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7">
+      <c r="A191" t="s">
+        <v>201</v>
+      </c>
+      <c r="C191" t="s">
+        <v>621</v>
+      </c>
+      <c r="D191" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7">
+      <c r="A192" t="s">
+        <v>202</v>
+      </c>
+      <c r="C192" t="s">
+        <v>621</v>
+      </c>
+      <c r="D192" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7">
+      <c r="A193" t="s">
+        <v>203</v>
+      </c>
+      <c r="C193" t="s">
+        <v>621</v>
+      </c>
+      <c r="D193" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194" t="s">
+        <v>204</v>
+      </c>
+      <c r="B194" t="s">
+        <v>492</v>
+      </c>
+      <c r="C194" t="s">
+        <v>621</v>
+      </c>
+      <c r="D194" t="s">
+        <v>633</v>
+      </c>
+      <c r="G194" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195" t="s">
+        <v>205</v>
+      </c>
+      <c r="B195" t="s">
+        <v>493</v>
+      </c>
+      <c r="C195" t="s">
+        <v>621</v>
+      </c>
+      <c r="D195" t="s">
+        <v>633</v>
+      </c>
+      <c r="G195" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196" t="s">
+        <v>206</v>
+      </c>
+      <c r="B196" t="s">
+        <v>494</v>
+      </c>
+      <c r="C196" t="s">
+        <v>608</v>
+      </c>
+      <c r="D196" t="s">
+        <v>630</v>
+      </c>
+      <c r="F196" t="s">
+        <v>730</v>
+      </c>
+      <c r="G196" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7">
+      <c r="A197" t="s">
+        <v>207</v>
+      </c>
+      <c r="B197" t="s">
+        <v>495</v>
+      </c>
+      <c r="C197" t="s">
+        <v>608</v>
+      </c>
+      <c r="D197" t="s">
+        <v>630</v>
+      </c>
+      <c r="E197" t="s">
+        <v>703</v>
+      </c>
+      <c r="F197" t="s">
+        <v>731</v>
+      </c>
+      <c r="G197" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7">
+      <c r="A198" t="s">
+        <v>208</v>
+      </c>
+      <c r="B198" t="s">
+        <v>496</v>
+      </c>
+      <c r="C198" t="s">
+        <v>608</v>
+      </c>
+      <c r="D198" t="s">
+        <v>630</v>
+      </c>
+      <c r="E198" t="s">
+        <v>704</v>
+      </c>
+      <c r="F198" t="s">
+        <v>732</v>
+      </c>
+      <c r="G198" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7">
+      <c r="A199" t="s">
+        <v>209</v>
+      </c>
+      <c r="B199" t="s">
+        <v>497</v>
+      </c>
+      <c r="C199" t="s">
+        <v>608</v>
+      </c>
+      <c r="D199" t="s">
+        <v>630</v>
+      </c>
+      <c r="E199" t="s">
+        <v>705</v>
+      </c>
+      <c r="F199" t="s">
+        <v>733</v>
+      </c>
+      <c r="G199" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7">
+      <c r="A200" t="s">
+        <v>210</v>
+      </c>
+      <c r="B200" t="s">
+        <v>498</v>
+      </c>
+      <c r="C200" t="s">
+        <v>622</v>
+      </c>
+      <c r="D200" t="s">
+        <v>630</v>
+      </c>
+      <c r="G200" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7">
+      <c r="A201" t="s">
+        <v>211</v>
+      </c>
+      <c r="C201" t="s">
+        <v>622</v>
+      </c>
+      <c r="D201" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7">
+      <c r="A202" t="s">
+        <v>212</v>
+      </c>
+      <c r="C202" t="s">
+        <v>622</v>
+      </c>
+      <c r="D202" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7">
+      <c r="A203" t="s">
+        <v>213</v>
+      </c>
+      <c r="C203" t="s">
+        <v>622</v>
+      </c>
+      <c r="D203" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7">
+      <c r="A204" t="s">
+        <v>214</v>
+      </c>
+      <c r="B204" t="s">
+        <v>377</v>
+      </c>
+      <c r="C204" t="s">
+        <v>623</v>
+      </c>
+      <c r="D204" t="s">
+        <v>630</v>
+      </c>
+      <c r="G204" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7">
+      <c r="A205" t="s">
+        <v>215</v>
+      </c>
+      <c r="C205" t="s">
+        <v>623</v>
+      </c>
+      <c r="D205" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7">
+      <c r="A206" t="s">
+        <v>216</v>
+      </c>
+      <c r="C206" t="s">
+        <v>623</v>
+      </c>
+      <c r="D206" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7">
+      <c r="A207" t="s">
+        <v>217</v>
+      </c>
+      <c r="B207" t="s">
+        <v>499</v>
+      </c>
+      <c r="C207" t="s">
+        <v>623</v>
+      </c>
+      <c r="D207" t="s">
+        <v>630</v>
+      </c>
+      <c r="E207" t="s">
+        <v>706</v>
+      </c>
+      <c r="G207" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7">
+      <c r="A208" t="s">
+        <v>218</v>
+      </c>
+      <c r="C208" t="s">
+        <v>623</v>
+      </c>
+      <c r="D208" t="s">
+        <v>630</v>
+      </c>
+      <c r="E208" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7">
+      <c r="A209" t="s">
+        <v>219</v>
+      </c>
+      <c r="C209" t="s">
+        <v>623</v>
+      </c>
+      <c r="D209" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7">
+      <c r="A210" t="s">
+        <v>220</v>
+      </c>
+      <c r="B210" t="s">
+        <v>500</v>
+      </c>
+      <c r="C210" t="s">
+        <v>624</v>
+      </c>
+      <c r="D210" t="s">
+        <v>630</v>
+      </c>
+      <c r="E210" t="s">
+        <v>708</v>
+      </c>
+      <c r="G210" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7">
+      <c r="A211" t="s">
+        <v>221</v>
+      </c>
+      <c r="B211" t="s">
+        <v>501</v>
+      </c>
+      <c r="C211" t="s">
+        <v>624</v>
+      </c>
+      <c r="D211" t="s">
+        <v>630</v>
+      </c>
+      <c r="G211" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7">
+      <c r="A212" t="s">
+        <v>222</v>
+      </c>
+      <c r="C212" t="s">
+        <v>624</v>
+      </c>
+      <c r="D212" t="s">
+        <v>630</v>
+      </c>
+      <c r="E212" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7">
+      <c r="A213" t="s">
+        <v>223</v>
+      </c>
+      <c r="C213" t="s">
+        <v>624</v>
+      </c>
+      <c r="D213" t="s">
+        <v>643</v>
+      </c>
+      <c r="E213" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7">
+      <c r="A214" t="s">
+        <v>224</v>
+      </c>
+      <c r="B214" t="s">
+        <v>502</v>
+      </c>
+      <c r="C214" t="s">
+        <v>607</v>
+      </c>
+      <c r="D214" t="s">
+        <v>630</v>
+      </c>
+      <c r="G214" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7">
+      <c r="A215" t="s">
+        <v>225</v>
+      </c>
+      <c r="B215" t="s">
+        <v>503</v>
+      </c>
+      <c r="C215" t="s">
+        <v>607</v>
+      </c>
+      <c r="D215" t="s">
+        <v>630</v>
+      </c>
+      <c r="G215" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7">
+      <c r="A216" t="s">
+        <v>226</v>
+      </c>
+      <c r="C216" t="s">
+        <v>607</v>
+      </c>
+      <c r="D216" t="s">
+        <v>630</v>
+      </c>
+      <c r="E216" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7">
+      <c r="A217" t="s">
+        <v>227</v>
+      </c>
+      <c r="B217" t="s">
+        <v>504</v>
+      </c>
+      <c r="C217" t="s">
+        <v>625</v>
+      </c>
+      <c r="D217" t="s">
+        <v>630</v>
+      </c>
+      <c r="E217" t="s">
+        <v>712</v>
+      </c>
+      <c r="G217" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7">
+      <c r="A218" t="s">
+        <v>228</v>
+      </c>
+      <c r="B218" t="s">
+        <v>505</v>
+      </c>
+      <c r="C218" t="s">
+        <v>625</v>
+      </c>
+      <c r="D218" t="s">
+        <v>630</v>
+      </c>
+      <c r="E218" t="s">
+        <v>712</v>
+      </c>
+      <c r="G218" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7">
+      <c r="A219" t="s">
+        <v>229</v>
+      </c>
+      <c r="B219" t="s">
+        <v>344</v>
+      </c>
+      <c r="C219" t="s">
+        <v>626</v>
+      </c>
+      <c r="D219" t="s">
+        <v>630</v>
+      </c>
+      <c r="E219" t="s">
+        <v>713</v>
+      </c>
+      <c r="G219" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7">
+      <c r="A220" t="s">
+        <v>230</v>
+      </c>
+      <c r="C220" t="s">
+        <v>626</v>
+      </c>
+      <c r="D220" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7">
+      <c r="A221" t="s">
+        <v>231</v>
+      </c>
+      <c r="B221" t="s">
+        <v>506</v>
+      </c>
+      <c r="C221" t="s">
+        <v>626</v>
+      </c>
+      <c r="D221" t="s">
+        <v>630</v>
+      </c>
+      <c r="G221" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7">
+      <c r="A222" t="s">
+        <v>232</v>
+      </c>
+      <c r="B222" t="s">
+        <v>507</v>
+      </c>
+      <c r="C222" t="s">
+        <v>627</v>
+      </c>
+      <c r="D222" t="s">
+        <v>630</v>
+      </c>
+      <c r="E222" t="s">
+        <v>714</v>
+      </c>
+      <c r="G222" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7">
+      <c r="A223" t="s">
+        <v>233</v>
+      </c>
+      <c r="B223" t="s">
+        <v>508</v>
+      </c>
+      <c r="C223" t="s">
+        <v>627</v>
+      </c>
+      <c r="D223" t="s">
+        <v>630</v>
+      </c>
+      <c r="G223" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7">
+      <c r="A224" t="s">
+        <v>234</v>
+      </c>
+      <c r="B224" t="s">
+        <v>509</v>
+      </c>
+      <c r="C224" t="s">
+        <v>627</v>
+      </c>
+      <c r="D224" t="s">
+        <v>652</v>
+      </c>
+      <c r="G224" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7">
+      <c r="A225" t="s">
+        <v>235</v>
+      </c>
+      <c r="B225" t="s">
+        <v>510</v>
+      </c>
+      <c r="C225" t="s">
+        <v>627</v>
+      </c>
+      <c r="D225" t="s">
+        <v>630</v>
+      </c>
+      <c r="F225" t="s">
+        <v>734</v>
+      </c>
+      <c r="G225" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7">
+      <c r="A226" t="s">
+        <v>236</v>
+      </c>
+      <c r="B226" t="s">
+        <v>511</v>
+      </c>
+      <c r="C226" t="s">
+        <v>627</v>
+      </c>
+      <c r="D226" t="s">
+        <v>630</v>
+      </c>
+      <c r="G226" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7">
+      <c r="A227" t="s">
+        <v>237</v>
+      </c>
+      <c r="C227" t="s">
+        <v>627</v>
+      </c>
+      <c r="D227" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228" t="s">
+        <v>238</v>
+      </c>
+      <c r="B228" t="s">
+        <v>512</v>
+      </c>
+      <c r="C228" t="s">
+        <v>612</v>
+      </c>
+      <c r="D228" t="s">
+        <v>630</v>
+      </c>
+      <c r="G228" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229" t="s">
+        <v>239</v>
+      </c>
+      <c r="B229" t="s">
+        <v>513</v>
+      </c>
+      <c r="C229" t="s">
+        <v>612</v>
+      </c>
+      <c r="D229" t="s">
+        <v>630</v>
+      </c>
+      <c r="G229" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7">
+      <c r="A230" t="s">
+        <v>240</v>
+      </c>
+      <c r="B230" t="s">
+        <v>514</v>
+      </c>
+      <c r="C230" t="s">
+        <v>612</v>
+      </c>
+      <c r="D230" t="s">
+        <v>630</v>
+      </c>
+      <c r="G230" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231" t="s">
+        <v>241</v>
+      </c>
+      <c r="B231" t="s">
+        <v>515</v>
+      </c>
+      <c r="C231" t="s">
+        <v>612</v>
+      </c>
+      <c r="D231" t="s">
+        <v>630</v>
+      </c>
+      <c r="G231" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7">
+      <c r="A232" t="s">
+        <v>242</v>
+      </c>
+      <c r="B232" t="s">
+        <v>516</v>
+      </c>
+      <c r="C232" t="s">
+        <v>612</v>
+      </c>
+      <c r="D232" t="s">
+        <v>630</v>
+      </c>
+      <c r="G232" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7">
+      <c r="A233" t="s">
+        <v>243</v>
+      </c>
+      <c r="B233" t="s">
+        <v>517</v>
+      </c>
+      <c r="C233" t="s">
+        <v>612</v>
+      </c>
+      <c r="D233" t="s">
+        <v>630</v>
+      </c>
+      <c r="G233" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7">
+      <c r="A234" t="s">
+        <v>244</v>
+      </c>
+      <c r="B234" t="s">
+        <v>518</v>
+      </c>
+      <c r="C234" t="s">
+        <v>612</v>
+      </c>
+      <c r="D234" t="s">
+        <v>630</v>
+      </c>
+      <c r="G234" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235" t="s">
+        <v>245</v>
+      </c>
+      <c r="B235" t="s">
+        <v>519</v>
+      </c>
+      <c r="C235" t="s">
+        <v>612</v>
+      </c>
+      <c r="D235" t="s">
+        <v>630</v>
+      </c>
+      <c r="G235" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7">
+      <c r="A236" t="s">
+        <v>246</v>
+      </c>
+      <c r="B236" t="s">
+        <v>520</v>
+      </c>
+      <c r="C236" t="s">
+        <v>612</v>
+      </c>
+      <c r="D236" t="s">
+        <v>630</v>
+      </c>
+      <c r="G236" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7">
+      <c r="A237" t="s">
+        <v>247</v>
+      </c>
+      <c r="B237" t="s">
+        <v>521</v>
+      </c>
+      <c r="C237" t="s">
+        <v>612</v>
+      </c>
+      <c r="D237" t="s">
+        <v>630</v>
+      </c>
+      <c r="G237" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7">
+      <c r="A238" t="s">
+        <v>248</v>
+      </c>
+      <c r="B238" t="s">
+        <v>522</v>
+      </c>
+      <c r="C238" t="s">
+        <v>612</v>
+      </c>
+      <c r="D238" t="s">
+        <v>630</v>
+      </c>
+      <c r="G238" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7">
+      <c r="A239" t="s">
+        <v>249</v>
+      </c>
+      <c r="B239" t="s">
+        <v>523</v>
+      </c>
+      <c r="C239" t="s">
+        <v>612</v>
+      </c>
+      <c r="D239" t="s">
+        <v>630</v>
+      </c>
+      <c r="G239" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240" t="s">
+        <v>250</v>
+      </c>
+      <c r="B240" t="s">
+        <v>524</v>
+      </c>
+      <c r="C240" t="s">
+        <v>606</v>
+      </c>
+      <c r="D240" t="s">
+        <v>630</v>
+      </c>
+      <c r="G240" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241" t="s">
+        <v>251</v>
+      </c>
+      <c r="B241" t="s">
+        <v>525</v>
+      </c>
+      <c r="C241" t="s">
+        <v>606</v>
+      </c>
+      <c r="D241" t="s">
+        <v>630</v>
+      </c>
+      <c r="G241" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
+      <c r="A242" t="s">
+        <v>252</v>
+      </c>
+      <c r="B242" t="s">
+        <v>526</v>
+      </c>
+      <c r="C242" t="s">
+        <v>606</v>
+      </c>
+      <c r="D242" t="s">
+        <v>630</v>
+      </c>
+      <c r="G242" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7">
+      <c r="A243" t="s">
+        <v>253</v>
+      </c>
+      <c r="B243" t="s">
+        <v>527</v>
+      </c>
+      <c r="C243" t="s">
+        <v>606</v>
+      </c>
+      <c r="D243" t="s">
+        <v>630</v>
+      </c>
+      <c r="G243" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="A244" t="s">
+        <v>254</v>
+      </c>
+      <c r="B244" t="s">
+        <v>528</v>
+      </c>
+      <c r="C244" t="s">
+        <v>606</v>
+      </c>
+      <c r="D244" t="s">
+        <v>630</v>
+      </c>
+      <c r="G244" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245" t="s">
+        <v>255</v>
+      </c>
+      <c r="B245" t="s">
+        <v>529</v>
+      </c>
+      <c r="C245" t="s">
+        <v>606</v>
+      </c>
+      <c r="D245" t="s">
+        <v>630</v>
+      </c>
+      <c r="G245" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7">
+      <c r="A246" t="s">
+        <v>256</v>
+      </c>
+      <c r="B246" t="s">
+        <v>530</v>
+      </c>
+      <c r="C246" t="s">
+        <v>606</v>
+      </c>
+      <c r="D246" t="s">
+        <v>630</v>
+      </c>
+      <c r="G246" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7">
+      <c r="A247" t="s">
+        <v>257</v>
+      </c>
+      <c r="B247" t="s">
+        <v>531</v>
+      </c>
+      <c r="C247" t="s">
+        <v>606</v>
+      </c>
+      <c r="D247" t="s">
+        <v>630</v>
+      </c>
+      <c r="G247" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7">
+      <c r="A248" t="s">
+        <v>258</v>
+      </c>
+      <c r="B248" t="s">
+        <v>532</v>
+      </c>
+      <c r="C248" t="s">
+        <v>606</v>
+      </c>
+      <c r="D248" t="s">
+        <v>630</v>
+      </c>
+      <c r="G248" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7">
+      <c r="A249" t="s">
+        <v>259</v>
+      </c>
+      <c r="B249" t="s">
+        <v>533</v>
+      </c>
+      <c r="C249" t="s">
+        <v>614</v>
+      </c>
+      <c r="D249" t="s">
+        <v>630</v>
+      </c>
+      <c r="G249" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
+      <c r="A250" t="s">
+        <v>260</v>
+      </c>
+      <c r="B250" t="s">
+        <v>534</v>
+      </c>
+      <c r="C250" t="s">
+        <v>614</v>
+      </c>
+      <c r="D250" t="s">
+        <v>630</v>
+      </c>
+      <c r="G250" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="A251" t="s">
+        <v>261</v>
+      </c>
+      <c r="B251" t="s">
+        <v>535</v>
+      </c>
+      <c r="C251" t="s">
+        <v>615</v>
+      </c>
+      <c r="D251" t="s">
+        <v>630</v>
+      </c>
+      <c r="G251" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
+      <c r="A252" t="s">
+        <v>262</v>
+      </c>
+      <c r="B252" t="s">
+        <v>536</v>
+      </c>
+      <c r="C252" t="s">
+        <v>615</v>
+      </c>
+      <c r="D252" t="s">
+        <v>630</v>
+      </c>
+      <c r="G252" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7">
+      <c r="A253" t="s">
+        <v>263</v>
+      </c>
+      <c r="B253" t="s">
+        <v>537</v>
+      </c>
+      <c r="C253" t="s">
+        <v>615</v>
+      </c>
+      <c r="D253" t="s">
+        <v>630</v>
+      </c>
+      <c r="G253" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7">
+      <c r="A254" t="s">
+        <v>264</v>
+      </c>
+      <c r="B254" t="s">
+        <v>538</v>
+      </c>
+      <c r="C254" t="s">
+        <v>615</v>
+      </c>
+      <c r="D254" t="s">
+        <v>630</v>
+      </c>
+      <c r="G254" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7">
+      <c r="A255" t="s">
+        <v>265</v>
+      </c>
+      <c r="B255" t="s">
+        <v>539</v>
+      </c>
+      <c r="C255" t="s">
+        <v>615</v>
+      </c>
+      <c r="D255" t="s">
+        <v>630</v>
+      </c>
+      <c r="G255" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7">
+      <c r="A256" t="s">
+        <v>266</v>
+      </c>
+      <c r="B256" t="s">
+        <v>540</v>
+      </c>
+      <c r="C256" t="s">
+        <v>609</v>
+      </c>
+      <c r="D256" t="s">
+        <v>630</v>
+      </c>
+      <c r="G256" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
+      <c r="A257" t="s">
+        <v>267</v>
+      </c>
+      <c r="B257" t="s">
+        <v>541</v>
+      </c>
+      <c r="C257" t="s">
+        <v>609</v>
+      </c>
+      <c r="D257" t="s">
+        <v>630</v>
+      </c>
+      <c r="G257" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
+      <c r="A258" t="s">
+        <v>268</v>
+      </c>
+      <c r="B258" t="s">
+        <v>542</v>
+      </c>
+      <c r="C258" t="s">
+        <v>612</v>
+      </c>
+      <c r="D258" t="s">
+        <v>630</v>
+      </c>
+      <c r="G258" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
+      <c r="A259" t="s">
+        <v>269</v>
+      </c>
+      <c r="B259" t="s">
+        <v>543</v>
+      </c>
+      <c r="C259" t="s">
+        <v>612</v>
+      </c>
+      <c r="D259" t="s">
+        <v>630</v>
+      </c>
+      <c r="G259" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
+      <c r="A260" t="s">
+        <v>270</v>
+      </c>
+      <c r="B260" t="s">
+        <v>544</v>
+      </c>
+      <c r="C260" t="s">
+        <v>612</v>
+      </c>
+      <c r="D260" t="s">
+        <v>630</v>
+      </c>
+      <c r="G260" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
+      <c r="A261" t="s">
+        <v>271</v>
+      </c>
+      <c r="B261" t="s">
+        <v>545</v>
+      </c>
+      <c r="C261" t="s">
+        <v>612</v>
+      </c>
+      <c r="D261" t="s">
+        <v>630</v>
+      </c>
+      <c r="G261" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
+      <c r="A262" t="s">
+        <v>272</v>
+      </c>
+      <c r="B262" t="s">
+        <v>546</v>
+      </c>
+      <c r="C262" t="s">
+        <v>612</v>
+      </c>
+      <c r="D262" t="s">
+        <v>630</v>
+      </c>
+      <c r="G262" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7">
+      <c r="A263" t="s">
+        <v>273</v>
+      </c>
+      <c r="B263" t="s">
+        <v>547</v>
+      </c>
+      <c r="C263" t="s">
+        <v>612</v>
+      </c>
+      <c r="D263" t="s">
+        <v>630</v>
+      </c>
+      <c r="G263" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
+      <c r="A264" t="s">
+        <v>274</v>
+      </c>
+      <c r="B264" t="s">
+        <v>548</v>
+      </c>
+      <c r="C264" t="s">
+        <v>612</v>
+      </c>
+      <c r="D264" t="s">
+        <v>630</v>
+      </c>
+      <c r="G264" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
+      <c r="A265" t="s">
+        <v>275</v>
+      </c>
+      <c r="B265" t="s">
+        <v>549</v>
+      </c>
+      <c r="C265" t="s">
+        <v>612</v>
+      </c>
+      <c r="D265" t="s">
+        <v>630</v>
+      </c>
+      <c r="G265" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
+      <c r="A266" t="s">
+        <v>276</v>
+      </c>
+      <c r="B266" t="s">
+        <v>550</v>
+      </c>
+      <c r="C266" t="s">
+        <v>610</v>
+      </c>
+      <c r="D266" t="s">
+        <v>655</v>
+      </c>
+      <c r="G266" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
+      <c r="A267" t="s">
+        <v>277</v>
+      </c>
+      <c r="B267" t="s">
+        <v>551</v>
+      </c>
+      <c r="C267" t="s">
+        <v>628</v>
+      </c>
+      <c r="D267" t="s">
+        <v>655</v>
+      </c>
+      <c r="G267" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7">
+      <c r="A268" t="s">
+        <v>278</v>
+      </c>
+      <c r="B268" t="s">
+        <v>552</v>
+      </c>
+      <c r="C268" t="s">
+        <v>606</v>
+      </c>
+      <c r="D268" t="s">
+        <v>655</v>
+      </c>
+      <c r="G268" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
+      <c r="A269" t="s">
+        <v>279</v>
+      </c>
+      <c r="B269" t="s">
+        <v>553</v>
+      </c>
+      <c r="C269" t="s">
+        <v>629</v>
+      </c>
+      <c r="D269" t="s">
+        <v>655</v>
+      </c>
+      <c r="G269" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
+      <c r="A270" t="s">
+        <v>280</v>
+      </c>
+      <c r="B270" t="s">
+        <v>554</v>
+      </c>
+      <c r="C270" t="s">
+        <v>615</v>
+      </c>
+      <c r="D270" t="s">
+        <v>655</v>
+      </c>
+      <c r="G270" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7">
+      <c r="A271" t="s">
+        <v>281</v>
+      </c>
+      <c r="B271" t="s">
+        <v>555</v>
+      </c>
+      <c r="C271" t="s">
+        <v>612</v>
+      </c>
+      <c r="D271" t="s">
+        <v>655</v>
+      </c>
+      <c r="G271" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
+      <c r="A272" t="s">
+        <v>282</v>
+      </c>
+      <c r="B272" t="s">
+        <v>556</v>
+      </c>
+      <c r="C272" t="s">
+        <v>612</v>
+      </c>
+      <c r="D272" t="s">
+        <v>655</v>
+      </c>
+      <c r="G272" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
+      <c r="A273" t="s">
+        <v>283</v>
+      </c>
+      <c r="B273" t="s">
+        <v>557</v>
+      </c>
+      <c r="C273" t="s">
+        <v>612</v>
+      </c>
+      <c r="D273" t="s">
+        <v>655</v>
+      </c>
+      <c r="G273" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
+      <c r="A274" t="s">
+        <v>284</v>
+      </c>
+      <c r="B274" t="s">
+        <v>558</v>
+      </c>
+      <c r="C274" t="s">
+        <v>606</v>
+      </c>
+      <c r="D274" t="s">
+        <v>655</v>
+      </c>
+      <c r="G274" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
+      <c r="A275" t="s">
+        <v>285</v>
+      </c>
+      <c r="B275" t="s">
+        <v>559</v>
+      </c>
+      <c r="C275" t="s">
+        <v>606</v>
+      </c>
+      <c r="D275" t="s">
+        <v>655</v>
+      </c>
+      <c r="G275" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
+      <c r="A276" t="s">
+        <v>286</v>
+      </c>
+      <c r="B276" t="s">
+        <v>560</v>
+      </c>
+      <c r="C276" t="s">
+        <v>610</v>
+      </c>
+      <c r="D276" t="s">
+        <v>655</v>
+      </c>
+      <c r="G276" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
+      <c r="A277" t="s">
+        <v>287</v>
+      </c>
+      <c r="B277" t="s">
+        <v>561</v>
+      </c>
+      <c r="C277" t="s">
+        <v>610</v>
+      </c>
+      <c r="D277" t="s">
+        <v>655</v>
+      </c>
+      <c r="G277" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
+      <c r="A278" t="s">
+        <v>288</v>
+      </c>
+      <c r="B278" t="s">
+        <v>562</v>
+      </c>
+      <c r="C278" t="s">
+        <v>610</v>
+      </c>
+      <c r="D278" t="s">
+        <v>655</v>
+      </c>
+      <c r="G278" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
+      <c r="A279" t="s">
+        <v>289</v>
+      </c>
+      <c r="B279" t="s">
+        <v>563</v>
+      </c>
+      <c r="C279" t="s">
+        <v>612</v>
+      </c>
+      <c r="D279" t="s">
+        <v>655</v>
+      </c>
+      <c r="G279" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
+      <c r="A280" t="s">
+        <v>290</v>
+      </c>
+      <c r="B280" t="s">
+        <v>564</v>
+      </c>
+      <c r="C280" t="s">
+        <v>606</v>
+      </c>
+      <c r="D280" t="s">
+        <v>644</v>
+      </c>
+      <c r="G280" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
+      <c r="A281" t="s">
+        <v>291</v>
+      </c>
+      <c r="B281" t="s">
+        <v>565</v>
+      </c>
+      <c r="C281" t="s">
+        <v>612</v>
+      </c>
+      <c r="D281" t="s">
+        <v>656</v>
+      </c>
+      <c r="G281" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282" t="s">
+        <v>292</v>
+      </c>
+      <c r="B282" t="s">
+        <v>566</v>
+      </c>
+      <c r="C282" t="s">
+        <v>611</v>
+      </c>
+      <c r="D282" t="s">
+        <v>644</v>
+      </c>
+      <c r="G282" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283" t="s">
+        <v>293</v>
+      </c>
+      <c r="B283" t="s">
+        <v>567</v>
+      </c>
+      <c r="C283" t="s">
+        <v>612</v>
+      </c>
+      <c r="D283" t="s">
+        <v>644</v>
+      </c>
+      <c r="G283" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284" t="s">
+        <v>294</v>
+      </c>
+      <c r="B284" t="s">
+        <v>568</v>
+      </c>
+      <c r="C284" t="s">
+        <v>605</v>
+      </c>
+      <c r="D284" t="s">
+        <v>630</v>
+      </c>
+      <c r="F284" t="s">
+        <v>715</v>
+      </c>
+      <c r="G284" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285" t="s">
+        <v>295</v>
+      </c>
+      <c r="B285" t="s">
+        <v>569</v>
+      </c>
+      <c r="C285" t="s">
+        <v>615</v>
+      </c>
+      <c r="D285" t="s">
+        <v>655</v>
+      </c>
+      <c r="G285" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286" t="s">
+        <v>296</v>
+      </c>
+      <c r="B286" t="s">
+        <v>570</v>
+      </c>
+      <c r="C286" t="s">
+        <v>606</v>
+      </c>
+      <c r="D286" t="s">
+        <v>655</v>
+      </c>
+      <c r="G286" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287" t="s">
+        <v>297</v>
+      </c>
+      <c r="B287" t="s">
+        <v>571</v>
+      </c>
+      <c r="C287" t="s">
+        <v>609</v>
+      </c>
+      <c r="D287" t="s">
+        <v>655</v>
+      </c>
+      <c r="G287" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
+      <c r="A288" t="s">
+        <v>298</v>
+      </c>
+      <c r="B288" t="s">
+        <v>572</v>
+      </c>
+      <c r="C288" t="s">
+        <v>612</v>
+      </c>
+      <c r="D288" t="s">
+        <v>655</v>
+      </c>
+      <c r="G288" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7">
+      <c r="A289" t="s">
+        <v>299</v>
+      </c>
+      <c r="B289" t="s">
+        <v>573</v>
+      </c>
+      <c r="C289" t="s">
+        <v>612</v>
+      </c>
+      <c r="D289" t="s">
+        <v>655</v>
+      </c>
+      <c r="G289" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7">
+      <c r="A290" t="s">
+        <v>300</v>
+      </c>
+      <c r="B290" t="s">
+        <v>574</v>
+      </c>
+      <c r="C290" t="s">
+        <v>610</v>
+      </c>
+      <c r="D290" t="s">
+        <v>655</v>
+      </c>
+      <c r="G290" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7">
+      <c r="A291" t="s">
+        <v>301</v>
+      </c>
+      <c r="B291" t="s">
+        <v>575</v>
+      </c>
+      <c r="C291" t="s">
+        <v>610</v>
+      </c>
+      <c r="D291" t="s">
+        <v>655</v>
+      </c>
+      <c r="G291" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7">
+      <c r="A292" t="s">
+        <v>302</v>
+      </c>
+      <c r="B292" t="s">
+        <v>576</v>
+      </c>
+      <c r="C292" t="s">
+        <v>612</v>
+      </c>
+      <c r="D292" t="s">
+        <v>655</v>
+      </c>
+      <c r="G292" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7">
+      <c r="A293" t="s">
+        <v>303</v>
+      </c>
+      <c r="B293" t="s">
+        <v>577</v>
+      </c>
+      <c r="C293" t="s">
+        <v>617</v>
+      </c>
+      <c r="D293" t="s">
+        <v>655</v>
+      </c>
+      <c r="G293" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7">
+      <c r="A294" t="s">
+        <v>304</v>
+      </c>
+      <c r="B294" t="s">
+        <v>578</v>
+      </c>
+      <c r="C294" t="s">
+        <v>609</v>
+      </c>
+      <c r="D294" t="s">
+        <v>655</v>
+      </c>
+      <c r="G294" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7">
+      <c r="A295" t="s">
+        <v>140</v>
+      </c>
+      <c r="B295" t="s">
+        <v>579</v>
+      </c>
+      <c r="C295" t="s">
+        <v>615</v>
+      </c>
+      <c r="D295" t="s">
+        <v>655</v>
+      </c>
+      <c r="G295" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7">
+      <c r="A296" t="s">
+        <v>305</v>
+      </c>
+      <c r="B296" t="s">
+        <v>580</v>
+      </c>
+      <c r="C296" t="s">
+        <v>606</v>
+      </c>
+      <c r="D296" t="s">
+        <v>644</v>
+      </c>
+      <c r="G296" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7">
+      <c r="A297" t="s">
+        <v>306</v>
+      </c>
+      <c r="B297" t="s">
+        <v>581</v>
+      </c>
+      <c r="C297" t="s">
+        <v>615</v>
+      </c>
+      <c r="D297" t="s">
+        <v>644</v>
+      </c>
+      <c r="G297" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7">
+      <c r="A298" t="s">
+        <v>307</v>
+      </c>
+      <c r="B298" t="s">
+        <v>582</v>
+      </c>
+      <c r="C298" t="s">
+        <v>612</v>
+      </c>
+      <c r="D298" t="s">
+        <v>644</v>
+      </c>
+      <c r="G298" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7">
+      <c r="A299" t="s">
+        <v>308</v>
+      </c>
+      <c r="B299" t="s">
+        <v>583</v>
+      </c>
+      <c r="C299" t="s">
+        <v>610</v>
+      </c>
+      <c r="D299" t="s">
+        <v>644</v>
+      </c>
+      <c r="G299" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
+      <c r="A300" t="s">
+        <v>309</v>
+      </c>
+      <c r="B300" t="s">
+        <v>584</v>
+      </c>
+      <c r="C300" t="s">
+        <v>606</v>
+      </c>
+      <c r="D300" t="s">
+        <v>644</v>
+      </c>
+      <c r="G300" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7">
+      <c r="A301" t="s">
+        <v>310</v>
+      </c>
+      <c r="B301" t="s">
+        <v>585</v>
+      </c>
+      <c r="C301" t="s">
+        <v>606</v>
+      </c>
+      <c r="D301" t="s">
+        <v>644</v>
+      </c>
+      <c r="G301" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7">
+      <c r="A302" t="s">
+        <v>311</v>
+      </c>
+      <c r="B302" t="s">
+        <v>586</v>
+      </c>
+      <c r="C302" t="s">
+        <v>610</v>
+      </c>
+      <c r="D302" t="s">
+        <v>644</v>
+      </c>
+      <c r="G302" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7">
+      <c r="A303" t="s">
+        <v>312</v>
+      </c>
+      <c r="B303" t="s">
+        <v>587</v>
+      </c>
+      <c r="C303" t="s">
+        <v>611</v>
+      </c>
+      <c r="D303" t="s">
+        <v>644</v>
+      </c>
+      <c r="G303" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7">
+      <c r="A304" t="s">
+        <v>313</v>
+      </c>
+      <c r="B304" t="s">
+        <v>588</v>
+      </c>
+      <c r="C304" t="s">
+        <v>612</v>
+      </c>
+      <c r="D304" t="s">
+        <v>644</v>
+      </c>
+      <c r="G304" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7">
+      <c r="A305" t="s">
+        <v>314</v>
+      </c>
+      <c r="B305" t="s">
+        <v>589</v>
+      </c>
+      <c r="C305" t="s">
+        <v>612</v>
+      </c>
+      <c r="D305" t="s">
+        <v>644</v>
+      </c>
+      <c r="G305" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7">
+      <c r="A306" t="s">
+        <v>315</v>
+      </c>
+      <c r="B306" t="s">
+        <v>590</v>
+      </c>
+      <c r="C306" t="s">
+        <v>606</v>
+      </c>
+      <c r="D306" t="s">
+        <v>644</v>
+      </c>
+      <c r="G306" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7">
+      <c r="A307" t="s">
+        <v>316</v>
+      </c>
+      <c r="B307" t="s">
+        <v>591</v>
+      </c>
+      <c r="C307" t="s">
+        <v>606</v>
+      </c>
+      <c r="D307" t="s">
+        <v>644</v>
+      </c>
+      <c r="G307" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7">
+      <c r="A308" t="s">
+        <v>317</v>
+      </c>
+      <c r="B308" t="s">
+        <v>592</v>
+      </c>
+      <c r="C308" t="s">
+        <v>612</v>
+      </c>
+      <c r="D308" t="s">
+        <v>656</v>
+      </c>
+      <c r="G308" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7">
+      <c r="A309" t="s">
+        <v>318</v>
+      </c>
+      <c r="B309" t="s">
+        <v>593</v>
+      </c>
+      <c r="C309" t="s">
+        <v>612</v>
+      </c>
+      <c r="D309" t="s">
+        <v>643</v>
+      </c>
+      <c r="G309" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7">
+      <c r="A310" t="s">
+        <v>319</v>
+      </c>
+      <c r="B310" t="s">
+        <v>594</v>
+      </c>
+      <c r="C310" t="s">
+        <v>612</v>
+      </c>
+      <c r="D310" t="s">
+        <v>657</v>
+      </c>
+      <c r="G310" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7">
+      <c r="A311" t="s">
+        <v>320</v>
+      </c>
+      <c r="B311" t="s">
+        <v>595</v>
+      </c>
+      <c r="C311" t="s">
+        <v>612</v>
+      </c>
+      <c r="D311" t="s">
+        <v>645</v>
+      </c>
+      <c r="G311" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7">
+      <c r="A312" t="s">
+        <v>321</v>
+      </c>
+      <c r="B312" t="s">
+        <v>596</v>
+      </c>
+      <c r="C312" t="s">
+        <v>612</v>
+      </c>
+      <c r="D312" t="s">
+        <v>651</v>
+      </c>
+      <c r="G312" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7">
+      <c r="A313" t="s">
+        <v>322</v>
+      </c>
+      <c r="B313" t="s">
+        <v>597</v>
+      </c>
+      <c r="C313" t="s">
+        <v>612</v>
+      </c>
+      <c r="D313" t="s">
+        <v>654</v>
+      </c>
+      <c r="G313" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7">
+      <c r="A314" t="s">
+        <v>323</v>
+      </c>
+      <c r="B314" t="s">
+        <v>598</v>
+      </c>
+      <c r="C314" t="s">
+        <v>612</v>
+      </c>
+      <c r="D314" t="s">
+        <v>658</v>
+      </c>
+      <c r="G314" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7">
+      <c r="A315" t="s">
+        <v>324</v>
+      </c>
+      <c r="B315" t="s">
+        <v>599</v>
+      </c>
+      <c r="C315" t="s">
+        <v>606</v>
+      </c>
+      <c r="D315" t="s">
+        <v>652</v>
+      </c>
+      <c r="G315" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7">
+      <c r="A316" t="s">
+        <v>325</v>
+      </c>
+      <c r="B316" t="s">
+        <v>600</v>
+      </c>
+      <c r="C316" t="s">
+        <v>606</v>
+      </c>
+      <c r="D316" t="s">
+        <v>652</v>
+      </c>
+      <c r="G316" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7">
+      <c r="A317" t="s">
+        <v>326</v>
+      </c>
+      <c r="B317" t="s">
+        <v>601</v>
+      </c>
+      <c r="C317" t="s">
+        <v>612</v>
+      </c>
+      <c r="D317" t="s">
+        <v>659</v>
+      </c>
+      <c r="G317" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7">
+      <c r="A318" t="s">
+        <v>327</v>
+      </c>
+      <c r="B318" t="s">
+        <v>602</v>
+      </c>
+      <c r="C318" t="s">
+        <v>615</v>
+      </c>
+      <c r="D318" t="s">
+        <v>660</v>
+      </c>
+      <c r="G318" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7">
+      <c r="A319" t="s">
+        <v>328</v>
+      </c>
+      <c r="B319" t="s">
+        <v>603</v>
+      </c>
+      <c r="C319" t="s">
+        <v>609</v>
+      </c>
+      <c r="D319" t="s">
+        <v>644</v>
+      </c>
+      <c r="G319" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7">
+      <c r="A320" t="s">
+        <v>329</v>
+      </c>
+      <c r="B320" t="s">
+        <v>604</v>
+      </c>
+      <c r="C320" t="s">
+        <v>609</v>
+      </c>
+      <c r="D320" t="s">
+        <v>655</v>
+      </c>
+      <c r="G320" t="s">
+        <v>735</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1"/>
+    <hyperlink ref="F14" r:id="rId1"/>
+    <hyperlink ref="F15" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="745">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -1006,6 +1006,18 @@
     <t>Mosterts Mill Restoration Trust</t>
   </si>
   <si>
+    <t>Rondebosch United Church</t>
+  </si>
+  <si>
+    <t>Rosecourt Lodge</t>
+  </si>
+  <si>
+    <t>St Peter's Church Mowbray</t>
+  </si>
+  <si>
+    <t>Micklefield School</t>
+  </si>
+  <si>
     <t>info@ctsc.org.za</t>
   </si>
   <si>
@@ -1465,7 +1477,7 @@
     <t>info@chrysalisacademy.org.za</t>
   </si>
   <si>
-    <t>OtteryYouth@telkomsa.net</t>
+    <t>otteryyouth@telkomsa.net</t>
   </si>
   <si>
     <t>info@robbenisland.org.za</t>
@@ -1552,19 +1564,19 @@
     <t>info@capebirdclub.org.za</t>
   </si>
   <si>
-    <t>ACVVSWE@TELKOMSA.NET</t>
+    <t>acvvswe@telkomsa.net</t>
   </si>
   <si>
     <t>tamara@acvv.org.za</t>
   </si>
   <si>
-    <t>WILMAPAPIER2@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>INFO@GABRIELLACENTRE.ORG.ZA</t>
-  </si>
-  <si>
-    <t>HEIDI@HALLITRUST.CO.ZA</t>
+    <t>wilmapapier2@gmail.com</t>
+  </si>
+  <si>
+    <t>info@gabriellacentre.org.za</t>
+  </si>
+  <si>
+    <t>heidi@hallitrust.co.za</t>
   </si>
   <si>
     <t>gwenj@houseofboniwe.co.za</t>
@@ -1573,7 +1585,7 @@
     <t>kerry@soupertroopers.org</t>
   </si>
   <si>
-    <t>Darryn.Hector@uManity.co.za</t>
+    <t>darryn.hector@umanity.co.za</t>
   </si>
   <si>
     <t>info@commongood.org.za</t>
@@ -1597,7 +1609,7 @@
     <t>angels@angelsinc.co.za</t>
   </si>
   <si>
-    <t>Ayakhanya@gmail.com</t>
+    <t>ayakhanya@gmail.com</t>
   </si>
   <si>
     <t>matt@sosafrica.com</t>
@@ -1633,7 +1645,7 @@
     <t>admin@frcsa.org.za</t>
   </si>
   <si>
-    <t>Friendsofbca@mweb.co.za</t>
+    <t>friendsofbca@mweb.co.za</t>
   </si>
   <si>
     <t>info@orangeart.org.za</t>
@@ -1720,7 +1732,7 @@
     <t>kolbe.house@telkomsa.net</t>
   </si>
   <si>
-    <t>Imrah@ctsc.org.za</t>
+    <t>imrah@ctsc.org.za</t>
   </si>
   <si>
     <t>stephen@emg.org.za</t>
@@ -1738,7 +1750,7 @@
     <t>info@lmrid.capetown</t>
   </si>
   <si>
-    <t>Janine.Joemat@westerncape.gov.za</t>
+    <t>janine.joemat@westerncape.gov.za</t>
   </si>
   <si>
     <t>jacquikoep@gmail.com</t>
@@ -1759,7 +1771,7 @@
     <t>info@rondeboschvulekatrust.co.za</t>
   </si>
   <si>
-    <t>FriendsofRondeboschCommon@gmail.com</t>
+    <t>friendsofrondeboschcommon@gmail.com</t>
   </si>
   <si>
     <t>rcidoffices@gmail.com</t>
@@ -1829,6 +1841,21 @@
   </si>
   <si>
     <t>info@mostertsmill.org.za</t>
+  </si>
+  <si>
+    <t>office@rondeboschunited.co.za</t>
+  </si>
+  <si>
+    <t>volunteer@mmh.org.za</t>
+  </si>
+  <si>
+    <t>info@rosecourtlodge.co.za</t>
+  </si>
+  <si>
+    <t>office@stpetersmowbray.org.za</t>
+  </si>
+  <si>
+    <t>admin@micklefield.co.za</t>
   </si>
   <si>
     <t>Museums &amp; Heritage</t>
@@ -2566,7 +2593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L320"/>
+  <dimension ref="A1:L325"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2612,22 +2639,22 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C2" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="D2" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E2" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="F2" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="G2" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2635,22 +2662,22 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C3" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="D3" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E3" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="F3" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="G3" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2658,22 +2685,22 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C4" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D4" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E4" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="F4" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="G4" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2681,22 +2708,22 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C5" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D5" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E5" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="F5" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="G5" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2704,22 +2731,22 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C6" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="D6" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E6" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="F6" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="G6" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2727,22 +2754,22 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C7" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="D7" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E7" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="F7" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="G7" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2750,22 +2777,22 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C8" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D8" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E8" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="F8" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="G8" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2773,22 +2800,22 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C9" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D9" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E9" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="F9" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="G9" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2796,22 +2823,22 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C10" t="s">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="D10" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E10" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="F10" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="G10" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2819,22 +2846,22 @@
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C11" t="s">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="D11" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E11" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="F11" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="G11" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2842,22 +2869,22 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C12" t="s">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="D12" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E12" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="F12" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="G12" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2865,22 +2892,22 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C13" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="D13" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E13" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="F13" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="G13" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2888,22 +2915,22 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C14" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D14" t="s">
-        <v>631</v>
+        <v>640</v>
       </c>
       <c r="E14" t="s">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>716</v>
+        <v>725</v>
       </c>
       <c r="G14" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2911,22 +2938,22 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C15" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D15" t="s">
-        <v>631</v>
+        <v>640</v>
       </c>
       <c r="E15" t="s">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>717</v>
+        <v>726</v>
       </c>
       <c r="G15" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2934,16 +2961,16 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C16" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D16" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G16" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2951,16 +2978,16 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C17" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D17" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G17" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2968,16 +2995,16 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C18" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D18" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G18" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2985,16 +3012,16 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C19" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D19" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G19" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -3002,16 +3029,16 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C20" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D20" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G20" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3019,16 +3046,16 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C21" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D21" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G21" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3036,16 +3063,16 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C22" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D22" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G22" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3053,16 +3080,16 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C23" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D23" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G23" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3070,16 +3097,16 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C24" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D24" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G24" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3087,16 +3114,16 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C25" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D25" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G25" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3104,16 +3131,16 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C26" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="D26" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G26" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3121,16 +3148,16 @@
         <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C27" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="D27" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G27" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -3138,16 +3165,16 @@
         <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C28" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="D28" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G28" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3155,16 +3182,16 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C29" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="D29" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G29" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -3172,16 +3199,16 @@
         <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C30" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="D30" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G30" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3189,16 +3216,16 @@
         <v>41</v>
       </c>
       <c r="B31" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C31" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="D31" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G31" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3206,16 +3233,16 @@
         <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C32" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="D32" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G32" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3223,16 +3250,16 @@
         <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C33" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D33" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G33" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -3240,16 +3267,16 @@
         <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C34" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D34" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G34" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -3257,16 +3284,16 @@
         <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C35" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D35" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G35" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3274,16 +3301,16 @@
         <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C36" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D36" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G36" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -3291,16 +3318,16 @@
         <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C37" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D37" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G37" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -3308,16 +3335,16 @@
         <v>48</v>
       </c>
       <c r="B38" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C38" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D38" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G38" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -3325,16 +3352,16 @@
         <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C39" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D39" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G39" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3342,16 +3369,16 @@
         <v>50</v>
       </c>
       <c r="B40" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C40" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="D40" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G40" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -3359,16 +3386,16 @@
         <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C41" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="D41" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G41" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3376,16 +3403,16 @@
         <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C42" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="D42" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G42" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3393,16 +3420,16 @@
         <v>53</v>
       </c>
       <c r="B43" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C43" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="D43" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G43" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3410,16 +3437,16 @@
         <v>54</v>
       </c>
       <c r="B44" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C44" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="D44" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G44" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3427,16 +3454,16 @@
         <v>55</v>
       </c>
       <c r="B45" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C45" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D45" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G45" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3444,16 +3471,16 @@
         <v>56</v>
       </c>
       <c r="B46" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C46" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D46" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G46" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3461,16 +3488,16 @@
         <v>57</v>
       </c>
       <c r="B47" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C47" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D47" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G47" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3478,16 +3505,16 @@
         <v>58</v>
       </c>
       <c r="B48" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C48" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D48" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G48" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -3495,16 +3522,16 @@
         <v>59</v>
       </c>
       <c r="B49" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C49" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D49" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G49" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -3512,16 +3539,16 @@
         <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C50" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D50" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G50" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -3529,16 +3556,16 @@
         <v>61</v>
       </c>
       <c r="B51" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C51" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D51" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G51" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -3546,16 +3573,16 @@
         <v>62</v>
       </c>
       <c r="B52" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C52" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D52" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G52" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -3563,16 +3590,16 @@
         <v>63</v>
       </c>
       <c r="B53" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C53" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D53" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G53" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3580,16 +3607,16 @@
         <v>64</v>
       </c>
       <c r="B54" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C54" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D54" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G54" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -3597,16 +3624,16 @@
         <v>65</v>
       </c>
       <c r="B55" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C55" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="D55" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G55" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3614,16 +3641,16 @@
         <v>66</v>
       </c>
       <c r="B56" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C56" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="D56" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G56" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3631,16 +3658,16 @@
         <v>67</v>
       </c>
       <c r="B57" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C57" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="D57" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G57" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3648,16 +3675,16 @@
         <v>68</v>
       </c>
       <c r="B58" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C58" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D58" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G58" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3665,16 +3692,16 @@
         <v>69</v>
       </c>
       <c r="B59" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C59" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D59" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G59" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3682,16 +3709,16 @@
         <v>70</v>
       </c>
       <c r="B60" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C60" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D60" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G60" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3699,16 +3726,16 @@
         <v>71</v>
       </c>
       <c r="B61" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C61" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D61" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G61" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3716,16 +3743,16 @@
         <v>72</v>
       </c>
       <c r="B62" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C62" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D62" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G62" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3733,16 +3760,16 @@
         <v>73</v>
       </c>
       <c r="B63" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C63" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D63" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G63" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3750,16 +3777,16 @@
         <v>74</v>
       </c>
       <c r="B64" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C64" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D64" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G64" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3767,16 +3794,16 @@
         <v>75</v>
       </c>
       <c r="B65" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C65" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D65" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G65" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3784,16 +3811,16 @@
         <v>76</v>
       </c>
       <c r="B66" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C66" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D66" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G66" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3801,16 +3828,16 @@
         <v>77</v>
       </c>
       <c r="B67" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C67" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D67" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G67" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3818,16 +3845,16 @@
         <v>78</v>
       </c>
       <c r="B68" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C68" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D68" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G68" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3835,16 +3862,16 @@
         <v>79</v>
       </c>
       <c r="B69" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C69" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="D69" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G69" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3852,16 +3879,16 @@
         <v>80</v>
       </c>
       <c r="B70" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C70" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="D70" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G70" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3869,16 +3896,16 @@
         <v>81</v>
       </c>
       <c r="B71" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C71" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="D71" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G71" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3886,16 +3913,16 @@
         <v>82</v>
       </c>
       <c r="B72" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C72" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="D72" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G72" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3903,16 +3930,16 @@
         <v>83</v>
       </c>
       <c r="B73" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C73" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="D73" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G73" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3920,16 +3947,16 @@
         <v>84</v>
       </c>
       <c r="B74" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C74" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="D74" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G74" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3937,16 +3964,16 @@
         <v>85</v>
       </c>
       <c r="B75" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C75" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D75" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G75" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3954,16 +3981,16 @@
         <v>86</v>
       </c>
       <c r="B76" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C76" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D76" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G76" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3971,16 +3998,16 @@
         <v>87</v>
       </c>
       <c r="B77" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C77" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D77" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G77" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3988,16 +4015,16 @@
         <v>88</v>
       </c>
       <c r="B78" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C78" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D78" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G78" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -4005,16 +4032,16 @@
         <v>89</v>
       </c>
       <c r="B79" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C79" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D79" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G79" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -4022,16 +4049,16 @@
         <v>90</v>
       </c>
       <c r="B80" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C80" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D80" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G80" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -4039,16 +4066,16 @@
         <v>91</v>
       </c>
       <c r="B81" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C81" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D81" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G81" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -4056,16 +4083,16 @@
         <v>92</v>
       </c>
       <c r="B82" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C82" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D82" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G82" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -4073,16 +4100,16 @@
         <v>93</v>
       </c>
       <c r="B83" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C83" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D83" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G83" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -4090,16 +4117,16 @@
         <v>94</v>
       </c>
       <c r="B84" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C84" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D84" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G84" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -4107,16 +4134,16 @@
         <v>95</v>
       </c>
       <c r="B85" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C85" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="D85" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G85" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4124,16 +4151,16 @@
         <v>96</v>
       </c>
       <c r="B86" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C86" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="D86" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G86" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4141,16 +4168,16 @@
         <v>97</v>
       </c>
       <c r="B87" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C87" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="D87" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G87" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4158,16 +4185,16 @@
         <v>98</v>
       </c>
       <c r="B88" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C88" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="D88" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G88" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4175,16 +4202,16 @@
         <v>99</v>
       </c>
       <c r="B89" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C89" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="D89" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G89" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4192,16 +4219,16 @@
         <v>100</v>
       </c>
       <c r="B90" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C90" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D90" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G90" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4209,16 +4236,16 @@
         <v>101</v>
       </c>
       <c r="B91" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C91" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D91" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G91" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4226,16 +4253,16 @@
         <v>102</v>
       </c>
       <c r="B92" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C92" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D92" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G92" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -4243,16 +4270,16 @@
         <v>103</v>
       </c>
       <c r="B93" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C93" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D93" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G93" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -4260,16 +4287,16 @@
         <v>104</v>
       </c>
       <c r="B94" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C94" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D94" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G94" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -4277,16 +4304,16 @@
         <v>105</v>
       </c>
       <c r="B95" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C95" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D95" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G95" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -4294,16 +4321,16 @@
         <v>106</v>
       </c>
       <c r="B96" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C96" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D96" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G96" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4311,16 +4338,16 @@
         <v>107</v>
       </c>
       <c r="B97" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C97" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D97" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G97" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4328,16 +4355,16 @@
         <v>108</v>
       </c>
       <c r="B98" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C98" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D98" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G98" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4345,16 +4372,16 @@
         <v>109</v>
       </c>
       <c r="B99" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C99" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D99" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G99" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4362,16 +4389,16 @@
         <v>110</v>
       </c>
       <c r="B100" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C100" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D100" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G100" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4379,16 +4406,16 @@
         <v>111</v>
       </c>
       <c r="B101" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C101" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D101" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G101" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4396,16 +4423,16 @@
         <v>112</v>
       </c>
       <c r="B102" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C102" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D102" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G102" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4413,16 +4440,16 @@
         <v>113</v>
       </c>
       <c r="B103" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C103" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D103" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G103" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4430,16 +4457,16 @@
         <v>114</v>
       </c>
       <c r="B104" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C104" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D104" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G104" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4447,16 +4474,16 @@
         <v>115</v>
       </c>
       <c r="B105" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C105" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D105" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G105" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4464,16 +4491,16 @@
         <v>116</v>
       </c>
       <c r="B106" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C106" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D106" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G106" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4481,16 +4508,16 @@
         <v>117</v>
       </c>
       <c r="B107" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C107" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="D107" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G107" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4498,16 +4525,16 @@
         <v>118</v>
       </c>
       <c r="B108" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C108" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="D108" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G108" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4515,16 +4542,16 @@
         <v>119</v>
       </c>
       <c r="B109" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C109" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D109" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G109" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4532,16 +4559,16 @@
         <v>120</v>
       </c>
       <c r="B110" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C110" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D110" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G110" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4549,16 +4576,16 @@
         <v>121</v>
       </c>
       <c r="B111" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C111" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D111" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G111" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4566,16 +4593,16 @@
         <v>122</v>
       </c>
       <c r="B112" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C112" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D112" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G112" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4583,16 +4610,16 @@
         <v>123</v>
       </c>
       <c r="B113" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C113" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D113" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G113" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4600,16 +4627,16 @@
         <v>124</v>
       </c>
       <c r="B114" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C114" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
       <c r="D114" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G114" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4617,16 +4644,16 @@
         <v>125</v>
       </c>
       <c r="B115" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C115" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
       <c r="D115" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G115" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4634,16 +4661,16 @@
         <v>126</v>
       </c>
       <c r="B116" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C116" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
       <c r="D116" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G116" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4651,16 +4678,16 @@
         <v>127</v>
       </c>
       <c r="B117" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C117" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
       <c r="D117" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G117" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4668,16 +4695,16 @@
         <v>128</v>
       </c>
       <c r="B118" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C118" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
       <c r="D118" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G118" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4685,22 +4712,22 @@
         <v>129</v>
       </c>
       <c r="B119" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C119" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
       <c r="D119" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E119" t="s">
-        <v>664</v>
+        <v>673</v>
       </c>
       <c r="F119" t="s">
-        <v>718</v>
+        <v>727</v>
       </c>
       <c r="G119" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4708,19 +4735,19 @@
         <v>130</v>
       </c>
       <c r="B120" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C120" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
       <c r="D120" t="s">
-        <v>632</v>
+        <v>641</v>
       </c>
       <c r="E120" t="s">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="G120" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4728,16 +4755,16 @@
         <v>131</v>
       </c>
       <c r="B121" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C121" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
       <c r="D121" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G121" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4745,16 +4772,16 @@
         <v>132</v>
       </c>
       <c r="B122" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C122" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="D122" t="s">
-        <v>633</v>
+        <v>642</v>
       </c>
       <c r="G122" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4762,22 +4789,22 @@
         <v>133</v>
       </c>
       <c r="B123" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C123" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="D123" t="s">
-        <v>634</v>
+        <v>643</v>
       </c>
       <c r="E123" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="F123" t="s">
-        <v>719</v>
+        <v>728</v>
       </c>
       <c r="G123" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4785,16 +4812,16 @@
         <v>134</v>
       </c>
       <c r="B124" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C124" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="D124" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G124" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4802,16 +4829,16 @@
         <v>135</v>
       </c>
       <c r="B125" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C125" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="D125" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G125" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4819,16 +4846,16 @@
         <v>136</v>
       </c>
       <c r="B126" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C126" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="D126" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G126" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4836,16 +4863,16 @@
         <v>137</v>
       </c>
       <c r="B127" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C127" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="D127" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G127" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4853,19 +4880,19 @@
         <v>138</v>
       </c>
       <c r="B128" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C128" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="D128" t="s">
-        <v>635</v>
+        <v>644</v>
       </c>
       <c r="E128" t="s">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="G128" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4873,22 +4900,22 @@
         <v>139</v>
       </c>
       <c r="B129" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C129" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D129" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E129" t="s">
-        <v>668</v>
+        <v>677</v>
       </c>
       <c r="F129" t="s">
-        <v>720</v>
+        <v>729</v>
       </c>
       <c r="G129" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4896,16 +4923,16 @@
         <v>140</v>
       </c>
       <c r="B130" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C130" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D130" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G130" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4913,13 +4940,13 @@
         <v>141</v>
       </c>
       <c r="C131" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D131" t="s">
-        <v>636</v>
+        <v>645</v>
       </c>
       <c r="E131" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4927,19 +4954,19 @@
         <v>142</v>
       </c>
       <c r="B132" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C132" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D132" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="E132" t="s">
-        <v>670</v>
+        <v>679</v>
       </c>
       <c r="G132" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4947,19 +4974,19 @@
         <v>143</v>
       </c>
       <c r="B133" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C133" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D133" t="s">
-        <v>638</v>
+        <v>647</v>
       </c>
       <c r="E133" t="s">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="G133" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4967,10 +4994,10 @@
         <v>144</v>
       </c>
       <c r="C134" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D134" t="s">
-        <v>639</v>
+        <v>648</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4978,10 +5005,10 @@
         <v>145</v>
       </c>
       <c r="C135" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D135" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4989,16 +5016,16 @@
         <v>146</v>
       </c>
       <c r="B136" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C136" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D136" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G136" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -5006,16 +5033,16 @@
         <v>147</v>
       </c>
       <c r="B137" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C137" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D137" t="s">
-        <v>636</v>
+        <v>645</v>
       </c>
       <c r="G137" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -5023,10 +5050,10 @@
         <v>148</v>
       </c>
       <c r="C138" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D138" t="s">
-        <v>640</v>
+        <v>649</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -5034,10 +5061,10 @@
         <v>149</v>
       </c>
       <c r="C139" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D139" t="s">
-        <v>641</v>
+        <v>650</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -5045,10 +5072,10 @@
         <v>150</v>
       </c>
       <c r="C140" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D140" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -5056,16 +5083,16 @@
         <v>151</v>
       </c>
       <c r="B141" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C141" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D141" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G141" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -5073,22 +5100,22 @@
         <v>152</v>
       </c>
       <c r="B142" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C142" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D142" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E142" t="s">
-        <v>672</v>
+        <v>681</v>
       </c>
       <c r="F142" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="G142" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -5096,16 +5123,16 @@
         <v>153</v>
       </c>
       <c r="B143" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C143" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D143" t="s">
-        <v>640</v>
+        <v>649</v>
       </c>
       <c r="G143" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -5113,13 +5140,13 @@
         <v>154</v>
       </c>
       <c r="C144" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D144" t="s">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="E144" t="s">
-        <v>673</v>
+        <v>682</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -5127,10 +5154,10 @@
         <v>155</v>
       </c>
       <c r="C145" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D145" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -5138,19 +5165,19 @@
         <v>156</v>
       </c>
       <c r="B146" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C146" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D146" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="F146" t="s">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="G146" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -5158,22 +5185,22 @@
         <v>157</v>
       </c>
       <c r="B147" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C147" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D147" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E147" t="s">
-        <v>674</v>
+        <v>683</v>
       </c>
       <c r="F147" t="s">
-        <v>723</v>
+        <v>732</v>
       </c>
       <c r="G147" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5181,19 +5208,19 @@
         <v>158</v>
       </c>
       <c r="B148" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C148" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D148" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E148" t="s">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="G148" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5201,19 +5228,19 @@
         <v>159</v>
       </c>
       <c r="B149" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C149" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D149" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E149" t="s">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="G149" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5221,19 +5248,19 @@
         <v>160</v>
       </c>
       <c r="B150" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C150" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D150" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E150" t="s">
-        <v>677</v>
+        <v>686</v>
       </c>
       <c r="G150" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5241,19 +5268,19 @@
         <v>161</v>
       </c>
       <c r="B151" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C151" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D151" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E151" t="s">
-        <v>678</v>
+        <v>687</v>
       </c>
       <c r="G151" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5261,19 +5288,19 @@
         <v>162</v>
       </c>
       <c r="B152" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C152" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D152" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E152" t="s">
-        <v>679</v>
+        <v>688</v>
       </c>
       <c r="G152" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5281,10 +5308,10 @@
         <v>163</v>
       </c>
       <c r="C153" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D153" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5292,19 +5319,19 @@
         <v>164</v>
       </c>
       <c r="B154" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C154" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D154" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E154" t="s">
-        <v>680</v>
+        <v>689</v>
       </c>
       <c r="G154" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5312,16 +5339,16 @@
         <v>165</v>
       </c>
       <c r="B155" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C155" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D155" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G155" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5329,16 +5356,16 @@
         <v>166</v>
       </c>
       <c r="B156" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C156" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D156" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G156" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5346,22 +5373,22 @@
         <v>167</v>
       </c>
       <c r="B157" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C157" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D157" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="E157" t="s">
-        <v>681</v>
+        <v>690</v>
       </c>
       <c r="F157" t="s">
-        <v>724</v>
+        <v>733</v>
       </c>
       <c r="G157" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5369,19 +5396,19 @@
         <v>168</v>
       </c>
       <c r="B158" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C158" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D158" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E158" t="s">
-        <v>682</v>
+        <v>691</v>
       </c>
       <c r="G158" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5389,19 +5416,19 @@
         <v>169</v>
       </c>
       <c r="B159" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C159" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D159" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E159" t="s">
-        <v>683</v>
+        <v>692</v>
       </c>
       <c r="G159" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5409,19 +5436,19 @@
         <v>170</v>
       </c>
       <c r="B160" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C160" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D160" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E160" t="s">
-        <v>684</v>
+        <v>693</v>
       </c>
       <c r="G160" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5429,19 +5456,19 @@
         <v>171</v>
       </c>
       <c r="B161" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C161" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D161" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="E161" t="s">
-        <v>685</v>
+        <v>694</v>
       </c>
       <c r="G161" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5449,16 +5476,16 @@
         <v>172</v>
       </c>
       <c r="B162" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C162" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D162" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G162" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5466,19 +5493,19 @@
         <v>173</v>
       </c>
       <c r="B163" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C163" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D163" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E163" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="G163" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5486,19 +5513,19 @@
         <v>174</v>
       </c>
       <c r="B164" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C164" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D164" t="s">
-        <v>645</v>
+        <v>654</v>
       </c>
       <c r="E164" t="s">
-        <v>687</v>
+        <v>696</v>
       </c>
       <c r="G164" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5506,13 +5533,13 @@
         <v>175</v>
       </c>
       <c r="C165" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D165" t="s">
-        <v>636</v>
+        <v>645</v>
       </c>
       <c r="E165" t="s">
-        <v>688</v>
+        <v>697</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5520,19 +5547,19 @@
         <v>176</v>
       </c>
       <c r="B166" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C166" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D166" t="s">
-        <v>646</v>
+        <v>655</v>
       </c>
       <c r="E166" t="s">
-        <v>689</v>
+        <v>698</v>
       </c>
       <c r="G166" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5540,19 +5567,19 @@
         <v>177</v>
       </c>
       <c r="B167" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C167" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D167" t="s">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="E167" t="s">
-        <v>690</v>
+        <v>699</v>
       </c>
       <c r="G167" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5560,19 +5587,19 @@
         <v>178</v>
       </c>
       <c r="B168" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C168" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="D168" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E168" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="G168" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5580,19 +5607,19 @@
         <v>179</v>
       </c>
       <c r="B169" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C169" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="D169" t="s">
-        <v>648</v>
+        <v>657</v>
       </c>
       <c r="E169" t="s">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="G169" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5600,13 +5627,13 @@
         <v>180</v>
       </c>
       <c r="C170" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="D170" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="E170" t="s">
-        <v>693</v>
+        <v>702</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5614,13 +5641,13 @@
         <v>181</v>
       </c>
       <c r="C171" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="D171" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E171" t="s">
-        <v>694</v>
+        <v>703</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5628,13 +5655,13 @@
         <v>182</v>
       </c>
       <c r="C172" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="D172" t="s">
-        <v>636</v>
+        <v>645</v>
       </c>
       <c r="E172" t="s">
-        <v>695</v>
+        <v>704</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5642,16 +5669,16 @@
         <v>183</v>
       </c>
       <c r="B173" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C173" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="D173" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G173" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5659,19 +5686,19 @@
         <v>184</v>
       </c>
       <c r="B174" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C174" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="D174" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="F174" t="s">
-        <v>725</v>
+        <v>734</v>
       </c>
       <c r="G174" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5679,19 +5706,19 @@
         <v>185</v>
       </c>
       <c r="B175" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C175" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="D175" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="F175" t="s">
-        <v>726</v>
+        <v>735</v>
       </c>
       <c r="G175" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5699,10 +5726,10 @@
         <v>186</v>
       </c>
       <c r="C176" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="D176" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5710,10 +5737,10 @@
         <v>187</v>
       </c>
       <c r="C177" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="D177" t="s">
-        <v>650</v>
+        <v>659</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5721,10 +5748,10 @@
         <v>188</v>
       </c>
       <c r="C178" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="D178" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5732,22 +5759,22 @@
         <v>189</v>
       </c>
       <c r="B179" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C179" t="s">
-        <v>619</v>
+        <v>628</v>
       </c>
       <c r="D179" t="s">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="E179" t="s">
-        <v>696</v>
+        <v>705</v>
       </c>
       <c r="F179" t="s">
-        <v>727</v>
+        <v>736</v>
       </c>
       <c r="G179" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5755,10 +5782,10 @@
         <v>190</v>
       </c>
       <c r="C180" t="s">
-        <v>619</v>
+        <v>628</v>
       </c>
       <c r="D180" t="s">
-        <v>651</v>
+        <v>660</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5766,10 +5793,10 @@
         <v>191</v>
       </c>
       <c r="C181" t="s">
-        <v>619</v>
+        <v>628</v>
       </c>
       <c r="D181" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5777,19 +5804,19 @@
         <v>192</v>
       </c>
       <c r="B182" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C182" t="s">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="D182" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E182" t="s">
-        <v>697</v>
+        <v>706</v>
       </c>
       <c r="G182" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5797,19 +5824,19 @@
         <v>193</v>
       </c>
       <c r="B183" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C183" t="s">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="D183" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="F183" t="s">
-        <v>728</v>
+        <v>737</v>
       </c>
       <c r="G183" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5817,10 +5844,10 @@
         <v>194</v>
       </c>
       <c r="C184" t="s">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="D184" t="s">
-        <v>651</v>
+        <v>660</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5828,13 +5855,13 @@
         <v>195</v>
       </c>
       <c r="C185" t="s">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="D185" t="s">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="F185" t="s">
-        <v>729</v>
+        <v>738</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5842,13 +5869,13 @@
         <v>196</v>
       </c>
       <c r="C186" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="D186" t="s">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="E186" t="s">
-        <v>698</v>
+        <v>707</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5856,13 +5883,13 @@
         <v>197</v>
       </c>
       <c r="C187" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="D187" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E187" t="s">
-        <v>699</v>
+        <v>708</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5870,13 +5897,13 @@
         <v>198</v>
       </c>
       <c r="C188" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="D188" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E188" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5884,13 +5911,13 @@
         <v>199</v>
       </c>
       <c r="C189" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="D189" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E189" t="s">
-        <v>701</v>
+        <v>710</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5898,13 +5925,13 @@
         <v>200</v>
       </c>
       <c r="C190" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="D190" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E190" t="s">
-        <v>702</v>
+        <v>711</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5912,10 +5939,10 @@
         <v>201</v>
       </c>
       <c r="C191" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="D191" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -5923,10 +5950,10 @@
         <v>202</v>
       </c>
       <c r="C192" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="D192" t="s">
-        <v>654</v>
+        <v>663</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -5934,10 +5961,10 @@
         <v>203</v>
       </c>
       <c r="C193" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="D193" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -5945,16 +5972,16 @@
         <v>204</v>
       </c>
       <c r="B194" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C194" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="D194" t="s">
-        <v>633</v>
+        <v>642</v>
       </c>
       <c r="G194" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -5962,16 +5989,16 @@
         <v>205</v>
       </c>
       <c r="B195" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C195" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="D195" t="s">
-        <v>633</v>
+        <v>642</v>
       </c>
       <c r="G195" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -5979,19 +6006,19 @@
         <v>206</v>
       </c>
       <c r="B196" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C196" t="s">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="D196" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="F196" t="s">
-        <v>730</v>
+        <v>739</v>
       </c>
       <c r="G196" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -5999,22 +6026,22 @@
         <v>207</v>
       </c>
       <c r="B197" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C197" t="s">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="D197" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E197" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="F197" t="s">
-        <v>731</v>
+        <v>740</v>
       </c>
       <c r="G197" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6022,22 +6049,22 @@
         <v>208</v>
       </c>
       <c r="B198" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C198" t="s">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="D198" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E198" t="s">
-        <v>704</v>
+        <v>713</v>
       </c>
       <c r="F198" t="s">
-        <v>732</v>
+        <v>741</v>
       </c>
       <c r="G198" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6045,22 +6072,22 @@
         <v>209</v>
       </c>
       <c r="B199" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C199" t="s">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="D199" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E199" t="s">
-        <v>705</v>
+        <v>714</v>
       </c>
       <c r="F199" t="s">
-        <v>733</v>
+        <v>742</v>
       </c>
       <c r="G199" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6068,16 +6095,16 @@
         <v>210</v>
       </c>
       <c r="B200" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C200" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="D200" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G200" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6085,10 +6112,10 @@
         <v>211</v>
       </c>
       <c r="C201" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="D201" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6096,10 +6123,10 @@
         <v>212</v>
       </c>
       <c r="C202" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="D202" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6107,10 +6134,10 @@
         <v>213</v>
       </c>
       <c r="C203" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="D203" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6118,16 +6145,16 @@
         <v>214</v>
       </c>
       <c r="B204" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C204" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="D204" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G204" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6135,10 +6162,10 @@
         <v>215</v>
       </c>
       <c r="C205" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="D205" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6146,10 +6173,10 @@
         <v>216</v>
       </c>
       <c r="C206" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="D206" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6157,19 +6184,19 @@
         <v>217</v>
       </c>
       <c r="B207" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C207" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="D207" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E207" t="s">
-        <v>706</v>
+        <v>715</v>
       </c>
       <c r="G207" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6177,13 +6204,13 @@
         <v>218</v>
       </c>
       <c r="C208" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="D208" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E208" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6191,10 +6218,10 @@
         <v>219</v>
       </c>
       <c r="C209" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="D209" t="s">
-        <v>639</v>
+        <v>648</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6202,19 +6229,19 @@
         <v>220</v>
       </c>
       <c r="B210" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C210" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="D210" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E210" t="s">
-        <v>708</v>
+        <v>717</v>
       </c>
       <c r="G210" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6222,16 +6249,16 @@
         <v>221</v>
       </c>
       <c r="B211" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C211" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="D211" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G211" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6239,13 +6266,13 @@
         <v>222</v>
       </c>
       <c r="C212" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="D212" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E212" t="s">
-        <v>709</v>
+        <v>718</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6253,13 +6280,13 @@
         <v>223</v>
       </c>
       <c r="C213" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="D213" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="E213" t="s">
-        <v>710</v>
+        <v>719</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6267,16 +6294,16 @@
         <v>224</v>
       </c>
       <c r="B214" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C214" t="s">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="D214" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G214" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6284,16 +6311,16 @@
         <v>225</v>
       </c>
       <c r="B215" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C215" t="s">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="D215" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G215" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6301,13 +6328,13 @@
         <v>226</v>
       </c>
       <c r="C216" t="s">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="D216" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E216" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6315,19 +6342,19 @@
         <v>227</v>
       </c>
       <c r="B217" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C217" t="s">
-        <v>625</v>
+        <v>634</v>
       </c>
       <c r="D217" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E217" t="s">
-        <v>712</v>
+        <v>721</v>
       </c>
       <c r="G217" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6335,19 +6362,19 @@
         <v>228</v>
       </c>
       <c r="B218" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C218" t="s">
-        <v>625</v>
+        <v>634</v>
       </c>
       <c r="D218" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E218" t="s">
-        <v>712</v>
+        <v>721</v>
       </c>
       <c r="G218" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6355,19 +6382,19 @@
         <v>229</v>
       </c>
       <c r="B219" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C219" t="s">
-        <v>626</v>
+        <v>635</v>
       </c>
       <c r="D219" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E219" t="s">
-        <v>713</v>
+        <v>722</v>
       </c>
       <c r="G219" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6375,10 +6402,10 @@
         <v>230</v>
       </c>
       <c r="C220" t="s">
-        <v>626</v>
+        <v>635</v>
       </c>
       <c r="D220" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6386,16 +6413,16 @@
         <v>231</v>
       </c>
       <c r="B221" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C221" t="s">
-        <v>626</v>
+        <v>635</v>
       </c>
       <c r="D221" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G221" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6403,19 +6430,19 @@
         <v>232</v>
       </c>
       <c r="B222" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C222" t="s">
-        <v>627</v>
+        <v>636</v>
       </c>
       <c r="D222" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E222" t="s">
-        <v>714</v>
+        <v>723</v>
       </c>
       <c r="G222" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6423,16 +6450,16 @@
         <v>233</v>
       </c>
       <c r="B223" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C223" t="s">
-        <v>627</v>
+        <v>636</v>
       </c>
       <c r="D223" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G223" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6440,16 +6467,16 @@
         <v>234</v>
       </c>
       <c r="B224" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C224" t="s">
-        <v>627</v>
+        <v>636</v>
       </c>
       <c r="D224" t="s">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="G224" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6457,19 +6484,19 @@
         <v>235</v>
       </c>
       <c r="B225" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C225" t="s">
-        <v>627</v>
+        <v>636</v>
       </c>
       <c r="D225" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="F225" t="s">
-        <v>734</v>
+        <v>743</v>
       </c>
       <c r="G225" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6477,16 +6504,16 @@
         <v>236</v>
       </c>
       <c r="B226" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C226" t="s">
-        <v>627</v>
+        <v>636</v>
       </c>
       <c r="D226" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G226" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6494,10 +6521,10 @@
         <v>237</v>
       </c>
       <c r="C227" t="s">
-        <v>627</v>
+        <v>636</v>
       </c>
       <c r="D227" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6505,16 +6532,16 @@
         <v>238</v>
       </c>
       <c r="B228" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C228" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D228" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G228" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6522,16 +6549,16 @@
         <v>239</v>
       </c>
       <c r="B229" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C229" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D229" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G229" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6539,16 +6566,16 @@
         <v>240</v>
       </c>
       <c r="B230" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C230" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D230" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G230" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6556,16 +6583,16 @@
         <v>241</v>
       </c>
       <c r="B231" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C231" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D231" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G231" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6573,16 +6600,16 @@
         <v>242</v>
       </c>
       <c r="B232" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C232" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D232" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G232" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6590,16 +6617,16 @@
         <v>243</v>
       </c>
       <c r="B233" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C233" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D233" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G233" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6607,16 +6634,16 @@
         <v>244</v>
       </c>
       <c r="B234" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C234" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D234" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G234" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -6624,16 +6651,16 @@
         <v>245</v>
       </c>
       <c r="B235" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C235" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D235" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G235" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -6641,16 +6668,16 @@
         <v>246</v>
       </c>
       <c r="B236" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C236" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D236" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G236" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -6658,16 +6685,16 @@
         <v>247</v>
       </c>
       <c r="B237" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C237" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D237" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G237" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -6675,16 +6702,16 @@
         <v>248</v>
       </c>
       <c r="B238" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C238" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D238" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G238" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -6692,16 +6719,16 @@
         <v>249</v>
       </c>
       <c r="B239" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C239" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D239" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G239" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -6709,16 +6736,16 @@
         <v>250</v>
       </c>
       <c r="B240" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C240" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D240" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G240" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -6726,16 +6753,16 @@
         <v>251</v>
       </c>
       <c r="B241" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C241" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D241" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G241" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -6743,16 +6770,16 @@
         <v>252</v>
       </c>
       <c r="B242" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C242" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D242" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G242" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -6760,16 +6787,16 @@
         <v>253</v>
       </c>
       <c r="B243" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C243" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D243" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G243" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -6777,16 +6804,16 @@
         <v>254</v>
       </c>
       <c r="B244" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C244" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D244" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G244" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -6794,16 +6821,16 @@
         <v>255</v>
       </c>
       <c r="B245" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C245" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D245" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G245" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -6811,16 +6838,16 @@
         <v>256</v>
       </c>
       <c r="B246" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C246" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D246" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G246" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -6828,16 +6855,16 @@
         <v>257</v>
       </c>
       <c r="B247" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="C247" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D247" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G247" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -6845,16 +6872,16 @@
         <v>258</v>
       </c>
       <c r="B248" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C248" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D248" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G248" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -6862,16 +6889,16 @@
         <v>259</v>
       </c>
       <c r="B249" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C249" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="D249" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G249" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -6879,16 +6906,16 @@
         <v>260</v>
       </c>
       <c r="B250" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C250" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="D250" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G250" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -6896,16 +6923,16 @@
         <v>261</v>
       </c>
       <c r="B251" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="C251" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D251" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G251" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -6913,16 +6940,16 @@
         <v>262</v>
       </c>
       <c r="B252" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C252" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D252" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G252" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -6930,16 +6957,16 @@
         <v>263</v>
       </c>
       <c r="B253" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C253" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D253" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G253" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -6947,16 +6974,16 @@
         <v>264</v>
       </c>
       <c r="B254" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C254" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D254" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G254" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -6964,16 +6991,16 @@
         <v>265</v>
       </c>
       <c r="B255" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="C255" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D255" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G255" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -6981,16 +7008,16 @@
         <v>266</v>
       </c>
       <c r="B256" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C256" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D256" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G256" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -6998,16 +7025,16 @@
         <v>267</v>
       </c>
       <c r="B257" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="C257" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D257" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G257" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7015,16 +7042,16 @@
         <v>268</v>
       </c>
       <c r="B258" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C258" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D258" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G258" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7032,16 +7059,16 @@
         <v>269</v>
       </c>
       <c r="B259" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="C259" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D259" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G259" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7049,16 +7076,16 @@
         <v>270</v>
       </c>
       <c r="B260" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C260" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D260" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G260" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -7066,16 +7093,16 @@
         <v>271</v>
       </c>
       <c r="B261" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C261" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D261" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G261" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -7083,16 +7110,16 @@
         <v>272</v>
       </c>
       <c r="B262" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C262" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D262" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G262" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -7100,16 +7127,16 @@
         <v>273</v>
       </c>
       <c r="B263" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C263" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D263" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G263" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7117,16 +7144,16 @@
         <v>274</v>
       </c>
       <c r="B264" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C264" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D264" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G264" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -7134,16 +7161,16 @@
         <v>275</v>
       </c>
       <c r="B265" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C265" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D265" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="G265" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -7151,16 +7178,16 @@
         <v>276</v>
       </c>
       <c r="B266" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C266" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D266" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G266" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7168,16 +7195,16 @@
         <v>277</v>
       </c>
       <c r="B267" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C267" t="s">
-        <v>628</v>
+        <v>637</v>
       </c>
       <c r="D267" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G267" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7185,16 +7212,16 @@
         <v>278</v>
       </c>
       <c r="B268" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C268" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D268" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G268" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7202,16 +7229,16 @@
         <v>279</v>
       </c>
       <c r="B269" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C269" t="s">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="D269" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G269" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7219,16 +7246,16 @@
         <v>280</v>
       </c>
       <c r="B270" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C270" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D270" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G270" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7236,16 +7263,16 @@
         <v>281</v>
       </c>
       <c r="B271" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="C271" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D271" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G271" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -7253,16 +7280,16 @@
         <v>282</v>
       </c>
       <c r="B272" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C272" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D272" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G272" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7270,16 +7297,16 @@
         <v>283</v>
       </c>
       <c r="B273" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C273" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D273" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G273" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -7287,16 +7314,16 @@
         <v>284</v>
       </c>
       <c r="B274" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C274" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D274" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G274" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -7304,16 +7331,16 @@
         <v>285</v>
       </c>
       <c r="B275" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C275" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D275" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G275" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -7321,16 +7348,16 @@
         <v>286</v>
       </c>
       <c r="B276" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C276" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D276" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G276" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -7338,16 +7365,16 @@
         <v>287</v>
       </c>
       <c r="B277" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C277" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D277" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G277" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -7355,16 +7382,16 @@
         <v>288</v>
       </c>
       <c r="B278" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C278" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D278" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G278" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7372,16 +7399,16 @@
         <v>289</v>
       </c>
       <c r="B279" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="C279" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D279" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G279" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7389,16 +7416,16 @@
         <v>290</v>
       </c>
       <c r="B280" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C280" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D280" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="G280" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -7406,16 +7433,16 @@
         <v>291</v>
       </c>
       <c r="B281" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="C281" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D281" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="G281" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7423,16 +7450,16 @@
         <v>292</v>
       </c>
       <c r="B282" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="C282" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="D282" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="G282" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -7440,16 +7467,16 @@
         <v>293</v>
       </c>
       <c r="B283" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="C283" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D283" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="G283" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -7457,19 +7484,19 @@
         <v>294</v>
       </c>
       <c r="B284" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C284" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="D284" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="F284" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="G284" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -7477,16 +7504,16 @@
         <v>295</v>
       </c>
       <c r="B285" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="C285" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D285" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G285" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -7494,16 +7521,16 @@
         <v>296</v>
       </c>
       <c r="B286" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C286" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D286" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G286" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -7511,16 +7538,16 @@
         <v>297</v>
       </c>
       <c r="B287" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C287" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D287" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G287" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -7528,16 +7555,16 @@
         <v>298</v>
       </c>
       <c r="B288" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C288" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D288" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G288" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -7545,16 +7572,16 @@
         <v>299</v>
       </c>
       <c r="B289" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="C289" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D289" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G289" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -7562,16 +7589,16 @@
         <v>300</v>
       </c>
       <c r="B290" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C290" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D290" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G290" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -7579,16 +7606,16 @@
         <v>301</v>
       </c>
       <c r="B291" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C291" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D291" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G291" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -7596,16 +7623,16 @@
         <v>302</v>
       </c>
       <c r="B292" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C292" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D292" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G292" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -7613,16 +7640,16 @@
         <v>303</v>
       </c>
       <c r="B293" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C293" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="D293" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G293" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -7630,16 +7657,16 @@
         <v>304</v>
       </c>
       <c r="B294" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="C294" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D294" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G294" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -7647,16 +7674,16 @@
         <v>140</v>
       </c>
       <c r="B295" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C295" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D295" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="G295" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -7664,16 +7691,16 @@
         <v>305</v>
       </c>
       <c r="B296" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C296" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D296" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="G296" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="297" spans="1:7">
@@ -7681,16 +7708,16 @@
         <v>306</v>
       </c>
       <c r="B297" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="C297" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D297" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="G297" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="298" spans="1:7">
@@ -7698,16 +7725,16 @@
         <v>307</v>
       </c>
       <c r="B298" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C298" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D298" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="G298" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="299" spans="1:7">
@@ -7715,16 +7742,16 @@
         <v>308</v>
       </c>
       <c r="B299" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="C299" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D299" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="G299" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="300" spans="1:7">
@@ -7732,16 +7759,16 @@
         <v>309</v>
       </c>
       <c r="B300" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C300" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D300" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="G300" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="301" spans="1:7">
@@ -7749,16 +7776,16 @@
         <v>310</v>
       </c>
       <c r="B301" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="C301" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D301" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="G301" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="302" spans="1:7">
@@ -7766,16 +7793,16 @@
         <v>311</v>
       </c>
       <c r="B302" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C302" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D302" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="G302" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -7783,16 +7810,16 @@
         <v>312</v>
       </c>
       <c r="B303" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C303" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="D303" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="G303" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="304" spans="1:7">
@@ -7800,16 +7827,16 @@
         <v>313</v>
       </c>
       <c r="B304" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C304" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D304" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="G304" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="305" spans="1:7">
@@ -7817,16 +7844,16 @@
         <v>314</v>
       </c>
       <c r="B305" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="C305" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D305" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="G305" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="306" spans="1:7">
@@ -7834,16 +7861,16 @@
         <v>315</v>
       </c>
       <c r="B306" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C306" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D306" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="G306" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="307" spans="1:7">
@@ -7851,16 +7878,16 @@
         <v>316</v>
       </c>
       <c r="B307" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C307" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D307" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="G307" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="308" spans="1:7">
@@ -7868,16 +7895,16 @@
         <v>317</v>
       </c>
       <c r="B308" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C308" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D308" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="G308" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -7885,16 +7912,16 @@
         <v>318</v>
       </c>
       <c r="B309" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C309" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D309" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="G309" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="310" spans="1:7">
@@ -7902,16 +7929,16 @@
         <v>319</v>
       </c>
       <c r="B310" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C310" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D310" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="G310" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="311" spans="1:7">
@@ -7919,16 +7946,16 @@
         <v>320</v>
       </c>
       <c r="B311" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C311" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D311" t="s">
-        <v>645</v>
+        <v>654</v>
       </c>
       <c r="G311" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="312" spans="1:7">
@@ -7936,16 +7963,16 @@
         <v>321</v>
       </c>
       <c r="B312" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C312" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D312" t="s">
-        <v>651</v>
+        <v>660</v>
       </c>
       <c r="G312" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="313" spans="1:7">
@@ -7953,16 +7980,16 @@
         <v>322</v>
       </c>
       <c r="B313" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C313" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D313" t="s">
-        <v>654</v>
+        <v>663</v>
       </c>
       <c r="G313" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="314" spans="1:7">
@@ -7970,16 +7997,16 @@
         <v>323</v>
       </c>
       <c r="B314" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C314" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D314" t="s">
-        <v>658</v>
+        <v>667</v>
       </c>
       <c r="G314" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="315" spans="1:7">
@@ -7987,16 +8014,16 @@
         <v>324</v>
       </c>
       <c r="B315" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C315" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D315" t="s">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="G315" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="316" spans="1:7">
@@ -8004,16 +8031,16 @@
         <v>325</v>
       </c>
       <c r="B316" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C316" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="D316" t="s">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="G316" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="317" spans="1:7">
@@ -8021,16 +8048,16 @@
         <v>326</v>
       </c>
       <c r="B317" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C317" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D317" t="s">
-        <v>659</v>
+        <v>668</v>
       </c>
       <c r="G317" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="318" spans="1:7">
@@ -8038,16 +8065,16 @@
         <v>327</v>
       </c>
       <c r="B318" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C318" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D318" t="s">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="G318" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="319" spans="1:7">
@@ -8055,16 +8082,16 @@
         <v>328</v>
       </c>
       <c r="B319" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C319" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="D319" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="G319" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="320" spans="1:7">
@@ -8072,16 +8099,86 @@
         <v>329</v>
       </c>
       <c r="B320" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C320" t="s">
+        <v>618</v>
+      </c>
+      <c r="D320" t="s">
+        <v>664</v>
+      </c>
+      <c r="G320" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
+      <c r="A321" t="s">
+        <v>330</v>
+      </c>
+      <c r="B321" t="s">
         <v>609</v>
       </c>
-      <c r="D320" t="s">
-        <v>655</v>
-      </c>
-      <c r="G320" t="s">
-        <v>735</v>
+      <c r="C321" t="s">
+        <v>621</v>
+      </c>
+      <c r="D321" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
+      <c r="A322" t="s">
+        <v>300</v>
+      </c>
+      <c r="B322" t="s">
+        <v>610</v>
+      </c>
+      <c r="C322" t="s">
+        <v>621</v>
+      </c>
+      <c r="D322" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
+      <c r="A323" t="s">
+        <v>331</v>
+      </c>
+      <c r="B323" t="s">
+        <v>611</v>
+      </c>
+      <c r="C323" t="s">
+        <v>621</v>
+      </c>
+      <c r="D323" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
+      <c r="A324" t="s">
+        <v>332</v>
+      </c>
+      <c r="B324" t="s">
+        <v>612</v>
+      </c>
+      <c r="C324" t="s">
+        <v>621</v>
+      </c>
+      <c r="D324" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
+      <c r="A325" t="s">
+        <v>333</v>
+      </c>
+      <c r="B325" t="s">
+        <v>613</v>
+      </c>
+      <c r="C325" t="s">
+        <v>621</v>
+      </c>
+      <c r="D325" t="s">
+        <v>653</v>
       </c>
     </row>
   </sheetData>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1650" uniqueCount="745">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -8111,7 +8111,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="321" spans="1:4">
+    <row r="321" spans="1:7">
       <c r="A321" t="s">
         <v>330</v>
       </c>
@@ -8124,8 +8124,11 @@
       <c r="D321" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="322" spans="1:4">
+      <c r="G321" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7">
       <c r="A322" t="s">
         <v>300</v>
       </c>
@@ -8138,8 +8141,11 @@
       <c r="D322" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="323" spans="1:4">
+      <c r="G322" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7">
       <c r="A323" t="s">
         <v>331</v>
       </c>
@@ -8152,8 +8158,11 @@
       <c r="D323" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="324" spans="1:4">
+      <c r="G323" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7">
       <c r="A324" t="s">
         <v>332</v>
       </c>
@@ -8166,8 +8175,11 @@
       <c r="D324" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="325" spans="1:4">
+      <c r="G324" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7">
       <c r="A325" t="s">
         <v>333</v>
       </c>
@@ -8179,6 +8191,9 @@
       </c>
       <c r="D325" t="s">
         <v>653</v>
+      </c>
+      <c r="G325" t="s">
+        <v>744</v>
       </c>
     </row>
   </sheetData>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1650" uniqueCount="745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="749">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -1018,6 +1018,12 @@
     <t>Micklefield School</t>
   </si>
   <si>
+    <t>Barkly House Retirement Home</t>
+  </si>
+  <si>
+    <t>Rondebosch Boys High School</t>
+  </si>
+  <si>
     <t>info@ctsc.org.za</t>
   </si>
   <si>
@@ -1856,6 +1862,12 @@
   </si>
   <si>
     <t>admin@micklefield.co.za</t>
+  </si>
+  <si>
+    <t>info@cpoa.org.za</t>
+  </si>
+  <si>
+    <t>infoline@rondebosch.com</t>
   </si>
   <si>
     <t>Museums &amp; Heritage</t>
@@ -2593,7 +2605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L325"/>
+  <dimension ref="A1:L327"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2639,22 +2651,22 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C2" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D2" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E2" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="F2" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="G2" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2662,22 +2674,22 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C3" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D3" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E3" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="F3" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="G3" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2685,22 +2697,22 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C4" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D4" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E4" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="F4" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="G4" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2708,22 +2720,22 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C5" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D5" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E5" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="F5" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="G5" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2731,22 +2743,22 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C6" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D6" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E6" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="F6" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="G6" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2754,22 +2766,22 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C7" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D7" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E7" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="F7" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="G7" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2777,22 +2789,22 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C8" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D8" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E8" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="F8" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="G8" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2800,22 +2812,22 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C9" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D9" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E9" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="F9" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="G9" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2823,22 +2835,22 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C10" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="D10" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E10" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="F10" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="G10" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2846,22 +2858,22 @@
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C11" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="D11" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E11" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="F11" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="G11" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2869,22 +2881,22 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C12" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D12" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E12" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="F12" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="G12" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2892,22 +2904,22 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C13" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D13" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E13" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="F13" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="G13" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2915,22 +2927,22 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C14" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D14" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="E14" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="G14" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2938,22 +2950,22 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C15" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D15" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="E15" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="G15" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2961,16 +2973,16 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C16" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D16" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G16" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2978,16 +2990,16 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C17" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D17" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G17" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2995,16 +3007,16 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C18" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D18" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G18" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -3012,16 +3024,16 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C19" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D19" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G19" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -3029,16 +3041,16 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C20" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D20" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G20" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3046,16 +3058,16 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C21" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D21" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G21" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3063,16 +3075,16 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C22" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D22" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G22" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3080,16 +3092,16 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C23" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D23" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G23" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3097,16 +3109,16 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C24" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D24" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G24" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3114,16 +3126,16 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C25" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D25" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G25" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3131,16 +3143,16 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C26" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D26" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G26" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3148,16 +3160,16 @@
         <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C27" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D27" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G27" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -3165,16 +3177,16 @@
         <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C28" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D28" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G28" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3182,16 +3194,16 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C29" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D29" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G29" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -3199,16 +3211,16 @@
         <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C30" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D30" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G30" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3216,16 +3228,16 @@
         <v>41</v>
       </c>
       <c r="B31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C31" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D31" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G31" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3233,16 +3245,16 @@
         <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C32" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D32" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G32" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3250,16 +3262,16 @@
         <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C33" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D33" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G33" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -3267,16 +3279,16 @@
         <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C34" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D34" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G34" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -3284,16 +3296,16 @@
         <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C35" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D35" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G35" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3301,16 +3313,16 @@
         <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C36" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D36" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G36" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -3318,16 +3330,16 @@
         <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C37" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D37" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G37" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -3335,16 +3347,16 @@
         <v>48</v>
       </c>
       <c r="B38" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C38" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D38" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G38" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -3352,16 +3364,16 @@
         <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C39" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D39" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G39" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3369,16 +3381,16 @@
         <v>50</v>
       </c>
       <c r="B40" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C40" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D40" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G40" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -3386,16 +3398,16 @@
         <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C41" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D41" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G41" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3403,16 +3415,16 @@
         <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C42" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D42" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G42" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3420,16 +3432,16 @@
         <v>53</v>
       </c>
       <c r="B43" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C43" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D43" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G43" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3437,16 +3449,16 @@
         <v>54</v>
       </c>
       <c r="B44" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C44" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D44" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G44" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3454,16 +3466,16 @@
         <v>55</v>
       </c>
       <c r="B45" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C45" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D45" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G45" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3471,16 +3483,16 @@
         <v>56</v>
       </c>
       <c r="B46" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C46" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D46" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G46" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3488,16 +3500,16 @@
         <v>57</v>
       </c>
       <c r="B47" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C47" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D47" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G47" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3505,16 +3517,16 @@
         <v>58</v>
       </c>
       <c r="B48" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C48" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D48" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G48" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -3522,16 +3534,16 @@
         <v>59</v>
       </c>
       <c r="B49" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C49" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D49" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G49" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -3539,16 +3551,16 @@
         <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C50" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D50" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G50" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -3556,16 +3568,16 @@
         <v>61</v>
       </c>
       <c r="B51" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C51" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D51" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G51" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -3573,16 +3585,16 @@
         <v>62</v>
       </c>
       <c r="B52" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C52" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D52" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G52" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -3590,16 +3602,16 @@
         <v>63</v>
       </c>
       <c r="B53" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C53" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D53" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G53" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3607,16 +3619,16 @@
         <v>64</v>
       </c>
       <c r="B54" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C54" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D54" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G54" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -3624,16 +3636,16 @@
         <v>65</v>
       </c>
       <c r="B55" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C55" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D55" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G55" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3641,16 +3653,16 @@
         <v>66</v>
       </c>
       <c r="B56" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C56" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D56" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G56" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3658,16 +3670,16 @@
         <v>67</v>
       </c>
       <c r="B57" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C57" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D57" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G57" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3675,16 +3687,16 @@
         <v>68</v>
       </c>
       <c r="B58" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C58" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D58" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G58" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3692,16 +3704,16 @@
         <v>69</v>
       </c>
       <c r="B59" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C59" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D59" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G59" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3709,16 +3721,16 @@
         <v>70</v>
       </c>
       <c r="B60" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C60" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D60" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G60" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3726,16 +3738,16 @@
         <v>71</v>
       </c>
       <c r="B61" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C61" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D61" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G61" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3743,16 +3755,16 @@
         <v>72</v>
       </c>
       <c r="B62" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C62" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D62" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G62" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3760,16 +3772,16 @@
         <v>73</v>
       </c>
       <c r="B63" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C63" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D63" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G63" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3777,16 +3789,16 @@
         <v>74</v>
       </c>
       <c r="B64" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C64" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D64" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G64" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3794,16 +3806,16 @@
         <v>75</v>
       </c>
       <c r="B65" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C65" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D65" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G65" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3811,16 +3823,16 @@
         <v>76</v>
       </c>
       <c r="B66" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C66" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D66" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G66" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3828,16 +3840,16 @@
         <v>77</v>
       </c>
       <c r="B67" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C67" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D67" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G67" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3845,16 +3857,16 @@
         <v>78</v>
       </c>
       <c r="B68" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C68" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D68" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G68" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3862,16 +3874,16 @@
         <v>79</v>
       </c>
       <c r="B69" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C69" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D69" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G69" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3879,16 +3891,16 @@
         <v>80</v>
       </c>
       <c r="B70" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C70" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D70" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G70" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3896,16 +3908,16 @@
         <v>81</v>
       </c>
       <c r="B71" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C71" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D71" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G71" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3913,16 +3925,16 @@
         <v>82</v>
       </c>
       <c r="B72" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C72" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D72" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G72" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3930,16 +3942,16 @@
         <v>83</v>
       </c>
       <c r="B73" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C73" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D73" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G73" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3947,16 +3959,16 @@
         <v>84</v>
       </c>
       <c r="B74" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C74" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D74" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G74" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3964,16 +3976,16 @@
         <v>85</v>
       </c>
       <c r="B75" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C75" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D75" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G75" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3981,16 +3993,16 @@
         <v>86</v>
       </c>
       <c r="B76" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C76" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D76" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G76" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3998,16 +4010,16 @@
         <v>87</v>
       </c>
       <c r="B77" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C77" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D77" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G77" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -4015,16 +4027,16 @@
         <v>88</v>
       </c>
       <c r="B78" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C78" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D78" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G78" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -4032,16 +4044,16 @@
         <v>89</v>
       </c>
       <c r="B79" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C79" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D79" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G79" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -4049,16 +4061,16 @@
         <v>90</v>
       </c>
       <c r="B80" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C80" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D80" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G80" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -4066,16 +4078,16 @@
         <v>91</v>
       </c>
       <c r="B81" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C81" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D81" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G81" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -4083,16 +4095,16 @@
         <v>92</v>
       </c>
       <c r="B82" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C82" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D82" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G82" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -4100,16 +4112,16 @@
         <v>93</v>
       </c>
       <c r="B83" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C83" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D83" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G83" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -4117,16 +4129,16 @@
         <v>94</v>
       </c>
       <c r="B84" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C84" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D84" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G84" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -4134,16 +4146,16 @@
         <v>95</v>
       </c>
       <c r="B85" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C85" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D85" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G85" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4151,16 +4163,16 @@
         <v>96</v>
       </c>
       <c r="B86" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C86" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D86" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G86" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4168,16 +4180,16 @@
         <v>97</v>
       </c>
       <c r="B87" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C87" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D87" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G87" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4185,16 +4197,16 @@
         <v>98</v>
       </c>
       <c r="B88" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C88" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D88" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G88" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4202,16 +4214,16 @@
         <v>99</v>
       </c>
       <c r="B89" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C89" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D89" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G89" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4219,16 +4231,16 @@
         <v>100</v>
       </c>
       <c r="B90" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C90" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D90" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G90" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4236,16 +4248,16 @@
         <v>101</v>
       </c>
       <c r="B91" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C91" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D91" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G91" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4253,16 +4265,16 @@
         <v>102</v>
       </c>
       <c r="B92" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C92" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D92" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G92" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -4270,16 +4282,16 @@
         <v>103</v>
       </c>
       <c r="B93" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C93" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D93" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G93" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -4287,16 +4299,16 @@
         <v>104</v>
       </c>
       <c r="B94" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C94" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D94" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G94" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -4304,16 +4316,16 @@
         <v>105</v>
       </c>
       <c r="B95" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C95" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D95" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G95" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -4321,16 +4333,16 @@
         <v>106</v>
       </c>
       <c r="B96" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C96" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D96" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G96" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4338,16 +4350,16 @@
         <v>107</v>
       </c>
       <c r="B97" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C97" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D97" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G97" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4355,16 +4367,16 @@
         <v>108</v>
       </c>
       <c r="B98" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C98" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D98" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G98" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4372,16 +4384,16 @@
         <v>109</v>
       </c>
       <c r="B99" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C99" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D99" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G99" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4389,16 +4401,16 @@
         <v>110</v>
       </c>
       <c r="B100" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C100" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D100" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G100" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4406,16 +4418,16 @@
         <v>111</v>
       </c>
       <c r="B101" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C101" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D101" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G101" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4423,16 +4435,16 @@
         <v>112</v>
       </c>
       <c r="B102" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C102" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D102" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G102" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4440,16 +4452,16 @@
         <v>113</v>
       </c>
       <c r="B103" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C103" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D103" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G103" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4457,16 +4469,16 @@
         <v>114</v>
       </c>
       <c r="B104" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C104" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D104" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G104" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4474,16 +4486,16 @@
         <v>115</v>
       </c>
       <c r="B105" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C105" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D105" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G105" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4491,16 +4503,16 @@
         <v>116</v>
       </c>
       <c r="B106" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C106" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D106" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G106" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4508,16 +4520,16 @@
         <v>117</v>
       </c>
       <c r="B107" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C107" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D107" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G107" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4525,16 +4537,16 @@
         <v>118</v>
       </c>
       <c r="B108" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C108" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D108" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G108" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4542,16 +4554,16 @@
         <v>119</v>
       </c>
       <c r="B109" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C109" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D109" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G109" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4559,16 +4571,16 @@
         <v>120</v>
       </c>
       <c r="B110" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C110" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D110" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G110" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4576,16 +4588,16 @@
         <v>121</v>
       </c>
       <c r="B111" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C111" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D111" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G111" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4593,16 +4605,16 @@
         <v>122</v>
       </c>
       <c r="B112" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C112" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D112" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G112" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4610,16 +4622,16 @@
         <v>123</v>
       </c>
       <c r="B113" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C113" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D113" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G113" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4627,16 +4639,16 @@
         <v>124</v>
       </c>
       <c r="B114" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C114" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D114" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G114" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4644,16 +4656,16 @@
         <v>125</v>
       </c>
       <c r="B115" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C115" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D115" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G115" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4661,16 +4673,16 @@
         <v>126</v>
       </c>
       <c r="B116" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C116" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D116" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G116" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4678,16 +4690,16 @@
         <v>127</v>
       </c>
       <c r="B117" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C117" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D117" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G117" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4695,16 +4707,16 @@
         <v>128</v>
       </c>
       <c r="B118" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C118" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D118" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G118" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4712,22 +4724,22 @@
         <v>129</v>
       </c>
       <c r="B119" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C119" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D119" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E119" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="F119" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="G119" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4735,19 +4747,19 @@
         <v>130</v>
       </c>
       <c r="B120" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C120" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D120" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="E120" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="G120" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4755,16 +4767,16 @@
         <v>131</v>
       </c>
       <c r="B121" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C121" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D121" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G121" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4772,16 +4784,16 @@
         <v>132</v>
       </c>
       <c r="B122" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C122" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D122" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="G122" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4789,22 +4801,22 @@
         <v>133</v>
       </c>
       <c r="B123" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C123" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D123" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E123" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="F123" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G123" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4812,16 +4824,16 @@
         <v>134</v>
       </c>
       <c r="B124" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C124" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D124" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G124" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4829,16 +4841,16 @@
         <v>135</v>
       </c>
       <c r="B125" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C125" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D125" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G125" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4846,16 +4858,16 @@
         <v>136</v>
       </c>
       <c r="B126" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C126" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D126" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G126" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4863,16 +4875,16 @@
         <v>137</v>
       </c>
       <c r="B127" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C127" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D127" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G127" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4880,19 +4892,19 @@
         <v>138</v>
       </c>
       <c r="B128" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C128" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D128" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E128" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="G128" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4900,22 +4912,22 @@
         <v>139</v>
       </c>
       <c r="B129" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C129" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D129" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E129" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="F129" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="G129" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4923,16 +4935,16 @@
         <v>140</v>
       </c>
       <c r="B130" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C130" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D130" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G130" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4940,13 +4952,13 @@
         <v>141</v>
       </c>
       <c r="C131" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D131" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="E131" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4954,19 +4966,19 @@
         <v>142</v>
       </c>
       <c r="B132" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C132" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D132" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="E132" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="G132" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4974,19 +4986,19 @@
         <v>143</v>
       </c>
       <c r="B133" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C133" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D133" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="E133" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="G133" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4994,10 +5006,10 @@
         <v>144</v>
       </c>
       <c r="C134" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D134" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -5005,10 +5017,10 @@
         <v>145</v>
       </c>
       <c r="C135" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D135" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -5016,16 +5028,16 @@
         <v>146</v>
       </c>
       <c r="B136" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C136" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D136" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G136" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -5033,16 +5045,16 @@
         <v>147</v>
       </c>
       <c r="B137" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C137" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D137" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="G137" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -5050,10 +5062,10 @@
         <v>148</v>
       </c>
       <c r="C138" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D138" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -5061,10 +5073,10 @@
         <v>149</v>
       </c>
       <c r="C139" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D139" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -5072,10 +5084,10 @@
         <v>150</v>
       </c>
       <c r="C140" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D140" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -5083,16 +5095,16 @@
         <v>151</v>
       </c>
       <c r="B141" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C141" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D141" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G141" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -5100,22 +5112,22 @@
         <v>152</v>
       </c>
       <c r="B142" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C142" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D142" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E142" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="F142" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="G142" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -5123,16 +5135,16 @@
         <v>153</v>
       </c>
       <c r="B143" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C143" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D143" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="G143" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -5140,13 +5152,13 @@
         <v>154</v>
       </c>
       <c r="C144" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D144" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="E144" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -5154,10 +5166,10 @@
         <v>155</v>
       </c>
       <c r="C145" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D145" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -5165,19 +5177,19 @@
         <v>156</v>
       </c>
       <c r="B146" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C146" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D146" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="F146" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="G146" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -5185,22 +5197,22 @@
         <v>157</v>
       </c>
       <c r="B147" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C147" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D147" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E147" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="F147" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="G147" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5208,19 +5220,19 @@
         <v>158</v>
       </c>
       <c r="B148" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C148" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D148" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E148" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="G148" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5228,19 +5240,19 @@
         <v>159</v>
       </c>
       <c r="B149" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C149" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D149" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E149" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="G149" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5248,19 +5260,19 @@
         <v>160</v>
       </c>
       <c r="B150" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C150" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D150" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E150" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="G150" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5268,19 +5280,19 @@
         <v>161</v>
       </c>
       <c r="B151" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C151" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D151" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E151" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="G151" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5288,19 +5300,19 @@
         <v>162</v>
       </c>
       <c r="B152" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C152" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D152" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E152" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="G152" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5308,10 +5320,10 @@
         <v>163</v>
       </c>
       <c r="C153" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D153" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5319,19 +5331,19 @@
         <v>164</v>
       </c>
       <c r="B154" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C154" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D154" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E154" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="G154" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5339,16 +5351,16 @@
         <v>165</v>
       </c>
       <c r="B155" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C155" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D155" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G155" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5356,16 +5368,16 @@
         <v>166</v>
       </c>
       <c r="B156" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C156" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D156" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G156" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5373,22 +5385,22 @@
         <v>167</v>
       </c>
       <c r="B157" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C157" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D157" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="E157" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="F157" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="G157" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5396,19 +5408,19 @@
         <v>168</v>
       </c>
       <c r="B158" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C158" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D158" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E158" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G158" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5416,19 +5428,19 @@
         <v>169</v>
       </c>
       <c r="B159" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C159" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D159" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E159" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="G159" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5436,19 +5448,19 @@
         <v>170</v>
       </c>
       <c r="B160" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C160" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D160" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E160" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="G160" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5456,19 +5468,19 @@
         <v>171</v>
       </c>
       <c r="B161" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C161" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D161" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="E161" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="G161" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5476,16 +5488,16 @@
         <v>172</v>
       </c>
       <c r="B162" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C162" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D162" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G162" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5493,19 +5505,19 @@
         <v>173</v>
       </c>
       <c r="B163" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C163" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D163" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E163" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="G163" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5513,19 +5525,19 @@
         <v>174</v>
       </c>
       <c r="B164" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C164" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D164" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="E164" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="G164" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5533,13 +5545,13 @@
         <v>175</v>
       </c>
       <c r="C165" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D165" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="E165" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5547,19 +5559,19 @@
         <v>176</v>
       </c>
       <c r="B166" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C166" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D166" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="E166" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="G166" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5567,19 +5579,19 @@
         <v>177</v>
       </c>
       <c r="B167" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C167" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D167" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="E167" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="G167" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5587,19 +5599,19 @@
         <v>178</v>
       </c>
       <c r="B168" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C168" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D168" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E168" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="G168" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5607,19 +5619,19 @@
         <v>179</v>
       </c>
       <c r="B169" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C169" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D169" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="E169" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="G169" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5627,13 +5639,13 @@
         <v>180</v>
       </c>
       <c r="C170" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D170" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="E170" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5641,13 +5653,13 @@
         <v>181</v>
       </c>
       <c r="C171" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D171" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E171" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5655,13 +5667,13 @@
         <v>182</v>
       </c>
       <c r="C172" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D172" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="E172" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5669,16 +5681,16 @@
         <v>183</v>
       </c>
       <c r="B173" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C173" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D173" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G173" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5686,19 +5698,19 @@
         <v>184</v>
       </c>
       <c r="B174" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C174" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D174" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="F174" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="G174" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5706,19 +5718,19 @@
         <v>185</v>
       </c>
       <c r="B175" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C175" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D175" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="F175" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="G175" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5726,10 +5738,10 @@
         <v>186</v>
       </c>
       <c r="C176" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D176" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5737,10 +5749,10 @@
         <v>187</v>
       </c>
       <c r="C177" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D177" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5748,10 +5760,10 @@
         <v>188</v>
       </c>
       <c r="C178" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D178" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5759,22 +5771,22 @@
         <v>189</v>
       </c>
       <c r="B179" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C179" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D179" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="E179" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="F179" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="G179" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5782,10 +5794,10 @@
         <v>190</v>
       </c>
       <c r="C180" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D180" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5793,10 +5805,10 @@
         <v>191</v>
       </c>
       <c r="C181" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D181" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5804,19 +5816,19 @@
         <v>192</v>
       </c>
       <c r="B182" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C182" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="D182" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E182" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="G182" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5824,19 +5836,19 @@
         <v>193</v>
       </c>
       <c r="B183" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C183" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="D183" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="F183" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="G183" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5844,10 +5856,10 @@
         <v>194</v>
       </c>
       <c r="C184" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="D184" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5855,13 +5867,13 @@
         <v>195</v>
       </c>
       <c r="C185" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="D185" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="F185" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5869,13 +5881,13 @@
         <v>196</v>
       </c>
       <c r="C186" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D186" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="E186" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5883,13 +5895,13 @@
         <v>197</v>
       </c>
       <c r="C187" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D187" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E187" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5897,13 +5909,13 @@
         <v>198</v>
       </c>
       <c r="C188" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D188" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E188" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5911,13 +5923,13 @@
         <v>199</v>
       </c>
       <c r="C189" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D189" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E189" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5925,13 +5937,13 @@
         <v>200</v>
       </c>
       <c r="C190" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D190" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E190" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5939,10 +5951,10 @@
         <v>201</v>
       </c>
       <c r="C191" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D191" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -5950,10 +5962,10 @@
         <v>202</v>
       </c>
       <c r="C192" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D192" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -5961,10 +5973,10 @@
         <v>203</v>
       </c>
       <c r="C193" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D193" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -5972,16 +5984,16 @@
         <v>204</v>
       </c>
       <c r="B194" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C194" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D194" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="G194" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -5989,16 +6001,16 @@
         <v>205</v>
       </c>
       <c r="B195" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C195" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D195" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="G195" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6006,19 +6018,19 @@
         <v>206</v>
       </c>
       <c r="B196" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C196" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D196" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="F196" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="G196" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6026,22 +6038,22 @@
         <v>207</v>
       </c>
       <c r="B197" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C197" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D197" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E197" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="F197" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="G197" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6049,22 +6061,22 @@
         <v>208</v>
       </c>
       <c r="B198" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C198" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D198" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E198" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F198" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="G198" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6072,22 +6084,22 @@
         <v>209</v>
       </c>
       <c r="B199" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C199" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D199" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E199" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="F199" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="G199" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6095,16 +6107,16 @@
         <v>210</v>
       </c>
       <c r="B200" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C200" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="D200" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G200" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6112,10 +6124,10 @@
         <v>211</v>
       </c>
       <c r="C201" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="D201" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6123,10 +6135,10 @@
         <v>212</v>
       </c>
       <c r="C202" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="D202" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6134,10 +6146,10 @@
         <v>213</v>
       </c>
       <c r="C203" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="D203" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6145,16 +6157,16 @@
         <v>214</v>
       </c>
       <c r="B204" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C204" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D204" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G204" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6162,10 +6174,10 @@
         <v>215</v>
       </c>
       <c r="C205" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D205" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6173,10 +6185,10 @@
         <v>216</v>
       </c>
       <c r="C206" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D206" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6184,19 +6196,19 @@
         <v>217</v>
       </c>
       <c r="B207" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C207" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D207" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E207" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="G207" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6204,13 +6216,13 @@
         <v>218</v>
       </c>
       <c r="C208" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D208" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E208" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6218,10 +6230,10 @@
         <v>219</v>
       </c>
       <c r="C209" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D209" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6229,19 +6241,19 @@
         <v>220</v>
       </c>
       <c r="B210" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C210" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="D210" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E210" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="G210" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6249,16 +6261,16 @@
         <v>221</v>
       </c>
       <c r="B211" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C211" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="D211" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G211" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6266,13 +6278,13 @@
         <v>222</v>
       </c>
       <c r="C212" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="D212" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E212" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6280,13 +6292,13 @@
         <v>223</v>
       </c>
       <c r="C213" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="D213" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="E213" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6294,16 +6306,16 @@
         <v>224</v>
       </c>
       <c r="B214" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C214" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="D214" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G214" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6311,16 +6323,16 @@
         <v>225</v>
       </c>
       <c r="B215" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C215" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="D215" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G215" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6328,13 +6340,13 @@
         <v>226</v>
       </c>
       <c r="C216" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="D216" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E216" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6342,19 +6354,19 @@
         <v>227</v>
       </c>
       <c r="B217" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C217" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D217" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E217" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="G217" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6362,19 +6374,19 @@
         <v>228</v>
       </c>
       <c r="B218" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C218" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D218" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E218" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="G218" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6382,19 +6394,19 @@
         <v>229</v>
       </c>
       <c r="B219" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C219" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="D219" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E219" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="G219" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6402,10 +6414,10 @@
         <v>230</v>
       </c>
       <c r="C220" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="D220" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6413,16 +6425,16 @@
         <v>231</v>
       </c>
       <c r="B221" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C221" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="D221" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G221" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6430,19 +6442,19 @@
         <v>232</v>
       </c>
       <c r="B222" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C222" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D222" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E222" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="G222" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6450,16 +6462,16 @@
         <v>233</v>
       </c>
       <c r="B223" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C223" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D223" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G223" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6467,16 +6479,16 @@
         <v>234</v>
       </c>
       <c r="B224" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C224" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D224" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="G224" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6484,19 +6496,19 @@
         <v>235</v>
       </c>
       <c r="B225" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C225" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D225" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="F225" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="G225" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6504,16 +6516,16 @@
         <v>236</v>
       </c>
       <c r="B226" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C226" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D226" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G226" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6521,10 +6533,10 @@
         <v>237</v>
       </c>
       <c r="C227" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D227" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6532,16 +6544,16 @@
         <v>238</v>
       </c>
       <c r="B228" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C228" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D228" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G228" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6549,16 +6561,16 @@
         <v>239</v>
       </c>
       <c r="B229" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C229" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D229" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G229" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6566,16 +6578,16 @@
         <v>240</v>
       </c>
       <c r="B230" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C230" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D230" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G230" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6583,16 +6595,16 @@
         <v>241</v>
       </c>
       <c r="B231" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C231" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D231" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G231" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6600,16 +6612,16 @@
         <v>242</v>
       </c>
       <c r="B232" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C232" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D232" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G232" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6617,16 +6629,16 @@
         <v>243</v>
       </c>
       <c r="B233" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C233" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D233" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G233" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6634,16 +6646,16 @@
         <v>244</v>
       </c>
       <c r="B234" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C234" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D234" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G234" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -6651,16 +6663,16 @@
         <v>245</v>
       </c>
       <c r="B235" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C235" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D235" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G235" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -6668,16 +6680,16 @@
         <v>246</v>
       </c>
       <c r="B236" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C236" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D236" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G236" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -6685,16 +6697,16 @@
         <v>247</v>
       </c>
       <c r="B237" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C237" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D237" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G237" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -6702,16 +6714,16 @@
         <v>248</v>
       </c>
       <c r="B238" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C238" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D238" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G238" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -6719,16 +6731,16 @@
         <v>249</v>
       </c>
       <c r="B239" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C239" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D239" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G239" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -6736,16 +6748,16 @@
         <v>250</v>
       </c>
       <c r="B240" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C240" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D240" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G240" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -6753,16 +6765,16 @@
         <v>251</v>
       </c>
       <c r="B241" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C241" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D241" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G241" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -6770,16 +6782,16 @@
         <v>252</v>
       </c>
       <c r="B242" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C242" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D242" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G242" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -6787,16 +6799,16 @@
         <v>253</v>
       </c>
       <c r="B243" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C243" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D243" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G243" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -6804,16 +6816,16 @@
         <v>254</v>
       </c>
       <c r="B244" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C244" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D244" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G244" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -6821,16 +6833,16 @@
         <v>255</v>
       </c>
       <c r="B245" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C245" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D245" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G245" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -6838,16 +6850,16 @@
         <v>256</v>
       </c>
       <c r="B246" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C246" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D246" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G246" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -6855,16 +6867,16 @@
         <v>257</v>
       </c>
       <c r="B247" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C247" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D247" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G247" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -6872,16 +6884,16 @@
         <v>258</v>
       </c>
       <c r="B248" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C248" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D248" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G248" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -6889,16 +6901,16 @@
         <v>259</v>
       </c>
       <c r="B249" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C249" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D249" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G249" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -6906,16 +6918,16 @@
         <v>260</v>
       </c>
       <c r="B250" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C250" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D250" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G250" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -6923,16 +6935,16 @@
         <v>261</v>
       </c>
       <c r="B251" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C251" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D251" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G251" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -6940,16 +6952,16 @@
         <v>262</v>
       </c>
       <c r="B252" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C252" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D252" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G252" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -6957,16 +6969,16 @@
         <v>263</v>
       </c>
       <c r="B253" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C253" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D253" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G253" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -6974,16 +6986,16 @@
         <v>264</v>
       </c>
       <c r="B254" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C254" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D254" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G254" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -6991,16 +7003,16 @@
         <v>265</v>
       </c>
       <c r="B255" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C255" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D255" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G255" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7008,16 +7020,16 @@
         <v>266</v>
       </c>
       <c r="B256" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C256" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D256" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G256" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7025,16 +7037,16 @@
         <v>267</v>
       </c>
       <c r="B257" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C257" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D257" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G257" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7042,16 +7054,16 @@
         <v>268</v>
       </c>
       <c r="B258" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C258" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D258" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G258" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7059,16 +7071,16 @@
         <v>269</v>
       </c>
       <c r="B259" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C259" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D259" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G259" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7076,16 +7088,16 @@
         <v>270</v>
       </c>
       <c r="B260" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C260" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D260" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G260" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -7093,16 +7105,16 @@
         <v>271</v>
       </c>
       <c r="B261" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C261" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D261" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G261" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -7110,16 +7122,16 @@
         <v>272</v>
       </c>
       <c r="B262" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C262" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D262" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G262" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -7127,16 +7139,16 @@
         <v>273</v>
       </c>
       <c r="B263" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C263" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D263" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G263" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7144,16 +7156,16 @@
         <v>274</v>
       </c>
       <c r="B264" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C264" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D264" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G264" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -7161,16 +7173,16 @@
         <v>275</v>
       </c>
       <c r="B265" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C265" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D265" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G265" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -7178,16 +7190,16 @@
         <v>276</v>
       </c>
       <c r="B266" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C266" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D266" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G266" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7195,16 +7207,16 @@
         <v>277</v>
       </c>
       <c r="B267" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C267" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D267" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G267" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7212,16 +7224,16 @@
         <v>278</v>
       </c>
       <c r="B268" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C268" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D268" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G268" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7229,16 +7241,16 @@
         <v>279</v>
       </c>
       <c r="B269" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C269" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="D269" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G269" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7246,16 +7258,16 @@
         <v>280</v>
       </c>
       <c r="B270" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C270" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D270" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G270" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7263,16 +7275,16 @@
         <v>281</v>
       </c>
       <c r="B271" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C271" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D271" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G271" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -7280,16 +7292,16 @@
         <v>282</v>
       </c>
       <c r="B272" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C272" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D272" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G272" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7297,16 +7309,16 @@
         <v>283</v>
       </c>
       <c r="B273" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C273" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D273" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G273" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -7314,16 +7326,16 @@
         <v>284</v>
       </c>
       <c r="B274" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C274" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D274" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G274" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -7331,16 +7343,16 @@
         <v>285</v>
       </c>
       <c r="B275" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C275" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D275" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G275" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -7348,16 +7360,16 @@
         <v>286</v>
       </c>
       <c r="B276" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C276" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D276" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G276" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -7365,16 +7377,16 @@
         <v>287</v>
       </c>
       <c r="B277" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C277" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D277" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G277" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -7382,16 +7394,16 @@
         <v>288</v>
       </c>
       <c r="B278" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C278" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D278" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G278" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7399,16 +7411,16 @@
         <v>289</v>
       </c>
       <c r="B279" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C279" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D279" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G279" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7416,16 +7428,16 @@
         <v>290</v>
       </c>
       <c r="B280" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C280" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D280" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G280" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -7433,16 +7445,16 @@
         <v>291</v>
       </c>
       <c r="B281" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C281" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D281" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="G281" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7450,16 +7462,16 @@
         <v>292</v>
       </c>
       <c r="B282" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C282" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D282" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G282" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -7467,16 +7479,16 @@
         <v>293</v>
       </c>
       <c r="B283" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C283" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D283" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G283" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -7484,19 +7496,19 @@
         <v>294</v>
       </c>
       <c r="B284" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C284" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D284" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="F284" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="G284" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -7504,16 +7516,16 @@
         <v>295</v>
       </c>
       <c r="B285" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C285" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D285" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G285" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -7521,16 +7533,16 @@
         <v>296</v>
       </c>
       <c r="B286" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C286" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D286" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G286" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -7538,16 +7550,16 @@
         <v>297</v>
       </c>
       <c r="B287" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C287" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D287" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G287" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -7555,16 +7567,16 @@
         <v>298</v>
       </c>
       <c r="B288" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C288" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D288" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G288" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -7572,16 +7584,16 @@
         <v>299</v>
       </c>
       <c r="B289" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C289" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D289" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G289" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -7589,16 +7601,16 @@
         <v>300</v>
       </c>
       <c r="B290" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C290" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D290" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G290" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -7606,16 +7618,16 @@
         <v>301</v>
       </c>
       <c r="B291" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C291" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D291" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G291" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -7623,16 +7635,16 @@
         <v>302</v>
       </c>
       <c r="B292" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C292" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D292" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G292" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -7640,16 +7652,16 @@
         <v>303</v>
       </c>
       <c r="B293" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C293" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D293" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G293" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -7657,16 +7669,16 @@
         <v>304</v>
       </c>
       <c r="B294" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C294" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D294" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G294" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -7674,16 +7686,16 @@
         <v>140</v>
       </c>
       <c r="B295" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C295" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D295" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G295" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -7691,16 +7703,16 @@
         <v>305</v>
       </c>
       <c r="B296" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C296" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D296" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G296" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="297" spans="1:7">
@@ -7708,16 +7720,16 @@
         <v>306</v>
       </c>
       <c r="B297" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C297" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D297" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G297" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="298" spans="1:7">
@@ -7725,16 +7737,16 @@
         <v>307</v>
       </c>
       <c r="B298" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C298" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D298" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G298" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="299" spans="1:7">
@@ -7742,16 +7754,16 @@
         <v>308</v>
       </c>
       <c r="B299" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C299" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D299" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G299" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="300" spans="1:7">
@@ -7759,16 +7771,16 @@
         <v>309</v>
       </c>
       <c r="B300" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C300" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D300" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G300" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="301" spans="1:7">
@@ -7776,16 +7788,16 @@
         <v>310</v>
       </c>
       <c r="B301" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C301" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D301" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G301" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="302" spans="1:7">
@@ -7793,16 +7805,16 @@
         <v>311</v>
       </c>
       <c r="B302" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C302" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D302" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G302" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -7810,16 +7822,16 @@
         <v>312</v>
       </c>
       <c r="B303" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C303" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D303" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G303" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="304" spans="1:7">
@@ -7827,16 +7839,16 @@
         <v>313</v>
       </c>
       <c r="B304" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C304" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D304" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G304" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="305" spans="1:7">
@@ -7844,16 +7856,16 @@
         <v>314</v>
       </c>
       <c r="B305" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C305" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D305" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G305" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="306" spans="1:7">
@@ -7861,16 +7873,16 @@
         <v>315</v>
       </c>
       <c r="B306" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C306" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D306" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G306" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="307" spans="1:7">
@@ -7878,16 +7890,16 @@
         <v>316</v>
       </c>
       <c r="B307" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C307" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D307" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G307" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="308" spans="1:7">
@@ -7895,16 +7907,16 @@
         <v>317</v>
       </c>
       <c r="B308" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C308" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D308" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="G308" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -7912,16 +7924,16 @@
         <v>318</v>
       </c>
       <c r="B309" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C309" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D309" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="G309" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="310" spans="1:7">
@@ -7929,16 +7941,16 @@
         <v>319</v>
       </c>
       <c r="B310" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C310" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D310" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="G310" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="311" spans="1:7">
@@ -7946,16 +7958,16 @@
         <v>320</v>
       </c>
       <c r="B311" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C311" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D311" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="G311" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="312" spans="1:7">
@@ -7963,16 +7975,16 @@
         <v>321</v>
       </c>
       <c r="B312" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C312" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D312" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="G312" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="313" spans="1:7">
@@ -7980,16 +7992,16 @@
         <v>322</v>
       </c>
       <c r="B313" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C313" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D313" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="G313" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="314" spans="1:7">
@@ -7997,16 +8009,16 @@
         <v>323</v>
       </c>
       <c r="B314" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C314" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D314" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="G314" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="315" spans="1:7">
@@ -8014,16 +8026,16 @@
         <v>324</v>
       </c>
       <c r="B315" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C315" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D315" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="G315" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="316" spans="1:7">
@@ -8031,16 +8043,16 @@
         <v>325</v>
       </c>
       <c r="B316" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C316" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D316" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="G316" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="317" spans="1:7">
@@ -8048,16 +8060,16 @@
         <v>326</v>
       </c>
       <c r="B317" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C317" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D317" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G317" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="318" spans="1:7">
@@ -8065,16 +8077,16 @@
         <v>327</v>
       </c>
       <c r="B318" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C318" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D318" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="G318" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="319" spans="1:7">
@@ -8082,16 +8094,16 @@
         <v>328</v>
       </c>
       <c r="B319" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C319" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D319" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G319" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="320" spans="1:7">
@@ -8099,16 +8111,16 @@
         <v>329</v>
       </c>
       <c r="B320" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C320" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D320" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G320" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="321" spans="1:7">
@@ -8116,16 +8128,16 @@
         <v>330</v>
       </c>
       <c r="B321" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C321" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D321" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G321" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="322" spans="1:7">
@@ -8133,16 +8145,16 @@
         <v>300</v>
       </c>
       <c r="B322" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C322" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D322" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G322" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="323" spans="1:7">
@@ -8150,16 +8162,16 @@
         <v>331</v>
       </c>
       <c r="B323" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C323" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D323" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G323" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="324" spans="1:7">
@@ -8167,16 +8179,16 @@
         <v>332</v>
       </c>
       <c r="B324" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C324" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D324" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G324" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="325" spans="1:7">
@@ -8184,16 +8196,50 @@
         <v>333</v>
       </c>
       <c r="B325" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C325" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D325" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G325" t="s">
-        <v>744</v>
+        <v>748</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7">
+      <c r="A326" t="s">
+        <v>334</v>
+      </c>
+      <c r="B326" t="s">
+        <v>616</v>
+      </c>
+      <c r="C326" t="s">
+        <v>625</v>
+      </c>
+      <c r="D326" t="s">
+        <v>657</v>
+      </c>
+      <c r="G326" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7">
+      <c r="A327" t="s">
+        <v>335</v>
+      </c>
+      <c r="B327" t="s">
+        <v>617</v>
+      </c>
+      <c r="C327" t="s">
+        <v>625</v>
+      </c>
+      <c r="D327" t="s">
+        <v>657</v>
+      </c>
+      <c r="G327" t="s">
+        <v>748</v>
       </c>
     </row>
   </sheetData>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="753">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -1024,6 +1024,12 @@
     <t>Rondebosch Boys High School</t>
   </si>
   <si>
+    <t>The Homestead Mowbray</t>
+  </si>
+  <si>
+    <t>Western Province Preparatory School</t>
+  </si>
+  <si>
     <t>info@ctsc.org.za</t>
   </si>
   <si>
@@ -1868,6 +1874,12 @@
   </si>
   <si>
     <t>infoline@rondebosch.com</t>
+  </si>
+  <si>
+    <t>info@thehomestead.org.za</t>
+  </si>
+  <si>
+    <t>admissions@wpps.org.za</t>
   </si>
   <si>
     <t>Museums &amp; Heritage</t>
@@ -2605,7 +2617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L327"/>
+  <dimension ref="A1:L329"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2651,22 +2663,22 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C2" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D2" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E2" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="F2" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G2" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2674,22 +2686,22 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C3" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D3" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E3" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="F3" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G3" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2697,22 +2709,22 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C4" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D4" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E4" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="F4" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G4" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2720,22 +2732,22 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C5" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E5" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="F5" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2743,22 +2755,22 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C6" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D6" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E6" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="F6" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G6" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2766,22 +2778,22 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C7" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D7" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E7" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="F7" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G7" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2789,22 +2801,22 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C8" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D8" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E8" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="F8" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G8" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2812,22 +2824,22 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C9" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D9" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E9" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="F9" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G9" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2835,22 +2847,22 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C10" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D10" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E10" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="F10" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G10" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2858,22 +2870,22 @@
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C11" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D11" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E11" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="F11" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G11" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2881,22 +2893,22 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D12" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E12" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="F12" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G12" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2904,22 +2916,22 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C13" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D13" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E13" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="F13" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G13" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2927,22 +2939,22 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C14" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D14" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E14" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="G14" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2950,22 +2962,22 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C15" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D15" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E15" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="G15" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2973,16 +2985,16 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C16" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D16" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G16" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2990,16 +3002,16 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C17" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D17" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G17" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -3007,16 +3019,16 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C18" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D18" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G18" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -3024,16 +3036,16 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C19" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D19" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G19" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -3041,16 +3053,16 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C20" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D20" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G20" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3058,16 +3070,16 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C21" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D21" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G21" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3075,16 +3087,16 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C22" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D22" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G22" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3092,16 +3104,16 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C23" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D23" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G23" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3109,16 +3121,16 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C24" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D24" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G24" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3126,16 +3138,16 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C25" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D25" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G25" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3143,16 +3155,16 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C26" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D26" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G26" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3160,16 +3172,16 @@
         <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C27" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D27" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G27" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -3177,16 +3189,16 @@
         <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C28" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D28" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G28" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3194,16 +3206,16 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C29" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D29" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G29" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -3211,16 +3223,16 @@
         <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C30" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D30" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G30" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3228,16 +3240,16 @@
         <v>41</v>
       </c>
       <c r="B31" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C31" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D31" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G31" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3245,16 +3257,16 @@
         <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C32" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D32" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G32" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3262,16 +3274,16 @@
         <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C33" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D33" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G33" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -3279,16 +3291,16 @@
         <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C34" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D34" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G34" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -3296,16 +3308,16 @@
         <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C35" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D35" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G35" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3313,16 +3325,16 @@
         <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C36" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D36" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G36" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -3330,16 +3342,16 @@
         <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C37" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D37" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G37" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -3347,16 +3359,16 @@
         <v>48</v>
       </c>
       <c r="B38" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C38" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D38" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G38" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -3364,16 +3376,16 @@
         <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C39" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D39" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G39" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3381,16 +3393,16 @@
         <v>50</v>
       </c>
       <c r="B40" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C40" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D40" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G40" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -3398,16 +3410,16 @@
         <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C41" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D41" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G41" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3415,16 +3427,16 @@
         <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C42" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D42" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G42" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3432,16 +3444,16 @@
         <v>53</v>
       </c>
       <c r="B43" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C43" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D43" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G43" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3449,16 +3461,16 @@
         <v>54</v>
       </c>
       <c r="B44" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C44" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D44" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G44" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3466,16 +3478,16 @@
         <v>55</v>
       </c>
       <c r="B45" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C45" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D45" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G45" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3483,16 +3495,16 @@
         <v>56</v>
       </c>
       <c r="B46" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C46" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D46" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G46" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3500,16 +3512,16 @@
         <v>57</v>
       </c>
       <c r="B47" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C47" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D47" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G47" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3517,16 +3529,16 @@
         <v>58</v>
       </c>
       <c r="B48" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C48" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D48" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G48" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -3534,16 +3546,16 @@
         <v>59</v>
       </c>
       <c r="B49" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C49" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D49" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G49" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -3551,16 +3563,16 @@
         <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C50" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D50" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G50" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -3568,16 +3580,16 @@
         <v>61</v>
       </c>
       <c r="B51" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C51" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D51" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G51" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -3585,16 +3597,16 @@
         <v>62</v>
       </c>
       <c r="B52" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C52" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D52" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G52" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -3602,16 +3614,16 @@
         <v>63</v>
       </c>
       <c r="B53" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C53" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D53" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G53" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3619,16 +3631,16 @@
         <v>64</v>
       </c>
       <c r="B54" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C54" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D54" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G54" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -3636,16 +3648,16 @@
         <v>65</v>
       </c>
       <c r="B55" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C55" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D55" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G55" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3653,16 +3665,16 @@
         <v>66</v>
       </c>
       <c r="B56" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C56" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D56" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G56" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3670,16 +3682,16 @@
         <v>67</v>
       </c>
       <c r="B57" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C57" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D57" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G57" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3687,16 +3699,16 @@
         <v>68</v>
       </c>
       <c r="B58" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C58" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D58" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G58" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3704,16 +3716,16 @@
         <v>69</v>
       </c>
       <c r="B59" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C59" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D59" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G59" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3721,16 +3733,16 @@
         <v>70</v>
       </c>
       <c r="B60" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C60" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D60" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G60" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3738,16 +3750,16 @@
         <v>71</v>
       </c>
       <c r="B61" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C61" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D61" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G61" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3755,16 +3767,16 @@
         <v>72</v>
       </c>
       <c r="B62" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C62" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D62" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G62" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3772,16 +3784,16 @@
         <v>73</v>
       </c>
       <c r="B63" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C63" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D63" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G63" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3789,16 +3801,16 @@
         <v>74</v>
       </c>
       <c r="B64" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C64" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D64" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G64" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3806,16 +3818,16 @@
         <v>75</v>
       </c>
       <c r="B65" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C65" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D65" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G65" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3823,16 +3835,16 @@
         <v>76</v>
       </c>
       <c r="B66" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C66" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D66" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G66" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3840,16 +3852,16 @@
         <v>77</v>
       </c>
       <c r="B67" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C67" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D67" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G67" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3857,16 +3869,16 @@
         <v>78</v>
       </c>
       <c r="B68" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C68" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D68" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G68" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3874,16 +3886,16 @@
         <v>79</v>
       </c>
       <c r="B69" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C69" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D69" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G69" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3891,16 +3903,16 @@
         <v>80</v>
       </c>
       <c r="B70" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C70" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D70" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G70" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3908,16 +3920,16 @@
         <v>81</v>
       </c>
       <c r="B71" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C71" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D71" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G71" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3925,16 +3937,16 @@
         <v>82</v>
       </c>
       <c r="B72" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C72" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D72" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G72" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3942,16 +3954,16 @@
         <v>83</v>
       </c>
       <c r="B73" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C73" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D73" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G73" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3959,16 +3971,16 @@
         <v>84</v>
       </c>
       <c r="B74" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C74" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D74" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G74" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3976,16 +3988,16 @@
         <v>85</v>
       </c>
       <c r="B75" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C75" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D75" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G75" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3993,16 +4005,16 @@
         <v>86</v>
       </c>
       <c r="B76" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C76" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D76" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G76" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -4010,16 +4022,16 @@
         <v>87</v>
       </c>
       <c r="B77" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C77" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D77" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G77" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -4027,16 +4039,16 @@
         <v>88</v>
       </c>
       <c r="B78" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C78" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D78" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G78" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -4044,16 +4056,16 @@
         <v>89</v>
       </c>
       <c r="B79" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C79" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D79" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G79" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -4061,16 +4073,16 @@
         <v>90</v>
       </c>
       <c r="B80" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C80" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D80" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G80" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -4078,16 +4090,16 @@
         <v>91</v>
       </c>
       <c r="B81" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C81" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D81" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G81" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -4095,16 +4107,16 @@
         <v>92</v>
       </c>
       <c r="B82" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C82" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D82" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G82" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -4112,16 +4124,16 @@
         <v>93</v>
       </c>
       <c r="B83" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C83" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D83" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G83" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -4129,16 +4141,16 @@
         <v>94</v>
       </c>
       <c r="B84" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C84" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D84" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G84" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -4146,16 +4158,16 @@
         <v>95</v>
       </c>
       <c r="B85" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C85" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D85" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G85" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4163,16 +4175,16 @@
         <v>96</v>
       </c>
       <c r="B86" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C86" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D86" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G86" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4180,16 +4192,16 @@
         <v>97</v>
       </c>
       <c r="B87" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C87" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D87" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G87" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4197,16 +4209,16 @@
         <v>98</v>
       </c>
       <c r="B88" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C88" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D88" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G88" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4214,16 +4226,16 @@
         <v>99</v>
       </c>
       <c r="B89" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C89" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D89" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G89" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4231,16 +4243,16 @@
         <v>100</v>
       </c>
       <c r="B90" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C90" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D90" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G90" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4248,16 +4260,16 @@
         <v>101</v>
       </c>
       <c r="B91" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C91" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D91" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G91" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4265,16 +4277,16 @@
         <v>102</v>
       </c>
       <c r="B92" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C92" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D92" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G92" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -4282,16 +4294,16 @@
         <v>103</v>
       </c>
       <c r="B93" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C93" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D93" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G93" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -4299,16 +4311,16 @@
         <v>104</v>
       </c>
       <c r="B94" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C94" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D94" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G94" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -4316,16 +4328,16 @@
         <v>105</v>
       </c>
       <c r="B95" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C95" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D95" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G95" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -4333,16 +4345,16 @@
         <v>106</v>
       </c>
       <c r="B96" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C96" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D96" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G96" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4350,16 +4362,16 @@
         <v>107</v>
       </c>
       <c r="B97" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C97" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D97" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G97" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4367,16 +4379,16 @@
         <v>108</v>
       </c>
       <c r="B98" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C98" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D98" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G98" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4384,16 +4396,16 @@
         <v>109</v>
       </c>
       <c r="B99" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C99" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D99" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G99" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4401,16 +4413,16 @@
         <v>110</v>
       </c>
       <c r="B100" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C100" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D100" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G100" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4418,16 +4430,16 @@
         <v>111</v>
       </c>
       <c r="B101" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C101" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D101" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G101" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4435,16 +4447,16 @@
         <v>112</v>
       </c>
       <c r="B102" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C102" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D102" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G102" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4452,16 +4464,16 @@
         <v>113</v>
       </c>
       <c r="B103" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C103" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D103" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G103" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4469,16 +4481,16 @@
         <v>114</v>
       </c>
       <c r="B104" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C104" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D104" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G104" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4486,16 +4498,16 @@
         <v>115</v>
       </c>
       <c r="B105" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C105" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D105" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G105" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4503,16 +4515,16 @@
         <v>116</v>
       </c>
       <c r="B106" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C106" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D106" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G106" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4520,16 +4532,16 @@
         <v>117</v>
       </c>
       <c r="B107" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C107" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D107" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G107" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4537,16 +4549,16 @@
         <v>118</v>
       </c>
       <c r="B108" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C108" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D108" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G108" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4554,16 +4566,16 @@
         <v>119</v>
       </c>
       <c r="B109" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C109" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D109" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G109" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4571,16 +4583,16 @@
         <v>120</v>
       </c>
       <c r="B110" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C110" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D110" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G110" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4588,16 +4600,16 @@
         <v>121</v>
       </c>
       <c r="B111" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C111" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D111" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G111" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4605,16 +4617,16 @@
         <v>122</v>
       </c>
       <c r="B112" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C112" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D112" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G112" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4622,16 +4634,16 @@
         <v>123</v>
       </c>
       <c r="B113" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C113" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D113" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G113" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4639,16 +4651,16 @@
         <v>124</v>
       </c>
       <c r="B114" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C114" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="D114" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G114" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4656,16 +4668,16 @@
         <v>125</v>
       </c>
       <c r="B115" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C115" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="D115" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G115" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4673,16 +4685,16 @@
         <v>126</v>
       </c>
       <c r="B116" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C116" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="D116" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G116" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4690,16 +4702,16 @@
         <v>127</v>
       </c>
       <c r="B117" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C117" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="D117" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G117" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4707,16 +4719,16 @@
         <v>128</v>
       </c>
       <c r="B118" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C118" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="D118" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G118" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4724,22 +4736,22 @@
         <v>129</v>
       </c>
       <c r="B119" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C119" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="D119" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E119" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="F119" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="G119" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4747,19 +4759,19 @@
         <v>130</v>
       </c>
       <c r="B120" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C120" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="D120" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="E120" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="G120" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4767,16 +4779,16 @@
         <v>131</v>
       </c>
       <c r="B121" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C121" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="D121" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G121" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4784,16 +4796,16 @@
         <v>132</v>
       </c>
       <c r="B122" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C122" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D122" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="G122" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4801,22 +4813,22 @@
         <v>133</v>
       </c>
       <c r="B123" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C123" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D123" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="E123" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="F123" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="G123" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4824,16 +4836,16 @@
         <v>134</v>
       </c>
       <c r="B124" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C124" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D124" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G124" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4841,16 +4853,16 @@
         <v>135</v>
       </c>
       <c r="B125" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C125" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D125" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G125" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4858,16 +4870,16 @@
         <v>136</v>
       </c>
       <c r="B126" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C126" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D126" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G126" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4875,16 +4887,16 @@
         <v>137</v>
       </c>
       <c r="B127" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C127" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D127" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G127" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4892,19 +4904,19 @@
         <v>138</v>
       </c>
       <c r="B128" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C128" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D128" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="E128" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="G128" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4912,22 +4924,22 @@
         <v>139</v>
       </c>
       <c r="B129" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C129" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D129" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E129" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="F129" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="G129" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4935,16 +4947,16 @@
         <v>140</v>
       </c>
       <c r="B130" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C130" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D130" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G130" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4952,13 +4964,13 @@
         <v>141</v>
       </c>
       <c r="C131" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D131" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="E131" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4966,19 +4978,19 @@
         <v>142</v>
       </c>
       <c r="B132" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C132" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D132" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="E132" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="G132" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4986,19 +4998,19 @@
         <v>143</v>
       </c>
       <c r="B133" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C133" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D133" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="E133" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="G133" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -5006,10 +5018,10 @@
         <v>144</v>
       </c>
       <c r="C134" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D134" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -5017,10 +5029,10 @@
         <v>145</v>
       </c>
       <c r="C135" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D135" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -5028,16 +5040,16 @@
         <v>146</v>
       </c>
       <c r="B136" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C136" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D136" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G136" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -5045,16 +5057,16 @@
         <v>147</v>
       </c>
       <c r="B137" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C137" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D137" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="G137" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -5062,10 +5074,10 @@
         <v>148</v>
       </c>
       <c r="C138" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D138" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -5073,10 +5085,10 @@
         <v>149</v>
       </c>
       <c r="C139" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D139" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -5084,10 +5096,10 @@
         <v>150</v>
       </c>
       <c r="C140" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D140" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -5095,16 +5107,16 @@
         <v>151</v>
       </c>
       <c r="B141" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C141" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D141" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G141" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -5112,22 +5124,22 @@
         <v>152</v>
       </c>
       <c r="B142" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C142" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D142" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E142" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="F142" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="G142" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -5135,16 +5147,16 @@
         <v>153</v>
       </c>
       <c r="B143" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C143" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D143" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="G143" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -5152,13 +5164,13 @@
         <v>154</v>
       </c>
       <c r="C144" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D144" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="E144" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -5166,10 +5178,10 @@
         <v>155</v>
       </c>
       <c r="C145" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D145" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -5177,19 +5189,19 @@
         <v>156</v>
       </c>
       <c r="B146" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C146" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D146" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="F146" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="G146" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -5197,22 +5209,22 @@
         <v>157</v>
       </c>
       <c r="B147" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C147" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D147" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E147" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="F147" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="G147" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5220,19 +5232,19 @@
         <v>158</v>
       </c>
       <c r="B148" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C148" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D148" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E148" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="G148" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5240,19 +5252,19 @@
         <v>159</v>
       </c>
       <c r="B149" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C149" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D149" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E149" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="G149" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5260,19 +5272,19 @@
         <v>160</v>
       </c>
       <c r="B150" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C150" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D150" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E150" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="G150" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5280,19 +5292,19 @@
         <v>161</v>
       </c>
       <c r="B151" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C151" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D151" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E151" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G151" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5300,19 +5312,19 @@
         <v>162</v>
       </c>
       <c r="B152" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C152" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D152" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E152" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="G152" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5320,10 +5332,10 @@
         <v>163</v>
       </c>
       <c r="C153" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D153" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5331,19 +5343,19 @@
         <v>164</v>
       </c>
       <c r="B154" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C154" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D154" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E154" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="G154" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5351,16 +5363,16 @@
         <v>165</v>
       </c>
       <c r="B155" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C155" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D155" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G155" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5368,16 +5380,16 @@
         <v>166</v>
       </c>
       <c r="B156" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C156" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D156" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G156" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5385,22 +5397,22 @@
         <v>167</v>
       </c>
       <c r="B157" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C157" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D157" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="E157" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="F157" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="G157" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5408,19 +5420,19 @@
         <v>168</v>
       </c>
       <c r="B158" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C158" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D158" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E158" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="G158" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5428,19 +5440,19 @@
         <v>169</v>
       </c>
       <c r="B159" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C159" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D159" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E159" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="G159" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5448,19 +5460,19 @@
         <v>170</v>
       </c>
       <c r="B160" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C160" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D160" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E160" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="G160" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5468,19 +5480,19 @@
         <v>171</v>
       </c>
       <c r="B161" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C161" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D161" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="E161" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="G161" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5488,16 +5500,16 @@
         <v>172</v>
       </c>
       <c r="B162" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C162" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D162" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G162" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5505,19 +5517,19 @@
         <v>173</v>
       </c>
       <c r="B163" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C163" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D163" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E163" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="G163" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5525,19 +5537,19 @@
         <v>174</v>
       </c>
       <c r="B164" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C164" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D164" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="E164" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="G164" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5545,13 +5557,13 @@
         <v>175</v>
       </c>
       <c r="C165" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D165" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="E165" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5559,19 +5571,19 @@
         <v>176</v>
       </c>
       <c r="B166" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C166" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D166" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="E166" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="G166" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5579,19 +5591,19 @@
         <v>177</v>
       </c>
       <c r="B167" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C167" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D167" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="E167" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="G167" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5599,19 +5611,19 @@
         <v>178</v>
       </c>
       <c r="B168" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C168" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D168" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E168" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="G168" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5619,19 +5631,19 @@
         <v>179</v>
       </c>
       <c r="B169" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C169" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D169" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="E169" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="G169" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5639,13 +5651,13 @@
         <v>180</v>
       </c>
       <c r="C170" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D170" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="E170" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5653,13 +5665,13 @@
         <v>181</v>
       </c>
       <c r="C171" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D171" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E171" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5667,13 +5679,13 @@
         <v>182</v>
       </c>
       <c r="C172" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D172" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="E172" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5681,16 +5693,16 @@
         <v>183</v>
       </c>
       <c r="B173" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C173" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D173" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G173" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5698,19 +5710,19 @@
         <v>184</v>
       </c>
       <c r="B174" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C174" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D174" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="F174" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="G174" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5718,19 +5730,19 @@
         <v>185</v>
       </c>
       <c r="B175" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C175" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D175" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="F175" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="G175" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5738,10 +5750,10 @@
         <v>186</v>
       </c>
       <c r="C176" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="D176" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5749,10 +5761,10 @@
         <v>187</v>
       </c>
       <c r="C177" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="D177" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5760,10 +5772,10 @@
         <v>188</v>
       </c>
       <c r="C178" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="D178" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5771,22 +5783,22 @@
         <v>189</v>
       </c>
       <c r="B179" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C179" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D179" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="E179" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="F179" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="G179" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5794,10 +5806,10 @@
         <v>190</v>
       </c>
       <c r="C180" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D180" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5805,10 +5817,10 @@
         <v>191</v>
       </c>
       <c r="C181" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D181" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5816,19 +5828,19 @@
         <v>192</v>
       </c>
       <c r="B182" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C182" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="D182" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E182" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="G182" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5836,19 +5848,19 @@
         <v>193</v>
       </c>
       <c r="B183" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C183" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="D183" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="F183" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="G183" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5856,10 +5868,10 @@
         <v>194</v>
       </c>
       <c r="C184" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="D184" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5867,13 +5879,13 @@
         <v>195</v>
       </c>
       <c r="C185" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="D185" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="F185" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5881,13 +5893,13 @@
         <v>196</v>
       </c>
       <c r="C186" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D186" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="E186" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5895,13 +5907,13 @@
         <v>197</v>
       </c>
       <c r="C187" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D187" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E187" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5909,13 +5921,13 @@
         <v>198</v>
       </c>
       <c r="C188" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D188" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E188" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5923,13 +5935,13 @@
         <v>199</v>
       </c>
       <c r="C189" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D189" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E189" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5937,13 +5949,13 @@
         <v>200</v>
       </c>
       <c r="C190" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D190" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E190" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5951,10 +5963,10 @@
         <v>201</v>
       </c>
       <c r="C191" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D191" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -5962,10 +5974,10 @@
         <v>202</v>
       </c>
       <c r="C192" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D192" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -5973,10 +5985,10 @@
         <v>203</v>
       </c>
       <c r="C193" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D193" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -5984,16 +5996,16 @@
         <v>204</v>
       </c>
       <c r="B194" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C194" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D194" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="G194" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6001,16 +6013,16 @@
         <v>205</v>
       </c>
       <c r="B195" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C195" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D195" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="G195" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6018,19 +6030,19 @@
         <v>206</v>
       </c>
       <c r="B196" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C196" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D196" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="F196" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="G196" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6038,22 +6050,22 @@
         <v>207</v>
       </c>
       <c r="B197" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C197" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D197" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E197" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="F197" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="G197" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6061,22 +6073,22 @@
         <v>208</v>
       </c>
       <c r="B198" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C198" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D198" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E198" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="F198" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="G198" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6084,22 +6096,22 @@
         <v>209</v>
       </c>
       <c r="B199" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C199" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D199" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E199" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="F199" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="G199" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6107,16 +6119,16 @@
         <v>210</v>
       </c>
       <c r="B200" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C200" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="D200" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G200" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6124,10 +6136,10 @@
         <v>211</v>
       </c>
       <c r="C201" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="D201" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6135,10 +6147,10 @@
         <v>212</v>
       </c>
       <c r="C202" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="D202" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6146,10 +6158,10 @@
         <v>213</v>
       </c>
       <c r="C203" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="D203" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6157,16 +6169,16 @@
         <v>214</v>
       </c>
       <c r="B204" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C204" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D204" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G204" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6174,10 +6186,10 @@
         <v>215</v>
       </c>
       <c r="C205" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D205" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6185,10 +6197,10 @@
         <v>216</v>
       </c>
       <c r="C206" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D206" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6196,19 +6208,19 @@
         <v>217</v>
       </c>
       <c r="B207" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C207" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D207" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E207" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="G207" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6216,13 +6228,13 @@
         <v>218</v>
       </c>
       <c r="C208" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D208" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E208" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6230,10 +6242,10 @@
         <v>219</v>
       </c>
       <c r="C209" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D209" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6241,19 +6253,19 @@
         <v>220</v>
       </c>
       <c r="B210" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C210" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D210" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E210" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="G210" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6261,16 +6273,16 @@
         <v>221</v>
       </c>
       <c r="B211" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C211" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D211" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G211" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6278,13 +6290,13 @@
         <v>222</v>
       </c>
       <c r="C212" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D212" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E212" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6292,13 +6304,13 @@
         <v>223</v>
       </c>
       <c r="C213" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D213" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="E213" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6306,16 +6318,16 @@
         <v>224</v>
       </c>
       <c r="B214" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C214" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D214" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G214" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6323,16 +6335,16 @@
         <v>225</v>
       </c>
       <c r="B215" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C215" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D215" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G215" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6340,13 +6352,13 @@
         <v>226</v>
       </c>
       <c r="C216" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D216" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E216" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6354,19 +6366,19 @@
         <v>227</v>
       </c>
       <c r="B217" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C217" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="D217" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E217" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="G217" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6374,19 +6386,19 @@
         <v>228</v>
       </c>
       <c r="B218" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C218" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="D218" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E218" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="G218" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6394,19 +6406,19 @@
         <v>229</v>
       </c>
       <c r="B219" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C219" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="D219" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E219" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="G219" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6414,10 +6426,10 @@
         <v>230</v>
       </c>
       <c r="C220" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="D220" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6425,16 +6437,16 @@
         <v>231</v>
       </c>
       <c r="B221" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C221" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="D221" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G221" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6442,19 +6454,19 @@
         <v>232</v>
       </c>
       <c r="B222" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C222" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="D222" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E222" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="G222" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6462,16 +6474,16 @@
         <v>233</v>
       </c>
       <c r="B223" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C223" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="D223" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G223" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6479,16 +6491,16 @@
         <v>234</v>
       </c>
       <c r="B224" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C224" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="D224" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="G224" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6496,19 +6508,19 @@
         <v>235</v>
       </c>
       <c r="B225" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C225" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="D225" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="F225" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="G225" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6516,16 +6528,16 @@
         <v>236</v>
       </c>
       <c r="B226" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C226" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="D226" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G226" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6533,10 +6545,10 @@
         <v>237</v>
       </c>
       <c r="C227" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="D227" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6544,16 +6556,16 @@
         <v>238</v>
       </c>
       <c r="B228" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C228" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D228" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G228" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6561,16 +6573,16 @@
         <v>239</v>
       </c>
       <c r="B229" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C229" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D229" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G229" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6578,16 +6590,16 @@
         <v>240</v>
       </c>
       <c r="B230" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C230" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D230" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G230" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6595,16 +6607,16 @@
         <v>241</v>
       </c>
       <c r="B231" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C231" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D231" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G231" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6612,16 +6624,16 @@
         <v>242</v>
       </c>
       <c r="B232" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C232" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D232" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G232" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6629,16 +6641,16 @@
         <v>243</v>
       </c>
       <c r="B233" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C233" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D233" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G233" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6646,16 +6658,16 @@
         <v>244</v>
       </c>
       <c r="B234" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C234" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D234" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G234" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -6663,16 +6675,16 @@
         <v>245</v>
       </c>
       <c r="B235" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C235" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D235" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G235" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -6680,16 +6692,16 @@
         <v>246</v>
       </c>
       <c r="B236" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C236" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D236" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G236" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -6697,16 +6709,16 @@
         <v>247</v>
       </c>
       <c r="B237" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C237" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D237" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G237" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -6714,16 +6726,16 @@
         <v>248</v>
       </c>
       <c r="B238" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C238" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D238" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G238" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -6731,16 +6743,16 @@
         <v>249</v>
       </c>
       <c r="B239" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C239" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D239" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G239" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -6748,16 +6760,16 @@
         <v>250</v>
       </c>
       <c r="B240" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C240" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D240" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G240" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -6765,16 +6777,16 @@
         <v>251</v>
       </c>
       <c r="B241" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C241" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D241" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G241" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -6782,16 +6794,16 @@
         <v>252</v>
       </c>
       <c r="B242" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C242" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D242" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G242" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -6799,16 +6811,16 @@
         <v>253</v>
       </c>
       <c r="B243" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C243" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D243" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G243" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -6816,16 +6828,16 @@
         <v>254</v>
       </c>
       <c r="B244" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C244" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D244" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G244" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -6833,16 +6845,16 @@
         <v>255</v>
       </c>
       <c r="B245" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C245" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D245" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G245" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -6850,16 +6862,16 @@
         <v>256</v>
       </c>
       <c r="B246" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C246" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D246" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G246" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -6867,16 +6879,16 @@
         <v>257</v>
       </c>
       <c r="B247" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C247" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D247" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G247" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -6884,16 +6896,16 @@
         <v>258</v>
       </c>
       <c r="B248" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C248" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D248" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G248" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -6901,16 +6913,16 @@
         <v>259</v>
       </c>
       <c r="B249" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C249" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D249" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G249" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -6918,16 +6930,16 @@
         <v>260</v>
       </c>
       <c r="B250" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C250" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D250" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G250" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -6935,16 +6947,16 @@
         <v>261</v>
       </c>
       <c r="B251" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C251" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D251" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G251" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -6952,16 +6964,16 @@
         <v>262</v>
       </c>
       <c r="B252" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C252" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D252" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G252" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -6969,16 +6981,16 @@
         <v>263</v>
       </c>
       <c r="B253" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C253" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D253" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G253" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -6986,16 +6998,16 @@
         <v>264</v>
       </c>
       <c r="B254" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C254" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D254" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G254" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7003,16 +7015,16 @@
         <v>265</v>
       </c>
       <c r="B255" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C255" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D255" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G255" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7020,16 +7032,16 @@
         <v>266</v>
       </c>
       <c r="B256" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C256" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D256" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G256" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7037,16 +7049,16 @@
         <v>267</v>
       </c>
       <c r="B257" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C257" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D257" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G257" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7054,16 +7066,16 @@
         <v>268</v>
       </c>
       <c r="B258" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C258" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D258" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G258" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7071,16 +7083,16 @@
         <v>269</v>
       </c>
       <c r="B259" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C259" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D259" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G259" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7088,16 +7100,16 @@
         <v>270</v>
       </c>
       <c r="B260" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C260" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D260" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G260" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -7105,16 +7117,16 @@
         <v>271</v>
       </c>
       <c r="B261" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C261" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D261" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G261" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -7122,16 +7134,16 @@
         <v>272</v>
       </c>
       <c r="B262" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C262" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D262" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G262" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -7139,16 +7151,16 @@
         <v>273</v>
       </c>
       <c r="B263" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C263" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D263" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G263" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7156,16 +7168,16 @@
         <v>274</v>
       </c>
       <c r="B264" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C264" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D264" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G264" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -7173,16 +7185,16 @@
         <v>275</v>
       </c>
       <c r="B265" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C265" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D265" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G265" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -7190,16 +7202,16 @@
         <v>276</v>
       </c>
       <c r="B266" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C266" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D266" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G266" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7207,16 +7219,16 @@
         <v>277</v>
       </c>
       <c r="B267" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C267" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="D267" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G267" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7224,16 +7236,16 @@
         <v>278</v>
       </c>
       <c r="B268" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C268" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D268" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G268" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7241,16 +7253,16 @@
         <v>279</v>
       </c>
       <c r="B269" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C269" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="D269" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G269" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7258,16 +7270,16 @@
         <v>280</v>
       </c>
       <c r="B270" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C270" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D270" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G270" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7275,16 +7287,16 @@
         <v>281</v>
       </c>
       <c r="B271" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C271" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D271" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G271" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -7292,16 +7304,16 @@
         <v>282</v>
       </c>
       <c r="B272" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C272" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D272" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G272" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7309,16 +7321,16 @@
         <v>283</v>
       </c>
       <c r="B273" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C273" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D273" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G273" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -7326,16 +7338,16 @@
         <v>284</v>
       </c>
       <c r="B274" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C274" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D274" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G274" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -7343,16 +7355,16 @@
         <v>285</v>
       </c>
       <c r="B275" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C275" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D275" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G275" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -7360,16 +7372,16 @@
         <v>286</v>
       </c>
       <c r="B276" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C276" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D276" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G276" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -7377,16 +7389,16 @@
         <v>287</v>
       </c>
       <c r="B277" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C277" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D277" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G277" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -7394,16 +7406,16 @@
         <v>288</v>
       </c>
       <c r="B278" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C278" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D278" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G278" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7411,16 +7423,16 @@
         <v>289</v>
       </c>
       <c r="B279" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C279" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D279" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G279" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7428,16 +7440,16 @@
         <v>290</v>
       </c>
       <c r="B280" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C280" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D280" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G280" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -7445,16 +7457,16 @@
         <v>291</v>
       </c>
       <c r="B281" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C281" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D281" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="G281" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7462,16 +7474,16 @@
         <v>292</v>
       </c>
       <c r="B282" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C282" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D282" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G282" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -7479,16 +7491,16 @@
         <v>293</v>
       </c>
       <c r="B283" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C283" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D283" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G283" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -7496,19 +7508,19 @@
         <v>294</v>
       </c>
       <c r="B284" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C284" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D284" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="F284" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G284" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -7516,16 +7528,16 @@
         <v>295</v>
       </c>
       <c r="B285" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C285" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D285" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G285" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -7533,16 +7545,16 @@
         <v>296</v>
       </c>
       <c r="B286" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C286" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D286" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G286" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -7550,16 +7562,16 @@
         <v>297</v>
       </c>
       <c r="B287" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C287" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D287" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G287" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -7567,16 +7579,16 @@
         <v>298</v>
       </c>
       <c r="B288" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C288" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D288" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G288" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -7584,16 +7596,16 @@
         <v>299</v>
       </c>
       <c r="B289" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C289" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D289" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G289" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -7601,16 +7613,16 @@
         <v>300</v>
       </c>
       <c r="B290" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C290" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D290" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G290" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -7618,16 +7630,16 @@
         <v>301</v>
       </c>
       <c r="B291" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C291" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D291" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G291" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -7635,16 +7647,16 @@
         <v>302</v>
       </c>
       <c r="B292" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C292" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D292" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G292" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -7652,16 +7664,16 @@
         <v>303</v>
       </c>
       <c r="B293" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C293" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D293" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G293" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -7669,16 +7681,16 @@
         <v>304</v>
       </c>
       <c r="B294" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C294" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D294" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G294" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -7686,16 +7698,16 @@
         <v>140</v>
       </c>
       <c r="B295" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C295" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D295" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G295" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -7703,16 +7715,16 @@
         <v>305</v>
       </c>
       <c r="B296" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C296" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D296" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G296" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="297" spans="1:7">
@@ -7720,16 +7732,16 @@
         <v>306</v>
       </c>
       <c r="B297" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C297" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D297" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G297" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="298" spans="1:7">
@@ -7737,16 +7749,16 @@
         <v>307</v>
       </c>
       <c r="B298" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C298" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D298" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G298" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="299" spans="1:7">
@@ -7754,16 +7766,16 @@
         <v>308</v>
       </c>
       <c r="B299" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C299" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D299" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G299" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="300" spans="1:7">
@@ -7771,16 +7783,16 @@
         <v>309</v>
       </c>
       <c r="B300" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C300" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D300" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G300" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="301" spans="1:7">
@@ -7788,16 +7800,16 @@
         <v>310</v>
       </c>
       <c r="B301" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C301" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D301" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G301" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="302" spans="1:7">
@@ -7805,16 +7817,16 @@
         <v>311</v>
       </c>
       <c r="B302" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C302" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D302" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G302" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -7822,16 +7834,16 @@
         <v>312</v>
       </c>
       <c r="B303" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C303" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D303" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G303" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="304" spans="1:7">
@@ -7839,16 +7851,16 @@
         <v>313</v>
       </c>
       <c r="B304" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C304" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D304" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G304" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="305" spans="1:7">
@@ -7856,16 +7868,16 @@
         <v>314</v>
       </c>
       <c r="B305" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C305" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D305" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G305" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="306" spans="1:7">
@@ -7873,16 +7885,16 @@
         <v>315</v>
       </c>
       <c r="B306" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C306" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D306" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G306" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="307" spans="1:7">
@@ -7890,16 +7902,16 @@
         <v>316</v>
       </c>
       <c r="B307" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C307" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D307" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G307" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="308" spans="1:7">
@@ -7907,16 +7919,16 @@
         <v>317</v>
       </c>
       <c r="B308" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C308" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D308" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="G308" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -7924,16 +7936,16 @@
         <v>318</v>
       </c>
       <c r="B309" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C309" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D309" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="G309" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="310" spans="1:7">
@@ -7941,16 +7953,16 @@
         <v>319</v>
       </c>
       <c r="B310" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C310" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D310" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="G310" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="311" spans="1:7">
@@ -7958,16 +7970,16 @@
         <v>320</v>
       </c>
       <c r="B311" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C311" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D311" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="G311" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="312" spans="1:7">
@@ -7975,16 +7987,16 @@
         <v>321</v>
       </c>
       <c r="B312" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C312" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D312" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G312" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="313" spans="1:7">
@@ -7992,16 +8004,16 @@
         <v>322</v>
       </c>
       <c r="B313" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C313" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D313" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="G313" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="314" spans="1:7">
@@ -8009,16 +8021,16 @@
         <v>323</v>
       </c>
       <c r="B314" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C314" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D314" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="G314" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="315" spans="1:7">
@@ -8026,16 +8038,16 @@
         <v>324</v>
       </c>
       <c r="B315" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C315" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D315" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="G315" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="316" spans="1:7">
@@ -8043,16 +8055,16 @@
         <v>325</v>
       </c>
       <c r="B316" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C316" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D316" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="G316" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="317" spans="1:7">
@@ -8060,16 +8072,16 @@
         <v>326</v>
       </c>
       <c r="B317" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C317" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D317" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="G317" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="318" spans="1:7">
@@ -8077,16 +8089,16 @@
         <v>327</v>
       </c>
       <c r="B318" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C318" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D318" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="G318" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="319" spans="1:7">
@@ -8094,16 +8106,16 @@
         <v>328</v>
       </c>
       <c r="B319" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C319" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D319" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G319" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="320" spans="1:7">
@@ -8111,16 +8123,16 @@
         <v>329</v>
       </c>
       <c r="B320" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C320" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D320" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G320" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="321" spans="1:7">
@@ -8128,16 +8140,16 @@
         <v>330</v>
       </c>
       <c r="B321" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C321" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D321" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G321" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="322" spans="1:7">
@@ -8145,16 +8157,16 @@
         <v>300</v>
       </c>
       <c r="B322" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C322" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D322" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G322" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="323" spans="1:7">
@@ -8162,16 +8174,16 @@
         <v>331</v>
       </c>
       <c r="B323" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C323" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D323" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G323" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="324" spans="1:7">
@@ -8179,16 +8191,16 @@
         <v>332</v>
       </c>
       <c r="B324" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C324" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D324" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G324" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="325" spans="1:7">
@@ -8196,16 +8208,16 @@
         <v>333</v>
       </c>
       <c r="B325" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C325" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D325" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G325" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="326" spans="1:7">
@@ -8213,16 +8225,16 @@
         <v>334</v>
       </c>
       <c r="B326" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C326" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D326" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G326" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="327" spans="1:7">
@@ -8230,16 +8242,50 @@
         <v>335</v>
       </c>
       <c r="B327" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C327" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D327" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="G327" t="s">
-        <v>748</v>
+        <v>752</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7">
+      <c r="A328" t="s">
+        <v>336</v>
+      </c>
+      <c r="B328" t="s">
+        <v>620</v>
+      </c>
+      <c r="C328" t="s">
+        <v>629</v>
+      </c>
+      <c r="D328" t="s">
+        <v>672</v>
+      </c>
+      <c r="G328" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7">
+      <c r="A329" t="s">
+        <v>337</v>
+      </c>
+      <c r="B329" t="s">
+        <v>621</v>
+      </c>
+      <c r="C329" t="s">
+        <v>629</v>
+      </c>
+      <c r="D329" t="s">
+        <v>661</v>
+      </c>
+      <c r="G329" t="s">
+        <v>752</v>
       </c>
     </row>
   </sheetData>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2025" uniqueCount="875">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -1030,6 +1030,159 @@
     <t>Western Province Preparatory School</t>
   </si>
   <si>
+    <t>South African Education and Environment Project (SAEP)</t>
+  </si>
+  <si>
+    <t>Absolute Health Services - Health and Safety Training</t>
+  </si>
+  <si>
+    <t>Masthead (Pty) Ltd - Head Office</t>
+  </si>
+  <si>
+    <t>Common Ground Church Rondebosch</t>
+  </si>
+  <si>
+    <t>Rondebosch Park</t>
+  </si>
+  <si>
+    <t>HelloAsia! Rondebosch</t>
+  </si>
+  <si>
+    <t>HOPE hearing &amp; language opportunities</t>
+  </si>
+  <si>
+    <t>Friends of Vista Nova</t>
+  </si>
+  <si>
+    <t>The Children's Hospital Trust</t>
+  </si>
+  <si>
+    <t>Via Volunteers</t>
+  </si>
+  <si>
+    <t>Anchor House Of Hope</t>
+  </si>
+  <si>
+    <t>OpenHeritage</t>
+  </si>
+  <si>
+    <t>gold Youth Development Agency</t>
+  </si>
+  <si>
+    <t>CIEE Study Abroad Cape Town</t>
+  </si>
+  <si>
+    <t>ChildSafe South Africa</t>
+  </si>
+  <si>
+    <t>Community Media Trust</t>
+  </si>
+  <si>
+    <t>6th Rondebosch Scout Group</t>
+  </si>
+  <si>
+    <t>UCT YMCA Christian Study Centre</t>
+  </si>
+  <si>
+    <t>Kay-Dee Educare Centre Cc</t>
+  </si>
+  <si>
+    <t>Learn and Grow Montessori</t>
+  </si>
+  <si>
+    <t>THE CHAPEL LANE ACADEMY</t>
+  </si>
+  <si>
+    <t>Fledglings Educational Playgroup</t>
+  </si>
+  <si>
+    <t>Twinkles Playschool</t>
+  </si>
+  <si>
+    <t>Moms and Tots Rondebosch</t>
+  </si>
+  <si>
+    <t>Rondebosch Montessori Pre-School</t>
+  </si>
+  <si>
+    <t>Learning Unlimited</t>
+  </si>
+  <si>
+    <t>Rosedon House</t>
+  </si>
+  <si>
+    <t>Alignd</t>
+  </si>
+  <si>
+    <t>Africam</t>
+  </si>
+  <si>
+    <t>St. Patrick's Catholic Church</t>
+  </si>
+  <si>
+    <t>Mossop Hall</t>
+  </si>
+  <si>
+    <t>Thicket Road Church of Christ</t>
+  </si>
+  <si>
+    <t>RedPost Church</t>
+  </si>
+  <si>
+    <t>St Michael’s Catholic Church Rondebosch</t>
+  </si>
+  <si>
+    <t>St Paul's Anglican Church</t>
+  </si>
+  <si>
+    <t>Memorial Chapel</t>
+  </si>
+  <si>
+    <t>St. George's Grammar School</t>
+  </si>
+  <si>
+    <t>Eduvos Cape Town - Mowbray Campus</t>
+  </si>
+  <si>
+    <t>Thandokhulu High School</t>
+  </si>
+  <si>
+    <t>St Joseph's Marist College</t>
+  </si>
+  <si>
+    <t>Montessori Early Learning Foundation Teacher Training College</t>
+  </si>
+  <si>
+    <t>redAcademy</t>
+  </si>
+  <si>
+    <t>Groote Schuur Primary</t>
+  </si>
+  <si>
+    <t>Rosebank Junior School</t>
+  </si>
+  <si>
+    <t>Forres Preparatory School</t>
+  </si>
+  <si>
+    <t>Rustenburg Girls' Junior School</t>
+  </si>
+  <si>
+    <t>Rondebosch Heart Centre</t>
+  </si>
+  <si>
+    <t>CA Cape Doctors Rondebosch</t>
+  </si>
+  <si>
+    <t>The Medical Suite - Dr ZH Nakhwa &amp; Dr S Hamdulay</t>
+  </si>
+  <si>
+    <t>Rondebosch Health &amp; Wellness Centre - Dr LW Biggs</t>
+  </si>
+  <si>
+    <t>Willowmead Medical Centre</t>
+  </si>
+  <si>
     <t>info@ctsc.org.za</t>
   </si>
   <si>
@@ -1880,6 +2033,219 @@
   </si>
   <si>
     <t>admissions@wpps.org.za</t>
+  </si>
+  <si>
+    <t>rspack@1.6.8</t>
+  </si>
+  <si>
+    <t>core-js-bundle@3.2.1</t>
+  </si>
+  <si>
+    <t>sales@absolutehealth.co.za</t>
+  </si>
+  <si>
+    <t>ctown@masthead.co.za</t>
+  </si>
+  <si>
+    <t>durban@masthead.co.za</t>
+  </si>
+  <si>
+    <t>user@domain.com.</t>
+  </si>
+  <si>
+    <t>events.applications@capetown.gov.za</t>
+  </si>
+  <si>
+    <t>info@friendsofrondeboschpark.org.za</t>
+  </si>
+  <si>
+    <t>info@helloasia.co.za</t>
+  </si>
+  <si>
+    <t>chencihan.barry@gmail.com</t>
+  </si>
+  <si>
+    <t>admin@hope-hear.org</t>
+  </si>
+  <si>
+    <t>vistanovapta@mweb.co.za</t>
+  </si>
+  <si>
+    <t>cht@chtrust.org.za</t>
+  </si>
+  <si>
+    <t>info@viavolunteers.com</t>
+  </si>
+  <si>
+    <t>info@theanchorhouseofhope.org</t>
+  </si>
+  <si>
+    <t>info@openheritage.org.za</t>
+  </si>
+  <si>
+    <t>info@goldyouth.org</t>
+  </si>
+  <si>
+    <t>slick-carousel@1.8.1</t>
+  </si>
+  <si>
+    <t>contact@ciee.org</t>
+  </si>
+  <si>
+    <t>info@childsafe.org.za</t>
+  </si>
+  <si>
+    <t>info@cmt.org.za</t>
+  </si>
+  <si>
+    <t>whistleblower@cmt.org.za</t>
+  </si>
+  <si>
+    <t>carol@inprocess.co.za</t>
+  </si>
+  <si>
+    <t>joymerryweather@gmail.com</t>
+  </si>
+  <si>
+    <t>jim@uct-y.org</t>
+  </si>
+  <si>
+    <t>info@uct-y.org</t>
+  </si>
+  <si>
+    <t>info@kaydee.co.za</t>
+  </si>
+  <si>
+    <t>info@learnandgrowmontessori.org.za</t>
+  </si>
+  <si>
+    <t>charl@chapellane.co.za</t>
+  </si>
+  <si>
+    <t>info@fledglings.co.za</t>
+  </si>
+  <si>
+    <t>erika@twinklesplayschool.co.za</t>
+  </si>
+  <si>
+    <t>info@momsandtots.co.za</t>
+  </si>
+  <si>
+    <t>info@rondeboschmontessori.co.za</t>
+  </si>
+  <si>
+    <t>admin@learningunlimited.co.za</t>
+  </si>
+  <si>
+    <t>info@wccpa.org.za</t>
+  </si>
+  <si>
+    <t>info@alignd.co.za</t>
+  </si>
+  <si>
+    <t>info@africam.com</t>
+  </si>
+  <si>
+    <t>zoomies@africam.com</t>
+  </si>
+  <si>
+    <t>chancery@adct.org.za</t>
+  </si>
+  <si>
+    <t>thezimbo@gmail.com</t>
+  </si>
+  <si>
+    <t>leadership@thicketroadcoc.co.za</t>
+  </si>
+  <si>
+    <t>shabangujr@gmail.com</t>
+  </si>
+  <si>
+    <t>janine@rjboulle.com</t>
+  </si>
+  <si>
+    <t>deaconlesr@gmail.com</t>
+  </si>
+  <si>
+    <t>dpratt@mweb.co.za</t>
+  </si>
+  <si>
+    <t>stpauls@netdial.co.za</t>
+  </si>
+  <si>
+    <t>info@bishops.org.za</t>
+  </si>
+  <si>
+    <t>info@sggs.co.za</t>
+  </si>
+  <si>
+    <t>marketing.admissions@sggs.co.za</t>
+  </si>
+  <si>
+    <t>jquery@3.7.1</t>
+  </si>
+  <si>
+    <t>bootstrap@5.3.0-alpha3</t>
+  </si>
+  <si>
+    <t>thandokhulu.sec@wcgschools.gov.za</t>
+  </si>
+  <si>
+    <t>admin@maristsj.co.za</t>
+  </si>
+  <si>
+    <t>admin@elfmontessori.co.za</t>
+  </si>
+  <si>
+    <t>info@redacademy.co.za</t>
+  </si>
+  <si>
+    <t>support@redacademy.co.za</t>
+  </si>
+  <si>
+    <t>marketing@micklefield.co.za</t>
+  </si>
+  <si>
+    <t>toni@gsps.co.za</t>
+  </si>
+  <si>
+    <t>sport@gsps.co.za</t>
+  </si>
+  <si>
+    <t>rosebank.prim@wcgschools.gov.za</t>
+  </si>
+  <si>
+    <t>admin@forres.co.za</t>
+  </si>
+  <si>
+    <t>admin@rgjs.org.za</t>
+  </si>
+  <si>
+    <t>mark.dobson@uct.ac.za</t>
+  </si>
+  <si>
+    <t>enquiries@rondeboschmc.com</t>
+  </si>
+  <si>
+    <t>cacdclaremont@gmail.com</t>
+  </si>
+  <si>
+    <t>reception@capedoctors.co.za</t>
+  </si>
+  <si>
+    <t>reception@themedicalsuite.co.za</t>
+  </si>
+  <si>
+    <t>shorelinehealthza@gmail.com</t>
+  </si>
+  <si>
+    <t>rondebosch.health@gmail.com</t>
+  </si>
+  <si>
+    <t>info@drroyker.co.za</t>
+  </si>
+  <si>
+    <t>info@willowmead.co.za</t>
   </si>
   <si>
     <t>Museums &amp; Heritage</t>
@@ -2617,7 +2983,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L329"/>
+  <dimension ref="A1:L400"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2663,22 +3029,22 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>338</v>
+        <v>389</v>
       </c>
       <c r="C2" t="s">
-        <v>622</v>
+        <v>744</v>
       </c>
       <c r="D2" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E2" t="s">
-        <v>678</v>
+        <v>800</v>
       </c>
       <c r="F2" t="s">
-        <v>732</v>
+        <v>854</v>
       </c>
       <c r="G2" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2686,22 +3052,22 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>339</v>
+        <v>390</v>
       </c>
       <c r="C3" t="s">
-        <v>622</v>
+        <v>744</v>
       </c>
       <c r="D3" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E3" t="s">
-        <v>678</v>
+        <v>800</v>
       </c>
       <c r="F3" t="s">
-        <v>732</v>
+        <v>854</v>
       </c>
       <c r="G3" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2709,22 +3075,22 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>340</v>
+        <v>391</v>
       </c>
       <c r="C4" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D4" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E4" t="s">
-        <v>678</v>
+        <v>800</v>
       </c>
       <c r="F4" t="s">
-        <v>732</v>
+        <v>854</v>
       </c>
       <c r="G4" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2732,22 +3098,22 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>341</v>
+        <v>392</v>
       </c>
       <c r="C5" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D5" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E5" t="s">
-        <v>678</v>
+        <v>800</v>
       </c>
       <c r="F5" t="s">
-        <v>732</v>
+        <v>854</v>
       </c>
       <c r="G5" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2755,22 +3121,22 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>342</v>
+        <v>393</v>
       </c>
       <c r="C6" t="s">
-        <v>622</v>
+        <v>744</v>
       </c>
       <c r="D6" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E6" t="s">
-        <v>678</v>
+        <v>800</v>
       </c>
       <c r="F6" t="s">
-        <v>732</v>
+        <v>854</v>
       </c>
       <c r="G6" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2778,22 +3144,22 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>343</v>
+        <v>394</v>
       </c>
       <c r="C7" t="s">
-        <v>622</v>
+        <v>744</v>
       </c>
       <c r="D7" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E7" t="s">
-        <v>678</v>
+        <v>800</v>
       </c>
       <c r="F7" t="s">
-        <v>732</v>
+        <v>854</v>
       </c>
       <c r="G7" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2801,22 +3167,22 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>344</v>
+        <v>395</v>
       </c>
       <c r="C8" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D8" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E8" t="s">
-        <v>678</v>
+        <v>800</v>
       </c>
       <c r="F8" t="s">
-        <v>732</v>
+        <v>854</v>
       </c>
       <c r="G8" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2824,22 +3190,22 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>345</v>
+        <v>396</v>
       </c>
       <c r="C9" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D9" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E9" t="s">
-        <v>678</v>
+        <v>800</v>
       </c>
       <c r="F9" t="s">
-        <v>732</v>
+        <v>854</v>
       </c>
       <c r="G9" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2847,22 +3213,22 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>346</v>
+        <v>397</v>
       </c>
       <c r="C10" t="s">
-        <v>624</v>
+        <v>746</v>
       </c>
       <c r="D10" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E10" t="s">
-        <v>678</v>
+        <v>800</v>
       </c>
       <c r="F10" t="s">
-        <v>732</v>
+        <v>854</v>
       </c>
       <c r="G10" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2870,22 +3236,22 @@
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>347</v>
+        <v>398</v>
       </c>
       <c r="C11" t="s">
-        <v>624</v>
+        <v>746</v>
       </c>
       <c r="D11" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E11" t="s">
-        <v>678</v>
+        <v>800</v>
       </c>
       <c r="F11" t="s">
-        <v>732</v>
+        <v>854</v>
       </c>
       <c r="G11" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2893,22 +3259,22 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>348</v>
+        <v>399</v>
       </c>
       <c r="C12" t="s">
-        <v>625</v>
+        <v>747</v>
       </c>
       <c r="D12" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E12" t="s">
-        <v>678</v>
+        <v>800</v>
       </c>
       <c r="F12" t="s">
-        <v>732</v>
+        <v>854</v>
       </c>
       <c r="G12" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2916,22 +3282,22 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>349</v>
+        <v>400</v>
       </c>
       <c r="C13" t="s">
-        <v>622</v>
+        <v>744</v>
       </c>
       <c r="D13" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E13" t="s">
-        <v>678</v>
+        <v>800</v>
       </c>
       <c r="F13" t="s">
-        <v>732</v>
+        <v>854</v>
       </c>
       <c r="G13" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2939,22 +3305,22 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>350</v>
+        <v>401</v>
       </c>
       <c r="C14" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D14" t="s">
-        <v>648</v>
+        <v>770</v>
       </c>
       <c r="E14" t="s">
-        <v>679</v>
+        <v>801</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>733</v>
+        <v>855</v>
       </c>
       <c r="G14" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2962,22 +3328,22 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>351</v>
+        <v>402</v>
       </c>
       <c r="C15" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D15" t="s">
-        <v>648</v>
+        <v>770</v>
       </c>
       <c r="E15" t="s">
-        <v>680</v>
+        <v>802</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>734</v>
+        <v>856</v>
       </c>
       <c r="G15" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2985,16 +3351,16 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>352</v>
+        <v>403</v>
       </c>
       <c r="C16" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D16" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G16" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -3002,16 +3368,16 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>353</v>
+        <v>404</v>
       </c>
       <c r="C17" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D17" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G17" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -3019,16 +3385,16 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>354</v>
+        <v>405</v>
       </c>
       <c r="C18" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D18" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G18" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -3036,16 +3402,16 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>355</v>
+        <v>406</v>
       </c>
       <c r="C19" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D19" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G19" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -3053,16 +3419,16 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>356</v>
+        <v>407</v>
       </c>
       <c r="C20" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D20" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G20" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3070,16 +3436,16 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>357</v>
+        <v>408</v>
       </c>
       <c r="C21" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D21" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G21" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3087,16 +3453,16 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>358</v>
+        <v>409</v>
       </c>
       <c r="C22" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D22" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G22" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3104,16 +3470,16 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>359</v>
+        <v>410</v>
       </c>
       <c r="C23" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D23" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G23" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3121,16 +3487,16 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>360</v>
+        <v>411</v>
       </c>
       <c r="C24" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D24" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G24" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3138,16 +3504,16 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>361</v>
+        <v>412</v>
       </c>
       <c r="C25" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D25" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G25" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3155,16 +3521,16 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>362</v>
+        <v>413</v>
       </c>
       <c r="C26" t="s">
-        <v>628</v>
+        <v>750</v>
       </c>
       <c r="D26" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G26" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3172,16 +3538,16 @@
         <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>363</v>
+        <v>414</v>
       </c>
       <c r="C27" t="s">
-        <v>628</v>
+        <v>750</v>
       </c>
       <c r="D27" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G27" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -3189,16 +3555,16 @@
         <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>364</v>
+        <v>415</v>
       </c>
       <c r="C28" t="s">
-        <v>628</v>
+        <v>750</v>
       </c>
       <c r="D28" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G28" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3206,16 +3572,16 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>365</v>
+        <v>416</v>
       </c>
       <c r="C29" t="s">
-        <v>628</v>
+        <v>750</v>
       </c>
       <c r="D29" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G29" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -3223,16 +3589,16 @@
         <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>366</v>
+        <v>417</v>
       </c>
       <c r="C30" t="s">
-        <v>628</v>
+        <v>750</v>
       </c>
       <c r="D30" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G30" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3240,16 +3606,16 @@
         <v>41</v>
       </c>
       <c r="B31" t="s">
-        <v>367</v>
+        <v>418</v>
       </c>
       <c r="C31" t="s">
-        <v>628</v>
+        <v>750</v>
       </c>
       <c r="D31" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G31" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3257,16 +3623,16 @@
         <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>368</v>
+        <v>419</v>
       </c>
       <c r="C32" t="s">
-        <v>628</v>
+        <v>750</v>
       </c>
       <c r="D32" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G32" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3274,16 +3640,16 @@
         <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>369</v>
+        <v>420</v>
       </c>
       <c r="C33" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D33" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G33" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -3291,16 +3657,16 @@
         <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>370</v>
+        <v>421</v>
       </c>
       <c r="C34" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D34" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G34" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -3308,16 +3674,16 @@
         <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>371</v>
+        <v>422</v>
       </c>
       <c r="C35" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D35" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G35" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3325,16 +3691,16 @@
         <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>372</v>
+        <v>423</v>
       </c>
       <c r="C36" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D36" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G36" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -3342,16 +3708,16 @@
         <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>373</v>
+        <v>424</v>
       </c>
       <c r="C37" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D37" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G37" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -3359,16 +3725,16 @@
         <v>48</v>
       </c>
       <c r="B38" t="s">
-        <v>374</v>
+        <v>425</v>
       </c>
       <c r="C38" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D38" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G38" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -3376,16 +3742,16 @@
         <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>375</v>
+        <v>426</v>
       </c>
       <c r="C39" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D39" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G39" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3393,16 +3759,16 @@
         <v>50</v>
       </c>
       <c r="B40" t="s">
-        <v>376</v>
+        <v>427</v>
       </c>
       <c r="C40" t="s">
-        <v>630</v>
+        <v>752</v>
       </c>
       <c r="D40" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G40" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -3410,16 +3776,16 @@
         <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>377</v>
+        <v>428</v>
       </c>
       <c r="C41" t="s">
-        <v>630</v>
+        <v>752</v>
       </c>
       <c r="D41" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G41" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3427,16 +3793,16 @@
         <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>378</v>
+        <v>429</v>
       </c>
       <c r="C42" t="s">
-        <v>630</v>
+        <v>752</v>
       </c>
       <c r="D42" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G42" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3444,16 +3810,16 @@
         <v>53</v>
       </c>
       <c r="B43" t="s">
-        <v>379</v>
+        <v>430</v>
       </c>
       <c r="C43" t="s">
-        <v>630</v>
+        <v>752</v>
       </c>
       <c r="D43" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G43" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3461,16 +3827,16 @@
         <v>54</v>
       </c>
       <c r="B44" t="s">
-        <v>380</v>
+        <v>431</v>
       </c>
       <c r="C44" t="s">
-        <v>630</v>
+        <v>752</v>
       </c>
       <c r="D44" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G44" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3478,16 +3844,16 @@
         <v>55</v>
       </c>
       <c r="B45" t="s">
-        <v>381</v>
+        <v>432</v>
       </c>
       <c r="C45" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D45" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G45" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3495,16 +3861,16 @@
         <v>56</v>
       </c>
       <c r="B46" t="s">
-        <v>382</v>
+        <v>433</v>
       </c>
       <c r="C46" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D46" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G46" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3512,16 +3878,16 @@
         <v>57</v>
       </c>
       <c r="B47" t="s">
-        <v>383</v>
+        <v>434</v>
       </c>
       <c r="C47" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D47" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G47" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3529,16 +3895,16 @@
         <v>58</v>
       </c>
       <c r="B48" t="s">
-        <v>384</v>
+        <v>435</v>
       </c>
       <c r="C48" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D48" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G48" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -3546,16 +3912,16 @@
         <v>59</v>
       </c>
       <c r="B49" t="s">
-        <v>385</v>
+        <v>436</v>
       </c>
       <c r="C49" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D49" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G49" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -3563,16 +3929,16 @@
         <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>386</v>
+        <v>437</v>
       </c>
       <c r="C50" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D50" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G50" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -3580,16 +3946,16 @@
         <v>61</v>
       </c>
       <c r="B51" t="s">
-        <v>387</v>
+        <v>438</v>
       </c>
       <c r="C51" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D51" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G51" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -3597,16 +3963,16 @@
         <v>62</v>
       </c>
       <c r="B52" t="s">
-        <v>388</v>
+        <v>439</v>
       </c>
       <c r="C52" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D52" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G52" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -3614,16 +3980,16 @@
         <v>63</v>
       </c>
       <c r="B53" t="s">
-        <v>389</v>
+        <v>440</v>
       </c>
       <c r="C53" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D53" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G53" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3631,16 +3997,16 @@
         <v>64</v>
       </c>
       <c r="B54" t="s">
-        <v>390</v>
+        <v>441</v>
       </c>
       <c r="C54" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D54" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G54" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -3648,16 +4014,16 @@
         <v>65</v>
       </c>
       <c r="B55" t="s">
-        <v>391</v>
+        <v>442</v>
       </c>
       <c r="C55" t="s">
-        <v>631</v>
+        <v>753</v>
       </c>
       <c r="D55" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G55" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3665,16 +4031,16 @@
         <v>66</v>
       </c>
       <c r="B56" t="s">
-        <v>392</v>
+        <v>443</v>
       </c>
       <c r="C56" t="s">
-        <v>631</v>
+        <v>753</v>
       </c>
       <c r="D56" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G56" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3682,16 +4048,16 @@
         <v>67</v>
       </c>
       <c r="B57" t="s">
-        <v>393</v>
+        <v>444</v>
       </c>
       <c r="C57" t="s">
-        <v>631</v>
+        <v>753</v>
       </c>
       <c r="D57" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G57" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3699,16 +4065,16 @@
         <v>68</v>
       </c>
       <c r="B58" t="s">
-        <v>394</v>
+        <v>445</v>
       </c>
       <c r="C58" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D58" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G58" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3716,16 +4082,16 @@
         <v>69</v>
       </c>
       <c r="B59" t="s">
-        <v>395</v>
+        <v>446</v>
       </c>
       <c r="C59" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D59" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G59" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3733,16 +4099,16 @@
         <v>70</v>
       </c>
       <c r="B60" t="s">
-        <v>396</v>
+        <v>447</v>
       </c>
       <c r="C60" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D60" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G60" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3750,16 +4116,16 @@
         <v>71</v>
       </c>
       <c r="B61" t="s">
-        <v>397</v>
+        <v>448</v>
       </c>
       <c r="C61" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D61" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G61" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3767,16 +4133,16 @@
         <v>72</v>
       </c>
       <c r="B62" t="s">
-        <v>398</v>
+        <v>449</v>
       </c>
       <c r="C62" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D62" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G62" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3784,16 +4150,16 @@
         <v>73</v>
       </c>
       <c r="B63" t="s">
-        <v>399</v>
+        <v>450</v>
       </c>
       <c r="C63" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D63" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G63" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3801,16 +4167,16 @@
         <v>74</v>
       </c>
       <c r="B64" t="s">
-        <v>400</v>
+        <v>451</v>
       </c>
       <c r="C64" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D64" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G64" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3818,16 +4184,16 @@
         <v>75</v>
       </c>
       <c r="B65" t="s">
-        <v>401</v>
+        <v>452</v>
       </c>
       <c r="C65" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D65" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G65" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3835,16 +4201,16 @@
         <v>76</v>
       </c>
       <c r="B66" t="s">
-        <v>402</v>
+        <v>453</v>
       </c>
       <c r="C66" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D66" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G66" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3852,16 +4218,16 @@
         <v>77</v>
       </c>
       <c r="B67" t="s">
-        <v>403</v>
+        <v>454</v>
       </c>
       <c r="C67" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D67" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G67" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3869,16 +4235,16 @@
         <v>78</v>
       </c>
       <c r="B68" t="s">
-        <v>404</v>
+        <v>455</v>
       </c>
       <c r="C68" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D68" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G68" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3886,16 +4252,16 @@
         <v>79</v>
       </c>
       <c r="B69" t="s">
-        <v>405</v>
+        <v>456</v>
       </c>
       <c r="C69" t="s">
-        <v>628</v>
+        <v>750</v>
       </c>
       <c r="D69" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G69" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3903,16 +4269,16 @@
         <v>80</v>
       </c>
       <c r="B70" t="s">
-        <v>406</v>
+        <v>457</v>
       </c>
       <c r="C70" t="s">
-        <v>628</v>
+        <v>750</v>
       </c>
       <c r="D70" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G70" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3920,16 +4286,16 @@
         <v>81</v>
       </c>
       <c r="B71" t="s">
-        <v>407</v>
+        <v>458</v>
       </c>
       <c r="C71" t="s">
-        <v>628</v>
+        <v>750</v>
       </c>
       <c r="D71" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G71" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3937,16 +4303,16 @@
         <v>82</v>
       </c>
       <c r="B72" t="s">
-        <v>408</v>
+        <v>459</v>
       </c>
       <c r="C72" t="s">
-        <v>628</v>
+        <v>750</v>
       </c>
       <c r="D72" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G72" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3954,16 +4320,16 @@
         <v>83</v>
       </c>
       <c r="B73" t="s">
-        <v>409</v>
+        <v>460</v>
       </c>
       <c r="C73" t="s">
-        <v>628</v>
+        <v>750</v>
       </c>
       <c r="D73" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G73" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3971,16 +4337,16 @@
         <v>84</v>
       </c>
       <c r="B74" t="s">
-        <v>410</v>
+        <v>461</v>
       </c>
       <c r="C74" t="s">
-        <v>628</v>
+        <v>750</v>
       </c>
       <c r="D74" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G74" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3988,16 +4354,16 @@
         <v>85</v>
       </c>
       <c r="B75" t="s">
-        <v>411</v>
+        <v>462</v>
       </c>
       <c r="C75" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D75" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G75" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -4005,16 +4371,16 @@
         <v>86</v>
       </c>
       <c r="B76" t="s">
-        <v>412</v>
+        <v>463</v>
       </c>
       <c r="C76" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D76" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G76" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -4022,16 +4388,16 @@
         <v>87</v>
       </c>
       <c r="B77" t="s">
-        <v>413</v>
+        <v>464</v>
       </c>
       <c r="C77" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D77" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G77" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -4039,16 +4405,16 @@
         <v>88</v>
       </c>
       <c r="B78" t="s">
-        <v>414</v>
+        <v>465</v>
       </c>
       <c r="C78" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D78" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G78" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -4056,16 +4422,16 @@
         <v>89</v>
       </c>
       <c r="B79" t="s">
-        <v>415</v>
+        <v>466</v>
       </c>
       <c r="C79" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D79" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G79" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -4073,16 +4439,16 @@
         <v>90</v>
       </c>
       <c r="B80" t="s">
-        <v>416</v>
+        <v>467</v>
       </c>
       <c r="C80" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D80" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G80" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -4090,16 +4456,16 @@
         <v>91</v>
       </c>
       <c r="B81" t="s">
-        <v>417</v>
+        <v>468</v>
       </c>
       <c r="C81" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D81" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G81" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -4107,16 +4473,16 @@
         <v>92</v>
       </c>
       <c r="B82" t="s">
-        <v>418</v>
+        <v>469</v>
       </c>
       <c r="C82" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D82" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G82" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -4124,16 +4490,16 @@
         <v>93</v>
       </c>
       <c r="B83" t="s">
-        <v>419</v>
+        <v>470</v>
       </c>
       <c r="C83" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D83" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G83" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -4141,16 +4507,16 @@
         <v>94</v>
       </c>
       <c r="B84" t="s">
-        <v>420</v>
+        <v>471</v>
       </c>
       <c r="C84" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D84" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G84" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -4158,16 +4524,16 @@
         <v>95</v>
       </c>
       <c r="B85" t="s">
-        <v>421</v>
+        <v>472</v>
       </c>
       <c r="C85" t="s">
-        <v>630</v>
+        <v>752</v>
       </c>
       <c r="D85" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G85" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4175,16 +4541,16 @@
         <v>96</v>
       </c>
       <c r="B86" t="s">
-        <v>422</v>
+        <v>473</v>
       </c>
       <c r="C86" t="s">
-        <v>630</v>
+        <v>752</v>
       </c>
       <c r="D86" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G86" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4192,16 +4558,16 @@
         <v>97</v>
       </c>
       <c r="B87" t="s">
-        <v>423</v>
+        <v>474</v>
       </c>
       <c r="C87" t="s">
-        <v>630</v>
+        <v>752</v>
       </c>
       <c r="D87" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G87" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4209,16 +4575,16 @@
         <v>98</v>
       </c>
       <c r="B88" t="s">
-        <v>424</v>
+        <v>475</v>
       </c>
       <c r="C88" t="s">
-        <v>630</v>
+        <v>752</v>
       </c>
       <c r="D88" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G88" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4226,16 +4592,16 @@
         <v>99</v>
       </c>
       <c r="B89" t="s">
-        <v>425</v>
+        <v>476</v>
       </c>
       <c r="C89" t="s">
-        <v>630</v>
+        <v>752</v>
       </c>
       <c r="D89" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G89" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4243,16 +4609,16 @@
         <v>100</v>
       </c>
       <c r="B90" t="s">
-        <v>426</v>
+        <v>477</v>
       </c>
       <c r="C90" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D90" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G90" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4260,16 +4626,16 @@
         <v>101</v>
       </c>
       <c r="B91" t="s">
-        <v>427</v>
+        <v>478</v>
       </c>
       <c r="C91" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D91" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G91" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4277,16 +4643,16 @@
         <v>102</v>
       </c>
       <c r="B92" t="s">
-        <v>428</v>
+        <v>479</v>
       </c>
       <c r="C92" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D92" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G92" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -4294,16 +4660,16 @@
         <v>103</v>
       </c>
       <c r="B93" t="s">
-        <v>429</v>
+        <v>480</v>
       </c>
       <c r="C93" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D93" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G93" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -4311,16 +4677,16 @@
         <v>104</v>
       </c>
       <c r="B94" t="s">
-        <v>430</v>
+        <v>481</v>
       </c>
       <c r="C94" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D94" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G94" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -4328,16 +4694,16 @@
         <v>105</v>
       </c>
       <c r="B95" t="s">
-        <v>431</v>
+        <v>482</v>
       </c>
       <c r="C95" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D95" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G95" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -4345,16 +4711,16 @@
         <v>106</v>
       </c>
       <c r="B96" t="s">
-        <v>432</v>
+        <v>483</v>
       </c>
       <c r="C96" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D96" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G96" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4362,16 +4728,16 @@
         <v>107</v>
       </c>
       <c r="B97" t="s">
-        <v>433</v>
+        <v>484</v>
       </c>
       <c r="C97" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D97" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G97" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4379,16 +4745,16 @@
         <v>108</v>
       </c>
       <c r="B98" t="s">
-        <v>434</v>
+        <v>485</v>
       </c>
       <c r="C98" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D98" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G98" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4396,16 +4762,16 @@
         <v>109</v>
       </c>
       <c r="B99" t="s">
-        <v>435</v>
+        <v>486</v>
       </c>
       <c r="C99" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D99" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G99" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4413,16 +4779,16 @@
         <v>110</v>
       </c>
       <c r="B100" t="s">
-        <v>436</v>
+        <v>487</v>
       </c>
       <c r="C100" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D100" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G100" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4430,16 +4796,16 @@
         <v>111</v>
       </c>
       <c r="B101" t="s">
-        <v>437</v>
+        <v>488</v>
       </c>
       <c r="C101" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D101" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G101" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4447,16 +4813,16 @@
         <v>112</v>
       </c>
       <c r="B102" t="s">
-        <v>438</v>
+        <v>489</v>
       </c>
       <c r="C102" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D102" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G102" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4464,16 +4830,16 @@
         <v>113</v>
       </c>
       <c r="B103" t="s">
-        <v>439</v>
+        <v>490</v>
       </c>
       <c r="C103" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D103" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G103" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4481,16 +4847,16 @@
         <v>114</v>
       </c>
       <c r="B104" t="s">
-        <v>440</v>
+        <v>491</v>
       </c>
       <c r="C104" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D104" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G104" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4498,16 +4864,16 @@
         <v>115</v>
       </c>
       <c r="B105" t="s">
-        <v>441</v>
+        <v>492</v>
       </c>
       <c r="C105" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D105" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G105" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4515,16 +4881,16 @@
         <v>116</v>
       </c>
       <c r="B106" t="s">
-        <v>442</v>
+        <v>493</v>
       </c>
       <c r="C106" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D106" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G106" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4532,16 +4898,16 @@
         <v>117</v>
       </c>
       <c r="B107" t="s">
-        <v>443</v>
+        <v>494</v>
       </c>
       <c r="C107" t="s">
-        <v>631</v>
+        <v>753</v>
       </c>
       <c r="D107" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G107" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4549,16 +4915,16 @@
         <v>118</v>
       </c>
       <c r="B108" t="s">
-        <v>444</v>
+        <v>495</v>
       </c>
       <c r="C108" t="s">
-        <v>631</v>
+        <v>753</v>
       </c>
       <c r="D108" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G108" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4566,16 +4932,16 @@
         <v>119</v>
       </c>
       <c r="B109" t="s">
-        <v>445</v>
+        <v>496</v>
       </c>
       <c r="C109" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D109" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G109" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4583,16 +4949,16 @@
         <v>120</v>
       </c>
       <c r="B110" t="s">
-        <v>446</v>
+        <v>497</v>
       </c>
       <c r="C110" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D110" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G110" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4600,16 +4966,16 @@
         <v>121</v>
       </c>
       <c r="B111" t="s">
-        <v>447</v>
+        <v>498</v>
       </c>
       <c r="C111" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D111" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G111" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4617,16 +4983,16 @@
         <v>122</v>
       </c>
       <c r="B112" t="s">
-        <v>448</v>
+        <v>499</v>
       </c>
       <c r="C112" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D112" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G112" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4634,16 +5000,16 @@
         <v>123</v>
       </c>
       <c r="B113" t="s">
-        <v>449</v>
+        <v>500</v>
       </c>
       <c r="C113" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D113" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G113" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4651,16 +5017,16 @@
         <v>124</v>
       </c>
       <c r="B114" t="s">
-        <v>450</v>
+        <v>501</v>
       </c>
       <c r="C114" t="s">
-        <v>633</v>
+        <v>755</v>
       </c>
       <c r="D114" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G114" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4668,16 +5034,16 @@
         <v>125</v>
       </c>
       <c r="B115" t="s">
-        <v>451</v>
+        <v>502</v>
       </c>
       <c r="C115" t="s">
-        <v>633</v>
+        <v>755</v>
       </c>
       <c r="D115" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G115" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4685,16 +5051,16 @@
         <v>126</v>
       </c>
       <c r="B116" t="s">
-        <v>452</v>
+        <v>503</v>
       </c>
       <c r="C116" t="s">
-        <v>633</v>
+        <v>755</v>
       </c>
       <c r="D116" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G116" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4702,16 +5068,16 @@
         <v>127</v>
       </c>
       <c r="B117" t="s">
-        <v>453</v>
+        <v>504</v>
       </c>
       <c r="C117" t="s">
-        <v>633</v>
+        <v>755</v>
       </c>
       <c r="D117" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G117" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4719,16 +5085,16 @@
         <v>128</v>
       </c>
       <c r="B118" t="s">
-        <v>454</v>
+        <v>505</v>
       </c>
       <c r="C118" t="s">
-        <v>633</v>
+        <v>755</v>
       </c>
       <c r="D118" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G118" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4736,22 +5102,22 @@
         <v>129</v>
       </c>
       <c r="B119" t="s">
-        <v>380</v>
+        <v>431</v>
       </c>
       <c r="C119" t="s">
-        <v>633</v>
+        <v>755</v>
       </c>
       <c r="D119" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E119" t="s">
-        <v>681</v>
+        <v>803</v>
       </c>
       <c r="F119" t="s">
-        <v>735</v>
+        <v>857</v>
       </c>
       <c r="G119" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4759,19 +5125,19 @@
         <v>130</v>
       </c>
       <c r="B120" t="s">
-        <v>455</v>
+        <v>506</v>
       </c>
       <c r="C120" t="s">
-        <v>633</v>
+        <v>755</v>
       </c>
       <c r="D120" t="s">
-        <v>649</v>
+        <v>771</v>
       </c>
       <c r="E120" t="s">
-        <v>682</v>
+        <v>804</v>
       </c>
       <c r="G120" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4779,16 +5145,16 @@
         <v>131</v>
       </c>
       <c r="B121" t="s">
-        <v>456</v>
+        <v>507</v>
       </c>
       <c r="C121" t="s">
-        <v>633</v>
+        <v>755</v>
       </c>
       <c r="D121" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G121" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4796,16 +5162,16 @@
         <v>132</v>
       </c>
       <c r="B122" t="s">
-        <v>457</v>
+        <v>508</v>
       </c>
       <c r="C122" t="s">
-        <v>631</v>
+        <v>753</v>
       </c>
       <c r="D122" t="s">
-        <v>650</v>
+        <v>772</v>
       </c>
       <c r="G122" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4813,22 +5179,22 @@
         <v>133</v>
       </c>
       <c r="B123" t="s">
-        <v>458</v>
+        <v>509</v>
       </c>
       <c r="C123" t="s">
-        <v>631</v>
+        <v>753</v>
       </c>
       <c r="D123" t="s">
-        <v>651</v>
+        <v>773</v>
       </c>
       <c r="E123" t="s">
-        <v>683</v>
+        <v>805</v>
       </c>
       <c r="F123" t="s">
-        <v>736</v>
+        <v>858</v>
       </c>
       <c r="G123" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4836,16 +5202,16 @@
         <v>134</v>
       </c>
       <c r="B124" t="s">
-        <v>459</v>
+        <v>510</v>
       </c>
       <c r="C124" t="s">
-        <v>631</v>
+        <v>753</v>
       </c>
       <c r="D124" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G124" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4853,16 +5219,16 @@
         <v>135</v>
       </c>
       <c r="B125" t="s">
-        <v>460</v>
+        <v>511</v>
       </c>
       <c r="C125" t="s">
-        <v>631</v>
+        <v>753</v>
       </c>
       <c r="D125" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G125" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4870,16 +5236,16 @@
         <v>136</v>
       </c>
       <c r="B126" t="s">
-        <v>461</v>
+        <v>512</v>
       </c>
       <c r="C126" t="s">
-        <v>631</v>
+        <v>753</v>
       </c>
       <c r="D126" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G126" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4887,16 +5253,16 @@
         <v>137</v>
       </c>
       <c r="B127" t="s">
-        <v>462</v>
+        <v>513</v>
       </c>
       <c r="C127" t="s">
-        <v>631</v>
+        <v>753</v>
       </c>
       <c r="D127" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G127" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4904,19 +5270,19 @@
         <v>138</v>
       </c>
       <c r="B128" t="s">
-        <v>463</v>
+        <v>514</v>
       </c>
       <c r="C128" t="s">
-        <v>631</v>
+        <v>753</v>
       </c>
       <c r="D128" t="s">
-        <v>652</v>
+        <v>774</v>
       </c>
       <c r="E128" t="s">
-        <v>684</v>
+        <v>806</v>
       </c>
       <c r="G128" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4924,22 +5290,22 @@
         <v>139</v>
       </c>
       <c r="B129" t="s">
-        <v>464</v>
+        <v>515</v>
       </c>
       <c r="C129" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D129" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E129" t="s">
-        <v>685</v>
+        <v>807</v>
       </c>
       <c r="F129" t="s">
-        <v>737</v>
+        <v>859</v>
       </c>
       <c r="G129" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4947,16 +5313,16 @@
         <v>140</v>
       </c>
       <c r="B130" t="s">
-        <v>465</v>
+        <v>516</v>
       </c>
       <c r="C130" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D130" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G130" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4964,13 +5330,13 @@
         <v>141</v>
       </c>
       <c r="C131" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D131" t="s">
-        <v>653</v>
+        <v>775</v>
       </c>
       <c r="E131" t="s">
-        <v>686</v>
+        <v>808</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4978,19 +5344,19 @@
         <v>142</v>
       </c>
       <c r="B132" t="s">
-        <v>466</v>
+        <v>517</v>
       </c>
       <c r="C132" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D132" t="s">
-        <v>654</v>
+        <v>776</v>
       </c>
       <c r="E132" t="s">
-        <v>687</v>
+        <v>809</v>
       </c>
       <c r="G132" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4998,19 +5364,19 @@
         <v>143</v>
       </c>
       <c r="B133" t="s">
-        <v>467</v>
+        <v>518</v>
       </c>
       <c r="C133" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D133" t="s">
-        <v>655</v>
+        <v>777</v>
       </c>
       <c r="E133" t="s">
-        <v>688</v>
+        <v>810</v>
       </c>
       <c r="G133" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -5018,10 +5384,10 @@
         <v>144</v>
       </c>
       <c r="C134" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D134" t="s">
-        <v>656</v>
+        <v>778</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -5029,10 +5395,10 @@
         <v>145</v>
       </c>
       <c r="C135" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D135" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -5040,16 +5406,16 @@
         <v>146</v>
       </c>
       <c r="B136" t="s">
-        <v>468</v>
+        <v>519</v>
       </c>
       <c r="C136" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D136" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G136" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -5057,16 +5423,16 @@
         <v>147</v>
       </c>
       <c r="B137" t="s">
-        <v>469</v>
+        <v>520</v>
       </c>
       <c r="C137" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D137" t="s">
-        <v>653</v>
+        <v>775</v>
       </c>
       <c r="G137" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -5074,10 +5440,10 @@
         <v>148</v>
       </c>
       <c r="C138" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D138" t="s">
-        <v>657</v>
+        <v>779</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -5085,10 +5451,10 @@
         <v>149</v>
       </c>
       <c r="C139" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D139" t="s">
-        <v>658</v>
+        <v>780</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -5096,10 +5462,10 @@
         <v>150</v>
       </c>
       <c r="C140" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D140" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -5107,16 +5473,16 @@
         <v>151</v>
       </c>
       <c r="B141" t="s">
-        <v>385</v>
+        <v>436</v>
       </c>
       <c r="C141" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D141" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G141" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -5124,22 +5490,22 @@
         <v>152</v>
       </c>
       <c r="B142" t="s">
-        <v>470</v>
+        <v>521</v>
       </c>
       <c r="C142" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D142" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E142" t="s">
-        <v>689</v>
+        <v>811</v>
       </c>
       <c r="F142" t="s">
-        <v>738</v>
+        <v>860</v>
       </c>
       <c r="G142" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -5147,16 +5513,16 @@
         <v>153</v>
       </c>
       <c r="B143" t="s">
-        <v>471</v>
+        <v>522</v>
       </c>
       <c r="C143" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D143" t="s">
-        <v>657</v>
+        <v>779</v>
       </c>
       <c r="G143" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -5164,13 +5530,13 @@
         <v>154</v>
       </c>
       <c r="C144" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D144" t="s">
-        <v>659</v>
+        <v>781</v>
       </c>
       <c r="E144" t="s">
-        <v>690</v>
+        <v>812</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -5178,10 +5544,10 @@
         <v>155</v>
       </c>
       <c r="C145" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D145" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -5189,19 +5555,19 @@
         <v>156</v>
       </c>
       <c r="B146" t="s">
-        <v>472</v>
+        <v>523</v>
       </c>
       <c r="C146" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D146" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="F146" t="s">
-        <v>739</v>
+        <v>861</v>
       </c>
       <c r="G146" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -5209,22 +5575,22 @@
         <v>157</v>
       </c>
       <c r="B147" t="s">
-        <v>473</v>
+        <v>524</v>
       </c>
       <c r="C147" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D147" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E147" t="s">
-        <v>691</v>
+        <v>813</v>
       </c>
       <c r="F147" t="s">
-        <v>740</v>
+        <v>862</v>
       </c>
       <c r="G147" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5232,19 +5598,19 @@
         <v>158</v>
       </c>
       <c r="B148" t="s">
-        <v>474</v>
+        <v>525</v>
       </c>
       <c r="C148" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D148" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E148" t="s">
-        <v>692</v>
+        <v>814</v>
       </c>
       <c r="G148" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5252,19 +5618,19 @@
         <v>159</v>
       </c>
       <c r="B149" t="s">
-        <v>475</v>
+        <v>526</v>
       </c>
       <c r="C149" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D149" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E149" t="s">
-        <v>693</v>
+        <v>815</v>
       </c>
       <c r="G149" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5272,19 +5638,19 @@
         <v>160</v>
       </c>
       <c r="B150" t="s">
-        <v>476</v>
+        <v>527</v>
       </c>
       <c r="C150" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D150" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E150" t="s">
-        <v>694</v>
+        <v>816</v>
       </c>
       <c r="G150" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5292,19 +5658,19 @@
         <v>161</v>
       </c>
       <c r="B151" t="s">
-        <v>477</v>
+        <v>528</v>
       </c>
       <c r="C151" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D151" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E151" t="s">
-        <v>695</v>
+        <v>817</v>
       </c>
       <c r="G151" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5312,19 +5678,19 @@
         <v>162</v>
       </c>
       <c r="B152" t="s">
-        <v>478</v>
+        <v>529</v>
       </c>
       <c r="C152" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D152" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E152" t="s">
-        <v>696</v>
+        <v>818</v>
       </c>
       <c r="G152" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5332,10 +5698,10 @@
         <v>163</v>
       </c>
       <c r="C153" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D153" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5343,19 +5709,19 @@
         <v>164</v>
       </c>
       <c r="B154" t="s">
-        <v>479</v>
+        <v>530</v>
       </c>
       <c r="C154" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D154" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E154" t="s">
-        <v>697</v>
+        <v>819</v>
       </c>
       <c r="G154" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5363,16 +5729,16 @@
         <v>165</v>
       </c>
       <c r="B155" t="s">
-        <v>480</v>
+        <v>531</v>
       </c>
       <c r="C155" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D155" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G155" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5380,16 +5746,16 @@
         <v>166</v>
       </c>
       <c r="B156" t="s">
-        <v>481</v>
+        <v>532</v>
       </c>
       <c r="C156" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D156" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G156" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5397,22 +5763,22 @@
         <v>167</v>
       </c>
       <c r="B157" t="s">
-        <v>482</v>
+        <v>533</v>
       </c>
       <c r="C157" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D157" t="s">
-        <v>660</v>
+        <v>782</v>
       </c>
       <c r="E157" t="s">
-        <v>698</v>
+        <v>820</v>
       </c>
       <c r="F157" t="s">
-        <v>741</v>
+        <v>863</v>
       </c>
       <c r="G157" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5420,19 +5786,19 @@
         <v>168</v>
       </c>
       <c r="B158" t="s">
-        <v>483</v>
+        <v>534</v>
       </c>
       <c r="C158" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D158" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E158" t="s">
-        <v>699</v>
+        <v>821</v>
       </c>
       <c r="G158" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5440,19 +5806,19 @@
         <v>169</v>
       </c>
       <c r="B159" t="s">
-        <v>484</v>
+        <v>535</v>
       </c>
       <c r="C159" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D159" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E159" t="s">
-        <v>700</v>
+        <v>822</v>
       </c>
       <c r="G159" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5460,19 +5826,19 @@
         <v>170</v>
       </c>
       <c r="B160" t="s">
-        <v>485</v>
+        <v>536</v>
       </c>
       <c r="C160" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D160" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E160" t="s">
-        <v>701</v>
+        <v>823</v>
       </c>
       <c r="G160" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5480,19 +5846,19 @@
         <v>171</v>
       </c>
       <c r="B161" t="s">
-        <v>486</v>
+        <v>537</v>
       </c>
       <c r="C161" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D161" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="E161" t="s">
-        <v>702</v>
+        <v>824</v>
       </c>
       <c r="G161" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5500,16 +5866,16 @@
         <v>172</v>
       </c>
       <c r="B162" t="s">
-        <v>487</v>
+        <v>538</v>
       </c>
       <c r="C162" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D162" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G162" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5517,19 +5883,19 @@
         <v>173</v>
       </c>
       <c r="B163" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="C163" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D163" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E163" t="s">
-        <v>703</v>
+        <v>825</v>
       </c>
       <c r="G163" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5537,19 +5903,19 @@
         <v>174</v>
       </c>
       <c r="B164" t="s">
-        <v>489</v>
+        <v>540</v>
       </c>
       <c r="C164" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D164" t="s">
-        <v>662</v>
+        <v>784</v>
       </c>
       <c r="E164" t="s">
-        <v>704</v>
+        <v>826</v>
       </c>
       <c r="G164" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5557,13 +5923,13 @@
         <v>175</v>
       </c>
       <c r="C165" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D165" t="s">
-        <v>653</v>
+        <v>775</v>
       </c>
       <c r="E165" t="s">
-        <v>705</v>
+        <v>827</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5571,19 +5937,19 @@
         <v>176</v>
       </c>
       <c r="B166" t="s">
-        <v>490</v>
+        <v>541</v>
       </c>
       <c r="C166" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D166" t="s">
-        <v>663</v>
+        <v>785</v>
       </c>
       <c r="E166" t="s">
-        <v>706</v>
+        <v>828</v>
       </c>
       <c r="G166" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5591,19 +5957,19 @@
         <v>177</v>
       </c>
       <c r="B167" t="s">
-        <v>491</v>
+        <v>542</v>
       </c>
       <c r="C167" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D167" t="s">
-        <v>664</v>
+        <v>786</v>
       </c>
       <c r="E167" t="s">
-        <v>707</v>
+        <v>829</v>
       </c>
       <c r="G167" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5611,19 +5977,19 @@
         <v>178</v>
       </c>
       <c r="B168" t="s">
-        <v>492</v>
+        <v>543</v>
       </c>
       <c r="C168" t="s">
-        <v>622</v>
+        <v>744</v>
       </c>
       <c r="D168" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E168" t="s">
-        <v>708</v>
+        <v>830</v>
       </c>
       <c r="G168" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5631,19 +5997,19 @@
         <v>179</v>
       </c>
       <c r="B169" t="s">
-        <v>493</v>
+        <v>544</v>
       </c>
       <c r="C169" t="s">
-        <v>622</v>
+        <v>744</v>
       </c>
       <c r="D169" t="s">
-        <v>665</v>
+        <v>787</v>
       </c>
       <c r="E169" t="s">
-        <v>709</v>
+        <v>831</v>
       </c>
       <c r="G169" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5651,13 +6017,13 @@
         <v>180</v>
       </c>
       <c r="C170" t="s">
-        <v>622</v>
+        <v>744</v>
       </c>
       <c r="D170" t="s">
-        <v>666</v>
+        <v>788</v>
       </c>
       <c r="E170" t="s">
-        <v>710</v>
+        <v>832</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5665,13 +6031,13 @@
         <v>181</v>
       </c>
       <c r="C171" t="s">
-        <v>622</v>
+        <v>744</v>
       </c>
       <c r="D171" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E171" t="s">
-        <v>711</v>
+        <v>833</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5679,13 +6045,13 @@
         <v>182</v>
       </c>
       <c r="C172" t="s">
-        <v>622</v>
+        <v>744</v>
       </c>
       <c r="D172" t="s">
-        <v>653</v>
+        <v>775</v>
       </c>
       <c r="E172" t="s">
-        <v>712</v>
+        <v>834</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5693,16 +6059,16 @@
         <v>183</v>
       </c>
       <c r="B173" t="s">
-        <v>494</v>
+        <v>545</v>
       </c>
       <c r="C173" t="s">
-        <v>634</v>
+        <v>756</v>
       </c>
       <c r="D173" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G173" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5710,19 +6076,19 @@
         <v>184</v>
       </c>
       <c r="B174" t="s">
-        <v>495</v>
+        <v>546</v>
       </c>
       <c r="C174" t="s">
-        <v>634</v>
+        <v>756</v>
       </c>
       <c r="D174" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="F174" t="s">
-        <v>742</v>
+        <v>864</v>
       </c>
       <c r="G174" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5730,19 +6096,19 @@
         <v>185</v>
       </c>
       <c r="B175" t="s">
-        <v>496</v>
+        <v>547</v>
       </c>
       <c r="C175" t="s">
-        <v>634</v>
+        <v>756</v>
       </c>
       <c r="D175" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="F175" t="s">
-        <v>743</v>
+        <v>865</v>
       </c>
       <c r="G175" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5750,10 +6116,10 @@
         <v>186</v>
       </c>
       <c r="C176" t="s">
-        <v>635</v>
+        <v>757</v>
       </c>
       <c r="D176" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5761,10 +6127,10 @@
         <v>187</v>
       </c>
       <c r="C177" t="s">
-        <v>635</v>
+        <v>757</v>
       </c>
       <c r="D177" t="s">
-        <v>667</v>
+        <v>789</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5772,10 +6138,10 @@
         <v>188</v>
       </c>
       <c r="C178" t="s">
-        <v>635</v>
+        <v>757</v>
       </c>
       <c r="D178" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5783,22 +6149,22 @@
         <v>189</v>
       </c>
       <c r="B179" t="s">
-        <v>497</v>
+        <v>548</v>
       </c>
       <c r="C179" t="s">
-        <v>636</v>
+        <v>758</v>
       </c>
       <c r="D179" t="s">
-        <v>667</v>
+        <v>789</v>
       </c>
       <c r="E179" t="s">
-        <v>713</v>
+        <v>835</v>
       </c>
       <c r="F179" t="s">
-        <v>744</v>
+        <v>866</v>
       </c>
       <c r="G179" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5806,10 +6172,10 @@
         <v>190</v>
       </c>
       <c r="C180" t="s">
-        <v>636</v>
+        <v>758</v>
       </c>
       <c r="D180" t="s">
-        <v>668</v>
+        <v>790</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5817,10 +6183,10 @@
         <v>191</v>
       </c>
       <c r="C181" t="s">
-        <v>636</v>
+        <v>758</v>
       </c>
       <c r="D181" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5828,19 +6194,19 @@
         <v>192</v>
       </c>
       <c r="B182" t="s">
-        <v>498</v>
+        <v>549</v>
       </c>
       <c r="C182" t="s">
-        <v>637</v>
+        <v>759</v>
       </c>
       <c r="D182" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E182" t="s">
-        <v>714</v>
+        <v>836</v>
       </c>
       <c r="G182" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5848,19 +6214,19 @@
         <v>193</v>
       </c>
       <c r="B183" t="s">
-        <v>499</v>
+        <v>550</v>
       </c>
       <c r="C183" t="s">
-        <v>637</v>
+        <v>759</v>
       </c>
       <c r="D183" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="F183" t="s">
-        <v>745</v>
+        <v>867</v>
       </c>
       <c r="G183" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5868,10 +6234,10 @@
         <v>194</v>
       </c>
       <c r="C184" t="s">
-        <v>637</v>
+        <v>759</v>
       </c>
       <c r="D184" t="s">
-        <v>668</v>
+        <v>790</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5879,13 +6245,13 @@
         <v>195</v>
       </c>
       <c r="C185" t="s">
-        <v>637</v>
+        <v>759</v>
       </c>
       <c r="D185" t="s">
-        <v>669</v>
+        <v>791</v>
       </c>
       <c r="F185" t="s">
-        <v>746</v>
+        <v>868</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5893,13 +6259,13 @@
         <v>196</v>
       </c>
       <c r="C186" t="s">
-        <v>638</v>
+        <v>760</v>
       </c>
       <c r="D186" t="s">
-        <v>670</v>
+        <v>792</v>
       </c>
       <c r="E186" t="s">
-        <v>715</v>
+        <v>837</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5907,13 +6273,13 @@
         <v>197</v>
       </c>
       <c r="C187" t="s">
-        <v>638</v>
+        <v>760</v>
       </c>
       <c r="D187" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E187" t="s">
-        <v>716</v>
+        <v>838</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5921,13 +6287,13 @@
         <v>198</v>
       </c>
       <c r="C188" t="s">
-        <v>638</v>
+        <v>760</v>
       </c>
       <c r="D188" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E188" t="s">
-        <v>717</v>
+        <v>839</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5935,13 +6301,13 @@
         <v>199</v>
       </c>
       <c r="C189" t="s">
-        <v>638</v>
+        <v>760</v>
       </c>
       <c r="D189" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E189" t="s">
-        <v>718</v>
+        <v>840</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5949,13 +6315,13 @@
         <v>200</v>
       </c>
       <c r="C190" t="s">
-        <v>638</v>
+        <v>760</v>
       </c>
       <c r="D190" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E190" t="s">
-        <v>719</v>
+        <v>841</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5963,10 +6329,10 @@
         <v>201</v>
       </c>
       <c r="C191" t="s">
-        <v>638</v>
+        <v>760</v>
       </c>
       <c r="D191" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -5974,10 +6340,10 @@
         <v>202</v>
       </c>
       <c r="C192" t="s">
-        <v>638</v>
+        <v>760</v>
       </c>
       <c r="D192" t="s">
-        <v>671</v>
+        <v>793</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -5985,10 +6351,10 @@
         <v>203</v>
       </c>
       <c r="C193" t="s">
-        <v>638</v>
+        <v>760</v>
       </c>
       <c r="D193" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -5996,16 +6362,16 @@
         <v>204</v>
       </c>
       <c r="B194" t="s">
-        <v>500</v>
+        <v>551</v>
       </c>
       <c r="C194" t="s">
-        <v>638</v>
+        <v>760</v>
       </c>
       <c r="D194" t="s">
-        <v>650</v>
+        <v>772</v>
       </c>
       <c r="G194" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6013,16 +6379,16 @@
         <v>205</v>
       </c>
       <c r="B195" t="s">
-        <v>501</v>
+        <v>552</v>
       </c>
       <c r="C195" t="s">
-        <v>638</v>
+        <v>760</v>
       </c>
       <c r="D195" t="s">
-        <v>650</v>
+        <v>772</v>
       </c>
       <c r="G195" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6030,19 +6396,19 @@
         <v>206</v>
       </c>
       <c r="B196" t="s">
-        <v>502</v>
+        <v>553</v>
       </c>
       <c r="C196" t="s">
-        <v>625</v>
+        <v>747</v>
       </c>
       <c r="D196" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="F196" t="s">
-        <v>747</v>
+        <v>869</v>
       </c>
       <c r="G196" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6050,22 +6416,22 @@
         <v>207</v>
       </c>
       <c r="B197" t="s">
-        <v>503</v>
+        <v>554</v>
       </c>
       <c r="C197" t="s">
-        <v>625</v>
+        <v>747</v>
       </c>
       <c r="D197" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E197" t="s">
-        <v>720</v>
+        <v>842</v>
       </c>
       <c r="F197" t="s">
-        <v>748</v>
+        <v>870</v>
       </c>
       <c r="G197" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6073,22 +6439,22 @@
         <v>208</v>
       </c>
       <c r="B198" t="s">
-        <v>504</v>
+        <v>555</v>
       </c>
       <c r="C198" t="s">
-        <v>625</v>
+        <v>747</v>
       </c>
       <c r="D198" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E198" t="s">
-        <v>721</v>
+        <v>843</v>
       </c>
       <c r="F198" t="s">
-        <v>749</v>
+        <v>871</v>
       </c>
       <c r="G198" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6096,22 +6462,22 @@
         <v>209</v>
       </c>
       <c r="B199" t="s">
-        <v>505</v>
+        <v>556</v>
       </c>
       <c r="C199" t="s">
-        <v>625</v>
+        <v>747</v>
       </c>
       <c r="D199" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E199" t="s">
-        <v>722</v>
+        <v>844</v>
       </c>
       <c r="F199" t="s">
-        <v>750</v>
+        <v>872</v>
       </c>
       <c r="G199" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6119,16 +6485,16 @@
         <v>210</v>
       </c>
       <c r="B200" t="s">
-        <v>506</v>
+        <v>557</v>
       </c>
       <c r="C200" t="s">
-        <v>639</v>
+        <v>761</v>
       </c>
       <c r="D200" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G200" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6136,10 +6502,10 @@
         <v>211</v>
       </c>
       <c r="C201" t="s">
-        <v>639</v>
+        <v>761</v>
       </c>
       <c r="D201" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6147,10 +6513,10 @@
         <v>212</v>
       </c>
       <c r="C202" t="s">
-        <v>639</v>
+        <v>761</v>
       </c>
       <c r="D202" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6158,10 +6524,10 @@
         <v>213</v>
       </c>
       <c r="C203" t="s">
-        <v>639</v>
+        <v>761</v>
       </c>
       <c r="D203" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6169,16 +6535,16 @@
         <v>214</v>
       </c>
       <c r="B204" t="s">
-        <v>385</v>
+        <v>436</v>
       </c>
       <c r="C204" t="s">
-        <v>640</v>
+        <v>762</v>
       </c>
       <c r="D204" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G204" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6186,10 +6552,10 @@
         <v>215</v>
       </c>
       <c r="C205" t="s">
-        <v>640</v>
+        <v>762</v>
       </c>
       <c r="D205" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6197,10 +6563,10 @@
         <v>216</v>
       </c>
       <c r="C206" t="s">
-        <v>640</v>
+        <v>762</v>
       </c>
       <c r="D206" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6208,19 +6574,19 @@
         <v>217</v>
       </c>
       <c r="B207" t="s">
-        <v>507</v>
+        <v>558</v>
       </c>
       <c r="C207" t="s">
-        <v>640</v>
+        <v>762</v>
       </c>
       <c r="D207" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E207" t="s">
-        <v>723</v>
+        <v>845</v>
       </c>
       <c r="G207" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6228,13 +6594,13 @@
         <v>218</v>
       </c>
       <c r="C208" t="s">
-        <v>640</v>
+        <v>762</v>
       </c>
       <c r="D208" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E208" t="s">
-        <v>724</v>
+        <v>846</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6242,10 +6608,10 @@
         <v>219</v>
       </c>
       <c r="C209" t="s">
-        <v>640</v>
+        <v>762</v>
       </c>
       <c r="D209" t="s">
-        <v>656</v>
+        <v>778</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6253,19 +6619,19 @@
         <v>220</v>
       </c>
       <c r="B210" t="s">
-        <v>508</v>
+        <v>559</v>
       </c>
       <c r="C210" t="s">
-        <v>641</v>
+        <v>763</v>
       </c>
       <c r="D210" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E210" t="s">
-        <v>725</v>
+        <v>847</v>
       </c>
       <c r="G210" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6273,16 +6639,16 @@
         <v>221</v>
       </c>
       <c r="B211" t="s">
-        <v>509</v>
+        <v>560</v>
       </c>
       <c r="C211" t="s">
-        <v>641</v>
+        <v>763</v>
       </c>
       <c r="D211" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G211" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6290,13 +6656,13 @@
         <v>222</v>
       </c>
       <c r="C212" t="s">
-        <v>641</v>
+        <v>763</v>
       </c>
       <c r="D212" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E212" t="s">
-        <v>726</v>
+        <v>848</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6304,13 +6670,13 @@
         <v>223</v>
       </c>
       <c r="C213" t="s">
-        <v>641</v>
+        <v>763</v>
       </c>
       <c r="D213" t="s">
-        <v>660</v>
+        <v>782</v>
       </c>
       <c r="E213" t="s">
-        <v>727</v>
+        <v>849</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6318,16 +6684,16 @@
         <v>224</v>
       </c>
       <c r="B214" t="s">
-        <v>510</v>
+        <v>561</v>
       </c>
       <c r="C214" t="s">
-        <v>624</v>
+        <v>746</v>
       </c>
       <c r="D214" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G214" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6335,16 +6701,16 @@
         <v>225</v>
       </c>
       <c r="B215" t="s">
-        <v>511</v>
+        <v>562</v>
       </c>
       <c r="C215" t="s">
-        <v>624</v>
+        <v>746</v>
       </c>
       <c r="D215" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G215" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6352,13 +6718,13 @@
         <v>226</v>
       </c>
       <c r="C216" t="s">
-        <v>624</v>
+        <v>746</v>
       </c>
       <c r="D216" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E216" t="s">
-        <v>728</v>
+        <v>850</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6366,19 +6732,19 @@
         <v>227</v>
       </c>
       <c r="B217" t="s">
-        <v>512</v>
+        <v>563</v>
       </c>
       <c r="C217" t="s">
-        <v>642</v>
+        <v>764</v>
       </c>
       <c r="D217" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E217" t="s">
-        <v>729</v>
+        <v>851</v>
       </c>
       <c r="G217" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6386,19 +6752,19 @@
         <v>228</v>
       </c>
       <c r="B218" t="s">
-        <v>513</v>
+        <v>564</v>
       </c>
       <c r="C218" t="s">
-        <v>642</v>
+        <v>764</v>
       </c>
       <c r="D218" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E218" t="s">
-        <v>729</v>
+        <v>851</v>
       </c>
       <c r="G218" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6406,19 +6772,19 @@
         <v>229</v>
       </c>
       <c r="B219" t="s">
-        <v>352</v>
+        <v>403</v>
       </c>
       <c r="C219" t="s">
-        <v>643</v>
+        <v>765</v>
       </c>
       <c r="D219" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E219" t="s">
-        <v>730</v>
+        <v>852</v>
       </c>
       <c r="G219" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6426,10 +6792,10 @@
         <v>230</v>
       </c>
       <c r="C220" t="s">
-        <v>643</v>
+        <v>765</v>
       </c>
       <c r="D220" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6437,16 +6803,16 @@
         <v>231</v>
       </c>
       <c r="B221" t="s">
-        <v>514</v>
+        <v>565</v>
       </c>
       <c r="C221" t="s">
-        <v>643</v>
+        <v>765</v>
       </c>
       <c r="D221" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G221" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6454,19 +6820,19 @@
         <v>232</v>
       </c>
       <c r="B222" t="s">
-        <v>515</v>
+        <v>566</v>
       </c>
       <c r="C222" t="s">
-        <v>644</v>
+        <v>766</v>
       </c>
       <c r="D222" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="E222" t="s">
-        <v>731</v>
+        <v>853</v>
       </c>
       <c r="G222" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6474,16 +6840,16 @@
         <v>233</v>
       </c>
       <c r="B223" t="s">
-        <v>516</v>
+        <v>567</v>
       </c>
       <c r="C223" t="s">
-        <v>644</v>
+        <v>766</v>
       </c>
       <c r="D223" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G223" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6491,16 +6857,16 @@
         <v>234</v>
       </c>
       <c r="B224" t="s">
-        <v>517</v>
+        <v>568</v>
       </c>
       <c r="C224" t="s">
-        <v>644</v>
+        <v>766</v>
       </c>
       <c r="D224" t="s">
-        <v>669</v>
+        <v>791</v>
       </c>
       <c r="G224" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6508,19 +6874,19 @@
         <v>235</v>
       </c>
       <c r="B225" t="s">
-        <v>518</v>
+        <v>569</v>
       </c>
       <c r="C225" t="s">
-        <v>644</v>
+        <v>766</v>
       </c>
       <c r="D225" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="F225" t="s">
-        <v>751</v>
+        <v>873</v>
       </c>
       <c r="G225" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6528,16 +6894,16 @@
         <v>236</v>
       </c>
       <c r="B226" t="s">
-        <v>519</v>
+        <v>570</v>
       </c>
       <c r="C226" t="s">
-        <v>644</v>
+        <v>766</v>
       </c>
       <c r="D226" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G226" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6545,10 +6911,10 @@
         <v>237</v>
       </c>
       <c r="C227" t="s">
-        <v>644</v>
+        <v>766</v>
       </c>
       <c r="D227" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6556,16 +6922,16 @@
         <v>238</v>
       </c>
       <c r="B228" t="s">
-        <v>520</v>
+        <v>571</v>
       </c>
       <c r="C228" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D228" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G228" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6573,16 +6939,16 @@
         <v>239</v>
       </c>
       <c r="B229" t="s">
-        <v>521</v>
+        <v>572</v>
       </c>
       <c r="C229" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D229" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G229" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6590,16 +6956,16 @@
         <v>240</v>
       </c>
       <c r="B230" t="s">
-        <v>522</v>
+        <v>573</v>
       </c>
       <c r="C230" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D230" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G230" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6607,16 +6973,16 @@
         <v>241</v>
       </c>
       <c r="B231" t="s">
-        <v>523</v>
+        <v>574</v>
       </c>
       <c r="C231" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D231" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G231" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6624,16 +6990,16 @@
         <v>242</v>
       </c>
       <c r="B232" t="s">
-        <v>524</v>
+        <v>575</v>
       </c>
       <c r="C232" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D232" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G232" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6641,16 +7007,16 @@
         <v>243</v>
       </c>
       <c r="B233" t="s">
-        <v>525</v>
+        <v>576</v>
       </c>
       <c r="C233" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D233" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G233" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6658,16 +7024,16 @@
         <v>244</v>
       </c>
       <c r="B234" t="s">
-        <v>526</v>
+        <v>577</v>
       </c>
       <c r="C234" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D234" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G234" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -6675,16 +7041,16 @@
         <v>245</v>
       </c>
       <c r="B235" t="s">
-        <v>527</v>
+        <v>578</v>
       </c>
       <c r="C235" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D235" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G235" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -6692,16 +7058,16 @@
         <v>246</v>
       </c>
       <c r="B236" t="s">
-        <v>528</v>
+        <v>579</v>
       </c>
       <c r="C236" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D236" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G236" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -6709,16 +7075,16 @@
         <v>247</v>
       </c>
       <c r="B237" t="s">
-        <v>529</v>
+        <v>580</v>
       </c>
       <c r="C237" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D237" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G237" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -6726,16 +7092,16 @@
         <v>248</v>
       </c>
       <c r="B238" t="s">
-        <v>530</v>
+        <v>581</v>
       </c>
       <c r="C238" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D238" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G238" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -6743,16 +7109,16 @@
         <v>249</v>
       </c>
       <c r="B239" t="s">
-        <v>531</v>
+        <v>582</v>
       </c>
       <c r="C239" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D239" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G239" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -6760,16 +7126,16 @@
         <v>250</v>
       </c>
       <c r="B240" t="s">
-        <v>532</v>
+        <v>583</v>
       </c>
       <c r="C240" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D240" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G240" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -6777,16 +7143,16 @@
         <v>251</v>
       </c>
       <c r="B241" t="s">
-        <v>533</v>
+        <v>584</v>
       </c>
       <c r="C241" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D241" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G241" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -6794,16 +7160,16 @@
         <v>252</v>
       </c>
       <c r="B242" t="s">
-        <v>534</v>
+        <v>585</v>
       </c>
       <c r="C242" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D242" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G242" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -6811,16 +7177,16 @@
         <v>253</v>
       </c>
       <c r="B243" t="s">
-        <v>535</v>
+        <v>586</v>
       </c>
       <c r="C243" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D243" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G243" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -6828,16 +7194,16 @@
         <v>254</v>
       </c>
       <c r="B244" t="s">
-        <v>536</v>
+        <v>587</v>
       </c>
       <c r="C244" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D244" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G244" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -6845,16 +7211,16 @@
         <v>255</v>
       </c>
       <c r="B245" t="s">
-        <v>537</v>
+        <v>588</v>
       </c>
       <c r="C245" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D245" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G245" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -6862,16 +7228,16 @@
         <v>256</v>
       </c>
       <c r="B246" t="s">
-        <v>538</v>
+        <v>589</v>
       </c>
       <c r="C246" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D246" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G246" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -6879,16 +7245,16 @@
         <v>257</v>
       </c>
       <c r="B247" t="s">
-        <v>539</v>
+        <v>590</v>
       </c>
       <c r="C247" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D247" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G247" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -6896,16 +7262,16 @@
         <v>258</v>
       </c>
       <c r="B248" t="s">
-        <v>540</v>
+        <v>591</v>
       </c>
       <c r="C248" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D248" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G248" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -6913,16 +7279,16 @@
         <v>259</v>
       </c>
       <c r="B249" t="s">
-        <v>541</v>
+        <v>592</v>
       </c>
       <c r="C249" t="s">
-        <v>631</v>
+        <v>753</v>
       </c>
       <c r="D249" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G249" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -6930,16 +7296,16 @@
         <v>260</v>
       </c>
       <c r="B250" t="s">
-        <v>542</v>
+        <v>593</v>
       </c>
       <c r="C250" t="s">
-        <v>631</v>
+        <v>753</v>
       </c>
       <c r="D250" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G250" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -6947,16 +7313,16 @@
         <v>261</v>
       </c>
       <c r="B251" t="s">
-        <v>543</v>
+        <v>594</v>
       </c>
       <c r="C251" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D251" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G251" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -6964,16 +7330,16 @@
         <v>262</v>
       </c>
       <c r="B252" t="s">
-        <v>544</v>
+        <v>595</v>
       </c>
       <c r="C252" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D252" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G252" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -6981,16 +7347,16 @@
         <v>263</v>
       </c>
       <c r="B253" t="s">
-        <v>545</v>
+        <v>596</v>
       </c>
       <c r="C253" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D253" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G253" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -6998,16 +7364,16 @@
         <v>264</v>
       </c>
       <c r="B254" t="s">
-        <v>546</v>
+        <v>597</v>
       </c>
       <c r="C254" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D254" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G254" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7015,16 +7381,16 @@
         <v>265</v>
       </c>
       <c r="B255" t="s">
-        <v>547</v>
+        <v>598</v>
       </c>
       <c r="C255" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D255" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G255" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7032,16 +7398,16 @@
         <v>266</v>
       </c>
       <c r="B256" t="s">
-        <v>548</v>
+        <v>599</v>
       </c>
       <c r="C256" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D256" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G256" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7049,16 +7415,16 @@
         <v>267</v>
       </c>
       <c r="B257" t="s">
-        <v>549</v>
+        <v>600</v>
       </c>
       <c r="C257" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D257" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G257" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7066,16 +7432,16 @@
         <v>268</v>
       </c>
       <c r="B258" t="s">
-        <v>550</v>
+        <v>601</v>
       </c>
       <c r="C258" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D258" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G258" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7083,16 +7449,16 @@
         <v>269</v>
       </c>
       <c r="B259" t="s">
-        <v>551</v>
+        <v>602</v>
       </c>
       <c r="C259" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D259" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G259" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7100,16 +7466,16 @@
         <v>270</v>
       </c>
       <c r="B260" t="s">
-        <v>552</v>
+        <v>603</v>
       </c>
       <c r="C260" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D260" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G260" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -7117,16 +7483,16 @@
         <v>271</v>
       </c>
       <c r="B261" t="s">
-        <v>553</v>
+        <v>604</v>
       </c>
       <c r="C261" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D261" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G261" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -7134,16 +7500,16 @@
         <v>272</v>
       </c>
       <c r="B262" t="s">
-        <v>554</v>
+        <v>605</v>
       </c>
       <c r="C262" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D262" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G262" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -7151,16 +7517,16 @@
         <v>273</v>
       </c>
       <c r="B263" t="s">
-        <v>555</v>
+        <v>606</v>
       </c>
       <c r="C263" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D263" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G263" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7168,16 +7534,16 @@
         <v>274</v>
       </c>
       <c r="B264" t="s">
-        <v>556</v>
+        <v>607</v>
       </c>
       <c r="C264" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D264" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G264" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -7185,16 +7551,16 @@
         <v>275</v>
       </c>
       <c r="B265" t="s">
-        <v>557</v>
+        <v>608</v>
       </c>
       <c r="C265" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D265" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="G265" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -7202,16 +7568,16 @@
         <v>276</v>
       </c>
       <c r="B266" t="s">
-        <v>558</v>
+        <v>609</v>
       </c>
       <c r="C266" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D266" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G266" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7219,16 +7585,16 @@
         <v>277</v>
       </c>
       <c r="B267" t="s">
-        <v>559</v>
+        <v>610</v>
       </c>
       <c r="C267" t="s">
-        <v>645</v>
+        <v>767</v>
       </c>
       <c r="D267" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G267" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7236,16 +7602,16 @@
         <v>278</v>
       </c>
       <c r="B268" t="s">
-        <v>560</v>
+        <v>611</v>
       </c>
       <c r="C268" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D268" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G268" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7253,16 +7619,16 @@
         <v>279</v>
       </c>
       <c r="B269" t="s">
-        <v>561</v>
+        <v>612</v>
       </c>
       <c r="C269" t="s">
-        <v>646</v>
+        <v>768</v>
       </c>
       <c r="D269" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G269" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7270,16 +7636,16 @@
         <v>280</v>
       </c>
       <c r="B270" t="s">
-        <v>562</v>
+        <v>613</v>
       </c>
       <c r="C270" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D270" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G270" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7287,16 +7653,16 @@
         <v>281</v>
       </c>
       <c r="B271" t="s">
-        <v>563</v>
+        <v>614</v>
       </c>
       <c r="C271" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D271" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G271" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -7304,16 +7670,16 @@
         <v>282</v>
       </c>
       <c r="B272" t="s">
-        <v>564</v>
+        <v>615</v>
       </c>
       <c r="C272" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D272" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G272" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7321,16 +7687,16 @@
         <v>283</v>
       </c>
       <c r="B273" t="s">
-        <v>565</v>
+        <v>616</v>
       </c>
       <c r="C273" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D273" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G273" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -7338,16 +7704,16 @@
         <v>284</v>
       </c>
       <c r="B274" t="s">
-        <v>566</v>
+        <v>617</v>
       </c>
       <c r="C274" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D274" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G274" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -7355,16 +7721,16 @@
         <v>285</v>
       </c>
       <c r="B275" t="s">
-        <v>567</v>
+        <v>618</v>
       </c>
       <c r="C275" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D275" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G275" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -7372,16 +7738,16 @@
         <v>286</v>
       </c>
       <c r="B276" t="s">
-        <v>568</v>
+        <v>619</v>
       </c>
       <c r="C276" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D276" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G276" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -7389,16 +7755,16 @@
         <v>287</v>
       </c>
       <c r="B277" t="s">
-        <v>569</v>
+        <v>620</v>
       </c>
       <c r="C277" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D277" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G277" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -7406,16 +7772,16 @@
         <v>288</v>
       </c>
       <c r="B278" t="s">
-        <v>570</v>
+        <v>621</v>
       </c>
       <c r="C278" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D278" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G278" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7423,16 +7789,16 @@
         <v>289</v>
       </c>
       <c r="B279" t="s">
-        <v>571</v>
+        <v>622</v>
       </c>
       <c r="C279" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D279" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G279" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7440,16 +7806,16 @@
         <v>290</v>
       </c>
       <c r="B280" t="s">
-        <v>572</v>
+        <v>623</v>
       </c>
       <c r="C280" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D280" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G280" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -7457,16 +7823,16 @@
         <v>291</v>
       </c>
       <c r="B281" t="s">
-        <v>573</v>
+        <v>624</v>
       </c>
       <c r="C281" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D281" t="s">
-        <v>673</v>
+        <v>795</v>
       </c>
       <c r="G281" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7474,16 +7840,16 @@
         <v>292</v>
       </c>
       <c r="B282" t="s">
-        <v>574</v>
+        <v>625</v>
       </c>
       <c r="C282" t="s">
-        <v>628</v>
+        <v>750</v>
       </c>
       <c r="D282" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G282" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -7491,16 +7857,16 @@
         <v>293</v>
       </c>
       <c r="B283" t="s">
-        <v>575</v>
+        <v>626</v>
       </c>
       <c r="C283" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D283" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G283" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -7508,19 +7874,19 @@
         <v>294</v>
       </c>
       <c r="B284" t="s">
-        <v>576</v>
+        <v>627</v>
       </c>
       <c r="C284" t="s">
-        <v>622</v>
+        <v>744</v>
       </c>
       <c r="D284" t="s">
-        <v>647</v>
+        <v>769</v>
       </c>
       <c r="F284" t="s">
-        <v>732</v>
+        <v>854</v>
       </c>
       <c r="G284" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -7528,16 +7894,16 @@
         <v>295</v>
       </c>
       <c r="B285" t="s">
-        <v>577</v>
+        <v>628</v>
       </c>
       <c r="C285" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D285" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G285" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -7545,16 +7911,16 @@
         <v>296</v>
       </c>
       <c r="B286" t="s">
-        <v>578</v>
+        <v>629</v>
       </c>
       <c r="C286" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D286" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G286" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -7562,16 +7928,16 @@
         <v>297</v>
       </c>
       <c r="B287" t="s">
-        <v>579</v>
+        <v>630</v>
       </c>
       <c r="C287" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D287" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G287" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -7579,16 +7945,16 @@
         <v>298</v>
       </c>
       <c r="B288" t="s">
-        <v>580</v>
+        <v>631</v>
       </c>
       <c r="C288" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D288" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G288" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -7596,16 +7962,16 @@
         <v>299</v>
       </c>
       <c r="B289" t="s">
-        <v>581</v>
+        <v>632</v>
       </c>
       <c r="C289" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D289" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G289" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -7613,16 +7979,16 @@
         <v>300</v>
       </c>
       <c r="B290" t="s">
-        <v>582</v>
+        <v>633</v>
       </c>
       <c r="C290" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D290" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G290" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -7630,16 +7996,16 @@
         <v>301</v>
       </c>
       <c r="B291" t="s">
-        <v>583</v>
+        <v>634</v>
       </c>
       <c r="C291" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D291" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G291" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -7647,16 +8013,16 @@
         <v>302</v>
       </c>
       <c r="B292" t="s">
-        <v>584</v>
+        <v>635</v>
       </c>
       <c r="C292" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D292" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G292" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -7664,16 +8030,16 @@
         <v>303</v>
       </c>
       <c r="B293" t="s">
-        <v>585</v>
+        <v>636</v>
       </c>
       <c r="C293" t="s">
-        <v>634</v>
+        <v>756</v>
       </c>
       <c r="D293" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G293" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -7681,16 +8047,16 @@
         <v>304</v>
       </c>
       <c r="B294" t="s">
-        <v>586</v>
+        <v>637</v>
       </c>
       <c r="C294" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D294" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G294" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -7698,16 +8064,16 @@
         <v>140</v>
       </c>
       <c r="B295" t="s">
-        <v>587</v>
+        <v>638</v>
       </c>
       <c r="C295" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D295" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G295" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -7715,16 +8081,16 @@
         <v>305</v>
       </c>
       <c r="B296" t="s">
-        <v>588</v>
+        <v>639</v>
       </c>
       <c r="C296" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D296" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G296" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="297" spans="1:7">
@@ -7732,16 +8098,16 @@
         <v>306</v>
       </c>
       <c r="B297" t="s">
-        <v>589</v>
+        <v>640</v>
       </c>
       <c r="C297" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D297" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G297" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="298" spans="1:7">
@@ -7749,16 +8115,16 @@
         <v>307</v>
       </c>
       <c r="B298" t="s">
-        <v>590</v>
+        <v>641</v>
       </c>
       <c r="C298" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D298" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G298" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="299" spans="1:7">
@@ -7766,16 +8132,16 @@
         <v>308</v>
       </c>
       <c r="B299" t="s">
-        <v>591</v>
+        <v>642</v>
       </c>
       <c r="C299" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D299" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G299" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="300" spans="1:7">
@@ -7783,16 +8149,16 @@
         <v>309</v>
       </c>
       <c r="B300" t="s">
-        <v>592</v>
+        <v>643</v>
       </c>
       <c r="C300" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D300" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G300" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="301" spans="1:7">
@@ -7800,16 +8166,16 @@
         <v>310</v>
       </c>
       <c r="B301" t="s">
-        <v>593</v>
+        <v>644</v>
       </c>
       <c r="C301" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D301" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G301" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="302" spans="1:7">
@@ -7817,16 +8183,16 @@
         <v>311</v>
       </c>
       <c r="B302" t="s">
-        <v>594</v>
+        <v>645</v>
       </c>
       <c r="C302" t="s">
-        <v>627</v>
+        <v>749</v>
       </c>
       <c r="D302" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G302" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -7834,16 +8200,16 @@
         <v>312</v>
       </c>
       <c r="B303" t="s">
-        <v>595</v>
+        <v>646</v>
       </c>
       <c r="C303" t="s">
-        <v>628</v>
+        <v>750</v>
       </c>
       <c r="D303" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G303" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="304" spans="1:7">
@@ -7851,16 +8217,16 @@
         <v>313</v>
       </c>
       <c r="B304" t="s">
-        <v>596</v>
+        <v>647</v>
       </c>
       <c r="C304" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D304" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G304" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="305" spans="1:7">
@@ -7868,16 +8234,16 @@
         <v>314</v>
       </c>
       <c r="B305" t="s">
-        <v>597</v>
+        <v>648</v>
       </c>
       <c r="C305" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D305" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G305" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="306" spans="1:7">
@@ -7885,16 +8251,16 @@
         <v>315</v>
       </c>
       <c r="B306" t="s">
-        <v>598</v>
+        <v>649</v>
       </c>
       <c r="C306" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D306" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G306" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="307" spans="1:7">
@@ -7902,16 +8268,16 @@
         <v>316</v>
       </c>
       <c r="B307" t="s">
-        <v>599</v>
+        <v>650</v>
       </c>
       <c r="C307" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D307" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G307" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="308" spans="1:7">
@@ -7919,16 +8285,16 @@
         <v>317</v>
       </c>
       <c r="B308" t="s">
-        <v>600</v>
+        <v>651</v>
       </c>
       <c r="C308" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D308" t="s">
-        <v>673</v>
+        <v>795</v>
       </c>
       <c r="G308" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -7936,16 +8302,16 @@
         <v>318</v>
       </c>
       <c r="B309" t="s">
-        <v>601</v>
+        <v>652</v>
       </c>
       <c r="C309" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D309" t="s">
-        <v>660</v>
+        <v>782</v>
       </c>
       <c r="G309" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="310" spans="1:7">
@@ -7953,16 +8319,16 @@
         <v>319</v>
       </c>
       <c r="B310" t="s">
-        <v>602</v>
+        <v>653</v>
       </c>
       <c r="C310" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D310" t="s">
-        <v>674</v>
+        <v>796</v>
       </c>
       <c r="G310" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="311" spans="1:7">
@@ -7970,16 +8336,16 @@
         <v>320</v>
       </c>
       <c r="B311" t="s">
-        <v>603</v>
+        <v>654</v>
       </c>
       <c r="C311" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D311" t="s">
-        <v>662</v>
+        <v>784</v>
       </c>
       <c r="G311" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="312" spans="1:7">
@@ -7987,16 +8353,16 @@
         <v>321</v>
       </c>
       <c r="B312" t="s">
-        <v>604</v>
+        <v>655</v>
       </c>
       <c r="C312" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D312" t="s">
-        <v>668</v>
+        <v>790</v>
       </c>
       <c r="G312" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="313" spans="1:7">
@@ -8004,16 +8370,16 @@
         <v>322</v>
       </c>
       <c r="B313" t="s">
-        <v>605</v>
+        <v>656</v>
       </c>
       <c r="C313" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D313" t="s">
-        <v>671</v>
+        <v>793</v>
       </c>
       <c r="G313" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="314" spans="1:7">
@@ -8021,16 +8387,16 @@
         <v>323</v>
       </c>
       <c r="B314" t="s">
-        <v>606</v>
+        <v>657</v>
       </c>
       <c r="C314" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D314" t="s">
-        <v>675</v>
+        <v>797</v>
       </c>
       <c r="G314" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="315" spans="1:7">
@@ -8038,16 +8404,16 @@
         <v>324</v>
       </c>
       <c r="B315" t="s">
-        <v>607</v>
+        <v>658</v>
       </c>
       <c r="C315" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D315" t="s">
-        <v>669</v>
+        <v>791</v>
       </c>
       <c r="G315" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="316" spans="1:7">
@@ -8055,16 +8421,16 @@
         <v>325</v>
       </c>
       <c r="B316" t="s">
-        <v>608</v>
+        <v>659</v>
       </c>
       <c r="C316" t="s">
-        <v>623</v>
+        <v>745</v>
       </c>
       <c r="D316" t="s">
-        <v>669</v>
+        <v>791</v>
       </c>
       <c r="G316" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="317" spans="1:7">
@@ -8072,16 +8438,16 @@
         <v>326</v>
       </c>
       <c r="B317" t="s">
-        <v>609</v>
+        <v>660</v>
       </c>
       <c r="C317" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D317" t="s">
-        <v>676</v>
+        <v>798</v>
       </c>
       <c r="G317" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="318" spans="1:7">
@@ -8089,16 +8455,16 @@
         <v>327</v>
       </c>
       <c r="B318" t="s">
-        <v>610</v>
+        <v>661</v>
       </c>
       <c r="C318" t="s">
-        <v>632</v>
+        <v>754</v>
       </c>
       <c r="D318" t="s">
-        <v>677</v>
+        <v>799</v>
       </c>
       <c r="G318" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="319" spans="1:7">
@@ -8106,16 +8472,16 @@
         <v>328</v>
       </c>
       <c r="B319" t="s">
-        <v>611</v>
+        <v>662</v>
       </c>
       <c r="C319" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D319" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G319" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="320" spans="1:7">
@@ -8123,16 +8489,16 @@
         <v>329</v>
       </c>
       <c r="B320" t="s">
-        <v>612</v>
+        <v>663</v>
       </c>
       <c r="C320" t="s">
-        <v>626</v>
+        <v>748</v>
       </c>
       <c r="D320" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G320" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="321" spans="1:7">
@@ -8140,16 +8506,16 @@
         <v>330</v>
       </c>
       <c r="B321" t="s">
-        <v>613</v>
+        <v>664</v>
       </c>
       <c r="C321" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D321" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G321" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="322" spans="1:7">
@@ -8157,16 +8523,16 @@
         <v>300</v>
       </c>
       <c r="B322" t="s">
-        <v>614</v>
+        <v>665</v>
       </c>
       <c r="C322" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D322" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G322" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="323" spans="1:7">
@@ -8174,16 +8540,16 @@
         <v>331</v>
       </c>
       <c r="B323" t="s">
-        <v>615</v>
+        <v>666</v>
       </c>
       <c r="C323" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D323" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G323" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="324" spans="1:7">
@@ -8191,16 +8557,16 @@
         <v>332</v>
       </c>
       <c r="B324" t="s">
-        <v>616</v>
+        <v>667</v>
       </c>
       <c r="C324" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D324" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G324" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="325" spans="1:7">
@@ -8208,16 +8574,16 @@
         <v>333</v>
       </c>
       <c r="B325" t="s">
-        <v>617</v>
+        <v>668</v>
       </c>
       <c r="C325" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D325" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G325" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="326" spans="1:7">
@@ -8225,16 +8591,16 @@
         <v>334</v>
       </c>
       <c r="B326" t="s">
-        <v>618</v>
+        <v>669</v>
       </c>
       <c r="C326" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D326" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G326" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="327" spans="1:7">
@@ -8242,16 +8608,16 @@
         <v>335</v>
       </c>
       <c r="B327" t="s">
-        <v>619</v>
+        <v>670</v>
       </c>
       <c r="C327" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D327" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G327" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="328" spans="1:7">
@@ -8259,16 +8625,16 @@
         <v>336</v>
       </c>
       <c r="B328" t="s">
-        <v>620</v>
+        <v>671</v>
       </c>
       <c r="C328" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D328" t="s">
-        <v>672</v>
+        <v>794</v>
       </c>
       <c r="G328" t="s">
-        <v>752</v>
+        <v>874</v>
       </c>
     </row>
     <row r="329" spans="1:7">
@@ -8276,16 +8642,1223 @@
         <v>337</v>
       </c>
       <c r="B329" t="s">
-        <v>621</v>
+        <v>672</v>
       </c>
       <c r="C329" t="s">
-        <v>629</v>
+        <v>751</v>
       </c>
       <c r="D329" t="s">
-        <v>661</v>
+        <v>783</v>
       </c>
       <c r="G329" t="s">
-        <v>752</v>
+        <v>874</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7">
+      <c r="A330" t="s">
+        <v>338</v>
+      </c>
+      <c r="B330" t="s">
+        <v>673</v>
+      </c>
+      <c r="C330" t="s">
+        <v>751</v>
+      </c>
+      <c r="D330" t="s">
+        <v>794</v>
+      </c>
+      <c r="G330" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7">
+      <c r="A331" t="s">
+        <v>338</v>
+      </c>
+      <c r="B331" t="s">
+        <v>674</v>
+      </c>
+      <c r="C331" t="s">
+        <v>751</v>
+      </c>
+      <c r="D331" t="s">
+        <v>794</v>
+      </c>
+      <c r="G331" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7">
+      <c r="A332" t="s">
+        <v>339</v>
+      </c>
+      <c r="B332" t="s">
+        <v>675</v>
+      </c>
+      <c r="C332" t="s">
+        <v>751</v>
+      </c>
+      <c r="D332" t="s">
+        <v>794</v>
+      </c>
+      <c r="G332" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7">
+      <c r="A333" t="s">
+        <v>340</v>
+      </c>
+      <c r="B333" t="s">
+        <v>676</v>
+      </c>
+      <c r="C333" t="s">
+        <v>751</v>
+      </c>
+      <c r="D333" t="s">
+        <v>794</v>
+      </c>
+      <c r="G333" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7">
+      <c r="A334" t="s">
+        <v>340</v>
+      </c>
+      <c r="B334" t="s">
+        <v>677</v>
+      </c>
+      <c r="C334" t="s">
+        <v>751</v>
+      </c>
+      <c r="D334" t="s">
+        <v>794</v>
+      </c>
+      <c r="G334" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7">
+      <c r="A335" t="s">
+        <v>341</v>
+      </c>
+      <c r="B335" t="s">
+        <v>678</v>
+      </c>
+      <c r="C335" t="s">
+        <v>751</v>
+      </c>
+      <c r="D335" t="s">
+        <v>783</v>
+      </c>
+      <c r="G335" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7">
+      <c r="A336" t="s">
+        <v>342</v>
+      </c>
+      <c r="B336" t="s">
+        <v>679</v>
+      </c>
+      <c r="C336" t="s">
+        <v>751</v>
+      </c>
+      <c r="D336" t="s">
+        <v>783</v>
+      </c>
+      <c r="G336" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7">
+      <c r="A337" t="s">
+        <v>342</v>
+      </c>
+      <c r="B337" t="s">
+        <v>680</v>
+      </c>
+      <c r="C337" t="s">
+        <v>751</v>
+      </c>
+      <c r="D337" t="s">
+        <v>783</v>
+      </c>
+      <c r="G337" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7">
+      <c r="A338" t="s">
+        <v>343</v>
+      </c>
+      <c r="B338" t="s">
+        <v>681</v>
+      </c>
+      <c r="C338" t="s">
+        <v>751</v>
+      </c>
+      <c r="D338" t="s">
+        <v>783</v>
+      </c>
+      <c r="G338" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7">
+      <c r="A339" t="s">
+        <v>343</v>
+      </c>
+      <c r="B339" t="s">
+        <v>682</v>
+      </c>
+      <c r="C339" t="s">
+        <v>751</v>
+      </c>
+      <c r="D339" t="s">
+        <v>783</v>
+      </c>
+      <c r="G339" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7">
+      <c r="A340" t="s">
+        <v>344</v>
+      </c>
+      <c r="B340" t="s">
+        <v>683</v>
+      </c>
+      <c r="C340" t="s">
+        <v>751</v>
+      </c>
+      <c r="D340" t="s">
+        <v>794</v>
+      </c>
+      <c r="G340" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7">
+      <c r="A341" t="s">
+        <v>345</v>
+      </c>
+      <c r="B341" t="s">
+        <v>684</v>
+      </c>
+      <c r="C341" t="s">
+        <v>751</v>
+      </c>
+      <c r="D341" t="s">
+        <v>783</v>
+      </c>
+      <c r="G341" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7">
+      <c r="A342" t="s">
+        <v>346</v>
+      </c>
+      <c r="B342" t="s">
+        <v>685</v>
+      </c>
+      <c r="C342" t="s">
+        <v>751</v>
+      </c>
+      <c r="D342" t="s">
+        <v>783</v>
+      </c>
+      <c r="G342" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7">
+      <c r="A343" t="s">
+        <v>347</v>
+      </c>
+      <c r="B343" t="s">
+        <v>686</v>
+      </c>
+      <c r="C343" t="s">
+        <v>751</v>
+      </c>
+      <c r="D343" t="s">
+        <v>783</v>
+      </c>
+      <c r="G343" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7">
+      <c r="A344" t="s">
+        <v>348</v>
+      </c>
+      <c r="B344" t="s">
+        <v>687</v>
+      </c>
+      <c r="C344" t="s">
+        <v>751</v>
+      </c>
+      <c r="D344" t="s">
+        <v>794</v>
+      </c>
+      <c r="G344" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7">
+      <c r="A345" t="s">
+        <v>349</v>
+      </c>
+      <c r="B345" t="s">
+        <v>688</v>
+      </c>
+      <c r="C345" t="s">
+        <v>751</v>
+      </c>
+      <c r="D345" t="s">
+        <v>794</v>
+      </c>
+      <c r="G345" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7">
+      <c r="A346" t="s">
+        <v>350</v>
+      </c>
+      <c r="B346" t="s">
+        <v>689</v>
+      </c>
+      <c r="C346" t="s">
+        <v>751</v>
+      </c>
+      <c r="D346" t="s">
+        <v>783</v>
+      </c>
+      <c r="G346" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7">
+      <c r="A347" t="s">
+        <v>350</v>
+      </c>
+      <c r="B347" t="s">
+        <v>690</v>
+      </c>
+      <c r="C347" t="s">
+        <v>751</v>
+      </c>
+      <c r="D347" t="s">
+        <v>783</v>
+      </c>
+      <c r="G347" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7">
+      <c r="A348" t="s">
+        <v>351</v>
+      </c>
+      <c r="B348" t="s">
+        <v>691</v>
+      </c>
+      <c r="C348" t="s">
+        <v>751</v>
+      </c>
+      <c r="D348" t="s">
+        <v>783</v>
+      </c>
+      <c r="G348" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7">
+      <c r="A349" t="s">
+        <v>352</v>
+      </c>
+      <c r="B349" t="s">
+        <v>692</v>
+      </c>
+      <c r="C349" t="s">
+        <v>751</v>
+      </c>
+      <c r="D349" t="s">
+        <v>783</v>
+      </c>
+      <c r="G349" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7">
+      <c r="A350" t="s">
+        <v>353</v>
+      </c>
+      <c r="B350" t="s">
+        <v>693</v>
+      </c>
+      <c r="C350" t="s">
+        <v>751</v>
+      </c>
+      <c r="D350" t="s">
+        <v>783</v>
+      </c>
+      <c r="G350" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7">
+      <c r="A351" t="s">
+        <v>353</v>
+      </c>
+      <c r="B351" t="s">
+        <v>694</v>
+      </c>
+      <c r="C351" t="s">
+        <v>751</v>
+      </c>
+      <c r="D351" t="s">
+        <v>783</v>
+      </c>
+      <c r="G351" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7">
+      <c r="A352" t="s">
+        <v>354</v>
+      </c>
+      <c r="B352" t="s">
+        <v>695</v>
+      </c>
+      <c r="C352" t="s">
+        <v>751</v>
+      </c>
+      <c r="D352" t="s">
+        <v>783</v>
+      </c>
+      <c r="G352" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7">
+      <c r="A353" t="s">
+        <v>354</v>
+      </c>
+      <c r="B353" t="s">
+        <v>696</v>
+      </c>
+      <c r="C353" t="s">
+        <v>751</v>
+      </c>
+      <c r="D353" t="s">
+        <v>783</v>
+      </c>
+      <c r="G353" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7">
+      <c r="A354" t="s">
+        <v>355</v>
+      </c>
+      <c r="B354" t="s">
+        <v>697</v>
+      </c>
+      <c r="C354" t="s">
+        <v>751</v>
+      </c>
+      <c r="D354" t="s">
+        <v>783</v>
+      </c>
+      <c r="G354" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7">
+      <c r="A355" t="s">
+        <v>355</v>
+      </c>
+      <c r="B355" t="s">
+        <v>698</v>
+      </c>
+      <c r="C355" t="s">
+        <v>751</v>
+      </c>
+      <c r="D355" t="s">
+        <v>783</v>
+      </c>
+      <c r="G355" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7">
+      <c r="A356" t="s">
+        <v>356</v>
+      </c>
+      <c r="B356" t="s">
+        <v>699</v>
+      </c>
+      <c r="C356" t="s">
+        <v>751</v>
+      </c>
+      <c r="D356" t="s">
+        <v>794</v>
+      </c>
+      <c r="G356" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7">
+      <c r="A357" t="s">
+        <v>357</v>
+      </c>
+      <c r="B357" t="s">
+        <v>700</v>
+      </c>
+      <c r="C357" t="s">
+        <v>751</v>
+      </c>
+      <c r="D357" t="s">
+        <v>794</v>
+      </c>
+      <c r="G357" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7">
+      <c r="A358" t="s">
+        <v>358</v>
+      </c>
+      <c r="B358" t="s">
+        <v>701</v>
+      </c>
+      <c r="C358" t="s">
+        <v>751</v>
+      </c>
+      <c r="D358" t="s">
+        <v>783</v>
+      </c>
+      <c r="G358" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7">
+      <c r="A359" t="s">
+        <v>359</v>
+      </c>
+      <c r="B359" t="s">
+        <v>702</v>
+      </c>
+      <c r="C359" t="s">
+        <v>751</v>
+      </c>
+      <c r="D359" t="s">
+        <v>783</v>
+      </c>
+      <c r="G359" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7">
+      <c r="A360" t="s">
+        <v>360</v>
+      </c>
+      <c r="B360" t="s">
+        <v>703</v>
+      </c>
+      <c r="C360" t="s">
+        <v>751</v>
+      </c>
+      <c r="D360" t="s">
+        <v>783</v>
+      </c>
+      <c r="G360" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7">
+      <c r="A361" t="s">
+        <v>361</v>
+      </c>
+      <c r="B361" t="s">
+        <v>704</v>
+      </c>
+      <c r="C361" t="s">
+        <v>751</v>
+      </c>
+      <c r="D361" t="s">
+        <v>783</v>
+      </c>
+      <c r="G361" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7">
+      <c r="A362" t="s">
+        <v>362</v>
+      </c>
+      <c r="B362" t="s">
+        <v>705</v>
+      </c>
+      <c r="C362" t="s">
+        <v>751</v>
+      </c>
+      <c r="D362" t="s">
+        <v>783</v>
+      </c>
+      <c r="G362" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7">
+      <c r="A363" t="s">
+        <v>363</v>
+      </c>
+      <c r="B363" t="s">
+        <v>706</v>
+      </c>
+      <c r="C363" t="s">
+        <v>751</v>
+      </c>
+      <c r="D363" t="s">
+        <v>783</v>
+      </c>
+      <c r="G363" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7">
+      <c r="A364" t="s">
+        <v>364</v>
+      </c>
+      <c r="B364" t="s">
+        <v>707</v>
+      </c>
+      <c r="C364" t="s">
+        <v>751</v>
+      </c>
+      <c r="D364" t="s">
+        <v>783</v>
+      </c>
+      <c r="G364" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7">
+      <c r="A365" t="s">
+        <v>365</v>
+      </c>
+      <c r="B365" t="s">
+        <v>708</v>
+      </c>
+      <c r="C365" t="s">
+        <v>751</v>
+      </c>
+      <c r="D365" t="s">
+        <v>794</v>
+      </c>
+      <c r="G365" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7">
+      <c r="A366" t="s">
+        <v>366</v>
+      </c>
+      <c r="B366" t="s">
+        <v>709</v>
+      </c>
+      <c r="C366" t="s">
+        <v>751</v>
+      </c>
+      <c r="D366" t="s">
+        <v>783</v>
+      </c>
+      <c r="G366" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7">
+      <c r="A367" t="s">
+        <v>366</v>
+      </c>
+      <c r="B367" t="s">
+        <v>710</v>
+      </c>
+      <c r="C367" t="s">
+        <v>751</v>
+      </c>
+      <c r="D367" t="s">
+        <v>783</v>
+      </c>
+      <c r="G367" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7">
+      <c r="A368" t="s">
+        <v>367</v>
+      </c>
+      <c r="B368" t="s">
+        <v>711</v>
+      </c>
+      <c r="C368" t="s">
+        <v>751</v>
+      </c>
+      <c r="D368" t="s">
+        <v>794</v>
+      </c>
+      <c r="G368" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7">
+      <c r="A369" t="s">
+        <v>368</v>
+      </c>
+      <c r="B369" t="s">
+        <v>712</v>
+      </c>
+      <c r="C369" t="s">
+        <v>751</v>
+      </c>
+      <c r="D369" t="s">
+        <v>794</v>
+      </c>
+      <c r="G369" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7">
+      <c r="A370" t="s">
+        <v>369</v>
+      </c>
+      <c r="B370" t="s">
+        <v>713</v>
+      </c>
+      <c r="C370" t="s">
+        <v>751</v>
+      </c>
+      <c r="D370" t="s">
+        <v>794</v>
+      </c>
+      <c r="G370" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7">
+      <c r="A371" t="s">
+        <v>370</v>
+      </c>
+      <c r="B371" t="s">
+        <v>714</v>
+      </c>
+      <c r="C371" t="s">
+        <v>751</v>
+      </c>
+      <c r="D371" t="s">
+        <v>794</v>
+      </c>
+      <c r="G371" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7">
+      <c r="A372" t="s">
+        <v>371</v>
+      </c>
+      <c r="B372" t="s">
+        <v>715</v>
+      </c>
+      <c r="C372" t="s">
+        <v>751</v>
+      </c>
+      <c r="D372" t="s">
+        <v>783</v>
+      </c>
+      <c r="G372" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7">
+      <c r="A373" t="s">
+        <v>371</v>
+      </c>
+      <c r="B373" t="s">
+        <v>716</v>
+      </c>
+      <c r="C373" t="s">
+        <v>751</v>
+      </c>
+      <c r="D373" t="s">
+        <v>783</v>
+      </c>
+      <c r="G373" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7">
+      <c r="A374" t="s">
+        <v>372</v>
+      </c>
+      <c r="B374" t="s">
+        <v>717</v>
+      </c>
+      <c r="C374" t="s">
+        <v>751</v>
+      </c>
+      <c r="D374" t="s">
+        <v>783</v>
+      </c>
+      <c r="G374" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7">
+      <c r="A375" t="s">
+        <v>372</v>
+      </c>
+      <c r="B375" t="s">
+        <v>718</v>
+      </c>
+      <c r="C375" t="s">
+        <v>751</v>
+      </c>
+      <c r="D375" t="s">
+        <v>783</v>
+      </c>
+      <c r="G375" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7">
+      <c r="A376" t="s">
+        <v>373</v>
+      </c>
+      <c r="B376" t="s">
+        <v>719</v>
+      </c>
+      <c r="C376" t="s">
+        <v>751</v>
+      </c>
+      <c r="D376" t="s">
+        <v>783</v>
+      </c>
+      <c r="G376" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7">
+      <c r="A377" t="s">
+        <v>374</v>
+      </c>
+      <c r="B377" t="s">
+        <v>720</v>
+      </c>
+      <c r="C377" t="s">
+        <v>751</v>
+      </c>
+      <c r="D377" t="s">
+        <v>794</v>
+      </c>
+      <c r="G377" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7">
+      <c r="A378" t="s">
+        <v>374</v>
+      </c>
+      <c r="B378" t="s">
+        <v>721</v>
+      </c>
+      <c r="C378" t="s">
+        <v>751</v>
+      </c>
+      <c r="D378" t="s">
+        <v>794</v>
+      </c>
+      <c r="G378" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7">
+      <c r="A379" t="s">
+        <v>375</v>
+      </c>
+      <c r="B379" t="s">
+        <v>722</v>
+      </c>
+      <c r="C379" t="s">
+        <v>751</v>
+      </c>
+      <c r="D379" t="s">
+        <v>794</v>
+      </c>
+      <c r="G379" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7">
+      <c r="A380" t="s">
+        <v>375</v>
+      </c>
+      <c r="B380" t="s">
+        <v>723</v>
+      </c>
+      <c r="C380" t="s">
+        <v>751</v>
+      </c>
+      <c r="D380" t="s">
+        <v>794</v>
+      </c>
+      <c r="G380" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7">
+      <c r="A381" t="s">
+        <v>376</v>
+      </c>
+      <c r="B381" t="s">
+        <v>724</v>
+      </c>
+      <c r="C381" t="s">
+        <v>751</v>
+      </c>
+      <c r="D381" t="s">
+        <v>794</v>
+      </c>
+      <c r="G381" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7">
+      <c r="A382" t="s">
+        <v>377</v>
+      </c>
+      <c r="B382" t="s">
+        <v>725</v>
+      </c>
+      <c r="C382" t="s">
+        <v>751</v>
+      </c>
+      <c r="D382" t="s">
+        <v>783</v>
+      </c>
+      <c r="G382" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7">
+      <c r="A383" t="s">
+        <v>378</v>
+      </c>
+      <c r="B383" t="s">
+        <v>726</v>
+      </c>
+      <c r="C383" t="s">
+        <v>751</v>
+      </c>
+      <c r="D383" t="s">
+        <v>794</v>
+      </c>
+      <c r="G383" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7">
+      <c r="A384" t="s">
+        <v>379</v>
+      </c>
+      <c r="B384" t="s">
+        <v>727</v>
+      </c>
+      <c r="C384" t="s">
+        <v>751</v>
+      </c>
+      <c r="D384" t="s">
+        <v>794</v>
+      </c>
+      <c r="G384" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7">
+      <c r="A385" t="s">
+        <v>379</v>
+      </c>
+      <c r="B385" t="s">
+        <v>728</v>
+      </c>
+      <c r="C385" t="s">
+        <v>751</v>
+      </c>
+      <c r="D385" t="s">
+        <v>794</v>
+      </c>
+      <c r="G385" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="386" spans="1:7">
+      <c r="A386" t="s">
+        <v>333</v>
+      </c>
+      <c r="B386" t="s">
+        <v>729</v>
+      </c>
+      <c r="C386" t="s">
+        <v>751</v>
+      </c>
+      <c r="D386" t="s">
+        <v>783</v>
+      </c>
+      <c r="G386" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7">
+      <c r="A387" t="s">
+        <v>380</v>
+      </c>
+      <c r="B387" t="s">
+        <v>730</v>
+      </c>
+      <c r="C387" t="s">
+        <v>751</v>
+      </c>
+      <c r="D387" t="s">
+        <v>783</v>
+      </c>
+      <c r="G387" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7">
+      <c r="A388" t="s">
+        <v>380</v>
+      </c>
+      <c r="B388" t="s">
+        <v>731</v>
+      </c>
+      <c r="C388" t="s">
+        <v>751</v>
+      </c>
+      <c r="D388" t="s">
+        <v>783</v>
+      </c>
+      <c r="G388" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7">
+      <c r="A389" t="s">
+        <v>381</v>
+      </c>
+      <c r="B389" t="s">
+        <v>732</v>
+      </c>
+      <c r="C389" t="s">
+        <v>751</v>
+      </c>
+      <c r="D389" t="s">
+        <v>783</v>
+      </c>
+      <c r="G389" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7">
+      <c r="A390" t="s">
+        <v>382</v>
+      </c>
+      <c r="B390" t="s">
+        <v>733</v>
+      </c>
+      <c r="C390" t="s">
+        <v>751</v>
+      </c>
+      <c r="D390" t="s">
+        <v>783</v>
+      </c>
+      <c r="G390" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7">
+      <c r="A391" t="s">
+        <v>383</v>
+      </c>
+      <c r="B391" t="s">
+        <v>734</v>
+      </c>
+      <c r="C391" t="s">
+        <v>751</v>
+      </c>
+      <c r="D391" t="s">
+        <v>783</v>
+      </c>
+      <c r="G391" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7">
+      <c r="A392" t="s">
+        <v>56</v>
+      </c>
+      <c r="B392" t="s">
+        <v>735</v>
+      </c>
+      <c r="C392" t="s">
+        <v>751</v>
+      </c>
+      <c r="D392" t="s">
+        <v>783</v>
+      </c>
+      <c r="G392" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7">
+      <c r="A393" t="s">
+        <v>384</v>
+      </c>
+      <c r="B393" t="s">
+        <v>736</v>
+      </c>
+      <c r="C393" t="s">
+        <v>751</v>
+      </c>
+      <c r="D393" t="s">
+        <v>783</v>
+      </c>
+      <c r="G393" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7">
+      <c r="A394" t="s">
+        <v>385</v>
+      </c>
+      <c r="B394" t="s">
+        <v>737</v>
+      </c>
+      <c r="C394" t="s">
+        <v>751</v>
+      </c>
+      <c r="D394" t="s">
+        <v>783</v>
+      </c>
+      <c r="G394" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7">
+      <c r="A395" t="s">
+        <v>385</v>
+      </c>
+      <c r="B395" t="s">
+        <v>738</v>
+      </c>
+      <c r="C395" t="s">
+        <v>751</v>
+      </c>
+      <c r="D395" t="s">
+        <v>783</v>
+      </c>
+      <c r="G395" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7">
+      <c r="A396" t="s">
+        <v>386</v>
+      </c>
+      <c r="B396" t="s">
+        <v>739</v>
+      </c>
+      <c r="C396" t="s">
+        <v>751</v>
+      </c>
+      <c r="D396" t="s">
+        <v>783</v>
+      </c>
+      <c r="G396" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7">
+      <c r="A397" t="s">
+        <v>387</v>
+      </c>
+      <c r="B397" t="s">
+        <v>740</v>
+      </c>
+      <c r="C397" t="s">
+        <v>751</v>
+      </c>
+      <c r="D397" t="s">
+        <v>783</v>
+      </c>
+      <c r="G397" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="398" spans="1:7">
+      <c r="A398" t="s">
+        <v>387</v>
+      </c>
+      <c r="B398" t="s">
+        <v>741</v>
+      </c>
+      <c r="C398" t="s">
+        <v>751</v>
+      </c>
+      <c r="D398" t="s">
+        <v>783</v>
+      </c>
+      <c r="G398" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="399" spans="1:7">
+      <c r="A399" t="s">
+        <v>388</v>
+      </c>
+      <c r="B399" t="s">
+        <v>742</v>
+      </c>
+      <c r="C399" t="s">
+        <v>751</v>
+      </c>
+      <c r="D399" t="s">
+        <v>783</v>
+      </c>
+      <c r="G399" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7">
+      <c r="A400" t="s">
+        <v>388</v>
+      </c>
+      <c r="B400" t="s">
+        <v>743</v>
+      </c>
+      <c r="C400" t="s">
+        <v>751</v>
+      </c>
+      <c r="D400" t="s">
+        <v>783</v>
+      </c>
+      <c r="G400" t="s">
+        <v>874</v>
       </c>
     </row>
   </sheetData>

--- a/results/master_contacts.xlsx
+++ b/results/master_contacts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2025" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2289" uniqueCount="1018">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -1183,6 +1183,105 @@
     <t>Willowmead Medical Centre</t>
   </si>
   <si>
+    <t>Association for Visual Arts (AVA Gallery)</t>
+  </si>
+  <si>
+    <t>The Cape Gallery</t>
+  </si>
+  <si>
+    <t>Southern Guild Cape Town</t>
+  </si>
+  <si>
+    <t>WHATIFTHEWORLD</t>
+  </si>
+  <si>
+    <t>Homecoming Centre</t>
+  </si>
+  <si>
+    <t>Nathan Chikoto Recycle Artist（GALLERY）</t>
+  </si>
+  <si>
+    <t>South African National Gallery</t>
+  </si>
+  <si>
+    <t>COMMUNITY CHEST OF WESTERN CAPE</t>
+  </si>
+  <si>
+    <t>Just Grace NPC</t>
+  </si>
+  <si>
+    <t>National Development Agency</t>
+  </si>
+  <si>
+    <t>VPUU</t>
+  </si>
+  <si>
+    <t>Centre for Environmental Rights</t>
+  </si>
+  <si>
+    <t>9Miles Project</t>
+  </si>
+  <si>
+    <t>Amy Foundation Trust South Africa (Formerly Amy Biehl Foundation Trust)</t>
+  </si>
+  <si>
+    <t>Scalabrini Centre of Cape Town</t>
+  </si>
+  <si>
+    <t>SAE Institute - Cape Town</t>
+  </si>
+  <si>
+    <t>CIPC Cape Town</t>
+  </si>
+  <si>
+    <t>District Six Museum</t>
+  </si>
+  <si>
+    <t>Castle of Good Hope</t>
+  </si>
+  <si>
+    <t>Cape Town Heritage Trust</t>
+  </si>
+  <si>
+    <t>18 Gangster Museum / Township Tours</t>
+  </si>
+  <si>
+    <t>Lighthouse</t>
+  </si>
+  <si>
+    <t>Heart of Cape Town Museum</t>
+  </si>
+  <si>
+    <t>Groot Constantia Museum</t>
+  </si>
+  <si>
+    <t>First Nations Heritage Centre</t>
+  </si>
+  <si>
+    <t>Youth In Transformation</t>
+  </si>
+  <si>
+    <t>Cape Town Tutors</t>
+  </si>
+  <si>
+    <t>YearBeyond</t>
+  </si>
+  <si>
+    <t>Life Choices</t>
+  </si>
+  <si>
+    <t>Cape Town Multi Service Centre</t>
+  </si>
+  <si>
+    <t>iKhaya Le Themba - Home of Hope</t>
+  </si>
+  <si>
+    <t>T.A English Cape Town</t>
+  </si>
+  <si>
+    <t>Realistic Child And Youth Care Centre</t>
+  </si>
+  <si>
     <t>info@ctsc.org.za</t>
   </si>
   <si>
@@ -2050,7 +2149,7 @@
     <t>durban@masthead.co.za</t>
   </si>
   <si>
-    <t>user@domain.com.</t>
+    <t>user@domain.com</t>
   </si>
   <si>
     <t>events.applications@capetown.gov.za</t>
@@ -2248,6 +2347,138 @@
     <t>info@willowmead.co.za</t>
   </si>
   <si>
+    <t>admin@ava.co.za</t>
+  </si>
+  <si>
+    <t>artscape@artscape.co.za</t>
+  </si>
+  <si>
+    <t>web@capegallery.co.za</t>
+  </si>
+  <si>
+    <t>u002f@-33.917154</t>
+  </si>
+  <si>
+    <t>u002f@-33.9099196</t>
+  </si>
+  <si>
+    <t>justin@whatiftheworld.com</t>
+  </si>
+  <si>
+    <t>akshar@whatiftheworld.com</t>
+  </si>
+  <si>
+    <t>joe@districtsix.co.za</t>
+  </si>
+  <si>
+    <t>info@nathan-chikoto-recycle-artist.com</t>
+  </si>
+  <si>
+    <t>mediaofficer@iziko.org.za</t>
+  </si>
+  <si>
+    <t>dag@dag.org.za</t>
+  </si>
+  <si>
+    <t>media@dag.org.za</t>
+  </si>
+  <si>
+    <t>needhelp@meipaly.com</t>
+  </si>
+  <si>
+    <t>contact@justgrace.co.za</t>
+  </si>
+  <si>
+    <t>aos@2.3.1</t>
+  </si>
+  <si>
+    <t>info@nda.org.za</t>
+  </si>
+  <si>
+    <t>hello@vpuu.org.za</t>
+  </si>
+  <si>
+    <t>info@cer.org.za</t>
+  </si>
+  <si>
+    <t>info@9milesproject.org</t>
+  </si>
+  <si>
+    <t>info@amyfoundation.co.za</t>
+  </si>
+  <si>
+    <t>whistleblower@scalabrini.org.za</t>
+  </si>
+  <si>
+    <t>bootstrap-icons@1.10.5</t>
+  </si>
+  <si>
+    <t>cklokow@cipc.co.za</t>
+  </si>
+  <si>
+    <t>tlebete@cipc.co.za</t>
+  </si>
+  <si>
+    <t>tina@districtsix.co.za</t>
+  </si>
+  <si>
+    <t>info@castleofgoodhope.co.za</t>
+  </si>
+  <si>
+    <t>admin@heritage.co.za</t>
+  </si>
+  <si>
+    <t>info@18gm.co.za</t>
+  </si>
+  <si>
+    <t>infow@robben-island.org.za</t>
+  </si>
+  <si>
+    <t>info@heartofcapetown.co.za</t>
+  </si>
+  <si>
+    <t>theheartofcapetownmuseum@gmail.com</t>
+  </si>
+  <si>
+    <t>info@jhuis.co.za</t>
+  </si>
+  <si>
+    <t>reservations@jhuis.co.za</t>
+  </si>
+  <si>
+    <t>admin@firstnationscollective.com</t>
+  </si>
+  <si>
+    <t>info@youthintransformation.org</t>
+  </si>
+  <si>
+    <t>info@capetowntutors.com</t>
+  </si>
+  <si>
+    <t>yearbeyond@westerncape.gov.za</t>
+  </si>
+  <si>
+    <t>hello@teachme2.com</t>
+  </si>
+  <si>
+    <t>info@lifechoices.co.za</t>
+  </si>
+  <si>
+    <t>admin@ctmsc.org.za</t>
+  </si>
+  <si>
+    <t>socialw1@ctmsc.org.za</t>
+  </si>
+  <si>
+    <t>team@ikhayalethemba.org.za</t>
+  </si>
+  <si>
+    <t>teacherallicia@gmail.co.za</t>
+  </si>
+  <si>
+    <t>info@realisticcycc.co.za</t>
+  </si>
+  <si>
     <t>Museums &amp; Heritage</t>
   </si>
   <si>
@@ -2323,6 +2554,9 @@
     <t>Refugee &amp; Migrant Support</t>
   </si>
   <si>
+    <t>Historic Sites</t>
+  </si>
+  <si>
     <t>Cape Town</t>
   </si>
   <si>
@@ -2578,6 +2812,93 @@
     <t>082 497 7721</t>
   </si>
   <si>
+    <t>021 424 7436</t>
+  </si>
+  <si>
+    <t>021 410 9800</t>
+  </si>
+  <si>
+    <t>021 423 5309</t>
+  </si>
+  <si>
+    <t>021 461 2856</t>
+  </si>
+  <si>
+    <t>021 569 0680</t>
+  </si>
+  <si>
+    <t>071 795 8304</t>
+  </si>
+  <si>
+    <t>021 448 7886</t>
+  </si>
+  <si>
+    <t>021 487 1500</t>
+  </si>
+  <si>
+    <t>079 043 8932</t>
+  </si>
+  <si>
+    <t>021 422 5175</t>
+  </si>
+  <si>
+    <t>021 447 0086</t>
+  </si>
+  <si>
+    <t>021 447 1647</t>
+  </si>
+  <si>
+    <t>082 997 8754</t>
+  </si>
+  <si>
+    <t>021 447 1690</t>
+  </si>
+  <si>
+    <t>021 465 6433</t>
+  </si>
+  <si>
+    <t>087 057 1972</t>
+  </si>
+  <si>
+    <t>086 100 2472</t>
+  </si>
+  <si>
+    <t>012 461 4673</t>
+  </si>
+  <si>
+    <t>021 426 2157</t>
+  </si>
+  <si>
+    <t>063 758 0185</t>
+  </si>
+  <si>
+    <t>021 404 1967</t>
+  </si>
+  <si>
+    <t>021 794 5128</t>
+  </si>
+  <si>
+    <t>073 895 9293</t>
+  </si>
+  <si>
+    <t>021 483 9844</t>
+  </si>
+  <si>
+    <t>021 300 0971</t>
+  </si>
+  <si>
+    <t>021 696 4157</t>
+  </si>
+  <si>
+    <t>021 448 3430</t>
+  </si>
+  <si>
+    <t>021 791 6060</t>
+  </si>
+  <si>
+    <t>084 573 3528</t>
+  </si>
+  <si>
     <t>www.ctsc.org.za</t>
   </si>
   <si>
@@ -2636,6 +2957,114 @@
   </si>
   <si>
     <t>www.cmacofct.com</t>
+  </si>
+  <si>
+    <t>https://www.ava.co.za/</t>
+  </si>
+  <si>
+    <t>http://www.artscape.co.za/</t>
+  </si>
+  <si>
+    <t>http://www.capegallery.co.za/</t>
+  </si>
+  <si>
+    <t>https://southernguild.com/</t>
+  </si>
+  <si>
+    <t>https://www.whatiftheworld.com/</t>
+  </si>
+  <si>
+    <t>https://homecomingcentre.co.za/</t>
+  </si>
+  <si>
+    <t>http://www.nathan-chikoto-recycle-artist.com/</t>
+  </si>
+  <si>
+    <t>http://www.iziko.org.za/museums/south-african-national-gallery</t>
+  </si>
+  <si>
+    <t>http://www.dag.org.za/</t>
+  </si>
+  <si>
+    <t>http://www.comchest.org.za/</t>
+  </si>
+  <si>
+    <t>http://www.justgrace.co.za/</t>
+  </si>
+  <si>
+    <t>http://www.nda.org.za/</t>
+  </si>
+  <si>
+    <t>https://vpuu.org.za/</t>
+  </si>
+  <si>
+    <t>https://cer.org.za/</t>
+  </si>
+  <si>
+    <t>http://www.9milesproject.org/</t>
+  </si>
+  <si>
+    <t>http://www.amyfoundation.co.za/</t>
+  </si>
+  <si>
+    <t>https://www.scalabrini.org.za/</t>
+  </si>
+  <si>
+    <t>https://www.sae.edu.za/</t>
+  </si>
+  <si>
+    <t>https://www.cipc.co.za/</t>
+  </si>
+  <si>
+    <t>http://www.districtsix.co.za/</t>
+  </si>
+  <si>
+    <t>https://www.castleofgoodhope.co.za/</t>
+  </si>
+  <si>
+    <t>http://www.heritage.org.za/home/</t>
+  </si>
+  <si>
+    <t>http://www.18gm.co.za/</t>
+  </si>
+  <si>
+    <t>http://www.robben-island.org.za/</t>
+  </si>
+  <si>
+    <t>https://heartofcapetown.co.za/</t>
+  </si>
+  <si>
+    <t>http://www.grootconstantia.co.za/</t>
+  </si>
+  <si>
+    <t>https://firstnationscollective.com/</t>
+  </si>
+  <si>
+    <t>https://www.youthintransformation.org/</t>
+  </si>
+  <si>
+    <t>https://capetowntutors.com/</t>
+  </si>
+  <si>
+    <t>http://yearbeyond.org/</t>
+  </si>
+  <si>
+    <t>https://www.teachme2.com/</t>
+  </si>
+  <si>
+    <t>http://www.lifechoices.co.za/</t>
+  </si>
+  <si>
+    <t>http://ctmsc.co.za/</t>
+  </si>
+  <si>
+    <t>http://www.ikhayalethemba.org.za/</t>
+  </si>
+  <si>
+    <t>https://teacherallicia.co.za/</t>
+  </si>
+  <si>
+    <t>https://www.realisticcycc.co.za/</t>
   </si>
   <si>
     <t>Yes</t>
@@ -2983,7 +3412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L400"/>
+  <dimension ref="A1:L444"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -3029,22 +3458,22 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>389</v>
+        <v>422</v>
       </c>
       <c r="C2" t="s">
-        <v>744</v>
+        <v>821</v>
       </c>
       <c r="D2" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E2" t="s">
-        <v>800</v>
+        <v>878</v>
       </c>
       <c r="F2" t="s">
-        <v>854</v>
+        <v>961</v>
       </c>
       <c r="G2" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -3052,22 +3481,22 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>390</v>
+        <v>423</v>
       </c>
       <c r="C3" t="s">
-        <v>744</v>
+        <v>821</v>
       </c>
       <c r="D3" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E3" t="s">
-        <v>800</v>
+        <v>878</v>
       </c>
       <c r="F3" t="s">
-        <v>854</v>
+        <v>961</v>
       </c>
       <c r="G3" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -3075,22 +3504,22 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>391</v>
+        <v>424</v>
       </c>
       <c r="C4" t="s">
-        <v>745</v>
+        <v>822</v>
       </c>
       <c r="D4" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E4" t="s">
-        <v>800</v>
+        <v>878</v>
       </c>
       <c r="F4" t="s">
-        <v>854</v>
+        <v>961</v>
       </c>
       <c r="G4" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -3098,22 +3527,22 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>392</v>
+        <v>425</v>
       </c>
       <c r="C5" t="s">
-        <v>745</v>
+        <v>822</v>
       </c>
       <c r="D5" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E5" t="s">
-        <v>800</v>
+        <v>878</v>
       </c>
       <c r="F5" t="s">
-        <v>854</v>
+        <v>961</v>
       </c>
       <c r="G5" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -3121,22 +3550,22 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>393</v>
+        <v>426</v>
       </c>
       <c r="C6" t="s">
-        <v>744</v>
+        <v>821</v>
       </c>
       <c r="D6" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E6" t="s">
-        <v>800</v>
+        <v>878</v>
       </c>
       <c r="F6" t="s">
-        <v>854</v>
+        <v>961</v>
       </c>
       <c r="G6" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3144,22 +3573,22 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>394</v>
+        <v>427</v>
       </c>
       <c r="C7" t="s">
-        <v>744</v>
+        <v>821</v>
       </c>
       <c r="D7" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E7" t="s">
-        <v>800</v>
+        <v>878</v>
       </c>
       <c r="F7" t="s">
-        <v>854</v>
+        <v>961</v>
       </c>
       <c r="G7" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -3167,22 +3596,22 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>395</v>
+        <v>428</v>
       </c>
       <c r="C8" t="s">
-        <v>745</v>
+        <v>822</v>
       </c>
       <c r="D8" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E8" t="s">
-        <v>800</v>
+        <v>878</v>
       </c>
       <c r="F8" t="s">
-        <v>854</v>
+        <v>961</v>
       </c>
       <c r="G8" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -3190,22 +3619,22 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>396</v>
+        <v>429</v>
       </c>
       <c r="C9" t="s">
-        <v>745</v>
+        <v>822</v>
       </c>
       <c r="D9" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E9" t="s">
-        <v>800</v>
+        <v>878</v>
       </c>
       <c r="F9" t="s">
-        <v>854</v>
+        <v>961</v>
       </c>
       <c r="G9" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -3213,22 +3642,22 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>397</v>
+        <v>430</v>
       </c>
       <c r="C10" t="s">
-        <v>746</v>
+        <v>823</v>
       </c>
       <c r="D10" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E10" t="s">
-        <v>800</v>
+        <v>878</v>
       </c>
       <c r="F10" t="s">
-        <v>854</v>
+        <v>961</v>
       </c>
       <c r="G10" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -3236,22 +3665,22 @@
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>398</v>
+        <v>431</v>
       </c>
       <c r="C11" t="s">
-        <v>746</v>
+        <v>823</v>
       </c>
       <c r="D11" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E11" t="s">
-        <v>800</v>
+        <v>878</v>
       </c>
       <c r="F11" t="s">
-        <v>854</v>
+        <v>961</v>
       </c>
       <c r="G11" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -3259,22 +3688,22 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>399</v>
+        <v>432</v>
       </c>
       <c r="C12" t="s">
-        <v>747</v>
+        <v>824</v>
       </c>
       <c r="D12" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E12" t="s">
-        <v>800</v>
+        <v>878</v>
       </c>
       <c r="F12" t="s">
-        <v>854</v>
+        <v>961</v>
       </c>
       <c r="G12" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -3282,22 +3711,22 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>400</v>
+        <v>433</v>
       </c>
       <c r="C13" t="s">
-        <v>744</v>
+        <v>821</v>
       </c>
       <c r="D13" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E13" t="s">
-        <v>800</v>
+        <v>878</v>
       </c>
       <c r="F13" t="s">
-        <v>854</v>
+        <v>961</v>
       </c>
       <c r="G13" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -3305,22 +3734,22 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>401</v>
+        <v>434</v>
       </c>
       <c r="C14" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D14" t="s">
-        <v>770</v>
+        <v>848</v>
       </c>
       <c r="E14" t="s">
-        <v>801</v>
+        <v>879</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>855</v>
+        <v>962</v>
       </c>
       <c r="G14" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -3328,22 +3757,22 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>402</v>
+        <v>435</v>
       </c>
       <c r="C15" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D15" t="s">
-        <v>770</v>
+        <v>848</v>
       </c>
       <c r="E15" t="s">
-        <v>802</v>
+        <v>880</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>856</v>
+        <v>963</v>
       </c>
       <c r="G15" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -3351,16 +3780,16 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>403</v>
+        <v>436</v>
       </c>
       <c r="C16" t="s">
-        <v>749</v>
+        <v>826</v>
       </c>
       <c r="D16" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G16" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -3368,16 +3797,16 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>404</v>
+        <v>437</v>
       </c>
       <c r="C17" t="s">
-        <v>749</v>
+        <v>826</v>
       </c>
       <c r="D17" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G17" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -3385,16 +3814,16 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>405</v>
+        <v>438</v>
       </c>
       <c r="C18" t="s">
-        <v>749</v>
+        <v>826</v>
       </c>
       <c r="D18" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G18" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -3402,16 +3831,16 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>406</v>
+        <v>439</v>
       </c>
       <c r="C19" t="s">
-        <v>749</v>
+        <v>826</v>
       </c>
       <c r="D19" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G19" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -3419,16 +3848,16 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="C20" t="s">
-        <v>749</v>
+        <v>826</v>
       </c>
       <c r="D20" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G20" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3436,16 +3865,16 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>408</v>
+        <v>441</v>
       </c>
       <c r="C21" t="s">
-        <v>749</v>
+        <v>826</v>
       </c>
       <c r="D21" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G21" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3453,16 +3882,16 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>409</v>
+        <v>442</v>
       </c>
       <c r="C22" t="s">
-        <v>749</v>
+        <v>826</v>
       </c>
       <c r="D22" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G22" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3470,16 +3899,16 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>410</v>
+        <v>443</v>
       </c>
       <c r="C23" t="s">
-        <v>749</v>
+        <v>826</v>
       </c>
       <c r="D23" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G23" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3487,16 +3916,16 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>411</v>
+        <v>444</v>
       </c>
       <c r="C24" t="s">
-        <v>749</v>
+        <v>826</v>
       </c>
       <c r="D24" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G24" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3504,16 +3933,16 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>412</v>
+        <v>445</v>
       </c>
       <c r="C25" t="s">
-        <v>749</v>
+        <v>826</v>
       </c>
       <c r="D25" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G25" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3521,16 +3950,16 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>413</v>
+        <v>446</v>
       </c>
       <c r="C26" t="s">
-        <v>750</v>
+        <v>827</v>
       </c>
       <c r="D26" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G26" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3538,16 +3967,16 @@
         <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>414</v>
+        <v>447</v>
       </c>
       <c r="C27" t="s">
-        <v>750</v>
+        <v>827</v>
       </c>
       <c r="D27" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G27" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -3555,16 +3984,16 @@
         <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>415</v>
+        <v>448</v>
       </c>
       <c r="C28" t="s">
-        <v>750</v>
+        <v>827</v>
       </c>
       <c r="D28" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G28" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3572,16 +4001,16 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>416</v>
+        <v>449</v>
       </c>
       <c r="C29" t="s">
-        <v>750</v>
+        <v>827</v>
       </c>
       <c r="D29" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G29" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -3589,16 +4018,16 @@
         <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>417</v>
+        <v>450</v>
       </c>
       <c r="C30" t="s">
-        <v>750</v>
+        <v>827</v>
       </c>
       <c r="D30" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G30" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3606,16 +4035,16 @@
         <v>41</v>
       </c>
       <c r="B31" t="s">
-        <v>418</v>
+        <v>451</v>
       </c>
       <c r="C31" t="s">
-        <v>750</v>
+        <v>827</v>
       </c>
       <c r="D31" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G31" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3623,16 +4052,16 @@
         <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>419</v>
+        <v>452</v>
       </c>
       <c r="C32" t="s">
-        <v>750</v>
+        <v>827</v>
       </c>
       <c r="D32" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G32" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3640,16 +4069,16 @@
         <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>420</v>
+        <v>453</v>
       </c>
       <c r="C33" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D33" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G33" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -3657,16 +4086,16 @@
         <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>421</v>
+        <v>454</v>
       </c>
       <c r="C34" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D34" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G34" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -3674,16 +4103,16 @@
         <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>422</v>
+        <v>455</v>
       </c>
       <c r="C35" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D35" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G35" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3691,16 +4120,16 @@
         <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>423</v>
+        <v>456</v>
       </c>
       <c r="C36" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D36" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G36" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -3708,16 +4137,16 @@
         <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>424</v>
+        <v>457</v>
       </c>
       <c r="C37" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D37" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G37" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -3725,16 +4154,16 @@
         <v>48</v>
       </c>
       <c r="B38" t="s">
-        <v>425</v>
+        <v>458</v>
       </c>
       <c r="C38" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D38" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G38" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -3742,16 +4171,16 @@
         <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>426</v>
+        <v>459</v>
       </c>
       <c r="C39" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D39" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G39" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3759,16 +4188,16 @@
         <v>50</v>
       </c>
       <c r="B40" t="s">
-        <v>427</v>
+        <v>460</v>
       </c>
       <c r="C40" t="s">
-        <v>752</v>
+        <v>829</v>
       </c>
       <c r="D40" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G40" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -3776,16 +4205,16 @@
         <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>428</v>
+        <v>461</v>
       </c>
       <c r="C41" t="s">
-        <v>752</v>
+        <v>829</v>
       </c>
       <c r="D41" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G41" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3793,16 +4222,16 @@
         <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>429</v>
+        <v>462</v>
       </c>
       <c r="C42" t="s">
-        <v>752</v>
+        <v>829</v>
       </c>
       <c r="D42" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G42" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3810,16 +4239,16 @@
         <v>53</v>
       </c>
       <c r="B43" t="s">
-        <v>430</v>
+        <v>463</v>
       </c>
       <c r="C43" t="s">
-        <v>752</v>
+        <v>829</v>
       </c>
       <c r="D43" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G43" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3827,16 +4256,16 @@
         <v>54</v>
       </c>
       <c r="B44" t="s">
-        <v>431</v>
+        <v>464</v>
       </c>
       <c r="C44" t="s">
-        <v>752</v>
+        <v>829</v>
       </c>
       <c r="D44" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G44" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3844,16 +4273,16 @@
         <v>55</v>
       </c>
       <c r="B45" t="s">
-        <v>432</v>
+        <v>465</v>
       </c>
       <c r="C45" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D45" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G45" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3861,16 +4290,16 @@
         <v>56</v>
       </c>
       <c r="B46" t="s">
-        <v>433</v>
+        <v>466</v>
       </c>
       <c r="C46" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D46" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G46" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3878,16 +4307,16 @@
         <v>57</v>
       </c>
       <c r="B47" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="C47" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D47" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G47" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3895,16 +4324,16 @@
         <v>58</v>
       </c>
       <c r="B48" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C48" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D48" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G48" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -3912,16 +4341,16 @@
         <v>59</v>
       </c>
       <c r="B49" t="s">
-        <v>436</v>
+        <v>469</v>
       </c>
       <c r="C49" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D49" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G49" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -3929,16 +4358,16 @@
         <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>437</v>
+        <v>470</v>
       </c>
       <c r="C50" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D50" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G50" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -3946,16 +4375,16 @@
         <v>61</v>
       </c>
       <c r="B51" t="s">
-        <v>438</v>
+        <v>471</v>
       </c>
       <c r="C51" t="s">
-        <v>745</v>
+        <v>822</v>
       </c>
       <c r="D51" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G51" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -3963,16 +4392,16 @@
         <v>62</v>
       </c>
       <c r="B52" t="s">
-        <v>439</v>
+        <v>472</v>
       </c>
       <c r="C52" t="s">
-        <v>745</v>
+        <v>822</v>
       </c>
       <c r="D52" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G52" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -3980,16 +4409,16 @@
         <v>63</v>
       </c>
       <c r="B53" t="s">
-        <v>440</v>
+        <v>473</v>
       </c>
       <c r="C53" t="s">
-        <v>745</v>
+        <v>822</v>
       </c>
       <c r="D53" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G53" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3997,16 +4426,16 @@
         <v>64</v>
       </c>
       <c r="B54" t="s">
-        <v>441</v>
+        <v>474</v>
       </c>
       <c r="C54" t="s">
-        <v>745</v>
+        <v>822</v>
       </c>
       <c r="D54" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G54" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -4014,16 +4443,16 @@
         <v>65</v>
       </c>
       <c r="B55" t="s">
-        <v>442</v>
+        <v>475</v>
       </c>
       <c r="C55" t="s">
-        <v>753</v>
+        <v>830</v>
       </c>
       <c r="D55" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G55" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -4031,16 +4460,16 @@
         <v>66</v>
       </c>
       <c r="B56" t="s">
-        <v>443</v>
+        <v>476</v>
       </c>
       <c r="C56" t="s">
-        <v>753</v>
+        <v>830</v>
       </c>
       <c r="D56" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G56" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -4048,16 +4477,16 @@
         <v>67</v>
       </c>
       <c r="B57" t="s">
-        <v>444</v>
+        <v>477</v>
       </c>
       <c r="C57" t="s">
-        <v>753</v>
+        <v>830</v>
       </c>
       <c r="D57" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G57" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -4065,16 +4494,16 @@
         <v>68</v>
       </c>
       <c r="B58" t="s">
-        <v>445</v>
+        <v>478</v>
       </c>
       <c r="C58" t="s">
-        <v>754</v>
+        <v>831</v>
       </c>
       <c r="D58" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G58" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -4082,16 +4511,16 @@
         <v>69</v>
       </c>
       <c r="B59" t="s">
-        <v>446</v>
+        <v>479</v>
       </c>
       <c r="C59" t="s">
-        <v>754</v>
+        <v>831</v>
       </c>
       <c r="D59" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G59" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -4099,16 +4528,16 @@
         <v>70</v>
       </c>
       <c r="B60" t="s">
-        <v>447</v>
+        <v>480</v>
       </c>
       <c r="C60" t="s">
-        <v>754</v>
+        <v>831</v>
       </c>
       <c r="D60" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G60" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -4116,16 +4545,16 @@
         <v>71</v>
       </c>
       <c r="B61" t="s">
-        <v>448</v>
+        <v>481</v>
       </c>
       <c r="C61" t="s">
-        <v>749</v>
+        <v>826</v>
       </c>
       <c r="D61" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G61" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -4133,16 +4562,16 @@
         <v>72</v>
       </c>
       <c r="B62" t="s">
-        <v>449</v>
+        <v>482</v>
       </c>
       <c r="C62" t="s">
-        <v>749</v>
+        <v>826</v>
       </c>
       <c r="D62" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G62" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -4150,16 +4579,16 @@
         <v>73</v>
       </c>
       <c r="B63" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="C63" t="s">
-        <v>749</v>
+        <v>826</v>
       </c>
       <c r="D63" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G63" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -4167,16 +4596,16 @@
         <v>74</v>
       </c>
       <c r="B64" t="s">
-        <v>451</v>
+        <v>484</v>
       </c>
       <c r="C64" t="s">
-        <v>749</v>
+        <v>826</v>
       </c>
       <c r="D64" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G64" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -4184,16 +4613,16 @@
         <v>75</v>
       </c>
       <c r="B65" t="s">
-        <v>452</v>
+        <v>485</v>
       </c>
       <c r="C65" t="s">
-        <v>749</v>
+        <v>826</v>
       </c>
       <c r="D65" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G65" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -4201,16 +4630,16 @@
         <v>76</v>
       </c>
       <c r="B66" t="s">
-        <v>453</v>
+        <v>486</v>
       </c>
       <c r="C66" t="s">
-        <v>749</v>
+        <v>826</v>
       </c>
       <c r="D66" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G66" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -4218,16 +4647,16 @@
         <v>77</v>
       </c>
       <c r="B67" t="s">
-        <v>454</v>
+        <v>487</v>
       </c>
       <c r="C67" t="s">
-        <v>749</v>
+        <v>826</v>
       </c>
       <c r="D67" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G67" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -4235,16 +4664,16 @@
         <v>78</v>
       </c>
       <c r="B68" t="s">
-        <v>455</v>
+        <v>488</v>
       </c>
       <c r="C68" t="s">
-        <v>749</v>
+        <v>826</v>
       </c>
       <c r="D68" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G68" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -4252,16 +4681,16 @@
         <v>79</v>
       </c>
       <c r="B69" t="s">
-        <v>456</v>
+        <v>489</v>
       </c>
       <c r="C69" t="s">
-        <v>750</v>
+        <v>827</v>
       </c>
       <c r="D69" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G69" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4269,16 +4698,16 @@
         <v>80</v>
       </c>
       <c r="B70" t="s">
-        <v>457</v>
+        <v>490</v>
       </c>
       <c r="C70" t="s">
-        <v>750</v>
+        <v>827</v>
       </c>
       <c r="D70" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G70" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -4286,16 +4715,16 @@
         <v>81</v>
       </c>
       <c r="B71" t="s">
-        <v>458</v>
+        <v>491</v>
       </c>
       <c r="C71" t="s">
-        <v>750</v>
+        <v>827</v>
       </c>
       <c r="D71" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G71" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -4303,16 +4732,16 @@
         <v>82</v>
       </c>
       <c r="B72" t="s">
-        <v>459</v>
+        <v>492</v>
       </c>
       <c r="C72" t="s">
-        <v>750</v>
+        <v>827</v>
       </c>
       <c r="D72" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G72" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -4320,16 +4749,16 @@
         <v>83</v>
       </c>
       <c r="B73" t="s">
-        <v>460</v>
+        <v>493</v>
       </c>
       <c r="C73" t="s">
-        <v>750</v>
+        <v>827</v>
       </c>
       <c r="D73" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G73" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -4337,16 +4766,16 @@
         <v>84</v>
       </c>
       <c r="B74" t="s">
-        <v>461</v>
+        <v>494</v>
       </c>
       <c r="C74" t="s">
-        <v>750</v>
+        <v>827</v>
       </c>
       <c r="D74" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G74" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -4354,16 +4783,16 @@
         <v>85</v>
       </c>
       <c r="B75" t="s">
-        <v>462</v>
+        <v>495</v>
       </c>
       <c r="C75" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D75" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G75" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -4371,16 +4800,16 @@
         <v>86</v>
       </c>
       <c r="B76" t="s">
-        <v>463</v>
+        <v>496</v>
       </c>
       <c r="C76" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D76" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G76" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -4388,16 +4817,16 @@
         <v>87</v>
       </c>
       <c r="B77" t="s">
-        <v>464</v>
+        <v>497</v>
       </c>
       <c r="C77" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D77" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G77" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -4405,16 +4834,16 @@
         <v>88</v>
       </c>
       <c r="B78" t="s">
-        <v>465</v>
+        <v>498</v>
       </c>
       <c r="C78" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D78" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G78" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -4422,16 +4851,16 @@
         <v>89</v>
       </c>
       <c r="B79" t="s">
-        <v>466</v>
+        <v>499</v>
       </c>
       <c r="C79" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D79" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G79" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -4439,16 +4868,16 @@
         <v>90</v>
       </c>
       <c r="B80" t="s">
-        <v>467</v>
+        <v>500</v>
       </c>
       <c r="C80" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D80" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G80" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -4456,16 +4885,16 @@
         <v>91</v>
       </c>
       <c r="B81" t="s">
-        <v>468</v>
+        <v>501</v>
       </c>
       <c r="C81" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D81" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G81" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -4473,16 +4902,16 @@
         <v>92</v>
       </c>
       <c r="B82" t="s">
-        <v>469</v>
+        <v>502</v>
       </c>
       <c r="C82" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D82" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G82" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -4490,16 +4919,16 @@
         <v>93</v>
       </c>
       <c r="B83" t="s">
-        <v>470</v>
+        <v>503</v>
       </c>
       <c r="C83" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D83" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G83" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -4507,16 +4936,16 @@
         <v>94</v>
       </c>
       <c r="B84" t="s">
-        <v>471</v>
+        <v>504</v>
       </c>
       <c r="C84" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D84" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G84" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -4524,16 +4953,16 @@
         <v>95</v>
       </c>
       <c r="B85" t="s">
-        <v>472</v>
+        <v>505</v>
       </c>
       <c r="C85" t="s">
-        <v>752</v>
+        <v>829</v>
       </c>
       <c r="D85" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G85" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4541,16 +4970,16 @@
         <v>96</v>
       </c>
       <c r="B86" t="s">
-        <v>473</v>
+        <v>506</v>
       </c>
       <c r="C86" t="s">
-        <v>752</v>
+        <v>829</v>
       </c>
       <c r="D86" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G86" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4558,16 +4987,16 @@
         <v>97</v>
       </c>
       <c r="B87" t="s">
-        <v>474</v>
+        <v>507</v>
       </c>
       <c r="C87" t="s">
-        <v>752</v>
+        <v>829</v>
       </c>
       <c r="D87" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G87" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4575,16 +5004,16 @@
         <v>98</v>
       </c>
       <c r="B88" t="s">
-        <v>475</v>
+        <v>508</v>
       </c>
       <c r="C88" t="s">
-        <v>752</v>
+        <v>829</v>
       </c>
       <c r="D88" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G88" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4592,16 +5021,16 @@
         <v>99</v>
       </c>
       <c r="B89" t="s">
-        <v>476</v>
+        <v>509</v>
       </c>
       <c r="C89" t="s">
-        <v>752</v>
+        <v>829</v>
       </c>
       <c r="D89" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G89" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4609,16 +5038,16 @@
         <v>100</v>
       </c>
       <c r="B90" t="s">
-        <v>477</v>
+        <v>510</v>
       </c>
       <c r="C90" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D90" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G90" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4626,16 +5055,16 @@
         <v>101</v>
       </c>
       <c r="B91" t="s">
-        <v>478</v>
+        <v>511</v>
       </c>
       <c r="C91" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D91" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G91" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4643,16 +5072,16 @@
         <v>102</v>
       </c>
       <c r="B92" t="s">
-        <v>479</v>
+        <v>512</v>
       </c>
       <c r="C92" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D92" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G92" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -4660,16 +5089,16 @@
         <v>103</v>
       </c>
       <c r="B93" t="s">
-        <v>480</v>
+        <v>513</v>
       </c>
       <c r="C93" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D93" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G93" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -4677,16 +5106,16 @@
         <v>104</v>
       </c>
       <c r="B94" t="s">
-        <v>481</v>
+        <v>514</v>
       </c>
       <c r="C94" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D94" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G94" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -4694,16 +5123,16 @@
         <v>105</v>
       </c>
       <c r="B95" t="s">
-        <v>482</v>
+        <v>515</v>
       </c>
       <c r="C95" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D95" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G95" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -4711,16 +5140,16 @@
         <v>106</v>
       </c>
       <c r="B96" t="s">
-        <v>483</v>
+        <v>516</v>
       </c>
       <c r="C96" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D96" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G96" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4728,16 +5157,16 @@
         <v>107</v>
       </c>
       <c r="B97" t="s">
-        <v>484</v>
+        <v>517</v>
       </c>
       <c r="C97" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D97" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G97" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4745,16 +5174,16 @@
         <v>108</v>
       </c>
       <c r="B98" t="s">
-        <v>485</v>
+        <v>518</v>
       </c>
       <c r="C98" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D98" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G98" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4762,16 +5191,16 @@
         <v>109</v>
       </c>
       <c r="B99" t="s">
-        <v>486</v>
+        <v>519</v>
       </c>
       <c r="C99" t="s">
-        <v>745</v>
+        <v>822</v>
       </c>
       <c r="D99" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G99" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4779,16 +5208,16 @@
         <v>110</v>
       </c>
       <c r="B100" t="s">
-        <v>487</v>
+        <v>520</v>
       </c>
       <c r="C100" t="s">
-        <v>745</v>
+        <v>822</v>
       </c>
       <c r="D100" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G100" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4796,16 +5225,16 @@
         <v>111</v>
       </c>
       <c r="B101" t="s">
-        <v>488</v>
+        <v>521</v>
       </c>
       <c r="C101" t="s">
-        <v>745</v>
+        <v>822</v>
       </c>
       <c r="D101" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G101" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4813,16 +5242,16 @@
         <v>112</v>
       </c>
       <c r="B102" t="s">
-        <v>489</v>
+        <v>522</v>
       </c>
       <c r="C102" t="s">
-        <v>745</v>
+        <v>822</v>
       </c>
       <c r="D102" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G102" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4830,16 +5259,16 @@
         <v>113</v>
       </c>
       <c r="B103" t="s">
-        <v>490</v>
+        <v>523</v>
       </c>
       <c r="C103" t="s">
-        <v>745</v>
+        <v>822</v>
       </c>
       <c r="D103" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G103" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4847,16 +5276,16 @@
         <v>114</v>
       </c>
       <c r="B104" t="s">
-        <v>491</v>
+        <v>524</v>
       </c>
       <c r="C104" t="s">
-        <v>745</v>
+        <v>822</v>
       </c>
       <c r="D104" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G104" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4864,16 +5293,16 @@
         <v>115</v>
       </c>
       <c r="B105" t="s">
-        <v>492</v>
+        <v>525</v>
       </c>
       <c r="C105" t="s">
-        <v>745</v>
+        <v>822</v>
       </c>
       <c r="D105" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G105" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4881,16 +5310,16 @@
         <v>116</v>
       </c>
       <c r="B106" t="s">
-        <v>493</v>
+        <v>526</v>
       </c>
       <c r="C106" t="s">
-        <v>745</v>
+        <v>822</v>
       </c>
       <c r="D106" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G106" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4898,16 +5327,16 @@
         <v>117</v>
       </c>
       <c r="B107" t="s">
-        <v>494</v>
+        <v>527</v>
       </c>
       <c r="C107" t="s">
-        <v>753</v>
+        <v>830</v>
       </c>
       <c r="D107" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G107" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4915,16 +5344,16 @@
         <v>118</v>
       </c>
       <c r="B108" t="s">
-        <v>495</v>
+        <v>528</v>
       </c>
       <c r="C108" t="s">
-        <v>753</v>
+        <v>830</v>
       </c>
       <c r="D108" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G108" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4932,16 +5361,16 @@
         <v>119</v>
       </c>
       <c r="B109" t="s">
-        <v>496</v>
+        <v>529</v>
       </c>
       <c r="C109" t="s">
-        <v>754</v>
+        <v>831</v>
       </c>
       <c r="D109" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G109" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4949,16 +5378,16 @@
         <v>120</v>
       </c>
       <c r="B110" t="s">
-        <v>497</v>
+        <v>530</v>
       </c>
       <c r="C110" t="s">
-        <v>754</v>
+        <v>831</v>
       </c>
       <c r="D110" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G110" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4966,16 +5395,16 @@
         <v>121</v>
       </c>
       <c r="B111" t="s">
-        <v>498</v>
+        <v>531</v>
       </c>
       <c r="C111" t="s">
-        <v>754</v>
+        <v>831</v>
       </c>
       <c r="D111" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G111" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4983,16 +5412,16 @@
         <v>122</v>
       </c>
       <c r="B112" t="s">
-        <v>499</v>
+        <v>532</v>
       </c>
       <c r="C112" t="s">
-        <v>754</v>
+        <v>831</v>
       </c>
       <c r="D112" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G112" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -5000,16 +5429,16 @@
         <v>123</v>
       </c>
       <c r="B113" t="s">
-        <v>500</v>
+        <v>533</v>
       </c>
       <c r="C113" t="s">
-        <v>754</v>
+        <v>831</v>
       </c>
       <c r="D113" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G113" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -5017,16 +5446,16 @@
         <v>124</v>
       </c>
       <c r="B114" t="s">
-        <v>501</v>
+        <v>534</v>
       </c>
       <c r="C114" t="s">
-        <v>755</v>
+        <v>832</v>
       </c>
       <c r="D114" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G114" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -5034,16 +5463,16 @@
         <v>125</v>
       </c>
       <c r="B115" t="s">
-        <v>502</v>
+        <v>535</v>
       </c>
       <c r="C115" t="s">
-        <v>755</v>
+        <v>832</v>
       </c>
       <c r="D115" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G115" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -5051,16 +5480,16 @@
         <v>126</v>
       </c>
       <c r="B116" t="s">
-        <v>503</v>
+        <v>536</v>
       </c>
       <c r="C116" t="s">
-        <v>755</v>
+        <v>832</v>
       </c>
       <c r="D116" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G116" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -5068,16 +5497,16 @@
         <v>127</v>
       </c>
       <c r="B117" t="s">
-        <v>504</v>
+        <v>537</v>
       </c>
       <c r="C117" t="s">
-        <v>755</v>
+        <v>832</v>
       </c>
       <c r="D117" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G117" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -5085,16 +5514,16 @@
         <v>128</v>
       </c>
       <c r="B118" t="s">
-        <v>505</v>
+        <v>538</v>
       </c>
       <c r="C118" t="s">
-        <v>755</v>
+        <v>832</v>
       </c>
       <c r="D118" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G118" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -5102,22 +5531,22 @@
         <v>129</v>
       </c>
       <c r="B119" t="s">
-        <v>431</v>
+        <v>464</v>
       </c>
       <c r="C119" t="s">
-        <v>755</v>
+        <v>832</v>
       </c>
       <c r="D119" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E119" t="s">
-        <v>803</v>
+        <v>881</v>
       </c>
       <c r="F119" t="s">
-        <v>857</v>
+        <v>964</v>
       </c>
       <c r="G119" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5125,19 +5554,19 @@
         <v>130</v>
       </c>
       <c r="B120" t="s">
-        <v>506</v>
+        <v>539</v>
       </c>
       <c r="C120" t="s">
-        <v>755</v>
+        <v>832</v>
       </c>
       <c r="D120" t="s">
-        <v>771</v>
+        <v>849</v>
       </c>
       <c r="E120" t="s">
-        <v>804</v>
+        <v>882</v>
       </c>
       <c r="G120" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -5145,16 +5574,16 @@
         <v>131</v>
       </c>
       <c r="B121" t="s">
-        <v>507</v>
+        <v>540</v>
       </c>
       <c r="C121" t="s">
-        <v>755</v>
+        <v>832</v>
       </c>
       <c r="D121" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G121" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -5162,16 +5591,16 @@
         <v>132</v>
       </c>
       <c r="B122" t="s">
-        <v>508</v>
+        <v>541</v>
       </c>
       <c r="C122" t="s">
-        <v>753</v>
+        <v>830</v>
       </c>
       <c r="D122" t="s">
-        <v>772</v>
+        <v>850</v>
       </c>
       <c r="G122" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -5179,22 +5608,22 @@
         <v>133</v>
       </c>
       <c r="B123" t="s">
-        <v>509</v>
+        <v>542</v>
       </c>
       <c r="C123" t="s">
-        <v>753</v>
+        <v>830</v>
       </c>
       <c r="D123" t="s">
-        <v>773</v>
+        <v>851</v>
       </c>
       <c r="E123" t="s">
-        <v>805</v>
+        <v>883</v>
       </c>
       <c r="F123" t="s">
-        <v>858</v>
+        <v>965</v>
       </c>
       <c r="G123" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -5202,16 +5631,16 @@
         <v>134</v>
       </c>
       <c r="B124" t="s">
-        <v>510</v>
+        <v>543</v>
       </c>
       <c r="C124" t="s">
-        <v>753</v>
+        <v>830</v>
       </c>
       <c r="D124" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G124" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -5219,16 +5648,16 @@
         <v>135</v>
       </c>
       <c r="B125" t="s">
-        <v>511</v>
+        <v>544</v>
       </c>
       <c r="C125" t="s">
-        <v>753</v>
+        <v>830</v>
       </c>
       <c r="D125" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G125" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -5236,16 +5665,16 @@
         <v>136</v>
       </c>
       <c r="B126" t="s">
-        <v>512</v>
+        <v>545</v>
       </c>
       <c r="C126" t="s">
-        <v>753</v>
+        <v>830</v>
       </c>
       <c r="D126" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G126" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -5253,16 +5682,16 @@
         <v>137</v>
       </c>
       <c r="B127" t="s">
-        <v>513</v>
+        <v>546</v>
       </c>
       <c r="C127" t="s">
-        <v>753</v>
+        <v>830</v>
       </c>
       <c r="D127" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G127" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -5270,19 +5699,19 @@
         <v>138</v>
       </c>
       <c r="B128" t="s">
-        <v>514</v>
+        <v>547</v>
       </c>
       <c r="C128" t="s">
-        <v>753</v>
+        <v>830</v>
       </c>
       <c r="D128" t="s">
-        <v>774</v>
+        <v>852</v>
       </c>
       <c r="E128" t="s">
-        <v>806</v>
+        <v>884</v>
       </c>
       <c r="G128" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -5290,22 +5719,22 @@
         <v>139</v>
       </c>
       <c r="B129" t="s">
-        <v>515</v>
+        <v>548</v>
       </c>
       <c r="C129" t="s">
-        <v>754</v>
+        <v>831</v>
       </c>
       <c r="D129" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E129" t="s">
-        <v>807</v>
+        <v>885</v>
       </c>
       <c r="F129" t="s">
-        <v>859</v>
+        <v>966</v>
       </c>
       <c r="G129" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5313,16 +5742,16 @@
         <v>140</v>
       </c>
       <c r="B130" t="s">
-        <v>516</v>
+        <v>549</v>
       </c>
       <c r="C130" t="s">
-        <v>754</v>
+        <v>831</v>
       </c>
       <c r="D130" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G130" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -5330,13 +5759,13 @@
         <v>141</v>
       </c>
       <c r="C131" t="s">
-        <v>754</v>
+        <v>831</v>
       </c>
       <c r="D131" t="s">
-        <v>775</v>
+        <v>853</v>
       </c>
       <c r="E131" t="s">
-        <v>808</v>
+        <v>886</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -5344,19 +5773,19 @@
         <v>142</v>
       </c>
       <c r="B132" t="s">
-        <v>517</v>
+        <v>550</v>
       </c>
       <c r="C132" t="s">
-        <v>754</v>
+        <v>831</v>
       </c>
       <c r="D132" t="s">
-        <v>776</v>
+        <v>854</v>
       </c>
       <c r="E132" t="s">
-        <v>809</v>
+        <v>887</v>
       </c>
       <c r="G132" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -5364,19 +5793,19 @@
         <v>143</v>
       </c>
       <c r="B133" t="s">
-        <v>518</v>
+        <v>551</v>
       </c>
       <c r="C133" t="s">
-        <v>754</v>
+        <v>831</v>
       </c>
       <c r="D133" t="s">
-        <v>777</v>
+        <v>855</v>
       </c>
       <c r="E133" t="s">
-        <v>810</v>
+        <v>888</v>
       </c>
       <c r="G133" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -5384,10 +5813,10 @@
         <v>144</v>
       </c>
       <c r="C134" t="s">
-        <v>754</v>
+        <v>831</v>
       </c>
       <c r="D134" t="s">
-        <v>778</v>
+        <v>856</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -5395,10 +5824,10 @@
         <v>145</v>
       </c>
       <c r="C135" t="s">
-        <v>754</v>
+        <v>831</v>
       </c>
       <c r="D135" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -5406,16 +5835,16 @@
         <v>146</v>
       </c>
       <c r="B136" t="s">
-        <v>519</v>
+        <v>552</v>
       </c>
       <c r="C136" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D136" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G136" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -5423,16 +5852,16 @@
         <v>147</v>
       </c>
       <c r="B137" t="s">
-        <v>520</v>
+        <v>553</v>
       </c>
       <c r="C137" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D137" t="s">
-        <v>775</v>
+        <v>853</v>
       </c>
       <c r="G137" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -5440,10 +5869,10 @@
         <v>148</v>
       </c>
       <c r="C138" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D138" t="s">
-        <v>779</v>
+        <v>857</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -5451,10 +5880,10 @@
         <v>149</v>
       </c>
       <c r="C139" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D139" t="s">
-        <v>780</v>
+        <v>858</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -5462,10 +5891,10 @@
         <v>150</v>
       </c>
       <c r="C140" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D140" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -5473,16 +5902,16 @@
         <v>151</v>
       </c>
       <c r="B141" t="s">
-        <v>436</v>
+        <v>469</v>
       </c>
       <c r="C141" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D141" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G141" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -5490,22 +5919,22 @@
         <v>152</v>
       </c>
       <c r="B142" t="s">
-        <v>521</v>
+        <v>554</v>
       </c>
       <c r="C142" t="s">
-        <v>748</v>
+        <v>825</v>
       </c>
       <c r="D142" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E142" t="s">
-        <v>811</v>
+        <v>889</v>
       </c>
       <c r="F142" t="s">
-        <v>860</v>
+        <v>967</v>
       </c>
       <c r="G142" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -5513,16 +5942,16 @@
         <v>153</v>
       </c>
       <c r="B143" t="s">
-        <v>522</v>
+        <v>555</v>
       </c>
       <c r="C143" t="s">
-        <v>745</v>
+        <v>822</v>
       </c>
       <c r="D143" t="s">
-        <v>779</v>
+        <v>857</v>
       </c>
       <c r="G143" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -5530,13 +5959,13 @@
         <v>154</v>
       </c>
       <c r="C144" t="s">
-        <v>745</v>
+        <v>822</v>
       </c>
       <c r="D144" t="s">
-        <v>781</v>
+        <v>859</v>
       </c>
       <c r="E144" t="s">
-        <v>812</v>
+        <v>890</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -5544,10 +5973,10 @@
         <v>155</v>
       </c>
       <c r="C145" t="s">
-        <v>745</v>
+        <v>822</v>
       </c>
       <c r="D145" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -5555,19 +5984,19 @@
         <v>156</v>
       </c>
       <c r="B146" t="s">
-        <v>523</v>
+        <v>556</v>
       </c>
       <c r="C146" t="s">
-        <v>745</v>
+        <v>822</v>
       </c>
       <c r="D146" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="F146" t="s">
-        <v>861</v>
+        <v>968</v>
       </c>
       <c r="G146" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -5575,22 +6004,22 @@
         <v>157</v>
       </c>
       <c r="B147" t="s">
-        <v>524</v>
+        <v>557</v>
       </c>
       <c r="C147" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D147" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E147" t="s">
-        <v>813</v>
+        <v>891</v>
       </c>
       <c r="F147" t="s">
-        <v>862</v>
+        <v>969</v>
       </c>
       <c r="G147" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5598,19 +6027,19 @@
         <v>158</v>
       </c>
       <c r="B148" t="s">
-        <v>525</v>
+        <v>558</v>
       </c>
       <c r="C148" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D148" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E148" t="s">
-        <v>814</v>
+        <v>892</v>
       </c>
       <c r="G148" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5618,19 +6047,19 @@
         <v>159</v>
       </c>
       <c r="B149" t="s">
-        <v>526</v>
+        <v>559</v>
       </c>
       <c r="C149" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D149" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E149" t="s">
-        <v>815</v>
+        <v>893</v>
       </c>
       <c r="G149" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5638,19 +6067,19 @@
         <v>160</v>
       </c>
       <c r="B150" t="s">
-        <v>527</v>
+        <v>560</v>
       </c>
       <c r="C150" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D150" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E150" t="s">
-        <v>816</v>
+        <v>894</v>
       </c>
       <c r="G150" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5658,19 +6087,19 @@
         <v>161</v>
       </c>
       <c r="B151" t="s">
-        <v>528</v>
+        <v>561</v>
       </c>
       <c r="C151" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D151" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E151" t="s">
-        <v>817</v>
+        <v>895</v>
       </c>
       <c r="G151" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5678,19 +6107,19 @@
         <v>162</v>
       </c>
       <c r="B152" t="s">
-        <v>529</v>
+        <v>562</v>
       </c>
       <c r="C152" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D152" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E152" t="s">
-        <v>818</v>
+        <v>896</v>
       </c>
       <c r="G152" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5698,10 +6127,10 @@
         <v>163</v>
       </c>
       <c r="C153" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D153" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5709,19 +6138,19 @@
         <v>164</v>
       </c>
       <c r="B154" t="s">
-        <v>530</v>
+        <v>563</v>
       </c>
       <c r="C154" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D154" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E154" t="s">
-        <v>819</v>
+        <v>897</v>
       </c>
       <c r="G154" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5729,16 +6158,16 @@
         <v>165</v>
       </c>
       <c r="B155" t="s">
-        <v>531</v>
+        <v>564</v>
       </c>
       <c r="C155" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D155" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G155" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5746,16 +6175,16 @@
         <v>166</v>
       </c>
       <c r="B156" t="s">
-        <v>532</v>
+        <v>565</v>
       </c>
       <c r="C156" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D156" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="G156" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5763,22 +6192,22 @@
         <v>167</v>
       </c>
       <c r="B157" t="s">
-        <v>533</v>
+        <v>566</v>
       </c>
       <c r="C157" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D157" t="s">
-        <v>782</v>
+        <v>860</v>
       </c>
       <c r="E157" t="s">
-        <v>820</v>
+        <v>898</v>
       </c>
       <c r="F157" t="s">
-        <v>863</v>
+        <v>970</v>
       </c>
       <c r="G157" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5786,19 +6215,19 @@
         <v>168</v>
       </c>
       <c r="B158" t="s">
-        <v>534</v>
+        <v>567</v>
       </c>
       <c r="C158" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D158" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E158" t="s">
-        <v>821</v>
+        <v>899</v>
       </c>
       <c r="G158" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5806,19 +6235,19 @@
         <v>169</v>
       </c>
       <c r="B159" t="s">
-        <v>535</v>
+        <v>568</v>
       </c>
       <c r="C159" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D159" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E159" t="s">
-        <v>822</v>
+        <v>900</v>
       </c>
       <c r="G159" t="s">
-        <v>874</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5826,19 +6255,19 @@
         <v>170</v>
       </c>
       <c r="B160" t="s">
-        <v>536</v>
+        <v>569</v>
       </c>
       <c r="C160" t="s">
-        <v>751</v>
+        <v>828</v>
       </c>
       <c r="D160" t="s">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="E160